--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="149">
   <si>
     <t>MATRIZ CNPJ: 40.357.820/0001-50R Y DOIS - 58082-025
  ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
@@ -302,6 +302,18 @@
     <t>157 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 2 UND</t>
   </si>
   <si>
+    <t>CAMPO - 25 X 28 C/05</t>
+  </si>
+  <si>
+    <t>S&amp;J DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1588 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND </t>
+  </si>
+  <si>
     <t>CAMPO - 45 X 50</t>
   </si>
   <si>
@@ -311,18 +323,18 @@
     <t>680</t>
   </si>
   <si>
+    <t>1586 - CAMPO OPERATORIO NAO ESTERIL 45X50 - PCT 50</t>
+  </si>
+  <si>
+    <t>MED &amp; FARMA DISTRIBUIDORA DE MEDICAMENTOS E PRODUTOS</t>
+  </si>
+  <si>
+    <t>655</t>
+  </si>
+  <si>
     <t>155 - CAMPO OPERATORIO NAO ESTERIL 45X50 - PCT 50 UND</t>
   </si>
   <si>
-    <t>1586 - CAMPO OPERATORIO NAO ESTERIL 45X50 - PCT 50</t>
-  </si>
-  <si>
-    <t>MED &amp; FARMA DISTRIBUIDORA DE MEDICAMENTOS E PRODUTOS</t>
-  </si>
-  <si>
-    <t>655</t>
-  </si>
-  <si>
     <t>METTA FARMA DISTRIBUIDORA</t>
   </si>
   <si>
@@ -431,7 +443,7 @@
     <t>PCT NÃO EST. - 11 FIOS</t>
   </si>
   <si>
-    <t>314 - GAZE NAO ESTÉRIL 11 FIOS H</t>
+    <t xml:space="preserve">313 - GAZE NAO ESTÉRIL 11 FIOS </t>
   </si>
   <si>
     <t>339 - GAZE NAO ESTÉRIL 11 FIOS BA - PCT 500 UND</t>
@@ -605,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L237"/>
+  <dimension ref="A1:L242"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
   <cols>
     <col customWidth="1" width="89.23828125" min="1" max="1"/>
@@ -3586,16 +3598,16 @@
         <v>99</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>300</v>
+        <v>1400</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>46</v>
+        <v>4.8</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>13800</v>
+        <v>6720</v>
       </c>
       <c r="G123" s="8">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="H123" s="6" t="n">
         <v>0</v>
@@ -3604,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="J123" s="6" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
     </row>
     <row r="124" customHeight="1" ht="15" spans="1:5">
@@ -3615,277 +3627,277 @@
         <v>19</v>
       </c>
       <c r="C124" s="11" t="n">
+        <v>6720</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E124" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A125" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" ht="15" spans="1:12">
+      <c r="A126" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L126" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" ht="15" spans="1:1">
+      <c r="A127" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" ht="15" spans="1:10">
+      <c r="A128" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D128" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="E128" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="F128" s="7" t="n">
         <v>13800</v>
       </c>
-      <c r="D124" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E124" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" customHeight="1" ht="15" spans="1:1">
-      <c r="A125" s="2" t="s">
+      <c r="G128" s="8">
+        <v>46112</v>
+      </c>
+      <c r="H128" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" ht="15" spans="1:5">
+      <c r="A129" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B129" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C129" s="11" t="n">
+        <v>13800</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E129" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" ht="15" spans="1:1">
+      <c r="A130" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="126" customHeight="1" ht="15" spans="1:10">
-      <c r="A126" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B126" s="5" t="s">
+    <row r="131" customHeight="1" ht="15" spans="1:10">
+      <c r="A131" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B131" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C126" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D126" s="6" t="n">
+      <c r="C131" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D131" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E126" s="7" t="n">
+      <c r="E131" s="7" t="n">
         <v>55.09</v>
       </c>
-      <c r="F126" s="7" t="n">
+      <c r="F131" s="7" t="n">
         <v>3305.4</v>
       </c>
-      <c r="G126" s="8">
+      <c r="G131" s="8">
         <v>46107</v>
       </c>
-      <c r="H126" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="6" t="s">
+      <c r="H131" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="127" customHeight="1" ht="15" spans="1:5">
-      <c r="A127" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B127" s="10" t="s">
+    <row r="132" customHeight="1" ht="15" spans="1:5">
+      <c r="A132" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B132" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C127" s="11" t="n">
+      <c r="C132" s="11" t="n">
         <v>3305.4</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E127" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" customHeight="1" ht="15" spans="1:1">
-      <c r="A128" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="129" customHeight="1" ht="15" spans="1:10">
-      <c r="A129" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D129" s="6" t="n">
+      <c r="D132" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E132" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" ht="15" spans="1:1">
+      <c r="A133" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" ht="15" spans="1:10">
+      <c r="A134" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D134" s="6" t="n">
         <v>1008</v>
       </c>
-      <c r="E129" s="7" t="n">
+      <c r="E134" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="F129" s="7" t="n">
+      <c r="F134" s="7" t="n">
         <v>41328</v>
       </c>
-      <c r="G129" s="8">
+      <c r="G134" s="8">
         <v>46104</v>
       </c>
-      <c r="H129" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="6" t="s">
+      <c r="H134" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="130" customHeight="1" ht="15" spans="1:5">
-      <c r="A130" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B130" s="10" t="s">
+    <row r="135" customHeight="1" ht="15" spans="1:5">
+      <c r="A135" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B135" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C130" s="11" t="n">
+      <c r="C135" s="11" t="n">
         <v>41328</v>
       </c>
-      <c r="D130" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E130" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" customHeight="1" ht="15" spans="1:1">
-      <c r="A131" s="2" t="s">
+      <c r="D135" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E135" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" ht="15" spans="1:1">
+      <c r="A136" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" ht="15" spans="1:10">
+      <c r="A137" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C137" s="5" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="132" customHeight="1" ht="15" spans="1:10">
-      <c r="A132" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D132" s="6" t="n">
+      <c r="D137" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="E132" s="7" t="n">
+      <c r="E137" s="7" t="n">
         <v>51.98</v>
       </c>
-      <c r="F132" s="7" t="n">
+      <c r="F137" s="7" t="n">
         <v>12475.2</v>
       </c>
-      <c r="G132" s="8">
+      <c r="G137" s="8">
         <v>46101</v>
       </c>
-      <c r="H132" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="6" t="s">
+      <c r="H137" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="133" customHeight="1" ht="15" spans="1:5">
-      <c r="A133" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B133" s="10" t="s">
+    <row r="138" customHeight="1" ht="15" spans="1:5">
+      <c r="A138" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B138" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C133" s="11" t="n">
+      <c r="C138" s="11" t="n">
         <v>12475.2</v>
       </c>
-      <c r="D133" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E133" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" customHeight="1" ht="15" spans="1:1">
-      <c r="A134" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="135" customHeight="1" ht="15" spans="1:10">
-      <c r="A135" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D135" s="6" t="n">
-        <v>300</v>
-      </c>
-      <c r="E135" s="7" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="F135" s="7" t="n">
-        <v>14850</v>
-      </c>
-      <c r="G135" s="8">
-        <v>46107</v>
-      </c>
-      <c r="H135" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="136" customHeight="1" ht="15" spans="1:5">
-      <c r="A136" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B136" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C136" s="11" t="n">
-        <v>14850</v>
-      </c>
-      <c r="D136" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E136" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A137" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" customHeight="1" ht="15" spans="1:12">
-      <c r="A138" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F138" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G138" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H138" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I138" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J138" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K138" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L138" s="3" t="s">
-        <v>12</v>
+      <c r="D138" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E138" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="139" customHeight="1" ht="15" spans="1:1">
       <c r="A139" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="140" customHeight="1" ht="15" spans="1:10">
@@ -3893,31 +3905,31 @@
         <v>14</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="E140" s="7" t="n">
-        <v>39.89</v>
+        <v>49.5</v>
       </c>
       <c r="F140" s="7" t="n">
-        <v>59835</v>
+        <v>14850</v>
       </c>
       <c r="G140" s="8">
         <v>46107</v>
       </c>
       <c r="H140" s="6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I140" s="9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="J140" s="6" t="s">
-        <v>109</v>
+        <v>50</v>
       </c>
     </row>
     <row r="141" customHeight="1" ht="15" spans="1:5">
@@ -3928,169 +3940,169 @@
         <v>19</v>
       </c>
       <c r="C141" s="11" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E141" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A142" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" ht="15" spans="1:12">
+      <c r="A143" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J143" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L143" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" ht="15" spans="1:1">
+      <c r="A144" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" ht="15" spans="1:10">
+      <c r="A145" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D145" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E145" s="7" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="F145" s="7" t="n">
         <v>59835</v>
       </c>
-      <c r="D141" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E141" s="12" t="n">
+      <c r="G145" s="8">
+        <v>46107</v>
+      </c>
+      <c r="H145" s="6" t="n">
         <v>24</v>
       </c>
-    </row>
-    <row r="142" customHeight="1" ht="15" spans="1:1">
-      <c r="A142" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="143" customHeight="1" ht="15" spans="1:10">
-      <c r="A143" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D143" s="6" t="n">
+      <c r="I145" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J145" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" ht="15" spans="1:5">
+      <c r="A146" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C146" s="11" t="n">
+        <v>59835</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E146" s="12" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" ht="15" spans="1:1">
+      <c r="A147" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" ht="15" spans="1:10">
+      <c r="A148" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D148" s="6" t="n">
         <v>204</v>
       </c>
-      <c r="E143" s="7" t="n">
+      <c r="E148" s="7" t="n">
         <v>44.8</v>
       </c>
-      <c r="F143" s="7" t="n">
+      <c r="F148" s="7" t="n">
         <v>9139.2</v>
       </c>
-      <c r="G143" s="8">
+      <c r="G148" s="8">
         <v>46113</v>
       </c>
-      <c r="H143" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" s="6" t="s">
+      <c r="H148" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="144" customHeight="1" ht="15" spans="1:5">
-      <c r="A144" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B144" s="10" t="s">
+    <row r="149" customHeight="1" ht="15" spans="1:5">
+      <c r="A149" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B149" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C144" s="11" t="n">
+      <c r="C149" s="11" t="n">
         <v>9139.2</v>
       </c>
-      <c r="D144" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E144" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" customHeight="1" ht="15" spans="1:1">
-      <c r="A145" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="146" customHeight="1" ht="15" spans="1:10">
-      <c r="A146" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D146" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E146" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="F146" s="7" t="n">
-        <v>88000</v>
-      </c>
-      <c r="G146" s="8">
-        <v>46112</v>
-      </c>
-      <c r="H146" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="147" customHeight="1" ht="15" spans="1:5">
-      <c r="A147" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B147" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C147" s="11" t="n">
-        <v>88000</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E147" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A148" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" customHeight="1" ht="15" spans="1:12">
-      <c r="A149" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F149" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G149" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H149" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I149" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J149" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K149" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L149" s="3" t="s">
-        <v>12</v>
+      <c r="D149" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E149" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150" customHeight="1" ht="15" spans="1:1">
       <c r="A150" s="2" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
     </row>
     <row r="151" customHeight="1" ht="15" spans="1:10">
@@ -4098,31 +4110,31 @@
         <v>14</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="E151" s="7" t="n">
-        <v>0.37</v>
+        <v>44</v>
       </c>
       <c r="F151" s="7" t="n">
-        <v>11100</v>
+        <v>88000</v>
       </c>
       <c r="G151" s="8">
-        <v>46113</v>
+        <v>46112</v>
       </c>
       <c r="H151" s="6" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J151" s="6" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
     </row>
     <row r="152" customHeight="1" ht="15" spans="1:5">
@@ -4133,115 +4145,115 @@
         <v>19</v>
       </c>
       <c r="C152" s="11" t="n">
+        <v>88000</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E152" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A153" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" ht="15" spans="1:12">
+      <c r="A154" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J154" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L154" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" ht="15" spans="1:1">
+      <c r="A155" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" ht="15" spans="1:10">
+      <c r="A156" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D156" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E156" s="7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F156" s="7" t="n">
         <v>11100</v>
       </c>
-      <c r="D152" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E152" s="12" t="n">
+      <c r="G156" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H156" s="6" t="n">
         <v>9000</v>
       </c>
-    </row>
-    <row r="153" customHeight="1" ht="15" spans="1:1">
-      <c r="A153" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="154" customHeight="1" ht="15" spans="1:10">
-      <c r="A154" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B154" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D154" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E154" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F154" s="7" t="n">
-        <v>19000</v>
-      </c>
-      <c r="G154" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H154" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J154" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="155" customHeight="1" ht="15" spans="1:5">
-      <c r="A155" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B155" s="10" t="s">
+      <c r="I156" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="J156" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" ht="15" spans="1:5">
+      <c r="A157" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B157" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C155" s="11" t="n">
-        <v>19000</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E155" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A156" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" customHeight="1" ht="15" spans="1:12">
-      <c r="A157" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E157" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G157" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H157" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I157" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J157" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K157" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L157" s="3" t="s">
-        <v>12</v>
+      <c r="C157" s="11" t="n">
+        <v>11100</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E157" s="12" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="158" customHeight="1" ht="15" spans="1:1">
       <c r="A158" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="159" customHeight="1" ht="15" spans="1:10">
@@ -4249,19 +4261,19 @@
         <v>14</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D159" s="6" t="n">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="E159" s="7" t="n">
-        <v>0.485</v>
+        <v>0.38</v>
       </c>
       <c r="F159" s="7" t="n">
-        <v>19400</v>
+        <v>19000</v>
       </c>
       <c r="G159" s="8">
         <v>46113</v>
@@ -4273,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="6" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="160" customHeight="1" ht="15" spans="1:5">
@@ -4284,277 +4296,277 @@
         <v>19</v>
       </c>
       <c r="C160" s="11" t="n">
+        <v>19000</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E160" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A161" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" ht="15" spans="1:12">
+      <c r="A162" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J162" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K162" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L162" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" ht="15" spans="1:1">
+      <c r="A163" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" ht="15" spans="1:10">
+      <c r="A164" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D164" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E164" s="7" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="F164" s="7" t="n">
         <v>19400</v>
       </c>
-      <c r="D160" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E160" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" customHeight="1" ht="15" spans="1:1">
-      <c r="A161" s="2" t="s">
+      <c r="G164" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H164" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" ht="15" spans="1:5">
+      <c r="A165" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B165" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C165" s="11" t="n">
+        <v>19400</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E165" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" ht="15" spans="1:1">
+      <c r="A166" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="162" customHeight="1" ht="15" spans="1:10">
-      <c r="A162" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B162" s="5" t="s">
+    <row r="167" customHeight="1" ht="15" spans="1:10">
+      <c r="A167" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B167" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C162" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D162" s="6" t="n">
+      <c r="C167" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D167" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="E162" s="7" t="n">
+      <c r="E167" s="7" t="n">
         <v>0.41</v>
       </c>
-      <c r="F162" s="7" t="n">
+      <c r="F167" s="7" t="n">
         <v>18450</v>
       </c>
-      <c r="G162" s="8">
+      <c r="G167" s="8">
         <v>46113</v>
       </c>
-      <c r="H162" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" s="6" t="s">
+      <c r="H167" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="163" customHeight="1" ht="15" spans="1:5">
-      <c r="A163" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B163" s="10" t="s">
+    <row r="168" customHeight="1" ht="15" spans="1:5">
+      <c r="A168" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B168" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C163" s="11" t="n">
+      <c r="C168" s="11" t="n">
         <v>18450</v>
       </c>
-      <c r="D163" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E163" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" customHeight="1" ht="15" spans="1:1">
-      <c r="A164" s="2" t="s">
+      <c r="D168" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E168" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" ht="15" spans="1:1">
+      <c r="A169" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="165" customHeight="1" ht="15" spans="1:10">
-      <c r="A165" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B165" s="5" t="s">
+    <row r="170" customHeight="1" ht="15" spans="1:10">
+      <c r="A170" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B170" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C165" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D165" s="6" t="n">
+      <c r="C170" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D170" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="E165" s="7" t="n">
+      <c r="E170" s="7" t="n">
         <v>0.38</v>
       </c>
-      <c r="F165" s="7" t="n">
+      <c r="F170" s="7" t="n">
         <v>19000</v>
       </c>
-      <c r="G165" s="8">
+      <c r="G170" s="8">
         <v>46113</v>
       </c>
-      <c r="H165" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I165" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J165" s="6" t="s">
+      <c r="H170" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="166" customHeight="1" ht="15" spans="1:5">
-      <c r="A166" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B166" s="10" t="s">
+    <row r="171" customHeight="1" ht="15" spans="1:5">
+      <c r="A171" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B171" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C166" s="11" t="n">
+      <c r="C171" s="11" t="n">
         <v>19000</v>
       </c>
-      <c r="D166" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E166" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" customHeight="1" ht="15" spans="1:1">
-      <c r="A167" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="168" customHeight="1" ht="15" spans="1:10">
-      <c r="A168" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B168" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D168" s="6" t="n">
+      <c r="D171" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E171" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" ht="15" spans="1:1">
+      <c r="A172" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" ht="15" spans="1:10">
+      <c r="A173" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D173" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="E168" s="7" t="n">
+      <c r="E173" s="7" t="n">
         <v>0.4</v>
       </c>
-      <c r="F168" s="7" t="n">
+      <c r="F173" s="7" t="n">
         <v>20000</v>
       </c>
-      <c r="G168" s="8">
+      <c r="G173" s="8">
         <v>46113</v>
       </c>
-      <c r="H168" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I168" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" s="6" t="s">
+      <c r="H173" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="169" customHeight="1" ht="15" spans="1:5">
-      <c r="A169" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B169" s="10" t="s">
+    <row r="174" customHeight="1" ht="15" spans="1:5">
+      <c r="A174" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B174" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C169" s="11" t="n">
+      <c r="C174" s="11" t="n">
         <v>20000</v>
       </c>
-      <c r="D169" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E169" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" customHeight="1" ht="15" spans="1:1">
-      <c r="A170" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="171" customHeight="1" ht="15" spans="1:10">
-      <c r="A171" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C171" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D171" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E171" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F171" s="7" t="n">
-        <v>7600</v>
-      </c>
-      <c r="G171" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H171" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I171" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J171" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="172" customHeight="1" ht="15" spans="1:5">
-      <c r="A172" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B172" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C172" s="11" t="n">
-        <v>7600</v>
-      </c>
-      <c r="D172" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E172" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A173" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" customHeight="1" ht="15" spans="1:12">
-      <c r="A174" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E174" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F174" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G174" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H174" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I174" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J174" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K174" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L174" s="3" t="s">
-        <v>12</v>
+      <c r="D174" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E174" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="175" customHeight="1" ht="15" spans="1:1">
       <c r="A175" s="2" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="176" customHeight="1" ht="15" spans="1:10">
@@ -4562,22 +4574,22 @@
         <v>14</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D176" s="6" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E176" s="7" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="F176" s="7" t="n">
-        <v>4000</v>
+        <v>7600</v>
       </c>
       <c r="G176" s="8">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="H176" s="6" t="n">
         <v>0</v>
@@ -4586,7 +4598,7 @@
         <v>0</v>
       </c>
       <c r="J176" s="6" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
     </row>
     <row r="177" customHeight="1" ht="15" spans="1:5">
@@ -4597,7 +4609,7 @@
         <v>19</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>4000</v>
+        <v>7600</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>18</v>
@@ -4616,7 +4628,7 @@
         <v>1</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>3</v>
@@ -4651,7 +4663,7 @@
     </row>
     <row r="180" customHeight="1" ht="15" spans="1:1">
       <c r="A180" s="2" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
     </row>
     <row r="181" customHeight="1" ht="15" spans="1:10">
@@ -4659,117 +4671,96 @@
         <v>14</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D181" s="6" t="n">
-        <v>358000</v>
+        <v>10000</v>
       </c>
       <c r="E181" s="7" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="F181" s="7" t="n">
-        <v>136040</v>
+        <v>4000</v>
       </c>
       <c r="G181" s="8">
-        <v>46092</v>
+        <v>46107</v>
       </c>
       <c r="H181" s="6" t="n">
-        <v>303000</v>
+        <v>0</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>84.64</v>
+        <v>0</v>
       </c>
       <c r="J181" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="182" customHeight="1" ht="15" spans="1:10">
-      <c r="A182" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D182" s="6" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E182" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F182" s="7" t="n">
-        <v>30400</v>
-      </c>
-      <c r="G182" s="8">
-        <v>46097</v>
-      </c>
-      <c r="H182" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I182" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J182" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="183" customHeight="1" ht="15" spans="1:10">
-      <c r="A183" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D183" s="6" t="n">
-        <v>500000</v>
-      </c>
-      <c r="E183" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F183" s="7" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G183" s="8">
-        <v>46101</v>
-      </c>
-      <c r="H183" s="6" t="n">
-        <v>435000</v>
-      </c>
-      <c r="I183" s="9" t="n">
-        <v>87</v>
-      </c>
-      <c r="J183" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="184" customHeight="1" ht="15" spans="1:5">
-      <c r="A184" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B184" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" ht="15" spans="1:5">
+      <c r="A182" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B182" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C184" s="11" t="n">
-        <v>356440</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E184" s="12" t="n">
-        <v>738000</v>
+      <c r="C182" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E182" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A183" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" ht="15" spans="1:12">
+      <c r="A184" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H184" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I184" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J184" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K184" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L184" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="185" customHeight="1" ht="15" spans="1:1">
       <c r="A185" s="2" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="186" customHeight="1" ht="15" spans="1:10">
@@ -4777,204 +4768,225 @@
         <v>14</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D186" s="6" t="n">
+        <v>358000</v>
+      </c>
+      <c r="E186" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F186" s="7" t="n">
+        <v>136040</v>
+      </c>
+      <c r="G186" s="8">
+        <v>46092</v>
+      </c>
+      <c r="H186" s="6" t="n">
+        <v>303000</v>
+      </c>
+      <c r="I186" s="9" t="n">
+        <v>84.64</v>
+      </c>
+      <c r="J186" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" ht="15" spans="1:10">
+      <c r="A187" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D187" s="6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E187" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F187" s="7" t="n">
+        <v>30400</v>
+      </c>
+      <c r="G187" s="8">
+        <v>46097</v>
+      </c>
+      <c r="H187" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" ht="15" spans="1:10">
+      <c r="A188" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D188" s="6" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E188" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F188" s="7" t="n">
+        <v>190000</v>
+      </c>
+      <c r="G188" s="8">
+        <v>46101</v>
+      </c>
+      <c r="H188" s="6" t="n">
+        <v>435000</v>
+      </c>
+      <c r="I188" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="J188" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" ht="15" spans="1:5">
+      <c r="A189" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B189" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C189" s="11" t="n">
+        <v>356440</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E189" s="12" t="n">
+        <v>738000</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" ht="15" spans="1:1">
+      <c r="A190" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" ht="15" spans="1:10">
+      <c r="A191" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D191" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="E186" s="7" t="n">
+      <c r="E191" s="7" t="n">
         <v>0.33</v>
       </c>
-      <c r="F186" s="7" t="n">
+      <c r="F191" s="7" t="n">
         <v>9900</v>
       </c>
-      <c r="G186" s="8">
+      <c r="G191" s="8">
         <v>46114</v>
       </c>
-      <c r="H186" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I186" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J186" s="6" t="s">
+      <c r="H191" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="187" customHeight="1" ht="15" spans="1:5">
-      <c r="A187" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B187" s="10" t="s">
+    <row r="192" customHeight="1" ht="15" spans="1:5">
+      <c r="A192" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B192" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C187" s="11" t="n">
+      <c r="C192" s="11" t="n">
         <v>9900</v>
       </c>
-      <c r="D187" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E187" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" customHeight="1" ht="15" spans="1:1">
-      <c r="A188" s="2" t="s">
+      <c r="D192" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E192" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" ht="15" spans="1:1">
+      <c r="A193" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="194" customHeight="1" ht="15" spans="1:10">
+      <c r="A194" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C194" s="5" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="189" customHeight="1" ht="15" spans="1:10">
-      <c r="A189" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D189" s="6" t="n">
+      <c r="D194" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="E189" s="7" t="n">
+      <c r="E194" s="7" t="n">
         <v>0.42</v>
       </c>
-      <c r="F189" s="7" t="n">
+      <c r="F194" s="7" t="n">
         <v>8400</v>
       </c>
-      <c r="G189" s="8">
+      <c r="G194" s="8">
         <v>46111</v>
       </c>
-      <c r="H189" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I189" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J189" s="6" t="s">
+      <c r="H194" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="190" customHeight="1" ht="15" spans="1:5">
-      <c r="A190" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B190" s="10" t="s">
+    <row r="195" customHeight="1" ht="15" spans="1:5">
+      <c r="A195" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B195" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C190" s="11" t="n">
+      <c r="C195" s="11" t="n">
         <v>8400</v>
       </c>
-      <c r="D190" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E190" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" customHeight="1" ht="15" spans="1:1">
-      <c r="A191" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="192" customHeight="1" ht="15" spans="1:10">
-      <c r="A192" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B192" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C192" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D192" s="6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E192" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F192" s="7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G192" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H192" s="6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I192" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="J192" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="193" customHeight="1" ht="15" spans="1:5">
-      <c r="A193" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B193" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C193" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D193" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E193" s="12" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="194" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A194" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" customHeight="1" ht="15" spans="1:12">
-      <c r="A195" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E195" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F195" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G195" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H195" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I195" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J195" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K195" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L195" s="3" t="s">
-        <v>12</v>
+      <c r="D195" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E195" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="196" customHeight="1" ht="15" spans="1:1">
       <c r="A196" s="2" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
     </row>
     <row r="197" customHeight="1" ht="15" spans="1:10">
@@ -4982,31 +4994,31 @@
         <v>14</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D197" s="6" t="n">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="E197" s="7" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="F197" s="7" t="n">
-        <v>21000</v>
+        <v>2000</v>
       </c>
       <c r="G197" s="8">
         <v>46113</v>
       </c>
       <c r="H197" s="6" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="I197" s="9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J197" s="6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="198" customHeight="1" ht="15" spans="1:5">
@@ -5017,115 +5029,115 @@
         <v>19</v>
       </c>
       <c r="C198" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E198" s="12" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="199" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A199" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" customHeight="1" ht="15" spans="1:12">
+      <c r="A200" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H200" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I200" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J200" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K200" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L200" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" ht="15" spans="1:1">
+      <c r="A201" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" ht="15" spans="1:10">
+      <c r="A202" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D202" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E202" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F202" s="7" t="n">
         <v>21000</v>
       </c>
-      <c r="D198" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E198" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" customHeight="1" ht="15" spans="1:1">
-      <c r="A199" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="200" customHeight="1" ht="15" spans="1:10">
-      <c r="A200" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B200" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D200" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E200" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F200" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G200" s="8">
+      <c r="G202" s="8">
         <v>46113</v>
       </c>
-      <c r="H200" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I200" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J200" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="201" customHeight="1" ht="15" spans="1:5">
-      <c r="A201" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B201" s="10" t="s">
+      <c r="H202" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" ht="15" spans="1:5">
+      <c r="A203" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B203" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C201" s="11" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D201" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E201" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A202" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" customHeight="1" ht="15" spans="1:12">
-      <c r="A203" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E203" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F203" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G203" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H203" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I203" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J203" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K203" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L203" s="3" t="s">
-        <v>12</v>
+      <c r="C203" s="11" t="n">
+        <v>21000</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E203" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="204" customHeight="1" ht="15" spans="1:1">
       <c r="A204" s="2" t="s">
-        <v>38</v>
+        <v>114</v>
       </c>
     </row>
     <row r="205" customHeight="1" ht="15" spans="1:10">
@@ -5133,19 +5145,19 @@
         <v>14</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>3024</v>
+        <v>20000</v>
       </c>
       <c r="E205" s="7" t="n">
-        <v>14.5</v>
+        <v>0.4</v>
       </c>
       <c r="F205" s="7" t="n">
-        <v>43848</v>
+        <v>8000</v>
       </c>
       <c r="G205" s="8">
         <v>46113</v>
@@ -5157,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="J205" s="6" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
     </row>
     <row r="206" customHeight="1" ht="15" spans="1:5">
@@ -5168,115 +5180,115 @@
         <v>19</v>
       </c>
       <c r="C206" s="11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E206" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A207" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" ht="15" spans="1:12">
+      <c r="A208" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H208" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I208" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J208" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K208" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L208" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" ht="15" spans="1:1">
+      <c r="A209" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" ht="15" spans="1:10">
+      <c r="A210" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D210" s="6" t="n">
+        <v>3024</v>
+      </c>
+      <c r="E210" s="7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F210" s="7" t="n">
         <v>43848</v>
       </c>
-      <c r="D206" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E206" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207" customHeight="1" ht="15" spans="1:1">
-      <c r="A207" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="208" customHeight="1" ht="15" spans="1:10">
-      <c r="A208" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B208" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D208" s="6" t="n">
-        <v>1224</v>
-      </c>
-      <c r="E208" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="F208" s="7" t="n">
-        <v>11016</v>
-      </c>
-      <c r="G208" s="8">
-        <v>46114</v>
-      </c>
-      <c r="H208" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I208" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J208" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="209" customHeight="1" ht="15" spans="1:5">
-      <c r="A209" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B209" s="10" t="s">
+      <c r="G210" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H210" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="211" customHeight="1" ht="15" spans="1:5">
+      <c r="A211" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B211" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C209" s="11" t="n">
-        <v>11016</v>
-      </c>
-      <c r="D209" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E209" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A210" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211" customHeight="1" ht="15" spans="1:12">
-      <c r="A211" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E211" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F211" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G211" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H211" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I211" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J211" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K211" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L211" s="3" t="s">
-        <v>12</v>
+      <c r="C211" s="11" t="n">
+        <v>43848</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E211" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="212" customHeight="1" ht="15" spans="1:1">
       <c r="A212" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="213" customHeight="1" ht="15" spans="1:10">
@@ -5284,22 +5296,22 @@
         <v>14</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>500</v>
+        <v>1224</v>
       </c>
       <c r="E213" s="7" t="n">
-        <v>36.66</v>
+        <v>9</v>
       </c>
       <c r="F213" s="7" t="n">
-        <v>18330</v>
+        <v>11016</v>
       </c>
       <c r="G213" s="8">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="H213" s="6" t="n">
         <v>0</v>
@@ -5308,7 +5320,7 @@
         <v>0</v>
       </c>
       <c r="J213" s="6" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
     </row>
     <row r="214" customHeight="1" ht="15" spans="1:5">
@@ -5319,147 +5331,147 @@
         <v>19</v>
       </c>
       <c r="C214" s="11" t="n">
+        <v>11016</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E214" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A215" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" customHeight="1" ht="15" spans="1:12">
+      <c r="A216" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H216" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I216" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J216" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K216" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L216" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" ht="15" spans="1:1">
+      <c r="A217" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" ht="15" spans="1:10">
+      <c r="A218" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D218" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="E218" s="7" t="n">
+        <v>36.66</v>
+      </c>
+      <c r="F218" s="7" t="n">
         <v>18330</v>
       </c>
-      <c r="D214" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E214" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" customHeight="1" ht="15" spans="1:1">
-      <c r="A215" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="216" customHeight="1" ht="15" spans="1:10">
-      <c r="A216" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B216" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C216" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D216" s="6" t="n">
+      <c r="G218" s="8">
+        <v>46107</v>
+      </c>
+      <c r="H218" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" ht="15" spans="1:5">
+      <c r="A219" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B219" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C219" s="11" t="n">
+        <v>18330</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E219" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" ht="15" spans="1:1">
+      <c r="A220" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" ht="15" spans="1:10">
+      <c r="A221" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D221" s="6" t="n">
         <v>24000</v>
       </c>
-      <c r="E216" s="7" t="n">
+      <c r="E221" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="F216" s="7" t="n">
+      <c r="F221" s="7" t="n">
         <v>312000</v>
       </c>
-      <c r="G216" s="8">
+      <c r="G221" s="8">
         <v>46100</v>
       </c>
-      <c r="H216" s="6" t="n">
+      <c r="H221" s="6" t="n">
         <v>9000</v>
       </c>
-      <c r="I216" s="9" t="n">
+      <c r="I221" s="9" t="n">
         <v>37.5</v>
       </c>
-      <c r="J216" s="6" t="s">
+      <c r="J221" s="6" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="217" customHeight="1" ht="15" spans="1:10">
-      <c r="A217" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B217" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C217" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D217" s="6" t="n">
-        <v>2010</v>
-      </c>
-      <c r="E217" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="F217" s="7" t="n">
-        <v>26130</v>
-      </c>
-      <c r="G217" s="8">
-        <v>46108</v>
-      </c>
-      <c r="H217" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I217" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J217" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="218" customHeight="1" ht="15" spans="1:5">
-      <c r="A218" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B218" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C218" s="11" t="n">
-        <v>338130</v>
-      </c>
-      <c r="D218" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E218" s="12" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="219" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A219" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" customHeight="1" ht="15" spans="1:12">
-      <c r="A220" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E220" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F220" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G220" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H220" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I220" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J220" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K220" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L220" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="221" customHeight="1" ht="15" spans="1:1">
-      <c r="A221" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="222" customHeight="1" ht="15" spans="1:10">
@@ -5467,22 +5479,22 @@
         <v>14</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D222" s="6" t="n">
-        <v>3000</v>
+        <v>2010</v>
       </c>
       <c r="E222" s="7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F222" s="7" t="n">
-        <v>33000</v>
+        <v>26130</v>
       </c>
       <c r="G222" s="8">
-        <v>46113</v>
+        <v>46108</v>
       </c>
       <c r="H222" s="6" t="n">
         <v>0</v>
@@ -5491,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="J222" s="6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="223" customHeight="1" ht="15" spans="1:5">
@@ -5502,115 +5514,115 @@
         <v>19</v>
       </c>
       <c r="C223" s="11" t="n">
+        <v>338130</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E223" s="12" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="224" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A224" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" customHeight="1" ht="15" spans="1:12">
+      <c r="A225" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H225" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I225" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J225" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K225" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L225" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="226" customHeight="1" ht="15" spans="1:1">
+      <c r="A226" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="227" customHeight="1" ht="15" spans="1:10">
+      <c r="A227" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D227" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E227" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F227" s="7" t="n">
         <v>33000</v>
       </c>
-      <c r="D223" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E223" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" customHeight="1" ht="15" spans="1:1">
-      <c r="A224" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="225" customHeight="1" ht="15" spans="1:10">
-      <c r="A225" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B225" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D225" s="6" t="n">
-        <v>1024</v>
-      </c>
-      <c r="E225" s="7" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="F225" s="7" t="n">
-        <v>16076.8</v>
-      </c>
-      <c r="G225" s="8">
+      <c r="G227" s="8">
         <v>46113</v>
       </c>
-      <c r="H225" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I225" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J225" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="226" customHeight="1" ht="15" spans="1:5">
-      <c r="A226" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B226" s="10" t="s">
+      <c r="H227" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="228" customHeight="1" ht="15" spans="1:5">
+      <c r="A228" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B228" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C226" s="11" t="n">
-        <v>16076.8</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E226" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A227" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" customHeight="1" ht="15" spans="1:12">
-      <c r="A228" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D228" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F228" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G228" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H228" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I228" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J228" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K228" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L228" s="3" t="s">
-        <v>12</v>
+      <c r="C228" s="11" t="n">
+        <v>33000</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E228" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="229" customHeight="1" ht="15" spans="1:1">
       <c r="A229" s="2" t="s">
-        <v>38</v>
+        <v>114</v>
       </c>
     </row>
     <row r="230" customHeight="1" ht="15" spans="1:10">
@@ -5618,19 +5630,19 @@
         <v>14</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D230" s="6" t="n">
-        <v>2000</v>
+        <v>1024</v>
       </c>
       <c r="E230" s="7" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="F230" s="7" t="n">
-        <v>27000</v>
+        <v>16076.8</v>
       </c>
       <c r="G230" s="8">
         <v>46113</v>
@@ -5642,7 +5654,7 @@
         <v>0</v>
       </c>
       <c r="J230" s="6" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
     </row>
     <row r="231" customHeight="1" ht="15" spans="1:5">
@@ -5653,120 +5665,217 @@
         <v>19</v>
       </c>
       <c r="C231" s="11" t="n">
+        <v>16076.8</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E231" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A232" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" ht="15" spans="1:12">
+      <c r="A233" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J233" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K233" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L233" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" ht="15" spans="1:1">
+      <c r="A234" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" ht="15" spans="1:10">
+      <c r="A235" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D235" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E235" s="7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F235" s="7" t="n">
         <v>27000</v>
       </c>
-      <c r="D231" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E231" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" customHeight="1" ht="15" spans="1:1">
-      <c r="A232" s="2" t="s">
+      <c r="G235" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H235" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I235" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="236" customHeight="1" ht="15" spans="1:5">
+      <c r="A236" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B236" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C236" s="11" t="n">
+        <v>27000</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E236" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" customHeight="1" ht="15" spans="1:1">
+      <c r="A237" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="233" customHeight="1" ht="15" spans="1:10">
-      <c r="A233" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B233" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D233" s="6" t="n">
+    <row r="238" customHeight="1" ht="15" spans="1:10">
+      <c r="A238" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D238" s="6" t="n">
         <v>1800</v>
       </c>
-      <c r="E233" s="7" t="n">
+      <c r="E238" s="7" t="n">
         <v>4.89</v>
       </c>
-      <c r="F233" s="7" t="n">
+      <c r="F238" s="7" t="n">
         <v>8802</v>
       </c>
-      <c r="G233" s="8">
+      <c r="G238" s="8">
         <v>46099</v>
       </c>
-      <c r="H233" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I233" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J233" s="6" t="s">
+      <c r="H238" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I238" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="234" customHeight="1" ht="15" spans="1:5">
-      <c r="A234" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B234" s="10" t="s">
+    <row r="239" customHeight="1" ht="15" spans="1:5">
+      <c r="A239" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B239" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C234" s="11" t="n">
+      <c r="C239" s="11" t="n">
         <v>8802</v>
       </c>
-      <c r="D234" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E234" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" customHeight="1" ht="15" spans="1:1">
-      <c r="A235" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="236" customHeight="1" ht="15" spans="1:10">
-      <c r="A236" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B236" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C236" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D236" s="6" t="n">
+      <c r="D239" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E239" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" customHeight="1" ht="15" spans="1:1">
+      <c r="A240" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="241" customHeight="1" ht="15" spans="1:10">
+      <c r="A241" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D241" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="E236" s="7" t="n">
+      <c r="E241" s="7" t="n">
         <v>6.78</v>
       </c>
-      <c r="F236" s="7" t="n">
+      <c r="F241" s="7" t="n">
         <v>54240</v>
       </c>
-      <c r="G236" s="8">
+      <c r="G241" s="8">
         <v>46113</v>
       </c>
-      <c r="H236" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I236" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J236" s="6" t="s">
+      <c r="H241" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="237" customHeight="1" ht="15" spans="1:5">
-      <c r="A237" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B237" s="10" t="s">
+    <row r="242" customHeight="1" ht="15" spans="1:5">
+      <c r="A242" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B242" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C237" s="11" t="n">
+      <c r="C242" s="11" t="n">
         <v>54240</v>
       </c>
-      <c r="D237" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E237" s="12" t="n">
+      <c r="D242" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E242" s="12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -5078,7 +5078,7 @@
     </row>
     <row r="215" customHeight="1" ht="15" spans="1:1">
       <c r="A215" s="2" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
     </row>
     <row r="216" customHeight="1" ht="15" spans="1:10">
@@ -5086,22 +5086,22 @@
         <v>14</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="C216" s="5" t="s">
         <v>133</v>
       </c>
       <c r="D216" s="6" t="n">
-        <v>800</v>
+        <v>2016</v>
       </c>
       <c r="E216" s="7" t="n">
-        <v>14.22</v>
+        <v>6.99</v>
       </c>
       <c r="F216" s="7" t="n">
-        <v>11376</v>
+        <v>14091.84</v>
       </c>
       <c r="G216" s="8">
-        <v>46121</v>
+        <v>46132</v>
       </c>
       <c r="H216" s="6" t="n">
         <v>0</v>
@@ -5110,7 +5110,7 @@
         <v>0</v>
       </c>
       <c r="J216" s="6" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="217" customHeight="1" ht="15" spans="1:5">
@@ -5121,7 +5121,7 @@
         <v>19</v>
       </c>
       <c r="C217" s="11" t="n">
-        <v>11376</v>
+        <v>14091.84</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>18</v>

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="153">
   <si>
     <t>MATRIZ CNPJ: 40.357.820/0001-50R Y DOIS - 58082-025
  ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
@@ -218,6 +218,12 @@
     <t>1665 - ATADURA DE CREPE 13 FIOS 30 X 1,80  PCT 12</t>
   </si>
   <si>
+    <t>SABRINA MARTHA RAMALHO MENDES COM. DE ART. MED. LTDA</t>
+  </si>
+  <si>
+    <t>779</t>
+  </si>
+  <si>
     <t>TOUREIROFARMA</t>
   </si>
   <si>
@@ -359,6 +365,12 @@
     <t xml:space="preserve">2070 - GAZE CIRCULAR NAO ESTERIL 09 FIOS </t>
   </si>
   <si>
+    <t>780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132 - GAZE CIRCULAR NAO ESTERIL 09 FIOS </t>
+  </si>
+  <si>
     <t xml:space="preserve">85 - GAZE CIRCULAR NAO ESTERIL 09 FIOS </t>
   </si>
   <si>
@@ -416,12 +428,12 @@
     <t>329 - GAZE NAO ESTÉRIL 13 FIOS IA</t>
   </si>
   <si>
+    <t>349 - GAZE NAO ESTÉRIL 13 FIOS  - PCT 500 UND</t>
+  </si>
+  <si>
     <t xml:space="preserve">2080 - GAZE NAO ESTÉRIL 13 FIOS </t>
   </si>
   <si>
-    <t>349 - GAZE NAO ESTÉRIL 13 FIOS  - PCT 500 UND</t>
-  </si>
-  <si>
     <t>MEDFASP SERVICOS &amp; COMERCIO LTDA</t>
   </si>
   <si>
@@ -453,15 +465,6 @@
   </si>
   <si>
     <t xml:space="preserve">08 - GAZE NAO ESTÉRIL 09 FIOS </t>
-  </si>
-  <si>
-    <t>DENTAL PB LTDA</t>
-  </si>
-  <si>
-    <t>778</t>
-  </si>
-  <si>
-    <t>SERGIO ROBERTO</t>
   </si>
   <si>
     <t>13 - GAZE NAO ESTÉRIL 09 FIOS I</t>
@@ -626,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L259"/>
+  <dimension ref="A1:L268"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
   <cols>
     <col customWidth="1" width="89.23828125" min="1" max="1"/>
@@ -768,10 +771,10 @@
         <v>46122</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1760</v>
+        <v>0</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>23.26</v>
+        <v>0</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>23</v>
@@ -791,7 +794,7 @@
         <v>18</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1760</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customHeight="1" ht="77.35" spans="1:1">
@@ -2425,179 +2428,179 @@
         <v>69</v>
       </c>
       <c r="C75" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D75" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="E75" s="7" t="n">
+        <v>9.37</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>655.9</v>
+      </c>
+      <c r="G75" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" ht="15" spans="1:5">
+      <c r="A76" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>655.9</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" ht="15" spans="1:1">
+      <c r="A77" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" ht="15" spans="1:10">
+      <c r="A78" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D78" s="6" t="n">
         <v>330</v>
       </c>
-      <c r="E75" s="7" t="n">
+      <c r="E78" s="7" t="n">
         <v>4.91</v>
       </c>
-      <c r="F75" s="7" t="n">
+      <c r="F78" s="7" t="n">
         <v>1620.3</v>
       </c>
-      <c r="G75" s="8">
+      <c r="G78" s="8">
         <v>46076</v>
       </c>
-      <c r="H75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="6" t="s">
+      <c r="H78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="76" customHeight="1" ht="15" spans="1:10">
-      <c r="A76" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D76" s="6" t="n">
+    <row r="79" customHeight="1" ht="15" spans="1:10">
+      <c r="A79" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D79" s="6" t="n">
         <v>660</v>
       </c>
-      <c r="E76" s="7" t="n">
+      <c r="E79" s="7" t="n">
         <v>4.91</v>
       </c>
-      <c r="F76" s="7" t="n">
+      <c r="F79" s="7" t="n">
         <v>3240.6</v>
       </c>
-      <c r="G76" s="8">
+      <c r="G79" s="8">
         <v>46107</v>
       </c>
-      <c r="H76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="6" t="s">
+      <c r="H79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="77" customHeight="1" ht="15" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B77" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C77" s="11" t="n">
+    <row r="80" customHeight="1" ht="15" spans="1:5">
+      <c r="A80" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" s="11" t="n">
         <v>4860.9</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E77" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A78" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" ht="15" spans="1:12">
-      <c r="A79" s="2" t="s">
+      <c r="D80" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A81" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" ht="15" spans="1:12">
+      <c r="A82" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C79" s="2" t="s">
+      <c r="B82" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="D82" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E82" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F82" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G79" s="3" t="s">
+      <c r="G82" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H79" s="3" t="s">
+      <c r="H82" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I79" s="3" t="s">
+      <c r="I82" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J79" s="3" t="s">
+      <c r="J82" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K79" s="2" t="s">
+      <c r="K82" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L79" s="3" t="s">
+      <c r="L82" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" ht="15" spans="1:1">
-      <c r="A80" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" ht="15" spans="1:10">
-      <c r="A81" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D81" s="6" t="n">
-        <v>200100</v>
-      </c>
-      <c r="E81" s="7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F81" s="7" t="n">
-        <v>820410</v>
-      </c>
-      <c r="G81" s="8">
-        <v>46119</v>
-      </c>
-      <c r="H81" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" ht="15" spans="1:5">
-      <c r="A82" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B82" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C82" s="11" t="n">
-        <v>820410</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="83" customHeight="1" ht="15" spans="1:1">
       <c r="A83" s="2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84" customHeight="1" ht="15" spans="1:10">
@@ -2605,22 +2608,22 @@
         <v>14</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>77</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>1050</v>
+        <v>200100</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>5.77</v>
+        <v>4.1</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>6058.5</v>
+        <v>820410</v>
       </c>
       <c r="G84" s="8">
-        <v>46134</v>
+        <v>46119</v>
       </c>
       <c r="H84" s="6" t="n">
         <v>0</v>
@@ -2629,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" customHeight="1" ht="15" spans="1:5">
@@ -2640,7 +2643,7 @@
         <v>19</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>6058.5</v>
+        <v>820410</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>18</v>
@@ -2651,7 +2654,7 @@
     </row>
     <row r="86" customHeight="1" ht="15" spans="1:1">
       <c r="A86" s="2" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
     </row>
     <row r="87" customHeight="1" ht="15" spans="1:10">
@@ -2659,22 +2662,22 @@
         <v>14</v>
       </c>
       <c r="B87" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C87" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C87" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D87" s="6" t="n">
-        <v>600</v>
+        <v>1050</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>4.8</v>
+        <v>5.77</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>2880</v>
+        <v>6058.5</v>
       </c>
       <c r="G87" s="8">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="H87" s="6" t="n">
         <v>0</v>
@@ -2683,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
     </row>
     <row r="88" customHeight="1" ht="15" spans="1:5">
@@ -2694,115 +2697,115 @@
         <v>19</v>
       </c>
       <c r="C88" s="11" t="n">
+        <v>6058.5</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" ht="15" spans="1:1">
+      <c r="A89" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" ht="15" spans="1:10">
+      <c r="A90" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F90" s="7" t="n">
         <v>2880</v>
       </c>
-      <c r="D88" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E88" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A89" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" customHeight="1" ht="15" spans="1:12">
-      <c r="A90" s="2" t="s">
+      <c r="G90" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" ht="15" spans="1:5">
+      <c r="A91" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C91" s="11" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A92" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" ht="15" spans="1:12">
+      <c r="A93" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C90" s="2" t="s">
+      <c r="B93" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D93" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E93" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F93" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="G93" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H90" s="3" t="s">
+      <c r="H93" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I90" s="3" t="s">
+      <c r="I93" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J90" s="3" t="s">
+      <c r="J93" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K90" s="2" t="s">
+      <c r="K93" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L90" s="3" t="s">
+      <c r="L93" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" ht="15" spans="1:1">
-      <c r="A91" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="92" customHeight="1" ht="15" spans="1:10">
-      <c r="A92" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D92" s="6" t="n">
-        <v>204</v>
-      </c>
-      <c r="E92" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="F92" s="7" t="n">
-        <v>9180</v>
-      </c>
-      <c r="G92" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H92" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="93" customHeight="1" ht="15" spans="1:5">
-      <c r="A93" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B93" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C93" s="11" t="n">
-        <v>9180</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E93" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="94" customHeight="1" ht="15" spans="1:1">
       <c r="A94" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="95" customHeight="1" ht="15" spans="1:10">
@@ -2810,22 +2813,22 @@
         <v>14</v>
       </c>
       <c r="B95" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C95" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C95" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="D95" s="6" t="n">
-        <v>804</v>
+        <v>204</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>45.9</v>
+        <v>45</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>36903.6</v>
+        <v>9180</v>
       </c>
       <c r="G95" s="8">
-        <v>46132</v>
+        <v>46127</v>
       </c>
       <c r="H95" s="6" t="n">
         <v>0</v>
@@ -2834,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96" customHeight="1" ht="15" spans="1:5">
@@ -2845,7 +2848,7 @@
         <v>19</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>36903.6</v>
+        <v>9180</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>18</v>
@@ -2856,7 +2859,7 @@
     </row>
     <row r="97" customHeight="1" ht="15" spans="1:1">
       <c r="A97" s="2" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
     </row>
     <row r="98" customHeight="1" ht="15" spans="1:10">
@@ -2864,22 +2867,22 @@
         <v>14</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>648</v>
+        <v>804</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>29678.4</v>
+        <v>36903.6</v>
       </c>
       <c r="G98" s="8">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="H98" s="6" t="n">
         <v>0</v>
@@ -2888,7 +2891,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
     <row r="99" customHeight="1" ht="15" spans="1:5">
@@ -2899,7 +2902,7 @@
         <v>19</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>29678.4</v>
+        <v>36903.6</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>18</v>
@@ -2910,7 +2913,7 @@
     </row>
     <row r="100" customHeight="1" ht="15" spans="1:1">
       <c r="A100" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="101" customHeight="1" ht="15" spans="1:10">
@@ -2918,22 +2921,22 @@
         <v>14</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>36</v>
+        <v>648</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>55.09</v>
+        <v>45.8</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>1983.24</v>
+        <v>29678.4</v>
       </c>
       <c r="G101" s="8">
-        <v>46134</v>
+        <v>46128</v>
       </c>
       <c r="H101" s="6" t="n">
         <v>0</v>
@@ -2942,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="102" customHeight="1" ht="15" spans="1:5">
@@ -2953,7 +2956,7 @@
         <v>19</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>1983.24</v>
+        <v>29678.4</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>18</v>
@@ -2964,7 +2967,7 @@
     </row>
     <row r="103" customHeight="1" ht="15" spans="1:1">
       <c r="A103" s="2" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
     </row>
     <row r="104" customHeight="1" ht="15" spans="1:10">
@@ -2972,22 +2975,22 @@
         <v>14</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>1008</v>
+        <v>36</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>41</v>
+        <v>55.09</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>41328</v>
+        <v>1983.24</v>
       </c>
       <c r="G104" s="8">
-        <v>46104</v>
+        <v>46134</v>
       </c>
       <c r="H104" s="6" t="n">
         <v>0</v>
@@ -2996,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="105" customHeight="1" ht="15" spans="1:5">
@@ -3007,115 +3010,115 @@
         <v>19</v>
       </c>
       <c r="C105" s="11" t="n">
+        <v>1983.24</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" ht="15" spans="1:1">
+      <c r="A106" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" ht="15" spans="1:10">
+      <c r="A107" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D107" s="6" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E107" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="F107" s="7" t="n">
         <v>41328</v>
       </c>
-      <c r="D105" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A106" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" customHeight="1" ht="15" spans="1:12">
-      <c r="A107" s="2" t="s">
+      <c r="G107" s="8">
+        <v>46104</v>
+      </c>
+      <c r="H107" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" ht="15" spans="1:5">
+      <c r="A108" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>41328</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A109" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" ht="15" spans="1:12">
+      <c r="A110" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C107" s="2" t="s">
+      <c r="B110" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D110" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E107" s="3" t="s">
+      <c r="E110" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F107" s="3" t="s">
+      <c r="F110" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G107" s="3" t="s">
+      <c r="G110" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H107" s="3" t="s">
+      <c r="H110" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I107" s="3" t="s">
+      <c r="I110" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J107" s="3" t="s">
+      <c r="J110" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K107" s="2" t="s">
+      <c r="K110" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L107" s="3" t="s">
+      <c r="L110" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="108" customHeight="1" ht="15" spans="1:1">
-      <c r="A108" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="109" customHeight="1" ht="15" spans="1:10">
-      <c r="A109" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D109" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E109" s="7" t="n">
-        <v>21.84</v>
-      </c>
-      <c r="F109" s="7" t="n">
-        <v>32760</v>
-      </c>
-      <c r="G109" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H109" s="6" t="n">
-        <v>768</v>
-      </c>
-      <c r="I109" s="9" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="J109" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="110" customHeight="1" ht="15" spans="1:5">
-      <c r="A110" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B110" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C110" s="11" t="n">
-        <v>32760</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E110" s="12" t="n">
-        <v>768</v>
       </c>
     </row>
     <row r="111" customHeight="1" ht="15" spans="1:1">
       <c r="A111" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="112" customHeight="1" ht="15" spans="1:10">
@@ -3123,31 +3126,31 @@
         <v>14</v>
       </c>
       <c r="B112" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D112" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="F112" s="7" t="n">
+        <v>32760</v>
+      </c>
+      <c r="G112" s="8">
+        <v>46127</v>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>768</v>
+      </c>
+      <c r="I112" s="9" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J112" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D112" s="6" t="n">
-        <v>2004</v>
-      </c>
-      <c r="E112" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="F112" s="7" t="n">
-        <v>88176</v>
-      </c>
-      <c r="G112" s="8">
-        <v>46112</v>
-      </c>
-      <c r="H112" s="6" t="n">
-        <v>480</v>
-      </c>
-      <c r="I112" s="9" t="n">
-        <v>23.95</v>
-      </c>
-      <c r="J112" s="6" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="113" customHeight="1" ht="15" spans="1:5">
@@ -3158,115 +3161,115 @@
         <v>19</v>
       </c>
       <c r="C113" s="11" t="n">
+        <v>32760</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" ht="15" spans="1:1">
+      <c r="A114" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" ht="15" spans="1:10">
+      <c r="A115" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D115" s="6" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E115" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="F115" s="7" t="n">
         <v>88176</v>
       </c>
-      <c r="D113" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E113" s="12" t="n">
+      <c r="G115" s="8">
+        <v>46112</v>
+      </c>
+      <c r="H115" s="6" t="n">
         <v>480</v>
       </c>
-    </row>
-    <row r="114" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A114" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" customHeight="1" ht="15" spans="1:12">
-      <c r="A115" s="2" t="s">
+      <c r="I115" s="9" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="J115" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" ht="15" spans="1:5">
+      <c r="A116" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C116" s="11" t="n">
+        <v>88176</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E116" s="12" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A117" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" ht="15" spans="1:12">
+      <c r="A118" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C115" s="2" t="s">
+      <c r="B118" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D115" s="2" t="s">
+      <c r="D118" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E115" s="3" t="s">
+      <c r="E118" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F115" s="3" t="s">
+      <c r="F118" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G115" s="3" t="s">
+      <c r="G118" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H115" s="3" t="s">
+      <c r="H118" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I115" s="3" t="s">
+      <c r="I118" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J115" s="3" t="s">
+      <c r="J118" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K115" s="2" t="s">
+      <c r="K118" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L115" s="3" t="s">
+      <c r="L118" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="116" customHeight="1" ht="15" spans="1:1">
-      <c r="A116" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="117" customHeight="1" ht="15" spans="1:10">
-      <c r="A117" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D117" s="6" t="n">
-        <v>13000</v>
-      </c>
-      <c r="E117" s="7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F117" s="7" t="n">
-        <v>5460</v>
-      </c>
-      <c r="G117" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H117" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="118" customHeight="1" ht="15" spans="1:5">
-      <c r="A118" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B118" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C118" s="11" t="n">
-        <v>5460</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E118" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="119" customHeight="1" ht="15" spans="1:1">
       <c r="A119" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="120" customHeight="1" ht="15" spans="1:10">
@@ -3274,22 +3277,22 @@
         <v>14</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="E120" s="7" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="F120" s="7" t="n">
-        <v>3700</v>
+        <v>5460</v>
       </c>
       <c r="G120" s="8">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="H120" s="6" t="n">
         <v>0</v>
@@ -3298,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="121" customHeight="1" ht="15" spans="1:5">
@@ -3309,7 +3312,7 @@
         <v>19</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>3700</v>
+        <v>5460</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>18</v>
@@ -3320,7 +3323,7 @@
     </row>
     <row r="122" customHeight="1" ht="15" spans="1:1">
       <c r="A122" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="123" customHeight="1" ht="15" spans="1:10">
@@ -3328,19 +3331,19 @@
         <v>14</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="E123" s="7" t="n">
         <v>0.37</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>14800</v>
+        <v>3700</v>
       </c>
       <c r="G123" s="8">
         <v>46132</v>
@@ -3363,7 +3366,7 @@
         <v>19</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>14800</v>
+        <v>3700</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>18</v>
@@ -3374,7 +3377,7 @@
     </row>
     <row r="125" customHeight="1" ht="15" spans="1:1">
       <c r="A125" s="2" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="126" customHeight="1" ht="15" spans="1:10">
@@ -3382,19 +3385,19 @@
         <v>14</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="E126" s="7" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="F126" s="7" t="n">
-        <v>10500</v>
+        <v>14800</v>
       </c>
       <c r="G126" s="8">
         <v>46132</v>
@@ -3406,7 +3409,7 @@
         <v>0</v>
       </c>
       <c r="J126" s="6" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
     </row>
     <row r="127" customHeight="1" ht="15" spans="1:5">
@@ -3417,115 +3420,115 @@
         <v>19</v>
       </c>
       <c r="C127" s="11" t="n">
+        <v>14800</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E127" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" ht="15" spans="1:1">
+      <c r="A128" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" ht="15" spans="1:10">
+      <c r="A129" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D129" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E129" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F129" s="7" t="n">
         <v>10500</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E127" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A128" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" customHeight="1" ht="15" spans="1:12">
-      <c r="A129" s="2" t="s">
+      <c r="G129" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H129" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" ht="15" spans="1:5">
+      <c r="A130" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C130" s="11" t="n">
+        <v>10500</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E130" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A131" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" ht="15" spans="1:12">
+      <c r="A132" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C129" s="2" t="s">
+      <c r="B132" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D129" s="2" t="s">
+      <c r="D132" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E129" s="3" t="s">
+      <c r="E132" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F129" s="3" t="s">
+      <c r="F132" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G129" s="3" t="s">
+      <c r="G132" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H129" s="3" t="s">
+      <c r="H132" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I129" s="3" t="s">
+      <c r="I132" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J129" s="3" t="s">
+      <c r="J132" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K129" s="2" t="s">
+      <c r="K132" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L129" s="3" t="s">
+      <c r="L132" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="130" customHeight="1" ht="15" spans="1:1">
-      <c r="A130" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="131" customHeight="1" ht="15" spans="1:10">
-      <c r="A131" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D131" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="E131" s="7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F131" s="7" t="n">
-        <v>70000</v>
-      </c>
-      <c r="G131" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H131" s="6" t="n">
-        <v>18000</v>
-      </c>
-      <c r="I131" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J131" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="132" customHeight="1" ht="15" spans="1:5">
-      <c r="A132" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B132" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C132" s="11" t="n">
-        <v>70000</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E132" s="12" t="n">
-        <v>18000</v>
       </c>
     </row>
     <row r="133" customHeight="1" ht="15" spans="1:1">
       <c r="A133" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="134" customHeight="1" ht="15" spans="1:10">
@@ -3533,31 +3536,31 @@
         <v>14</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>1000</v>
+        <v>200000</v>
       </c>
       <c r="E134" s="7" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="F134" s="7" t="n">
-        <v>450</v>
+        <v>70000</v>
       </c>
       <c r="G134" s="8">
-        <v>46134</v>
+        <v>46132</v>
       </c>
       <c r="H134" s="6" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J134" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
     <row r="135" customHeight="1" ht="15" spans="1:5">
@@ -3568,18 +3571,18 @@
         <v>19</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>450</v>
+        <v>70000</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E135" s="12" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="136" customHeight="1" ht="15" spans="1:1">
       <c r="A136" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="137" customHeight="1" ht="15" spans="1:10">
@@ -3587,22 +3590,22 @@
         <v>14</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>99</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>40000</v>
+        <v>1000</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>0.485</v>
+        <v>0.45</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>19400</v>
+        <v>450</v>
       </c>
       <c r="G137" s="8">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="H137" s="6" t="n">
         <v>0</v>
@@ -3611,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="J137" s="6" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="138" customHeight="1" ht="15" spans="1:5">
@@ -3622,7 +3625,7 @@
         <v>19</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>19400</v>
+        <v>450</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>18</v>
@@ -3633,7 +3636,7 @@
     </row>
     <row r="139" customHeight="1" ht="15" spans="1:1">
       <c r="A139" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="140" customHeight="1" ht="15" spans="1:10">
@@ -3641,22 +3644,22 @@
         <v>14</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E140" s="7" t="n">
-        <v>0.38</v>
+        <v>0.485</v>
       </c>
       <c r="F140" s="7" t="n">
-        <v>3800</v>
+        <v>19400</v>
       </c>
       <c r="G140" s="8">
-        <v>46132</v>
+        <v>46113</v>
       </c>
       <c r="H140" s="6" t="n">
         <v>0</v>
@@ -3676,7 +3679,7 @@
         <v>19</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>3800</v>
+        <v>19400</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>18</v>
@@ -3687,7 +3690,7 @@
     </row>
     <row r="142" customHeight="1" ht="15" spans="1:1">
       <c r="A142" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="143" customHeight="1" ht="15" spans="1:10">
@@ -3695,19 +3698,19 @@
         <v>14</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="E143" s="7" t="n">
         <v>0.38</v>
       </c>
       <c r="F143" s="7" t="n">
-        <v>11400</v>
+        <v>3800</v>
       </c>
       <c r="G143" s="8">
         <v>46132</v>
@@ -3730,147 +3733,147 @@
         <v>19</v>
       </c>
       <c r="C144" s="11" t="n">
+        <v>3800</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E144" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" ht="15" spans="1:1">
+      <c r="A145" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" ht="15" spans="1:10">
+      <c r="A146" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D146" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E146" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F146" s="7" t="n">
         <v>11400</v>
       </c>
-      <c r="D144" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E144" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A145" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" customHeight="1" ht="15" spans="1:12">
-      <c r="A146" s="2" t="s">
+      <c r="G146" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H146" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" ht="15" spans="1:5">
+      <c r="A147" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C147" s="11" t="n">
+        <v>11400</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E147" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A148" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" ht="15" spans="1:12">
+      <c r="A149" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C146" s="2" t="s">
+      <c r="B149" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D146" s="2" t="s">
+      <c r="D149" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E146" s="3" t="s">
+      <c r="E149" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F146" s="3" t="s">
+      <c r="F149" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G146" s="3" t="s">
+      <c r="G149" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H146" s="3" t="s">
+      <c r="H149" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I146" s="3" t="s">
+      <c r="I149" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J146" s="3" t="s">
+      <c r="J149" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K146" s="2" t="s">
+      <c r="K149" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L146" s="3" t="s">
+      <c r="L149" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="147" customHeight="1" ht="15" spans="1:1">
-      <c r="A147" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="148" customHeight="1" ht="15" spans="1:10">
-      <c r="A148" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C148" s="5" t="s">
+    <row r="150" customHeight="1" ht="15" spans="1:1">
+      <c r="A150" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D148" s="6" t="n">
+    </row>
+    <row r="151" customHeight="1" ht="15" spans="1:10">
+      <c r="A151" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D151" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="E148" s="7" t="n">
+      <c r="E151" s="7" t="n">
         <v>0.4</v>
       </c>
-      <c r="F148" s="7" t="n">
+      <c r="F151" s="7" t="n">
         <v>20000</v>
       </c>
-      <c r="G148" s="8">
+      <c r="G151" s="8">
         <v>46132</v>
       </c>
-      <c r="H148" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" s="6" t="s">
+      <c r="H151" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="6" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="149" customHeight="1" ht="15" spans="1:10">
-      <c r="A149" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D149" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E149" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F149" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G149" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H149" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="150" customHeight="1" ht="15" spans="1:5">
-      <c r="A150" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B150" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C150" s="11" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D150" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E150" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" customHeight="1" ht="15" spans="1:1">
-      <c r="A151" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="152" customHeight="1" ht="15" spans="1:10">
@@ -3881,16 +3884,16 @@
         <v>106</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D152" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E152" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F152" s="7" t="n">
         <v>20000</v>
-      </c>
-      <c r="E152" s="7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F152" s="7" t="n">
-        <v>8400</v>
       </c>
       <c r="G152" s="8">
         <v>46132</v>
@@ -3902,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="J152" s="6" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
     </row>
     <row r="153" customHeight="1" ht="15" spans="1:5">
@@ -3913,7 +3916,7 @@
         <v>19</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>8400</v>
+        <v>40000</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>18</v>
@@ -3935,19 +3938,19 @@
         <v>108</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D155" s="6" t="n">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="E155" s="7" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="F155" s="7" t="n">
-        <v>9900</v>
+        <v>8400</v>
       </c>
       <c r="G155" s="8">
-        <v>46114</v>
+        <v>46132</v>
       </c>
       <c r="H155" s="6" t="n">
         <v>0</v>
@@ -3956,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="J155" s="6" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="156" customHeight="1" ht="15" spans="1:5">
@@ -3967,7 +3970,7 @@
         <v>19</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>9900</v>
+        <v>8400</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>18</v>
@@ -3978,7 +3981,7 @@
     </row>
     <row r="157" customHeight="1" ht="15" spans="1:1">
       <c r="A157" s="2" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
     </row>
     <row r="158" customHeight="1" ht="15" spans="1:10">
@@ -3986,22 +3989,22 @@
         <v>14</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D158" s="6" t="n">
-        <v>100000</v>
+        <v>30000</v>
       </c>
       <c r="E158" s="7" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="F158" s="7" t="n">
-        <v>42000</v>
+        <v>9900</v>
       </c>
       <c r="G158" s="8">
-        <v>46128</v>
+        <v>46114</v>
       </c>
       <c r="H158" s="6" t="n">
         <v>0</v>
@@ -4010,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="6" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
     </row>
     <row r="159" customHeight="1" ht="15" spans="1:5">
@@ -4021,115 +4024,115 @@
         <v>19</v>
       </c>
       <c r="C159" s="11" t="n">
+        <v>9900</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E159" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" ht="15" spans="1:1">
+      <c r="A160" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" ht="15" spans="1:10">
+      <c r="A161" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D161" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E161" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F161" s="7" t="n">
         <v>42000</v>
       </c>
-      <c r="D159" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E159" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A160" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" customHeight="1" ht="15" spans="1:12">
-      <c r="A161" s="2" t="s">
+      <c r="G161" s="8">
+        <v>46128</v>
+      </c>
+      <c r="H161" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" ht="15" spans="1:5">
+      <c r="A162" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B162" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C162" s="11" t="n">
+        <v>42000</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E162" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A163" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" ht="15" spans="1:12">
+      <c r="A164" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C161" s="2" t="s">
+      <c r="B164" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C164" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D161" s="2" t="s">
+      <c r="D164" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E161" s="3" t="s">
+      <c r="E164" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F161" s="3" t="s">
+      <c r="F164" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G161" s="3" t="s">
+      <c r="G164" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H161" s="3" t="s">
+      <c r="H164" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I161" s="3" t="s">
+      <c r="I164" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J161" s="3" t="s">
+      <c r="J164" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K161" s="2" t="s">
+      <c r="K164" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L161" s="3" t="s">
+      <c r="L164" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="162" customHeight="1" ht="15" spans="1:1">
-      <c r="A162" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="163" customHeight="1" ht="15" spans="1:10">
-      <c r="A163" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D163" s="6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E163" s="7" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="F163" s="7" t="n">
-        <v>1410</v>
-      </c>
-      <c r="G163" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H163" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J163" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="164" customHeight="1" ht="15" spans="1:5">
-      <c r="A164" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B164" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C164" s="11" t="n">
-        <v>1410</v>
-      </c>
-      <c r="D164" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E164" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="165" customHeight="1" ht="15" spans="1:1">
       <c r="A165" s="2" t="s">
-        <v>110</v>
+        <v>51</v>
       </c>
     </row>
     <row r="166" customHeight="1" ht="15" spans="1:10">
@@ -4137,22 +4140,22 @@
         <v>14</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D166" s="6" t="n">
-        <v>100000</v>
+        <v>3000</v>
       </c>
       <c r="E166" s="7" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="F166" s="7" t="n">
-        <v>40000</v>
+        <v>1410</v>
       </c>
       <c r="G166" s="8">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="H166" s="6" t="n">
         <v>0</v>
@@ -4161,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="J166" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="167" customHeight="1" ht="15" spans="1:5">
@@ -4172,7 +4175,7 @@
         <v>19</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>40000</v>
+        <v>1410</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>18</v>
@@ -4183,7 +4186,7 @@
     </row>
     <row r="168" customHeight="1" ht="15" spans="1:1">
       <c r="A168" s="2" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
     </row>
     <row r="169" customHeight="1" ht="15" spans="1:10">
@@ -4191,19 +4194,19 @@
         <v>14</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D169" s="6" t="n">
-        <v>5000</v>
+        <v>100000</v>
       </c>
       <c r="E169" s="7" t="n">
         <v>0.4</v>
       </c>
       <c r="F169" s="7" t="n">
-        <v>2000</v>
+        <v>40000</v>
       </c>
       <c r="G169" s="8">
         <v>46132</v>
@@ -4215,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="J169" s="6" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="170" customHeight="1" ht="15" spans="1:5">
@@ -4226,7 +4229,7 @@
         <v>19</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>2000</v>
+        <v>40000</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>18</v>
@@ -4237,7 +4240,7 @@
     </row>
     <row r="171" customHeight="1" ht="15" spans="1:1">
       <c r="A171" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="172" customHeight="1" ht="15" spans="1:10">
@@ -4245,19 +4248,19 @@
         <v>14</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D172" s="6" t="n">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="E172" s="7" t="n">
         <v>0.4</v>
       </c>
       <c r="F172" s="7" t="n">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="G172" s="8">
         <v>46132</v>
@@ -4280,169 +4283,169 @@
         <v>19</v>
       </c>
       <c r="C173" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E173" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" ht="15" spans="1:1">
+      <c r="A174" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" ht="15" spans="1:10">
+      <c r="A175" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D175" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E175" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F175" s="7" t="n">
         <v>20000</v>
       </c>
-      <c r="D173" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E173" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A174" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" customHeight="1" ht="15" spans="1:12">
-      <c r="A175" s="2" t="s">
+      <c r="G175" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H175" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" ht="15" spans="1:5">
+      <c r="A176" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B176" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C176" s="11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E176" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" customHeight="1" ht="15" spans="1:1">
+      <c r="A177" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="178" customHeight="1" ht="15" spans="1:10">
+      <c r="A178" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D178" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E178" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F178" s="7" t="n">
+        <v>420</v>
+      </c>
+      <c r="G178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H178" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="179" customHeight="1" ht="15" spans="1:5">
+      <c r="A179" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B179" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C179" s="11" t="n">
+        <v>420</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E179" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A180" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" ht="15" spans="1:12">
+      <c r="A181" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B175" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C175" s="2" t="s">
+      <c r="B181" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D175" s="2" t="s">
+      <c r="D181" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E175" s="3" t="s">
+      <c r="E181" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F175" s="3" t="s">
+      <c r="F181" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G175" s="3" t="s">
+      <c r="G181" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H175" s="3" t="s">
+      <c r="H181" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I175" s="3" t="s">
+      <c r="I181" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J175" s="3" t="s">
+      <c r="J181" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K175" s="2" t="s">
+      <c r="K181" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L175" s="3" t="s">
+      <c r="L181" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="176" customHeight="1" ht="15" spans="1:1">
-      <c r="A176" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="177" customHeight="1" ht="15" spans="1:10">
-      <c r="A177" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D177" s="6" t="n">
-        <v>3024</v>
-      </c>
-      <c r="E177" s="7" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="F177" s="7" t="n">
-        <v>37195.2</v>
-      </c>
-      <c r="G177" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H177" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I177" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J177" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="178" customHeight="1" ht="15" spans="1:5">
-      <c r="A178" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B178" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C178" s="11" t="n">
-        <v>37195.2</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E178" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" customHeight="1" ht="15" spans="1:1">
-      <c r="A179" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="180" customHeight="1" ht="15" spans="1:10">
-      <c r="A180" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D180" s="6" t="n">
-        <v>3024</v>
-      </c>
-      <c r="E180" s="7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F180" s="7" t="n">
-        <v>43848</v>
-      </c>
-      <c r="G180" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H180" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I180" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J180" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="181" customHeight="1" ht="15" spans="1:5">
-      <c r="A181" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B181" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C181" s="11" t="n">
-        <v>43848</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E181" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="182" customHeight="1" ht="15" spans="1:1">
       <c r="A182" s="2" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
     </row>
     <row r="183" customHeight="1" ht="15" spans="1:10">
@@ -4450,22 +4453,22 @@
         <v>14</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D183" s="6" t="n">
-        <v>36</v>
+        <v>3024</v>
       </c>
       <c r="E183" s="7" t="n">
-        <v>17.18</v>
+        <v>12.3</v>
       </c>
       <c r="F183" s="7" t="n">
-        <v>618.48</v>
+        <v>37195.2</v>
       </c>
       <c r="G183" s="8">
-        <v>46134</v>
+        <v>46127</v>
       </c>
       <c r="H183" s="6" t="n">
         <v>0</v>
@@ -4474,7 +4477,7 @@
         <v>0</v>
       </c>
       <c r="J183" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
     <row r="184" customHeight="1" ht="15" spans="1:5">
@@ -4485,201 +4488,201 @@
         <v>19</v>
       </c>
       <c r="C184" s="11" t="n">
+        <v>37195.2</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E184" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" ht="15" spans="1:1">
+      <c r="A185" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" ht="15" spans="1:10">
+      <c r="A186" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D186" s="6" t="n">
+        <v>3024</v>
+      </c>
+      <c r="E186" s="7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F186" s="7" t="n">
+        <v>43848</v>
+      </c>
+      <c r="G186" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H186" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" ht="15" spans="1:10">
+      <c r="A187" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D187" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="E187" s="7" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="F187" s="7" t="n">
+        <v>11310</v>
+      </c>
+      <c r="G187" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H187" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" ht="15" spans="1:5">
+      <c r="A188" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C188" s="11" t="n">
+        <v>55158</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E188" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" ht="15" spans="1:1">
+      <c r="A189" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" ht="15" spans="1:10">
+      <c r="A190" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D190" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="E190" s="7" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="F190" s="7" t="n">
         <v>618.48</v>
       </c>
-      <c r="D184" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E184" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A185" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" customHeight="1" ht="15" spans="1:12">
-      <c r="A186" s="2" t="s">
+      <c r="G190" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H190" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" ht="15" spans="1:5">
+      <c r="A191" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C191" s="11" t="n">
+        <v>618.48</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E191" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A192" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" ht="15" spans="1:12">
+      <c r="A193" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B186" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C186" s="2" t="s">
+      <c r="B193" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C193" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D186" s="2" t="s">
+      <c r="D193" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E186" s="3" t="s">
+      <c r="E193" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F186" s="3" t="s">
+      <c r="F193" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G186" s="3" t="s">
+      <c r="G193" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H186" s="3" t="s">
+      <c r="H193" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I186" s="3" t="s">
+      <c r="I193" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J186" s="3" t="s">
+      <c r="J193" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K186" s="2" t="s">
+      <c r="K193" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L186" s="3" t="s">
+      <c r="L193" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="187" customHeight="1" ht="15" spans="1:1">
-      <c r="A187" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="188" customHeight="1" ht="15" spans="1:10">
-      <c r="A188" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B188" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C188" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D188" s="6" t="n">
-        <v>510</v>
-      </c>
-      <c r="E188" s="7" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F188" s="7" t="n">
-        <v>7089</v>
-      </c>
-      <c r="G188" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H188" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J188" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="189" customHeight="1" ht="15" spans="1:10">
-      <c r="A189" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D189" s="6" t="n">
-        <v>510</v>
-      </c>
-      <c r="E189" s="7" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F189" s="7" t="n">
-        <v>7089</v>
-      </c>
-      <c r="G189" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H189" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I189" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J189" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="190" customHeight="1" ht="15" spans="1:5">
-      <c r="A190" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B190" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C190" s="11" t="n">
-        <v>14178</v>
-      </c>
-      <c r="D190" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E190" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" customHeight="1" ht="15" spans="1:1">
-      <c r="A191" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="192" customHeight="1" ht="15" spans="1:10">
-      <c r="A192" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B192" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C192" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D192" s="6" t="n">
-        <v>5004</v>
-      </c>
-      <c r="E192" s="7" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="F192" s="7" t="n">
-        <v>59997.96</v>
-      </c>
-      <c r="G192" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H192" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J192" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="193" customHeight="1" ht="15" spans="1:5">
-      <c r="A193" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B193" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C193" s="11" t="n">
-        <v>59997.96</v>
-      </c>
-      <c r="D193" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E193" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="194" customHeight="1" ht="15" spans="1:1">
       <c r="A194" s="2" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
     </row>
     <row r="195" customHeight="1" ht="15" spans="1:10">
@@ -4687,592 +4690,592 @@
         <v>14</v>
       </c>
       <c r="B195" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D195" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="E195" s="7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F195" s="7" t="n">
+        <v>7089</v>
+      </c>
+      <c r="G195" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H195" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="196" customHeight="1" ht="15" spans="1:10">
+      <c r="A196" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D196" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="E196" s="7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F196" s="7" t="n">
+        <v>7089</v>
+      </c>
+      <c r="G196" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H196" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="197" customHeight="1" ht="15" spans="1:5">
+      <c r="A197" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B197" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C197" s="11" t="n">
+        <v>14178</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E197" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" customHeight="1" ht="15" spans="1:1">
+      <c r="A198" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="199" customHeight="1" ht="15" spans="1:10">
+      <c r="A199" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D199" s="6" t="n">
+        <v>5004</v>
+      </c>
+      <c r="E199" s="7" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="F199" s="7" t="n">
+        <v>59997.96</v>
+      </c>
+      <c r="G199" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H199" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="200" customHeight="1" ht="15" spans="1:5">
+      <c r="A200" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C200" s="11" t="n">
+        <v>59997.96</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E200" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" ht="15" spans="1:1">
+      <c r="A201" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" ht="15" spans="1:10">
+      <c r="A202" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B202" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C195" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D195" s="6" t="n">
+      <c r="C202" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D202" s="6" t="n">
         <v>8010</v>
       </c>
-      <c r="E195" s="7" t="n">
+      <c r="E202" s="7" t="n">
         <v>20.79</v>
       </c>
-      <c r="F195" s="7" t="n">
+      <c r="F202" s="7" t="n">
         <v>166527.9</v>
       </c>
-      <c r="G195" s="8">
+      <c r="G202" s="8">
         <v>46122</v>
       </c>
-      <c r="H195" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I195" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J195" s="6" t="s">
+      <c r="H202" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="196" customHeight="1" ht="15" spans="1:5">
-      <c r="A196" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B196" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C196" s="11" t="n">
+    <row r="203" customHeight="1" ht="15" spans="1:5">
+      <c r="A203" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C203" s="11" t="n">
         <v>166527.9</v>
       </c>
-      <c r="D196" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E196" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" customHeight="1" ht="15" spans="1:1">
-      <c r="A197" s="2" t="s">
+      <c r="D203" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E203" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" ht="15" spans="1:1">
+      <c r="A204" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="198" customHeight="1" ht="15" spans="1:10">
-      <c r="A198" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B198" s="5" t="s">
+    <row r="205" customHeight="1" ht="15" spans="1:10">
+      <c r="A205" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B205" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C198" s="5" t="s">
+      <c r="C205" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D205" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E205" s="7" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="F205" s="7" t="n">
+        <v>1327.8</v>
+      </c>
+      <c r="G205" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H205" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" ht="15" spans="1:5">
+      <c r="A206" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B206" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C206" s="11" t="n">
+        <v>1327.8</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E206" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A207" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" ht="15" spans="1:12">
+      <c r="A208" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H208" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I208" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J208" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K208" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L208" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" ht="15" spans="1:1">
+      <c r="A209" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" ht="15" spans="1:10">
+      <c r="A210" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D210" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E210" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F210" s="7" t="n">
+        <v>312000</v>
+      </c>
+      <c r="G210" s="8">
+        <v>46100</v>
+      </c>
+      <c r="H210" s="6" t="n">
+        <v>18900</v>
+      </c>
+      <c r="I210" s="9" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="J210" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="211" customHeight="1" ht="15" spans="1:5">
+      <c r="A211" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B211" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C211" s="11" t="n">
+        <v>312000</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E211" s="12" t="n">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="212" customHeight="1" ht="15" spans="1:1">
+      <c r="A212" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="213" customHeight="1" ht="15" spans="1:10">
+      <c r="A213" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D213" s="6" t="n">
+        <v>810</v>
+      </c>
+      <c r="E213" s="7" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="F213" s="7" t="n">
+        <v>16102.8</v>
+      </c>
+      <c r="G213" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H213" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="214" customHeight="1" ht="15" spans="1:5">
+      <c r="A214" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B214" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C214" s="11" t="n">
+        <v>16102.8</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E214" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A215" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" customHeight="1" ht="15" spans="1:12">
+      <c r="A216" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H216" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I216" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J216" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K216" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L216" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" ht="15" spans="1:1">
+      <c r="A217" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" ht="15" spans="1:10">
+      <c r="A218" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D218" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E218" s="7" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="F218" s="7" t="n">
+        <v>3690</v>
+      </c>
+      <c r="G218" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H218" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" ht="15" spans="1:5">
+      <c r="A219" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B219" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C219" s="11" t="n">
+        <v>3690</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E219" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A220" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" ht="15" spans="1:12">
+      <c r="A221" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H221" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I221" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J221" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K221" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L221" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="222" customHeight="1" ht="15" spans="1:1">
+      <c r="A222" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D198" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E198" s="7" t="n">
-        <v>22.13</v>
-      </c>
-      <c r="F198" s="7" t="n">
-        <v>1327.8</v>
-      </c>
-      <c r="G198" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H198" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I198" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J198" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="199" customHeight="1" ht="15" spans="1:5">
-      <c r="A199" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B199" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C199" s="11" t="n">
-        <v>1327.8</v>
-      </c>
-      <c r="D199" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E199" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A200" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" customHeight="1" ht="15" spans="1:12">
-      <c r="A201" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E201" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F201" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G201" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H201" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I201" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J201" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K201" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L201" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="202" customHeight="1" ht="15" spans="1:1">
-      <c r="A202" s="2" t="s">
+    </row>
+    <row r="223" customHeight="1" ht="15" spans="1:10">
+      <c r="A223" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B223" s="5" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="203" customHeight="1" ht="15" spans="1:10">
-      <c r="A203" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B203" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C203" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D203" s="6" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E203" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="F203" s="7" t="n">
-        <v>312000</v>
-      </c>
-      <c r="G203" s="8">
-        <v>46100</v>
-      </c>
-      <c r="H203" s="6" t="n">
-        <v>18900</v>
-      </c>
-      <c r="I203" s="9" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="J203" s="6" t="s">
+      <c r="C223" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D223" s="6" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E223" s="7" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F223" s="7" t="n">
+        <v>14091.84</v>
+      </c>
+      <c r="G223" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H223" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="204" customHeight="1" ht="15" spans="1:5">
-      <c r="A204" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B204" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C204" s="11" t="n">
-        <v>312000</v>
-      </c>
-      <c r="D204" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E204" s="12" t="n">
-        <v>18900</v>
-      </c>
-    </row>
-    <row r="205" customHeight="1" ht="15" spans="1:1">
-      <c r="A205" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="206" customHeight="1" ht="15" spans="1:10">
-      <c r="A206" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B206" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C206" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D206" s="6" t="n">
-        <v>810</v>
-      </c>
-      <c r="E206" s="7" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="F206" s="7" t="n">
-        <v>16102.8</v>
-      </c>
-      <c r="G206" s="8">
-        <v>46133</v>
-      </c>
-      <c r="H206" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I206" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J206" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="207" customHeight="1" ht="15" spans="1:5">
-      <c r="A207" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B207" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C207" s="11" t="n">
-        <v>16102.8</v>
-      </c>
-      <c r="D207" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E207" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A208" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209" customHeight="1" ht="15" spans="1:12">
-      <c r="A209" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D209" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E209" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F209" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G209" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H209" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I209" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J209" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K209" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L209" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="210" customHeight="1" ht="15" spans="1:1">
-      <c r="A210" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="211" customHeight="1" ht="15" spans="1:10">
-      <c r="A211" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B211" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C211" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D211" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E211" s="7" t="n">
-        <v>18.45</v>
-      </c>
-      <c r="F211" s="7" t="n">
-        <v>3690</v>
-      </c>
-      <c r="G211" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H211" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I211" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J211" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="212" customHeight="1" ht="15" spans="1:5">
-      <c r="A212" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B212" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C212" s="11" t="n">
-        <v>3690</v>
-      </c>
-      <c r="D212" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E212" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A213" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" customHeight="1" ht="15" spans="1:12">
-      <c r="A214" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D214" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E214" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F214" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G214" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H214" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I214" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J214" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K214" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L214" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="215" customHeight="1" ht="15" spans="1:1">
-      <c r="A215" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="216" customHeight="1" ht="15" spans="1:10">
-      <c r="A216" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B216" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C216" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D216" s="6" t="n">
-        <v>2016</v>
-      </c>
-      <c r="E216" s="7" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F216" s="7" t="n">
+    <row r="224" customHeight="1" ht="15" spans="1:5">
+      <c r="A224" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B224" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C224" s="11" t="n">
         <v>14091.84</v>
       </c>
-      <c r="G216" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H216" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I216" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J216" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="217" customHeight="1" ht="15" spans="1:5">
-      <c r="A217" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B217" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C217" s="11" t="n">
-        <v>14091.84</v>
-      </c>
-      <c r="D217" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E217" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" customHeight="1" ht="15" spans="1:1">
-      <c r="A218" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="219" customHeight="1" ht="15" spans="1:10">
-      <c r="A219" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B219" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C219" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D219" s="6" t="n">
-        <v>224</v>
-      </c>
-      <c r="E219" s="7" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F219" s="7" t="n">
-        <v>3740.8</v>
-      </c>
-      <c r="G219" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H219" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I219" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J219" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="220" customHeight="1" ht="15" spans="1:5">
-      <c r="A220" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B220" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C220" s="11" t="n">
-        <v>3740.8</v>
-      </c>
-      <c r="D220" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E220" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" customHeight="1" ht="15" spans="1:1">
-      <c r="A221" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="222" customHeight="1" ht="15" spans="1:10">
-      <c r="A222" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B222" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C222" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D222" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E222" s="7" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F222" s="7" t="n">
-        <v>4278</v>
-      </c>
-      <c r="G222" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H222" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I222" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J222" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="223" customHeight="1" ht="15" spans="1:5">
-      <c r="A223" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B223" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C223" s="11" t="n">
-        <v>4278</v>
-      </c>
-      <c r="D223" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E223" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" customHeight="1" ht="15" spans="1:1">
-      <c r="A224" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="225" customHeight="1" ht="15" spans="1:10">
-      <c r="A225" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B225" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D225" s="6" t="n">
-        <v>1024</v>
-      </c>
-      <c r="E225" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="F225" s="7" t="n">
-        <v>16281.6</v>
-      </c>
-      <c r="G225" s="8">
-        <v>46125</v>
-      </c>
-      <c r="H225" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I225" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J225" s="6" t="s">
-        <v>91</v>
+      <c r="D224" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E224" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" customHeight="1" ht="15" spans="1:1">
+      <c r="A225" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="226" customHeight="1" ht="15" spans="1:10">
@@ -5280,22 +5283,22 @@
         <v>14</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C226" s="5" t="s">
         <v>138</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>2016</v>
+        <v>1024</v>
       </c>
       <c r="E226" s="7" t="n">
-        <v>15.9</v>
+        <v>16.9</v>
       </c>
       <c r="F226" s="7" t="n">
-        <v>32054.4</v>
+        <v>17305.6</v>
       </c>
       <c r="G226" s="8">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="H226" s="6" t="n">
         <v>0</v>
@@ -5304,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="J226" s="6" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
     </row>
     <row r="227" customHeight="1" ht="15" spans="1:5">
@@ -5315,7 +5318,7 @@
         <v>19</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>48336</v>
+        <v>17305.6</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>18</v>
@@ -5324,160 +5327,160 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A228" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" customHeight="1" ht="15" spans="1:12">
-      <c r="A229" s="2" t="s">
+    <row r="228" customHeight="1" ht="15" spans="1:1">
+      <c r="A228" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" ht="15" spans="1:10">
+      <c r="A229" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D229" s="6" t="n">
+        <v>224</v>
+      </c>
+      <c r="E229" s="7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F229" s="7" t="n">
+        <v>3740.8</v>
+      </c>
+      <c r="G229" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H229" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I229" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="230" customHeight="1" ht="15" spans="1:5">
+      <c r="A230" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C230" s="11" t="n">
+        <v>3740.8</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E230" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" customHeight="1" ht="15" spans="1:1">
+      <c r="A231" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" ht="15" spans="1:10">
+      <c r="A232" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D232" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E232" s="7" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="F232" s="7" t="n">
+        <v>4278</v>
+      </c>
+      <c r="G232" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H232" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I232" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" ht="15" spans="1:5">
+      <c r="A233" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B233" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C233" s="11" t="n">
+        <v>4278</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E233" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A234" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" ht="15" spans="1:12">
+      <c r="A235" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B229" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C229" s="2" t="s">
+      <c r="B235" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C235" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D229" s="2" t="s">
+      <c r="D235" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E229" s="3" t="s">
+      <c r="E235" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F229" s="3" t="s">
+      <c r="F235" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G229" s="3" t="s">
+      <c r="G235" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H229" s="3" t="s">
+      <c r="H235" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I229" s="3" t="s">
+      <c r="I235" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J229" s="3" t="s">
+      <c r="J235" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K229" s="2" t="s">
+      <c r="K235" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L229" s="3" t="s">
+      <c r="L235" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="230" customHeight="1" ht="15" spans="1:1">
-      <c r="A230" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="231" customHeight="1" ht="15" spans="1:10">
-      <c r="A231" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B231" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D231" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E231" s="7" t="n">
-        <v>14.46</v>
-      </c>
-      <c r="F231" s="7" t="n">
-        <v>14460</v>
-      </c>
-      <c r="G231" s="8">
-        <v>46126</v>
-      </c>
-      <c r="H231" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I231" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J231" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="232" customHeight="1" ht="15" spans="1:5">
-      <c r="A232" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B232" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C232" s="11" t="n">
-        <v>14460</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E232" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" customHeight="1" ht="15" spans="1:1">
-      <c r="A233" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="234" customHeight="1" ht="15" spans="1:10">
-      <c r="A234" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B234" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C234" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D234" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E234" s="7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F234" s="7" t="n">
-        <v>27000</v>
-      </c>
-      <c r="G234" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H234" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I234" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J234" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="235" customHeight="1" ht="15" spans="1:5">
-      <c r="A235" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B235" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C235" s="11" t="n">
-        <v>27000</v>
-      </c>
-      <c r="D235" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E235" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="236" customHeight="1" ht="15" spans="1:1">
       <c r="A236" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="237" customHeight="1" ht="15" spans="1:10">
@@ -5485,107 +5488,128 @@
         <v>14</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>360</v>
+        <v>1024</v>
       </c>
       <c r="E237" s="7" t="n">
-        <v>6.99</v>
+        <v>15.9</v>
       </c>
       <c r="F237" s="7" t="n">
-        <v>2516.4</v>
+        <v>16281.6</v>
       </c>
       <c r="G237" s="8">
+        <v>46125</v>
+      </c>
+      <c r="H237" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I237" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="238" customHeight="1" ht="15" spans="1:10">
+      <c r="A238" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D238" s="6" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E238" s="7" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F238" s="7" t="n">
+        <v>32054.4</v>
+      </c>
+      <c r="G238" s="8">
         <v>46132</v>
       </c>
-      <c r="H237" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I237" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J237" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="238" customHeight="1" ht="15" spans="1:5">
-      <c r="A238" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B238" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C238" s="11" t="n">
-        <v>2516.4</v>
-      </c>
-      <c r="D238" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E238" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" customHeight="1" ht="15" spans="1:1">
-      <c r="A239" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="240" customHeight="1" ht="15" spans="1:10">
-      <c r="A240" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B240" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C240" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D240" s="6" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E240" s="7" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F240" s="7" t="n">
-        <v>7549.2</v>
-      </c>
-      <c r="G240" s="8">
-        <v>46133</v>
-      </c>
-      <c r="H240" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I240" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J240" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="241" customHeight="1" ht="15" spans="1:5">
-      <c r="A241" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B241" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C241" s="11" t="n">
-        <v>7549.2</v>
-      </c>
-      <c r="D241" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E241" s="12" t="n">
-        <v>0</v>
+      <c r="H238" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I238" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="239" customHeight="1" ht="15" spans="1:5">
+      <c r="A239" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B239" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C239" s="11" t="n">
+        <v>48336</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E239" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A240" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" customHeight="1" ht="15" spans="1:12">
+      <c r="A241" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H241" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I241" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J241" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K241" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L241" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="242" customHeight="1" ht="15" spans="1:1">
       <c r="A242" s="2" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
     </row>
     <row r="243" customHeight="1" ht="15" spans="1:10">
@@ -5593,22 +5617,22 @@
         <v>14</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D243" s="6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E243" s="7" t="n">
-        <v>10.5</v>
+        <v>14.46</v>
       </c>
       <c r="F243" s="7" t="n">
-        <v>5250</v>
+        <v>14460</v>
       </c>
       <c r="G243" s="8">
-        <v>46132</v>
+        <v>46126</v>
       </c>
       <c r="H243" s="6" t="n">
         <v>0</v>
@@ -5617,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="J243" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="244" customHeight="1" ht="15" spans="1:5">
@@ -5628,201 +5652,180 @@
         <v>19</v>
       </c>
       <c r="C244" s="11" t="n">
+        <v>14460</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E244" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" customHeight="1" ht="15" spans="1:1">
+      <c r="A245" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="246" customHeight="1" ht="15" spans="1:10">
+      <c r="A246" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D246" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E246" s="7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F246" s="7" t="n">
+        <v>27000</v>
+      </c>
+      <c r="G246" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H246" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I246" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="247" customHeight="1" ht="15" spans="1:5">
+      <c r="A247" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B247" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C247" s="11" t="n">
+        <v>27000</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E247" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" customHeight="1" ht="15" spans="1:1">
+      <c r="A248" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="249" customHeight="1" ht="15" spans="1:10">
+      <c r="A249" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D249" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="E249" s="7" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F249" s="7" t="n">
+        <v>2516.4</v>
+      </c>
+      <c r="G249" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H249" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I249" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="250" customHeight="1" ht="15" spans="1:5">
+      <c r="A250" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B250" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C250" s="11" t="n">
+        <v>2516.4</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E250" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" customHeight="1" ht="15" spans="1:1">
+      <c r="A251" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="252" customHeight="1" ht="15" spans="1:10">
+      <c r="A252" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D252" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="E252" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F252" s="7" t="n">
         <v>5250</v>
       </c>
-      <c r="D244" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E244" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A245" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246" customHeight="1" ht="15" spans="1:12">
-      <c r="A246" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E246" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F246" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G246" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H246" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I246" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J246" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K246" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L246" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="247" customHeight="1" ht="15" spans="1:1">
-      <c r="A247" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="248" customHeight="1" ht="15" spans="1:10">
-      <c r="A248" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B248" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C248" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D248" s="6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E248" s="7" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="F248" s="7" t="n">
-        <v>8802</v>
-      </c>
-      <c r="G248" s="8">
-        <v>46099</v>
-      </c>
-      <c r="H248" s="6" t="n">
-        <v>1008</v>
-      </c>
-      <c r="I248" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="J248" s="6" t="s">
+      <c r="G252" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H252" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I252" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="253" customHeight="1" ht="15" spans="1:5">
+      <c r="A253" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B253" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C253" s="11" t="n">
+        <v>5250</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E253" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" customHeight="1" ht="15" spans="1:1">
+      <c r="A254" s="2" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="249" customHeight="1" ht="15" spans="1:5">
-      <c r="A249" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B249" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C249" s="11" t="n">
-        <v>8802</v>
-      </c>
-      <c r="D249" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E249" s="12" t="n">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="250" customHeight="1" ht="15" spans="1:1">
-      <c r="A250" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="251" customHeight="1" ht="15" spans="1:10">
-      <c r="A251" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B251" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C251" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D251" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E251" s="7" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="F251" s="7" t="n">
-        <v>3218</v>
-      </c>
-      <c r="G251" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H251" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I251" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J251" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="252" customHeight="1" ht="15" spans="1:5">
-      <c r="A252" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B252" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C252" s="11" t="n">
-        <v>3218</v>
-      </c>
-      <c r="D252" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E252" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" customHeight="1" ht="15" spans="1:1">
-      <c r="A253" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="254" customHeight="1" ht="15" spans="1:10">
-      <c r="A254" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B254" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C254" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D254" s="6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E254" s="7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F254" s="7" t="n">
-        <v>36600</v>
-      </c>
-      <c r="G254" s="8">
-        <v>46125</v>
-      </c>
-      <c r="H254" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I254" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J254" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="255" customHeight="1" ht="15" spans="1:10">
@@ -5830,31 +5833,31 @@
         <v>14</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D255" s="6" t="n">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="E255" s="7" t="n">
-        <v>12.2</v>
+        <v>4.89</v>
       </c>
       <c r="F255" s="7" t="n">
-        <v>24400</v>
+        <v>8802</v>
       </c>
       <c r="G255" s="8">
-        <v>46132</v>
+        <v>46099</v>
       </c>
       <c r="H255" s="6" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="I255" s="9" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J255" s="6" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
     </row>
     <row r="256" customHeight="1" ht="15" spans="1:5">
@@ -5865,66 +5868,249 @@
         <v>19</v>
       </c>
       <c r="C256" s="11" t="n">
+        <v>8802</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E256" s="12" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="257" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A257" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" customHeight="1" ht="15" spans="1:12">
+      <c r="A258" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H258" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I258" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J258" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K258" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L258" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="259" customHeight="1" ht="15" spans="1:1">
+      <c r="A259" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="260" customHeight="1" ht="15" spans="1:10">
+      <c r="A260" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D260" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E260" s="7" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="F260" s="7" t="n">
+        <v>3218</v>
+      </c>
+      <c r="G260" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H260" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I260" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="261" customHeight="1" ht="15" spans="1:5">
+      <c r="A261" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B261" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C261" s="11" t="n">
+        <v>3218</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E261" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" customHeight="1" ht="15" spans="1:1">
+      <c r="A262" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="263" customHeight="1" ht="15" spans="1:10">
+      <c r="A263" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D263" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E263" s="7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F263" s="7" t="n">
+        <v>36600</v>
+      </c>
+      <c r="G263" s="8">
+        <v>46125</v>
+      </c>
+      <c r="H263" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="264" customHeight="1" ht="15" spans="1:10">
+      <c r="A264" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D264" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E264" s="7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F264" s="7" t="n">
+        <v>24400</v>
+      </c>
+      <c r="G264" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H264" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="265" customHeight="1" ht="15" spans="1:5">
+      <c r="A265" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B265" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C265" s="11" t="n">
         <v>61000</v>
       </c>
-      <c r="D256" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E256" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" customHeight="1" ht="15" spans="1:1">
-      <c r="A257" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="258" customHeight="1" ht="15" spans="1:10">
-      <c r="A258" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B258" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C258" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D258" s="6" t="n">
+      <c r="D265" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E265" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" customHeight="1" ht="15" spans="1:1">
+      <c r="A266" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="267" customHeight="1" ht="15" spans="1:10">
+      <c r="A267" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D267" s="6" t="n">
         <v>520</v>
       </c>
-      <c r="E258" s="7" t="n">
+      <c r="E267" s="7" t="n">
         <v>13.2</v>
       </c>
-      <c r="F258" s="7" t="n">
+      <c r="F267" s="7" t="n">
         <v>6864</v>
       </c>
-      <c r="G258" s="8">
+      <c r="G267" s="8">
         <v>46132</v>
       </c>
-      <c r="H258" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I258" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J258" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="259" customHeight="1" ht="15" spans="1:5">
-      <c r="A259" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B259" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C259" s="11" t="n">
+      <c r="H267" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="268" customHeight="1" ht="15" spans="1:5">
+      <c r="A268" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B268" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C268" s="11" t="n">
         <v>6864</v>
       </c>
-      <c r="D259" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E259" s="12" t="n">
+      <c r="D268" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E268" s="12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="150">
   <si>
     <t>MATRIZ CNPJ: 40.357.820/0001-50R Y DOIS - 58082-025
  ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
@@ -218,12 +218,6 @@
     <t>1665 - ATADURA DE CREPE 13 FIOS 30 X 1,80  PCT 12</t>
   </si>
   <si>
-    <t>SABRINA MARTHA RAMALHO MENDES COM. DE ART. MED. LTDA</t>
-  </si>
-  <si>
-    <t>779</t>
-  </si>
-  <si>
     <t>TOUREIROFARMA</t>
   </si>
   <si>
@@ -251,15 +245,15 @@
     <t>ELIENE RESENDE</t>
   </si>
   <si>
+    <t>ZOE MED</t>
+  </si>
+  <si>
+    <t>766</t>
+  </si>
+  <si>
     <t xml:space="preserve">1588 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND </t>
   </si>
   <si>
-    <t>ZOE MED</t>
-  </si>
-  <si>
-    <t>766</t>
-  </si>
-  <si>
     <t>JOSEMAR</t>
   </si>
   <si>
@@ -371,9 +365,6 @@
     <t xml:space="preserve">132 - GAZE CIRCULAR NAO ESTERIL 09 FIOS </t>
   </si>
   <si>
-    <t xml:space="preserve">85 - GAZE CIRCULAR NAO ESTERIL 09 FIOS </t>
-  </si>
-  <si>
     <t>GAZE EM ROLO - 13 FIOS</t>
   </si>
   <si>
@@ -398,22 +389,22 @@
     <t>282 - GAZE CIRCULAR NAO ESTERIL 13 FIOS JA</t>
   </si>
   <si>
+    <t>NACIONAL COMERCIO E REPRESENTACAO</t>
+  </si>
+  <si>
+    <t>644</t>
+  </si>
+  <si>
+    <t>277 - GAZE CIRCULAR NAO ESTERIL 13 FIOS EA</t>
+  </si>
+  <si>
+    <t>PROMED HOSPITALAR</t>
+  </si>
+  <si>
+    <t>777</t>
+  </si>
+  <si>
     <t>279 - GAZE CIRCULAR NAO ESTERIL 13 FIOS GA</t>
-  </si>
-  <si>
-    <t>NACIONAL COMERCIO E REPRESENTACAO</t>
-  </si>
-  <si>
-    <t>644</t>
-  </si>
-  <si>
-    <t>277 - GAZE CIRCULAR NAO ESTERIL 13 FIOS EA</t>
-  </si>
-  <si>
-    <t>PROMED HOSPITALAR</t>
-  </si>
-  <si>
-    <t>777</t>
   </si>
   <si>
     <t>PCT NÃO EST. - 11 FIOS</t>
@@ -629,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L268"/>
+  <dimension ref="A1:L241"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
   <cols>
     <col customWidth="1" width="89.23828125" min="1" max="1"/>
@@ -1553,13 +1544,13 @@
         <v>27</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>5.99</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>2066.55</v>
+        <v>2396</v>
       </c>
       <c r="G41" s="8">
         <v>46134</v>
@@ -1585,13 +1576,13 @@
         <v>28</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>7.55</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>1510</v>
+        <v>2038.5</v>
       </c>
       <c r="G42" s="8">
         <v>46134</v>
@@ -1617,13 +1608,13 @@
         <v>29</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>340</v>
+        <v>375</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>8.84</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>3005.6</v>
+        <v>3315</v>
       </c>
       <c r="G43" s="8">
         <v>46134</v>
@@ -1649,13 +1640,13 @@
         <v>30</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>11.46</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>2292</v>
+        <v>2750.4</v>
       </c>
       <c r="G44" s="8">
         <v>46134</v>
@@ -1710,7 +1701,7 @@
         <v>19</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>12156.15</v>
+        <v>13781.9</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>18</v>
@@ -2428,179 +2419,179 @@
         <v>69</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D75" s="6" t="n">
+        <v>330</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>1620.3</v>
+      </c>
+      <c r="G75" s="8">
+        <v>46076</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" ht="15" spans="1:10">
+      <c r="A76" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E75" s="7" t="n">
-        <v>9.37</v>
-      </c>
-      <c r="F75" s="7" t="n">
-        <v>655.9</v>
-      </c>
-      <c r="G75" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" ht="15" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B76" s="10" t="s">
+      <c r="D76" s="6" t="n">
+        <v>660</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>3240.6</v>
+      </c>
+      <c r="G76" s="8">
+        <v>46107</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" ht="15" spans="1:5">
+      <c r="A77" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B77" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C76" s="11" t="n">
-        <v>655.9</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E76" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" ht="15" spans="1:1">
-      <c r="A77" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" ht="15" spans="1:10">
-      <c r="A78" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C78" s="5" t="s">
+      <c r="C77" s="11" t="n">
+        <v>4860.9</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E77" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A78" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" ht="15" spans="1:12">
+      <c r="A79" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D78" s="6" t="n">
-        <v>330</v>
-      </c>
-      <c r="E78" s="7" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="F78" s="7" t="n">
-        <v>1620.3</v>
-      </c>
-      <c r="G78" s="8">
-        <v>46076</v>
-      </c>
-      <c r="H78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" ht="15" spans="1:10">
-      <c r="A79" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B79" s="5" t="s">
+      <c r="C79" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" ht="15" spans="1:1">
+      <c r="A80" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D79" s="6" t="n">
-        <v>660</v>
-      </c>
-      <c r="E79" s="7" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="F79" s="7" t="n">
-        <v>3240.6</v>
-      </c>
-      <c r="G79" s="8">
-        <v>46107</v>
-      </c>
-      <c r="H79" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" ht="15" spans="1:5">
-      <c r="A80" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B80" s="10" t="s">
+    </row>
+    <row r="81" customHeight="1" ht="15" spans="1:10">
+      <c r="A81" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>200100</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>820410</v>
+      </c>
+      <c r="G81" s="8">
+        <v>46119</v>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" ht="15" spans="1:5">
+      <c r="A82" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B82" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C80" s="11" t="n">
-        <v>4860.9</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E80" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A81" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" ht="15" spans="1:12">
-      <c r="A82" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K82" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L82" s="3" t="s">
-        <v>12</v>
+      <c r="C82" s="11" t="n">
+        <v>820410</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E82" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83" customHeight="1" ht="15" spans="1:1">
       <c r="A83" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84" customHeight="1" ht="15" spans="1:10">
@@ -2608,31 +2599,31 @@
         <v>14</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>200100</v>
+        <v>600</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>820410</v>
+        <v>2880</v>
       </c>
       <c r="G84" s="8">
-        <v>46119</v>
+        <v>46132</v>
       </c>
       <c r="H84" s="6" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" customHeight="1" ht="15" spans="1:5">
@@ -2643,169 +2634,169 @@
         <v>19</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>820410</v>
+        <v>2880</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E85" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" ht="15" spans="1:1">
-      <c r="A86" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" ht="15" spans="1:10">
-      <c r="A87" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D87" s="6" t="n">
-        <v>1050</v>
-      </c>
-      <c r="E87" s="7" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="F87" s="7" t="n">
-        <v>6058.5</v>
-      </c>
-      <c r="G87" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="88" customHeight="1" ht="15" spans="1:5">
-      <c r="A88" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B88" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A86" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" ht="15" spans="1:12">
+      <c r="A87" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" ht="15" spans="1:1">
+      <c r="A88" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" ht="15" spans="1:10">
+      <c r="A89" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>204</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>9180</v>
+      </c>
+      <c r="G89" s="8">
+        <v>46127</v>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" ht="15" spans="1:5">
+      <c r="A90" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B90" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>6058.5</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E88" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" ht="15" spans="1:1">
-      <c r="A89" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="90" customHeight="1" ht="15" spans="1:10">
-      <c r="A90" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D90" s="6" t="n">
-        <v>600</v>
-      </c>
-      <c r="E90" s="7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F90" s="7" t="n">
-        <v>2880</v>
-      </c>
-      <c r="G90" s="8">
+      <c r="C90" s="11" t="n">
+        <v>9180</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" ht="15" spans="1:1">
+      <c r="A91" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" ht="15" spans="1:10">
+      <c r="A92" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D92" s="6" t="n">
+        <v>804</v>
+      </c>
+      <c r="E92" s="7" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="F92" s="7" t="n">
+        <v>36903.6</v>
+      </c>
+      <c r="G92" s="8">
         <v>46132</v>
       </c>
-      <c r="H90" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" ht="15" spans="1:5">
-      <c r="A91" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B91" s="10" t="s">
+      <c r="H92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" ht="15" spans="1:5">
+      <c r="A93" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B93" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C91" s="11" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E91" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A92" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" customHeight="1" ht="15" spans="1:12">
-      <c r="A93" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J93" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K93" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L93" s="3" t="s">
-        <v>12</v>
+      <c r="C93" s="11" t="n">
+        <v>36903.6</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E93" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94" customHeight="1" ht="15" spans="1:1">
       <c r="A94" s="2" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
     </row>
     <row r="95" customHeight="1" ht="15" spans="1:10">
@@ -2813,22 +2804,22 @@
         <v>14</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>204</v>
+        <v>648</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>45</v>
+        <v>45.8</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>9180</v>
+        <v>29678.4</v>
       </c>
       <c r="G95" s="8">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="H95" s="6" t="n">
         <v>0</v>
@@ -2848,7 +2839,7 @@
         <v>19</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>9180</v>
+        <v>29678.4</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>18</v>
@@ -2870,19 +2861,19 @@
         <v>88</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>804</v>
+        <v>1008</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>45.9</v>
+        <v>41</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>36903.6</v>
+        <v>41328</v>
       </c>
       <c r="G98" s="8">
-        <v>46132</v>
+        <v>46104</v>
       </c>
       <c r="H98" s="6" t="n">
         <v>0</v>
@@ -2902,7 +2893,7 @@
         <v>19</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>36903.6</v>
+        <v>41328</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>18</v>
@@ -2913,7 +2904,7 @@
     </row>
     <row r="100" customHeight="1" ht="15" spans="1:1">
       <c r="A100" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
     </row>
     <row r="101" customHeight="1" ht="15" spans="1:10">
@@ -2921,31 +2912,31 @@
         <v>14</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>648</v>
+        <v>1500</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>45.8</v>
+        <v>21.84</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>29678.4</v>
+        <v>32760</v>
       </c>
       <c r="G101" s="8">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>0</v>
+        <v>768</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>0</v>
+        <v>51.2</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="102" customHeight="1" ht="15" spans="1:5">
@@ -2956,633 +2947,654 @@
         <v>19</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>29678.4</v>
+        <v>32760</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" customHeight="1" ht="15" spans="1:1">
-      <c r="A103" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="104" customHeight="1" ht="15" spans="1:10">
-      <c r="A104" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D104" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="E104" s="7" t="n">
-        <v>55.09</v>
-      </c>
-      <c r="F104" s="7" t="n">
-        <v>1983.24</v>
-      </c>
-      <c r="G104" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H104" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="105" customHeight="1" ht="15" spans="1:5">
-      <c r="A105" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B105" s="10" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A103" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" ht="15" spans="1:12">
+      <c r="A104" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L104" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" ht="15" spans="1:1">
+      <c r="A105" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" ht="15" spans="1:10">
+      <c r="A106" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D106" s="6" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="F106" s="7" t="n">
+        <v>88176</v>
+      </c>
+      <c r="G106" s="8">
+        <v>46112</v>
+      </c>
+      <c r="H106" s="6" t="n">
+        <v>480</v>
+      </c>
+      <c r="I106" s="9" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="J106" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" ht="15" spans="1:5">
+      <c r="A107" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B107" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C105" s="11" t="n">
-        <v>1983.24</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" customHeight="1" ht="15" spans="1:1">
-      <c r="A106" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="107" customHeight="1" ht="15" spans="1:10">
-      <c r="A107" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D107" s="6" t="n">
-        <v>1008</v>
-      </c>
-      <c r="E107" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="F107" s="7" t="n">
-        <v>41328</v>
-      </c>
-      <c r="G107" s="8">
-        <v>46104</v>
-      </c>
-      <c r="H107" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="6" t="s">
+      <c r="C107" s="11" t="n">
+        <v>88176</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A108" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" ht="15" spans="1:12">
+      <c r="A109" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J109" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L109" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" ht="15" spans="1:1">
+      <c r="A110" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" ht="15" spans="1:10">
+      <c r="A111" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D111" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E111" s="7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F111" s="7" t="n">
+        <v>3700</v>
+      </c>
+      <c r="G111" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H111" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="108" customHeight="1" ht="15" spans="1:5">
-      <c r="A108" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B108" s="10" t="s">
+    <row r="112" customHeight="1" ht="15" spans="1:5">
+      <c r="A112" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B112" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C108" s="11" t="n">
-        <v>41328</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E108" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A109" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" customHeight="1" ht="15" spans="1:12">
-      <c r="A110" s="2" t="s">
+      <c r="C112" s="11" t="n">
+        <v>3700</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E112" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" ht="15" spans="1:1">
+      <c r="A113" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" ht="15" spans="1:10">
+      <c r="A114" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D114" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E114" s="7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F114" s="7" t="n">
+        <v>14800</v>
+      </c>
+      <c r="G114" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" ht="15" spans="1:5">
+      <c r="A115" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B115" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C115" s="11" t="n">
+        <v>14800</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" ht="15" spans="1:1">
+      <c r="A116" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" ht="15" spans="1:10">
+      <c r="A117" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D117" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E117" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F117" s="7" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G117" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H117" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I117" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="J117" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" ht="15" spans="1:5">
+      <c r="A118" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C118" s="11" t="n">
+        <v>10500</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E118" s="12" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A119" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" ht="15" spans="1:12">
+      <c r="A120" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C110" s="2" t="s">
+      <c r="B120" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="D120" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E110" s="3" t="s">
+      <c r="E120" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="F120" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G110" s="3" t="s">
+      <c r="G120" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H110" s="3" t="s">
+      <c r="H120" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I110" s="3" t="s">
+      <c r="I120" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J110" s="3" t="s">
+      <c r="J120" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K110" s="2" t="s">
+      <c r="K120" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L110" s="3" t="s">
+      <c r="L120" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="111" customHeight="1" ht="15" spans="1:1">
-      <c r="A111" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="112" customHeight="1" ht="15" spans="1:10">
-      <c r="A112" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D112" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E112" s="7" t="n">
-        <v>21.84</v>
-      </c>
-      <c r="F112" s="7" t="n">
-        <v>32760</v>
-      </c>
-      <c r="G112" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H112" s="6" t="n">
-        <v>768</v>
-      </c>
-      <c r="I112" s="9" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="J112" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="113" customHeight="1" ht="15" spans="1:5">
-      <c r="A113" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B113" s="10" t="s">
+    <row r="121" customHeight="1" ht="15" spans="1:1">
+      <c r="A121" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" ht="15" spans="1:10">
+      <c r="A122" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D122" s="6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E122" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F122" s="7" t="n">
+        <v>70000</v>
+      </c>
+      <c r="G122" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H122" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I122" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J122" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" ht="15" spans="1:5">
+      <c r="A123" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B123" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C113" s="11" t="n">
-        <v>32760</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E113" s="12" t="n">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="114" customHeight="1" ht="15" spans="1:1">
-      <c r="A114" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="115" customHeight="1" ht="15" spans="1:10">
-      <c r="A115" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D115" s="6" t="n">
-        <v>2004</v>
-      </c>
-      <c r="E115" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="F115" s="7" t="n">
-        <v>88176</v>
-      </c>
-      <c r="G115" s="8">
-        <v>46112</v>
-      </c>
-      <c r="H115" s="6" t="n">
-        <v>480</v>
-      </c>
-      <c r="I115" s="9" t="n">
-        <v>23.95</v>
-      </c>
-      <c r="J115" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="116" customHeight="1" ht="15" spans="1:5">
-      <c r="A116" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B116" s="10" t="s">
+      <c r="C123" s="11" t="n">
+        <v>70000</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" ht="15" spans="1:1">
+      <c r="A124" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" ht="15" spans="1:10">
+      <c r="A125" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D125" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E125" s="7" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="F125" s="7" t="n">
+        <v>19400</v>
+      </c>
+      <c r="G125" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" ht="15" spans="1:5">
+      <c r="A126" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B126" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C116" s="11" t="n">
-        <v>88176</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E116" s="12" t="n">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="117" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A117" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" customHeight="1" ht="15" spans="1:12">
-      <c r="A118" s="2" t="s">
+      <c r="C126" s="11" t="n">
+        <v>19400</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E126" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" ht="15" spans="1:1">
+      <c r="A127" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" ht="15" spans="1:10">
+      <c r="A128" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D128" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E128" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F128" s="7" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G128" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H128" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" ht="15" spans="1:5">
+      <c r="A129" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B129" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C129" s="11" t="n">
+        <v>3800</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E129" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" ht="15" spans="1:1">
+      <c r="A130" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" ht="15" spans="1:10">
+      <c r="A131" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D131" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E131" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F131" s="7" t="n">
+        <v>11400</v>
+      </c>
+      <c r="G131" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H131" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" ht="15" spans="1:5">
+      <c r="A132" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B132" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C132" s="11" t="n">
+        <v>11400</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E132" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A133" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" ht="15" spans="1:12">
+      <c r="A134" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C118" s="2" t="s">
+      <c r="B134" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D134" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E118" s="3" t="s">
+      <c r="E134" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F118" s="3" t="s">
+      <c r="F134" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G118" s="3" t="s">
+      <c r="G134" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H118" s="3" t="s">
+      <c r="H134" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I118" s="3" t="s">
+      <c r="I134" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J118" s="3" t="s">
+      <c r="J134" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K118" s="2" t="s">
+      <c r="K134" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L118" s="3" t="s">
+      <c r="L134" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="119" customHeight="1" ht="15" spans="1:1">
-      <c r="A119" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="120" customHeight="1" ht="15" spans="1:10">
-      <c r="A120" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D120" s="6" t="n">
-        <v>13000</v>
-      </c>
-      <c r="E120" s="7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F120" s="7" t="n">
-        <v>5460</v>
-      </c>
-      <c r="G120" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H120" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="121" customHeight="1" ht="15" spans="1:5">
-      <c r="A121" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B121" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C121" s="11" t="n">
-        <v>5460</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E121" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" customHeight="1" ht="15" spans="1:1">
-      <c r="A122" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="123" customHeight="1" ht="15" spans="1:10">
-      <c r="A123" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D123" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E123" s="7" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="F123" s="7" t="n">
-        <v>3700</v>
-      </c>
-      <c r="G123" s="8">
+    <row r="135" customHeight="1" ht="15" spans="1:1">
+      <c r="A135" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" ht="15" spans="1:10">
+      <c r="A136" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D136" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E136" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F136" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G136" s="8">
         <v>46132</v>
       </c>
-      <c r="H123" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="6" t="s">
+      <c r="H136" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="6" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="124" customHeight="1" ht="15" spans="1:5">
-      <c r="A124" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B124" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C124" s="11" t="n">
-        <v>3700</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E124" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" customHeight="1" ht="15" spans="1:1">
-      <c r="A125" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="126" customHeight="1" ht="15" spans="1:10">
-      <c r="A126" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D126" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E126" s="7" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="F126" s="7" t="n">
-        <v>14800</v>
-      </c>
-      <c r="G126" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H126" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="127" customHeight="1" ht="15" spans="1:5">
-      <c r="A127" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B127" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C127" s="11" t="n">
-        <v>14800</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E127" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" customHeight="1" ht="15" spans="1:1">
-      <c r="A128" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="129" customHeight="1" ht="15" spans="1:10">
-      <c r="A129" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D129" s="6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E129" s="7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F129" s="7" t="n">
-        <v>10500</v>
-      </c>
-      <c r="G129" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H129" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="130" customHeight="1" ht="15" spans="1:5">
-      <c r="A130" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B130" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C130" s="11" t="n">
-        <v>10500</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E130" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A131" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" customHeight="1" ht="15" spans="1:12">
-      <c r="A132" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F132" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G132" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H132" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I132" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J132" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K132" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L132" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="133" customHeight="1" ht="15" spans="1:1">
-      <c r="A133" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="134" customHeight="1" ht="15" spans="1:10">
-      <c r="A134" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D134" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="E134" s="7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F134" s="7" t="n">
-        <v>70000</v>
-      </c>
-      <c r="G134" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H134" s="6" t="n">
-        <v>18000</v>
-      </c>
-      <c r="I134" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J134" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="135" customHeight="1" ht="15" spans="1:5">
-      <c r="A135" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B135" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C135" s="11" t="n">
-        <v>70000</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E135" s="12" t="n">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="136" customHeight="1" ht="15" spans="1:1">
-      <c r="A136" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="137" customHeight="1" ht="15" spans="1:10">
@@ -3590,22 +3602,22 @@
         <v>14</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>1000</v>
+        <v>50000</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>450</v>
+        <v>20000</v>
       </c>
       <c r="G137" s="8">
-        <v>46134</v>
+        <v>46132</v>
       </c>
       <c r="H137" s="6" t="n">
         <v>0</v>
@@ -3614,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="J137" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
     <row r="138" customHeight="1" ht="15" spans="1:5">
@@ -3625,7 +3637,7 @@
         <v>19</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>450</v>
+        <v>40000</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>18</v>
@@ -3636,7 +3648,7 @@
     </row>
     <row r="139" customHeight="1" ht="15" spans="1:1">
       <c r="A139" s="2" t="s">
-        <v>55</v>
+        <v>105</v>
       </c>
     </row>
     <row r="140" customHeight="1" ht="15" spans="1:10">
@@ -3644,22 +3656,22 @@
         <v>14</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E140" s="7" t="n">
-        <v>0.485</v>
+        <v>0.42</v>
       </c>
       <c r="F140" s="7" t="n">
-        <v>19400</v>
+        <v>8400</v>
       </c>
       <c r="G140" s="8">
-        <v>46113</v>
+        <v>46132</v>
       </c>
       <c r="H140" s="6" t="n">
         <v>0</v>
@@ -3668,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="J140" s="6" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
     </row>
     <row r="141" customHeight="1" ht="15" spans="1:5">
@@ -3679,7 +3691,7 @@
         <v>19</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>19400</v>
+        <v>8400</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>18</v>
@@ -3690,7 +3702,7 @@
     </row>
     <row r="142" customHeight="1" ht="15" spans="1:1">
       <c r="A142" s="2" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
     </row>
     <row r="143" customHeight="1" ht="15" spans="1:10">
@@ -3698,22 +3710,22 @@
         <v>14</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="E143" s="7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F143" s="7" t="n">
-        <v>3800</v>
+        <v>9900</v>
       </c>
       <c r="G143" s="8">
-        <v>46132</v>
+        <v>46114</v>
       </c>
       <c r="H143" s="6" t="n">
         <v>0</v>
@@ -3722,7 +3734,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="6" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="144" customHeight="1" ht="15" spans="1:5">
@@ -3733,7 +3745,7 @@
         <v>19</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>3800</v>
+        <v>9900</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>18</v>
@@ -3744,7 +3756,7 @@
     </row>
     <row r="145" customHeight="1" ht="15" spans="1:1">
       <c r="A145" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="146" customHeight="1" ht="15" spans="1:10">
@@ -3752,22 +3764,22 @@
         <v>14</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D146" s="6" t="n">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="E146" s="7" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="F146" s="7" t="n">
-        <v>11400</v>
+        <v>42000</v>
       </c>
       <c r="G146" s="8">
-        <v>46132</v>
+        <v>46128</v>
       </c>
       <c r="H146" s="6" t="n">
         <v>0</v>
@@ -3776,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="J146" s="6" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="147" customHeight="1" ht="15" spans="1:5">
@@ -3787,7 +3799,7 @@
         <v>19</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>11400</v>
+        <v>42000</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>18</v>
@@ -3806,7 +3818,7 @@
         <v>1</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>3</v>
@@ -3841,7 +3853,7 @@
     </row>
     <row r="150" customHeight="1" ht="15" spans="1:1">
       <c r="A150" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="151" customHeight="1" ht="15" spans="1:10">
@@ -3849,19 +3861,19 @@
         <v>14</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="E151" s="7" t="n">
         <v>0.4</v>
       </c>
       <c r="F151" s="7" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="G151" s="8">
         <v>46132</v>
@@ -3873,266 +3885,266 @@
         <v>0</v>
       </c>
       <c r="J151" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" ht="15" spans="1:5">
+      <c r="A152" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C152" s="11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E152" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" ht="15" spans="1:1">
+      <c r="A153" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" ht="15" spans="1:10">
+      <c r="A154" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D154" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E154" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F154" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G154" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H154" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="152" customHeight="1" ht="15" spans="1:10">
-      <c r="A152" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D152" s="6" t="n">
+    <row r="155" customHeight="1" ht="15" spans="1:5">
+      <c r="A155" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B155" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C155" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E155" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" ht="15" spans="1:1">
+      <c r="A156" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" ht="15" spans="1:10">
+      <c r="A157" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D157" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="E152" s="7" t="n">
+      <c r="E157" s="7" t="n">
         <v>0.4</v>
       </c>
-      <c r="F152" s="7" t="n">
+      <c r="F157" s="7" t="n">
         <v>20000</v>
       </c>
-      <c r="G152" s="8">
+      <c r="G157" s="8">
         <v>46132</v>
       </c>
-      <c r="H152" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" s="6" t="s">
+      <c r="H157" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="153" customHeight="1" ht="15" spans="1:5">
-      <c r="A153" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B153" s="10" t="s">
+    <row r="158" customHeight="1" ht="15" spans="1:5">
+      <c r="A158" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B158" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="11" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D153" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E153" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" customHeight="1" ht="15" spans="1:1">
-      <c r="A154" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="155" customHeight="1" ht="15" spans="1:10">
-      <c r="A155" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D155" s="6" t="n">
+      <c r="C158" s="11" t="n">
         <v>20000</v>
       </c>
-      <c r="E155" s="7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F155" s="7" t="n">
-        <v>8400</v>
-      </c>
-      <c r="G155" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H155" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I155" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="156" customHeight="1" ht="15" spans="1:5">
-      <c r="A156" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B156" s="10" t="s">
+      <c r="D158" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E158" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A159" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" ht="15" spans="1:12">
+      <c r="A160" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J160" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K160" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L160" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" ht="15" spans="1:1">
+      <c r="A161" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" ht="15" spans="1:10">
+      <c r="A162" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D162" s="6" t="n">
+        <v>3024</v>
+      </c>
+      <c r="E162" s="7" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F162" s="7" t="n">
+        <v>37195.2</v>
+      </c>
+      <c r="G162" s="8">
+        <v>46127</v>
+      </c>
+      <c r="H162" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" ht="15" spans="1:5">
+      <c r="A163" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B163" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C156" s="11" t="n">
-        <v>8400</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E156" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" customHeight="1" ht="15" spans="1:1">
-      <c r="A157" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="158" customHeight="1" ht="15" spans="1:10">
-      <c r="A158" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B158" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D158" s="6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E158" s="7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="F158" s="7" t="n">
-        <v>9900</v>
-      </c>
-      <c r="G158" s="8">
-        <v>46114</v>
-      </c>
-      <c r="H158" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I158" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J158" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="159" customHeight="1" ht="15" spans="1:5">
-      <c r="A159" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B159" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C159" s="11" t="n">
-        <v>9900</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E159" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" customHeight="1" ht="15" spans="1:1">
-      <c r="A160" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="161" customHeight="1" ht="15" spans="1:10">
-      <c r="A161" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D161" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E161" s="7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F161" s="7" t="n">
-        <v>42000</v>
-      </c>
-      <c r="G161" s="8">
-        <v>46128</v>
-      </c>
-      <c r="H161" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J161" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="162" customHeight="1" ht="15" spans="1:5">
-      <c r="A162" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B162" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C162" s="11" t="n">
-        <v>42000</v>
-      </c>
-      <c r="D162" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E162" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A163" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" customHeight="1" ht="15" spans="1:12">
+      <c r="C163" s="11" t="n">
+        <v>37195.2</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E163" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" ht="15" spans="1:1">
       <c r="A164" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E164" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F164" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G164" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H164" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I164" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J164" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K164" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L164" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="165" customHeight="1" ht="15" spans="1:1">
-      <c r="A165" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" ht="15" spans="1:10">
+      <c r="A165" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D165" s="6" t="n">
+        <v>3024</v>
+      </c>
+      <c r="E165" s="7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F165" s="7" t="n">
+        <v>43848</v>
+      </c>
+      <c r="G165" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="166" customHeight="1" ht="15" spans="1:10">
@@ -4140,19 +4152,19 @@
         <v>14</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="D166" s="6" t="n">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="E166" s="7" t="n">
-        <v>0.47</v>
+        <v>18.85</v>
       </c>
       <c r="F166" s="7" t="n">
-        <v>1410</v>
+        <v>11310</v>
       </c>
       <c r="G166" s="8">
         <v>46134</v>
@@ -4164,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="J166" s="6" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="167" customHeight="1" ht="15" spans="1:5">
@@ -4175,7 +4187,7 @@
         <v>19</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>1410</v>
+        <v>55158</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>18</v>
@@ -4184,63 +4196,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" customHeight="1" ht="15" spans="1:1">
-      <c r="A168" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="169" customHeight="1" ht="15" spans="1:10">
-      <c r="A169" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D169" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E169" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F169" s="7" t="n">
-        <v>40000</v>
-      </c>
-      <c r="G169" s="8">
+    <row r="168" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A168" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" ht="15" spans="1:12">
+      <c r="A169" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H169" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I169" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J169" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K169" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L169" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" ht="15" spans="1:1">
+      <c r="A170" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="171" customHeight="1" ht="15" spans="1:10">
+      <c r="A171" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D171" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="E171" s="7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F171" s="7" t="n">
+        <v>7089</v>
+      </c>
+      <c r="G171" s="8">
         <v>46132</v>
       </c>
-      <c r="H169" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I169" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J169" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="170" customHeight="1" ht="15" spans="1:5">
-      <c r="A170" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B170" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C170" s="11" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D170" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E170" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" customHeight="1" ht="15" spans="1:1">
-      <c r="A171" s="2" t="s">
-        <v>61</v>
+      <c r="H171" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="172" customHeight="1" ht="15" spans="1:10">
@@ -4248,19 +4281,19 @@
         <v>14</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="D172" s="6" t="n">
-        <v>5000</v>
+        <v>510</v>
       </c>
       <c r="E172" s="7" t="n">
-        <v>0.4</v>
+        <v>13.9</v>
       </c>
       <c r="F172" s="7" t="n">
-        <v>2000</v>
+        <v>7089</v>
       </c>
       <c r="G172" s="8">
         <v>46132</v>
@@ -4283,7 +4316,7 @@
         <v>19</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>2000</v>
+        <v>14178</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>18</v>
@@ -4294,7 +4327,7 @@
     </row>
     <row r="174" customHeight="1" ht="15" spans="1:1">
       <c r="A174" s="2" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
     </row>
     <row r="175" customHeight="1" ht="15" spans="1:10">
@@ -4302,19 +4335,19 @@
         <v>14</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="D175" s="6" t="n">
-        <v>50000</v>
+        <v>5004</v>
       </c>
       <c r="E175" s="7" t="n">
-        <v>0.4</v>
+        <v>11.99</v>
       </c>
       <c r="F175" s="7" t="n">
-        <v>20000</v>
+        <v>59997.96</v>
       </c>
       <c r="G175" s="8">
         <v>46132</v>
@@ -4337,7 +4370,7 @@
         <v>19</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>20000</v>
+        <v>59997.96</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>18</v>
@@ -4348,7 +4381,7 @@
     </row>
     <row r="177" customHeight="1" ht="15" spans="1:1">
       <c r="A177" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
     </row>
     <row r="178" customHeight="1" ht="15" spans="1:10">
@@ -4356,22 +4389,22 @@
         <v>14</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="D178" s="6" t="n">
-        <v>1000</v>
+        <v>8010</v>
       </c>
       <c r="E178" s="7" t="n">
-        <v>0.42</v>
+        <v>20.79</v>
       </c>
       <c r="F178" s="7" t="n">
-        <v>420</v>
+        <v>166527.9</v>
       </c>
       <c r="G178" s="8">
-        <v>46134</v>
+        <v>46122</v>
       </c>
       <c r="H178" s="6" t="n">
         <v>0</v>
@@ -4391,7 +4424,7 @@
         <v>19</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>420</v>
+        <v>166527.9</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>18</v>
@@ -4400,106 +4433,106 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A180" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" customHeight="1" ht="15" spans="1:12">
-      <c r="A181" s="2" t="s">
+    <row r="180" customHeight="1" ht="15" spans="1:1">
+      <c r="A180" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" ht="15" spans="1:10">
+      <c r="A181" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D181" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E181" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F181" s="7" t="n">
+        <v>312000</v>
+      </c>
+      <c r="G181" s="8">
+        <v>46100</v>
+      </c>
+      <c r="H181" s="6" t="n">
+        <v>18900</v>
+      </c>
+      <c r="I181" s="9" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="J181" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" ht="15" spans="1:5">
+      <c r="A182" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C182" s="11" t="n">
+        <v>312000</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E182" s="12" t="n">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A183" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" ht="15" spans="1:12">
+      <c r="A184" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C181" s="2" t="s">
+      <c r="B184" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D181" s="2" t="s">
+      <c r="D184" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E181" s="3" t="s">
+      <c r="E184" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F181" s="3" t="s">
+      <c r="F184" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G181" s="3" t="s">
+      <c r="G184" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H181" s="3" t="s">
+      <c r="H184" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I181" s="3" t="s">
+      <c r="I184" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J181" s="3" t="s">
+      <c r="J184" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K181" s="2" t="s">
+      <c r="K184" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L181" s="3" t="s">
+      <c r="L184" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="182" customHeight="1" ht="15" spans="1:1">
-      <c r="A182" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="183" customHeight="1" ht="15" spans="1:10">
-      <c r="A183" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D183" s="6" t="n">
-        <v>3024</v>
-      </c>
-      <c r="E183" s="7" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="F183" s="7" t="n">
-        <v>37195.2</v>
-      </c>
-      <c r="G183" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H183" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I183" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J183" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="184" customHeight="1" ht="15" spans="1:5">
-      <c r="A184" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B184" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C184" s="11" t="n">
-        <v>37195.2</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E184" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="185" customHeight="1" ht="15" spans="1:1">
       <c r="A185" s="2" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
     </row>
     <row r="186" customHeight="1" ht="15" spans="1:10">
@@ -4507,22 +4540,22 @@
         <v>14</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>37</v>
+        <v>129</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D186" s="6" t="n">
-        <v>3024</v>
+        <v>810</v>
       </c>
       <c r="E186" s="7" t="n">
-        <v>14.5</v>
+        <v>19.88</v>
       </c>
       <c r="F186" s="7" t="n">
-        <v>43848</v>
+        <v>16102.8</v>
       </c>
       <c r="G186" s="8">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="H186" s="6" t="n">
         <v>0</v>
@@ -4531,190 +4564,169 @@
         <v>0</v>
       </c>
       <c r="J186" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="187" customHeight="1" ht="15" spans="1:10">
-      <c r="A187" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B187" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D187" s="6" t="n">
-        <v>600</v>
-      </c>
-      <c r="E187" s="7" t="n">
-        <v>18.85</v>
-      </c>
-      <c r="F187" s="7" t="n">
-        <v>11310</v>
-      </c>
-      <c r="G187" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" ht="15" spans="1:5">
+      <c r="A187" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B187" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C187" s="11" t="n">
+        <v>16102.8</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E187" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A188" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" ht="15" spans="1:12">
+      <c r="A189" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H189" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I189" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J189" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K189" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L189" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" ht="15" spans="1:1">
+      <c r="A190" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" ht="15" spans="1:10">
+      <c r="A191" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D191" s="6" t="n">
+        <v>224</v>
+      </c>
+      <c r="E191" s="7" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="F191" s="7" t="n">
+        <v>4132.8</v>
+      </c>
+      <c r="G191" s="8">
         <v>46134</v>
       </c>
-      <c r="H187" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I187" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J187" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="188" customHeight="1" ht="15" spans="1:5">
-      <c r="A188" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B188" s="10" t="s">
+      <c r="H191" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="192" customHeight="1" ht="15" spans="1:5">
+      <c r="A192" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B192" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C188" s="11" t="n">
-        <v>55158</v>
-      </c>
-      <c r="D188" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E188" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" customHeight="1" ht="15" spans="1:1">
-      <c r="A189" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="190" customHeight="1" ht="15" spans="1:10">
-      <c r="A190" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B190" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C190" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D190" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="E190" s="7" t="n">
-        <v>17.18</v>
-      </c>
-      <c r="F190" s="7" t="n">
-        <v>618.48</v>
-      </c>
-      <c r="G190" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H190" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I190" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J190" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="191" customHeight="1" ht="15" spans="1:5">
-      <c r="A191" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B191" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C191" s="11" t="n">
-        <v>618.48</v>
-      </c>
-      <c r="D191" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E191" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A192" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" customHeight="1" ht="15" spans="1:12">
-      <c r="A193" s="2" t="s">
+      <c r="C192" s="11" t="n">
+        <v>4132.8</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E192" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A193" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" customHeight="1" ht="15" spans="1:12">
+      <c r="A194" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B193" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C193" s="2" t="s">
+      <c r="B194" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C194" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D193" s="2" t="s">
+      <c r="D194" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E193" s="3" t="s">
+      <c r="E194" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F193" s="3" t="s">
+      <c r="F194" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G193" s="3" t="s">
+      <c r="G194" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H193" s="3" t="s">
+      <c r="H194" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I193" s="3" t="s">
+      <c r="I194" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J193" s="3" t="s">
+      <c r="J194" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K193" s="2" t="s">
+      <c r="K194" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L193" s="3" t="s">
+      <c r="L194" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="194" customHeight="1" ht="15" spans="1:1">
-      <c r="A194" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="195" customHeight="1" ht="15" spans="1:10">
-      <c r="A195" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B195" s="5" t="s">
+    <row r="195" customHeight="1" ht="15" spans="1:1">
+      <c r="A195" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="C195" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D195" s="6" t="n">
-        <v>510</v>
-      </c>
-      <c r="E195" s="7" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F195" s="7" t="n">
-        <v>7089</v>
-      </c>
-      <c r="G195" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H195" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I195" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J195" s="6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="196" customHeight="1" ht="15" spans="1:10">
@@ -4722,19 +4734,19 @@
         <v>14</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="D196" s="6" t="n">
-        <v>510</v>
+        <v>2016</v>
       </c>
       <c r="E196" s="7" t="n">
-        <v>13.9</v>
+        <v>6.99</v>
       </c>
       <c r="F196" s="7" t="n">
-        <v>7089</v>
+        <v>14091.84</v>
       </c>
       <c r="G196" s="8">
         <v>46132</v>
@@ -4757,7 +4769,7 @@
         <v>19</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>14178</v>
+        <v>14091.84</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>18</v>
@@ -4768,7 +4780,7 @@
     </row>
     <row r="198" customHeight="1" ht="15" spans="1:1">
       <c r="A198" s="2" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
     </row>
     <row r="199" customHeight="1" ht="15" spans="1:10">
@@ -4776,22 +4788,22 @@
         <v>14</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D199" s="6" t="n">
-        <v>5004</v>
+        <v>1024</v>
       </c>
       <c r="E199" s="7" t="n">
-        <v>11.99</v>
+        <v>16.9</v>
       </c>
       <c r="F199" s="7" t="n">
-        <v>59997.96</v>
+        <v>17305.6</v>
       </c>
       <c r="G199" s="8">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="H199" s="6" t="n">
         <v>0</v>
@@ -4800,7 +4812,7 @@
         <v>0</v>
       </c>
       <c r="J199" s="6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="200" customHeight="1" ht="15" spans="1:5">
@@ -4811,7 +4823,7 @@
         <v>19</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>59997.96</v>
+        <v>17305.6</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>18</v>
@@ -4822,7 +4834,7 @@
     </row>
     <row r="201" customHeight="1" ht="15" spans="1:1">
       <c r="A201" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="202" customHeight="1" ht="15" spans="1:10">
@@ -4830,22 +4842,22 @@
         <v>14</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D202" s="6" t="n">
-        <v>8010</v>
+        <v>224</v>
       </c>
       <c r="E202" s="7" t="n">
-        <v>20.79</v>
+        <v>16.7</v>
       </c>
       <c r="F202" s="7" t="n">
-        <v>166527.9</v>
+        <v>3740.8</v>
       </c>
       <c r="G202" s="8">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="H202" s="6" t="n">
         <v>0</v>
@@ -4854,7 +4866,7 @@
         <v>0</v>
       </c>
       <c r="J202" s="6" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
     </row>
     <row r="203" customHeight="1" ht="15" spans="1:5">
@@ -4865,7 +4877,7 @@
         <v>19</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>166527.9</v>
+        <v>3740.8</v>
       </c>
       <c r="D203" s="3" t="s">
         <v>18</v>
@@ -4887,16 +4899,16 @@
         <v>52</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>60</v>
+        <v>224</v>
       </c>
       <c r="E205" s="7" t="n">
-        <v>22.13</v>
+        <v>21.39</v>
       </c>
       <c r="F205" s="7" t="n">
-        <v>1327.8</v>
+        <v>4791.36</v>
       </c>
       <c r="G205" s="8">
         <v>46134</v>
@@ -4919,7 +4931,7 @@
         <v>19</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>1327.8</v>
+        <v>4791.36</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>18</v>
@@ -4938,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>3</v>
@@ -4973,7 +4985,7 @@
     </row>
     <row r="209" customHeight="1" ht="15" spans="1:1">
       <c r="A209" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="210" customHeight="1" ht="15" spans="1:10">
@@ -4981,506 +4993,527 @@
         <v>14</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>24000</v>
+        <v>1024</v>
       </c>
       <c r="E210" s="7" t="n">
-        <v>13</v>
+        <v>15.9</v>
       </c>
       <c r="F210" s="7" t="n">
-        <v>312000</v>
+        <v>16281.6</v>
       </c>
       <c r="G210" s="8">
-        <v>46100</v>
+        <v>46125</v>
       </c>
       <c r="H210" s="6" t="n">
-        <v>18900</v>
+        <v>0</v>
       </c>
       <c r="I210" s="9" t="n">
-        <v>78.75</v>
+        <v>0</v>
       </c>
       <c r="J210" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="211" customHeight="1" ht="15" spans="1:5">
-      <c r="A211" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B211" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="211" customHeight="1" ht="15" spans="1:10">
+      <c r="A211" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D211" s="6" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E211" s="7" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F211" s="7" t="n">
+        <v>32054.4</v>
+      </c>
+      <c r="G211" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H211" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="212" customHeight="1" ht="15" spans="1:5">
+      <c r="A212" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B212" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C211" s="11" t="n">
-        <v>312000</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E211" s="12" t="n">
-        <v>18900</v>
-      </c>
-    </row>
-    <row r="212" customHeight="1" ht="15" spans="1:1">
-      <c r="A212" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="213" customHeight="1" ht="15" spans="1:10">
-      <c r="A213" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B213" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C213" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D213" s="6" t="n">
-        <v>810</v>
-      </c>
-      <c r="E213" s="7" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="F213" s="7" t="n">
-        <v>16102.8</v>
-      </c>
-      <c r="G213" s="8">
+      <c r="C212" s="11" t="n">
+        <v>48336</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E212" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A213" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" customHeight="1" ht="15" spans="1:12">
+      <c r="A214" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H214" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J214" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K214" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L214" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215" customHeight="1" ht="15" spans="1:1">
+      <c r="A215" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="216" customHeight="1" ht="15" spans="1:10">
+      <c r="A216" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D216" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E216" s="7" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="F216" s="7" t="n">
+        <v>14460</v>
+      </c>
+      <c r="G216" s="8">
+        <v>46126</v>
+      </c>
+      <c r="H216" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" ht="15" spans="1:5">
+      <c r="A217" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B217" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C217" s="11" t="n">
+        <v>14460</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E217" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" ht="15" spans="1:1">
+      <c r="A218" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" ht="15" spans="1:10">
+      <c r="A219" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D219" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E219" s="7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F219" s="7" t="n">
+        <v>27000</v>
+      </c>
+      <c r="G219" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H219" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" ht="15" spans="1:5">
+      <c r="A220" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B220" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C220" s="11" t="n">
+        <v>27000</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E220" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" ht="15" spans="1:1">
+      <c r="A221" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="222" customHeight="1" ht="15" spans="1:10">
+      <c r="A222" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C222" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D222" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="E222" s="7" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F222" s="7" t="n">
+        <v>2516.4</v>
+      </c>
+      <c r="G222" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H222" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" ht="15" spans="1:5">
+      <c r="A223" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B223" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C223" s="11" t="n">
+        <v>2516.4</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E223" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" customHeight="1" ht="15" spans="1:1">
+      <c r="A224" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="225" customHeight="1" ht="15" spans="1:10">
+      <c r="A225" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D225" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="E225" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F225" s="7" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G225" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H225" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I225" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="226" customHeight="1" ht="15" spans="1:5">
+      <c r="A226" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B226" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C226" s="11" t="n">
+        <v>5250</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E226" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" customHeight="1" ht="15" spans="1:1">
+      <c r="A227" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="228" customHeight="1" ht="15" spans="1:10">
+      <c r="A228" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D228" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E228" s="7" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="F228" s="7" t="n">
+        <v>8802</v>
+      </c>
+      <c r="G228" s="8">
+        <v>46099</v>
+      </c>
+      <c r="H228" s="6" t="n">
+        <v>1008</v>
+      </c>
+      <c r="I228" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="J228" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" ht="15" spans="1:5">
+      <c r="A229" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B229" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C229" s="11" t="n">
+        <v>8802</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E229" s="12" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="230" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A230" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" customHeight="1" ht="15" spans="1:12">
+      <c r="A231" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H231" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J231" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K231" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L231" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" ht="15" spans="1:1">
+      <c r="A232" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" ht="15" spans="1:10">
+      <c r="A233" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D233" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E233" s="7" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="F233" s="7" t="n">
+        <v>3218</v>
+      </c>
+      <c r="G233" s="8">
         <v>46134</v>
       </c>
-      <c r="H213" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I213" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J213" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="214" customHeight="1" ht="15" spans="1:5">
-      <c r="A214" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B214" s="10" t="s">
+      <c r="H233" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" ht="15" spans="1:5">
+      <c r="A234" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B234" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C214" s="11" t="n">
-        <v>16102.8</v>
-      </c>
-      <c r="D214" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E214" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A215" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" customHeight="1" ht="15" spans="1:12">
-      <c r="A216" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E216" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F216" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G216" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H216" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I216" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J216" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K216" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L216" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="217" customHeight="1" ht="15" spans="1:1">
-      <c r="A217" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="218" customHeight="1" ht="15" spans="1:10">
-      <c r="A218" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B218" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C218" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D218" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E218" s="7" t="n">
-        <v>18.45</v>
-      </c>
-      <c r="F218" s="7" t="n">
-        <v>3690</v>
-      </c>
-      <c r="G218" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H218" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I218" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J218" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="219" customHeight="1" ht="15" spans="1:5">
-      <c r="A219" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B219" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C219" s="11" t="n">
-        <v>3690</v>
-      </c>
-      <c r="D219" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E219" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A220" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" customHeight="1" ht="15" spans="1:12">
-      <c r="A221" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E221" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F221" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G221" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H221" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I221" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J221" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K221" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L221" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="222" customHeight="1" ht="15" spans="1:1">
-      <c r="A222" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="223" customHeight="1" ht="15" spans="1:10">
-      <c r="A223" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B223" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C223" s="5" t="s">
+      <c r="C234" s="11" t="n">
+        <v>3218</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E234" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" ht="15" spans="1:1">
+      <c r="A235" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D223" s="6" t="n">
-        <v>2016</v>
-      </c>
-      <c r="E223" s="7" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F223" s="7" t="n">
-        <v>14091.84</v>
-      </c>
-      <c r="G223" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H223" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I223" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J223" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="224" customHeight="1" ht="15" spans="1:5">
-      <c r="A224" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B224" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C224" s="11" t="n">
-        <v>14091.84</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E224" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" customHeight="1" ht="15" spans="1:1">
-      <c r="A225" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="226" customHeight="1" ht="15" spans="1:10">
-      <c r="A226" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B226" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C226" s="5" t="s">
+    </row>
+    <row r="236" customHeight="1" ht="15" spans="1:10">
+      <c r="A236" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B236" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D226" s="6" t="n">
-        <v>1024</v>
-      </c>
-      <c r="E226" s="7" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="F226" s="7" t="n">
-        <v>17305.6</v>
-      </c>
-      <c r="G226" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H226" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I226" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J226" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="227" customHeight="1" ht="15" spans="1:5">
-      <c r="A227" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B227" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C227" s="11" t="n">
-        <v>17305.6</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E227" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" customHeight="1" ht="15" spans="1:1">
-      <c r="A228" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="229" customHeight="1" ht="15" spans="1:10">
-      <c r="A229" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B229" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D229" s="6" t="n">
-        <v>224</v>
-      </c>
-      <c r="E229" s="7" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F229" s="7" t="n">
-        <v>3740.8</v>
-      </c>
-      <c r="G229" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H229" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I229" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J229" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="230" customHeight="1" ht="15" spans="1:5">
-      <c r="A230" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B230" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C230" s="11" t="n">
-        <v>3740.8</v>
-      </c>
-      <c r="D230" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E230" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" customHeight="1" ht="15" spans="1:1">
-      <c r="A231" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="232" customHeight="1" ht="15" spans="1:10">
-      <c r="A232" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B232" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C232" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D232" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E232" s="7" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F232" s="7" t="n">
-        <v>4278</v>
-      </c>
-      <c r="G232" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H232" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I232" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J232" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="233" customHeight="1" ht="15" spans="1:5">
-      <c r="A233" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B233" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C233" s="11" t="n">
-        <v>4278</v>
-      </c>
-      <c r="D233" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E233" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A234" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" customHeight="1" ht="15" spans="1:12">
-      <c r="A235" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E235" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F235" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G235" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H235" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I235" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J235" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K235" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L235" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="236" customHeight="1" ht="15" spans="1:1">
-      <c r="A236" s="2" t="s">
-        <v>140</v>
+      <c r="C236" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D236" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E236" s="7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F236" s="7" t="n">
+        <v>36600</v>
+      </c>
+      <c r="G236" s="8">
+        <v>46125</v>
+      </c>
+      <c r="H236" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I236" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" s="6" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="237" customHeight="1" ht="15" spans="1:10">
@@ -5488,22 +5521,22 @@
         <v>14</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>1024</v>
+        <v>2000</v>
       </c>
       <c r="E237" s="7" t="n">
-        <v>15.9</v>
+        <v>12.2</v>
       </c>
       <c r="F237" s="7" t="n">
-        <v>16281.6</v>
+        <v>24400</v>
       </c>
       <c r="G237" s="8">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="H237" s="6" t="n">
         <v>0</v>
@@ -5512,606 +5545,78 @@
         <v>0</v>
       </c>
       <c r="J237" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="238" customHeight="1" ht="15" spans="1:10">
-      <c r="A238" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B238" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C238" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D238" s="6" t="n">
-        <v>2016</v>
-      </c>
-      <c r="E238" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="F238" s="7" t="n">
-        <v>32054.4</v>
-      </c>
-      <c r="G238" s="8">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="238" customHeight="1" ht="15" spans="1:5">
+      <c r="A238" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B238" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C238" s="11" t="n">
+        <v>61000</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E238" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" customHeight="1" ht="15" spans="1:1">
+      <c r="A239" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="240" customHeight="1" ht="15" spans="1:10">
+      <c r="A240" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D240" s="6" t="n">
+        <v>520</v>
+      </c>
+      <c r="E240" s="7" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F240" s="7" t="n">
+        <v>6864</v>
+      </c>
+      <c r="G240" s="8">
         <v>46132</v>
       </c>
-      <c r="H238" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I238" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J238" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="239" customHeight="1" ht="15" spans="1:5">
-      <c r="A239" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B239" s="10" t="s">
+      <c r="H240" s="6" t="n">
+        <v>280</v>
+      </c>
+      <c r="I240" s="9" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="J240" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="241" customHeight="1" ht="15" spans="1:5">
+      <c r="A241" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B241" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C239" s="11" t="n">
-        <v>48336</v>
-      </c>
-      <c r="D239" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E239" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A240" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" customHeight="1" ht="15" spans="1:12">
-      <c r="A241" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D241" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E241" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F241" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G241" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H241" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I241" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J241" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K241" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L241" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="242" customHeight="1" ht="15" spans="1:1">
-      <c r="A242" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="243" customHeight="1" ht="15" spans="1:10">
-      <c r="A243" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B243" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C243" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D243" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E243" s="7" t="n">
-        <v>14.46</v>
-      </c>
-      <c r="F243" s="7" t="n">
-        <v>14460</v>
-      </c>
-      <c r="G243" s="8">
-        <v>46126</v>
-      </c>
-      <c r="H243" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I243" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J243" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="244" customHeight="1" ht="15" spans="1:5">
-      <c r="A244" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B244" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C244" s="11" t="n">
-        <v>14460</v>
-      </c>
-      <c r="D244" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E244" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" customHeight="1" ht="15" spans="1:1">
-      <c r="A245" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="246" customHeight="1" ht="15" spans="1:10">
-      <c r="A246" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B246" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C246" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D246" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E246" s="7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F246" s="7" t="n">
-        <v>27000</v>
-      </c>
-      <c r="G246" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H246" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I246" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J246" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="247" customHeight="1" ht="15" spans="1:5">
-      <c r="A247" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B247" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C247" s="11" t="n">
-        <v>27000</v>
-      </c>
-      <c r="D247" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E247" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248" customHeight="1" ht="15" spans="1:1">
-      <c r="A248" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="249" customHeight="1" ht="15" spans="1:10">
-      <c r="A249" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B249" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C249" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D249" s="6" t="n">
-        <v>360</v>
-      </c>
-      <c r="E249" s="7" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F249" s="7" t="n">
-        <v>2516.4</v>
-      </c>
-      <c r="G249" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H249" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I249" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J249" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="250" customHeight="1" ht="15" spans="1:5">
-      <c r="A250" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B250" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C250" s="11" t="n">
-        <v>2516.4</v>
-      </c>
-      <c r="D250" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E250" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" customHeight="1" ht="15" spans="1:1">
-      <c r="A251" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="252" customHeight="1" ht="15" spans="1:10">
-      <c r="A252" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B252" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C252" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D252" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="E252" s="7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F252" s="7" t="n">
-        <v>5250</v>
-      </c>
-      <c r="G252" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H252" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I252" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J252" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="253" customHeight="1" ht="15" spans="1:5">
-      <c r="A253" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B253" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C253" s="11" t="n">
-        <v>5250</v>
-      </c>
-      <c r="D253" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E253" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" customHeight="1" ht="15" spans="1:1">
-      <c r="A254" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="255" customHeight="1" ht="15" spans="1:10">
-      <c r="A255" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B255" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C255" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D255" s="6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E255" s="7" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="F255" s="7" t="n">
-        <v>8802</v>
-      </c>
-      <c r="G255" s="8">
-        <v>46099</v>
-      </c>
-      <c r="H255" s="6" t="n">
-        <v>1008</v>
-      </c>
-      <c r="I255" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="J255" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="256" customHeight="1" ht="15" spans="1:5">
-      <c r="A256" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B256" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C256" s="11" t="n">
-        <v>8802</v>
-      </c>
-      <c r="D256" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E256" s="12" t="n">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="257" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A257" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" customHeight="1" ht="15" spans="1:12">
-      <c r="A258" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G258" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H258" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I258" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J258" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K258" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L258" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="259" customHeight="1" ht="15" spans="1:1">
-      <c r="A259" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="260" customHeight="1" ht="15" spans="1:10">
-      <c r="A260" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B260" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C260" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D260" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E260" s="7" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="F260" s="7" t="n">
-        <v>3218</v>
-      </c>
-      <c r="G260" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H260" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I260" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J260" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="261" customHeight="1" ht="15" spans="1:5">
-      <c r="A261" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B261" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C261" s="11" t="n">
-        <v>3218</v>
-      </c>
-      <c r="D261" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E261" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" customHeight="1" ht="15" spans="1:1">
-      <c r="A262" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="263" customHeight="1" ht="15" spans="1:10">
-      <c r="A263" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B263" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D263" s="6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E263" s="7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F263" s="7" t="n">
-        <v>36600</v>
-      </c>
-      <c r="G263" s="8">
-        <v>46125</v>
-      </c>
-      <c r="H263" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I263" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J263" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="264" customHeight="1" ht="15" spans="1:10">
-      <c r="A264" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B264" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C264" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D264" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E264" s="7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F264" s="7" t="n">
-        <v>24400</v>
-      </c>
-      <c r="G264" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H264" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I264" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J264" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="265" customHeight="1" ht="15" spans="1:5">
-      <c r="A265" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B265" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C265" s="11" t="n">
-        <v>61000</v>
-      </c>
-      <c r="D265" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E265" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" customHeight="1" ht="15" spans="1:1">
-      <c r="A266" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="267" customHeight="1" ht="15" spans="1:10">
-      <c r="A267" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B267" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C267" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D267" s="6" t="n">
-        <v>520</v>
-      </c>
-      <c r="E267" s="7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F267" s="7" t="n">
+      <c r="C241" s="11" t="n">
         <v>6864</v>
       </c>
-      <c r="G267" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H267" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I267" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J267" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="268" customHeight="1" ht="15" spans="1:5">
-      <c r="A268" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B268" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C268" s="11" t="n">
-        <v>6864</v>
-      </c>
-      <c r="D268" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E268" s="12" t="n">
-        <v>0</v>
+      <c r="D241" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E241" s="12" t="n">
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="159">
   <si>
     <t>MATRIZ CNPJ: 40.357.820/0001-50R Y DOIS - 58082-025
  ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
@@ -299,21 +299,15 @@
     <t>CAMPO - 45 X 50</t>
   </si>
   <si>
-    <t>DISTRIBUIDORA MAXIMUS</t>
-  </si>
-  <si>
-    <t>742</t>
+    <t>F F MELO MATERIAL MEDICO HOSPITALAR E ODONT.</t>
+  </si>
+  <si>
+    <t>764</t>
   </si>
   <si>
     <t>1586 - CAMPO OPERATORIO NAO ESTERIL 45X50 - PCT 50</t>
   </si>
   <si>
-    <t>F F MELO MATERIAL MEDICO HOSPITALAR E ODONT.</t>
-  </si>
-  <si>
-    <t>764</t>
-  </si>
-  <si>
     <t>MED &amp; FARMA DISTRIBUIDORA DE MEDICAMENTOS E PRODUTOS</t>
   </si>
   <si>
@@ -329,12 +323,6 @@
     <t>DANILO</t>
   </si>
   <si>
-    <t>VIRTUS COMERCIO DE PRODUTOS MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>681</t>
-  </si>
-  <si>
     <t>ESTERIL - 09 FIOS</t>
   </si>
   <si>
@@ -474,18 +462,6 @@
   </si>
   <si>
     <t xml:space="preserve">2080 - GAZE NAO ESTÉRIL 13 FIOS </t>
-  </si>
-  <si>
-    <t>MEDFASP SERVICOS &amp; COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2072 - GAZE NAO ESTÉRIL 13 FIOS </t>
-  </si>
-  <si>
-    <t>752</t>
   </si>
   <si>
     <t>PCT NÃO EST. - 9 FIOS</t>
@@ -671,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L276"/>
+  <dimension ref="A1:L258"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
   <cols>
     <col customWidth="1" width="89.23828125" min="1" max="1"/>
@@ -813,10 +789,10 @@
         <v>46122</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0</v>
+        <v>1760</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>0</v>
+        <v>23.26</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>23</v>
@@ -836,7 +812,7 @@
         <v>18</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>0</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="9" customHeight="1" ht="15" spans="1:1">
@@ -3107,25 +3083,25 @@
         <v>97</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>204</v>
+        <v>804</v>
       </c>
       <c r="E104" s="7" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="F104" s="7" t="n">
+        <v>36903.6</v>
+      </c>
+      <c r="G104" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="F104" s="7" t="n">
-        <v>9180</v>
-      </c>
-      <c r="G104" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H104" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="6" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="105" customHeight="1" ht="15" spans="1:5">
@@ -3136,7 +3112,7 @@
         <v>19</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>9180</v>
+        <v>36903.6</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>18</v>
@@ -3147,7 +3123,7 @@
     </row>
     <row r="106" customHeight="1" ht="15" spans="1:1">
       <c r="A106" s="2" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
     </row>
     <row r="107" customHeight="1" ht="15" spans="1:10">
@@ -3155,22 +3131,22 @@
         <v>14</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>97</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>804</v>
+        <v>648</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>36903.6</v>
+        <v>29678.4</v>
       </c>
       <c r="G107" s="8">
-        <v>46132</v>
+        <v>46128</v>
       </c>
       <c r="H107" s="6" t="n">
         <v>0</v>
@@ -3179,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="108" customHeight="1" ht="15" spans="1:5">
@@ -3190,7 +3166,7 @@
         <v>19</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>36903.6</v>
+        <v>29678.4</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>18</v>
@@ -3201,7 +3177,7 @@
     </row>
     <row r="109" customHeight="1" ht="15" spans="1:1">
       <c r="A109" s="2" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="110" customHeight="1" ht="15" spans="1:10">
@@ -3209,22 +3185,22 @@
         <v>14</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>97</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>648</v>
+        <v>1008</v>
       </c>
       <c r="E110" s="7" t="n">
-        <v>45.8</v>
+        <v>41</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>29678.4</v>
+        <v>41328</v>
       </c>
       <c r="G110" s="8">
-        <v>46128</v>
+        <v>46104</v>
       </c>
       <c r="H110" s="6" t="n">
         <v>0</v>
@@ -3233,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="111" customHeight="1" ht="15" spans="1:5">
@@ -3244,7 +3220,7 @@
         <v>19</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>29678.4</v>
+        <v>41328</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>18</v>
@@ -3269,25 +3245,25 @@
         <v>97</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>1008</v>
+        <v>1500</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>41</v>
+        <v>21.84</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>41328</v>
+        <v>32760</v>
       </c>
       <c r="G113" s="8">
-        <v>46104</v>
+        <v>46127</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>0</v>
+        <v>768</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>0</v>
+        <v>51.2</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
     </row>
     <row r="114" customHeight="1" ht="15" spans="1:5">
@@ -3298,115 +3274,115 @@
         <v>19</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>41328</v>
+        <v>32760</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" customHeight="1" ht="15" spans="1:1">
-      <c r="A115" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="116" customHeight="1" ht="15" spans="1:10">
-      <c r="A116" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B116" s="5" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A115" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" ht="15" spans="1:12">
+      <c r="A116" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C116" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D116" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E116" s="7" t="n">
-        <v>21.84</v>
-      </c>
-      <c r="F116" s="7" t="n">
-        <v>32760</v>
-      </c>
-      <c r="G116" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H116" s="6" t="n">
-        <v>768</v>
-      </c>
-      <c r="I116" s="9" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="J116" s="6" t="s">
+      <c r="C116" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L116" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" ht="15" spans="1:1">
+      <c r="A117" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" ht="15" spans="1:10">
+      <c r="A118" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C118" s="5" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="117" customHeight="1" ht="15" spans="1:5">
-      <c r="A117" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B117" s="10" t="s">
+      <c r="D118" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E118" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F118" s="7" t="n">
+        <v>2460</v>
+      </c>
+      <c r="G118" s="8">
+        <v>46135</v>
+      </c>
+      <c r="H118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" ht="15" spans="1:5">
+      <c r="A119" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B119" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C117" s="11" t="n">
-        <v>32760</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E117" s="12" t="n">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="118" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A118" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" customHeight="1" ht="15" spans="1:12">
-      <c r="A119" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G119" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J119" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K119" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L119" s="3" t="s">
-        <v>12</v>
+      <c r="C119" s="11" t="n">
+        <v>2460</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E119" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120" customHeight="1" ht="15" spans="1:1">
       <c r="A120" s="2" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
     </row>
     <row r="121" customHeight="1" ht="15" spans="1:10">
@@ -3414,31 +3390,31 @@
         <v>14</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>2004</v>
+        <v>10000</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>44</v>
+        <v>0.37</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>88176</v>
+        <v>3700</v>
       </c>
       <c r="G121" s="8">
-        <v>46112</v>
+        <v>46132</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>23.95</v>
+        <v>0</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
     </row>
     <row r="122" customHeight="1" ht="15" spans="1:5">
@@ -3449,169 +3425,169 @@
         <v>19</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>88176</v>
+        <v>3700</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="123" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A123" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" customHeight="1" ht="15" spans="1:12">
-      <c r="A124" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" ht="15" spans="1:1">
+      <c r="A123" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" ht="15" spans="1:10">
+      <c r="A124" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D124" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E124" s="7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F124" s="7" t="n">
+        <v>14800</v>
+      </c>
+      <c r="G124" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" ht="15" spans="1:5">
+      <c r="A125" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B125" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>14800</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E125" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" ht="15" spans="1:1">
+      <c r="A126" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" ht="15" spans="1:10">
+      <c r="A127" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D127" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E127" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F127" s="7" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G127" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H127" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I127" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="J127" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" ht="15" spans="1:5">
+      <c r="A128" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B128" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C128" s="11" t="n">
+        <v>10500</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E128" s="12" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A129" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" ht="15" spans="1:12">
+      <c r="A130" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C124" s="2" t="s">
+      <c r="B130" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="D130" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E124" s="3" t="s">
+      <c r="E130" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F124" s="3" t="s">
+      <c r="F130" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G124" s="3" t="s">
+      <c r="G130" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H124" s="3" t="s">
+      <c r="H130" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I124" s="3" t="s">
+      <c r="I130" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J124" s="3" t="s">
+      <c r="J130" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K124" s="2" t="s">
+      <c r="K130" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L124" s="3" t="s">
+      <c r="L130" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="125" customHeight="1" ht="15" spans="1:1">
-      <c r="A125" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="126" customHeight="1" ht="15" spans="1:10">
-      <c r="A126" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D126" s="6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E126" s="7" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="F126" s="7" t="n">
-        <v>2460</v>
-      </c>
-      <c r="G126" s="8">
-        <v>46135</v>
-      </c>
-      <c r="H126" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="127" customHeight="1" ht="15" spans="1:5">
-      <c r="A127" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B127" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C127" s="11" t="n">
-        <v>2460</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E127" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" customHeight="1" ht="15" spans="1:1">
-      <c r="A128" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="129" customHeight="1" ht="15" spans="1:10">
-      <c r="A129" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D129" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E129" s="7" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="F129" s="7" t="n">
-        <v>3700</v>
-      </c>
-      <c r="G129" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H129" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="130" customHeight="1" ht="15" spans="1:5">
-      <c r="A130" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B130" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C130" s="11" t="n">
-        <v>3700</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E130" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="131" customHeight="1" ht="15" spans="1:1">
       <c r="A131" s="2" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
     </row>
     <row r="132" customHeight="1" ht="15" spans="1:10">
@@ -3619,28 +3595,28 @@
         <v>14</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>40000</v>
+        <v>200000</v>
       </c>
       <c r="E132" s="7" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="F132" s="7" t="n">
-        <v>14800</v>
+        <v>70000</v>
       </c>
       <c r="G132" s="8">
         <v>46132</v>
       </c>
       <c r="H132" s="6" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J132" s="6" t="s">
         <v>45</v>
@@ -3654,18 +3630,18 @@
         <v>19</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>14800</v>
+        <v>70000</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E133" s="12" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="134" customHeight="1" ht="15" spans="1:1">
       <c r="A134" s="2" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
     </row>
     <row r="135" customHeight="1" ht="15" spans="1:10">
@@ -3673,31 +3649,31 @@
         <v>14</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>10500</v>
+        <v>7800</v>
       </c>
       <c r="G135" s="8">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="H135" s="6" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J135" s="6" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
     </row>
     <row r="136" customHeight="1" ht="15" spans="1:5">
@@ -3708,223 +3684,223 @@
         <v>19</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>10500</v>
+        <v>7800</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="137" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A137" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" customHeight="1" ht="15" spans="1:12">
-      <c r="A138" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" ht="15" spans="1:1">
+      <c r="A137" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" ht="15" spans="1:10">
+      <c r="A138" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D138" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E138" s="7" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="F138" s="7" t="n">
+        <v>19400</v>
+      </c>
+      <c r="G138" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H138" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" ht="15" spans="1:5">
+      <c r="A139" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B139" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C139" s="11" t="n">
+        <v>19400</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E139" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" ht="15" spans="1:1">
+      <c r="A140" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" ht="15" spans="1:10">
+      <c r="A141" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D141" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E141" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F141" s="7" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G141" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H141" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" ht="15" spans="1:5">
+      <c r="A142" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C142" s="11" t="n">
+        <v>3800</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E142" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" ht="15" spans="1:1">
+      <c r="A143" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" ht="15" spans="1:10">
+      <c r="A144" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D144" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E144" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F144" s="7" t="n">
+        <v>11400</v>
+      </c>
+      <c r="G144" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H144" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" ht="15" spans="1:5">
+      <c r="A145" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C145" s="11" t="n">
+        <v>11400</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E145" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A146" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" ht="15" spans="1:12">
+      <c r="A147" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C138" s="2" t="s">
+      <c r="B147" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="D147" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E138" s="3" t="s">
+      <c r="E147" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F138" s="3" t="s">
+      <c r="F147" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G138" s="3" t="s">
+      <c r="G147" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H138" s="3" t="s">
+      <c r="H147" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I138" s="3" t="s">
+      <c r="I147" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J138" s="3" t="s">
+      <c r="J147" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K138" s="2" t="s">
+      <c r="K147" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L138" s="3" t="s">
+      <c r="L147" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="139" customHeight="1" ht="15" spans="1:1">
-      <c r="A139" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="140" customHeight="1" ht="15" spans="1:10">
-      <c r="A140" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D140" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="E140" s="7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F140" s="7" t="n">
-        <v>70000</v>
-      </c>
-      <c r="G140" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H140" s="6" t="n">
-        <v>18000</v>
-      </c>
-      <c r="I140" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J140" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="141" customHeight="1" ht="15" spans="1:5">
-      <c r="A141" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B141" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C141" s="11" t="n">
-        <v>70000</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E141" s="12" t="n">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="142" customHeight="1" ht="15" spans="1:1">
-      <c r="A142" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="143" customHeight="1" ht="15" spans="1:10">
-      <c r="A143" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D143" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E143" s="7" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="F143" s="7" t="n">
-        <v>7800</v>
-      </c>
-      <c r="G143" s="8">
-        <v>46135</v>
-      </c>
-      <c r="H143" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="144" customHeight="1" ht="15" spans="1:5">
-      <c r="A144" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B144" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C144" s="11" t="n">
-        <v>7800</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E144" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" customHeight="1" ht="15" spans="1:1">
-      <c r="A145" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="146" customHeight="1" ht="15" spans="1:10">
-      <c r="A146" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D146" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E146" s="7" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="F146" s="7" t="n">
-        <v>19400</v>
-      </c>
-      <c r="G146" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H146" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="147" customHeight="1" ht="15" spans="1:5">
-      <c r="A147" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B147" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C147" s="11" t="n">
-        <v>19400</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E147" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="148" customHeight="1" ht="15" spans="1:1">
       <c r="A148" s="2" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
     </row>
     <row r="149" customHeight="1" ht="15" spans="1:10">
@@ -3932,22 +3908,22 @@
         <v>14</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D149" s="6" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="E149" s="7" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="F149" s="7" t="n">
-        <v>3800</v>
+        <v>20000</v>
       </c>
       <c r="G149" s="8">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="H149" s="6" t="n">
         <v>0</v>
@@ -3956,7 +3932,7 @@
         <v>0</v>
       </c>
       <c r="J149" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="150" customHeight="1" ht="15" spans="1:5">
@@ -3967,7 +3943,7 @@
         <v>19</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>3800</v>
+        <v>20000</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>18</v>
@@ -3976,343 +3952,343 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" customHeight="1" ht="15" spans="1:1">
-      <c r="A151" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="152" customHeight="1" ht="15" spans="1:10">
-      <c r="A152" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D152" s="6" t="n">
+    <row r="151" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A151" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" ht="15" spans="1:12">
+      <c r="A152" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J152" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L152" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" ht="15" spans="1:1">
+      <c r="A153" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" ht="15" spans="1:10">
+      <c r="A154" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D154" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E154" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F154" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G154" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H154" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" ht="15" spans="1:10">
+      <c r="A155" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D155" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E155" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F155" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G155" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H155" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" ht="15" spans="1:5">
+      <c r="A156" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C156" s="11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E156" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" ht="15" spans="1:1">
+      <c r="A157" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" ht="15" spans="1:10">
+      <c r="A158" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D158" s="6" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E158" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F158" s="7" t="n">
+        <v>26600</v>
+      </c>
+      <c r="G158" s="8">
+        <v>46135</v>
+      </c>
+      <c r="H158" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" ht="15" spans="1:5">
+      <c r="A159" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B159" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C159" s="11" t="n">
+        <v>26600</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E159" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" ht="15" spans="1:1">
+      <c r="A160" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" ht="15" spans="1:10">
+      <c r="A161" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D161" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E161" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F161" s="7" t="n">
+        <v>8400</v>
+      </c>
+      <c r="G161" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H161" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" ht="15" spans="1:5">
+      <c r="A162" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B162" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C162" s="11" t="n">
+        <v>8400</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E162" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" ht="15" spans="1:1">
+      <c r="A163" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" ht="15" spans="1:10">
+      <c r="A164" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D164" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="E152" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F152" s="7" t="n">
-        <v>11400</v>
-      </c>
-      <c r="G152" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H152" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="153" customHeight="1" ht="15" spans="1:5">
-      <c r="A153" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B153" s="10" t="s">
+      <c r="E164" s="7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F164" s="7" t="n">
+        <v>9900</v>
+      </c>
+      <c r="G164" s="8">
+        <v>46114</v>
+      </c>
+      <c r="H164" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" ht="15" spans="1:5">
+      <c r="A165" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B165" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="11" t="n">
-        <v>11400</v>
-      </c>
-      <c r="D153" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E153" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A154" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" customHeight="1" ht="15" spans="1:12">
-      <c r="A155" s="2" t="s">
+      <c r="C165" s="11" t="n">
+        <v>9900</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E165" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A166" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" ht="15" spans="1:12">
+      <c r="A167" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C155" s="2" t="s">
+      <c r="B167" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C167" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D155" s="2" t="s">
+      <c r="D167" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E155" s="3" t="s">
+      <c r="E167" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F155" s="3" t="s">
+      <c r="F167" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G155" s="3" t="s">
+      <c r="G167" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H155" s="3" t="s">
+      <c r="H167" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I155" s="3" t="s">
+      <c r="I167" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J155" s="3" t="s">
+      <c r="J167" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K155" s="2" t="s">
+      <c r="K167" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L155" s="3" t="s">
+      <c r="L167" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="156" customHeight="1" ht="15" spans="1:1">
-      <c r="A156" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="157" customHeight="1" ht="15" spans="1:10">
-      <c r="A157" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D157" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E157" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F157" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G157" s="8">
-        <v>46135</v>
-      </c>
-      <c r="H157" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I157" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="158" customHeight="1" ht="15" spans="1:5">
-      <c r="A158" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B158" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C158" s="11" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D158" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E158" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A159" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" customHeight="1" ht="15" spans="1:12">
-      <c r="A160" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E160" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F160" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G160" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H160" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I160" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J160" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K160" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L160" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="161" customHeight="1" ht="15" spans="1:1">
-      <c r="A161" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="162" customHeight="1" ht="15" spans="1:10">
-      <c r="A162" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B162" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D162" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E162" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F162" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G162" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H162" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="163" customHeight="1" ht="15" spans="1:10">
-      <c r="A163" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D163" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E163" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F163" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G163" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H163" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J163" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="164" customHeight="1" ht="15" spans="1:5">
-      <c r="A164" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B164" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C164" s="11" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D164" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E164" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" customHeight="1" ht="15" spans="1:1">
-      <c r="A165" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="166" customHeight="1" ht="15" spans="1:10">
-      <c r="A166" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B166" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D166" s="6" t="n">
-        <v>70000</v>
-      </c>
-      <c r="E166" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F166" s="7" t="n">
-        <v>26600</v>
-      </c>
-      <c r="G166" s="8">
-        <v>46135</v>
-      </c>
-      <c r="H166" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I166" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="167" customHeight="1" ht="15" spans="1:5">
-      <c r="A167" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B167" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C167" s="11" t="n">
-        <v>26600</v>
-      </c>
-      <c r="D167" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E167" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="168" customHeight="1" ht="15" spans="1:1">
       <c r="A168" s="2" t="s">
-        <v>121</v>
+        <v>61</v>
       </c>
     </row>
     <row r="169" customHeight="1" ht="15" spans="1:10">
@@ -4320,22 +4296,22 @@
         <v>14</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D169" s="6" t="n">
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="E169" s="7" t="n">
         <v>0.42</v>
       </c>
       <c r="F169" s="7" t="n">
-        <v>8400</v>
+        <v>42000</v>
       </c>
       <c r="G169" s="8">
-        <v>46132</v>
+        <v>46128</v>
       </c>
       <c r="H169" s="6" t="n">
         <v>0</v>
@@ -4344,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="J169" s="6" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
     </row>
     <row r="170" customHeight="1" ht="15" spans="1:5">
@@ -4355,7 +4331,7 @@
         <v>19</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>8400</v>
+        <v>42000</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>18</v>
@@ -4366,7 +4342,7 @@
     </row>
     <row r="171" customHeight="1" ht="15" spans="1:1">
       <c r="A171" s="2" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
     </row>
     <row r="172" customHeight="1" ht="15" spans="1:10">
@@ -4374,22 +4350,22 @@
         <v>14</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D172" s="6" t="n">
-        <v>30000</v>
+        <v>6000</v>
       </c>
       <c r="E172" s="7" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="F172" s="7" t="n">
-        <v>9900</v>
+        <v>2640</v>
       </c>
       <c r="G172" s="8">
-        <v>46114</v>
+        <v>46135</v>
       </c>
       <c r="H172" s="6" t="n">
         <v>0</v>
@@ -4398,7 +4374,7 @@
         <v>0</v>
       </c>
       <c r="J172" s="6" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
     </row>
     <row r="173" customHeight="1" ht="15" spans="1:5">
@@ -4409,7 +4385,7 @@
         <v>19</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>9900</v>
+        <v>2640</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>18</v>
@@ -4418,214 +4394,214 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A174" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" customHeight="1" ht="15" spans="1:12">
-      <c r="A175" s="2" t="s">
+    <row r="174" customHeight="1" ht="15" spans="1:1">
+      <c r="A174" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" ht="15" spans="1:10">
+      <c r="A175" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D175" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E175" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F175" s="7" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G175" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H175" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" ht="15" spans="1:5">
+      <c r="A176" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B176" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C176" s="11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E176" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" customHeight="1" ht="15" spans="1:1">
+      <c r="A177" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="178" customHeight="1" ht="15" spans="1:10">
+      <c r="A178" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D178" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E178" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F178" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G178" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H178" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="179" customHeight="1" ht="15" spans="1:5">
+      <c r="A179" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B179" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C179" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E179" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" ht="15" spans="1:1">
+      <c r="A180" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" ht="15" spans="1:10">
+      <c r="A181" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D181" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E181" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F181" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G181" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H181" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" ht="15" spans="1:5">
+      <c r="A182" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C182" s="11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E182" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A183" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" ht="15" spans="1:12">
+      <c r="A184" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B175" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C175" s="2" t="s">
+      <c r="B184" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D175" s="2" t="s">
+      <c r="D184" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E175" s="3" t="s">
+      <c r="E184" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F175" s="3" t="s">
+      <c r="F184" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G175" s="3" t="s">
+      <c r="G184" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H175" s="3" t="s">
+      <c r="H184" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I175" s="3" t="s">
+      <c r="I184" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J175" s="3" t="s">
+      <c r="J184" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K175" s="2" t="s">
+      <c r="K184" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L175" s="3" t="s">
+      <c r="L184" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="176" customHeight="1" ht="15" spans="1:1">
-      <c r="A176" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="177" customHeight="1" ht="15" spans="1:10">
-      <c r="A177" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D177" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E177" s="7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F177" s="7" t="n">
-        <v>42000</v>
-      </c>
-      <c r="G177" s="8">
-        <v>46128</v>
-      </c>
-      <c r="H177" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I177" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J177" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="178" customHeight="1" ht="15" spans="1:5">
-      <c r="A178" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B178" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C178" s="11" t="n">
-        <v>42000</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E178" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" customHeight="1" ht="15" spans="1:1">
-      <c r="A179" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="180" customHeight="1" ht="15" spans="1:10">
-      <c r="A180" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D180" s="6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E180" s="7" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F180" s="7" t="n">
-        <v>2640</v>
-      </c>
-      <c r="G180" s="8">
-        <v>46135</v>
-      </c>
-      <c r="H180" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I180" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J180" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="181" customHeight="1" ht="15" spans="1:5">
-      <c r="A181" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B181" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C181" s="11" t="n">
-        <v>2640</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E181" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" customHeight="1" ht="15" spans="1:1">
-      <c r="A182" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="183" customHeight="1" ht="15" spans="1:10">
-      <c r="A183" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D183" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E183" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F183" s="7" t="n">
-        <v>40000</v>
-      </c>
-      <c r="G183" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H183" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I183" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J183" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="184" customHeight="1" ht="15" spans="1:5">
-      <c r="A184" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B184" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C184" s="11" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E184" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="185" customHeight="1" ht="15" spans="1:1">
       <c r="A185" s="2" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
     </row>
     <row r="186" customHeight="1" ht="15" spans="1:10">
@@ -4633,22 +4609,22 @@
         <v>14</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D186" s="6" t="n">
-        <v>5000</v>
+        <v>3024</v>
       </c>
       <c r="E186" s="7" t="n">
-        <v>0.4</v>
+        <v>12.3</v>
       </c>
       <c r="F186" s="7" t="n">
-        <v>2000</v>
+        <v>37195.2</v>
       </c>
       <c r="G186" s="8">
-        <v>46132</v>
+        <v>46127</v>
       </c>
       <c r="H186" s="6" t="n">
         <v>0</v>
@@ -4668,7 +4644,7 @@
         <v>19</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>2000</v>
+        <v>37195.2</v>
       </c>
       <c r="D187" s="3" t="s">
         <v>18</v>
@@ -4679,7 +4655,7 @@
     </row>
     <row r="188" customHeight="1" ht="15" spans="1:1">
       <c r="A188" s="2" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
     </row>
     <row r="189" customHeight="1" ht="15" spans="1:10">
@@ -4687,22 +4663,22 @@
         <v>14</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D189" s="6" t="n">
-        <v>50000</v>
+        <v>3024</v>
       </c>
       <c r="E189" s="7" t="n">
-        <v>0.4</v>
+        <v>14.5</v>
       </c>
       <c r="F189" s="7" t="n">
-        <v>20000</v>
+        <v>43848</v>
       </c>
       <c r="G189" s="8">
-        <v>46132</v>
+        <v>46113</v>
       </c>
       <c r="H189" s="6" t="n">
         <v>0</v>
@@ -4711,158 +4687,158 @@
         <v>0</v>
       </c>
       <c r="J189" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="190" customHeight="1" ht="15" spans="1:5">
-      <c r="A190" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B190" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" ht="15" spans="1:10">
+      <c r="A190" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D190" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="E190" s="7" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="F190" s="7" t="n">
+        <v>11310</v>
+      </c>
+      <c r="G190" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H190" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" ht="15" spans="1:5">
+      <c r="A191" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B191" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C190" s="11" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D190" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E190" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A191" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" customHeight="1" ht="15" spans="1:12">
+      <c r="C191" s="11" t="n">
+        <v>55158</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E191" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" customHeight="1" ht="15" spans="1:1">
       <c r="A192" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" ht="15" spans="1:10">
+      <c r="A193" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D193" s="6" t="n">
+        <v>216</v>
+      </c>
+      <c r="E193" s="7" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="F193" s="7" t="n">
+        <v>3451.68</v>
+      </c>
+      <c r="G193" s="8">
+        <v>46135</v>
+      </c>
+      <c r="H193" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="194" customHeight="1" ht="15" spans="1:5">
+      <c r="A194" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C194" s="11" t="n">
+        <v>3451.68</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E194" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A195" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" customHeight="1" ht="15" spans="1:12">
+      <c r="A196" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B192" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C192" s="2" t="s">
+      <c r="B196" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C196" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D192" s="2" t="s">
+      <c r="D196" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E192" s="3" t="s">
+      <c r="E196" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F192" s="3" t="s">
+      <c r="F196" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G192" s="3" t="s">
+      <c r="G196" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H192" s="3" t="s">
+      <c r="H196" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I192" s="3" t="s">
+      <c r="I196" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J192" s="3" t="s">
+      <c r="J196" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K192" s="2" t="s">
+      <c r="K196" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L192" s="3" t="s">
+      <c r="L196" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="193" customHeight="1" ht="15" spans="1:1">
-      <c r="A193" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="194" customHeight="1" ht="15" spans="1:10">
-      <c r="A194" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B194" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C194" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D194" s="6" t="n">
-        <v>3024</v>
-      </c>
-      <c r="E194" s="7" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="F194" s="7" t="n">
-        <v>37195.2</v>
-      </c>
-      <c r="G194" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H194" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I194" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J194" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="195" customHeight="1" ht="15" spans="1:5">
-      <c r="A195" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B195" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C195" s="11" t="n">
-        <v>37195.2</v>
-      </c>
-      <c r="D195" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E195" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" customHeight="1" ht="15" spans="1:1">
-      <c r="A196" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="197" customHeight="1" ht="15" spans="1:10">
-      <c r="A197" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D197" s="6" t="n">
-        <v>3024</v>
-      </c>
-      <c r="E197" s="7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F197" s="7" t="n">
-        <v>43848</v>
-      </c>
-      <c r="G197" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H197" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I197" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J197" s="6" t="s">
-        <v>49</v>
+    <row r="197" customHeight="1" ht="15" spans="1:1">
+      <c r="A197" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="198" customHeight="1" ht="15" spans="1:10">
@@ -4876,16 +4852,16 @@
         <v>132</v>
       </c>
       <c r="D198" s="6" t="n">
-        <v>600</v>
+        <v>510</v>
       </c>
       <c r="E198" s="7" t="n">
-        <v>18.85</v>
+        <v>13.9</v>
       </c>
       <c r="F198" s="7" t="n">
-        <v>11310</v>
+        <v>7089</v>
       </c>
       <c r="G198" s="8">
-        <v>46134</v>
+        <v>46132</v>
       </c>
       <c r="H198" s="6" t="n">
         <v>0</v>
@@ -4894,266 +4870,266 @@
         <v>0</v>
       </c>
       <c r="J198" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="199" customHeight="1" ht="15" spans="1:5">
-      <c r="A199" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B199" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="199" customHeight="1" ht="15" spans="1:10">
+      <c r="A199" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D199" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="E199" s="7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F199" s="7" t="n">
+        <v>7089</v>
+      </c>
+      <c r="G199" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H199" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="200" customHeight="1" ht="15" spans="1:5">
+      <c r="A200" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B200" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C199" s="11" t="n">
-        <v>55158</v>
-      </c>
-      <c r="D199" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E199" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" customHeight="1" ht="15" spans="1:1">
-      <c r="A200" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="201" customHeight="1" ht="15" spans="1:10">
-      <c r="A201" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B201" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D201" s="6" t="n">
-        <v>216</v>
-      </c>
-      <c r="E201" s="7" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="F201" s="7" t="n">
-        <v>3451.68</v>
-      </c>
-      <c r="G201" s="8">
-        <v>46135</v>
-      </c>
-      <c r="H201" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I201" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J201" s="6" t="s">
+      <c r="C200" s="11" t="n">
+        <v>14178</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E200" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" ht="15" spans="1:1">
+      <c r="A201" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" ht="15" spans="1:10">
+      <c r="A202" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D202" s="6" t="n">
+        <v>5004</v>
+      </c>
+      <c r="E202" s="7" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="F202" s="7" t="n">
+        <v>59997.96</v>
+      </c>
+      <c r="G202" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H202" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" ht="15" spans="1:5">
+      <c r="A203" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C203" s="11" t="n">
+        <v>59997.96</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E203" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" ht="15" spans="1:1">
+      <c r="A204" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" ht="15" spans="1:10">
+      <c r="A205" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D205" s="6" t="n">
+        <v>8010</v>
+      </c>
+      <c r="E205" s="7" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="F205" s="7" t="n">
+        <v>166527.9</v>
+      </c>
+      <c r="G205" s="8">
+        <v>46122</v>
+      </c>
+      <c r="H205" s="6" t="n">
+        <v>2010</v>
+      </c>
+      <c r="I205" s="9" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="J205" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="202" customHeight="1" ht="15" spans="1:5">
-      <c r="A202" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B202" s="10" t="s">
+    <row r="206" customHeight="1" ht="15" spans="1:5">
+      <c r="A206" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B206" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C202" s="11" t="n">
-        <v>3451.68</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E202" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A203" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" customHeight="1" ht="15" spans="1:12">
-      <c r="A204" s="2" t="s">
+      <c r="C206" s="11" t="n">
+        <v>166527.9</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E206" s="12" t="n">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" ht="15" spans="1:1">
+      <c r="A207" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" ht="15" spans="1:10">
+      <c r="A208" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D208" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E208" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F208" s="7" t="n">
+        <v>312000</v>
+      </c>
+      <c r="G208" s="8">
+        <v>46100</v>
+      </c>
+      <c r="H208" s="6" t="n">
+        <v>18900</v>
+      </c>
+      <c r="I208" s="9" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="J208" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" ht="15" spans="1:5">
+      <c r="A209" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B209" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C209" s="11" t="n">
+        <v>312000</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E209" s="12" t="n">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A210" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" customHeight="1" ht="15" spans="1:12">
+      <c r="A211" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B204" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C204" s="2" t="s">
+      <c r="B211" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C211" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D204" s="2" t="s">
+      <c r="D211" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E204" s="3" t="s">
+      <c r="E211" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F204" s="3" t="s">
+      <c r="F211" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G204" s="3" t="s">
+      <c r="G211" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H204" s="3" t="s">
+      <c r="H211" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I204" s="3" t="s">
+      <c r="I211" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J204" s="3" t="s">
+      <c r="J211" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K204" s="2" t="s">
+      <c r="K211" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L204" s="3" t="s">
+      <c r="L211" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="205" customHeight="1" ht="15" spans="1:1">
-      <c r="A205" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="206" customHeight="1" ht="15" spans="1:10">
-      <c r="A206" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B206" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C206" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D206" s="6" t="n">
-        <v>510</v>
-      </c>
-      <c r="E206" s="7" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F206" s="7" t="n">
-        <v>7089</v>
-      </c>
-      <c r="G206" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H206" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I206" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J206" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="207" customHeight="1" ht="15" spans="1:10">
-      <c r="A207" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B207" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C207" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D207" s="6" t="n">
-        <v>510</v>
-      </c>
-      <c r="E207" s="7" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F207" s="7" t="n">
-        <v>7089</v>
-      </c>
-      <c r="G207" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H207" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I207" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J207" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="208" customHeight="1" ht="15" spans="1:5">
-      <c r="A208" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B208" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C208" s="11" t="n">
-        <v>14178</v>
-      </c>
-      <c r="D208" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E208" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209" customHeight="1" ht="15" spans="1:1">
-      <c r="A209" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="210" customHeight="1" ht="15" spans="1:10">
-      <c r="A210" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B210" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C210" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D210" s="6" t="n">
-        <v>5004</v>
-      </c>
-      <c r="E210" s="7" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="F210" s="7" t="n">
-        <v>59997.96</v>
-      </c>
-      <c r="G210" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H210" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I210" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J210" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="211" customHeight="1" ht="15" spans="1:5">
-      <c r="A211" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B211" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C211" s="11" t="n">
-        <v>59997.96</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E211" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="212" customHeight="1" ht="15" spans="1:1">
       <c r="A212" s="2" t="s">
-        <v>20</v>
+        <v>141</v>
       </c>
     </row>
     <row r="213" customHeight="1" ht="15" spans="1:10">
@@ -5161,22 +5137,22 @@
         <v>14</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>8010</v>
+        <v>810</v>
       </c>
       <c r="E213" s="7" t="n">
-        <v>20.79</v>
+        <v>19.88</v>
       </c>
       <c r="F213" s="7" t="n">
-        <v>166527.9</v>
+        <v>16102.8</v>
       </c>
       <c r="G213" s="8">
-        <v>46122</v>
+        <v>46134</v>
       </c>
       <c r="H213" s="6" t="n">
         <v>0</v>
@@ -5185,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="J213" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="214" customHeight="1" ht="15" spans="1:5">
@@ -5196,7 +5172,7 @@
         <v>19</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>166527.9</v>
+        <v>16102.8</v>
       </c>
       <c r="D214" s="3" t="s">
         <v>18</v>
@@ -5205,203 +5181,203 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" customHeight="1" ht="15" spans="1:1">
-      <c r="A215" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="216" customHeight="1" ht="15" spans="1:10">
-      <c r="A216" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B216" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C216" s="5" t="s">
+    <row r="215" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A215" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" customHeight="1" ht="15" spans="1:12">
+      <c r="A216" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B216" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D216" s="6" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E216" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="F216" s="7" t="n">
-        <v>312000</v>
-      </c>
-      <c r="G216" s="8">
-        <v>46100</v>
-      </c>
-      <c r="H216" s="6" t="n">
-        <v>18900</v>
-      </c>
-      <c r="I216" s="9" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="J216" s="6" t="s">
+      <c r="C216" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H216" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I216" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J216" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K216" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L216" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" ht="15" spans="1:1">
+      <c r="A217" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" ht="15" spans="1:10">
+      <c r="A218" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D218" s="6" t="n">
+        <v>224</v>
+      </c>
+      <c r="E218" s="7" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="F218" s="7" t="n">
+        <v>4132.8</v>
+      </c>
+      <c r="G218" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H218" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" ht="15" spans="1:5">
+      <c r="A219" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B219" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C219" s="11" t="n">
+        <v>4132.8</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E219" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A220" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" ht="15" spans="1:12">
+      <c r="A221" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H221" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I221" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J221" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K221" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L221" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="222" customHeight="1" ht="15" spans="1:1">
+      <c r="A222" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" ht="15" spans="1:10">
+      <c r="A223" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D223" s="6" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E223" s="7" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F223" s="7" t="n">
+        <v>14091.84</v>
+      </c>
+      <c r="G223" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H223" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="217" customHeight="1" ht="15" spans="1:5">
-      <c r="A217" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B217" s="10" t="s">
+    <row r="224" customHeight="1" ht="15" spans="1:5">
+      <c r="A224" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B224" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C217" s="11" t="n">
-        <v>312000</v>
-      </c>
-      <c r="D217" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E217" s="12" t="n">
-        <v>18900</v>
-      </c>
-    </row>
-    <row r="218" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A218" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" customHeight="1" ht="15" spans="1:12">
-      <c r="A219" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E219" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F219" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G219" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H219" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I219" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J219" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K219" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L219" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="220" customHeight="1" ht="15" spans="1:1">
-      <c r="A220" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="221" customHeight="1" ht="15" spans="1:10">
-      <c r="A221" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B221" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C221" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D221" s="6" t="n">
-        <v>810</v>
-      </c>
-      <c r="E221" s="7" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="F221" s="7" t="n">
-        <v>16102.8</v>
-      </c>
-      <c r="G221" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H221" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I221" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J221" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="222" customHeight="1" ht="15" spans="1:5">
-      <c r="A222" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B222" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C222" s="11" t="n">
-        <v>16102.8</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E222" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A223" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" customHeight="1" ht="15" spans="1:12">
-      <c r="A224" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E224" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F224" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G224" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H224" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I224" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J224" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K224" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L224" s="3" t="s">
-        <v>12</v>
+      <c r="C224" s="11" t="n">
+        <v>14091.84</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E224" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="225" customHeight="1" ht="15" spans="1:1">
       <c r="A225" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="226" customHeight="1" ht="15" spans="1:10">
@@ -5409,19 +5385,19 @@
         <v>14</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>224</v>
+        <v>1024</v>
       </c>
       <c r="E226" s="7" t="n">
-        <v>18.45</v>
+        <v>16.9</v>
       </c>
       <c r="F226" s="7" t="n">
-        <v>4132.8</v>
+        <v>17305.6</v>
       </c>
       <c r="G226" s="8">
         <v>46134</v>
@@ -5433,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="J226" s="6" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="227" customHeight="1" ht="15" spans="1:5">
@@ -5444,7 +5420,7 @@
         <v>19</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>4132.8</v>
+        <v>17305.6</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>18</v>
@@ -5453,160 +5429,160 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A228" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" customHeight="1" ht="15" spans="1:12">
-      <c r="A229" s="2" t="s">
+    <row r="228" customHeight="1" ht="15" spans="1:1">
+      <c r="A228" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" ht="15" spans="1:10">
+      <c r="A229" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D229" s="6" t="n">
+        <v>224</v>
+      </c>
+      <c r="E229" s="7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F229" s="7" t="n">
+        <v>3740.8</v>
+      </c>
+      <c r="G229" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H229" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I229" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="230" customHeight="1" ht="15" spans="1:5">
+      <c r="A230" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C230" s="11" t="n">
+        <v>3740.8</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E230" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" customHeight="1" ht="15" spans="1:1">
+      <c r="A231" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" ht="15" spans="1:10">
+      <c r="A232" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D232" s="6" t="n">
+        <v>224</v>
+      </c>
+      <c r="E232" s="7" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="F232" s="7" t="n">
+        <v>4791.36</v>
+      </c>
+      <c r="G232" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H232" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I232" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" ht="15" spans="1:5">
+      <c r="A233" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B233" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C233" s="11" t="n">
+        <v>4791.36</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E233" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A234" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" ht="15" spans="1:12">
+      <c r="A235" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B229" s="2" t="s">
+      <c r="B235" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C229" s="2" t="s">
+      <c r="C235" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D229" s="2" t="s">
+      <c r="D235" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E229" s="3" t="s">
+      <c r="E235" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F229" s="3" t="s">
+      <c r="F235" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G229" s="3" t="s">
+      <c r="G235" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H229" s="3" t="s">
+      <c r="H235" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I229" s="3" t="s">
+      <c r="I235" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J229" s="3" t="s">
+      <c r="J235" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K229" s="2" t="s">
+      <c r="K235" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L229" s="3" t="s">
+      <c r="L235" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="230" customHeight="1" ht="15" spans="1:1">
-      <c r="A230" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="231" customHeight="1" ht="15" spans="1:10">
-      <c r="A231" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B231" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D231" s="6" t="n">
-        <v>2016</v>
-      </c>
-      <c r="E231" s="7" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F231" s="7" t="n">
-        <v>14091.84</v>
-      </c>
-      <c r="G231" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H231" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I231" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J231" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="232" customHeight="1" ht="15" spans="1:5">
-      <c r="A232" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B232" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C232" s="11" t="n">
-        <v>14091.84</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E232" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" customHeight="1" ht="15" spans="1:1">
-      <c r="A233" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="234" customHeight="1" ht="15" spans="1:10">
-      <c r="A234" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B234" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C234" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D234" s="6" t="n">
-        <v>1024</v>
-      </c>
-      <c r="E234" s="7" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="F234" s="7" t="n">
-        <v>17305.6</v>
-      </c>
-      <c r="G234" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H234" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I234" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J234" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="235" customHeight="1" ht="15" spans="1:5">
-      <c r="A235" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B235" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C235" s="11" t="n">
-        <v>17305.6</v>
-      </c>
-      <c r="D235" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E235" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="236" customHeight="1" ht="15" spans="1:1">
       <c r="A236" s="2" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
     </row>
     <row r="237" customHeight="1" ht="15" spans="1:10">
@@ -5614,22 +5590,22 @@
         <v>14</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="C237" s="5" t="s">
         <v>153</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>224</v>
+        <v>1000</v>
       </c>
       <c r="E237" s="7" t="n">
-        <v>16.7</v>
+        <v>14.46</v>
       </c>
       <c r="F237" s="7" t="n">
-        <v>3740.8</v>
+        <v>14460</v>
       </c>
       <c r="G237" s="8">
-        <v>46132</v>
+        <v>46126</v>
       </c>
       <c r="H237" s="6" t="n">
         <v>0</v>
@@ -5638,7 +5614,7 @@
         <v>0</v>
       </c>
       <c r="J237" s="6" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="238" customHeight="1" ht="15" spans="1:5">
@@ -5649,7 +5625,7 @@
         <v>19</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>3740.8</v>
+        <v>14460</v>
       </c>
       <c r="D238" s="3" t="s">
         <v>18</v>
@@ -5660,7 +5636,7 @@
     </row>
     <row r="239" customHeight="1" ht="15" spans="1:1">
       <c r="A239" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="240" customHeight="1" ht="15" spans="1:10">
@@ -5668,22 +5644,22 @@
         <v>14</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D240" s="6" t="n">
-        <v>224</v>
+        <v>2000</v>
       </c>
       <c r="E240" s="7" t="n">
-        <v>21.39</v>
+        <v>13.5</v>
       </c>
       <c r="F240" s="7" t="n">
-        <v>4791.36</v>
+        <v>27000</v>
       </c>
       <c r="G240" s="8">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="H240" s="6" t="n">
         <v>0</v>
@@ -5692,7 +5668,7 @@
         <v>0</v>
       </c>
       <c r="J240" s="6" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="241" customHeight="1" ht="15" spans="1:5">
@@ -5703,7 +5679,7 @@
         <v>19</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>4791.36</v>
+        <v>27000</v>
       </c>
       <c r="D241" s="3" t="s">
         <v>18</v>
@@ -5712,84 +5688,63 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A242" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" customHeight="1" ht="15" spans="1:12">
-      <c r="A243" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D243" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E243" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F243" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G243" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H243" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I243" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J243" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K243" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L243" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="244" customHeight="1" ht="15" spans="1:1">
-      <c r="A244" s="2" t="s">
+    <row r="242" customHeight="1" ht="15" spans="1:1">
+      <c r="A242" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="245" customHeight="1" ht="15" spans="1:10">
-      <c r="A245" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B245" s="5" t="s">
+    <row r="243" customHeight="1" ht="15" spans="1:10">
+      <c r="A243" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B243" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C245" s="5" t="s">
+      <c r="C243" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D245" s="6" t="n">
-        <v>1024</v>
-      </c>
-      <c r="E245" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="F245" s="7" t="n">
-        <v>16281.6</v>
-      </c>
-      <c r="G245" s="8">
-        <v>46125</v>
-      </c>
-      <c r="H245" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I245" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J245" s="6" t="s">
-        <v>104</v>
+      <c r="D243" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="E243" s="7" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F243" s="7" t="n">
+        <v>2516.4</v>
+      </c>
+      <c r="G243" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H243" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="244" customHeight="1" ht="15" spans="1:5">
+      <c r="A244" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B244" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C244" s="11" t="n">
+        <v>2516.4</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E244" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" customHeight="1" ht="15" spans="1:1">
+      <c r="A245" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="246" customHeight="1" ht="15" spans="1:10">
@@ -5797,19 +5752,19 @@
         <v>14</v>
       </c>
       <c r="B246" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C246" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C246" s="5" t="s">
-        <v>156</v>
-      </c>
       <c r="D246" s="6" t="n">
-        <v>2016</v>
+        <v>500</v>
       </c>
       <c r="E246" s="7" t="n">
-        <v>15.9</v>
+        <v>10.5</v>
       </c>
       <c r="F246" s="7" t="n">
-        <v>32054.4</v>
+        <v>5250</v>
       </c>
       <c r="G246" s="8">
         <v>46132</v>
@@ -5821,7 +5776,7 @@
         <v>0</v>
       </c>
       <c r="J246" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="247" customHeight="1" ht="15" spans="1:5">
@@ -5832,7 +5787,7 @@
         <v>19</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>48336</v>
+        <v>5250</v>
       </c>
       <c r="D247" s="3" t="s">
         <v>18</v>
@@ -5841,106 +5796,106 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A248" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" customHeight="1" ht="15" spans="1:12">
-      <c r="A249" s="2" t="s">
+    <row r="248" customHeight="1" ht="15" spans="1:1">
+      <c r="A248" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="249" customHeight="1" ht="15" spans="1:10">
+      <c r="A249" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D249" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E249" s="7" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="F249" s="7" t="n">
+        <v>8802</v>
+      </c>
+      <c r="G249" s="8">
+        <v>46099</v>
+      </c>
+      <c r="H249" s="6" t="n">
+        <v>1008</v>
+      </c>
+      <c r="I249" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="J249" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="250" customHeight="1" ht="15" spans="1:5">
+      <c r="A250" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B250" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C250" s="11" t="n">
+        <v>8802</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E250" s="12" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="251" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A251" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" customHeight="1" ht="15" spans="1:12">
+      <c r="A252" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B249" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C249" s="2" t="s">
+      <c r="B252" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C252" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D249" s="2" t="s">
+      <c r="D252" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E249" s="3" t="s">
+      <c r="E252" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F249" s="3" t="s">
+      <c r="F252" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G249" s="3" t="s">
+      <c r="G252" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H249" s="3" t="s">
+      <c r="H252" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I249" s="3" t="s">
+      <c r="I252" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J249" s="3" t="s">
+      <c r="J252" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K249" s="2" t="s">
+      <c r="K252" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L249" s="3" t="s">
+      <c r="L252" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="250" customHeight="1" ht="15" spans="1:1">
-      <c r="A250" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="251" customHeight="1" ht="15" spans="1:10">
-      <c r="A251" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B251" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C251" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D251" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E251" s="7" t="n">
-        <v>14.46</v>
-      </c>
-      <c r="F251" s="7" t="n">
-        <v>14460</v>
-      </c>
-      <c r="G251" s="8">
-        <v>46126</v>
-      </c>
-      <c r="H251" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I251" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J251" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="252" customHeight="1" ht="15" spans="1:5">
-      <c r="A252" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B252" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C252" s="11" t="n">
-        <v>14460</v>
-      </c>
-      <c r="D252" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E252" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="253" customHeight="1" ht="15" spans="1:1">
       <c r="A253" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="254" customHeight="1" ht="15" spans="1:10">
@@ -5948,22 +5903,22 @@
         <v>14</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D254" s="6" t="n">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="E254" s="7" t="n">
-        <v>13.5</v>
+        <v>16.09</v>
       </c>
       <c r="F254" s="7" t="n">
-        <v>27000</v>
+        <v>3218</v>
       </c>
       <c r="G254" s="8">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="H254" s="6" t="n">
         <v>0</v>
@@ -5972,7 +5927,7 @@
         <v>0</v>
       </c>
       <c r="J254" s="6" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
     </row>
     <row r="255" customHeight="1" ht="15" spans="1:5">
@@ -5983,7 +5938,7 @@
         <v>19</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>27000</v>
+        <v>3218</v>
       </c>
       <c r="D255" s="3" t="s">
         <v>18</v>
@@ -5994,7 +5949,7 @@
     </row>
     <row r="256" customHeight="1" ht="15" spans="1:1">
       <c r="A256" s="2" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
     </row>
     <row r="257" customHeight="1" ht="15" spans="1:10">
@@ -6002,31 +5957,31 @@
         <v>14</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D257" s="6" t="n">
-        <v>360</v>
+        <v>520</v>
       </c>
       <c r="E257" s="7" t="n">
-        <v>6.99</v>
+        <v>13.2</v>
       </c>
       <c r="F257" s="7" t="n">
-        <v>2516.4</v>
+        <v>6864</v>
       </c>
       <c r="G257" s="8">
         <v>46132</v>
       </c>
       <c r="H257" s="6" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="I257" s="9" t="n">
-        <v>0</v>
+        <v>53.85</v>
       </c>
       <c r="J257" s="6" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
     </row>
     <row r="258" customHeight="1" ht="15" spans="1:5">
@@ -6037,357 +5992,12 @@
         <v>19</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>2516.4</v>
+        <v>6864</v>
       </c>
       <c r="D258" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E258" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" customHeight="1" ht="15" spans="1:1">
-      <c r="A259" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="260" customHeight="1" ht="15" spans="1:10">
-      <c r="A260" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B260" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C260" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D260" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="E260" s="7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F260" s="7" t="n">
-        <v>5250</v>
-      </c>
-      <c r="G260" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H260" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I260" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J260" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="261" customHeight="1" ht="15" spans="1:5">
-      <c r="A261" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B261" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C261" s="11" t="n">
-        <v>5250</v>
-      </c>
-      <c r="D261" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E261" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" customHeight="1" ht="15" spans="1:1">
-      <c r="A262" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="263" customHeight="1" ht="15" spans="1:10">
-      <c r="A263" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B263" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D263" s="6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E263" s="7" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="F263" s="7" t="n">
-        <v>8802</v>
-      </c>
-      <c r="G263" s="8">
-        <v>46099</v>
-      </c>
-      <c r="H263" s="6" t="n">
-        <v>1008</v>
-      </c>
-      <c r="I263" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="J263" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="264" customHeight="1" ht="15" spans="1:5">
-      <c r="A264" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B264" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C264" s="11" t="n">
-        <v>8802</v>
-      </c>
-      <c r="D264" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E264" s="12" t="n">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="265" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A265" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" customHeight="1" ht="15" spans="1:12">
-      <c r="A266" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E266" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F266" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G266" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H266" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I266" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J266" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K266" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L266" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="267" customHeight="1" ht="15" spans="1:1">
-      <c r="A267" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="268" customHeight="1" ht="15" spans="1:10">
-      <c r="A268" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B268" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C268" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D268" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E268" s="7" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="F268" s="7" t="n">
-        <v>3218</v>
-      </c>
-      <c r="G268" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H268" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I268" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J268" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="269" customHeight="1" ht="15" spans="1:5">
-      <c r="A269" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B269" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C269" s="11" t="n">
-        <v>3218</v>
-      </c>
-      <c r="D269" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E269" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" customHeight="1" ht="15" spans="1:1">
-      <c r="A270" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="271" customHeight="1" ht="15" spans="1:10">
-      <c r="A271" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B271" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C271" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D271" s="6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E271" s="7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F271" s="7" t="n">
-        <v>36600</v>
-      </c>
-      <c r="G271" s="8">
-        <v>46125</v>
-      </c>
-      <c r="H271" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I271" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J271" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="272" customHeight="1" ht="15" spans="1:10">
-      <c r="A272" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B272" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C272" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D272" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E272" s="7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F272" s="7" t="n">
-        <v>24400</v>
-      </c>
-      <c r="G272" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H272" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I272" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J272" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="273" customHeight="1" ht="15" spans="1:5">
-      <c r="A273" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B273" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C273" s="11" t="n">
-        <v>61000</v>
-      </c>
-      <c r="D273" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E273" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274" customHeight="1" ht="15" spans="1:1">
-      <c r="A274" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="275" customHeight="1" ht="15" spans="1:10">
-      <c r="A275" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B275" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C275" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D275" s="6" t="n">
-        <v>520</v>
-      </c>
-      <c r="E275" s="7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F275" s="7" t="n">
-        <v>6864</v>
-      </c>
-      <c r="G275" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H275" s="6" t="n">
-        <v>280</v>
-      </c>
-      <c r="I275" s="9" t="n">
-        <v>53.85</v>
-      </c>
-      <c r="J275" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="276" customHeight="1" ht="15" spans="1:5">
-      <c r="A276" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B276" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C276" s="11" t="n">
-        <v>6864</v>
-      </c>
-      <c r="D276" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E276" s="12" t="n">
         <v>280</v>
       </c>
     </row>

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="160">
   <si>
     <t>MATRIZ CNPJ: 40.357.820/0001-50R Y DOIS - 58082-025
  ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
@@ -242,13 +242,16 @@
     <t>788</t>
   </si>
   <si>
-    <t>LG MED HOSP</t>
-  </si>
-  <si>
-    <t>745</t>
-  </si>
-  <si>
-    <t>KELLEN</t>
+    <t>JMC COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>841</t>
+  </si>
+  <si>
+    <t>1590 - ATADURA DE CREPE 13 FIOS 12 X 1,20  PCT 12 FARMA C</t>
+  </si>
+  <si>
+    <t>1593 - ATADURA DE CREPE 13 FIOS 20 X 1,20  PCT 12 FARMA C</t>
   </si>
   <si>
     <t>MAPEMI - BRASIL DISTRIBUICAO E LOGISTICA FARMACEUTICA</t>
@@ -278,9 +281,6 @@
     <t>JOSEMAR</t>
   </si>
   <si>
-    <t>1590 - ATADURA DE CREPE 13 FIOS 12 X 1,20  PCT 12 FARMA C</t>
-  </si>
-  <si>
     <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS</t>
   </si>
   <si>
@@ -428,10 +428,19 @@
     <t xml:space="preserve">85 - GAZE CIRCULAR NAO ESTERIL 09 FIOS </t>
   </si>
   <si>
-    <t>VIAMED LTDA</t>
-  </si>
-  <si>
-    <t>833</t>
+    <t>90 - GAZE CIRCULAR NAO ESTERIL 09 FIOS J</t>
+  </si>
+  <si>
+    <t>GAZE EM ROLO - 11 FIOS</t>
+  </si>
+  <si>
+    <t>PHARMAPLUS DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1687 - GAZE CIRCULAR NAO ESTERIL 11 FIOS </t>
   </si>
   <si>
     <t>GAZE EM ROLO - 13 FIOS</t>
@@ -440,6 +449,9 @@
     <t>282 - GAZE CIRCULAR NAO ESTERIL 13 FIOS JA</t>
   </si>
   <si>
+    <t>359 - GAZE CIRCULAR NAO ESTERIL 13 FIOS</t>
+  </si>
+  <si>
     <t>NACIONAL COMERCIO E REPRESENTACAO</t>
   </si>
   <si>
@@ -464,7 +476,7 @@
     <t>838</t>
   </si>
   <si>
-    <t>1958 - GAZE NAO ESTÉRIL 11 FIOS - PCT 500 UND</t>
+    <t xml:space="preserve">2091 - GAZE NAO ESTÉRIL 11 FIOS </t>
   </si>
   <si>
     <t>PCT NÃO EST. - 13 FIOS</t>
@@ -473,31 +485,13 @@
     <t>349 - GAZE NAO ESTÉRIL 13 FIOS  - PCT 500 UND</t>
   </si>
   <si>
-    <t>834</t>
-  </si>
-  <si>
-    <t>329 - GAZE NAO ESTÉRIL 13 FIOS IA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">326 - GAZE NAO ESTÉRIL 13 FIOS </t>
-  </si>
-  <si>
     <t>PCT NÃO EST. - 9 FIOS</t>
   </si>
   <si>
     <t>51 - GAZE NAO ESTÉRIL 09 FIOS - PCT 500 UND</t>
   </si>
   <si>
-    <t>BIOMED MATERIAIS MED HOSP LTDA</t>
-  </si>
-  <si>
-    <t>817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08 - GAZE NAO ESTÉRIL 09 FIOS </t>
-  </si>
-  <si>
-    <t>1957 - GAZE NAO ESTÉRIL 09 FIOS - PCT 500 UND</t>
+    <t xml:space="preserve">2090 - GAZE NAO ESTÉRIL 09 FIOS </t>
   </si>
 </sst>
 </file>
@@ -656,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L295"/>
+  <dimension ref="A1:L298"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
   <cols>
     <col customWidth="1" width="89.23828125" min="1" max="1"/>
@@ -3107,19 +3101,19 @@
         <v>77</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>1650</v>
+        <v>440</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>7.2</v>
+        <v>4.46</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>11880</v>
+        <v>1962.4</v>
       </c>
       <c r="G98" s="8">
-        <v>46128</v>
+        <v>46150</v>
       </c>
       <c r="H98" s="6" t="n">
         <v>0</v>
@@ -3128,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99" customHeight="1" ht="15" spans="1:10">
@@ -3139,19 +3133,19 @@
         <v>77</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>840</v>
+        <v>440</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>9.2</v>
+        <v>5.51</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>7728</v>
+        <v>2424.4</v>
       </c>
       <c r="G99" s="8">
-        <v>46128</v>
+        <v>46150</v>
       </c>
       <c r="H99" s="6" t="n">
         <v>0</v>
@@ -3160,93 +3154,93 @@
         <v>0</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" ht="15" spans="1:5">
-      <c r="A100" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B100" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" ht="15" spans="1:10">
+      <c r="A100" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D100" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="E100" s="7" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="F100" s="7" t="n">
+        <v>2275.2</v>
+      </c>
+      <c r="G100" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H100" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" ht="15" spans="1:10">
+      <c r="A101" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D101" s="6" t="n">
+        <v>420</v>
+      </c>
+      <c r="E101" s="7" t="n">
+        <v>8.14</v>
+      </c>
+      <c r="F101" s="7" t="n">
+        <v>3418.8</v>
+      </c>
+      <c r="G101" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" ht="15" spans="1:5">
+      <c r="A102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B102" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C100" s="11" t="n">
-        <v>19608</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E100" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" ht="15" spans="1:1">
-      <c r="A101" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="102" customHeight="1" ht="15" spans="1:10">
-      <c r="A102" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B102" s="5" t="s">
+      <c r="C102" s="11" t="n">
+        <v>10080.8</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" ht="15" spans="1:1">
+      <c r="A103" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D102" s="6" t="n">
-        <v>400</v>
-      </c>
-      <c r="E102" s="7" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="F102" s="7" t="n">
-        <v>2396</v>
-      </c>
-      <c r="G102" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H102" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="103" customHeight="1" ht="15" spans="1:10">
-      <c r="A103" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D103" s="6" t="n">
-        <v>270</v>
-      </c>
-      <c r="E103" s="7" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="F103" s="7" t="n">
-        <v>2038.5</v>
-      </c>
-      <c r="G103" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H103" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="6" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="104" customHeight="1" ht="15" spans="1:10">
@@ -3254,19 +3248,19 @@
         <v>14</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>8.84</v>
+        <v>5.99</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>3315</v>
+        <v>2396</v>
       </c>
       <c r="G104" s="8">
         <v>46134</v>
@@ -3278,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="105" customHeight="1" ht="15" spans="1:10">
@@ -3286,19 +3280,19 @@
         <v>14</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>11.46</v>
+        <v>7.55</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>2750.4</v>
+        <v>2038.5</v>
       </c>
       <c r="G105" s="8">
         <v>46134</v>
@@ -3310,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="106" customHeight="1" ht="15" spans="1:10">
@@ -3318,19 +3312,19 @@
         <v>14</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>200</v>
+        <v>375</v>
       </c>
       <c r="E106" s="7" t="n">
-        <v>16.41</v>
+        <v>8.84</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>3282</v>
+        <v>3315</v>
       </c>
       <c r="G106" s="8">
         <v>46134</v>
@@ -3342,136 +3336,136 @@
         <v>0</v>
       </c>
       <c r="J106" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" ht="15" spans="1:10">
+      <c r="A107" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B107" s="5" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="107" customHeight="1" ht="15" spans="1:5">
-      <c r="A107" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B107" s="10" t="s">
+      <c r="C107" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D107" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="E107" s="7" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="F107" s="7" t="n">
+        <v>2750.4</v>
+      </c>
+      <c r="G107" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H107" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" ht="15" spans="1:10">
+      <c r="A108" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="F108" s="7" t="n">
+        <v>3282</v>
+      </c>
+      <c r="G108" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H108" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" ht="15" spans="1:5">
+      <c r="A109" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B109" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C107" s="11" t="n">
+      <c r="C109" s="11" t="n">
         <v>13781.9</v>
       </c>
-      <c r="D107" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E107" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A108" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" customHeight="1" ht="15" spans="1:12">
-      <c r="A109" s="2" t="s">
+      <c r="D109" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A110" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" ht="15" spans="1:12">
+      <c r="A111" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B111" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C111" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="D111" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E109" s="3" t="s">
+      <c r="E111" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F109" s="3" t="s">
+      <c r="F111" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G109" s="3" t="s">
+      <c r="G111" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H109" s="3" t="s">
+      <c r="H111" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I109" s="3" t="s">
+      <c r="I111" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J109" s="3" t="s">
+      <c r="J111" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K109" s="2" t="s">
+      <c r="K111" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L109" s="3" t="s">
+      <c r="L111" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="110" customHeight="1" ht="15" spans="1:1">
-      <c r="A110" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="111" customHeight="1" ht="15" spans="1:10">
-      <c r="A111" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B111" s="5" t="s">
+    <row r="112" customHeight="1" ht="15" spans="1:1">
+      <c r="A112" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D111" s="6" t="n">
-        <v>360</v>
-      </c>
-      <c r="E111" s="7" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="F111" s="7" t="n">
-        <v>2372.4</v>
-      </c>
-      <c r="G111" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H111" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="112" customHeight="1" ht="15" spans="1:10">
-      <c r="A112" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D112" s="6" t="n">
-        <v>320</v>
-      </c>
-      <c r="E112" s="7" t="n">
-        <v>8.14</v>
-      </c>
-      <c r="F112" s="7" t="n">
-        <v>2604.8</v>
-      </c>
-      <c r="G112" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H112" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="113" customHeight="1" ht="15" spans="1:10">
@@ -3479,19 +3473,19 @@
         <v>14</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>210</v>
+        <v>360</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>9.63</v>
+        <v>6.59</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>2022.3</v>
+        <v>2372.4</v>
       </c>
       <c r="G113" s="8">
         <v>46113</v>
@@ -3511,19 +3505,19 @@
         <v>14</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="E114" s="7" t="n">
-        <v>12.37</v>
+        <v>8.14</v>
       </c>
       <c r="F114" s="7" t="n">
-        <v>1484.4</v>
+        <v>2604.8</v>
       </c>
       <c r="G114" s="8">
         <v>46113</v>
@@ -3538,90 +3532,90 @@
         <v>17</v>
       </c>
     </row>
-    <row r="115" customHeight="1" ht="15" spans="1:5">
-      <c r="A115" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B115" s="10" t="s">
+    <row r="115" customHeight="1" ht="15" spans="1:10">
+      <c r="A115" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D115" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="E115" s="7" t="n">
+        <v>9.63</v>
+      </c>
+      <c r="F115" s="7" t="n">
+        <v>2022.3</v>
+      </c>
+      <c r="G115" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" ht="15" spans="1:10">
+      <c r="A116" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D116" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="E116" s="7" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="F116" s="7" t="n">
+        <v>1484.4</v>
+      </c>
+      <c r="G116" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" ht="15" spans="1:5">
+      <c r="A117" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B117" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C115" s="11" t="n">
+      <c r="C117" s="11" t="n">
         <v>8483.9</v>
       </c>
-      <c r="D115" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E115" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" customHeight="1" ht="15" spans="1:1">
-      <c r="A116" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="117" customHeight="1" ht="15" spans="1:10">
-      <c r="A117" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B117" s="5" t="s">
+      <c r="D117" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" ht="15" spans="1:1">
+      <c r="A118" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D117" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E117" s="7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F117" s="7" t="n">
-        <v>5700</v>
-      </c>
-      <c r="G117" s="8">
-        <v>46141</v>
-      </c>
-      <c r="H117" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="118" customHeight="1" ht="15" spans="1:10">
-      <c r="A118" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D118" s="6" t="n">
-        <v>110</v>
-      </c>
-      <c r="E118" s="7" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F118" s="7" t="n">
-        <v>768.9</v>
-      </c>
-      <c r="G118" s="8">
-        <v>46141</v>
-      </c>
-      <c r="H118" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="6" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="119" customHeight="1" ht="15" spans="1:10">
@@ -3629,19 +3623,19 @@
         <v>14</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>720</v>
+        <v>1000</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>7.19</v>
+        <v>5.7</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>5176.8</v>
+        <v>5700</v>
       </c>
       <c r="G119" s="8">
         <v>46141</v>
@@ -3653,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="120" customHeight="1" ht="15" spans="1:10">
@@ -3661,19 +3655,19 @@
         <v>14</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>375</v>
+        <v>110</v>
       </c>
       <c r="E120" s="7" t="n">
-        <v>8.41</v>
+        <v>6.99</v>
       </c>
       <c r="F120" s="7" t="n">
-        <v>3153.75</v>
+        <v>768.9</v>
       </c>
       <c r="G120" s="8">
         <v>46141</v>
@@ -3685,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="121" customHeight="1" ht="15" spans="1:10">
@@ -3693,19 +3687,19 @@
         <v>14</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>300</v>
+        <v>720</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>10.92</v>
+        <v>7.19</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>3276</v>
+        <v>5176.8</v>
       </c>
       <c r="G121" s="8">
         <v>46141</v>
@@ -3717,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="122" customHeight="1" ht="15" spans="1:10">
@@ -3725,19 +3719,19 @@
         <v>14</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>200</v>
+        <v>375</v>
       </c>
       <c r="E122" s="7" t="n">
-        <v>15.62</v>
+        <v>8.41</v>
       </c>
       <c r="F122" s="7" t="n">
-        <v>3124</v>
+        <v>3153.75</v>
       </c>
       <c r="G122" s="8">
         <v>46141</v>
@@ -3749,93 +3743,93 @@
         <v>0</v>
       </c>
       <c r="J122" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" ht="15" spans="1:10">
+      <c r="A123" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="123" customHeight="1" ht="15" spans="1:5">
-      <c r="A123" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B123" s="10" t="s">
+      <c r="C123" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D123" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="E123" s="7" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="F123" s="7" t="n">
+        <v>3276</v>
+      </c>
+      <c r="G123" s="8">
+        <v>46141</v>
+      </c>
+      <c r="H123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" ht="15" spans="1:10">
+      <c r="A124" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E124" s="7" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="F124" s="7" t="n">
+        <v>3124</v>
+      </c>
+      <c r="G124" s="8">
+        <v>46141</v>
+      </c>
+      <c r="H124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" ht="15" spans="1:5">
+      <c r="A125" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B125" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C123" s="11" t="n">
+      <c r="C125" s="11" t="n">
         <v>21199.45</v>
       </c>
-      <c r="D123" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E123" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" customHeight="1" ht="15" spans="1:1">
-      <c r="A124" s="2" t="s">
+      <c r="D125" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E125" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" ht="15" spans="1:1">
+      <c r="A126" s="2" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="125" customHeight="1" ht="15" spans="1:10">
-      <c r="A125" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D125" s="6" t="n">
-        <v>270</v>
-      </c>
-      <c r="E125" s="7" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="F125" s="7" t="n">
-        <v>1730.7</v>
-      </c>
-      <c r="G125" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H125" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="126" customHeight="1" ht="15" spans="1:10">
-      <c r="A126" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D126" s="6" t="n">
-        <v>320</v>
-      </c>
-      <c r="E126" s="7" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="F126" s="7" t="n">
-        <v>2534.4</v>
-      </c>
-      <c r="G126" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H126" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="127" customHeight="1" ht="15" spans="1:10">
@@ -3846,16 +3840,16 @@
         <v>90</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>9.37</v>
+        <v>6.41</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>655.9</v>
+        <v>1730.7</v>
       </c>
       <c r="G127" s="8">
         <v>46113</v>
@@ -3875,22 +3869,22 @@
         <v>14</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="E128" s="7" t="n">
-        <v>6.41</v>
+        <v>7.92</v>
       </c>
       <c r="F128" s="7" t="n">
-        <v>1153.8</v>
+        <v>2534.4</v>
       </c>
       <c r="G128" s="8">
-        <v>46132</v>
+        <v>46113</v>
       </c>
       <c r="H128" s="6" t="n">
         <v>0</v>
@@ -3907,22 +3901,22 @@
         <v>14</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>7.92</v>
+        <v>9.37</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>1267.2</v>
+        <v>655.9</v>
       </c>
       <c r="G129" s="8">
-        <v>46132</v>
+        <v>46113</v>
       </c>
       <c r="H129" s="6" t="n">
         <v>0</v>
@@ -3934,133 +3928,133 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" customHeight="1" ht="15" spans="1:5">
-      <c r="A130" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B130" s="10" t="s">
+    <row r="130" customHeight="1" ht="15" spans="1:10">
+      <c r="A130" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D130" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="E130" s="7" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="F130" s="7" t="n">
+        <v>1153.8</v>
+      </c>
+      <c r="G130" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H130" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" ht="15" spans="1:10">
+      <c r="A131" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D131" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="E131" s="7" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="F131" s="7" t="n">
+        <v>1267.2</v>
+      </c>
+      <c r="G131" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H131" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" ht="15" spans="1:5">
+      <c r="A132" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B132" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C130" s="11" t="n">
+      <c r="C132" s="11" t="n">
         <v>7342</v>
       </c>
-      <c r="D130" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E130" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A131" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" customHeight="1" ht="15" spans="1:12">
-      <c r="A132" s="2" t="s">
+      <c r="D132" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E132" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A133" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" ht="15" spans="1:12">
+      <c r="A134" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B134" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C134" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="D134" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E132" s="3" t="s">
+      <c r="E134" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F132" s="3" t="s">
+      <c r="F134" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G132" s="3" t="s">
+      <c r="G134" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H132" s="3" t="s">
+      <c r="H134" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I132" s="3" t="s">
+      <c r="I134" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J132" s="3" t="s">
+      <c r="J134" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K132" s="2" t="s">
+      <c r="K134" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L132" s="3" t="s">
+      <c r="L134" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="133" customHeight="1" ht="15" spans="1:1">
-      <c r="A133" s="2" t="s">
+    <row r="135" customHeight="1" ht="15" spans="1:1">
+      <c r="A135" s="2" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="134" customHeight="1" ht="15" spans="1:10">
-      <c r="A134" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D134" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="E134" s="7" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="F134" s="7" t="n">
-        <v>576.9</v>
-      </c>
-      <c r="G134" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H134" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="135" customHeight="1" ht="15" spans="1:10">
-      <c r="A135" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D135" s="6" t="n">
-        <v>320</v>
-      </c>
-      <c r="E135" s="7" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="F135" s="7" t="n">
-        <v>2534.4</v>
-      </c>
-      <c r="G135" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H135" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" s="6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="136" customHeight="1" ht="15" spans="1:10">
@@ -4071,16 +4065,16 @@
         <v>93</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>700</v>
+        <v>90</v>
       </c>
       <c r="E136" s="7" t="n">
-        <v>9.37</v>
+        <v>6.41</v>
       </c>
       <c r="F136" s="7" t="n">
-        <v>6559</v>
+        <v>576.9</v>
       </c>
       <c r="G136" s="8">
         <v>46113</v>
@@ -4103,16 +4097,16 @@
         <v>93</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>12.03</v>
+        <v>7.92</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>4330.8</v>
+        <v>2534.4</v>
       </c>
       <c r="G137" s="8">
         <v>46113</v>
@@ -4132,22 +4126,22 @@
         <v>14</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="E138" s="7" t="n">
-        <v>7.92</v>
+        <v>9.37</v>
       </c>
       <c r="F138" s="7" t="n">
-        <v>3168</v>
+        <v>6559</v>
       </c>
       <c r="G138" s="8">
-        <v>46132</v>
+        <v>46113</v>
       </c>
       <c r="H138" s="6" t="n">
         <v>0</v>
@@ -4164,22 +4158,22 @@
         <v>14</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>140</v>
+        <v>360</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>17.34</v>
+        <v>12.03</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>2427.6</v>
+        <v>4330.8</v>
       </c>
       <c r="G139" s="8">
-        <v>46132</v>
+        <v>46113</v>
       </c>
       <c r="H139" s="6" t="n">
         <v>0</v>
@@ -4199,16 +4193,16 @@
         <v>94</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>280</v>
+        <v>400</v>
       </c>
       <c r="E140" s="7" t="n">
-        <v>9.37</v>
+        <v>7.92</v>
       </c>
       <c r="F140" s="7" t="n">
-        <v>2623.6</v>
+        <v>3168</v>
       </c>
       <c r="G140" s="8">
         <v>46132</v>
@@ -4231,16 +4225,16 @@
         <v>94</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="E141" s="7" t="n">
-        <v>12.03</v>
+        <v>17.34</v>
       </c>
       <c r="F141" s="7" t="n">
-        <v>3609</v>
+        <v>2427.6</v>
       </c>
       <c r="G141" s="8">
         <v>46132</v>
@@ -4255,2409 +4249,2430 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" customHeight="1" ht="15" spans="1:5">
-      <c r="A142" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B142" s="10" t="s">
+    <row r="142" customHeight="1" ht="15" spans="1:10">
+      <c r="A142" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D142" s="6" t="n">
+        <v>280</v>
+      </c>
+      <c r="E142" s="7" t="n">
+        <v>9.37</v>
+      </c>
+      <c r="F142" s="7" t="n">
+        <v>2623.6</v>
+      </c>
+      <c r="G142" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H142" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" ht="15" spans="1:10">
+      <c r="A143" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D143" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="E143" s="7" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="F143" s="7" t="n">
+        <v>3609</v>
+      </c>
+      <c r="G143" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H143" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" ht="15" spans="1:5">
+      <c r="A144" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B144" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C142" s="11" t="n">
+      <c r="C144" s="11" t="n">
         <v>25829.3</v>
       </c>
-      <c r="D142" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E142" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A143" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" customHeight="1" ht="15" spans="1:12">
-      <c r="A144" s="2" t="s">
+      <c r="D144" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E144" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A145" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" ht="15" spans="1:12">
+      <c r="A146" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B146" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C146" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D144" s="2" t="s">
+      <c r="D146" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E144" s="3" t="s">
+      <c r="E146" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F144" s="3" t="s">
+      <c r="F146" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G144" s="3" t="s">
+      <c r="G146" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H144" s="3" t="s">
+      <c r="H146" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I144" s="3" t="s">
+      <c r="I146" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J144" s="3" t="s">
+      <c r="J146" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K144" s="2" t="s">
+      <c r="K146" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L144" s="3" t="s">
+      <c r="L146" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="145" customHeight="1" ht="15" spans="1:1">
-      <c r="A145" s="2" t="s">
+    <row r="147" customHeight="1" ht="15" spans="1:1">
+      <c r="A147" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="146" customHeight="1" ht="15" spans="1:10">
-      <c r="A146" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B146" s="5" t="s">
+    <row r="148" customHeight="1" ht="15" spans="1:10">
+      <c r="A148" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B148" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C146" s="5" t="s">
+      <c r="C148" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D146" s="6" t="n">
+      <c r="D148" s="6" t="n">
         <v>200100</v>
       </c>
-      <c r="E146" s="7" t="n">
+      <c r="E148" s="7" t="n">
         <v>4.1</v>
       </c>
-      <c r="F146" s="7" t="n">
+      <c r="F148" s="7" t="n">
         <v>820410</v>
       </c>
-      <c r="G146" s="8">
+      <c r="G148" s="8">
         <v>46119</v>
       </c>
-      <c r="H146" s="6" t="n">
+      <c r="H148" s="6" t="n">
         <v>26400</v>
       </c>
-      <c r="I146" s="9" t="n">
+      <c r="I148" s="9" t="n">
         <v>13.19</v>
       </c>
-      <c r="J146" s="6" t="s">
+      <c r="J148" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="147" customHeight="1" ht="15" spans="1:5">
-      <c r="A147" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B147" s="10" t="s">
+    <row r="149" customHeight="1" ht="15" spans="1:5">
+      <c r="A149" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B149" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C147" s="11" t="n">
+      <c r="C149" s="11" t="n">
         <v>820410</v>
       </c>
-      <c r="D147" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E147" s="12" t="n">
+      <c r="D149" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E149" s="12" t="n">
         <v>26400</v>
       </c>
     </row>
-    <row r="148" customHeight="1" ht="15" spans="1:1">
-      <c r="A148" s="2" t="s">
+    <row r="150" customHeight="1" ht="15" spans="1:1">
+      <c r="A150" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="149" customHeight="1" ht="15" spans="1:10">
-      <c r="A149" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B149" s="5" t="s">
+    <row r="151" customHeight="1" ht="15" spans="1:10">
+      <c r="A151" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B151" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C149" s="5" t="s">
+      <c r="C151" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D149" s="6" t="n">
+      <c r="D151" s="6" t="n">
         <v>20100</v>
       </c>
-      <c r="E149" s="7" t="n">
+      <c r="E151" s="7" t="n">
         <v>4.45</v>
       </c>
-      <c r="F149" s="7" t="n">
+      <c r="F151" s="7" t="n">
         <v>89445</v>
       </c>
-      <c r="G149" s="8">
+      <c r="G151" s="8">
         <v>46139</v>
       </c>
-      <c r="H149" s="6" t="n">
+      <c r="H151" s="6" t="n">
         <v>5100</v>
       </c>
-      <c r="I149" s="9" t="n">
+      <c r="I151" s="9" t="n">
         <v>25.37</v>
       </c>
-      <c r="J149" s="6" t="s">
+      <c r="J151" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="150" customHeight="1" ht="15" spans="1:10">
-      <c r="A150" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B150" s="5" t="s">
+    <row r="152" customHeight="1" ht="15" spans="1:10">
+      <c r="A152" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B152" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C150" s="5" t="s">
+      <c r="C152" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D150" s="6" t="n">
+      <c r="D152" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="E150" s="7" t="n">
+      <c r="E152" s="7" t="n">
         <v>7.22</v>
       </c>
-      <c r="F150" s="7" t="n">
+      <c r="F152" s="7" t="n">
         <v>8664</v>
       </c>
-      <c r="G150" s="8">
+      <c r="G152" s="8">
         <v>46139</v>
       </c>
-      <c r="H150" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" s="6" t="s">
+      <c r="H152" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="151" customHeight="1" ht="15" spans="1:5">
-      <c r="A151" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B151" s="10" t="s">
+    <row r="153" customHeight="1" ht="15" spans="1:5">
+      <c r="A153" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B153" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C151" s="11" t="n">
+      <c r="C153" s="11" t="n">
         <v>98109</v>
       </c>
-      <c r="D151" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E151" s="12" t="n">
+      <c r="D153" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E153" s="12" t="n">
         <v>5100</v>
       </c>
     </row>
-    <row r="152" customHeight="1" ht="15" spans="1:1">
-      <c r="A152" s="2" t="s">
+    <row r="154" customHeight="1" ht="15" spans="1:1">
+      <c r="A154" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="153" customHeight="1" ht="15" spans="1:10">
-      <c r="A153" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B153" s="5" t="s">
+    <row r="155" customHeight="1" ht="15" spans="1:10">
+      <c r="A155" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B155" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C153" s="5" t="s">
+      <c r="C155" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D153" s="6" t="n">
+      <c r="D155" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="E153" s="7" t="n">
+      <c r="E155" s="7" t="n">
         <v>2.375</v>
       </c>
-      <c r="F153" s="7" t="n">
+      <c r="F155" s="7" t="n">
         <v>47500</v>
       </c>
-      <c r="G153" s="8">
+      <c r="G155" s="8">
         <v>46147</v>
       </c>
-      <c r="H153" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" s="6" t="s">
+      <c r="H155" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="154" customHeight="1" ht="15" spans="1:5">
-      <c r="A154" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B154" s="10" t="s">
+    <row r="156" customHeight="1" ht="15" spans="1:5">
+      <c r="A156" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B156" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C154" s="11" t="n">
+      <c r="C156" s="11" t="n">
         <v>47500</v>
       </c>
-      <c r="D154" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E154" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" customHeight="1" ht="15" spans="1:1">
-      <c r="A155" s="2" t="s">
+      <c r="D156" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E156" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" ht="15" spans="1:1">
+      <c r="A157" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="156" customHeight="1" ht="15" spans="1:10">
-      <c r="A156" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B156" s="5" t="s">
+    <row r="158" customHeight="1" ht="15" spans="1:10">
+      <c r="A158" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B158" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C156" s="5" t="s">
+      <c r="C158" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D156" s="6" t="n">
+      <c r="D158" s="6" t="n">
         <v>20100</v>
       </c>
-      <c r="E156" s="7" t="n">
+      <c r="E158" s="7" t="n">
         <v>4.99</v>
       </c>
-      <c r="F156" s="7" t="n">
+      <c r="F158" s="7" t="n">
         <v>100299</v>
       </c>
-      <c r="G156" s="8">
+      <c r="G158" s="8">
         <v>46147</v>
       </c>
-      <c r="H156" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J156" s="6" t="s">
+      <c r="H158" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="157" customHeight="1" ht="15" spans="1:5">
-      <c r="A157" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B157" s="10" t="s">
+    <row r="159" customHeight="1" ht="15" spans="1:5">
+      <c r="A159" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B159" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C157" s="11" t="n">
+      <c r="C159" s="11" t="n">
         <v>100299</v>
       </c>
-      <c r="D157" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E157" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A158" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" customHeight="1" ht="15" spans="1:12">
-      <c r="A159" s="2" t="s">
+      <c r="D159" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E159" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A160" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" ht="15" spans="1:12">
+      <c r="A161" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="B161" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C161" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D159" s="2" t="s">
+      <c r="D161" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E159" s="3" t="s">
+      <c r="E161" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F159" s="3" t="s">
+      <c r="F161" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G159" s="3" t="s">
+      <c r="G161" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H159" s="3" t="s">
+      <c r="H161" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I159" s="3" t="s">
+      <c r="I161" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J159" s="3" t="s">
+      <c r="J161" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K159" s="2" t="s">
+      <c r="K161" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L159" s="3" t="s">
+      <c r="L161" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="160" customHeight="1" ht="15" spans="1:1">
-      <c r="A160" s="2" t="s">
+    <row r="162" customHeight="1" ht="15" spans="1:1">
+      <c r="A162" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="161" customHeight="1" ht="15" spans="1:10">
-      <c r="A161" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B161" s="5" t="s">
+    <row r="163" customHeight="1" ht="15" spans="1:10">
+      <c r="A163" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B163" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C161" s="5" t="s">
+      <c r="C163" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D161" s="6" t="n">
+      <c r="D163" s="6" t="n">
         <v>1092</v>
       </c>
-      <c r="E161" s="7" t="n">
+      <c r="E163" s="7" t="n">
         <v>44.9</v>
       </c>
-      <c r="F161" s="7" t="n">
+      <c r="F163" s="7" t="n">
         <v>49030.8</v>
       </c>
-      <c r="G161" s="8">
+      <c r="G163" s="8">
         <v>46141</v>
       </c>
-      <c r="H161" s="6" t="n">
+      <c r="H163" s="6" t="n">
         <v>192</v>
       </c>
-      <c r="I161" s="9" t="n">
+      <c r="I163" s="9" t="n">
         <v>17.58</v>
       </c>
-      <c r="J161" s="6" t="s">
+      <c r="J163" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="162" customHeight="1" ht="15" spans="1:10">
-      <c r="A162" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B162" s="5" t="s">
+    <row r="164" customHeight="1" ht="15" spans="1:10">
+      <c r="A164" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B164" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C162" s="5" t="s">
+      <c r="C164" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D162" s="6" t="n">
+      <c r="D164" s="6" t="n">
         <v>504</v>
       </c>
-      <c r="E162" s="7" t="n">
+      <c r="E164" s="7" t="n">
         <v>44.9</v>
       </c>
-      <c r="F162" s="7" t="n">
+      <c r="F164" s="7" t="n">
         <v>22629.6</v>
       </c>
-      <c r="G162" s="8">
+      <c r="G164" s="8">
         <v>46141</v>
       </c>
-      <c r="H162" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" s="6" t="s">
+      <c r="H164" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="163" customHeight="1" ht="15" spans="1:5">
-      <c r="A163" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B163" s="10" t="s">
+    <row r="165" customHeight="1" ht="15" spans="1:5">
+      <c r="A165" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B165" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C163" s="11" t="n">
+      <c r="C165" s="11" t="n">
         <v>71660.4</v>
       </c>
-      <c r="D163" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E163" s="12" t="n">
+      <c r="D165" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E165" s="12" t="n">
         <v>192</v>
       </c>
     </row>
-    <row r="164" customHeight="1" ht="15" spans="1:1">
-      <c r="A164" s="2" t="s">
+    <row r="166" customHeight="1" ht="15" spans="1:1">
+      <c r="A166" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="165" customHeight="1" ht="15" spans="1:10">
-      <c r="A165" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B165" s="5" t="s">
+    <row r="167" customHeight="1" ht="15" spans="1:10">
+      <c r="A167" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B167" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C165" s="5" t="s">
+      <c r="C167" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D165" s="6" t="n">
+      <c r="D167" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="E165" s="7" t="n">
+      <c r="E167" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="F165" s="7" t="n">
+      <c r="F167" s="7" t="n">
         <v>18000</v>
       </c>
-      <c r="G165" s="8">
+      <c r="G167" s="8">
         <v>46147</v>
       </c>
-      <c r="H165" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I165" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J165" s="6" t="s">
+      <c r="H167" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="166" customHeight="1" ht="15" spans="1:5">
-      <c r="A166" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B166" s="10" t="s">
+    <row r="168" customHeight="1" ht="15" spans="1:5">
+      <c r="A168" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B168" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C166" s="11" t="n">
+      <c r="C168" s="11" t="n">
         <v>18000</v>
       </c>
-      <c r="D166" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E166" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" customHeight="1" ht="15" spans="1:1">
-      <c r="A167" s="2" t="s">
+      <c r="D168" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E168" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" ht="15" spans="1:1">
+      <c r="A169" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="168" customHeight="1" ht="15" spans="1:10">
-      <c r="A168" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B168" s="5" t="s">
+    <row r="170" customHeight="1" ht="15" spans="1:10">
+      <c r="A170" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B170" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C168" s="5" t="s">
+      <c r="C170" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D168" s="6" t="n">
+      <c r="D170" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="E168" s="7" t="n">
+      <c r="E170" s="7" t="n">
         <v>48.5</v>
       </c>
-      <c r="F168" s="7" t="n">
+      <c r="F170" s="7" t="n">
         <v>2328</v>
       </c>
-      <c r="G168" s="8">
+      <c r="G170" s="8">
         <v>46132</v>
       </c>
-      <c r="H168" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I168" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" s="6" t="s">
+      <c r="H170" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="169" customHeight="1" ht="15" spans="1:5">
-      <c r="A169" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B169" s="10" t="s">
+    <row r="171" customHeight="1" ht="15" spans="1:5">
+      <c r="A171" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B171" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C169" s="11" t="n">
+      <c r="C171" s="11" t="n">
         <v>2328</v>
       </c>
-      <c r="D169" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E169" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" customHeight="1" ht="15" spans="1:1">
-      <c r="A170" s="2" t="s">
+      <c r="D171" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E171" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" ht="15" spans="1:1">
+      <c r="A172" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="171" customHeight="1" ht="15" spans="1:10">
-      <c r="A171" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B171" s="5" t="s">
+    <row r="173" customHeight="1" ht="15" spans="1:10">
+      <c r="A173" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B173" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C171" s="5" t="s">
+      <c r="C173" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D171" s="6" t="n">
+      <c r="D173" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="E171" s="7" t="n">
+      <c r="E173" s="7" t="n">
         <v>34.65</v>
       </c>
-      <c r="F171" s="7" t="n">
+      <c r="F173" s="7" t="n">
         <v>8316</v>
       </c>
-      <c r="G171" s="8">
+      <c r="G173" s="8">
         <v>46148</v>
       </c>
-      <c r="H171" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I171" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J171" s="6" t="s">
+      <c r="H173" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="172" customHeight="1" ht="15" spans="1:5">
-      <c r="A172" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B172" s="10" t="s">
+    <row r="174" customHeight="1" ht="15" spans="1:5">
+      <c r="A174" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B174" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C172" s="11" t="n">
+      <c r="C174" s="11" t="n">
         <v>8316</v>
       </c>
-      <c r="D172" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E172" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A173" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" customHeight="1" ht="15" spans="1:12">
-      <c r="A174" s="2" t="s">
+      <c r="D174" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E174" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A175" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" ht="15" spans="1:12">
+      <c r="A176" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B174" s="2" t="s">
+      <c r="B176" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C174" s="2" t="s">
+      <c r="C176" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D174" s="2" t="s">
+      <c r="D176" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E174" s="3" t="s">
+      <c r="E176" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F174" s="3" t="s">
+      <c r="F176" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G174" s="3" t="s">
+      <c r="G176" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H174" s="3" t="s">
+      <c r="H176" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I174" s="3" t="s">
+      <c r="I176" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J174" s="3" t="s">
+      <c r="J176" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K174" s="2" t="s">
+      <c r="K176" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L174" s="3" t="s">
+      <c r="L176" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="175" customHeight="1" ht="15" spans="1:1">
-      <c r="A175" s="2" t="s">
+    <row r="177" customHeight="1" ht="15" spans="1:1">
+      <c r="A177" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="176" customHeight="1" ht="15" spans="1:10">
-      <c r="A176" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B176" s="5" t="s">
+    <row r="178" customHeight="1" ht="15" spans="1:10">
+      <c r="A178" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B178" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C176" s="5" t="s">
+      <c r="C178" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D176" s="6" t="n">
+      <c r="D178" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="E176" s="7" t="n">
+      <c r="E178" s="7" t="n">
         <v>45.9</v>
       </c>
-      <c r="F176" s="7" t="n">
+      <c r="F178" s="7" t="n">
         <v>55080</v>
       </c>
-      <c r="G176" s="8">
+      <c r="G178" s="8">
         <v>46147</v>
       </c>
-      <c r="H176" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J176" s="6" t="s">
+      <c r="H178" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="177" customHeight="1" ht="15" spans="1:5">
-      <c r="A177" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B177" s="10" t="s">
+    <row r="179" customHeight="1" ht="15" spans="1:5">
+      <c r="A179" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B179" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C177" s="11" t="n">
+      <c r="C179" s="11" t="n">
         <v>55080</v>
       </c>
-      <c r="D177" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E177" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" customHeight="1" ht="15" spans="1:1">
-      <c r="A178" s="2" t="s">
+      <c r="D179" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E179" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" ht="15" spans="1:1">
+      <c r="A180" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="179" customHeight="1" ht="15" spans="1:10">
-      <c r="A179" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B179" s="5" t="s">
+    <row r="181" customHeight="1" ht="15" spans="1:10">
+      <c r="A181" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B181" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C179" s="5" t="s">
+      <c r="C181" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D179" s="6" t="n">
+      <c r="D181" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="E179" s="7" t="n">
+      <c r="E181" s="7" t="n">
         <v>52.47</v>
       </c>
-      <c r="F179" s="7" t="n">
+      <c r="F181" s="7" t="n">
         <v>2518.56</v>
       </c>
-      <c r="G179" s="8">
+      <c r="G181" s="8">
         <v>46148</v>
       </c>
-      <c r="H179" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I179" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J179" s="6" t="s">
+      <c r="H181" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="180" customHeight="1" ht="15" spans="1:5">
-      <c r="A180" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B180" s="10" t="s">
+    <row r="182" customHeight="1" ht="15" spans="1:5">
+      <c r="A182" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B182" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C180" s="11" t="n">
+      <c r="C182" s="11" t="n">
         <v>2518.56</v>
       </c>
-      <c r="D180" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E180" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" customHeight="1" ht="15" spans="1:1">
-      <c r="A181" s="2" t="s">
+      <c r="D182" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E182" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" ht="15" spans="1:1">
+      <c r="A183" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="182" customHeight="1" ht="15" spans="1:10">
-      <c r="A182" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B182" s="5" t="s">
+    <row r="184" customHeight="1" ht="15" spans="1:10">
+      <c r="A184" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B184" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C182" s="5" t="s">
+      <c r="C184" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D182" s="6" t="n">
+      <c r="D184" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="E182" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="F182" s="7" t="n">
+      <c r="E184" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="F184" s="7" t="n">
         <v>13800</v>
       </c>
-      <c r="G182" s="8">
+      <c r="G184" s="8">
         <v>46147</v>
       </c>
-      <c r="H182" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I182" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J182" s="6" t="s">
+      <c r="H184" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="183" customHeight="1" ht="15" spans="1:5">
-      <c r="A183" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B183" s="10" t="s">
+    <row r="185" customHeight="1" ht="15" spans="1:5">
+      <c r="A185" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B185" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C183" s="11" t="n">
+      <c r="C185" s="11" t="n">
         <v>13800</v>
       </c>
-      <c r="D183" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E183" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" customHeight="1" ht="15" spans="1:1">
-      <c r="A184" s="2" t="s">
+      <c r="D185" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E185" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" ht="15" spans="1:1">
+      <c r="A186" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="185" customHeight="1" ht="15" spans="1:10">
-      <c r="A185" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B185" s="5" t="s">
+    <row r="187" customHeight="1" ht="15" spans="1:10">
+      <c r="A187" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B187" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C185" s="5" t="s">
+      <c r="C187" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D185" s="6" t="n">
+      <c r="D187" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="E185" s="7" t="n">
+      <c r="E187" s="7" t="n">
         <v>53.98</v>
       </c>
-      <c r="F185" s="7" t="n">
+      <c r="F187" s="7" t="n">
         <v>3886.56</v>
       </c>
-      <c r="G185" s="8">
+      <c r="G187" s="8">
         <v>46121</v>
       </c>
-      <c r="H185" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I185" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J185" s="6" t="s">
+      <c r="H187" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" ht="15" spans="1:5">
+      <c r="A188" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C188" s="11" t="n">
+        <v>3886.56</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E188" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" ht="15" spans="1:1">
+      <c r="A189" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" ht="15" spans="1:10">
+      <c r="A190" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D190" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E190" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="F190" s="7" t="n">
+        <v>51600</v>
+      </c>
+      <c r="G190" s="8">
+        <v>46147</v>
+      </c>
+      <c r="H190" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" ht="15" spans="1:5">
+      <c r="A191" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C191" s="11" t="n">
+        <v>51600</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E191" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A192" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" ht="15" spans="1:12">
+      <c r="A193" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H193" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I193" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J193" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K193" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L193" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="194" customHeight="1" ht="15" spans="1:1">
+      <c r="A194" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="195" customHeight="1" ht="15" spans="1:10">
+      <c r="A195" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B195" s="5" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="186" customHeight="1" ht="15" spans="1:5">
-      <c r="A186" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B186" s="10" t="s">
+      <c r="C195" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D195" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E195" s="7" t="n">
+        <v>53.98</v>
+      </c>
+      <c r="F195" s="7" t="n">
+        <v>1187.56</v>
+      </c>
+      <c r="G195" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H195" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="196" customHeight="1" ht="15" spans="1:5">
+      <c r="A196" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B196" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C186" s="11" t="n">
-        <v>3886.56</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E186" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" customHeight="1" ht="15" spans="1:1">
-      <c r="A187" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="188" customHeight="1" ht="15" spans="1:10">
-      <c r="A188" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B188" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C188" s="5" t="s">
+      <c r="C196" s="11" t="n">
+        <v>1187.56</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E196" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" customHeight="1" ht="15" spans="1:1">
+      <c r="A197" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="198" customHeight="1" ht="15" spans="1:10">
+      <c r="A198" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C198" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D188" s="6" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E188" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="F188" s="7" t="n">
-        <v>51600</v>
-      </c>
-      <c r="G188" s="8">
+      <c r="D198" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E198" s="7" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="F198" s="7" t="n">
+        <v>32760</v>
+      </c>
+      <c r="G198" s="8">
+        <v>46127</v>
+      </c>
+      <c r="H198" s="6" t="n">
+        <v>768</v>
+      </c>
+      <c r="I198" s="9" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J198" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="199" customHeight="1" ht="15" spans="1:5">
+      <c r="A199" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B199" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C199" s="11" t="n">
+        <v>32760</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E199" s="12" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="200" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A200" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" ht="15" spans="1:12">
+      <c r="A201" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H201" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I201" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J201" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K201" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L201" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" ht="15" spans="1:1">
+      <c r="A202" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" ht="15" spans="1:10">
+      <c r="A203" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D203" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E203" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F203" s="7" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G203" s="8">
         <v>46147</v>
       </c>
-      <c r="H188" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J188" s="6" t="s">
+      <c r="H203" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I203" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="189" customHeight="1" ht="15" spans="1:5">
-      <c r="A189" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B189" s="10" t="s">
+    <row r="204" customHeight="1" ht="15" spans="1:5">
+      <c r="A204" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B204" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C189" s="11" t="n">
-        <v>51600</v>
-      </c>
-      <c r="D189" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E189" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A190" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" customHeight="1" ht="15" spans="1:12">
-      <c r="A191" s="2" t="s">
+      <c r="C204" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E204" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A205" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" ht="15" spans="1:12">
+      <c r="A206" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B191" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C191" s="2" t="s">
+      <c r="B206" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C206" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D191" s="2" t="s">
+      <c r="D206" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E191" s="3" t="s">
+      <c r="E206" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F191" s="3" t="s">
+      <c r="F206" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G191" s="3" t="s">
+      <c r="G206" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H191" s="3" t="s">
+      <c r="H206" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I191" s="3" t="s">
+      <c r="I206" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J191" s="3" t="s">
+      <c r="J206" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K191" s="2" t="s">
+      <c r="K206" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L191" s="3" t="s">
+      <c r="L206" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="192" customHeight="1" ht="15" spans="1:1">
-      <c r="A192" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="193" customHeight="1" ht="15" spans="1:10">
-      <c r="A193" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B193" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D193" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="E193" s="7" t="n">
-        <v>53.98</v>
-      </c>
-      <c r="F193" s="7" t="n">
-        <v>1187.56</v>
-      </c>
-      <c r="G193" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H193" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J193" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="194" customHeight="1" ht="15" spans="1:5">
-      <c r="A194" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B194" s="10" t="s">
+    <row r="207" customHeight="1" ht="15" spans="1:1">
+      <c r="A207" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" ht="15" spans="1:10">
+      <c r="A208" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D208" s="6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E208" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F208" s="7" t="n">
+        <v>70000</v>
+      </c>
+      <c r="G208" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H208" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I208" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J208" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" ht="15" spans="1:5">
+      <c r="A209" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B209" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C194" s="11" t="n">
-        <v>1187.56</v>
-      </c>
-      <c r="D194" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E194" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" customHeight="1" ht="15" spans="1:1">
-      <c r="A195" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="196" customHeight="1" ht="15" spans="1:10">
-      <c r="A196" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B196" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C196" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D196" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E196" s="7" t="n">
-        <v>21.84</v>
-      </c>
-      <c r="F196" s="7" t="n">
-        <v>32760</v>
-      </c>
-      <c r="G196" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H196" s="6" t="n">
-        <v>768</v>
-      </c>
-      <c r="I196" s="9" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="J196" s="6" t="s">
+      <c r="C209" s="11" t="n">
+        <v>70000</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E209" s="12" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" ht="15" spans="1:1">
+      <c r="A210" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="211" customHeight="1" ht="15" spans="1:10">
+      <c r="A211" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D211" s="6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E211" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F211" s="7" t="n">
+        <v>30400</v>
+      </c>
+      <c r="G211" s="8">
+        <v>46139</v>
+      </c>
+      <c r="H211" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="212" customHeight="1" ht="15" spans="1:5">
+      <c r="A212" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B212" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C212" s="11" t="n">
+        <v>30400</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E212" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" customHeight="1" ht="15" spans="1:1">
+      <c r="A213" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="214" customHeight="1" ht="15" spans="1:10">
+      <c r="A214" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D214" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E214" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F214" s="7" t="n">
+        <v>15200</v>
+      </c>
+      <c r="G214" s="8">
+        <v>46147</v>
+      </c>
+      <c r="H214" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="215" customHeight="1" ht="15" spans="1:5">
+      <c r="A215" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B215" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C215" s="11" t="n">
+        <v>15200</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E215" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" customHeight="1" ht="15" spans="1:1">
+      <c r="A216" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" ht="15" spans="1:10">
+      <c r="A217" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D217" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E217" s="7" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F217" s="7" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G217" s="8">
+        <v>46139</v>
+      </c>
+      <c r="H217" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" ht="15" spans="1:5">
+      <c r="A218" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B218" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C218" s="11" t="n">
+        <v>6200</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E218" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" ht="15" spans="1:1">
+      <c r="A219" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" ht="15" spans="1:10">
+      <c r="A220" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D220" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E220" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F220" s="7" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G220" s="8">
+        <v>46148</v>
+      </c>
+      <c r="H220" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" ht="15" spans="1:5">
+      <c r="A221" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B221" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C221" s="11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E221" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A222" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" ht="15" spans="1:12">
+      <c r="A223" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H223" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I223" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J223" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K223" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L223" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="224" customHeight="1" ht="15" spans="1:1">
+      <c r="A224" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="225" customHeight="1" ht="15" spans="1:10">
+      <c r="A225" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D225" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E225" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F225" s="7" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G225" s="8">
+        <v>46139</v>
+      </c>
+      <c r="H225" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I225" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="226" customHeight="1" ht="15" spans="1:5">
+      <c r="A226" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B226" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C226" s="11" t="n">
+        <v>19000</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E226" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" customHeight="1" ht="15" spans="1:1">
+      <c r="A227" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="228" customHeight="1" ht="15" spans="1:10">
+      <c r="A228" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D228" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E228" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F228" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G228" s="8">
+        <v>46135</v>
+      </c>
+      <c r="H228" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I228" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" ht="15" spans="1:5">
+      <c r="A229" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B229" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C229" s="11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E229" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A230" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" customHeight="1" ht="15" spans="1:12">
+      <c r="A231" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H231" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J231" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K231" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L231" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" ht="15" spans="1:1">
+      <c r="A232" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" ht="15" spans="1:10">
+      <c r="A233" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D233" s="6" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E233" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F233" s="7" t="n">
+        <v>26600</v>
+      </c>
+      <c r="G233" s="8">
+        <v>46135</v>
+      </c>
+      <c r="H233" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" ht="15" spans="1:10">
+      <c r="A234" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D234" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E234" s="7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F234" s="7" t="n">
+        <v>9750</v>
+      </c>
+      <c r="G234" s="8">
+        <v>46139</v>
+      </c>
+      <c r="H234" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I234" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" ht="15" spans="1:5">
+      <c r="A235" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B235" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C235" s="11" t="n">
+        <v>36350</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E235" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" customHeight="1" ht="15" spans="1:1">
+      <c r="A236" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="237" customHeight="1" ht="15" spans="1:10">
+      <c r="A237" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D237" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E237" s="7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F237" s="7" t="n">
+        <v>6600</v>
+      </c>
+      <c r="G237" s="8">
+        <v>46148</v>
+      </c>
+      <c r="H237" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I237" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="238" customHeight="1" ht="15" spans="1:5">
+      <c r="A238" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B238" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C238" s="11" t="n">
+        <v>6600</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E238" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" customHeight="1" ht="15" spans="1:1">
+      <c r="A239" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="240" customHeight="1" ht="15" spans="1:10">
+      <c r="A240" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D240" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E240" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F240" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G240" s="8">
+        <v>46147</v>
+      </c>
+      <c r="H240" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I240" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="197" customHeight="1" ht="15" spans="1:5">
-      <c r="A197" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B197" s="10" t="s">
+    <row r="241" customHeight="1" ht="15" spans="1:5">
+      <c r="A241" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B241" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C197" s="11" t="n">
-        <v>32760</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E197" s="12" t="n">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="198" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A198" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" customHeight="1" ht="15" spans="1:12">
-      <c r="A199" s="2" t="s">
+      <c r="C241" s="11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E241" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" customHeight="1" ht="15" spans="1:1">
+      <c r="A242" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="243" customHeight="1" ht="15" spans="1:10">
+      <c r="A243" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D243" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E243" s="7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F243" s="7" t="n">
+        <v>8600</v>
+      </c>
+      <c r="G243" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H243" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="244" customHeight="1" ht="15" spans="1:5">
+      <c r="A244" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B244" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C244" s="11" t="n">
+        <v>8600</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E244" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A245" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" customHeight="1" ht="15" spans="1:12">
+      <c r="A246" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B199" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C199" s="2" t="s">
+      <c r="B246" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C246" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D199" s="2" t="s">
+      <c r="D246" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E199" s="3" t="s">
+      <c r="E246" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F199" s="3" t="s">
+      <c r="F246" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G199" s="3" t="s">
+      <c r="G246" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H199" s="3" t="s">
+      <c r="H246" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I199" s="3" t="s">
+      <c r="I246" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J199" s="3" t="s">
+      <c r="J246" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K199" s="2" t="s">
+      <c r="K246" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L199" s="3" t="s">
+      <c r="L246" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="200" customHeight="1" ht="15" spans="1:1">
-      <c r="A200" s="2" t="s">
+    <row r="247" customHeight="1" ht="15" spans="1:1">
+      <c r="A247" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="248" customHeight="1" ht="15" spans="1:10">
+      <c r="A248" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D248" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E248" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F248" s="7" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G248" s="8">
+        <v>46147</v>
+      </c>
+      <c r="H248" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I248" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="249" customHeight="1" ht="15" spans="1:5">
+      <c r="A249" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B249" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C249" s="11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E249" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A250" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" customHeight="1" ht="15" spans="1:12">
+      <c r="A251" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H251" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I251" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J251" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K251" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L251" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="252" customHeight="1" ht="15" spans="1:1">
+      <c r="A252" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="201" customHeight="1" ht="15" spans="1:10">
-      <c r="A201" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B201" s="5" t="s">
+    <row r="253" customHeight="1" ht="15" spans="1:10">
+      <c r="A253" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B253" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C201" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D201" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E201" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F201" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G201" s="8">
+      <c r="C253" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D253" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E253" s="7" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="F253" s="7" t="n">
+        <v>3388</v>
+      </c>
+      <c r="G253" s="8">
         <v>46147</v>
       </c>
-      <c r="H201" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I201" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J201" s="6" t="s">
+      <c r="H253" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I253" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="202" customHeight="1" ht="15" spans="1:5">
-      <c r="A202" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B202" s="10" t="s">
+    <row r="254" customHeight="1" ht="15" spans="1:5">
+      <c r="A254" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B254" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C202" s="11" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E202" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A203" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" customHeight="1" ht="15" spans="1:12">
-      <c r="A204" s="2" t="s">
+      <c r="C254" s="11" t="n">
+        <v>3388</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E254" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" customHeight="1" ht="15" spans="1:1">
+      <c r="A255" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="256" customHeight="1" ht="15" spans="1:10">
+      <c r="A256" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D256" s="6" t="n">
+        <v>1512</v>
+      </c>
+      <c r="E256" s="7" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="F256" s="7" t="n">
+        <v>16919.28</v>
+      </c>
+      <c r="G256" s="8">
+        <v>46148</v>
+      </c>
+      <c r="H256" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I256" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="257" customHeight="1" ht="15" spans="1:5">
+      <c r="A257" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B257" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C257" s="11" t="n">
+        <v>16919.28</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E257" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" customHeight="1" ht="15" spans="1:1">
+      <c r="A258" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="259" customHeight="1" ht="15" spans="1:10">
+      <c r="A259" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D259" s="6" t="n">
+        <v>760</v>
+      </c>
+      <c r="E259" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="F259" s="7" t="n">
+        <v>12920</v>
+      </c>
+      <c r="G259" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H259" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I259" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="260" customHeight="1" ht="15" spans="1:5">
+      <c r="A260" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B260" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C260" s="11" t="n">
+        <v>12920</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E260" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A261" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" customHeight="1" ht="15" spans="1:12">
+      <c r="A262" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B204" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C204" s="2" t="s">
+      <c r="B262" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C262" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D204" s="2" t="s">
+      <c r="D262" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E204" s="3" t="s">
+      <c r="E262" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F204" s="3" t="s">
+      <c r="F262" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G204" s="3" t="s">
+      <c r="G262" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H204" s="3" t="s">
+      <c r="H262" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I204" s="3" t="s">
+      <c r="I262" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J204" s="3" t="s">
+      <c r="J262" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K204" s="2" t="s">
+      <c r="K262" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L204" s="3" t="s">
+      <c r="L262" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="205" customHeight="1" ht="15" spans="1:1">
-      <c r="A205" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="206" customHeight="1" ht="15" spans="1:10">
-      <c r="A206" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B206" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C206" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D206" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="E206" s="7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F206" s="7" t="n">
-        <v>70000</v>
-      </c>
-      <c r="G206" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H206" s="6" t="n">
-        <v>18000</v>
-      </c>
-      <c r="I206" s="9" t="n">
+    <row r="263" customHeight="1" ht="15" spans="1:1">
+      <c r="A263" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="264" customHeight="1" ht="15" spans="1:10">
+      <c r="A264" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D264" s="6" t="n">
+        <v>720</v>
+      </c>
+      <c r="E264" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F264" s="7" t="n">
+        <v>10800</v>
+      </c>
+      <c r="G264" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H264" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="265" customHeight="1" ht="15" spans="1:5">
+      <c r="A265" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B265" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C265" s="11" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E265" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A266" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" customHeight="1" ht="15" spans="1:12">
+      <c r="A267" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G267" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H267" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I267" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J206" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="207" customHeight="1" ht="15" spans="1:5">
-      <c r="A207" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B207" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C207" s="11" t="n">
-        <v>70000</v>
-      </c>
-      <c r="D207" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E207" s="12" t="n">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="208" customHeight="1" ht="15" spans="1:1">
-      <c r="A208" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="209" customHeight="1" ht="15" spans="1:10">
-      <c r="A209" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B209" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C209" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D209" s="6" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E209" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F209" s="7" t="n">
-        <v>30400</v>
-      </c>
-      <c r="G209" s="8">
-        <v>46139</v>
-      </c>
-      <c r="H209" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I209" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J209" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="210" customHeight="1" ht="15" spans="1:5">
-      <c r="A210" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B210" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C210" s="11" t="n">
-        <v>30400</v>
-      </c>
-      <c r="D210" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E210" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211" customHeight="1" ht="15" spans="1:1">
-      <c r="A211" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="212" customHeight="1" ht="15" spans="1:10">
-      <c r="A212" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B212" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C212" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D212" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E212" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F212" s="7" t="n">
-        <v>15200</v>
-      </c>
-      <c r="G212" s="8">
-        <v>46147</v>
-      </c>
-      <c r="H212" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I212" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J212" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="213" customHeight="1" ht="15" spans="1:5">
-      <c r="A213" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B213" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C213" s="11" t="n">
-        <v>15200</v>
-      </c>
-      <c r="D213" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E213" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" customHeight="1" ht="15" spans="1:1">
-      <c r="A214" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="215" customHeight="1" ht="15" spans="1:10">
-      <c r="A215" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B215" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C215" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D215" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E215" s="7" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="F215" s="7" t="n">
-        <v>6200</v>
-      </c>
-      <c r="G215" s="8">
-        <v>46139</v>
-      </c>
-      <c r="H215" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I215" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J215" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="216" customHeight="1" ht="15" spans="1:5">
-      <c r="A216" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B216" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C216" s="11" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D216" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E216" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" customHeight="1" ht="15" spans="1:1">
-      <c r="A217" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="218" customHeight="1" ht="15" spans="1:10">
-      <c r="A218" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B218" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C218" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D218" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E218" s="7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="F218" s="7" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G218" s="8">
-        <v>46148</v>
-      </c>
-      <c r="H218" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I218" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J218" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="219" customHeight="1" ht="15" spans="1:5">
-      <c r="A219" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B219" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C219" s="11" t="n">
-        <v>5800</v>
-      </c>
-      <c r="D219" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E219" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A220" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" customHeight="1" ht="15" spans="1:12">
-      <c r="A221" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E221" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F221" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G221" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H221" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I221" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J221" s="3" t="s">
+      <c r="J267" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K221" s="2" t="s">
+      <c r="K267" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L221" s="3" t="s">
+      <c r="L267" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="222" customHeight="1" ht="15" spans="1:1">
-      <c r="A222" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="223" customHeight="1" ht="15" spans="1:10">
-      <c r="A223" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B223" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D223" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E223" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F223" s="7" t="n">
-        <v>19000</v>
-      </c>
-      <c r="G223" s="8">
-        <v>46139</v>
-      </c>
-      <c r="H223" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I223" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J223" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="224" customHeight="1" ht="15" spans="1:5">
-      <c r="A224" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B224" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C224" s="11" t="n">
-        <v>19000</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E224" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" customHeight="1" ht="15" spans="1:1">
-      <c r="A225" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="226" customHeight="1" ht="15" spans="1:10">
-      <c r="A226" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B226" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C226" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D226" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E226" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F226" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G226" s="8">
-        <v>46135</v>
-      </c>
-      <c r="H226" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I226" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J226" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="227" customHeight="1" ht="15" spans="1:5">
-      <c r="A227" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B227" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C227" s="11" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E227" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A228" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" customHeight="1" ht="15" spans="1:12">
-      <c r="A229" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D229" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E229" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F229" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G229" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H229" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I229" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J229" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K229" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L229" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="230" customHeight="1" ht="15" spans="1:1">
-      <c r="A230" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="231" customHeight="1" ht="15" spans="1:10">
-      <c r="A231" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B231" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D231" s="6" t="n">
-        <v>70000</v>
-      </c>
-      <c r="E231" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F231" s="7" t="n">
-        <v>26600</v>
-      </c>
-      <c r="G231" s="8">
-        <v>46135</v>
-      </c>
-      <c r="H231" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I231" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J231" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="232" customHeight="1" ht="15" spans="1:10">
-      <c r="A232" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B232" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C232" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D232" s="6" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E232" s="7" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F232" s="7" t="n">
-        <v>9750</v>
-      </c>
-      <c r="G232" s="8">
-        <v>46139</v>
-      </c>
-      <c r="H232" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I232" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J232" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="233" customHeight="1" ht="15" spans="1:5">
-      <c r="A233" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B233" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C233" s="11" t="n">
-        <v>36350</v>
-      </c>
-      <c r="D233" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E233" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" customHeight="1" ht="15" spans="1:1">
-      <c r="A234" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="235" customHeight="1" ht="15" spans="1:10">
-      <c r="A235" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B235" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C235" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D235" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E235" s="7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="F235" s="7" t="n">
-        <v>6600</v>
-      </c>
-      <c r="G235" s="8">
-        <v>46148</v>
-      </c>
-      <c r="H235" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I235" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J235" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="236" customHeight="1" ht="15" spans="1:5">
-      <c r="A236" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B236" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C236" s="11" t="n">
-        <v>6600</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E236" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" customHeight="1" ht="15" spans="1:1">
-      <c r="A237" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="238" customHeight="1" ht="15" spans="1:10">
-      <c r="A238" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B238" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C238" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D238" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E238" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F238" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G238" s="8">
-        <v>46147</v>
-      </c>
-      <c r="H238" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I238" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J238" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="239" customHeight="1" ht="15" spans="1:5">
-      <c r="A239" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B239" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C239" s="11" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D239" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E239" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" customHeight="1" ht="15" spans="1:1">
-      <c r="A240" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="241" customHeight="1" ht="15" spans="1:10">
-      <c r="A241" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B241" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C241" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D241" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E241" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F241" s="7" t="n">
-        <v>40000</v>
-      </c>
-      <c r="G241" s="8">
-        <v>46147</v>
-      </c>
-      <c r="H241" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I241" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J241" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="242" customHeight="1" ht="15" spans="1:5">
-      <c r="A242" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B242" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C242" s="11" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D242" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E242" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A243" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244" customHeight="1" ht="15" spans="1:12">
-      <c r="A244" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D244" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E244" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F244" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G244" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H244" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I244" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J244" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K244" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L244" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="245" customHeight="1" ht="15" spans="1:1">
-      <c r="A245" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="246" customHeight="1" ht="15" spans="1:10">
-      <c r="A246" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B246" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C246" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D246" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E246" s="7" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="F246" s="7" t="n">
-        <v>3388</v>
-      </c>
-      <c r="G246" s="8">
-        <v>46147</v>
-      </c>
-      <c r="H246" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I246" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J246" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="247" customHeight="1" ht="15" spans="1:5">
-      <c r="A247" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B247" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C247" s="11" t="n">
-        <v>3388</v>
-      </c>
-      <c r="D247" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E247" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248" customHeight="1" ht="15" spans="1:1">
-      <c r="A248" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="249" customHeight="1" ht="15" spans="1:10">
-      <c r="A249" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B249" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C249" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D249" s="6" t="n">
-        <v>1512</v>
-      </c>
-      <c r="E249" s="7" t="n">
-        <v>11.19</v>
-      </c>
-      <c r="F249" s="7" t="n">
-        <v>16919.28</v>
-      </c>
-      <c r="G249" s="8">
-        <v>46148</v>
-      </c>
-      <c r="H249" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I249" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J249" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="250" customHeight="1" ht="15" spans="1:5">
-      <c r="A250" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B250" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C250" s="11" t="n">
-        <v>16919.28</v>
-      </c>
-      <c r="D250" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E250" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" customHeight="1" ht="15" spans="1:1">
-      <c r="A251" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="252" customHeight="1" ht="15" spans="1:10">
-      <c r="A252" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B252" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C252" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D252" s="6" t="n">
-        <v>432</v>
-      </c>
-      <c r="E252" s="7" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="F252" s="7" t="n">
-        <v>6691.68</v>
-      </c>
-      <c r="G252" s="8">
-        <v>46147</v>
-      </c>
-      <c r="H252" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I252" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J252" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="253" customHeight="1" ht="15" spans="1:5">
-      <c r="A253" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B253" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C253" s="11" t="n">
-        <v>6691.68</v>
-      </c>
-      <c r="D253" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E253" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A254" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" customHeight="1" ht="15" spans="1:12">
-      <c r="A255" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D255" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E255" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F255" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G255" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H255" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I255" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J255" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K255" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L255" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="256" customHeight="1" ht="15" spans="1:1">
-      <c r="A256" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="257" customHeight="1" ht="15" spans="1:10">
-      <c r="A257" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B257" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C257" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D257" s="6" t="n">
-        <v>8010</v>
-      </c>
-      <c r="E257" s="7" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F257" s="7" t="n">
-        <v>166527.9</v>
-      </c>
-      <c r="G257" s="8">
-        <v>46122</v>
-      </c>
-      <c r="H257" s="6" t="n">
-        <v>2010</v>
-      </c>
-      <c r="I257" s="9" t="n">
-        <v>25.09</v>
-      </c>
-      <c r="J257" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="258" customHeight="1" ht="15" spans="1:5">
-      <c r="A258" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B258" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C258" s="11" t="n">
-        <v>166527.9</v>
-      </c>
-      <c r="D258" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E258" s="12" t="n">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="259" customHeight="1" ht="15" spans="1:1">
-      <c r="A259" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="260" customHeight="1" ht="15" spans="1:10">
-      <c r="A260" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B260" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C260" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D260" s="6" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E260" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="F260" s="7" t="n">
-        <v>312000</v>
-      </c>
-      <c r="G260" s="8">
-        <v>46100</v>
-      </c>
-      <c r="H260" s="6" t="n">
-        <v>18900</v>
-      </c>
-      <c r="I260" s="9" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="J260" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="261" customHeight="1" ht="15" spans="1:10">
-      <c r="A261" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B261" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C261" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D261" s="6" t="n">
-        <v>10020</v>
-      </c>
-      <c r="E261" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="F261" s="7" t="n">
-        <v>130260</v>
-      </c>
-      <c r="G261" s="8">
-        <v>46147</v>
-      </c>
-      <c r="H261" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I261" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J261" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="262" customHeight="1" ht="15" spans="1:5">
-      <c r="A262" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B262" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C262" s="11" t="n">
-        <v>442260</v>
-      </c>
-      <c r="D262" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E262" s="12" t="n">
-        <v>18900</v>
-      </c>
-    </row>
-    <row r="263" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A263" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" customHeight="1" ht="15" spans="1:12">
-      <c r="A264" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E264" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F264" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G264" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H264" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I264" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J264" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K264" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L264" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="265" customHeight="1" ht="15" spans="1:1">
-      <c r="A265" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="266" customHeight="1" ht="15" spans="1:10">
-      <c r="A266" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B266" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C266" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D266" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="E266" s="7" t="n">
-        <v>17.57</v>
-      </c>
-      <c r="F266" s="7" t="n">
-        <v>1124.48</v>
-      </c>
-      <c r="G266" s="8">
-        <v>46148</v>
-      </c>
-      <c r="H266" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I266" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J266" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="267" customHeight="1" ht="15" spans="1:5">
-      <c r="A267" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B267" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C267" s="11" t="n">
-        <v>1124.48</v>
-      </c>
-      <c r="D267" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E267" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="268" customHeight="1" ht="15" spans="1:1">
       <c r="A268" s="2" t="s">
-        <v>148</v>
+        <v>35</v>
       </c>
     </row>
     <row r="269" customHeight="1" ht="15" spans="1:10">
@@ -6665,31 +6680,31 @@
         <v>14</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>149</v>
+        <v>36</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D269" s="6" t="n">
-        <v>200</v>
+        <v>8010</v>
       </c>
       <c r="E269" s="7" t="n">
-        <v>16.5</v>
+        <v>20.79</v>
       </c>
       <c r="F269" s="7" t="n">
-        <v>3300</v>
+        <v>166527.9</v>
       </c>
       <c r="G269" s="8">
-        <v>46148</v>
+        <v>46122</v>
       </c>
       <c r="H269" s="6" t="n">
-        <v>0</v>
+        <v>2010</v>
       </c>
       <c r="I269" s="9" t="n">
-        <v>0</v>
+        <v>25.09</v>
       </c>
       <c r="J269" s="6" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="270" customHeight="1" ht="15" spans="1:5">
@@ -6700,428 +6715,449 @@
         <v>24</v>
       </c>
       <c r="C270" s="11" t="n">
+        <v>166527.9</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E270" s="12" t="n">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="271" customHeight="1" ht="15" spans="1:1">
+      <c r="A271" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="272" customHeight="1" ht="15" spans="1:10">
+      <c r="A272" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C272" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D272" s="6" t="n">
+        <v>2160</v>
+      </c>
+      <c r="E272" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F272" s="7" t="n">
+        <v>28080</v>
+      </c>
+      <c r="G272" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H272" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I272" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="273" customHeight="1" ht="15" spans="1:5">
+      <c r="A273" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B273" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C273" s="11" t="n">
+        <v>28080</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E273" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" customHeight="1" ht="15" spans="1:1">
+      <c r="A274" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="275" customHeight="1" ht="15" spans="1:10">
+      <c r="A275" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D275" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E275" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F275" s="7" t="n">
+        <v>312000</v>
+      </c>
+      <c r="G275" s="8">
+        <v>46100</v>
+      </c>
+      <c r="H275" s="6" t="n">
+        <v>18900</v>
+      </c>
+      <c r="I275" s="9" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="J275" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="276" customHeight="1" ht="15" spans="1:10">
+      <c r="A276" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D276" s="6" t="n">
+        <v>10020</v>
+      </c>
+      <c r="E276" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F276" s="7" t="n">
+        <v>130260</v>
+      </c>
+      <c r="G276" s="8">
+        <v>46147</v>
+      </c>
+      <c r="H276" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I276" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="277" customHeight="1" ht="15" spans="1:5">
+      <c r="A277" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B277" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C277" s="11" t="n">
+        <v>442260</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E277" s="12" t="n">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="278" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A278" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" customHeight="1" ht="15" spans="1:12">
+      <c r="A279" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G279" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H279" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I279" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J279" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K279" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L279" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="280" customHeight="1" ht="15" spans="1:1">
+      <c r="A280" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="281" customHeight="1" ht="15" spans="1:10">
+      <c r="A281" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D281" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E281" s="7" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="F281" s="7" t="n">
+        <v>1124.48</v>
+      </c>
+      <c r="G281" s="8">
+        <v>46148</v>
+      </c>
+      <c r="H281" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I281" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="282" customHeight="1" ht="15" spans="1:5">
+      <c r="A282" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B282" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C282" s="11" t="n">
+        <v>1124.48</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E282" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" customHeight="1" ht="15" spans="1:1">
+      <c r="A283" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="284" customHeight="1" ht="15" spans="1:10">
+      <c r="A284" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D284" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E284" s="7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F284" s="7" t="n">
         <v>3300</v>
       </c>
-      <c r="D270" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E270" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A271" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" customHeight="1" ht="15" spans="1:12">
-      <c r="A272" s="2" t="s">
+      <c r="G284" s="8">
+        <v>46148</v>
+      </c>
+      <c r="H284" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I284" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="285" customHeight="1" ht="15" spans="1:5">
+      <c r="A285" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B285" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C285" s="11" t="n">
+        <v>3300</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E285" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A286" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" customHeight="1" ht="15" spans="1:12">
+      <c r="A287" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B272" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C272" s="2" t="s">
+      <c r="B287" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C287" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D272" s="2" t="s">
+      <c r="D287" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E272" s="3" t="s">
+      <c r="E287" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F272" s="3" t="s">
+      <c r="F287" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G272" s="3" t="s">
+      <c r="G287" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H272" s="3" t="s">
+      <c r="H287" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I272" s="3" t="s">
+      <c r="I287" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J272" s="3" t="s">
+      <c r="J287" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K272" s="2" t="s">
+      <c r="K287" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L272" s="3" t="s">
+      <c r="L287" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="273" customHeight="1" ht="15" spans="1:1">
-      <c r="A273" s="2" t="s">
+    <row r="288" customHeight="1" ht="15" spans="1:1">
+      <c r="A288" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="274" customHeight="1" ht="15" spans="1:10">
-      <c r="A274" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B274" s="5" t="s">
+    <row r="289" customHeight="1" ht="15" spans="1:10">
+      <c r="A289" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B289" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C274" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D274" s="6" t="n">
+      <c r="C289" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D289" s="6" t="n">
         <v>128</v>
       </c>
-      <c r="E274" s="7" t="n">
+      <c r="E289" s="7" t="n">
         <v>20.37</v>
       </c>
-      <c r="F274" s="7" t="n">
+      <c r="F289" s="7" t="n">
         <v>2607.36</v>
       </c>
-      <c r="G274" s="8">
+      <c r="G289" s="8">
         <v>46148</v>
       </c>
-      <c r="H274" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I274" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J274" s="6" t="s">
+      <c r="H289" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I289" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="275" customHeight="1" ht="15" spans="1:5">
-      <c r="A275" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B275" s="10" t="s">
+    <row r="290" customHeight="1" ht="15" spans="1:5">
+      <c r="A290" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B290" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C275" s="11" t="n">
+      <c r="C290" s="11" t="n">
         <v>2607.36</v>
       </c>
-      <c r="D275" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E275" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276" customHeight="1" ht="15" spans="1:1">
-      <c r="A276" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="277" customHeight="1" ht="15" spans="1:10">
-      <c r="A277" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B277" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C277" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D277" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E277" s="7" t="n">
-        <v>13.79</v>
-      </c>
-      <c r="F277" s="7" t="n">
-        <v>13790</v>
-      </c>
-      <c r="G277" s="8">
-        <v>46147</v>
-      </c>
-      <c r="H277" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I277" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J277" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="278" customHeight="1" ht="15" spans="1:5">
-      <c r="A278" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B278" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C278" s="11" t="n">
-        <v>13790</v>
-      </c>
-      <c r="D278" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E278" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279" customHeight="1" ht="15" spans="1:1">
-      <c r="A279" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="280" customHeight="1" ht="15" spans="1:10">
-      <c r="A280" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B280" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C280" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D280" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E280" s="7" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="F280" s="7" t="n">
-        <v>2298</v>
-      </c>
-      <c r="G280" s="8">
-        <v>46147</v>
-      </c>
-      <c r="H280" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I280" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J280" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="281" customHeight="1" ht="15" spans="1:5">
-      <c r="A281" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B281" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C281" s="11" t="n">
-        <v>2298</v>
-      </c>
-      <c r="D281" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E281" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A282" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" customHeight="1" ht="15" spans="1:12">
-      <c r="A283" s="2" t="s">
+      <c r="D290" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E290" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A291" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" customHeight="1" ht="15" spans="1:12">
+      <c r="A292" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B283" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C283" s="2" t="s">
+      <c r="B292" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C292" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D283" s="2" t="s">
+      <c r="D292" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E283" s="3" t="s">
+      <c r="E292" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F283" s="3" t="s">
+      <c r="F292" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G283" s="3" t="s">
+      <c r="G292" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H283" s="3" t="s">
+      <c r="H292" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I283" s="3" t="s">
+      <c r="I292" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J283" s="3" t="s">
+      <c r="J292" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K283" s="2" t="s">
+      <c r="K292" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L283" s="3" t="s">
+      <c r="L292" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="284" customHeight="1" ht="15" spans="1:1">
-      <c r="A284" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="285" customHeight="1" ht="15" spans="1:10">
-      <c r="A285" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B285" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C285" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D285" s="6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E285" s="7" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F285" s="7" t="n">
-        <v>41700</v>
-      </c>
-      <c r="G285" s="8">
-        <v>46147</v>
-      </c>
-      <c r="H285" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I285" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J285" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="286" customHeight="1" ht="15" spans="1:5">
-      <c r="A286" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B286" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C286" s="11" t="n">
-        <v>41700</v>
-      </c>
-      <c r="D286" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E286" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287" customHeight="1" ht="15" spans="1:1">
-      <c r="A287" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="288" customHeight="1" ht="15" spans="1:10">
-      <c r="A288" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B288" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C288" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D288" s="6" t="n">
-        <v>432</v>
-      </c>
-      <c r="E288" s="7" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F288" s="7" t="n">
-        <v>3019.68</v>
-      </c>
-      <c r="G288" s="8">
-        <v>46147</v>
-      </c>
-      <c r="H288" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I288" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J288" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="289" customHeight="1" ht="15" spans="1:5">
-      <c r="A289" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B289" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C289" s="11" t="n">
-        <v>3019.68</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E289" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290" customHeight="1" ht="15" spans="1:1">
-      <c r="A290" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="291" customHeight="1" ht="15" spans="1:10">
-      <c r="A291" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B291" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C291" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D291" s="6" t="n">
-        <v>1224</v>
-      </c>
-      <c r="E291" s="7" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="F291" s="7" t="n">
-        <v>5985.36</v>
-      </c>
-      <c r="G291" s="8">
-        <v>46148</v>
-      </c>
-      <c r="H291" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I291" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J291" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="292" customHeight="1" ht="15" spans="1:5">
-      <c r="A292" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B292" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C292" s="11" t="n">
-        <v>5985.36</v>
-      </c>
-      <c r="D292" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E292" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="293" customHeight="1" ht="15" spans="1:1">
       <c r="A293" s="2" t="s">
-        <v>148</v>
+        <v>49</v>
       </c>
     </row>
     <row r="294" customHeight="1" ht="15" spans="1:10">
@@ -7129,22 +7165,22 @@
         <v>14</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D294" s="6" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="E294" s="7" t="n">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="F294" s="7" t="n">
-        <v>14500</v>
+        <v>41700</v>
       </c>
       <c r="G294" s="8">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="H294" s="6" t="n">
         <v>0</v>
@@ -7153,7 +7189,7 @@
         <v>0</v>
       </c>
       <c r="J294" s="6" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="295" customHeight="1" ht="15" spans="1:5">
@@ -7164,12 +7200,66 @@
         <v>24</v>
       </c>
       <c r="C295" s="11" t="n">
+        <v>41700</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E295" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" customHeight="1" ht="15" spans="1:1">
+      <c r="A296" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="297" customHeight="1" ht="15" spans="1:10">
+      <c r="A297" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D297" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E297" s="7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F297" s="7" t="n">
         <v>14500</v>
       </c>
-      <c r="D295" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E295" s="12" t="n">
+      <c r="G297" s="8">
+        <v>46148</v>
+      </c>
+      <c r="H297" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I297" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="298" customHeight="1" ht="15" spans="1:5">
+      <c r="A298" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B298" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C298" s="11" t="n">
+        <v>14500</v>
+      </c>
+      <c r="D298" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E298" s="12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="153">
   <si>
     <t>MATRIZ CNPJ: 40.357.820/0001-50R Y DOIS - 58082-025
  ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
@@ -311,9 +311,6 @@
     <t>ELIENE RESENDE</t>
   </si>
   <si>
-    <t xml:space="preserve">1588 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND </t>
-  </si>
-  <si>
     <t>1640 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND</t>
   </si>
   <si>
@@ -368,9 +365,6 @@
     <t xml:space="preserve">02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND </t>
   </si>
   <si>
-    <t xml:space="preserve">1642 - GAZE ESTÉRIL 11FIOS -  PCT 10 UND </t>
-  </si>
-  <si>
     <t>T J FEITOSA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
   </si>
   <si>
@@ -380,24 +374,39 @@
     <t>ESTERIL - 13 FIOS</t>
   </si>
   <si>
+    <t>DHERMA DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03 - GAZE ESTÉRIL 13FIOS - PCT 10 UND </t>
+  </si>
+  <si>
+    <t>KELLEN</t>
+  </si>
+  <si>
     <t>782</t>
   </si>
   <si>
-    <t xml:space="preserve">03 - GAZE ESTÉRIL 13FIOS - PCT 10 UND </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1643 - GAZE ESTÉRIL 13FIOS - PCT 10 UND </t>
-  </si>
-  <si>
     <t>842</t>
   </si>
   <si>
+    <t>730 - GAZE ESTÉRIL 13FIOS - MEDLIFE - PCT 10 UND</t>
+  </si>
+  <si>
+    <t>NORDESTE COMERCIAL DE PROD FARMACEUTICOS LTDA</t>
+  </si>
+  <si>
+    <t>844</t>
+  </si>
+  <si>
+    <t>04 - GAZE ESTÉRIL 13FIOS - CONVIVA - PCT 10 UND</t>
+  </si>
+  <si>
     <t>GAZE EM ROLO - 09 FIOS</t>
   </si>
   <si>
-    <t xml:space="preserve">85 - GAZE CIRCULAR NAO ESTERIL 09 FIOS </t>
-  </si>
-  <si>
     <t>90 - GAZE CIRCULAR NAO ESTERIL 09 FIOS J</t>
   </si>
   <si>
@@ -456,6 +465,9 @@
   </si>
   <si>
     <t>PCT NÃO EST. - 9 FIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08 - GAZE NAO ESTÉRIL 09 FIOS </t>
   </si>
   <si>
     <t xml:space="preserve">2090 - GAZE NAO ESTÉRIL 09 FIOS </t>
@@ -617,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L254"/>
+  <dimension ref="A1:L255"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
   <cols>
     <col customWidth="1" width="89.23828125" min="1" max="1"/>
@@ -4243,182 +4255,182 @@
         <v>14</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>99</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>20100</v>
+        <v>1200</v>
       </c>
       <c r="E144" s="7" t="n">
-        <v>4.45</v>
+        <v>7.22</v>
       </c>
       <c r="F144" s="7" t="n">
-        <v>89445</v>
+        <v>8664</v>
       </c>
       <c r="G144" s="8">
         <v>46139</v>
       </c>
       <c r="H144" s="6" t="n">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="I144" s="9" t="n">
-        <v>25.37</v>
+        <v>0</v>
       </c>
       <c r="J144" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="145" customHeight="1" ht="15" spans="1:10">
-      <c r="A145" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C145" s="5" t="s">
+    <row r="145" customHeight="1" ht="15" spans="1:5">
+      <c r="A145" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C145" s="11" t="n">
+        <v>8664</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E145" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" ht="15" spans="1:1">
+      <c r="A146" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D145" s="6" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E145" s="7" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="F145" s="7" t="n">
-        <v>8664</v>
-      </c>
-      <c r="G145" s="8">
-        <v>46139</v>
-      </c>
-      <c r="H145" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" s="6" t="s">
+    </row>
+    <row r="147" customHeight="1" ht="15" spans="1:10">
+      <c r="A147" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D147" s="6" t="n">
+        <v>20100</v>
+      </c>
+      <c r="E147" s="7" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="F147" s="7" t="n">
+        <v>100299</v>
+      </c>
+      <c r="G147" s="8">
+        <v>46147</v>
+      </c>
+      <c r="H147" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" ht="15" spans="1:5">
+      <c r="A148" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C148" s="11" t="n">
+        <v>100299</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E148" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A149" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" ht="15" spans="1:12">
+      <c r="A150" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H150" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J150" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K150" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L150" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" ht="15" spans="1:1">
+      <c r="A151" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" ht="15" spans="1:10">
+      <c r="A152" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D152" s="6" t="n">
+        <v>1092</v>
+      </c>
+      <c r="E152" s="7" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="F152" s="7" t="n">
+        <v>49030.8</v>
+      </c>
+      <c r="G152" s="8">
+        <v>46141</v>
+      </c>
+      <c r="H152" s="6" t="n">
+        <v>192</v>
+      </c>
+      <c r="I152" s="9" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="J152" s="6" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="146" customHeight="1" ht="15" spans="1:5">
-      <c r="A146" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B146" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C146" s="11" t="n">
-        <v>98109</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E146" s="12" t="n">
-        <v>5100</v>
-      </c>
-    </row>
-    <row r="147" customHeight="1" ht="15" spans="1:1">
-      <c r="A147" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="148" customHeight="1" ht="15" spans="1:10">
-      <c r="A148" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D148" s="6" t="n">
-        <v>20100</v>
-      </c>
-      <c r="E148" s="7" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="F148" s="7" t="n">
-        <v>100299</v>
-      </c>
-      <c r="G148" s="8">
-        <v>46147</v>
-      </c>
-      <c r="H148" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="149" customHeight="1" ht="15" spans="1:5">
-      <c r="A149" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B149" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C149" s="11" t="n">
-        <v>100299</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E149" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A150" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" customHeight="1" ht="15" spans="1:12">
-      <c r="A151" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E151" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F151" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G151" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H151" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I151" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J151" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K151" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L151" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="152" customHeight="1" ht="15" spans="1:1">
-      <c r="A152" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="153" customHeight="1" ht="15" spans="1:10">
@@ -4426,862 +4438,862 @@
         <v>14</v>
       </c>
       <c r="B153" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C153" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C153" s="5" t="s">
-        <v>106</v>
-      </c>
       <c r="D153" s="6" t="n">
-        <v>1092</v>
+        <v>504</v>
       </c>
       <c r="E153" s="7" t="n">
         <v>44.9</v>
       </c>
       <c r="F153" s="7" t="n">
-        <v>49030.8</v>
+        <v>22629.6</v>
       </c>
       <c r="G153" s="8">
         <v>46141</v>
       </c>
       <c r="H153" s="6" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>17.58</v>
+        <v>0</v>
       </c>
       <c r="J153" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="154" customHeight="1" ht="15" spans="1:10">
-      <c r="A154" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B154" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C154" s="5" t="s">
+    <row r="154" customHeight="1" ht="15" spans="1:5">
+      <c r="A154" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C154" s="11" t="n">
+        <v>71660.4</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E154" s="12" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" ht="15" spans="1:1">
+      <c r="A155" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D154" s="6" t="n">
-        <v>504</v>
-      </c>
-      <c r="E154" s="7" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="F154" s="7" t="n">
-        <v>22629.6</v>
-      </c>
-      <c r="G154" s="8">
-        <v>46141</v>
-      </c>
-      <c r="H154" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J154" s="6" t="s">
+    </row>
+    <row r="156" customHeight="1" ht="15" spans="1:10">
+      <c r="A156" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D156" s="6" t="n">
+        <v>408</v>
+      </c>
+      <c r="E156" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="F156" s="7" t="n">
+        <v>18360</v>
+      </c>
+      <c r="G156" s="8">
+        <v>46147</v>
+      </c>
+      <c r="H156" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" ht="15" spans="1:5">
+      <c r="A157" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B157" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C157" s="11" t="n">
+        <v>18360</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E157" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" ht="15" spans="1:1">
+      <c r="A158" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" ht="15" spans="1:10">
+      <c r="A159" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D159" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="E159" s="7" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="F159" s="7" t="n">
+        <v>2328</v>
+      </c>
+      <c r="G159" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H159" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" ht="15" spans="1:5">
+      <c r="A160" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B160" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C160" s="11" t="n">
+        <v>2328</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E160" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" ht="15" spans="1:1">
+      <c r="A161" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" ht="15" spans="1:10">
+      <c r="A162" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D162" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="E162" s="7" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="F162" s="7" t="n">
+        <v>8316</v>
+      </c>
+      <c r="G162" s="8">
+        <v>46148</v>
+      </c>
+      <c r="H162" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" ht="15" spans="1:5">
+      <c r="A163" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C163" s="11" t="n">
+        <v>8316</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E163" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A164" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" ht="15" spans="1:12">
+      <c r="A165" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H165" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I165" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J165" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L165" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" ht="15" spans="1:1">
+      <c r="A166" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" ht="15" spans="1:10">
+      <c r="A167" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D167" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E167" s="7" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="F167" s="7" t="n">
+        <v>55080</v>
+      </c>
+      <c r="G167" s="8">
+        <v>46147</v>
+      </c>
+      <c r="H167" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="155" customHeight="1" ht="15" spans="1:5">
-      <c r="A155" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B155" s="10" t="s">
+    <row r="168" customHeight="1" ht="15" spans="1:5">
+      <c r="A168" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B168" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C155" s="11" t="n">
-        <v>71660.4</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E155" s="12" t="n">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="156" customHeight="1" ht="15" spans="1:1">
-      <c r="A156" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="157" customHeight="1" ht="15" spans="1:10">
-      <c r="A157" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D157" s="6" t="n">
-        <v>400</v>
-      </c>
-      <c r="E157" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="F157" s="7" t="n">
-        <v>18000</v>
-      </c>
-      <c r="G157" s="8">
-        <v>46147</v>
-      </c>
-      <c r="H157" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I157" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="158" customHeight="1" ht="15" spans="1:5">
-      <c r="A158" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B158" s="10" t="s">
+      <c r="C168" s="11" t="n">
+        <v>55080</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E168" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" ht="15" spans="1:1">
+      <c r="A169" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" ht="15" spans="1:10">
+      <c r="A170" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D170" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="E170" s="7" t="n">
+        <v>52.47</v>
+      </c>
+      <c r="F170" s="7" t="n">
+        <v>2518.56</v>
+      </c>
+      <c r="G170" s="8">
+        <v>46148</v>
+      </c>
+      <c r="H170" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="171" customHeight="1" ht="15" spans="1:5">
+      <c r="A171" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B171" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C158" s="11" t="n">
-        <v>18000</v>
-      </c>
-      <c r="D158" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E158" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" customHeight="1" ht="15" spans="1:1">
-      <c r="A159" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="160" customHeight="1" ht="15" spans="1:10">
-      <c r="A160" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B160" s="5" t="s">
+      <c r="C171" s="11" t="n">
+        <v>2518.56</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E171" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" ht="15" spans="1:1">
+      <c r="A172" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" ht="15" spans="1:10">
+      <c r="A173" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C173" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C160" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D160" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="E160" s="7" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="F160" s="7" t="n">
-        <v>2328</v>
-      </c>
-      <c r="G160" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H160" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" s="6" t="s">
+      <c r="D173" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E173" s="7" t="n">
+        <v>53.98</v>
+      </c>
+      <c r="F173" s="7" t="n">
+        <v>3886.56</v>
+      </c>
+      <c r="G173" s="8">
+        <v>46121</v>
+      </c>
+      <c r="H173" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" ht="15" spans="1:5">
+      <c r="A174" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B174" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C174" s="11" t="n">
+        <v>3886.56</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E174" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" ht="15" spans="1:1">
+      <c r="A175" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" ht="15" spans="1:10">
+      <c r="A176" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D176" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E176" s="7" t="n">
+        <v>53.98</v>
+      </c>
+      <c r="F176" s="7" t="n">
+        <v>1295.52</v>
+      </c>
+      <c r="G176" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H176" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="177" customHeight="1" ht="15" spans="1:5">
+      <c r="A177" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B177" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C177" s="11" t="n">
+        <v>1295.52</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E177" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A178" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" customHeight="1" ht="15" spans="1:12">
+      <c r="A179" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H179" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I179" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J179" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K179" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L179" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" ht="15" spans="1:1">
+      <c r="A180" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" ht="15" spans="1:10">
+      <c r="A181" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D181" s="6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E181" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F181" s="7" t="n">
+        <v>30400</v>
+      </c>
+      <c r="G181" s="8">
+        <v>46139</v>
+      </c>
+      <c r="H181" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I181" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="J181" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" ht="15" spans="1:5">
+      <c r="A182" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C182" s="11" t="n">
+        <v>30400</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E182" s="12" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" ht="15" spans="1:1">
+      <c r="A183" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" ht="15" spans="1:10">
+      <c r="A184" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D184" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E184" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F184" s="7" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G184" s="8">
+        <v>46148</v>
+      </c>
+      <c r="H184" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" ht="15" spans="1:5">
+      <c r="A185" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B185" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C185" s="11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E185" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" ht="15" spans="1:1">
+      <c r="A186" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" ht="15" spans="1:10">
+      <c r="A187" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D187" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E187" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F187" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G187" s="8">
+        <v>46135</v>
+      </c>
+      <c r="H187" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="161" customHeight="1" ht="15" spans="1:5">
-      <c r="A161" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B161" s="10" t="s">
+    <row r="188" customHeight="1" ht="15" spans="1:5">
+      <c r="A188" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B188" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C161" s="11" t="n">
-        <v>2328</v>
-      </c>
-      <c r="D161" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E161" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" customHeight="1" ht="15" spans="1:1">
-      <c r="A162" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="163" customHeight="1" ht="15" spans="1:10">
-      <c r="A163" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D163" s="6" t="n">
-        <v>240</v>
-      </c>
-      <c r="E163" s="7" t="n">
-        <v>34.65</v>
-      </c>
-      <c r="F163" s="7" t="n">
-        <v>8316</v>
-      </c>
-      <c r="G163" s="8">
-        <v>46148</v>
-      </c>
-      <c r="H163" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J163" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="164" customHeight="1" ht="15" spans="1:5">
-      <c r="A164" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B164" s="10" t="s">
+      <c r="C188" s="11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E188" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A189" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" ht="15" spans="1:12">
+      <c r="A190" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H190" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I190" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J190" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K190" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L190" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" ht="15" spans="1:1">
+      <c r="A191" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="192" customHeight="1" ht="15" spans="1:10">
+      <c r="A192" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D192" s="6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E192" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F192" s="7" t="n">
+        <v>5040</v>
+      </c>
+      <c r="G192" s="8">
+        <v>46153</v>
+      </c>
+      <c r="H192" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" ht="15" spans="1:5">
+      <c r="A193" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B193" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C164" s="11" t="n">
-        <v>8316</v>
-      </c>
-      <c r="D164" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E164" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A165" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" customHeight="1" ht="15" spans="1:12">
-      <c r="A166" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E166" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F166" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G166" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H166" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I166" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J166" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K166" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L166" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="167" customHeight="1" ht="15" spans="1:1">
-      <c r="A167" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="168" customHeight="1" ht="15" spans="1:10">
-      <c r="A168" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B168" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D168" s="6" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E168" s="7" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="F168" s="7" t="n">
-        <v>55080</v>
-      </c>
-      <c r="G168" s="8">
-        <v>46147</v>
-      </c>
-      <c r="H168" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I168" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" s="6" t="s">
+      <c r="C193" s="11" t="n">
+        <v>5040</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E193" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" customHeight="1" ht="15" spans="1:1">
+      <c r="A194" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="195" customHeight="1" ht="15" spans="1:10">
+      <c r="A195" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D195" s="6" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E195" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F195" s="7" t="n">
+        <v>26600</v>
+      </c>
+      <c r="G195" s="8">
+        <v>46135</v>
+      </c>
+      <c r="H195" s="6" t="n">
+        <v>23000</v>
+      </c>
+      <c r="I195" s="9" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="J195" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="169" customHeight="1" ht="15" spans="1:5">
-      <c r="A169" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B169" s="10" t="s">
+    <row r="196" customHeight="1" ht="15" spans="1:10">
+      <c r="A196" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D196" s="6" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E196" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F196" s="7" t="n">
+        <v>456000</v>
+      </c>
+      <c r="G196" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H196" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197" customHeight="1" ht="15" spans="1:5">
+      <c r="A197" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B197" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C169" s="11" t="n">
-        <v>55080</v>
-      </c>
-      <c r="D169" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E169" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" customHeight="1" ht="15" spans="1:1">
-      <c r="A170" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="171" customHeight="1" ht="15" spans="1:10">
-      <c r="A171" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C171" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D171" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="E171" s="7" t="n">
-        <v>52.47</v>
-      </c>
-      <c r="F171" s="7" t="n">
-        <v>2518.56</v>
-      </c>
-      <c r="G171" s="8">
-        <v>46148</v>
-      </c>
-      <c r="H171" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I171" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J171" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="172" customHeight="1" ht="15" spans="1:5">
-      <c r="A172" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B172" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C172" s="11" t="n">
-        <v>2518.56</v>
-      </c>
-      <c r="D172" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E172" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" customHeight="1" ht="15" spans="1:1">
-      <c r="A173" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="174" customHeight="1" ht="15" spans="1:10">
-      <c r="A174" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D174" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="E174" s="7" t="n">
-        <v>53.98</v>
-      </c>
-      <c r="F174" s="7" t="n">
-        <v>3886.56</v>
-      </c>
-      <c r="G174" s="8">
-        <v>46121</v>
-      </c>
-      <c r="H174" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J174" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="175" customHeight="1" ht="15" spans="1:5">
-      <c r="A175" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B175" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C175" s="11" t="n">
-        <v>3886.56</v>
-      </c>
-      <c r="D175" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E175" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" customHeight="1" ht="15" spans="1:1">
-      <c r="A176" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="177" customHeight="1" ht="15" spans="1:10">
-      <c r="A177" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D177" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="E177" s="7" t="n">
-        <v>53.98</v>
-      </c>
-      <c r="F177" s="7" t="n">
-        <v>1187.56</v>
-      </c>
-      <c r="G177" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H177" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I177" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J177" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="178" customHeight="1" ht="15" spans="1:5">
-      <c r="A178" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B178" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C178" s="11" t="n">
-        <v>1187.56</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E178" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A179" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" customHeight="1" ht="15" spans="1:12">
-      <c r="A180" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E180" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F180" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G180" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H180" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I180" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J180" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K180" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L180" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="181" customHeight="1" ht="15" spans="1:1">
-      <c r="A181" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="182" customHeight="1" ht="15" spans="1:10">
-      <c r="A182" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D182" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="E182" s="7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F182" s="7" t="n">
-        <v>70000</v>
-      </c>
-      <c r="G182" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H182" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="I182" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="J182" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="183" customHeight="1" ht="15" spans="1:5">
-      <c r="A183" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B183" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C183" s="11" t="n">
-        <v>70000</v>
-      </c>
-      <c r="D183" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E183" s="12" t="n">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="184" customHeight="1" ht="15" spans="1:1">
-      <c r="A184" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="185" customHeight="1" ht="15" spans="1:10">
-      <c r="A185" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D185" s="6" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E185" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F185" s="7" t="n">
-        <v>30400</v>
-      </c>
-      <c r="G185" s="8">
-        <v>46139</v>
-      </c>
-      <c r="H185" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="I185" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="J185" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="186" customHeight="1" ht="15" spans="1:5">
-      <c r="A186" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B186" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C186" s="11" t="n">
-        <v>30400</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E186" s="12" t="n">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="187" customHeight="1" ht="15" spans="1:1">
-      <c r="A187" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="188" customHeight="1" ht="15" spans="1:10">
-      <c r="A188" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B188" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C188" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D188" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E188" s="7" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="F188" s="7" t="n">
-        <v>6200</v>
-      </c>
-      <c r="G188" s="8">
-        <v>46139</v>
-      </c>
-      <c r="H188" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J188" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="189" customHeight="1" ht="15" spans="1:5">
-      <c r="A189" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B189" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C189" s="11" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D189" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E189" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" customHeight="1" ht="15" spans="1:1">
-      <c r="A190" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="191" customHeight="1" ht="15" spans="1:10">
-      <c r="A191" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B191" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D191" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E191" s="7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="F191" s="7" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G191" s="8">
-        <v>46148</v>
-      </c>
-      <c r="H191" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I191" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J191" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="192" customHeight="1" ht="15" spans="1:5">
-      <c r="A192" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B192" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C192" s="11" t="n">
-        <v>5800</v>
-      </c>
-      <c r="D192" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E192" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" customHeight="1" ht="15" spans="1:1">
-      <c r="A193" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="194" customHeight="1" ht="15" spans="1:10">
-      <c r="A194" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B194" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C194" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D194" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E194" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F194" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G194" s="8">
-        <v>46135</v>
-      </c>
-      <c r="H194" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I194" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J194" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="195" customHeight="1" ht="15" spans="1:5">
-      <c r="A195" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B195" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C195" s="11" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D195" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E195" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A196" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" customHeight="1" ht="15" spans="1:12">
-      <c r="A197" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E197" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F197" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G197" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H197" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I197" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J197" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K197" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L197" s="3" t="s">
-        <v>12</v>
+      <c r="C197" s="11" t="n">
+        <v>482600</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E197" s="12" t="n">
+        <v>23000</v>
       </c>
     </row>
     <row r="198" customHeight="1" ht="15" spans="1:1">
       <c r="A198" s="2" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
     </row>
     <row r="199" customHeight="1" ht="15" spans="1:10">
@@ -5289,22 +5301,22 @@
         <v>14</v>
       </c>
       <c r="B199" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C199" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C199" s="5" t="s">
-        <v>123</v>
-      </c>
       <c r="D199" s="6" t="n">
-        <v>70000</v>
+        <v>20000</v>
       </c>
       <c r="E199" s="7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F199" s="7" t="n">
-        <v>26600</v>
+        <v>6600</v>
       </c>
       <c r="G199" s="8">
-        <v>46135</v>
+        <v>46148</v>
       </c>
       <c r="H199" s="6" t="n">
         <v>0</v>
@@ -5313,147 +5325,126 @@
         <v>0</v>
       </c>
       <c r="J199" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="200" customHeight="1" ht="15" spans="1:10">
-      <c r="A200" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B200" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D200" s="6" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E200" s="7" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F200" s="7" t="n">
-        <v>9750</v>
-      </c>
-      <c r="G200" s="8">
-        <v>46139</v>
-      </c>
-      <c r="H200" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I200" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J200" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="201" customHeight="1" ht="15" spans="1:10">
-      <c r="A201" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B201" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D201" s="6" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="E201" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F201" s="7" t="n">
-        <v>456000</v>
-      </c>
-      <c r="G201" s="8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="200" customHeight="1" ht="15" spans="1:5">
+      <c r="A200" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C200" s="11" t="n">
+        <v>6600</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E200" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" ht="15" spans="1:1">
+      <c r="A201" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" ht="15" spans="1:10">
+      <c r="A202" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D202" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E202" s="7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F202" s="7" t="n">
+        <v>8600</v>
+      </c>
+      <c r="G202" s="8">
         <v>46150</v>
       </c>
-      <c r="H201" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I201" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J201" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="202" customHeight="1" ht="15" spans="1:5">
-      <c r="A202" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B202" s="10" t="s">
+      <c r="H202" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" ht="15" spans="1:5">
+      <c r="A203" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B203" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C202" s="11" t="n">
-        <v>492350</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E202" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" customHeight="1" ht="15" spans="1:1">
-      <c r="A203" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="204" customHeight="1" ht="15" spans="1:10">
-      <c r="A204" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B204" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C204" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D204" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E204" s="7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="F204" s="7" t="n">
-        <v>6600</v>
-      </c>
-      <c r="G204" s="8">
-        <v>46148</v>
-      </c>
-      <c r="H204" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I204" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J204" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="205" customHeight="1" ht="15" spans="1:5">
-      <c r="A205" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B205" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C205" s="11" t="n">
-        <v>6600</v>
-      </c>
-      <c r="D205" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E205" s="12" t="n">
-        <v>0</v>
+      <c r="C203" s="11" t="n">
+        <v>8600</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E203" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A204" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" ht="15" spans="1:12">
+      <c r="A205" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H205" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I205" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J205" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K205" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L205" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="206" customHeight="1" ht="15" spans="1:1">
       <c r="A206" s="2" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
     </row>
     <row r="207" customHeight="1" ht="15" spans="1:10">
@@ -5461,22 +5452,22 @@
         <v>14</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="E207" s="7" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="F207" s="7" t="n">
-        <v>8600</v>
+        <v>40000</v>
       </c>
       <c r="G207" s="8">
-        <v>46150</v>
+        <v>46147</v>
       </c>
       <c r="H207" s="6" t="n">
         <v>0</v>
@@ -5496,7 +5487,7 @@
         <v>24</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>8600</v>
+        <v>40000</v>
       </c>
       <c r="D208" s="3" t="s">
         <v>23</v>
@@ -5507,7 +5498,7 @@
     </row>
     <row r="209" customHeight="1" ht="15" spans="1:1">
       <c r="A209" s="2" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
     </row>
     <row r="210" customHeight="1" ht="15" spans="1:10">
@@ -5515,877 +5506,909 @@
         <v>14</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="E210" s="7" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="F210" s="7" t="n">
-        <v>40000</v>
+        <v>4900</v>
       </c>
       <c r="G210" s="8">
+        <v>46153</v>
+      </c>
+      <c r="H210" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="211" customHeight="1" ht="15" spans="1:10">
+      <c r="A211" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D211" s="6" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E211" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F211" s="7" t="n">
+        <v>4620</v>
+      </c>
+      <c r="G211" s="8">
+        <v>46153</v>
+      </c>
+      <c r="H211" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="212" customHeight="1" ht="15" spans="1:5">
+      <c r="A212" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B212" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C212" s="11" t="n">
+        <v>9520</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E212" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A213" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" customHeight="1" ht="15" spans="1:12">
+      <c r="A214" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H214" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J214" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K214" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L214" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215" customHeight="1" ht="15" spans="1:1">
+      <c r="A215" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="216" customHeight="1" ht="15" spans="1:10">
+      <c r="A216" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D216" s="6" t="n">
+        <v>780</v>
+      </c>
+      <c r="E216" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="F216" s="7" t="n">
+        <v>13260</v>
+      </c>
+      <c r="G216" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H216" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" ht="15" spans="1:5">
+      <c r="A217" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B217" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C217" s="11" t="n">
+        <v>13260</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E217" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A218" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" ht="15" spans="1:12">
+      <c r="A219" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H219" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I219" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J219" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K219" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L219" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" ht="15" spans="1:1">
+      <c r="A220" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" ht="15" spans="1:10">
+      <c r="A221" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D221" s="6" t="n">
+        <v>720</v>
+      </c>
+      <c r="E221" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F221" s="7" t="n">
+        <v>10800</v>
+      </c>
+      <c r="G221" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H221" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="222" customHeight="1" ht="15" spans="1:5">
+      <c r="A222" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B222" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C222" s="11" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E222" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A223" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" customHeight="1" ht="15" spans="1:12">
+      <c r="A224" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H224" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I224" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J224" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K224" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L224" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="225" customHeight="1" ht="15" spans="1:1">
+      <c r="A225" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="226" customHeight="1" ht="15" spans="1:10">
+      <c r="A226" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D226" s="6" t="n">
+        <v>8025</v>
+      </c>
+      <c r="E226" s="7" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="F226" s="7" t="n">
+        <v>166839.75</v>
+      </c>
+      <c r="G226" s="8">
+        <v>46122</v>
+      </c>
+      <c r="H226" s="6" t="n">
+        <v>3475</v>
+      </c>
+      <c r="I226" s="9" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="J226" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="227" customHeight="1" ht="15" spans="1:5">
+      <c r="A227" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B227" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C227" s="11" t="n">
+        <v>166839.75</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E227" s="12" t="n">
+        <v>3475</v>
+      </c>
+    </row>
+    <row r="228" customHeight="1" ht="15" spans="1:1">
+      <c r="A228" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" ht="15" spans="1:10">
+      <c r="A229" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D229" s="6" t="n">
+        <v>2160</v>
+      </c>
+      <c r="E229" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F229" s="7" t="n">
+        <v>28080</v>
+      </c>
+      <c r="G229" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H229" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I229" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="230" customHeight="1" ht="15" spans="1:5">
+      <c r="A230" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C230" s="11" t="n">
+        <v>28080</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E230" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" customHeight="1" ht="15" spans="1:1">
+      <c r="A231" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" ht="15" spans="1:10">
+      <c r="A232" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D232" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E232" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F232" s="7" t="n">
+        <v>312000</v>
+      </c>
+      <c r="G232" s="8">
+        <v>46100</v>
+      </c>
+      <c r="H232" s="6" t="n">
+        <v>18900</v>
+      </c>
+      <c r="I232" s="9" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="J232" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" ht="15" spans="1:10">
+      <c r="A233" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D233" s="6" t="n">
+        <v>10020</v>
+      </c>
+      <c r="E233" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F233" s="7" t="n">
+        <v>130260</v>
+      </c>
+      <c r="G233" s="8">
         <v>46147</v>
       </c>
-      <c r="H210" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I210" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J210" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="211" customHeight="1" ht="15" spans="1:5">
-      <c r="A211" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B211" s="10" t="s">
+      <c r="H233" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" ht="15" spans="1:5">
+      <c r="A234" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B234" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C211" s="11" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E211" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A212" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" customHeight="1" ht="15" spans="1:12">
-      <c r="A213" s="2" t="s">
+      <c r="C234" s="11" t="n">
+        <v>442260</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E234" s="12" t="n">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A235" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" customHeight="1" ht="15" spans="1:12">
+      <c r="A236" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B213" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C213" s="2" t="s">
+      <c r="B236" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C236" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D213" s="2" t="s">
+      <c r="D236" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E213" s="3" t="s">
+      <c r="E236" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F213" s="3" t="s">
+      <c r="F236" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G213" s="3" t="s">
+      <c r="G236" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H213" s="3" t="s">
+      <c r="H236" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I213" s="3" t="s">
+      <c r="I236" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J213" s="3" t="s">
+      <c r="J236" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K213" s="2" t="s">
+      <c r="K236" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L213" s="3" t="s">
+      <c r="L236" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="214" customHeight="1" ht="15" spans="1:1">
-      <c r="A214" s="2" t="s">
+    <row r="237" customHeight="1" ht="15" spans="1:1">
+      <c r="A237" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="238" customHeight="1" ht="15" spans="1:10">
+      <c r="A238" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D238" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E238" s="7" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="F238" s="7" t="n">
+        <v>1124.48</v>
+      </c>
+      <c r="G238" s="8">
+        <v>46148</v>
+      </c>
+      <c r="H238" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I238" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="239" customHeight="1" ht="15" spans="1:5">
+      <c r="A239" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B239" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C239" s="11" t="n">
+        <v>1124.48</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E239" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" customHeight="1" ht="15" spans="1:1">
+      <c r="A240" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="241" customHeight="1" ht="15" spans="1:10">
+      <c r="A241" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D241" s="6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E241" s="7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F241" s="7" t="n">
+        <v>33396</v>
+      </c>
+      <c r="G241" s="8">
+        <v>46148</v>
+      </c>
+      <c r="H241" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="242" customHeight="1" ht="15" spans="1:5">
+      <c r="A242" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B242" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C242" s="11" t="n">
+        <v>33396</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E242" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A243" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" customHeight="1" ht="15" spans="1:12">
+      <c r="A244" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H244" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I244" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J244" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K244" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L244" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="245" customHeight="1" ht="15" spans="1:1">
+      <c r="A245" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="246" customHeight="1" ht="15" spans="1:10">
+      <c r="A246" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D246" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="E246" s="7" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="F246" s="7" t="n">
+        <v>2607.36</v>
+      </c>
+      <c r="G246" s="8">
+        <v>46148</v>
+      </c>
+      <c r="H246" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I246" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="247" customHeight="1" ht="15" spans="1:5">
+      <c r="A247" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B247" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C247" s="11" t="n">
+        <v>2607.36</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E247" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A248" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" customHeight="1" ht="15" spans="1:12">
+      <c r="A249" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H249" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I249" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J249" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K249" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L249" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="250" customHeight="1" ht="15" spans="1:1">
+      <c r="A250" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="215" customHeight="1" ht="15" spans="1:10">
-      <c r="A215" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B215" s="5" t="s">
+    <row r="251" customHeight="1" ht="15" spans="1:10">
+      <c r="A251" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B251" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C215" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D215" s="6" t="n">
-        <v>1512</v>
-      </c>
-      <c r="E215" s="7" t="n">
-        <v>11.19</v>
-      </c>
-      <c r="F215" s="7" t="n">
-        <v>16919.28</v>
-      </c>
-      <c r="G215" s="8">
+      <c r="C251" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D251" s="6" t="n">
+        <v>1224</v>
+      </c>
+      <c r="E251" s="7" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="F251" s="7" t="n">
+        <v>5985.36</v>
+      </c>
+      <c r="G251" s="8">
         <v>46148</v>
       </c>
-      <c r="H215" s="6" t="n">
-        <v>504</v>
-      </c>
-      <c r="I215" s="9" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="J215" s="6" t="s">
+      <c r="H251" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I251" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="216" customHeight="1" ht="15" spans="1:5">
-      <c r="A216" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B216" s="10" t="s">
+    <row r="252" customHeight="1" ht="15" spans="1:5">
+      <c r="A252" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B252" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C216" s="11" t="n">
-        <v>16919.28</v>
-      </c>
-      <c r="D216" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E216" s="12" t="n">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="217" customHeight="1" ht="15" spans="1:1">
-      <c r="A217" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="218" customHeight="1" ht="15" spans="1:10">
-      <c r="A218" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B218" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C218" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D218" s="6" t="n">
-        <v>760</v>
-      </c>
-      <c r="E218" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="F218" s="7" t="n">
-        <v>12920</v>
-      </c>
-      <c r="G218" s="8">
-        <v>46150</v>
-      </c>
-      <c r="H218" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I218" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J218" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="219" customHeight="1" ht="15" spans="1:5">
-      <c r="A219" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B219" s="10" t="s">
+      <c r="C252" s="11" t="n">
+        <v>5985.36</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E252" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" customHeight="1" ht="15" spans="1:1">
+      <c r="A253" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="254" customHeight="1" ht="15" spans="1:10">
+      <c r="A254" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D254" s="6" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E254" s="7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F254" s="7" t="n">
+        <v>14848</v>
+      </c>
+      <c r="G254" s="8">
+        <v>46148</v>
+      </c>
+      <c r="H254" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I254" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="255" customHeight="1" ht="15" spans="1:5">
+      <c r="A255" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B255" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C219" s="11" t="n">
-        <v>12920</v>
-      </c>
-      <c r="D219" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E219" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A220" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" customHeight="1" ht="15" spans="1:12">
-      <c r="A221" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E221" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F221" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G221" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H221" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I221" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J221" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K221" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L221" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="222" customHeight="1" ht="15" spans="1:1">
-      <c r="A222" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="223" customHeight="1" ht="15" spans="1:10">
-      <c r="A223" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B223" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D223" s="6" t="n">
-        <v>720</v>
-      </c>
-      <c r="E223" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="F223" s="7" t="n">
-        <v>10800</v>
-      </c>
-      <c r="G223" s="8">
-        <v>46150</v>
-      </c>
-      <c r="H223" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I223" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J223" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="224" customHeight="1" ht="15" spans="1:5">
-      <c r="A224" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B224" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C224" s="11" t="n">
-        <v>10800</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E224" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A225" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" customHeight="1" ht="15" spans="1:12">
-      <c r="A226" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E226" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F226" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G226" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H226" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I226" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J226" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K226" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L226" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="227" customHeight="1" ht="15" spans="1:1">
-      <c r="A227" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="228" customHeight="1" ht="15" spans="1:10">
-      <c r="A228" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B228" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C228" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D228" s="6" t="n">
-        <v>8010</v>
-      </c>
-      <c r="E228" s="7" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F228" s="7" t="n">
-        <v>166527.9</v>
-      </c>
-      <c r="G228" s="8">
-        <v>46122</v>
-      </c>
-      <c r="H228" s="6" t="n">
-        <v>3475</v>
-      </c>
-      <c r="I228" s="9" t="n">
-        <v>43.38</v>
-      </c>
-      <c r="J228" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="229" customHeight="1" ht="15" spans="1:5">
-      <c r="A229" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B229" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C229" s="11" t="n">
-        <v>166527.9</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E229" s="12" t="n">
-        <v>3475</v>
-      </c>
-    </row>
-    <row r="230" customHeight="1" ht="15" spans="1:1">
-      <c r="A230" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="231" customHeight="1" ht="15" spans="1:10">
-      <c r="A231" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B231" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D231" s="6" t="n">
-        <v>2160</v>
-      </c>
-      <c r="E231" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="F231" s="7" t="n">
-        <v>28080</v>
-      </c>
-      <c r="G231" s="8">
-        <v>46150</v>
-      </c>
-      <c r="H231" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I231" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J231" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="232" customHeight="1" ht="15" spans="1:5">
-      <c r="A232" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B232" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C232" s="11" t="n">
-        <v>28080</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E232" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" customHeight="1" ht="15" spans="1:1">
-      <c r="A233" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="234" customHeight="1" ht="15" spans="1:10">
-      <c r="A234" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B234" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C234" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D234" s="6" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E234" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="F234" s="7" t="n">
-        <v>312000</v>
-      </c>
-      <c r="G234" s="8">
-        <v>46100</v>
-      </c>
-      <c r="H234" s="6" t="n">
-        <v>18900</v>
-      </c>
-      <c r="I234" s="9" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="J234" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="235" customHeight="1" ht="15" spans="1:10">
-      <c r="A235" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B235" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C235" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D235" s="6" t="n">
-        <v>10020</v>
-      </c>
-      <c r="E235" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="F235" s="7" t="n">
-        <v>130260</v>
-      </c>
-      <c r="G235" s="8">
-        <v>46147</v>
-      </c>
-      <c r="H235" s="6" t="n">
-        <v>2010</v>
-      </c>
-      <c r="I235" s="9" t="n">
-        <v>20.06</v>
-      </c>
-      <c r="J235" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="236" customHeight="1" ht="15" spans="1:5">
-      <c r="A236" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B236" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C236" s="11" t="n">
-        <v>442260</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E236" s="12" t="n">
-        <v>20910</v>
-      </c>
-    </row>
-    <row r="237" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A237" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238" customHeight="1" ht="15" spans="1:12">
-      <c r="A238" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D238" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E238" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F238" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G238" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H238" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I238" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J238" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K238" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L238" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="239" customHeight="1" ht="15" spans="1:1">
-      <c r="A239" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="240" customHeight="1" ht="15" spans="1:10">
-      <c r="A240" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B240" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C240" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D240" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="E240" s="7" t="n">
-        <v>17.57</v>
-      </c>
-      <c r="F240" s="7" t="n">
-        <v>1124.48</v>
-      </c>
-      <c r="G240" s="8">
-        <v>46148</v>
-      </c>
-      <c r="H240" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I240" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J240" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="241" customHeight="1" ht="15" spans="1:5">
-      <c r="A241" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B241" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C241" s="11" t="n">
-        <v>1124.48</v>
-      </c>
-      <c r="D241" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E241" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242" customHeight="1" ht="15" spans="1:1">
-      <c r="A242" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="243" customHeight="1" ht="15" spans="1:10">
-      <c r="A243" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B243" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C243" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D243" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E243" s="7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F243" s="7" t="n">
-        <v>3300</v>
-      </c>
-      <c r="G243" s="8">
-        <v>46148</v>
-      </c>
-      <c r="H243" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I243" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J243" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="244" customHeight="1" ht="15" spans="1:5">
-      <c r="A244" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B244" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C244" s="11" t="n">
-        <v>3300</v>
-      </c>
-      <c r="D244" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E244" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A245" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246" customHeight="1" ht="15" spans="1:12">
-      <c r="A246" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E246" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F246" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G246" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H246" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I246" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J246" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K246" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L246" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="247" customHeight="1" ht="15" spans="1:1">
-      <c r="A247" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="248" customHeight="1" ht="15" spans="1:10">
-      <c r="A248" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B248" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C248" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D248" s="6" t="n">
-        <v>128</v>
-      </c>
-      <c r="E248" s="7" t="n">
-        <v>20.37</v>
-      </c>
-      <c r="F248" s="7" t="n">
-        <v>2607.36</v>
-      </c>
-      <c r="G248" s="8">
-        <v>46148</v>
-      </c>
-      <c r="H248" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I248" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J248" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="249" customHeight="1" ht="15" spans="1:5">
-      <c r="A249" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B249" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C249" s="11" t="n">
-        <v>2607.36</v>
-      </c>
-      <c r="D249" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E249" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A250" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" customHeight="1" ht="15" spans="1:12">
-      <c r="A251" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D251" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E251" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F251" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G251" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H251" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I251" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J251" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K251" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L251" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="252" customHeight="1" ht="15" spans="1:1">
-      <c r="A252" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="253" customHeight="1" ht="15" spans="1:10">
-      <c r="A253" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B253" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C253" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D253" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E253" s="7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F253" s="7" t="n">
-        <v>14500</v>
-      </c>
-      <c r="G253" s="8">
-        <v>46148</v>
-      </c>
-      <c r="H253" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I253" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J253" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="254" customHeight="1" ht="15" spans="1:5">
-      <c r="A254" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B254" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C254" s="11" t="n">
-        <v>14500</v>
-      </c>
-      <c r="D254" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E254" s="12" t="n">
+      <c r="C255" s="11" t="n">
+        <v>14848</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E255" s="12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="149">
   <si>
     <t>MATRIZ CNPJ: 40.357.820/0001-50R Y DOIS - 58082-025
  ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
@@ -116,6 +116,12 @@
     <t>796</t>
   </si>
   <si>
+    <t>FARMAGUEDES COMERCIO DE PROD FARMAC. MED E HOSP LTDA</t>
+  </si>
+  <si>
+    <t>871</t>
+  </si>
+  <si>
     <t>GRADUAL HOSPITALAR</t>
   </si>
   <si>
@@ -332,12 +338,24 @@
     <t>836</t>
   </si>
   <si>
+    <t>D &amp; V COMERCIO DE MATERIAL HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>872</t>
+  </si>
+  <si>
     <t>NOVA HOSPITALAR</t>
   </si>
   <si>
     <t>738</t>
   </si>
   <si>
+    <t>ESTERIL - 09 FIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 - GAZE ESTÉRIL 09 FIOS - PCT 10 UND </t>
+  </si>
+  <si>
     <t>ESTERIL - 11 FIOS</t>
   </si>
   <si>
@@ -347,12 +365,6 @@
     <t xml:space="preserve">02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND </t>
   </si>
   <si>
-    <t>T J FEITOSA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>783</t>
-  </si>
-  <si>
     <t>ESTERIL - 13 FIOS</t>
   </si>
   <si>
@@ -398,21 +410,21 @@
     <t>276 - GAZE CIRCULAR NAO ESTERIL 13 FIOS</t>
   </si>
   <si>
+    <t>CIDALAB COMERCIO DE ARTIGOS LABORAT E HOSP LTDA - ME</t>
+  </si>
+  <si>
+    <t>870</t>
+  </si>
+  <si>
+    <t>299 - GAZE CIRCULAR NAO ESTERIL 13 FIOS CA</t>
+  </si>
+  <si>
+    <t>SERGIO ROBERTO</t>
+  </si>
+  <si>
     <t>282 - GAZE CIRCULAR NAO ESTERIL 13 FIOS JA</t>
   </si>
   <si>
-    <t>J.J DISTRIBUIDORA DE PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>863</t>
-  </si>
-  <si>
-    <t>280 - GAZE CIRCULAR NAO ESTERIL 13 FIOS HA</t>
-  </si>
-  <si>
-    <t>PAIVA REPRESENTANTE</t>
-  </si>
-  <si>
     <t>NACIONAL COMERCIO E REPRESENTACAO</t>
   </si>
   <si>
@@ -432,6 +444,9 @@
   </si>
   <si>
     <t>329 - GAZE NAO ESTÉRIL 13 FIOS IA</t>
+  </si>
+  <si>
+    <t>349 - GAZE NAO ESTÉRIL 13 FIOS  - PCT 500 UND</t>
   </si>
   <si>
     <t>PCT NÃO EST. - 9 FIOS</t>
@@ -602,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L228"/>
+  <dimension ref="A1:L248"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
   <cols>
     <col customWidth="1" width="89.23828125" min="1" max="1"/>
@@ -1446,28 +1461,28 @@
         <v>35</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>7568</v>
+        <v>560</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>9.99</v>
+        <v>4.99</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>75604.32</v>
+        <v>2794.4</v>
       </c>
       <c r="G34" s="8">
-        <v>46122</v>
+        <v>46157</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>1760</v>
+        <v>0</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>23.26</v>
+        <v>0</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" customHeight="1" ht="15" spans="1:5">
@@ -1478,18 +1493,18 @@
         <v>24</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>75604.32</v>
+        <v>2794.4</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>1760</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" customHeight="1" ht="15" spans="1:1">
       <c r="A36" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" customHeight="1" ht="15" spans="1:10">
@@ -1497,256 +1512,214 @@
         <v>14</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>7568</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>75604.32</v>
+      </c>
+      <c r="G37" s="8">
+        <v>46122</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>1760</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="J37" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="5" t="s">
+    </row>
+    <row r="38" customHeight="1" ht="15" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>75604.32</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" ht="15" spans="1:1">
+      <c r="A39" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" ht="15" spans="1:10">
+      <c r="A40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D40" s="6" t="n">
         <v>602</v>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E40" s="7" t="n">
         <v>5.21</v>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F40" s="7" t="n">
         <v>3136.42</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G40" s="8">
         <v>46156</v>
       </c>
-      <c r="H37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" ht="15" spans="1:10">
-      <c r="A38" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" s="5" t="s">
+      <c r="H40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" ht="15" spans="1:10">
+      <c r="A41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D41" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="E38" s="7" t="n">
+      <c r="E41" s="7" t="n">
         <v>7.7</v>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F41" s="7" t="n">
         <v>4620</v>
       </c>
-      <c r="G38" s="8">
+      <c r="G41" s="8">
         <v>46156</v>
       </c>
-      <c r="H38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" ht="15" spans="1:10">
-      <c r="A39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C39" s="5" t="s">
+      <c r="H41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" ht="15" spans="1:10">
+      <c r="A42" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D42" s="6" t="n">
         <v>616</v>
       </c>
-      <c r="E39" s="7" t="n">
+      <c r="E42" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F42" s="7" t="n">
         <v>6153.84</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G42" s="8">
         <v>46156</v>
       </c>
-      <c r="H39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" ht="15" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B40" s="10" t="s">
+      <c r="H42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" ht="15" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="11" t="n">
+      <c r="C43" s="11" t="n">
         <v>13910.26</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" ht="15" spans="1:12">
-      <c r="A42" s="2" t="s">
+      <c r="D43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" ht="15" spans="1:12">
+      <c r="A45" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="B45" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="I45" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="K45" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L42" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="43" customHeight="1" ht="15" spans="1:1">
-      <c r="A43" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" ht="15" spans="1:10">
-      <c r="A44" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C44" s="5" t="s">
+    <row r="46" customHeight="1" ht="15" spans="1:1">
+      <c r="A46" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="D44" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>2690</v>
-      </c>
-      <c r="G44" s="8">
-        <v>46142</v>
-      </c>
-      <c r="H44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" ht="15" spans="1:10">
-      <c r="A45" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E45" s="7" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="F45" s="7" t="n">
-        <v>7322.4</v>
-      </c>
-      <c r="G45" s="8">
-        <v>46142</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" ht="15" spans="1:10">
-      <c r="A46" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D46" s="6" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>16078.5</v>
-      </c>
-      <c r="G46" s="8">
-        <v>46142</v>
-      </c>
-      <c r="H46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="47" customHeight="1" ht="15" spans="1:10">
@@ -1754,19 +1727,19 @@
         <v>14</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>2040</v>
+        <v>500</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>10.3</v>
+        <v>5.38</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>21012</v>
+        <v>2690</v>
       </c>
       <c r="G47" s="8">
         <v>46142</v>
@@ -1778,29 +1751,71 @@
         <v>0</v>
       </c>
       <c r="J47" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" ht="15" spans="1:10">
+      <c r="A48" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="48" customHeight="1" ht="15" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="11" t="n">
-        <v>47102.9</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E48" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" ht="15" spans="1:1">
-      <c r="A49" s="2" t="s">
+      <c r="C48" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>7322.4</v>
+      </c>
+      <c r="G48" s="8">
+        <v>46142</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" ht="15" spans="1:10">
+      <c r="A49" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>47</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>16078.5</v>
+      </c>
+      <c r="G49" s="8">
+        <v>46142</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="50" customHeight="1" ht="15" spans="1:10">
@@ -1808,85 +1823,85 @@
         <v>14</v>
       </c>
       <c r="B50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="D50" s="6" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>21012</v>
+      </c>
+      <c r="G50" s="8">
+        <v>46142</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" ht="15" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>47102.9</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" ht="15" spans="1:1">
+      <c r="A52" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D50" s="6" t="n">
+    </row>
+    <row r="53" customHeight="1" ht="15" spans="1:10">
+      <c r="A53" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D53" s="6" t="n">
         <v>1100</v>
       </c>
-      <c r="E50" s="7" t="n">
+      <c r="E53" s="7" t="n">
         <v>3.72</v>
       </c>
-      <c r="F50" s="7" t="n">
+      <c r="F53" s="7" t="n">
         <v>4092</v>
       </c>
-      <c r="G50" s="8">
+      <c r="G53" s="8">
         <v>46132</v>
       </c>
-      <c r="H50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" ht="15" spans="1:10">
-      <c r="A51" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D51" s="6" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E51" s="7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F51" s="7" t="n">
-        <v>5616</v>
-      </c>
-      <c r="G51" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" ht="15" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>9708</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E52" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" ht="15" spans="1:1">
-      <c r="A53" s="2" t="s">
-        <v>51</v>
+      <c r="H53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="54" customHeight="1" ht="15" spans="1:10">
@@ -1894,95 +1909,53 @@
         <v>14</v>
       </c>
       <c r="B54" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="D54" s="6" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>5616</v>
+      </c>
+      <c r="G54" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" ht="15" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>9708</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" ht="15" spans="1:1">
+      <c r="A56" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="D54" s="6" t="n">
-        <v>1012</v>
-      </c>
-      <c r="E54" s="7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>5464.8</v>
-      </c>
-      <c r="G54" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>440</v>
-      </c>
-      <c r="I54" s="9" t="n">
-        <v>43.48</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" ht="15" spans="1:10">
-      <c r="A55" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D55" s="6" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E55" s="7" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="F55" s="7" t="n">
-        <v>7524</v>
-      </c>
-      <c r="G55" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>480</v>
-      </c>
-      <c r="I55" s="9" t="n">
-        <v>43.64</v>
-      </c>
-      <c r="J55" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" ht="15" spans="1:10">
-      <c r="A56" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D56" s="6" t="n">
-        <v>1944</v>
-      </c>
-      <c r="E56" s="7" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="F56" s="7" t="n">
-        <v>10964.16</v>
-      </c>
-      <c r="G56" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>900</v>
-      </c>
-      <c r="I56" s="9" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="57" customHeight="1" ht="15" spans="1:10">
@@ -1990,31 +1963,31 @@
         <v>14</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>1890</v>
+        <v>1012</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>6.85</v>
+        <v>5.4</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>12946.5</v>
+        <v>5464.8</v>
       </c>
       <c r="G57" s="8">
         <v>46113</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>690</v>
+        <v>440</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>36.51</v>
+        <v>43.48</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" customHeight="1" ht="15" spans="1:10">
@@ -2022,31 +1995,31 @@
         <v>14</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>572</v>
+        <v>1100</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>7.25</v>
+        <v>6.84</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>4147</v>
+        <v>7524</v>
       </c>
       <c r="G58" s="8">
         <v>46113</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>260</v>
+        <v>480</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>45.45</v>
+        <v>43.64</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" customHeight="1" ht="15" spans="1:10">
@@ -2054,214 +2027,256 @@
         <v>14</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>726</v>
+        <v>1944</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>10.3</v>
+        <v>5.64</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>7477.8</v>
+        <v>10964.16</v>
       </c>
       <c r="G59" s="8">
         <v>46113</v>
       </c>
       <c r="H59" s="6" t="n">
+        <v>900</v>
+      </c>
+      <c r="I59" s="9" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" ht="15" spans="1:10">
+      <c r="A60" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>1890</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>12946.5</v>
+      </c>
+      <c r="G60" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>690</v>
+      </c>
+      <c r="I60" s="9" t="n">
+        <v>36.51</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" ht="15" spans="1:10">
+      <c r="A61" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>572</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>4147</v>
+      </c>
+      <c r="G61" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>260</v>
+      </c>
+      <c r="I61" s="9" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" ht="15" spans="1:10">
+      <c r="A62" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>726</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>7477.8</v>
+      </c>
+      <c r="G62" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H62" s="6" t="n">
         <v>264</v>
       </c>
-      <c r="I59" s="9" t="n">
+      <c r="I62" s="9" t="n">
         <v>36.36</v>
       </c>
-      <c r="J59" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" ht="15" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B60" s="10" t="s">
+      <c r="J62" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" ht="15" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B63" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="11" t="n">
+      <c r="C63" s="11" t="n">
         <v>48524.26</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E60" s="12" t="n">
+      <c r="D63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" s="12" t="n">
         <v>3034</v>
       </c>
     </row>
-    <row r="61" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A61" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" ht="15" spans="1:12">
-      <c r="A62" s="2" t="s">
+    <row r="64" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" ht="15" spans="1:12">
+      <c r="A65" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C62" s="2" t="s">
+      <c r="B65" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D65" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="E65" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F65" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G65" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="H65" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I62" s="3" t="s">
+      <c r="I65" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J62" s="3" t="s">
+      <c r="J65" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K62" s="2" t="s">
+      <c r="K65" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L62" s="3" t="s">
+      <c r="L65" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="63" customHeight="1" ht="15" spans="1:1">
-      <c r="A63" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" ht="15" spans="1:10">
-      <c r="A64" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D64" s="6" t="n">
+    <row r="66" customHeight="1" ht="15" spans="1:1">
+      <c r="A66" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" ht="15" spans="1:10">
+      <c r="A67" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="6" t="n">
         <v>800</v>
       </c>
-      <c r="E64" s="7" t="n">
+      <c r="E67" s="7" t="n">
         <v>5.2</v>
       </c>
-      <c r="F64" s="7" t="n">
+      <c r="F67" s="7" t="n">
         <v>4160</v>
       </c>
-      <c r="G64" s="8">
+      <c r="G67" s="8">
         <v>46139</v>
       </c>
-      <c r="H64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" ht="15" spans="1:10">
-      <c r="A65" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D65" s="6" t="n">
+      <c r="H67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" ht="15" spans="1:10">
+      <c r="A68" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D68" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="E65" s="7" t="n">
+      <c r="E68" s="7" t="n">
         <v>10.3</v>
       </c>
-      <c r="F65" s="7" t="n">
+      <c r="F68" s="7" t="n">
         <v>2472</v>
       </c>
-      <c r="G65" s="8">
+      <c r="G68" s="8">
         <v>46139</v>
       </c>
-      <c r="H65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" ht="15" spans="1:10">
-      <c r="A66" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D66" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="E66" s="7" t="n">
-        <v>13.87</v>
-      </c>
-      <c r="F66" s="7" t="n">
-        <v>554.8</v>
-      </c>
-      <c r="G66" s="8">
-        <v>46139</v>
-      </c>
-      <c r="H66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" ht="15" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B67" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="11" t="n">
-        <v>7186.8</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E67" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" ht="15" spans="1:1">
-      <c r="A68" s="2" t="s">
-        <v>63</v>
+      <c r="H68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="69" customHeight="1" ht="15" spans="1:10">
@@ -2269,19 +2284,19 @@
         <v>14</v>
       </c>
       <c r="B69" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="D69" s="6" t="n">
-        <v>1300</v>
+        <v>40</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>4.2</v>
+        <v>13.87</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>5460</v>
+        <v>554.8</v>
       </c>
       <c r="G69" s="8">
         <v>46139</v>
@@ -2296,68 +2311,26 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" customHeight="1" ht="15" spans="1:10">
-      <c r="A70" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D70" s="6" t="n">
-        <v>1050</v>
-      </c>
-      <c r="E70" s="7" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="F70" s="7" t="n">
-        <v>7182</v>
-      </c>
-      <c r="G70" s="8">
-        <v>46139</v>
-      </c>
-      <c r="H70" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" ht="15" spans="1:10">
-      <c r="A71" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D71" s="6" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E71" s="7" t="n">
-        <v>8.28</v>
-      </c>
-      <c r="F71" s="7" t="n">
-        <v>8445.6</v>
-      </c>
-      <c r="G71" s="8">
-        <v>46139</v>
-      </c>
-      <c r="H71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="6" t="s">
-        <v>17</v>
+    <row r="70" customHeight="1" ht="15" spans="1:5">
+      <c r="A70" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>7186.8</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" ht="15" spans="1:1">
+      <c r="A71" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="72" customHeight="1" ht="15" spans="1:10">
@@ -2365,22 +2338,22 @@
         <v>14</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>21700</v>
+        <v>1300</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>4.368</v>
+        <v>4.2</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>94785.6</v>
+        <v>5460</v>
       </c>
       <c r="G72" s="8">
-        <v>46156</v>
+        <v>46139</v>
       </c>
       <c r="H72" s="6" t="n">
         <v>0</v>
@@ -2392,26 +2365,68 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" customHeight="1" ht="15" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B73" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="11" t="n">
-        <v>115873.2</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E73" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" ht="15" spans="1:1">
-      <c r="A74" s="2" t="s">
+    <row r="73" customHeight="1" ht="15" spans="1:10">
+      <c r="A73" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>66</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>7182</v>
+      </c>
+      <c r="G73" s="8">
+        <v>46139</v>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" ht="15" spans="1:10">
+      <c r="A74" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>8.28</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>8445.6</v>
+      </c>
+      <c r="G74" s="8">
+        <v>46139</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="75" customHeight="1" ht="15" spans="1:10">
@@ -2422,16 +2437,16 @@
         <v>67</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>220</v>
+        <v>21700</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>3.97</v>
+        <v>4.368</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>873.4</v>
+        <v>94785.6</v>
       </c>
       <c r="G75" s="8">
         <v>46156</v>
@@ -2446,58 +2461,58 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" customHeight="1" ht="15" spans="1:10">
-      <c r="A76" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C76" s="5" t="s">
+    <row r="76" customHeight="1" ht="15" spans="1:5">
+      <c r="A76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>115873.2</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E76" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" ht="15" spans="1:1">
+      <c r="A77" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="6" t="n">
-        <v>280</v>
-      </c>
-      <c r="E76" s="7" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="F76" s="7" t="n">
-        <v>2030</v>
-      </c>
-      <c r="G76" s="8">
+    </row>
+    <row r="78" customHeight="1" ht="15" spans="1:10">
+      <c r="A78" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D78" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F78" s="7" t="n">
+        <v>873.4</v>
+      </c>
+      <c r="G78" s="8">
         <v>46156</v>
       </c>
-      <c r="H76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" ht="15" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B77" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C77" s="11" t="n">
-        <v>2903.4</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E77" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" ht="15" spans="1:1">
-      <c r="A78" s="2" t="s">
-        <v>69</v>
+      <c r="H78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="79" customHeight="1" ht="15" spans="1:10">
@@ -2505,223 +2520,181 @@
         <v>14</v>
       </c>
       <c r="B79" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="D79" s="6" t="n">
+        <v>280</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="F79" s="7" t="n">
+        <v>2030</v>
+      </c>
+      <c r="G79" s="8">
+        <v>46156</v>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" ht="15" spans="1:5">
+      <c r="A80" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>2903.4</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E80" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" ht="15" spans="1:1">
+      <c r="A81" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" ht="15" spans="1:10">
+      <c r="A82" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="E79" s="7" t="n">
+      <c r="E82" s="7" t="n">
         <v>5.2</v>
       </c>
-      <c r="F79" s="7" t="n">
+      <c r="F82" s="7" t="n">
         <v>3120</v>
       </c>
-      <c r="G79" s="8">
+      <c r="G82" s="8">
         <v>46139</v>
       </c>
-      <c r="H79" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" ht="15" spans="1:10">
-      <c r="A80" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D80" s="6" t="n">
+      <c r="H82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" ht="15" spans="1:10">
+      <c r="A83" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D83" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="E80" s="7" t="n">
+      <c r="E83" s="7" t="n">
         <v>10.3</v>
       </c>
-      <c r="F80" s="7" t="n">
+      <c r="F83" s="7" t="n">
         <v>1854</v>
       </c>
-      <c r="G80" s="8">
+      <c r="G83" s="8">
         <v>46139</v>
       </c>
-      <c r="H80" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" ht="15" spans="1:5">
-      <c r="A81" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B81" s="10" t="s">
+      <c r="H83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" ht="15" spans="1:5">
+      <c r="A84" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B84" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C81" s="11" t="n">
+      <c r="C84" s="11" t="n">
         <v>4974</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E81" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A82" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" ht="15" spans="1:12">
-      <c r="A83" s="2" t="s">
+      <c r="D84" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A85" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" ht="15" spans="1:12">
+      <c r="A86" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C83" s="2" t="s">
+      <c r="B86" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D86" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E86" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="F86" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="G86" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H83" s="3" t="s">
+      <c r="H86" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="I86" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="J86" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K83" s="2" t="s">
+      <c r="K86" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L83" s="3" t="s">
+      <c r="L86" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="84" customHeight="1" ht="15" spans="1:1">
-      <c r="A84" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" ht="15" spans="1:10">
-      <c r="A85" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D85" s="6" t="n">
-        <v>440</v>
-      </c>
-      <c r="E85" s="7" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="F85" s="7" t="n">
-        <v>1962.4</v>
-      </c>
-      <c r="G85" s="8">
-        <v>46150</v>
-      </c>
-      <c r="H85" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" ht="15" spans="1:10">
-      <c r="A86" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D86" s="6" t="n">
-        <v>440</v>
-      </c>
-      <c r="E86" s="7" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="F86" s="7" t="n">
-        <v>2424.4</v>
-      </c>
-      <c r="G86" s="8">
-        <v>46150</v>
-      </c>
-      <c r="H86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" ht="15" spans="1:10">
-      <c r="A87" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D87" s="6" t="n">
-        <v>360</v>
-      </c>
-      <c r="E87" s="7" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="F87" s="7" t="n">
-        <v>2275.2</v>
-      </c>
-      <c r="G87" s="8">
-        <v>46150</v>
-      </c>
-      <c r="H87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="6" t="s">
+    <row r="87" customHeight="1" ht="15" spans="1:1">
+      <c r="A87" s="2" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2730,19 +2703,19 @@
         <v>14</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>8.14</v>
+        <v>4.46</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>3418.8</v>
+        <v>1962.4</v>
       </c>
       <c r="G88" s="8">
         <v>46150</v>
@@ -2754,28 +2727,70 @@
         <v>0</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" ht="15" spans="1:5">
-      <c r="A89" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B89" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C89" s="11" t="n">
-        <v>10080.8</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E89" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" customHeight="1" ht="15" spans="1:1">
-      <c r="A90" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" ht="15" spans="1:10">
+      <c r="A89" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>440</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>2424.4</v>
+      </c>
+      <c r="G89" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" ht="15" spans="1:10">
+      <c r="A90" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="F90" s="7" t="n">
+        <v>2275.2</v>
+      </c>
+      <c r="G90" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="6" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2784,22 +2799,22 @@
         <v>14</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>5.99</v>
+        <v>8.14</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>2396</v>
+        <v>3418.8</v>
       </c>
       <c r="G91" s="8">
-        <v>46134</v>
+        <v>46150</v>
       </c>
       <c r="H91" s="6" t="n">
         <v>0</v>
@@ -2808,70 +2823,28 @@
         <v>0</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="92" customHeight="1" ht="15" spans="1:10">
-      <c r="A92" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D92" s="6" t="n">
-        <v>270</v>
-      </c>
-      <c r="E92" s="7" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="F92" s="7" t="n">
-        <v>2038.5</v>
-      </c>
-      <c r="G92" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H92" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="93" customHeight="1" ht="15" spans="1:10">
-      <c r="A93" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D93" s="6" t="n">
-        <v>375</v>
-      </c>
-      <c r="E93" s="7" t="n">
-        <v>8.84</v>
-      </c>
-      <c r="F93" s="7" t="n">
-        <v>3315</v>
-      </c>
-      <c r="G93" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H93" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" ht="15" spans="1:5">
+      <c r="A92" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C92" s="11" t="n">
+        <v>10080.8</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E92" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" ht="15" spans="1:1">
+      <c r="A93" s="2" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2880,19 +2853,19 @@
         <v>14</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>11.46</v>
+        <v>5.99</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>2750.4</v>
+        <v>2396</v>
       </c>
       <c r="G94" s="8">
         <v>46134</v>
@@ -2904,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" customHeight="1" ht="15" spans="1:10">
@@ -2912,19 +2885,19 @@
         <v>14</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>16.41</v>
+        <v>7.55</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>3282</v>
+        <v>2038.5</v>
       </c>
       <c r="G95" s="8">
         <v>46134</v>
@@ -2936,29 +2909,71 @@
         <v>0</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="96" customHeight="1" ht="15" spans="1:5">
-      <c r="A96" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B96" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C96" s="11" t="n">
-        <v>13781.9</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E96" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" customHeight="1" ht="15" spans="1:1">
-      <c r="A97" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" ht="15" spans="1:10">
+      <c r="A96" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B96" s="5" t="s">
         <v>78</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>375</v>
+      </c>
+      <c r="E96" s="7" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="F96" s="7" t="n">
+        <v>3315</v>
+      </c>
+      <c r="G96" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" ht="15" spans="1:10">
+      <c r="A97" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D97" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="F97" s="7" t="n">
+        <v>2750.4</v>
+      </c>
+      <c r="G97" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="98" customHeight="1" ht="15" spans="1:10">
@@ -2966,95 +2981,53 @@
         <v>14</v>
       </c>
       <c r="B98" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="F98" s="7" t="n">
+        <v>3282</v>
+      </c>
+      <c r="G98" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C98" s="5" t="s">
+    </row>
+    <row r="99" customHeight="1" ht="15" spans="1:5">
+      <c r="A99" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B99" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" s="11" t="n">
+        <v>13781.9</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" ht="15" spans="1:1">
+      <c r="A100" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="D98" s="6" t="n">
-        <v>360</v>
-      </c>
-      <c r="E98" s="7" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="F98" s="7" t="n">
-        <v>2372.4</v>
-      </c>
-      <c r="G98" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H98" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="99" customHeight="1" ht="15" spans="1:10">
-      <c r="A99" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D99" s="6" t="n">
-        <v>320</v>
-      </c>
-      <c r="E99" s="7" t="n">
-        <v>8.14</v>
-      </c>
-      <c r="F99" s="7" t="n">
-        <v>2604.8</v>
-      </c>
-      <c r="G99" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H99" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" ht="15" spans="1:10">
-      <c r="A100" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D100" s="6" t="n">
-        <v>210</v>
-      </c>
-      <c r="E100" s="7" t="n">
-        <v>9.63</v>
-      </c>
-      <c r="F100" s="7" t="n">
-        <v>2022.3</v>
-      </c>
-      <c r="G100" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H100" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="101" customHeight="1" ht="15" spans="1:10">
@@ -3062,19 +3035,19 @@
         <v>14</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>12.37</v>
+        <v>6.59</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>1484.4</v>
+        <v>2372.4</v>
       </c>
       <c r="G101" s="8">
         <v>46113</v>
@@ -3089,164 +3062,164 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" customHeight="1" ht="15" spans="1:5">
-      <c r="A102" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B102" s="10" t="s">
+    <row r="102" customHeight="1" ht="15" spans="1:10">
+      <c r="A102" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D102" s="6" t="n">
+        <v>320</v>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>8.14</v>
+      </c>
+      <c r="F102" s="7" t="n">
+        <v>2604.8</v>
+      </c>
+      <c r="G102" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H102" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" ht="15" spans="1:10">
+      <c r="A103" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D103" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="E103" s="7" t="n">
+        <v>9.63</v>
+      </c>
+      <c r="F103" s="7" t="n">
+        <v>2022.3</v>
+      </c>
+      <c r="G103" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" ht="15" spans="1:10">
+      <c r="A104" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D104" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="F104" s="7" t="n">
+        <v>1484.4</v>
+      </c>
+      <c r="G104" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" ht="15" spans="1:5">
+      <c r="A105" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B105" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C102" s="11" t="n">
+      <c r="C105" s="11" t="n">
         <v>8483.9</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E102" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A103" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" customHeight="1" ht="15" spans="1:12">
-      <c r="A104" s="2" t="s">
+      <c r="D105" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A106" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" ht="15" spans="1:12">
+      <c r="A107" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C104" s="2" t="s">
+      <c r="B107" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D107" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E104" s="3" t="s">
+      <c r="E107" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F104" s="3" t="s">
+      <c r="F107" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G104" s="3" t="s">
+      <c r="G107" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H104" s="3" t="s">
+      <c r="H107" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I104" s="3" t="s">
+      <c r="I107" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J104" s="3" t="s">
+      <c r="J107" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K104" s="2" t="s">
+      <c r="K107" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L104" s="3" t="s">
+      <c r="L107" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="105" customHeight="1" ht="15" spans="1:1">
-      <c r="A105" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="106" customHeight="1" ht="15" spans="1:10">
-      <c r="A106" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D106" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E106" s="7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F106" s="7" t="n">
-        <v>5700</v>
-      </c>
-      <c r="G106" s="8">
-        <v>46141</v>
-      </c>
-      <c r="H106" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="107" customHeight="1" ht="15" spans="1:10">
-      <c r="A107" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D107" s="6" t="n">
-        <v>110</v>
-      </c>
-      <c r="E107" s="7" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F107" s="7" t="n">
-        <v>768.9</v>
-      </c>
-      <c r="G107" s="8">
-        <v>46141</v>
-      </c>
-      <c r="H107" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="108" customHeight="1" ht="15" spans="1:10">
-      <c r="A108" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D108" s="6" t="n">
-        <v>720</v>
-      </c>
-      <c r="E108" s="7" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="F108" s="7" t="n">
-        <v>5176.8</v>
-      </c>
-      <c r="G108" s="8">
-        <v>46141</v>
-      </c>
-      <c r="H108" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="6" t="s">
+    <row r="108" customHeight="1" ht="15" spans="1:1">
+      <c r="A108" s="2" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3255,19 +3228,19 @@
         <v>14</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>375</v>
+        <v>1000</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>8.41</v>
+        <v>5.7</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>3153.75</v>
+        <v>5700</v>
       </c>
       <c r="G109" s="8">
         <v>46141</v>
@@ -3279,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="110" customHeight="1" ht="15" spans="1:10">
@@ -3287,19 +3260,19 @@
         <v>14</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="E110" s="7" t="n">
-        <v>10.92</v>
+        <v>6.99</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>3276</v>
+        <v>768.9</v>
       </c>
       <c r="G110" s="8">
         <v>46141</v>
@@ -3311,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="111" customHeight="1" ht="15" spans="1:10">
@@ -3319,19 +3292,19 @@
         <v>14</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>200</v>
+        <v>720</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>15.62</v>
+        <v>7.19</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>3124</v>
+        <v>5176.8</v>
       </c>
       <c r="G111" s="8">
         <v>46141</v>
@@ -3343,29 +3316,71 @@
         <v>0</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="112" customHeight="1" ht="15" spans="1:5">
-      <c r="A112" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B112" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C112" s="11" t="n">
-        <v>21199.45</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E112" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" customHeight="1" ht="15" spans="1:1">
-      <c r="A113" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" ht="15" spans="1:10">
+      <c r="A112" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B112" s="5" t="s">
         <v>87</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D112" s="6" t="n">
+        <v>375</v>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="F112" s="7" t="n">
+        <v>3153.75</v>
+      </c>
+      <c r="G112" s="8">
+        <v>46141</v>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" ht="15" spans="1:10">
+      <c r="A113" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D113" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="E113" s="7" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="F113" s="7" t="n">
+        <v>3276</v>
+      </c>
+      <c r="G113" s="8">
+        <v>46141</v>
+      </c>
+      <c r="H113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="6" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="114" customHeight="1" ht="15" spans="1:10">
@@ -3373,95 +3388,53 @@
         <v>14</v>
       </c>
       <c r="B114" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D114" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E114" s="7" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="F114" s="7" t="n">
+        <v>3124</v>
+      </c>
+      <c r="G114" s="8">
+        <v>46141</v>
+      </c>
+      <c r="H114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C114" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D114" s="6" t="n">
-        <v>270</v>
-      </c>
-      <c r="E114" s="7" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="F114" s="7" t="n">
-        <v>1730.7</v>
-      </c>
-      <c r="G114" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H114" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="115" customHeight="1" ht="15" spans="1:10">
-      <c r="A115" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D115" s="6" t="n">
-        <v>320</v>
-      </c>
-      <c r="E115" s="7" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="F115" s="7" t="n">
-        <v>2534.4</v>
-      </c>
-      <c r="G115" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H115" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="116" customHeight="1" ht="15" spans="1:10">
-      <c r="A116" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D116" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="E116" s="7" t="n">
-        <v>9.37</v>
-      </c>
-      <c r="F116" s="7" t="n">
-        <v>655.9</v>
-      </c>
-      <c r="G116" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H116" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="6" t="s">
-        <v>17</v>
+    </row>
+    <row r="115" customHeight="1" ht="15" spans="1:5">
+      <c r="A115" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B115" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C115" s="11" t="n">
+        <v>21199.45</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" ht="15" spans="1:1">
+      <c r="A116" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="117" customHeight="1" ht="15" spans="1:10">
@@ -3469,22 +3442,22 @@
         <v>14</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="E117" s="7" t="n">
         <v>6.41</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>1153.8</v>
+        <v>1730.7</v>
       </c>
       <c r="G117" s="8">
-        <v>46132</v>
+        <v>46113</v>
       </c>
       <c r="H117" s="6" t="n">
         <v>0</v>
@@ -3501,53 +3474,95 @@
         <v>14</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="E118" s="7" t="n">
         <v>7.92</v>
       </c>
       <c r="F118" s="7" t="n">
-        <v>1267.2</v>
+        <v>2534.4</v>
       </c>
       <c r="G118" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" ht="15" spans="1:10">
+      <c r="A119" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D119" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="E119" s="7" t="n">
+        <v>9.37</v>
+      </c>
+      <c r="F119" s="7" t="n">
+        <v>655.9</v>
+      </c>
+      <c r="G119" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" ht="15" spans="1:10">
+      <c r="A120" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D120" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="E120" s="7" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="F120" s="7" t="n">
+        <v>1153.8</v>
+      </c>
+      <c r="G120" s="8">
         <v>46132</v>
       </c>
-      <c r="H118" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="119" customHeight="1" ht="15" spans="1:5">
-      <c r="A119" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B119" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C119" s="11" t="n">
-        <v>7342</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E119" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" customHeight="1" ht="15" spans="1:1">
-      <c r="A120" s="2" t="s">
-        <v>90</v>
+      <c r="H120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="121" customHeight="1" ht="15" spans="1:10">
@@ -3558,19 +3573,19 @@
         <v>91</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>6.41</v>
+        <v>7.92</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>576.9</v>
+        <v>1267.2</v>
       </c>
       <c r="G121" s="8">
-        <v>46113</v>
+        <v>46132</v>
       </c>
       <c r="H121" s="6" t="n">
         <v>0</v>
@@ -3582,68 +3597,26 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" customHeight="1" ht="15" spans="1:10">
-      <c r="A122" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D122" s="6" t="n">
-        <v>320</v>
-      </c>
-      <c r="E122" s="7" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="F122" s="7" t="n">
-        <v>2534.4</v>
-      </c>
-      <c r="G122" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H122" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="123" customHeight="1" ht="15" spans="1:10">
-      <c r="A123" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D123" s="6" t="n">
-        <v>700</v>
-      </c>
-      <c r="E123" s="7" t="n">
-        <v>9.37</v>
-      </c>
-      <c r="F123" s="7" t="n">
-        <v>6559</v>
-      </c>
-      <c r="G123" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H123" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="6" t="s">
-        <v>17</v>
+    <row r="122" customHeight="1" ht="15" spans="1:5">
+      <c r="A122" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B122" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C122" s="11" t="n">
+        <v>7342</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E122" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" ht="15" spans="1:1">
+      <c r="A123" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="124" customHeight="1" ht="15" spans="1:10">
@@ -3651,19 +3624,19 @@
         <v>14</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="E124" s="7" t="n">
-        <v>12.03</v>
+        <v>6.41</v>
       </c>
       <c r="F124" s="7" t="n">
-        <v>4330.8</v>
+        <v>576.9</v>
       </c>
       <c r="G124" s="8">
         <v>46113</v>
@@ -3683,22 +3656,22 @@
         <v>14</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="E125" s="7" t="n">
         <v>7.92</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>3168</v>
+        <v>2534.4</v>
       </c>
       <c r="G125" s="8">
-        <v>46132</v>
+        <v>46113</v>
       </c>
       <c r="H125" s="6" t="n">
         <v>0</v>
@@ -3715,22 +3688,22 @@
         <v>14</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="E126" s="7" t="n">
-        <v>17.34</v>
+        <v>9.37</v>
       </c>
       <c r="F126" s="7" t="n">
-        <v>2427.6</v>
+        <v>6559</v>
       </c>
       <c r="G126" s="8">
-        <v>46132</v>
+        <v>46113</v>
       </c>
       <c r="H126" s="6" t="n">
         <v>0</v>
@@ -3747,22 +3720,22 @@
         <v>14</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>9.37</v>
+        <v>12.03</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>2623.6</v>
+        <v>4330.8</v>
       </c>
       <c r="G127" s="8">
-        <v>46132</v>
+        <v>46113</v>
       </c>
       <c r="H127" s="6" t="n">
         <v>0</v>
@@ -3779,19 +3752,19 @@
         <v>14</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>83</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E128" s="7" t="n">
-        <v>12.03</v>
+        <v>7.92</v>
       </c>
       <c r="F128" s="7" t="n">
-        <v>3609</v>
+        <v>3168</v>
       </c>
       <c r="G128" s="8">
         <v>46132</v>
@@ -3806,123 +3779,165 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" customHeight="1" ht="15" spans="1:5">
-      <c r="A129" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B129" s="10" t="s">
+    <row r="129" customHeight="1" ht="15" spans="1:10">
+      <c r="A129" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D129" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="E129" s="7" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="F129" s="7" t="n">
+        <v>2427.6</v>
+      </c>
+      <c r="G129" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H129" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" ht="15" spans="1:10">
+      <c r="A130" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D130" s="6" t="n">
+        <v>280</v>
+      </c>
+      <c r="E130" s="7" t="n">
+        <v>9.37</v>
+      </c>
+      <c r="F130" s="7" t="n">
+        <v>2623.6</v>
+      </c>
+      <c r="G130" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H130" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" ht="15" spans="1:10">
+      <c r="A131" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D131" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="E131" s="7" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="F131" s="7" t="n">
+        <v>3609</v>
+      </c>
+      <c r="G131" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H131" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" ht="15" spans="1:5">
+      <c r="A132" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B132" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C129" s="11" t="n">
+      <c r="C132" s="11" t="n">
         <v>25829.3</v>
       </c>
-      <c r="D129" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E129" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A130" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" customHeight="1" ht="15" spans="1:12">
-      <c r="A131" s="2" t="s">
+      <c r="D132" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E132" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A133" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" ht="15" spans="1:12">
+      <c r="A134" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C131" s="2" t="s">
+      <c r="B134" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="D134" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E131" s="3" t="s">
+      <c r="E134" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F131" s="3" t="s">
+      <c r="F134" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G131" s="3" t="s">
+      <c r="G134" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H131" s="3" t="s">
+      <c r="H134" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I131" s="3" t="s">
+      <c r="I134" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J131" s="3" t="s">
+      <c r="J134" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K131" s="2" t="s">
+      <c r="K134" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L131" s="3" t="s">
+      <c r="L134" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="132" customHeight="1" ht="15" spans="1:1">
-      <c r="A132" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="133" customHeight="1" ht="15" spans="1:10">
-      <c r="A133" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D133" s="6" t="n">
-        <v>2250</v>
-      </c>
-      <c r="E133" s="7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F133" s="7" t="n">
-        <v>11925</v>
-      </c>
-      <c r="G133" s="8">
-        <v>46156</v>
-      </c>
-      <c r="H133" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="134" customHeight="1" ht="15" spans="1:5">
-      <c r="A134" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B134" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C134" s="11" t="n">
-        <v>11925</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E134" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="135" customHeight="1" ht="15" spans="1:1">
       <c r="A135" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="136" customHeight="1" ht="15" spans="1:10">
@@ -3930,31 +3945,31 @@
         <v>14</v>
       </c>
       <c r="B136" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C136" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C136" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="D136" s="6" t="n">
-        <v>200100</v>
+        <v>2250</v>
       </c>
       <c r="E136" s="7" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="F136" s="7" t="n">
-        <v>820410</v>
+        <v>11925</v>
       </c>
       <c r="G136" s="8">
-        <v>46119</v>
+        <v>46156</v>
       </c>
       <c r="H136" s="6" t="n">
-        <v>26400</v>
+        <v>0</v>
       </c>
       <c r="I136" s="9" t="n">
-        <v>13.19</v>
+        <v>0</v>
       </c>
       <c r="J136" s="6" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
     </row>
     <row r="137" customHeight="1" ht="15" spans="1:5">
@@ -3965,18 +3980,18 @@
         <v>24</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>820410</v>
+        <v>11925</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E137" s="12" t="n">
-        <v>26400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" customHeight="1" ht="15" spans="1:1">
       <c r="A138" s="2" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
     </row>
     <row r="139" customHeight="1" ht="15" spans="1:10">
@@ -3984,31 +3999,31 @@
         <v>14</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>50100</v>
+        <v>200100</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>4.517</v>
+        <v>4.1</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>226301.7</v>
+        <v>820410</v>
       </c>
       <c r="G139" s="8">
-        <v>46156</v>
+        <v>46119</v>
       </c>
       <c r="H139" s="6" t="n">
-        <v>0</v>
+        <v>26400</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>0</v>
+        <v>13.19</v>
       </c>
       <c r="J139" s="6" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
     </row>
     <row r="140" customHeight="1" ht="15" spans="1:5">
@@ -4019,18 +4034,18 @@
         <v>24</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>226301.7</v>
+        <v>820410</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E140" s="12" t="n">
-        <v>0</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="141" customHeight="1" ht="15" spans="1:1">
       <c r="A141" s="2" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
     </row>
     <row r="142" customHeight="1" ht="15" spans="1:10">
@@ -4038,19 +4053,19 @@
         <v>14</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>1200</v>
+        <v>50100</v>
       </c>
       <c r="E142" s="7" t="n">
-        <v>5.1</v>
+        <v>4.517</v>
       </c>
       <c r="F142" s="7" t="n">
-        <v>6120</v>
+        <v>226301.7</v>
       </c>
       <c r="G142" s="8">
         <v>46156</v>
@@ -4073,115 +4088,115 @@
         <v>24</v>
       </c>
       <c r="C143" s="11" t="n">
+        <v>226301.7</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E143" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" ht="15" spans="1:1">
+      <c r="A144" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" ht="15" spans="1:10">
+      <c r="A145" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D145" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E145" s="7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F145" s="7" t="n">
         <v>6120</v>
       </c>
-      <c r="D143" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E143" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A144" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" customHeight="1" ht="15" spans="1:12">
-      <c r="A145" s="2" t="s">
+      <c r="G145" s="8">
+        <v>46156</v>
+      </c>
+      <c r="H145" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" ht="15" spans="1:5">
+      <c r="A146" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C146" s="11" t="n">
+        <v>6120</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E146" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A147" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" ht="15" spans="1:12">
+      <c r="A148" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C145" s="2" t="s">
+      <c r="B148" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D145" s="2" t="s">
+      <c r="D148" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E145" s="3" t="s">
+      <c r="E148" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F145" s="3" t="s">
+      <c r="F148" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G145" s="3" t="s">
+      <c r="G148" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H145" s="3" t="s">
+      <c r="H148" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I145" s="3" t="s">
+      <c r="I148" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J145" s="3" t="s">
+      <c r="J148" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K145" s="2" t="s">
+      <c r="K148" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L145" s="3" t="s">
+      <c r="L148" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="146" customHeight="1" ht="15" spans="1:1">
-      <c r="A146" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="147" customHeight="1" ht="15" spans="1:10">
-      <c r="A147" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B147" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D147" s="6" t="n">
-        <v>504</v>
-      </c>
-      <c r="E147" s="7" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="F147" s="7" t="n">
-        <v>22629.6</v>
-      </c>
-      <c r="G147" s="8">
-        <v>46141</v>
-      </c>
-      <c r="H147" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I147" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="148" customHeight="1" ht="15" spans="1:5">
-      <c r="A148" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B148" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C148" s="11" t="n">
-        <v>22629.6</v>
-      </c>
-      <c r="D148" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E148" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="149" customHeight="1" ht="15" spans="1:1">
       <c r="A149" s="2" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150" customHeight="1" ht="15" spans="1:10">
@@ -4189,22 +4204,22 @@
         <v>14</v>
       </c>
       <c r="B150" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C150" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C150" s="5" t="s">
-        <v>103</v>
-      </c>
       <c r="D150" s="6" t="n">
-        <v>408</v>
+        <v>504</v>
       </c>
       <c r="E150" s="7" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="F150" s="7" t="n">
-        <v>18360</v>
+        <v>22629.6</v>
       </c>
       <c r="G150" s="8">
-        <v>46147</v>
+        <v>46141</v>
       </c>
       <c r="H150" s="6" t="n">
         <v>0</v>
@@ -4213,7 +4228,7 @@
         <v>0</v>
       </c>
       <c r="J150" s="6" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
     </row>
     <row r="151" customHeight="1" ht="15" spans="1:5">
@@ -4224,7 +4239,7 @@
         <v>24</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>18360</v>
+        <v>22629.6</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>23</v>
@@ -4235,7 +4250,7 @@
     </row>
     <row r="152" customHeight="1" ht="15" spans="1:1">
       <c r="A152" s="2" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
     </row>
     <row r="153" customHeight="1" ht="15" spans="1:10">
@@ -4243,22 +4258,22 @@
         <v>14</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D153" s="6" t="n">
-        <v>180</v>
+        <v>408</v>
       </c>
       <c r="E153" s="7" t="n">
-        <v>49.5</v>
+        <v>45</v>
       </c>
       <c r="F153" s="7" t="n">
-        <v>8910</v>
+        <v>18360</v>
       </c>
       <c r="G153" s="8">
-        <v>46156</v>
+        <v>46147</v>
       </c>
       <c r="H153" s="6" t="n">
         <v>0</v>
@@ -4267,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="J153" s="6" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="154" customHeight="1" ht="15" spans="1:5">
@@ -4278,7 +4293,7 @@
         <v>24</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>8910</v>
+        <v>18360</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>23</v>
@@ -4289,7 +4304,7 @@
     </row>
     <row r="155" customHeight="1" ht="15" spans="1:1">
       <c r="A155" s="2" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
     </row>
     <row r="156" customHeight="1" ht="15" spans="1:10">
@@ -4297,22 +4312,22 @@
         <v>14</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D156" s="6" t="n">
-        <v>1200</v>
+        <v>204</v>
       </c>
       <c r="E156" s="7" t="n">
-        <v>45.9</v>
+        <v>49.5</v>
       </c>
       <c r="F156" s="7" t="n">
-        <v>55080</v>
+        <v>10098</v>
       </c>
       <c r="G156" s="8">
-        <v>46147</v>
+        <v>46157</v>
       </c>
       <c r="H156" s="6" t="n">
         <v>0</v>
@@ -4321,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="J156" s="6" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
     </row>
     <row r="157" customHeight="1" ht="15" spans="1:5">
@@ -4332,7 +4347,7 @@
         <v>24</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>55080</v>
+        <v>10098</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>23</v>
@@ -4343,7 +4358,7 @@
     </row>
     <row r="158" customHeight="1" ht="15" spans="1:1">
       <c r="A158" s="2" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
     </row>
     <row r="159" customHeight="1" ht="15" spans="1:10">
@@ -4351,19 +4366,19 @@
         <v>14</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D159" s="6" t="n">
-        <v>504</v>
+        <v>180</v>
       </c>
       <c r="E159" s="7" t="n">
         <v>49.5</v>
       </c>
       <c r="F159" s="7" t="n">
-        <v>24948</v>
+        <v>8910</v>
       </c>
       <c r="G159" s="8">
         <v>46156</v>
@@ -4386,417 +4401,417 @@
         <v>24</v>
       </c>
       <c r="C160" s="11" t="n">
+        <v>8910</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E160" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" ht="15" spans="1:1">
+      <c r="A161" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" ht="15" spans="1:10">
+      <c r="A162" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D162" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E162" s="7" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="F162" s="7" t="n">
+        <v>55080</v>
+      </c>
+      <c r="G162" s="8">
+        <v>46147</v>
+      </c>
+      <c r="H162" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" ht="15" spans="1:5">
+      <c r="A163" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C163" s="11" t="n">
+        <v>55080</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E163" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A164" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" ht="15" spans="1:12">
+      <c r="A165" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H165" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I165" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J165" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L165" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" ht="15" spans="1:1">
+      <c r="A166" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" ht="15" spans="1:10">
+      <c r="A167" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D167" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="E167" s="7" t="n">
+        <v>47.28</v>
+      </c>
+      <c r="F167" s="7" t="n">
+        <v>1702.08</v>
+      </c>
+      <c r="G167" s="8">
+        <v>46157</v>
+      </c>
+      <c r="H167" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="168" customHeight="1" ht="15" spans="1:5">
+      <c r="A168" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B168" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C168" s="11" t="n">
+        <v>1702.08</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E168" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" ht="15" spans="1:1">
+      <c r="A169" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" ht="15" spans="1:10">
+      <c r="A170" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D170" s="6" t="n">
+        <v>504</v>
+      </c>
+      <c r="E170" s="7" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F170" s="7" t="n">
         <v>24948</v>
       </c>
-      <c r="D160" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E160" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A161" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" customHeight="1" ht="15" spans="1:12">
-      <c r="A162" s="2" t="s">
+      <c r="G170" s="8">
+        <v>46156</v>
+      </c>
+      <c r="H170" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="171" customHeight="1" ht="15" spans="1:5">
+      <c r="A171" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B171" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C171" s="11" t="n">
+        <v>24948</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E171" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" ht="15" spans="1:1">
+      <c r="A172" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" ht="15" spans="1:10">
+      <c r="A173" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D173" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E173" s="7" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="F173" s="7" t="n">
+        <v>32760</v>
+      </c>
+      <c r="G173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="H173" s="6" t="n">
+        <v>768</v>
+      </c>
+      <c r="I173" s="9" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J173" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" ht="15" spans="1:5">
+      <c r="A174" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B174" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C174" s="11" t="n">
+        <v>32760</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E174" s="12" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A175" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" ht="15" spans="1:12">
+      <c r="A176" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B162" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C162" s="2" t="s">
+      <c r="B176" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C176" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D162" s="2" t="s">
+      <c r="D176" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E162" s="3" t="s">
+      <c r="E176" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F162" s="3" t="s">
+      <c r="F176" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G162" s="3" t="s">
+      <c r="G176" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H162" s="3" t="s">
+      <c r="H176" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I162" s="3" t="s">
+      <c r="I176" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J162" s="3" t="s">
+      <c r="J176" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K162" s="2" t="s">
+      <c r="K176" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L162" s="3" t="s">
+      <c r="L176" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="163" customHeight="1" ht="15" spans="1:1">
-      <c r="A163" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="164" customHeight="1" ht="15" spans="1:10">
-      <c r="A164" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B164" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D164" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E164" s="7" t="n">
-        <v>21.84</v>
-      </c>
-      <c r="F164" s="7" t="n">
-        <v>32760</v>
-      </c>
-      <c r="G164" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H164" s="6" t="n">
-        <v>768</v>
-      </c>
-      <c r="I164" s="9" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="J164" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="165" customHeight="1" ht="15" spans="1:5">
-      <c r="A165" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B165" s="10" t="s">
+    <row r="177" customHeight="1" ht="15" spans="1:1">
+      <c r="A177" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="178" customHeight="1" ht="15" spans="1:10">
+      <c r="A178" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D178" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E178" s="7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F178" s="7" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G178" s="8">
+        <v>46157</v>
+      </c>
+      <c r="H178" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="179" customHeight="1" ht="15" spans="1:5">
+      <c r="A179" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B179" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C165" s="11" t="n">
-        <v>32760</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E165" s="12" t="n">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="166" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A166" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" customHeight="1" ht="15" spans="1:12">
-      <c r="A167" s="2" t="s">
+      <c r="C179" s="11" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E179" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A180" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" ht="15" spans="1:12">
+      <c r="A181" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C167" s="2" t="s">
+      <c r="B181" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D167" s="2" t="s">
+      <c r="D181" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E167" s="3" t="s">
+      <c r="E181" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F167" s="3" t="s">
+      <c r="F181" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G167" s="3" t="s">
+      <c r="G181" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H167" s="3" t="s">
+      <c r="H181" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I167" s="3" t="s">
+      <c r="I181" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J167" s="3" t="s">
+      <c r="J181" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K167" s="2" t="s">
+      <c r="K181" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L167" s="3" t="s">
+      <c r="L181" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="168" customHeight="1" ht="15" spans="1:1">
-      <c r="A168" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="169" customHeight="1" ht="15" spans="1:10">
-      <c r="A169" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D169" s="6" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E169" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F169" s="7" t="n">
-        <v>4400</v>
-      </c>
-      <c r="G169" s="8">
-        <v>46156</v>
-      </c>
-      <c r="H169" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I169" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J169" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="170" customHeight="1" ht="15" spans="1:5">
-      <c r="A170" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B170" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C170" s="11" t="n">
-        <v>4400</v>
-      </c>
-      <c r="D170" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E170" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" customHeight="1" ht="15" spans="1:1">
-      <c r="A171" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="172" customHeight="1" ht="15" spans="1:10">
-      <c r="A172" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C172" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D172" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E172" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F172" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G172" s="8">
-        <v>46135</v>
-      </c>
-      <c r="H172" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I172" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J172" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="173" customHeight="1" ht="15" spans="1:5">
-      <c r="A173" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B173" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C173" s="11" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D173" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E173" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A174" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" customHeight="1" ht="15" spans="1:12">
-      <c r="A175" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E175" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F175" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G175" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H175" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I175" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J175" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K175" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L175" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="176" customHeight="1" ht="15" spans="1:1">
-      <c r="A176" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="177" customHeight="1" ht="15" spans="1:10">
-      <c r="A177" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D177" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E177" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F177" s="7" t="n">
-        <v>40000</v>
-      </c>
-      <c r="G177" s="8">
-        <v>46156</v>
-      </c>
-      <c r="H177" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I177" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J177" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="178" customHeight="1" ht="15" spans="1:5">
-      <c r="A178" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B178" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C178" s="11" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E178" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" customHeight="1" ht="15" spans="1:1">
-      <c r="A179" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="180" customHeight="1" ht="15" spans="1:10">
-      <c r="A180" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D180" s="6" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E180" s="7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F180" s="7" t="n">
-        <v>5040</v>
-      </c>
-      <c r="G180" s="8">
-        <v>46153</v>
-      </c>
-      <c r="H180" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I180" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J180" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="181" customHeight="1" ht="15" spans="1:5">
-      <c r="A181" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B181" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C181" s="11" t="n">
-        <v>5040</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E181" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="182" customHeight="1" ht="15" spans="1:1">
       <c r="A182" s="2" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
     </row>
     <row r="183" customHeight="1" ht="15" spans="1:10">
@@ -4804,22 +4819,22 @@
         <v>14</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D183" s="6" t="n">
-        <v>1200000</v>
+        <v>11000</v>
       </c>
       <c r="E183" s="7" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="F183" s="7" t="n">
-        <v>456000</v>
+        <v>4400</v>
       </c>
       <c r="G183" s="8">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="H183" s="6" t="n">
         <v>0</v>
@@ -4828,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="J183" s="6" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="184" customHeight="1" ht="15" spans="1:5">
@@ -4839,7 +4854,7 @@
         <v>24</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>456000</v>
+        <v>4400</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>23</v>
@@ -4858,7 +4873,7 @@
         <v>1</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>3</v>
@@ -4901,19 +4916,19 @@
         <v>14</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D188" s="6" t="n">
-        <v>3024</v>
+        <v>100000</v>
       </c>
       <c r="E188" s="7" t="n">
-        <v>12.3</v>
+        <v>0.4</v>
       </c>
       <c r="F188" s="7" t="n">
-        <v>37195.2</v>
+        <v>40000</v>
       </c>
       <c r="G188" s="8">
         <v>46156</v>
@@ -4936,7 +4951,7 @@
         <v>24</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>37195.2</v>
+        <v>40000</v>
       </c>
       <c r="D189" s="3" t="s">
         <v>23</v>
@@ -4947,7 +4962,7 @@
     </row>
     <row r="190" customHeight="1" ht="15" spans="1:1">
       <c r="A190" s="2" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
     </row>
     <row r="191" customHeight="1" ht="15" spans="1:10">
@@ -4955,31 +4970,31 @@
         <v>14</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="C191" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D191" s="6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E191" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F191" s="7" t="n">
+        <v>5040</v>
+      </c>
+      <c r="G191" s="8">
+        <v>46153</v>
+      </c>
+      <c r="H191" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="D191" s="6" t="n">
-        <v>2160</v>
-      </c>
-      <c r="E191" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="F191" s="7" t="n">
-        <v>25920</v>
-      </c>
-      <c r="G191" s="8">
-        <v>46156</v>
-      </c>
-      <c r="H191" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I191" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J191" s="6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="192" customHeight="1" ht="15" spans="1:5">
@@ -4990,320 +5005,320 @@
         <v>24</v>
       </c>
       <c r="C192" s="11" t="n">
+        <v>5040</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E192" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" ht="15" spans="1:1">
+      <c r="A193" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="194" customHeight="1" ht="15" spans="1:10">
+      <c r="A194" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D194" s="6" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E194" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F194" s="7" t="n">
+        <v>456000</v>
+      </c>
+      <c r="G194" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H194" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="195" customHeight="1" ht="15" spans="1:5">
+      <c r="A195" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B195" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C195" s="11" t="n">
+        <v>456000</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E195" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A196" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" customHeight="1" ht="15" spans="1:12">
+      <c r="A197" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H197" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I197" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J197" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K197" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L197" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="198" customHeight="1" ht="15" spans="1:1">
+      <c r="A198" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="199" customHeight="1" ht="15" spans="1:10">
+      <c r="A199" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D199" s="6" t="n">
+        <v>3024</v>
+      </c>
+      <c r="E199" s="7" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F199" s="7" t="n">
+        <v>37195.2</v>
+      </c>
+      <c r="G199" s="8">
+        <v>46156</v>
+      </c>
+      <c r="H199" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="200" customHeight="1" ht="15" spans="1:5">
+      <c r="A200" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C200" s="11" t="n">
+        <v>37195.2</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E200" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" ht="15" spans="1:1">
+      <c r="A201" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" ht="15" spans="1:10">
+      <c r="A202" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D202" s="6" t="n">
+        <v>2160</v>
+      </c>
+      <c r="E202" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F202" s="7" t="n">
         <v>25920</v>
       </c>
-      <c r="D192" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E192" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A193" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" customHeight="1" ht="15" spans="1:12">
-      <c r="A194" s="2" t="s">
+      <c r="G202" s="8">
+        <v>46156</v>
+      </c>
+      <c r="H202" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" ht="15" spans="1:5">
+      <c r="A203" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C203" s="11" t="n">
+        <v>25920</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E203" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" ht="15" spans="1:1">
+      <c r="A204" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" ht="15" spans="1:10">
+      <c r="A205" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D205" s="6" t="n">
+        <v>612</v>
+      </c>
+      <c r="E205" s="7" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="F205" s="7" t="n">
+        <v>7337.88</v>
+      </c>
+      <c r="G205" s="8">
+        <v>46157</v>
+      </c>
+      <c r="H205" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" ht="15" spans="1:5">
+      <c r="A206" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B206" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C206" s="11" t="n">
+        <v>7337.88</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E206" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A207" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" ht="15" spans="1:12">
+      <c r="A208" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B194" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C194" s="2" t="s">
+      <c r="B208" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C208" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D194" s="2" t="s">
+      <c r="D208" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E194" s="3" t="s">
+      <c r="E208" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F194" s="3" t="s">
+      <c r="F208" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G194" s="3" t="s">
+      <c r="G208" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H194" s="3" t="s">
+      <c r="H208" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I194" s="3" t="s">
+      <c r="I208" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J194" s="3" t="s">
+      <c r="J208" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K194" s="2" t="s">
+      <c r="K208" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L194" s="3" t="s">
+      <c r="L208" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="195" customHeight="1" ht="15" spans="1:1">
-      <c r="A195" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="196" customHeight="1" ht="15" spans="1:10">
-      <c r="A196" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B196" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C196" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D196" s="6" t="n">
-        <v>4020</v>
-      </c>
-      <c r="E196" s="7" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F196" s="7" t="n">
-        <v>53868</v>
-      </c>
-      <c r="G196" s="8">
-        <v>46154</v>
-      </c>
-      <c r="H196" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J196" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="197" customHeight="1" ht="15" spans="1:5">
-      <c r="A197" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B197" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C197" s="11" t="n">
-        <v>53868</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E197" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A198" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" customHeight="1" ht="15" spans="1:12">
-      <c r="A199" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E199" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F199" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G199" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H199" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I199" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J199" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K199" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L199" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="200" customHeight="1" ht="15" spans="1:1">
-      <c r="A200" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="201" customHeight="1" ht="15" spans="1:10">
-      <c r="A201" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B201" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D201" s="6" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E201" s="7" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F201" s="7" t="n">
-        <v>14178</v>
-      </c>
-      <c r="G201" s="8">
-        <v>46156</v>
-      </c>
-      <c r="H201" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I201" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J201" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="202" customHeight="1" ht="15" spans="1:5">
-      <c r="A202" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B202" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C202" s="11" t="n">
-        <v>14178</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E202" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" customHeight="1" ht="15" spans="1:1">
-      <c r="A203" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="204" customHeight="1" ht="15" spans="1:10">
-      <c r="A204" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B204" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C204" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D204" s="6" t="n">
-        <v>8025</v>
-      </c>
-      <c r="E204" s="7" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F204" s="7" t="n">
-        <v>166839.75</v>
-      </c>
-      <c r="G204" s="8">
-        <v>46122</v>
-      </c>
-      <c r="H204" s="6" t="n">
-        <v>3475</v>
-      </c>
-      <c r="I204" s="9" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="J204" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="205" customHeight="1" ht="15" spans="1:5">
-      <c r="A205" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B205" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C205" s="11" t="n">
-        <v>166839.75</v>
-      </c>
-      <c r="D205" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E205" s="12" t="n">
-        <v>3475</v>
-      </c>
-    </row>
-    <row r="206" customHeight="1" ht="15" spans="1:1">
-      <c r="A206" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="207" customHeight="1" ht="15" spans="1:10">
-      <c r="A207" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B207" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C207" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D207" s="6" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E207" s="7" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F207" s="7" t="n">
-        <v>21205.8</v>
-      </c>
-      <c r="G207" s="8">
-        <v>46156</v>
-      </c>
-      <c r="H207" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I207" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J207" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="208" customHeight="1" ht="15" spans="1:5">
-      <c r="A208" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B208" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C208" s="11" t="n">
-        <v>21205.8</v>
-      </c>
-      <c r="D208" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E208" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="209" customHeight="1" ht="15" spans="1:1">
       <c r="A209" s="2" t="s">
-        <v>133</v>
+        <v>65</v>
       </c>
     </row>
     <row r="210" customHeight="1" ht="15" spans="1:10">
@@ -5311,225 +5326,204 @@
         <v>14</v>
       </c>
       <c r="B210" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D210" s="6" t="n">
+        <v>4020</v>
+      </c>
+      <c r="E210" s="7" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F210" s="7" t="n">
+        <v>53868</v>
+      </c>
+      <c r="G210" s="8">
+        <v>46154</v>
+      </c>
+      <c r="H210" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="211" customHeight="1" ht="15" spans="1:5">
+      <c r="A211" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B211" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C211" s="11" t="n">
+        <v>53868</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E211" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A212" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" customHeight="1" ht="15" spans="1:12">
+      <c r="A213" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H213" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J213" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K213" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L213" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="214" customHeight="1" ht="15" spans="1:1">
+      <c r="A214" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="215" customHeight="1" ht="15" spans="1:10">
+      <c r="A215" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D215" s="6" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E215" s="7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F215" s="7" t="n">
+        <v>14178</v>
+      </c>
+      <c r="G215" s="8">
+        <v>46156</v>
+      </c>
+      <c r="H215" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="216" customHeight="1" ht="15" spans="1:5">
+      <c r="A216" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B216" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C216" s="11" t="n">
+        <v>14178</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E216" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" ht="15" spans="1:1">
+      <c r="A217" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" ht="15" spans="1:10">
+      <c r="A218" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C218" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C210" s="5" t="s">
+      <c r="D218" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E218" s="7" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F218" s="7" t="n">
+        <v>633.6</v>
+      </c>
+      <c r="G218" s="8">
+        <v>46157</v>
+      </c>
+      <c r="H218" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D210" s="6" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E210" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="F210" s="7" t="n">
-        <v>312000</v>
-      </c>
-      <c r="G210" s="8">
-        <v>46100</v>
-      </c>
-      <c r="H210" s="6" t="n">
-        <v>18900</v>
-      </c>
-      <c r="I210" s="9" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="J210" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="211" customHeight="1" ht="15" spans="1:10">
-      <c r="A211" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B211" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C211" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D211" s="6" t="n">
-        <v>2010</v>
-      </c>
-      <c r="E211" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="F211" s="7" t="n">
-        <v>26130</v>
-      </c>
-      <c r="G211" s="8">
-        <v>46156</v>
-      </c>
-      <c r="H211" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I211" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J211" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="212" customHeight="1" ht="15" spans="1:5">
-      <c r="A212" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B212" s="10" t="s">
+    </row>
+    <row r="219" customHeight="1" ht="15" spans="1:5">
+      <c r="A219" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B219" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C212" s="11" t="n">
-        <v>338130</v>
-      </c>
-      <c r="D212" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E212" s="12" t="n">
-        <v>18900</v>
-      </c>
-    </row>
-    <row r="213" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A213" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" customHeight="1" ht="15" spans="1:12">
-      <c r="A214" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D214" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E214" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F214" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G214" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H214" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I214" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J214" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K214" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L214" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="215" customHeight="1" ht="15" spans="1:1">
-      <c r="A215" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="216" customHeight="1" ht="15" spans="1:10">
-      <c r="A216" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B216" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C216" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D216" s="6" t="n">
-        <v>300</v>
-      </c>
-      <c r="E216" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F216" s="7" t="n">
-        <v>3450</v>
-      </c>
-      <c r="G216" s="8">
-        <v>46156</v>
-      </c>
-      <c r="H216" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I216" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J216" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="217" customHeight="1" ht="15" spans="1:5">
-      <c r="A217" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B217" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C217" s="11" t="n">
-        <v>3450</v>
-      </c>
-      <c r="D217" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E217" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A218" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" customHeight="1" ht="15" spans="1:12">
-      <c r="A219" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E219" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F219" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G219" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H219" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I219" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J219" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K219" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L219" s="3" t="s">
-        <v>12</v>
+      <c r="C219" s="11" t="n">
+        <v>633.6</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E219" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="220" customHeight="1" ht="15" spans="1:1">
       <c r="A220" s="2" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="221" customHeight="1" ht="15" spans="1:10">
@@ -5537,31 +5531,31 @@
         <v>14</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D221" s="6" t="n">
-        <v>2016</v>
+        <v>8025</v>
       </c>
       <c r="E221" s="7" t="n">
-        <v>5.8</v>
+        <v>20.79</v>
       </c>
       <c r="F221" s="7" t="n">
-        <v>11692.8</v>
+        <v>166839.75</v>
       </c>
       <c r="G221" s="8">
-        <v>46156</v>
+        <v>46122</v>
       </c>
       <c r="H221" s="6" t="n">
-        <v>0</v>
+        <v>3475</v>
       </c>
       <c r="I221" s="9" t="n">
-        <v>0</v>
+        <v>43.3</v>
       </c>
       <c r="J221" s="6" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="222" customHeight="1" ht="15" spans="1:5">
@@ -5572,18 +5566,18 @@
         <v>24</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>11692.8</v>
+        <v>166839.75</v>
       </c>
       <c r="D222" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E222" s="12" t="n">
-        <v>0</v>
+        <v>3475</v>
       </c>
     </row>
     <row r="223" customHeight="1" ht="15" spans="1:1">
       <c r="A223" s="2" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
     </row>
     <row r="224" customHeight="1" ht="15" spans="1:10">
@@ -5591,101 +5585,489 @@
         <v>14</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="C224" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D224" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E224" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F224" s="7" t="n">
+        <v>312000</v>
+      </c>
+      <c r="G224" s="8">
+        <v>46100</v>
+      </c>
+      <c r="H224" s="6" t="n">
+        <v>18900</v>
+      </c>
+      <c r="I224" s="9" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="J224" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="225" customHeight="1" ht="15" spans="1:10">
+      <c r="A225" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D225" s="6" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E225" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F225" s="7" t="n">
+        <v>26130</v>
+      </c>
+      <c r="G225" s="8">
+        <v>46156</v>
+      </c>
+      <c r="H225" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I225" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="226" customHeight="1" ht="15" spans="1:5">
+      <c r="A226" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B226" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C226" s="11" t="n">
+        <v>338130</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E226" s="12" t="n">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="227" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A227" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" customHeight="1" ht="15" spans="1:12">
+      <c r="A228" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B228" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D224" s="6" t="n">
+      <c r="C228" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H228" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I228" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J228" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K228" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L228" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" ht="15" spans="1:1">
+      <c r="A229" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="230" customHeight="1" ht="15" spans="1:10">
+      <c r="A230" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D230" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="E230" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F230" s="7" t="n">
+        <v>3450</v>
+      </c>
+      <c r="G230" s="8">
+        <v>46156</v>
+      </c>
+      <c r="H230" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="231" customHeight="1" ht="15" spans="1:5">
+      <c r="A231" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B231" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C231" s="11" t="n">
+        <v>3450</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E231" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" ht="15" spans="1:1">
+      <c r="A232" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" ht="15" spans="1:10">
+      <c r="A233" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D233" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E233" s="7" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="F233" s="7" t="n">
+        <v>1459.2</v>
+      </c>
+      <c r="G233" s="8">
+        <v>46157</v>
+      </c>
+      <c r="H233" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" ht="15" spans="1:5">
+      <c r="A234" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B234" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C234" s="11" t="n">
+        <v>1459.2</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E234" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A235" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" customHeight="1" ht="15" spans="1:12">
+      <c r="A236" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H236" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I236" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J236" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K236" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L236" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="237" customHeight="1" ht="15" spans="1:1">
+      <c r="A237" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="238" customHeight="1" ht="15" spans="1:10">
+      <c r="A238" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D238" s="6" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E238" s="7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F238" s="7" t="n">
+        <v>11692.8</v>
+      </c>
+      <c r="G238" s="8">
+        <v>46156</v>
+      </c>
+      <c r="H238" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I238" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="239" customHeight="1" ht="15" spans="1:5">
+      <c r="A239" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B239" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C239" s="11" t="n">
+        <v>11692.8</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E239" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" customHeight="1" ht="15" spans="1:1">
+      <c r="A240" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="241" customHeight="1" ht="15" spans="1:10">
+      <c r="A241" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D241" s="6" t="n">
+        <v>216</v>
+      </c>
+      <c r="E241" s="7" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F241" s="7" t="n">
+        <v>1509.84</v>
+      </c>
+      <c r="G241" s="8">
+        <v>46157</v>
+      </c>
+      <c r="H241" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="242" customHeight="1" ht="15" spans="1:5">
+      <c r="A242" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B242" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C242" s="11" t="n">
+        <v>1509.84</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E242" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" customHeight="1" ht="15" spans="1:1">
+      <c r="A243" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="244" customHeight="1" ht="15" spans="1:10">
+      <c r="A244" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D244" s="6" t="n">
         <v>1512</v>
       </c>
-      <c r="E224" s="7" t="n">
+      <c r="E244" s="7" t="n">
         <v>6.99</v>
       </c>
-      <c r="F224" s="7" t="n">
+      <c r="F244" s="7" t="n">
         <v>10568.88</v>
       </c>
-      <c r="G224" s="8">
+      <c r="G244" s="8">
         <v>46156</v>
       </c>
-      <c r="H224" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I224" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J224" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="225" customHeight="1" ht="15" spans="1:5">
-      <c r="A225" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B225" s="10" t="s">
+      <c r="H244" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I244" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="245" customHeight="1" ht="15" spans="1:5">
+      <c r="A245" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B245" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C225" s="11" t="n">
+      <c r="C245" s="11" t="n">
         <v>10568.88</v>
       </c>
-      <c r="D225" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E225" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" customHeight="1" ht="15" spans="1:1">
-      <c r="A226" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="227" customHeight="1" ht="15" spans="1:10">
-      <c r="A227" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B227" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C227" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D227" s="6" t="n">
+      <c r="D245" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E245" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" customHeight="1" ht="15" spans="1:1">
+      <c r="A246" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="247" customHeight="1" ht="15" spans="1:10">
+      <c r="A247" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D247" s="6" t="n">
         <v>1008</v>
       </c>
-      <c r="E227" s="7" t="n">
+      <c r="E247" s="7" t="n">
         <v>6.8</v>
       </c>
-      <c r="F227" s="7" t="n">
+      <c r="F247" s="7" t="n">
         <v>6854.4</v>
       </c>
-      <c r="G227" s="8">
+      <c r="G247" s="8">
         <v>46156</v>
       </c>
-      <c r="H227" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I227" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J227" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="228" customHeight="1" ht="15" spans="1:5">
-      <c r="A228" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B228" s="10" t="s">
+      <c r="H247" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I247" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="248" customHeight="1" ht="15" spans="1:5">
+      <c r="A248" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B248" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C228" s="11" t="n">
+      <c r="C248" s="11" t="n">
         <v>6854.4</v>
       </c>
-      <c r="D228" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E228" s="12" t="n">
+      <c r="D248" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E248" s="12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="180">
   <si>
     <t>MATRIZ CNPJ: 40.357.820/0001-50 R Y DOIS - 58082-025 ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
   </si>
@@ -205,6 +205,18 @@
     <t>890</t>
   </si>
   <si>
+    <t>CIRURGICA GUARARAPES</t>
+  </si>
+  <si>
+    <t>772</t>
+  </si>
+  <si>
+    <t>1589 - ATADURA DE CREPE 13 FIOS 10 X 1,20  PCT 12 FARMA C</t>
+  </si>
+  <si>
+    <t>1592 - ATADURA DE CREPE 13 FIOS 15 X 1,20  PCT 12 FARMA C</t>
+  </si>
+  <si>
     <t>DISTRIBUIDORA BRASIL</t>
   </si>
   <si>
@@ -235,15 +247,21 @@
     <t>889</t>
   </si>
   <si>
-    <t>1589 - ATADURA DE CREPE 13 FIOS 10 X 1,20  PCT 12 FARMA C</t>
-  </si>
-  <si>
-    <t>1592 - ATADURA DE CREPE 13 FIOS 15 X 1,20  PCT 12 FARMA C</t>
-  </si>
-  <si>
     <t>1594 - ATADURA DE CREPE 13 FIOS 30 X 1,20  PCT 12 FARMA C</t>
   </si>
   <si>
+    <t>HOSPMED</t>
+  </si>
+  <si>
+    <t>929</t>
+  </si>
+  <si>
+    <t>THIAGO RIBEIRO</t>
+  </si>
+  <si>
+    <t>1590 - ATADURA DE CREPE 13 FIOS 12 X 1,20  PCT 12 FARMA C</t>
+  </si>
+  <si>
     <t>JMC COMERCIAL LTDA</t>
   </si>
   <si>
@@ -253,9 +271,6 @@
     <t>DANILO</t>
   </si>
   <si>
-    <t>1590 - ATADURA DE CREPE 13 FIOS 12 X 1,20  PCT 12 FARMA C</t>
-  </si>
-  <si>
     <t>MAPEMI - BRASIL DISTRIBUICAO E LOGISTICA FARMACEUTICA</t>
   </si>
   <si>
@@ -298,9 +313,6 @@
     <t>692</t>
   </si>
   <si>
-    <t>767</t>
-  </si>
-  <si>
     <t>PROMED DIST. DE MEDIC E PROD. PARA SAUDE LTDA</t>
   </si>
   <si>
@@ -337,12 +349,6 @@
     <t xml:space="preserve">173 - ATADURA DE CREPE 13 FIOS 20 X 1,80  PCT 12  FARMA C </t>
   </si>
   <si>
-    <t>CAMPO - 25 X 28 C/02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1587 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 2 UND </t>
-  </si>
-  <si>
     <t>CAMPO - 25 X 28 C/05</t>
   </si>
   <si>
@@ -370,6 +376,12 @@
     <t>914</t>
   </si>
   <si>
+    <t>ENDOMED COMERCIO E REPRES DE MEDIC LTDA</t>
+  </si>
+  <si>
+    <t>928</t>
+  </si>
+  <si>
     <t>FLEX HOSPITALAR</t>
   </si>
   <si>
@@ -415,15 +427,21 @@
     <t xml:space="preserve">02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND </t>
   </si>
   <si>
+    <t>DISTRIBUIDORA RIO PARNAIBA</t>
+  </si>
+  <si>
+    <t>925</t>
+  </si>
+  <si>
     <t>ESTERIL - 13 FIOS</t>
   </si>
   <si>
+    <t xml:space="preserve">03 - GAZE ESTÉRIL 13FIOS - PCT 10 UND </t>
+  </si>
+  <si>
     <t>909</t>
   </si>
   <si>
-    <t xml:space="preserve">03 - GAZE ESTÉRIL 13FIOS - PCT 10 UND </t>
-  </si>
-  <si>
     <t>910</t>
   </si>
   <si>
@@ -439,7 +457,16 @@
     <t>GAZE EM ROLO - 09 FIOS</t>
   </si>
   <si>
+    <t>ALENCAR DISTRIB. DE MEDIC. E MAT. MEDICO-HOSP. LTDA</t>
+  </si>
+  <si>
+    <t>927</t>
+  </si>
+  <si>
     <t xml:space="preserve">85 - GAZE CIRCULAR NAO ESTERIL 09 FIOS </t>
+  </si>
+  <si>
+    <t>926</t>
   </si>
   <si>
     <t xml:space="preserve">84 - GAZE  CIRCULAR NAO ESTERIL 09 FIOS </t>
@@ -682,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L321"/>
+  <dimension ref="A1:L345"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
   <cols>
     <col customWidth="1" width="89.23828125" min="1" max="1"/>
@@ -2835,221 +2862,179 @@
         <v>65</v>
       </c>
       <c r="C90" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="F90" s="7" t="n">
+        <v>4092</v>
+      </c>
+      <c r="G90" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" ht="15" spans="1:10">
+      <c r="A91" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D91" s="6" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E91" s="7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>5616</v>
+      </c>
+      <c r="G91" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" ht="15" spans="1:5">
+      <c r="A92" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C92" s="11" t="n">
+        <v>9708</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E92" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" ht="15" spans="1:1">
+      <c r="A93" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" ht="15" spans="1:10">
+      <c r="A94" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C94" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D90" s="6" t="n">
+      <c r="D94" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="E90" s="7" t="n">
+      <c r="E94" s="7" t="n">
         <v>10.3</v>
       </c>
-      <c r="F90" s="7" t="n">
+      <c r="F94" s="7" t="n">
         <v>2472</v>
       </c>
-      <c r="G90" s="8">
+      <c r="G94" s="8">
         <v>46139</v>
       </c>
-      <c r="H90" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" ht="15" spans="1:5">
-      <c r="A91" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B91" s="10" t="s">
+      <c r="H94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" ht="15" spans="1:5">
+      <c r="A95" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B95" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C91" s="11" t="n">
+      <c r="C95" s="11" t="n">
         <v>2472</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E91" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A92" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" customHeight="1" ht="15" spans="1:12">
-      <c r="A93" s="2" t="s">
+      <c r="D95" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E95" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A96" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" ht="15" spans="1:12">
+      <c r="A97" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B97" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C97" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="D97" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="E97" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F97" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G93" s="3" t="s">
+      <c r="G97" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H93" s="3" t="s">
+      <c r="H97" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I93" s="3" t="s">
+      <c r="I97" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J93" s="3" t="s">
+      <c r="J97" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K93" s="2" t="s">
+      <c r="K97" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L93" s="3" t="s">
+      <c r="L97" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="94" customHeight="1" ht="15" spans="1:1">
-      <c r="A94" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="95" customHeight="1" ht="15" spans="1:10">
-      <c r="A95" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D95" s="6" t="n">
-        <v>1300</v>
-      </c>
-      <c r="E95" s="7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F95" s="7" t="n">
-        <v>5460</v>
-      </c>
-      <c r="G95" s="8">
-        <v>46139</v>
-      </c>
-      <c r="H95" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="96" customHeight="1" ht="15" spans="1:10">
-      <c r="A96" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D96" s="6" t="n">
-        <v>1050</v>
-      </c>
-      <c r="E96" s="7" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="F96" s="7" t="n">
-        <v>7182</v>
-      </c>
-      <c r="G96" s="8">
-        <v>46139</v>
-      </c>
-      <c r="H96" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="97" customHeight="1" ht="15" spans="1:10">
-      <c r="A97" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D97" s="6" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E97" s="7" t="n">
-        <v>8.28</v>
-      </c>
-      <c r="F97" s="7" t="n">
-        <v>8445.6</v>
-      </c>
-      <c r="G97" s="8">
-        <v>46139</v>
-      </c>
-      <c r="H97" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="98" customHeight="1" ht="15" spans="1:10">
-      <c r="A98" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D98" s="6" t="n">
-        <v>21700</v>
-      </c>
-      <c r="E98" s="7" t="n">
-        <v>4.368</v>
-      </c>
-      <c r="F98" s="7" t="n">
-        <v>94785.6</v>
-      </c>
-      <c r="G98" s="8">
-        <v>46156</v>
-      </c>
-      <c r="H98" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="6" t="s">
-        <v>17</v>
+    <row r="98" customHeight="1" ht="15" spans="1:1">
+      <c r="A98" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="99" customHeight="1" ht="15" spans="1:10">
@@ -3057,7 +3042,7 @@
         <v>14</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>58</v>
@@ -3072,7 +3057,7 @@
         <v>5460</v>
       </c>
       <c r="G99" s="8">
-        <v>46167</v>
+        <v>46139</v>
       </c>
       <c r="H99" s="6" t="n">
         <v>0</v>
@@ -3089,7 +3074,7 @@
         <v>14</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>60</v>
@@ -3104,7 +3089,7 @@
         <v>7182</v>
       </c>
       <c r="G100" s="8">
-        <v>46167</v>
+        <v>46139</v>
       </c>
       <c r="H100" s="6" t="n">
         <v>0</v>
@@ -3121,7 +3106,7 @@
         <v>14</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>61</v>
@@ -3136,38 +3121,80 @@
         <v>8445.6</v>
       </c>
       <c r="G101" s="8">
+        <v>46139</v>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" ht="15" spans="1:10">
+      <c r="A102" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D102" s="6" t="n">
+        <v>21700</v>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>4.368</v>
+      </c>
+      <c r="F102" s="7" t="n">
+        <v>94785.6</v>
+      </c>
+      <c r="G102" s="8">
+        <v>46156</v>
+      </c>
+      <c r="H102" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" ht="15" spans="1:10">
+      <c r="A103" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D103" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E103" s="7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F103" s="7" t="n">
+        <v>5460</v>
+      </c>
+      <c r="G103" s="8">
         <v>46167</v>
       </c>
-      <c r="H101" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="102" customHeight="1" ht="15" spans="1:5">
-      <c r="A102" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B102" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C102" s="11" t="n">
-        <v>136960.8</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E102" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" customHeight="1" ht="15" spans="1:1">
-      <c r="A103" s="2" t="s">
-        <v>70</v>
+      <c r="H103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="104" customHeight="1" ht="15" spans="1:10">
@@ -3175,22 +3202,22 @@
         <v>14</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>280</v>
+        <v>1050</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>7.25</v>
+        <v>6.84</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>2030</v>
+        <v>7182</v>
       </c>
       <c r="G104" s="8">
-        <v>46156</v>
+        <v>46167</v>
       </c>
       <c r="H104" s="6" t="n">
         <v>0</v>
@@ -3210,92 +3237,50 @@
         <v>73</v>
       </c>
       <c r="C105" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D105" s="6" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E105" s="7" t="n">
+        <v>8.28</v>
+      </c>
+      <c r="F105" s="7" t="n">
+        <v>8445.6</v>
+      </c>
+      <c r="G105" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" ht="15" spans="1:5">
+      <c r="A106" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C106" s="11" t="n">
+        <v>136960.8</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E106" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" ht="15" spans="1:1">
+      <c r="A107" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="D105" s="6" t="n">
-        <v>330</v>
-      </c>
-      <c r="E105" s="7" t="n">
-        <v>4.2876</v>
-      </c>
-      <c r="F105" s="7" t="n">
-        <v>1414.908</v>
-      </c>
-      <c r="G105" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H105" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="106" customHeight="1" ht="15" spans="1:10">
-      <c r="A106" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D106" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="E106" s="7" t="n">
-        <v>6.0804</v>
-      </c>
-      <c r="F106" s="7" t="n">
-        <v>1094.472</v>
-      </c>
-      <c r="G106" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H106" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="I106" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="J106" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="107" customHeight="1" ht="15" spans="1:10">
-      <c r="A107" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D107" s="6" t="n">
-        <v>350</v>
-      </c>
-      <c r="E107" s="7" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="F107" s="7" t="n">
-        <v>2740.5</v>
-      </c>
-      <c r="G107" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H107" s="6" t="n">
-        <v>140</v>
-      </c>
-      <c r="I107" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="J107" s="6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="108" customHeight="1" ht="15" spans="1:10">
@@ -3303,53 +3288,95 @@
         <v>14</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>11.5992</v>
+        <v>7.25</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>1159.92</v>
+        <v>2030</v>
       </c>
       <c r="G108" s="8">
+        <v>46156</v>
+      </c>
+      <c r="H108" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" ht="15" spans="1:10">
+      <c r="A109" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D109" s="6" t="n">
+        <v>330</v>
+      </c>
+      <c r="E109" s="7" t="n">
+        <v>4.2876</v>
+      </c>
+      <c r="F109" s="7" t="n">
+        <v>1414.908</v>
+      </c>
+      <c r="G109" s="8">
         <v>46164</v>
       </c>
-      <c r="H108" s="6" t="n">
+      <c r="H109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" ht="15" spans="1:10">
+      <c r="A110" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D110" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="E110" s="7" t="n">
+        <v>6.0804</v>
+      </c>
+      <c r="F110" s="7" t="n">
+        <v>1094.472</v>
+      </c>
+      <c r="G110" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I110" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="I108" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="J108" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="109" customHeight="1" ht="15" spans="1:5">
-      <c r="A109" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B109" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C109" s="11" t="n">
-        <v>8439.8</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E109" s="12" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="110" customHeight="1" ht="15" spans="1:1">
-      <c r="A110" s="2" t="s">
-        <v>77</v>
+      <c r="J110" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="111" customHeight="1" ht="15" spans="1:10">
@@ -3357,31 +3384,31 @@
         <v>14</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>440</v>
+        <v>350</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>4.46</v>
+        <v>7.83</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>1962.4</v>
+        <v>2740.5</v>
       </c>
       <c r="G111" s="8">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="H111" s="6" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112" customHeight="1" ht="15" spans="1:10">
@@ -3389,159 +3416,180 @@
         <v>14</v>
       </c>
       <c r="B112" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C112" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="D112" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>11.5992</v>
+      </c>
+      <c r="F112" s="7" t="n">
+        <v>1159.92</v>
+      </c>
+      <c r="G112" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I112" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="J112" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" ht="15" spans="1:5">
+      <c r="A113" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B113" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C113" s="11" t="n">
+        <v>8439.8</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" ht="15" spans="1:1">
+      <c r="A114" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" ht="15" spans="1:10">
+      <c r="A115" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D112" s="6" t="n">
-        <v>440</v>
-      </c>
-      <c r="E112" s="7" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="F112" s="7" t="n">
-        <v>2424.4</v>
-      </c>
-      <c r="G112" s="8">
-        <v>46150</v>
-      </c>
-      <c r="H112" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="113" customHeight="1" ht="15" spans="1:10">
-      <c r="A113" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D113" s="6" t="n">
-        <v>360</v>
-      </c>
-      <c r="E113" s="7" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="F113" s="7" t="n">
-        <v>2275.2</v>
-      </c>
-      <c r="G113" s="8">
-        <v>46150</v>
-      </c>
-      <c r="H113" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="114" customHeight="1" ht="15" spans="1:10">
-      <c r="A114" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D114" s="6" t="n">
-        <v>420</v>
-      </c>
-      <c r="E114" s="7" t="n">
+      <c r="C115" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D115" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="E115" s="7" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="F115" s="7" t="n">
+        <v>519.2</v>
+      </c>
+      <c r="G115" s="8">
+        <v>46170</v>
+      </c>
+      <c r="H115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" ht="15" spans="1:10">
+      <c r="A116" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D116" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E116" s="7" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="F116" s="7" t="n">
+        <v>646</v>
+      </c>
+      <c r="G116" s="8">
+        <v>46170</v>
+      </c>
+      <c r="H116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" ht="15" spans="1:10">
+      <c r="A117" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D117" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="E117" s="7" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="F117" s="7" t="n">
+        <v>641.3</v>
+      </c>
+      <c r="G117" s="8">
+        <v>46170</v>
+      </c>
+      <c r="H117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" ht="15" spans="1:10">
+      <c r="A118" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D118" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E118" s="7" t="n">
         <v>8.14</v>
       </c>
-      <c r="F114" s="7" t="n">
-        <v>3418.8</v>
-      </c>
-      <c r="G114" s="8">
-        <v>46150</v>
-      </c>
-      <c r="H114" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="115" customHeight="1" ht="15" spans="1:5">
-      <c r="A115" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B115" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C115" s="11" t="n">
-        <v>10080.8</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E115" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A116" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" customHeight="1" ht="15" spans="1:12">
-      <c r="A117" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G117" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I117" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J117" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K117" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L117" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="118" customHeight="1" ht="15" spans="1:1">
-      <c r="A118" s="2" t="s">
+      <c r="F118" s="7" t="n">
+        <v>732.6</v>
+      </c>
+      <c r="G118" s="8">
+        <v>46170</v>
+      </c>
+      <c r="H118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="6" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3550,22 +3598,22 @@
         <v>14</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>400</v>
+        <v>90</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>5.99</v>
+        <v>6.69</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>2396</v>
+        <v>602.1</v>
       </c>
       <c r="G119" s="8">
-        <v>46134</v>
+        <v>46170</v>
       </c>
       <c r="H119" s="6" t="n">
         <v>0</v>
@@ -3574,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="120" customHeight="1" ht="15" spans="1:10">
@@ -3582,22 +3630,22 @@
         <v>14</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>270</v>
+        <v>75</v>
       </c>
       <c r="E120" s="7" t="n">
-        <v>7.55</v>
+        <v>9.53</v>
       </c>
       <c r="F120" s="7" t="n">
-        <v>2038.5</v>
+        <v>714.75</v>
       </c>
       <c r="G120" s="8">
-        <v>46134</v>
+        <v>46170</v>
       </c>
       <c r="H120" s="6" t="n">
         <v>0</v>
@@ -3606,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="121" customHeight="1" ht="15" spans="1:10">
@@ -3614,22 +3662,22 @@
         <v>14</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C121" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D121" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="D121" s="6" t="n">
-        <v>375</v>
-      </c>
       <c r="E121" s="7" t="n">
-        <v>8.84</v>
+        <v>12.36</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>3315</v>
+        <v>741.6</v>
       </c>
       <c r="G121" s="8">
-        <v>46134</v>
+        <v>46170</v>
       </c>
       <c r="H121" s="6" t="n">
         <v>0</v>
@@ -3638,93 +3686,72 @@
         <v>0</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="122" customHeight="1" ht="15" spans="1:10">
-      <c r="A122" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D122" s="6" t="n">
-        <v>240</v>
-      </c>
-      <c r="E122" s="7" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="F122" s="7" t="n">
-        <v>2750.4</v>
-      </c>
-      <c r="G122" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H122" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="123" customHeight="1" ht="15" spans="1:10">
-      <c r="A123" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D123" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E123" s="7" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="F123" s="7" t="n">
-        <v>3282</v>
-      </c>
-      <c r="G123" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H123" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="124" customHeight="1" ht="15" spans="1:5">
-      <c r="A124" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B124" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" ht="15" spans="1:5">
+      <c r="A122" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B122" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C124" s="11" t="n">
-        <v>13781.9</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E124" s="12" t="n">
-        <v>0</v>
+      <c r="C122" s="11" t="n">
+        <v>4597.55</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E122" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A123" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" ht="15" spans="1:12">
+      <c r="A124" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L124" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="125" customHeight="1" ht="15" spans="1:1">
       <c r="A125" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="126" customHeight="1" ht="15" spans="1:10">
@@ -3732,22 +3759,22 @@
         <v>14</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>75</v>
+        <v>440</v>
       </c>
       <c r="E126" s="7" t="n">
-        <v>7.94</v>
+        <v>4.46</v>
       </c>
       <c r="F126" s="7" t="n">
-        <v>595.5</v>
+        <v>1962.4</v>
       </c>
       <c r="G126" s="8">
-        <v>46168</v>
+        <v>46150</v>
       </c>
       <c r="H126" s="6" t="n">
         <v>0</v>
@@ -3756,29 +3783,71 @@
         <v>0</v>
       </c>
       <c r="J126" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="127" customHeight="1" ht="15" spans="1:5">
-      <c r="A127" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B127" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C127" s="11" t="n">
-        <v>595.5</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E127" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" customHeight="1" ht="15" spans="1:1">
-      <c r="A128" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" ht="15" spans="1:10">
+      <c r="A127" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D127" s="6" t="n">
+        <v>440</v>
+      </c>
+      <c r="E127" s="7" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="F127" s="7" t="n">
+        <v>2424.4</v>
+      </c>
+      <c r="G127" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H127" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" ht="15" spans="1:10">
+      <c r="A128" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D128" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="E128" s="7" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="F128" s="7" t="n">
+        <v>2275.2</v>
+      </c>
+      <c r="G128" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H128" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="129" customHeight="1" ht="15" spans="1:10">
@@ -3786,22 +3855,22 @@
         <v>14</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>110</v>
+        <v>420</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>6.99</v>
+        <v>8.14</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>768.9</v>
+        <v>3418.8</v>
       </c>
       <c r="G129" s="8">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="H129" s="6" t="n">
         <v>0</v>
@@ -3810,93 +3879,93 @@
         <v>0</v>
       </c>
       <c r="J129" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="130" customHeight="1" ht="15" spans="1:10">
-      <c r="A130" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D130" s="6" t="n">
-        <v>300</v>
-      </c>
-      <c r="E130" s="7" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="F130" s="7" t="n">
-        <v>3276</v>
-      </c>
-      <c r="G130" s="8">
-        <v>46141</v>
-      </c>
-      <c r="H130" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="131" customHeight="1" ht="15" spans="1:10">
-      <c r="A131" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D131" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E131" s="7" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="F131" s="7" t="n">
-        <v>3124</v>
-      </c>
-      <c r="G131" s="8">
-        <v>46141</v>
-      </c>
-      <c r="H131" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="132" customHeight="1" ht="15" spans="1:5">
-      <c r="A132" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B132" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" ht="15" spans="1:5">
+      <c r="A130" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B130" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C132" s="11" t="n">
-        <v>7168.9</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E132" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" customHeight="1" ht="15" spans="1:1">
-      <c r="A133" s="2" t="s">
-        <v>91</v>
+      <c r="C130" s="11" t="n">
+        <v>10080.8</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E130" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" ht="15" spans="1:1">
+      <c r="A131" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" ht="15" spans="1:10">
+      <c r="A132" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D132" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="E132" s="7" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="F132" s="7" t="n">
+        <v>2396</v>
+      </c>
+      <c r="G132" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H132" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" ht="15" spans="1:10">
+      <c r="A133" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D133" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="E133" s="7" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="F133" s="7" t="n">
+        <v>2038.5</v>
+      </c>
+      <c r="G133" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="6" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="134" customHeight="1" ht="15" spans="1:10">
@@ -3904,22 +3973,22 @@
         <v>14</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>270</v>
+        <v>375</v>
       </c>
       <c r="E134" s="7" t="n">
-        <v>6.41</v>
+        <v>8.84</v>
       </c>
       <c r="F134" s="7" t="n">
-        <v>1730.7</v>
+        <v>3315</v>
       </c>
       <c r="G134" s="8">
-        <v>46168</v>
+        <v>46134</v>
       </c>
       <c r="H134" s="6" t="n">
         <v>0</v>
@@ -3928,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="6" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
     </row>
     <row r="135" customHeight="1" ht="15" spans="1:10">
@@ -3936,22 +4005,22 @@
         <v>14</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>7.92</v>
+        <v>11.46</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>2534.4</v>
+        <v>2750.4</v>
       </c>
       <c r="G135" s="8">
-        <v>46168</v>
+        <v>46134</v>
       </c>
       <c r="H135" s="6" t="n">
         <v>0</v>
@@ -3960,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="6" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
     </row>
     <row r="136" customHeight="1" ht="15" spans="1:10">
@@ -3968,22 +4037,22 @@
         <v>14</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="E136" s="7" t="n">
-        <v>9.37</v>
+        <v>16.41</v>
       </c>
       <c r="F136" s="7" t="n">
-        <v>655.9</v>
+        <v>3282</v>
       </c>
       <c r="G136" s="8">
-        <v>46168</v>
+        <v>46134</v>
       </c>
       <c r="H136" s="6" t="n">
         <v>0</v>
@@ -3992,7 +4061,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="6" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
     </row>
     <row r="137" customHeight="1" ht="15" spans="1:5">
@@ -4003,7 +4072,7 @@
         <v>27</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>4921</v>
+        <v>13781.9</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>26</v>
@@ -4012,148 +4081,106 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A138" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" customHeight="1" ht="15" spans="1:12">
-      <c r="A139" s="2" t="s">
+    <row r="138" customHeight="1" ht="15" spans="1:1">
+      <c r="A138" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" ht="15" spans="1:10">
+      <c r="A139" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D139" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="E139" s="7" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="F139" s="7" t="n">
+        <v>595.5</v>
+      </c>
+      <c r="G139" s="8">
+        <v>46168</v>
+      </c>
+      <c r="H139" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" ht="15" spans="1:5">
+      <c r="A140" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C140" s="11" t="n">
+        <v>595.5</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E140" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A141" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" ht="15" spans="1:12">
+      <c r="A142" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B142" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C139" s="2" t="s">
+      <c r="C142" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D139" s="2" t="s">
+      <c r="D142" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E139" s="3" t="s">
+      <c r="E142" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F139" s="3" t="s">
+      <c r="F142" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G139" s="3" t="s">
+      <c r="G142" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H139" s="3" t="s">
+      <c r="H142" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I139" s="3" t="s">
+      <c r="I142" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J139" s="3" t="s">
+      <c r="J142" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K139" s="2" t="s">
+      <c r="K142" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L139" s="3" t="s">
+      <c r="L142" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="140" customHeight="1" ht="15" spans="1:1">
-      <c r="A140" s="2" t="s">
+    <row r="143" customHeight="1" ht="15" spans="1:1">
+      <c r="A143" s="2" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="141" customHeight="1" ht="15" spans="1:10">
-      <c r="A141" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D141" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="E141" s="7" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="F141" s="7" t="n">
-        <v>576.9</v>
-      </c>
-      <c r="G141" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H141" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="142" customHeight="1" ht="15" spans="1:10">
-      <c r="A142" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D142" s="6" t="n">
-        <v>320</v>
-      </c>
-      <c r="E142" s="7" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="F142" s="7" t="n">
-        <v>2534.4</v>
-      </c>
-      <c r="G142" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H142" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="143" customHeight="1" ht="15" spans="1:10">
-      <c r="A143" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D143" s="6" t="n">
-        <v>700</v>
-      </c>
-      <c r="E143" s="7" t="n">
-        <v>9.37</v>
-      </c>
-      <c r="F143" s="7" t="n">
-        <v>6559</v>
-      </c>
-      <c r="G143" s="8">
-        <v>46113</v>
-      </c>
-      <c r="H143" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" s="6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="144" customHeight="1" ht="15" spans="1:10">
@@ -4164,19 +4191,19 @@
         <v>94</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>360</v>
+        <v>110</v>
       </c>
       <c r="E144" s="7" t="n">
-        <v>12.03</v>
+        <v>6.99</v>
       </c>
       <c r="F144" s="7" t="n">
-        <v>4330.8</v>
+        <v>768.9</v>
       </c>
       <c r="G144" s="8">
-        <v>46113</v>
+        <v>46141</v>
       </c>
       <c r="H144" s="6" t="n">
         <v>0</v>
@@ -4185,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="J144" s="6" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
     </row>
     <row r="145" customHeight="1" ht="15" spans="1:10">
@@ -4193,31 +4220,31 @@
         <v>14</v>
       </c>
       <c r="B145" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D145" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="E145" s="7" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="F145" s="7" t="n">
+        <v>3276</v>
+      </c>
+      <c r="G145" s="8">
+        <v>46141</v>
+      </c>
+      <c r="H145" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D145" s="6" t="n">
-        <v>400</v>
-      </c>
-      <c r="E145" s="7" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="F145" s="7" t="n">
-        <v>3168</v>
-      </c>
-      <c r="G145" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H145" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" s="6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="146" customHeight="1" ht="15" spans="1:10">
@@ -4225,117 +4252,117 @@
         <v>14</v>
       </c>
       <c r="B146" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D146" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E146" s="7" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="F146" s="7" t="n">
+        <v>3124</v>
+      </c>
+      <c r="G146" s="8">
+        <v>46141</v>
+      </c>
+      <c r="H146" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C146" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D146" s="6" t="n">
-        <v>280</v>
-      </c>
-      <c r="E146" s="7" t="n">
-        <v>9.37</v>
-      </c>
-      <c r="F146" s="7" t="n">
-        <v>2623.6</v>
-      </c>
-      <c r="G146" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H146" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="147" customHeight="1" ht="15" spans="1:10">
-      <c r="A147" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B147" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D147" s="6" t="n">
-        <v>300</v>
-      </c>
-      <c r="E147" s="7" t="n">
-        <v>12.03</v>
-      </c>
-      <c r="F147" s="7" t="n">
-        <v>3609</v>
-      </c>
-      <c r="G147" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H147" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I147" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="148" customHeight="1" ht="15" spans="1:10">
-      <c r="A148" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D148" s="6" t="n">
-        <v>140</v>
-      </c>
-      <c r="E148" s="7" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="F148" s="7" t="n">
-        <v>2427.6</v>
-      </c>
-      <c r="G148" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H148" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="149" customHeight="1" ht="15" spans="1:5">
-      <c r="A149" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B149" s="10" t="s">
+    </row>
+    <row r="147" customHeight="1" ht="15" spans="1:5">
+      <c r="A147" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B147" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C149" s="11" t="n">
-        <v>25829.3</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E149" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" customHeight="1" ht="15" spans="1:1">
-      <c r="A150" s="2" t="s">
+      <c r="C147" s="11" t="n">
+        <v>7168.9</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E147" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" ht="15" spans="1:1">
+      <c r="A148" s="2" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" ht="15" spans="1:10">
+      <c r="A149" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D149" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="E149" s="7" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="F149" s="7" t="n">
+        <v>1730.7</v>
+      </c>
+      <c r="G149" s="8">
+        <v>46168</v>
+      </c>
+      <c r="H149" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" ht="15" spans="1:10">
+      <c r="A150" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D150" s="6" t="n">
+        <v>320</v>
+      </c>
+      <c r="E150" s="7" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="F150" s="7" t="n">
+        <v>2534.4</v>
+      </c>
+      <c r="G150" s="8">
+        <v>46168</v>
+      </c>
+      <c r="H150" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="151" customHeight="1" ht="15" spans="1:10">
@@ -4346,19 +4373,19 @@
         <v>97</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>660</v>
+        <v>70</v>
       </c>
       <c r="E151" s="7" t="n">
-        <v>4.29</v>
+        <v>9.37</v>
       </c>
       <c r="F151" s="7" t="n">
-        <v>2831.4</v>
+        <v>655.9</v>
       </c>
       <c r="G151" s="8">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="H151" s="6" t="n">
         <v>0</v>
@@ -4367,71 +4394,29 @@
         <v>0</v>
       </c>
       <c r="J151" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="152" customHeight="1" ht="15" spans="1:10">
-      <c r="A152" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D152" s="6" t="n">
-        <v>660</v>
-      </c>
-      <c r="E152" s="7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F152" s="7" t="n">
-        <v>3498</v>
-      </c>
-      <c r="G152" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H152" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="153" customHeight="1" ht="15" spans="1:10">
-      <c r="A153" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D153" s="6" t="n">
-        <v>630</v>
-      </c>
-      <c r="E153" s="7" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="F153" s="7" t="n">
-        <v>3546.9</v>
-      </c>
-      <c r="G153" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H153" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" s="6" t="s">
-        <v>45</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" ht="15" spans="1:5">
+      <c r="A152" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C152" s="11" t="n">
+        <v>4921</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E152" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" ht="15" spans="1:1">
+      <c r="A153" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="154" customHeight="1" ht="15" spans="1:10">
@@ -4439,22 +4424,22 @@
         <v>14</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="E154" s="7" t="n">
-        <v>7.25</v>
+        <v>6.41</v>
       </c>
       <c r="F154" s="7" t="n">
-        <v>2537.5</v>
+        <v>576.9</v>
       </c>
       <c r="G154" s="8">
-        <v>46167</v>
+        <v>46113</v>
       </c>
       <c r="H154" s="6" t="n">
         <v>0</v>
@@ -4463,168 +4448,168 @@
         <v>0</v>
       </c>
       <c r="J154" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="155" customHeight="1" ht="15" spans="1:5">
-      <c r="A155" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B155" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" ht="15" spans="1:10">
+      <c r="A155" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D155" s="6" t="n">
+        <v>320</v>
+      </c>
+      <c r="E155" s="7" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="F155" s="7" t="n">
+        <v>2534.4</v>
+      </c>
+      <c r="G155" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H155" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" ht="15" spans="1:10">
+      <c r="A156" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D156" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="E156" s="7" t="n">
+        <v>9.37</v>
+      </c>
+      <c r="F156" s="7" t="n">
+        <v>6559</v>
+      </c>
+      <c r="G156" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H156" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" ht="15" spans="1:10">
+      <c r="A157" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D157" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="E157" s="7" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="F157" s="7" t="n">
+        <v>4330.8</v>
+      </c>
+      <c r="G157" s="8">
+        <v>46113</v>
+      </c>
+      <c r="H157" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" ht="15" spans="1:5">
+      <c r="A158" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B158" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C155" s="11" t="n">
-        <v>12413.8</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E155" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A156" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" customHeight="1" ht="15" spans="1:12">
-      <c r="A157" s="2" t="s">
+      <c r="C158" s="11" t="n">
+        <v>14001.1</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E158" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A159" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" ht="15" spans="1:12">
+      <c r="A160" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B157" s="2" t="s">
+      <c r="B160" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C157" s="2" t="s">
+      <c r="C160" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D157" s="2" t="s">
+      <c r="D160" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E157" s="3" t="s">
+      <c r="E160" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F157" s="3" t="s">
+      <c r="F160" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G157" s="3" t="s">
+      <c r="G160" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H157" s="3" t="s">
+      <c r="H160" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I157" s="3" t="s">
+      <c r="I160" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J157" s="3" t="s">
+      <c r="J160" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K157" s="2" t="s">
+      <c r="K160" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L157" s="3" t="s">
+      <c r="L160" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="158" customHeight="1" ht="15" spans="1:1">
-      <c r="A158" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="159" customHeight="1" ht="15" spans="1:10">
-      <c r="A159" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D159" s="6" t="n">
-        <v>550</v>
-      </c>
-      <c r="E159" s="7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F159" s="7" t="n">
-        <v>2255</v>
-      </c>
-      <c r="G159" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H159" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I159" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J159" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="160" customHeight="1" ht="15" spans="1:10">
-      <c r="A160" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D160" s="6" t="n">
-        <v>550</v>
-      </c>
-      <c r="E160" s="7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F160" s="7" t="n">
-        <v>2860</v>
-      </c>
-      <c r="G160" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H160" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="161" customHeight="1" ht="15" spans="1:10">
-      <c r="A161" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D161" s="6" t="n">
-        <v>540</v>
-      </c>
-      <c r="E161" s="7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F161" s="7" t="n">
-        <v>3348</v>
-      </c>
-      <c r="G161" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H161" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J161" s="6" t="s">
-        <v>17</v>
+    <row r="161" customHeight="1" ht="15" spans="1:1">
+      <c r="A161" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="162" customHeight="1" ht="15" spans="1:10">
@@ -4632,22 +4617,22 @@
         <v>14</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D162" s="6" t="n">
-        <v>560</v>
+        <v>660</v>
       </c>
       <c r="E162" s="7" t="n">
-        <v>7.5</v>
+        <v>4.29</v>
       </c>
       <c r="F162" s="7" t="n">
-        <v>4200</v>
+        <v>2831.4</v>
       </c>
       <c r="G162" s="8">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="H162" s="6" t="n">
         <v>0</v>
@@ -4656,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="J162" s="6" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="163" customHeight="1" ht="15" spans="1:10">
@@ -4664,22 +4649,22 @@
         <v>14</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D163" s="6" t="n">
-        <v>250</v>
+        <v>660</v>
       </c>
       <c r="E163" s="7" t="n">
-        <v>12.1</v>
+        <v>5.3</v>
       </c>
       <c r="F163" s="7" t="n">
-        <v>3025</v>
+        <v>3498</v>
       </c>
       <c r="G163" s="8">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="H163" s="6" t="n">
         <v>0</v>
@@ -4688,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="J163" s="6" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="164" customHeight="1" ht="15" spans="1:10">
@@ -4696,22 +4681,22 @@
         <v>14</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D164" s="6" t="n">
-        <v>550</v>
+        <v>630</v>
       </c>
       <c r="E164" s="7" t="n">
-        <v>4.1</v>
+        <v>5.63</v>
       </c>
       <c r="F164" s="7" t="n">
-        <v>2255</v>
+        <v>3546.9</v>
       </c>
       <c r="G164" s="8">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="H164" s="6" t="n">
         <v>0</v>
@@ -4720,7 +4705,7 @@
         <v>0</v>
       </c>
       <c r="J164" s="6" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="165" customHeight="1" ht="15" spans="1:10">
@@ -4728,22 +4713,22 @@
         <v>14</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D165" s="6" t="n">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="E165" s="7" t="n">
-        <v>5.2</v>
+        <v>7.25</v>
       </c>
       <c r="F165" s="7" t="n">
-        <v>2860</v>
+        <v>2537.5</v>
       </c>
       <c r="G165" s="8">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="H165" s="6" t="n">
         <v>0</v>
@@ -4752,71 +4737,29 @@
         <v>0</v>
       </c>
       <c r="J165" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="166" customHeight="1" ht="15" spans="1:10">
-      <c r="A166" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B166" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D166" s="6" t="n">
-        <v>540</v>
-      </c>
-      <c r="E166" s="7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F166" s="7" t="n">
-        <v>3348</v>
-      </c>
-      <c r="G166" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H166" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I166" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="167" customHeight="1" ht="15" spans="1:10">
-      <c r="A167" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B167" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D167" s="6" t="n">
-        <v>560</v>
-      </c>
-      <c r="E167" s="7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F167" s="7" t="n">
-        <v>4200</v>
-      </c>
-      <c r="G167" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H167" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J167" s="6" t="s">
-        <v>17</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" ht="15" spans="1:5">
+      <c r="A166" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B166" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C166" s="11" t="n">
+        <v>12413.8</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E166" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" ht="15" spans="1:1">
+      <c r="A167" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="168" customHeight="1" ht="15" spans="1:10">
@@ -4824,19 +4767,19 @@
         <v>14</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D168" s="6" t="n">
-        <v>250</v>
+        <v>550</v>
       </c>
       <c r="E168" s="7" t="n">
-        <v>12.1</v>
+        <v>4.1</v>
       </c>
       <c r="F168" s="7" t="n">
-        <v>3025</v>
+        <v>2255</v>
       </c>
       <c r="G168" s="8">
         <v>46164</v>
@@ -4851,26 +4794,68 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" customHeight="1" ht="15" spans="1:5">
-      <c r="A169" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B169" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C169" s="11" t="n">
-        <v>31376</v>
-      </c>
-      <c r="D169" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E169" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" customHeight="1" ht="15" spans="1:1">
-      <c r="A170" s="2" t="s">
-        <v>101</v>
+    <row r="169" customHeight="1" ht="15" spans="1:10">
+      <c r="A169" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D169" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="E169" s="7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F169" s="7" t="n">
+        <v>2860</v>
+      </c>
+      <c r="G169" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H169" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" ht="15" spans="1:10">
+      <c r="A170" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D170" s="6" t="n">
+        <v>540</v>
+      </c>
+      <c r="E170" s="7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F170" s="7" t="n">
+        <v>3348</v>
+      </c>
+      <c r="G170" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H170" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="171" customHeight="1" ht="15" spans="1:10">
@@ -4878,22 +4863,22 @@
         <v>14</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C171" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D171" s="6" t="n">
-        <v>300</v>
+        <v>560</v>
       </c>
       <c r="E171" s="7" t="n">
-        <v>11.15</v>
+        <v>7.5</v>
       </c>
       <c r="F171" s="7" t="n">
-        <v>3345</v>
+        <v>4200</v>
       </c>
       <c r="G171" s="8">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="H171" s="6" t="n">
         <v>0</v>
@@ -4902,29 +4887,71 @@
         <v>0</v>
       </c>
       <c r="J171" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="172" customHeight="1" ht="15" spans="1:5">
-      <c r="A172" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B172" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C172" s="11" t="n">
-        <v>3345</v>
-      </c>
-      <c r="D172" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E172" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" customHeight="1" ht="15" spans="1:1">
-      <c r="A173" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" ht="15" spans="1:10">
+      <c r="A172" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B172" s="5" t="s">
         <v>103</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D172" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="E172" s="7" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F172" s="7" t="n">
+        <v>3025</v>
+      </c>
+      <c r="G172" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H172" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" ht="15" spans="1:10">
+      <c r="A173" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D173" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="E173" s="7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F173" s="7" t="n">
+        <v>2255</v>
+      </c>
+      <c r="G173" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H173" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="174" customHeight="1" ht="15" spans="1:10">
@@ -4935,19 +4962,19 @@
         <v>104</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D174" s="6" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="E174" s="7" t="n">
-        <v>5.38</v>
+        <v>5.2</v>
       </c>
       <c r="F174" s="7" t="n">
-        <v>3228</v>
+        <v>2860</v>
       </c>
       <c r="G174" s="8">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="H174" s="6" t="n">
         <v>0</v>
@@ -4956,7 +4983,7 @@
         <v>0</v>
       </c>
       <c r="J174" s="6" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="175" customHeight="1" ht="15" spans="1:10">
@@ -4967,19 +4994,19 @@
         <v>104</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="D175" s="6" t="n">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="E175" s="7" t="n">
-        <v>7.94</v>
+        <v>6.2</v>
       </c>
       <c r="F175" s="7" t="n">
-        <v>4168.5</v>
+        <v>3348</v>
       </c>
       <c r="G175" s="8">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="H175" s="6" t="n">
         <v>0</v>
@@ -4988,7 +5015,7 @@
         <v>0</v>
       </c>
       <c r="J175" s="6" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="176" customHeight="1" ht="15" spans="1:10">
@@ -4999,190 +5026,211 @@
         <v>104</v>
       </c>
       <c r="C176" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D176" s="6" t="n">
+        <v>560</v>
+      </c>
+      <c r="E176" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F176" s="7" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G176" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H176" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177" customHeight="1" ht="15" spans="1:10">
+      <c r="A177" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D177" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="E177" s="7" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F177" s="7" t="n">
+        <v>3025</v>
+      </c>
+      <c r="G177" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H177" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178" customHeight="1" ht="15" spans="1:5">
+      <c r="A178" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B178" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C178" s="11" t="n">
+        <v>31376</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E178" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" customHeight="1" ht="15" spans="1:1">
+      <c r="A179" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" ht="15" spans="1:10">
+      <c r="A180" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D180" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="E180" s="7" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="F180" s="7" t="n">
+        <v>3345</v>
+      </c>
+      <c r="G180" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H180" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" ht="15" spans="1:5">
+      <c r="A181" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B181" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C181" s="11" t="n">
+        <v>3345</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E181" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A182" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" ht="15" spans="1:12">
+      <c r="A183" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H183" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I183" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J183" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K183" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L183" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" ht="15" spans="1:1">
+      <c r="A184" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D176" s="6" t="n">
+    </row>
+    <row r="185" customHeight="1" ht="15" spans="1:10">
+      <c r="A185" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D185" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="E176" s="7" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="F176" s="7" t="n">
-        <v>6180</v>
-      </c>
-      <c r="G176" s="8">
+      <c r="E185" s="7" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="F185" s="7" t="n">
+        <v>3228</v>
+      </c>
+      <c r="G185" s="8">
         <v>46168</v>
       </c>
-      <c r="H176" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J176" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="177" customHeight="1" ht="15" spans="1:5">
-      <c r="A177" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B177" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C177" s="11" t="n">
-        <v>13576.5</v>
-      </c>
-      <c r="D177" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E177" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A178" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" customHeight="1" ht="15" spans="1:12">
-      <c r="A179" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E179" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F179" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G179" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H179" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I179" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J179" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K179" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L179" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="180" customHeight="1" ht="15" spans="1:1">
-      <c r="A180" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="181" customHeight="1" ht="15" spans="1:10">
-      <c r="A181" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D181" s="6" t="n">
-        <v>10200</v>
-      </c>
-      <c r="E181" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F181" s="7" t="n">
-        <v>25500</v>
-      </c>
-      <c r="G181" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H181" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J181" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="182" customHeight="1" ht="15" spans="1:5">
-      <c r="A182" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B182" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C182" s="11" t="n">
-        <v>25500</v>
-      </c>
-      <c r="D182" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E182" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A183" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" customHeight="1" ht="15" spans="1:12">
-      <c r="A184" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E184" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F184" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G184" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H184" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I184" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J184" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K184" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L184" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="185" customHeight="1" ht="15" spans="1:1">
-      <c r="A185" s="2" t="s">
-        <v>111</v>
+      <c r="H185" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="186" customHeight="1" ht="15" spans="1:10">
@@ -5190,225 +5238,246 @@
         <v>14</v>
       </c>
       <c r="B186" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D186" s="6" t="n">
+        <v>525</v>
+      </c>
+      <c r="E186" s="7" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="F186" s="7" t="n">
+        <v>4168.5</v>
+      </c>
+      <c r="G186" s="8">
+        <v>46168</v>
+      </c>
+      <c r="H186" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" ht="15" spans="1:10">
+      <c r="A187" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D187" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="E187" s="7" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F187" s="7" t="n">
+        <v>6180</v>
+      </c>
+      <c r="G187" s="8">
+        <v>46168</v>
+      </c>
+      <c r="H187" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" ht="15" spans="1:5">
+      <c r="A188" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C188" s="11" t="n">
+        <v>13576.5</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E188" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A189" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" ht="15" spans="1:12">
+      <c r="A190" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B190" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C186" s="5" t="s">
+      <c r="C190" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H190" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I190" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J190" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K190" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L190" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" ht="15" spans="1:1">
+      <c r="A191" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D186" s="6" t="n">
+    </row>
+    <row r="192" customHeight="1" ht="15" spans="1:10">
+      <c r="A192" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D192" s="6" t="n">
         <v>200100</v>
       </c>
-      <c r="E186" s="7" t="n">
+      <c r="E192" s="7" t="n">
         <v>4.1</v>
       </c>
-      <c r="F186" s="7" t="n">
+      <c r="F192" s="7" t="n">
         <v>820410</v>
       </c>
-      <c r="G186" s="8">
+      <c r="G192" s="8">
         <v>46119</v>
       </c>
-      <c r="H186" s="6" t="n">
+      <c r="H192" s="6" t="n">
         <v>48900</v>
       </c>
-      <c r="I186" s="9" t="n">
+      <c r="I192" s="9" t="n">
         <v>24.44</v>
       </c>
-      <c r="J186" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="187" customHeight="1" ht="15" spans="1:5">
-      <c r="A187" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B187" s="10" t="s">
+      <c r="J192" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" ht="15" spans="1:5">
+      <c r="A193" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B193" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C187" s="11" t="n">
+      <c r="C193" s="11" t="n">
         <v>820410</v>
       </c>
-      <c r="D187" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E187" s="12" t="n">
+      <c r="D193" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E193" s="12" t="n">
         <v>48900</v>
       </c>
     </row>
-    <row r="188" customHeight="1" ht="15" spans="1:1">
-      <c r="A188" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="189" customHeight="1" ht="15" spans="1:10">
-      <c r="A189" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D189" s="6" t="n">
+    <row r="194" customHeight="1" ht="15" spans="1:1">
+      <c r="A194" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="195" customHeight="1" ht="15" spans="1:10">
+      <c r="A195" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D195" s="6" t="n">
         <v>50100</v>
       </c>
-      <c r="E189" s="7" t="n">
+      <c r="E195" s="7" t="n">
         <v>4.517</v>
       </c>
-      <c r="F189" s="7" t="n">
+      <c r="F195" s="7" t="n">
         <v>226301.7</v>
       </c>
-      <c r="G189" s="8">
+      <c r="G195" s="8">
         <v>46156</v>
       </c>
-      <c r="H189" s="6" t="n">
+      <c r="H195" s="6" t="n">
         <v>13350</v>
       </c>
-      <c r="I189" s="9" t="n">
+      <c r="I195" s="9" t="n">
         <v>26.65</v>
       </c>
-      <c r="J189" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="190" customHeight="1" ht="15" spans="1:10">
-      <c r="A190" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B190" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C190" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D190" s="6" t="n">
+      <c r="J195" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="196" customHeight="1" ht="15" spans="1:10">
+      <c r="A196" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D196" s="6" t="n">
         <v>50100</v>
       </c>
-      <c r="E190" s="7" t="n">
+      <c r="E196" s="7" t="n">
         <v>4.517</v>
       </c>
-      <c r="F190" s="7" t="n">
+      <c r="F196" s="7" t="n">
         <v>226301.7</v>
       </c>
-      <c r="G190" s="8">
+      <c r="G196" s="8">
         <v>46163</v>
       </c>
-      <c r="H190" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I190" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J190" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="191" customHeight="1" ht="15" spans="1:10">
-      <c r="A191" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B191" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D191" s="6" t="n">
-        <v>20100</v>
-      </c>
-      <c r="E191" s="7" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="F191" s="7" t="n">
-        <v>90852</v>
-      </c>
-      <c r="G191" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H191" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I191" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J191" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="192" customHeight="1" ht="15" spans="1:5">
-      <c r="A192" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B192" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C192" s="11" t="n">
-        <v>543455.4</v>
-      </c>
-      <c r="D192" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E192" s="12" t="n">
-        <v>13350</v>
-      </c>
-    </row>
-    <row r="193" customHeight="1" ht="15" spans="1:1">
-      <c r="A193" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="194" customHeight="1" ht="15" spans="1:10">
-      <c r="A194" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B194" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C194" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D194" s="6" t="n">
-        <v>5100</v>
-      </c>
-      <c r="E194" s="7" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="F194" s="7" t="n">
-        <v>25245</v>
-      </c>
-      <c r="G194" s="8">
-        <v>46169</v>
-      </c>
-      <c r="H194" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I194" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J194" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="195" customHeight="1" ht="15" spans="1:5">
-      <c r="A195" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B195" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C195" s="11" t="n">
-        <v>25245</v>
-      </c>
-      <c r="D195" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E195" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" customHeight="1" ht="15" spans="1:1">
-      <c r="A196" s="2" t="s">
-        <v>119</v>
+      <c r="H196" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="197" customHeight="1" ht="15" spans="1:10">
@@ -5416,22 +5485,22 @@
         <v>14</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D197" s="6" t="n">
-        <v>15000</v>
+        <v>20100</v>
       </c>
       <c r="E197" s="7" t="n">
-        <v>2.46</v>
+        <v>4.52</v>
       </c>
       <c r="F197" s="7" t="n">
-        <v>36900</v>
+        <v>90852</v>
       </c>
       <c r="G197" s="8">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="H197" s="6" t="n">
         <v>0</v>
@@ -5440,7 +5509,7 @@
         <v>0</v>
       </c>
       <c r="J197" s="6" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
     </row>
     <row r="198" customHeight="1" ht="15" spans="1:5">
@@ -5451,190 +5520,169 @@
         <v>27</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>36900</v>
+        <v>543455.4</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E198" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A199" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" customHeight="1" ht="15" spans="1:12">
-      <c r="A200" s="2" t="s">
+        <v>13350</v>
+      </c>
+    </row>
+    <row r="199" customHeight="1" ht="15" spans="1:1">
+      <c r="A199" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="200" customHeight="1" ht="15" spans="1:10">
+      <c r="A200" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D200" s="6" t="n">
+        <v>5100</v>
+      </c>
+      <c r="E200" s="7" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="F200" s="7" t="n">
+        <v>25245</v>
+      </c>
+      <c r="G200" s="8">
+        <v>46169</v>
+      </c>
+      <c r="H200" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" ht="15" spans="1:5">
+      <c r="A201" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B201" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C201" s="11" t="n">
+        <v>25245</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E201" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" ht="15" spans="1:1">
+      <c r="A202" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" ht="15" spans="1:10">
+      <c r="A203" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D203" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="E203" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F203" s="7" t="n">
+        <v>2940</v>
+      </c>
+      <c r="G203" s="8">
+        <v>46169</v>
+      </c>
+      <c r="H203" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I203" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" ht="15" spans="1:5">
+      <c r="A204" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C204" s="11" t="n">
+        <v>2940</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E204" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A205" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" ht="15" spans="1:12">
+      <c r="A206" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B200" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C200" s="2" t="s">
+      <c r="B206" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C206" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D200" s="2" t="s">
+      <c r="D206" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E200" s="3" t="s">
+      <c r="E206" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F200" s="3" t="s">
+      <c r="F206" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G200" s="3" t="s">
+      <c r="G206" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H200" s="3" t="s">
+      <c r="H206" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I200" s="3" t="s">
+      <c r="I206" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J200" s="3" t="s">
+      <c r="J206" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K200" s="2" t="s">
+      <c r="K206" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L200" s="3" t="s">
+      <c r="L206" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="201" customHeight="1" ht="15" spans="1:1">
-      <c r="A201" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="202" customHeight="1" ht="15" spans="1:10">
-      <c r="A202" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B202" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C202" s="5" t="s">
+    <row r="207" customHeight="1" ht="15" spans="1:1">
+      <c r="A207" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="D202" s="6" t="n">
-        <v>50100</v>
-      </c>
-      <c r="E202" s="7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F202" s="7" t="n">
-        <v>220440</v>
-      </c>
-      <c r="G202" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H202" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J202" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="203" customHeight="1" ht="15" spans="1:5">
-      <c r="A203" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B203" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C203" s="11" t="n">
-        <v>220440</v>
-      </c>
-      <c r="D203" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E203" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A204" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205" customHeight="1" ht="15" spans="1:12">
-      <c r="A205" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E205" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F205" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G205" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H205" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I205" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J205" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K205" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L205" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="206" customHeight="1" ht="15" spans="1:1">
-      <c r="A206" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="207" customHeight="1" ht="15" spans="1:10">
-      <c r="A207" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B207" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C207" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D207" s="6" t="n">
-        <v>504</v>
-      </c>
-      <c r="E207" s="7" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="F207" s="7" t="n">
-        <v>22629.6</v>
-      </c>
-      <c r="G207" s="8">
-        <v>46141</v>
-      </c>
-      <c r="H207" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I207" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J207" s="6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="208" customHeight="1" ht="15" spans="1:10">
@@ -5642,31 +5690,31 @@
         <v>14</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>23</v>
+        <v>124</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D208" s="6" t="n">
-        <v>3408</v>
+        <v>15000</v>
       </c>
       <c r="E208" s="7" t="n">
-        <v>44.9</v>
+        <v>2.46</v>
       </c>
       <c r="F208" s="7" t="n">
-        <v>153019.2</v>
+        <v>36900</v>
       </c>
       <c r="G208" s="8">
-        <v>46162</v>
+        <v>46168</v>
       </c>
       <c r="H208" s="6" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="I208" s="9" t="n">
-        <v>17.61</v>
+        <v>0</v>
       </c>
       <c r="J208" s="6" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
     </row>
     <row r="209" customHeight="1" ht="15" spans="1:5">
@@ -5677,18 +5725,18 @@
         <v>27</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>175648.8</v>
+        <v>36900</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E209" s="12" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" customHeight="1" ht="15" spans="1:1">
       <c r="A210" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="211" customHeight="1" ht="15" spans="1:10">
@@ -5696,22 +5744,22 @@
         <v>14</v>
       </c>
       <c r="B211" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C211" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C211" s="5" t="s">
-        <v>125</v>
-      </c>
       <c r="D211" s="6" t="n">
-        <v>408</v>
+        <v>50100</v>
       </c>
       <c r="E211" s="7" t="n">
-        <v>45</v>
+        <v>4.4</v>
       </c>
       <c r="F211" s="7" t="n">
-        <v>18360</v>
+        <v>220440</v>
       </c>
       <c r="G211" s="8">
-        <v>46147</v>
+        <v>46164</v>
       </c>
       <c r="H211" s="6" t="n">
         <v>0</v>
@@ -5720,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="J211" s="6" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
     </row>
     <row r="212" customHeight="1" ht="15" spans="1:5">
@@ -5731,7 +5779,7 @@
         <v>27</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>18360</v>
+        <v>220440</v>
       </c>
       <c r="D212" s="3" t="s">
         <v>26</v>
@@ -5740,63 +5788,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" customHeight="1" ht="15" spans="1:1">
-      <c r="A213" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="214" customHeight="1" ht="15" spans="1:10">
-      <c r="A214" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B214" s="5" t="s">
+    <row r="213" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A213" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" customHeight="1" ht="15" spans="1:12">
+      <c r="A214" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B214" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C214" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D214" s="6" t="n">
-        <v>2004</v>
-      </c>
-      <c r="E214" s="7" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="F214" s="7" t="n">
-        <v>93186</v>
-      </c>
-      <c r="G214" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H214" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I214" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J214" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="215" customHeight="1" ht="15" spans="1:5">
-      <c r="A215" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B215" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C215" s="11" t="n">
-        <v>93186</v>
-      </c>
-      <c r="D215" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E215" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" customHeight="1" ht="15" spans="1:1">
-      <c r="A216" s="2" t="s">
+      <c r="C214" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H214" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J214" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K214" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L214" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215" customHeight="1" ht="15" spans="1:1">
+      <c r="A215" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="216" customHeight="1" ht="15" spans="1:10">
+      <c r="A216" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C216" s="5" t="s">
         <v>129</v>
+      </c>
+      <c r="D216" s="6" t="n">
+        <v>504</v>
+      </c>
+      <c r="E216" s="7" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="F216" s="7" t="n">
+        <v>22629.6</v>
+      </c>
+      <c r="G216" s="8">
+        <v>46141</v>
+      </c>
+      <c r="H216" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="217" customHeight="1" ht="15" spans="1:10">
@@ -5804,31 +5873,31 @@
         <v>14</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D217" s="6" t="n">
-        <v>1500</v>
+        <v>3408</v>
       </c>
       <c r="E217" s="7" t="n">
-        <v>21.84</v>
+        <v>44.9</v>
       </c>
       <c r="F217" s="7" t="n">
-        <v>32760</v>
+        <v>153019.2</v>
       </c>
       <c r="G217" s="8">
-        <v>46127</v>
+        <v>46162</v>
       </c>
       <c r="H217" s="6" t="n">
-        <v>768</v>
+        <v>600</v>
       </c>
       <c r="I217" s="9" t="n">
-        <v>51.2</v>
+        <v>17.61</v>
       </c>
       <c r="J217" s="6" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
     </row>
     <row r="218" customHeight="1" ht="15" spans="1:5">
@@ -5839,298 +5908,277 @@
         <v>27</v>
       </c>
       <c r="C218" s="11" t="n">
+        <v>175648.8</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E218" s="12" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" ht="15" spans="1:1">
+      <c r="A219" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" ht="15" spans="1:10">
+      <c r="A220" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D220" s="6" t="n">
+        <v>408</v>
+      </c>
+      <c r="E220" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="F220" s="7" t="n">
+        <v>18360</v>
+      </c>
+      <c r="G220" s="8">
+        <v>46147</v>
+      </c>
+      <c r="H220" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" ht="15" spans="1:5">
+      <c r="A221" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B221" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C221" s="11" t="n">
+        <v>18360</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E221" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" customHeight="1" ht="15" spans="1:1">
+      <c r="A222" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" ht="15" spans="1:10">
+      <c r="A223" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D223" s="6" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E223" s="7" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F223" s="7" t="n">
+        <v>93186</v>
+      </c>
+      <c r="G223" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H223" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="224" customHeight="1" ht="15" spans="1:5">
+      <c r="A224" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B224" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C224" s="11" t="n">
+        <v>93186</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E224" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" customHeight="1" ht="15" spans="1:1">
+      <c r="A225" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="226" customHeight="1" ht="15" spans="1:10">
+      <c r="A226" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D226" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E226" s="7" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="F226" s="7" t="n">
         <v>32760</v>
       </c>
-      <c r="D218" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E218" s="12" t="n">
+      <c r="G226" s="8">
+        <v>46127</v>
+      </c>
+      <c r="H226" s="6" t="n">
         <v>768</v>
       </c>
-    </row>
-    <row r="219" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A219" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" customHeight="1" ht="15" spans="1:12">
-      <c r="A220" s="2" t="s">
+      <c r="I226" s="9" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J226" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="227" customHeight="1" ht="15" spans="1:5">
+      <c r="A227" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B227" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C227" s="11" t="n">
+        <v>32760</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E227" s="12" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="228" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A228" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" ht="15" spans="1:12">
+      <c r="A229" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B220" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C220" s="2" t="s">
+      <c r="B229" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C229" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D220" s="2" t="s">
+      <c r="D229" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E220" s="3" t="s">
+      <c r="E229" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F220" s="3" t="s">
+      <c r="F229" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G220" s="3" t="s">
+      <c r="G229" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H220" s="3" t="s">
+      <c r="H229" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I220" s="3" t="s">
+      <c r="I229" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J220" s="3" t="s">
+      <c r="J229" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K220" s="2" t="s">
+      <c r="K229" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L220" s="3" t="s">
+      <c r="L229" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="221" customHeight="1" ht="15" spans="1:1">
-      <c r="A221" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="222" customHeight="1" ht="15" spans="1:10">
-      <c r="A222" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B222" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C222" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D222" s="6" t="n">
+    <row r="230" customHeight="1" ht="15" spans="1:1">
+      <c r="A230" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="231" customHeight="1" ht="15" spans="1:10">
+      <c r="A231" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D231" s="6" t="n">
         <v>11000</v>
       </c>
-      <c r="E222" s="7" t="n">
+      <c r="E231" s="7" t="n">
         <v>0.4</v>
       </c>
-      <c r="F222" s="7" t="n">
+      <c r="F231" s="7" t="n">
         <v>4400</v>
       </c>
-      <c r="G222" s="8">
+      <c r="G231" s="8">
         <v>46156</v>
       </c>
-      <c r="H222" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I222" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J222" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="223" customHeight="1" ht="15" spans="1:5">
-      <c r="A223" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B223" s="10" t="s">
+      <c r="H231" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I231" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" ht="15" spans="1:5">
+      <c r="A232" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B232" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C223" s="11" t="n">
+      <c r="C232" s="11" t="n">
         <v>4400</v>
       </c>
-      <c r="D223" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E223" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" customHeight="1" ht="15" spans="1:1">
-      <c r="A224" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="225" customHeight="1" ht="15" spans="1:10">
-      <c r="A225" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B225" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D225" s="6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E225" s="7" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F225" s="7" t="n">
-        <v>2640</v>
-      </c>
-      <c r="G225" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H225" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I225" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J225" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="226" customHeight="1" ht="15" spans="1:5">
-      <c r="A226" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B226" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C226" s="11" t="n">
-        <v>2640</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E226" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" customHeight="1" ht="15" spans="1:1">
-      <c r="A227" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="228" customHeight="1" ht="15" spans="1:10">
-      <c r="A228" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B228" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C228" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D228" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E228" s="7" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="F228" s="7" t="n">
-        <v>7900</v>
-      </c>
-      <c r="G228" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H228" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I228" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J228" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="229" customHeight="1" ht="15" spans="1:5">
-      <c r="A229" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B229" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C229" s="11" t="n">
-        <v>7900</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E229" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A230" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" customHeight="1" ht="15" spans="1:12">
-      <c r="A231" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D231" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E231" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F231" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G231" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H231" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I231" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J231" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K231" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L231" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="232" customHeight="1" ht="15" spans="1:1">
-      <c r="A232" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="233" customHeight="1" ht="15" spans="1:10">
-      <c r="A233" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B233" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D233" s="6" t="n">
-        <v>205000</v>
-      </c>
-      <c r="E233" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F233" s="7" t="n">
-        <v>77900</v>
-      </c>
-      <c r="G233" s="8">
-        <v>46168</v>
-      </c>
-      <c r="H233" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I233" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J233" s="6" t="s">
-        <v>17</v>
+      <c r="D232" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E232" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" ht="15" spans="1:1">
+      <c r="A233" s="2" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="234" customHeight="1" ht="15" spans="1:10">
@@ -6138,19 +6186,19 @@
         <v>14</v>
       </c>
       <c r="B234" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C234" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C234" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="D234" s="6" t="n">
-        <v>205000</v>
+        <v>13000</v>
       </c>
       <c r="E234" s="7" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="F234" s="7" t="n">
-        <v>79950</v>
+        <v>5460</v>
       </c>
       <c r="G234" s="8">
         <v>46168</v>
@@ -6162,7 +6210,7 @@
         <v>0</v>
       </c>
       <c r="J234" s="6" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
     </row>
     <row r="235" customHeight="1" ht="15" spans="1:5">
@@ -6173,7 +6221,7 @@
         <v>27</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>157850</v>
+        <v>5460</v>
       </c>
       <c r="D235" s="3" t="s">
         <v>26</v>
@@ -6184,7 +6232,7 @@
     </row>
     <row r="236" customHeight="1" ht="15" spans="1:1">
       <c r="A236" s="2" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
     </row>
     <row r="237" customHeight="1" ht="15" spans="1:10">
@@ -6192,22 +6240,22 @@
         <v>14</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>30000</v>
+        <v>6000</v>
       </c>
       <c r="E237" s="7" t="n">
-        <v>0.415</v>
+        <v>0.44</v>
       </c>
       <c r="F237" s="7" t="n">
-        <v>12450</v>
+        <v>2640</v>
       </c>
       <c r="G237" s="8">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="H237" s="6" t="n">
         <v>0</v>
@@ -6216,7 +6264,7 @@
         <v>0</v>
       </c>
       <c r="J237" s="6" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
     </row>
     <row r="238" customHeight="1" ht="15" spans="1:5">
@@ -6227,7 +6275,7 @@
         <v>27</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>12450</v>
+        <v>2640</v>
       </c>
       <c r="D238" s="3" t="s">
         <v>26</v>
@@ -6238,7 +6286,7 @@
     </row>
     <row r="239" customHeight="1" ht="15" spans="1:1">
       <c r="A239" s="2" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="240" customHeight="1" ht="15" spans="1:10">
@@ -6246,22 +6294,22 @@
         <v>14</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D240" s="6" t="n">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="E240" s="7" t="n">
-        <v>0.216</v>
+        <v>0.395</v>
       </c>
       <c r="F240" s="7" t="n">
-        <v>21600</v>
+        <v>7900</v>
       </c>
       <c r="G240" s="8">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="H240" s="6" t="n">
         <v>0</v>
@@ -6270,7 +6318,7 @@
         <v>0</v>
       </c>
       <c r="J240" s="6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="241" customHeight="1" ht="15" spans="1:5">
@@ -6281,7 +6329,7 @@
         <v>27</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>21600</v>
+        <v>7900</v>
       </c>
       <c r="D241" s="3" t="s">
         <v>26</v>
@@ -6290,106 +6338,106 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" customHeight="1" ht="15" spans="1:1">
-      <c r="A242" s="2" t="s">
+    <row r="242" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A242" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" customHeight="1" ht="15" spans="1:12">
+      <c r="A243" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H243" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I243" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J243" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K243" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L243" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="244" customHeight="1" ht="15" spans="1:1">
+      <c r="A244" s="2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="243" customHeight="1" ht="15" spans="1:10">
-      <c r="A243" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B243" s="5" t="s">
+    <row r="245" customHeight="1" ht="15" spans="1:10">
+      <c r="A245" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B245" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C243" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D243" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E243" s="7" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="F243" s="7" t="n">
-        <v>20750</v>
-      </c>
-      <c r="G243" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H243" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I243" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J243" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="244" customHeight="1" ht="15" spans="1:5">
-      <c r="A244" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B244" s="10" t="s">
+      <c r="C245" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D245" s="6" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E245" s="7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F245" s="7" t="n">
+        <v>9240</v>
+      </c>
+      <c r="G245" s="8">
+        <v>46168</v>
+      </c>
+      <c r="H245" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I245" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="246" customHeight="1" ht="15" spans="1:5">
+      <c r="A246" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B246" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C244" s="11" t="n">
-        <v>20750</v>
-      </c>
-      <c r="D244" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E244" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A245" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246" customHeight="1" ht="15" spans="1:12">
-      <c r="A246" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E246" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F246" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G246" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H246" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I246" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J246" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K246" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L246" s="3" t="s">
-        <v>12</v>
+      <c r="C246" s="11" t="n">
+        <v>9240</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E246" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="247" customHeight="1" ht="15" spans="1:1">
       <c r="A247" s="2" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="248" customHeight="1" ht="15" spans="1:10">
@@ -6397,19 +6445,19 @@
         <v>14</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D248" s="6" t="n">
-        <v>14000</v>
+        <v>205000</v>
       </c>
       <c r="E248" s="7" t="n">
-        <v>0.49</v>
+        <v>0.38</v>
       </c>
       <c r="F248" s="7" t="n">
-        <v>6860</v>
+        <v>77900</v>
       </c>
       <c r="G248" s="8">
         <v>46168</v>
@@ -6421,7 +6469,7 @@
         <v>0</v>
       </c>
       <c r="J248" s="6" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="249" customHeight="1" ht="15" spans="1:10">
@@ -6429,19 +6477,19 @@
         <v>14</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D249" s="6" t="n">
-        <v>16000</v>
+        <v>205000</v>
       </c>
       <c r="E249" s="7" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="F249" s="7" t="n">
-        <v>6720</v>
+        <v>79950</v>
       </c>
       <c r="G249" s="8">
         <v>46168</v>
@@ -6453,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="J249" s="6" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="250" customHeight="1" ht="15" spans="1:5">
@@ -6464,7 +6512,7 @@
         <v>27</v>
       </c>
       <c r="C250" s="11" t="n">
-        <v>13580</v>
+        <v>157850</v>
       </c>
       <c r="D250" s="3" t="s">
         <v>26</v>
@@ -6473,1351 +6521,1804 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A251" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252" customHeight="1" ht="15" spans="1:12">
-      <c r="A252" s="2" t="s">
+    <row r="251" customHeight="1" ht="15" spans="1:1">
+      <c r="A251" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="252" customHeight="1" ht="15" spans="1:10">
+      <c r="A252" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D252" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E252" s="7" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F252" s="7" t="n">
+        <v>12450</v>
+      </c>
+      <c r="G252" s="8">
+        <v>46169</v>
+      </c>
+      <c r="H252" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I252" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="253" customHeight="1" ht="15" spans="1:5">
+      <c r="A253" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B253" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C253" s="11" t="n">
+        <v>12450</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E253" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" customHeight="1" ht="15" spans="1:1">
+      <c r="A254" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="255" customHeight="1" ht="15" spans="1:10">
+      <c r="A255" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D255" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E255" s="7" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="F255" s="7" t="n">
+        <v>21600</v>
+      </c>
+      <c r="G255" s="8">
+        <v>46168</v>
+      </c>
+      <c r="H255" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I255" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="256" customHeight="1" ht="15" spans="1:5">
+      <c r="A256" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B256" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C256" s="11" t="n">
+        <v>21600</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E256" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A257" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" customHeight="1" ht="15" spans="1:12">
+      <c r="A258" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B252" s="2" t="s">
+      <c r="B258" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H258" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I258" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J258" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K258" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L258" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="259" customHeight="1" ht="15" spans="1:1">
+      <c r="A259" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="260" customHeight="1" ht="15" spans="1:10">
+      <c r="A260" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C260" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C252" s="2" t="s">
+      <c r="D260" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E260" s="7" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F260" s="7" t="n">
+        <v>20750</v>
+      </c>
+      <c r="G260" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H260" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I260" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="261" customHeight="1" ht="15" spans="1:5">
+      <c r="A261" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B261" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C261" s="11" t="n">
+        <v>20750</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E261" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" customHeight="1" ht="15" spans="1:1">
+      <c r="A262" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="263" customHeight="1" ht="15" spans="1:10">
+      <c r="A263" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D263" s="6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E263" s="7" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F263" s="7" t="n">
+        <v>5880</v>
+      </c>
+      <c r="G263" s="8">
+        <v>46170</v>
+      </c>
+      <c r="H263" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="264" customHeight="1" ht="15" spans="1:5">
+      <c r="A264" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B264" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C264" s="11" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E264" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" customHeight="1" ht="15" spans="1:1">
+      <c r="A265" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="266" customHeight="1" ht="15" spans="1:10">
+      <c r="A266" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D266" s="6" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E266" s="7" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F266" s="7" t="n">
+        <v>6860</v>
+      </c>
+      <c r="G266" s="8">
+        <v>46168</v>
+      </c>
+      <c r="H266" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="267" customHeight="1" ht="15" spans="1:10">
+      <c r="A267" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D267" s="6" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E267" s="7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F267" s="7" t="n">
+        <v>7040</v>
+      </c>
+      <c r="G267" s="8">
+        <v>46168</v>
+      </c>
+      <c r="H267" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="268" customHeight="1" ht="15" spans="1:5">
+      <c r="A268" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B268" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C268" s="11" t="n">
+        <v>13900</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E268" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A269" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" customHeight="1" ht="15" spans="1:12">
+      <c r="A270" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C270" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D252" s="2" t="s">
+      <c r="D270" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E252" s="3" t="s">
+      <c r="E270" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F252" s="3" t="s">
+      <c r="F270" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G252" s="3" t="s">
+      <c r="G270" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H252" s="3" t="s">
+      <c r="H270" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I252" s="3" t="s">
+      <c r="I270" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J252" s="3" t="s">
+      <c r="J270" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K252" s="2" t="s">
+      <c r="K270" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L252" s="3" t="s">
+      <c r="L270" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="253" customHeight="1" ht="15" spans="1:1">
-      <c r="A253" s="2" t="s">
+    <row r="271" customHeight="1" ht="15" spans="1:1">
+      <c r="A271" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="272" customHeight="1" ht="15" spans="1:10">
+      <c r="A272" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C272" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D272" s="6" t="n">
+        <v>432</v>
+      </c>
+      <c r="E272" s="7" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="F272" s="7" t="n">
+        <v>6670.08</v>
+      </c>
+      <c r="G272" s="8">
+        <v>46170</v>
+      </c>
+      <c r="H272" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I272" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="273" customHeight="1" ht="15" spans="1:5">
+      <c r="A273" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B273" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C273" s="11" t="n">
+        <v>6670.08</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E273" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" customHeight="1" ht="15" spans="1:1">
+      <c r="A274" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="275" customHeight="1" ht="15" spans="1:10">
+      <c r="A275" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D275" s="6" t="n">
+        <v>1512</v>
+      </c>
+      <c r="E275" s="7" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F275" s="7" t="n">
+        <v>19202.4</v>
+      </c>
+      <c r="G275" s="8">
+        <v>46169</v>
+      </c>
+      <c r="H275" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="276" customHeight="1" ht="15" spans="1:5">
+      <c r="A276" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B276" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C276" s="11" t="n">
+        <v>19202.4</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E276" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" customHeight="1" ht="15" spans="1:1">
+      <c r="A277" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="278" customHeight="1" ht="15" spans="1:10">
+      <c r="A278" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D278" s="6" t="n">
+        <v>2160</v>
+      </c>
+      <c r="E278" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F278" s="7" t="n">
+        <v>25920</v>
+      </c>
+      <c r="G278" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H278" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="279" customHeight="1" ht="15" spans="1:5">
+      <c r="A279" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B279" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C279" s="11" t="n">
+        <v>25920</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E279" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" customHeight="1" ht="15" spans="1:1">
+      <c r="A280" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="281" customHeight="1" ht="15" spans="1:10">
+      <c r="A281" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D281" s="6" t="n">
+        <v>1512</v>
+      </c>
+      <c r="E281" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F281" s="7" t="n">
+        <v>19656</v>
+      </c>
+      <c r="G281" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H281" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I281" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="282" customHeight="1" ht="15" spans="1:5">
+      <c r="A282" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B282" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C282" s="11" t="n">
+        <v>19656</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E282" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A283" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" customHeight="1" ht="15" spans="1:12">
+      <c r="A284" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E284" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F284" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G284" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H284" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I284" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J284" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K284" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L284" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="285" customHeight="1" ht="15" spans="1:1">
+      <c r="A285" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="286" customHeight="1" ht="15" spans="1:10">
+      <c r="A286" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D286" s="6" t="n">
+        <v>8028</v>
+      </c>
+      <c r="E286" s="7" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="F286" s="7" t="n">
+        <v>96255.72</v>
+      </c>
+      <c r="G286" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H286" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I286" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="287" customHeight="1" ht="15" spans="1:5">
+      <c r="A287" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B287" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C287" s="11" t="n">
+        <v>96255.72</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E287" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" customHeight="1" ht="15" spans="1:1">
+      <c r="A288" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="289" customHeight="1" ht="15" spans="1:10">
+      <c r="A289" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D289" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E289" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F289" s="7" t="n">
+        <v>312000</v>
+      </c>
+      <c r="G289" s="8">
+        <v>46100</v>
+      </c>
+      <c r="H289" s="6" t="n">
+        <v>18900</v>
+      </c>
+      <c r="I289" s="9" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="J289" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="290" customHeight="1" ht="15" spans="1:5">
+      <c r="A290" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B290" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C290" s="11" t="n">
+        <v>312000</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E290" s="12" t="n">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="291" customHeight="1" ht="15" spans="1:1">
+      <c r="A291" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="292" customHeight="1" ht="15" spans="1:10">
+      <c r="A292" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D292" s="6" t="n">
+        <v>540</v>
+      </c>
+      <c r="E292" s="7" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="F292" s="7" t="n">
+        <v>8278.2</v>
+      </c>
+      <c r="G292" s="8">
+        <v>46168</v>
+      </c>
+      <c r="H292" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I292" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="293" customHeight="1" ht="15" spans="1:5">
+      <c r="A293" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B293" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C293" s="11" t="n">
+        <v>8278.2</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E293" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" customHeight="1" ht="15" spans="1:1">
+      <c r="A294" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="295" customHeight="1" ht="15" spans="1:10">
+      <c r="A295" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D295" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="E295" s="7" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="F295" s="7" t="n">
+        <v>4174.8</v>
+      </c>
+      <c r="G295" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H295" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I295" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J295" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="296" customHeight="1" ht="15" spans="1:5">
+      <c r="A296" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B296" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C296" s="11" t="n">
+        <v>4174.8</v>
+      </c>
+      <c r="D296" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E296" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A297" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" customHeight="1" ht="15" spans="1:12">
+      <c r="A298" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E298" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F298" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G298" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H298" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I298" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J298" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K298" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L298" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="299" customHeight="1" ht="15" spans="1:1">
+      <c r="A299" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="254" customHeight="1" ht="15" spans="1:10">
-      <c r="A254" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B254" s="5" t="s">
+    <row r="300" customHeight="1" ht="15" spans="1:10">
+      <c r="A300" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B300" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C254" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D254" s="6" t="n">
-        <v>2160</v>
-      </c>
-      <c r="E254" s="7" t="n">
+      <c r="C300" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D300" s="6" t="n">
+        <v>320</v>
+      </c>
+      <c r="E300" s="7" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="F300" s="7" t="n">
+        <v>5040</v>
+      </c>
+      <c r="G300" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H300" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I300" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="301" customHeight="1" ht="15" spans="1:5">
+      <c r="A301" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B301" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C301" s="11" t="n">
+        <v>5040</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E301" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" customHeight="1" ht="15" spans="1:1">
+      <c r="A302" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="303" customHeight="1" ht="15" spans="1:10">
+      <c r="A303" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D303" s="6" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E303" s="7" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="F303" s="7" t="n">
+        <v>33425.28</v>
+      </c>
+      <c r="G303" s="8">
+        <v>46162</v>
+      </c>
+      <c r="H303" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I303" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J303" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="304" customHeight="1" ht="15" spans="1:5">
+      <c r="A304" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B304" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C304" s="11" t="n">
+        <v>33425.28</v>
+      </c>
+      <c r="D304" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E304" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" customHeight="1" ht="15" spans="1:1">
+      <c r="A305" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="306" customHeight="1" ht="15" spans="1:10">
+      <c r="A306" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C306" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D306" s="6" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E306" s="7" t="n">
+        <v>9.8</v>
+      </c>
+      <c r="F306" s="7" t="n">
+        <v>9996</v>
+      </c>
+      <c r="G306" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H306" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I306" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="307" customHeight="1" ht="15" spans="1:10">
+      <c r="A307" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D307" s="6" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E307" s="7" t="n">
+        <v>9.8</v>
+      </c>
+      <c r="F307" s="7" t="n">
+        <v>9996</v>
+      </c>
+      <c r="G307" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H307" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I307" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J307" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="308" customHeight="1" ht="15" spans="1:5">
+      <c r="A308" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B308" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C308" s="11" t="n">
+        <v>19992</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E308" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A309" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" customHeight="1" ht="15" spans="1:12">
+      <c r="A310" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C310" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E310" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F310" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G310" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H310" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I310" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J310" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K310" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L310" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F254" s="7" t="n">
-        <v>25920</v>
-      </c>
-      <c r="G254" s="8">
+    </row>
+    <row r="311" customHeight="1" ht="15" spans="1:1">
+      <c r="A311" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="312" customHeight="1" ht="15" spans="1:10">
+      <c r="A312" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C312" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D312" s="6" t="n">
+        <v>4032</v>
+      </c>
+      <c r="E312" s="7" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F312" s="7" t="n">
+        <v>28183.68</v>
+      </c>
+      <c r="G312" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H312" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I312" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J312" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="313" customHeight="1" ht="15" spans="1:5">
+      <c r="A313" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B313" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C313" s="11" t="n">
+        <v>28183.68</v>
+      </c>
+      <c r="D313" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E313" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" customHeight="1" ht="15" spans="1:1">
+      <c r="A314" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="315" customHeight="1" ht="15" spans="1:10">
+      <c r="A315" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D315" s="6" t="n">
+        <v>320</v>
+      </c>
+      <c r="E315" s="7" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="F315" s="7" t="n">
+        <v>5360</v>
+      </c>
+      <c r="G315" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H315" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I315" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="316" customHeight="1" ht="15" spans="1:5">
+      <c r="A316" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B316" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C316" s="11" t="n">
+        <v>5360</v>
+      </c>
+      <c r="D316" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E316" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" customHeight="1" ht="15" spans="1:1">
+      <c r="A317" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="318" customHeight="1" ht="15" spans="1:10">
+      <c r="A318" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D318" s="6" t="n">
+        <v>512</v>
+      </c>
+      <c r="E318" s="7" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="F318" s="7" t="n">
+        <v>9154.56</v>
+      </c>
+      <c r="G318" s="8">
+        <v>46169</v>
+      </c>
+      <c r="H318" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I318" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="319" customHeight="1" ht="15" spans="1:5">
+      <c r="A319" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B319" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C319" s="11" t="n">
+        <v>9154.56</v>
+      </c>
+      <c r="D319" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E319" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" customHeight="1" ht="15" spans="1:1">
+      <c r="A320" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="321" customHeight="1" ht="15" spans="1:10">
+      <c r="A321" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D321" s="6" t="n">
+        <v>714</v>
+      </c>
+      <c r="E321" s="7" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="F321" s="7" t="n">
+        <v>16921.8</v>
+      </c>
+      <c r="G321" s="8">
+        <v>46169</v>
+      </c>
+      <c r="H321" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I321" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="322" customHeight="1" ht="15" spans="1:5">
+      <c r="A322" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B322" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C322" s="11" t="n">
+        <v>16921.8</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E322" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A323" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" customHeight="1" ht="15" spans="1:12">
+      <c r="A324" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E324" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F324" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G324" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H324" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I324" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J324" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K324" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L324" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="325" customHeight="1" ht="15" spans="1:1">
+      <c r="A325" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="326" customHeight="1" ht="15" spans="1:10">
+      <c r="A326" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C326" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D326" s="6" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E326" s="7" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F326" s="7" t="n">
+        <v>7045.92</v>
+      </c>
+      <c r="G326" s="8">
+        <v>46169</v>
+      </c>
+      <c r="H326" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I326" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="327" customHeight="1" ht="15" spans="1:5">
+      <c r="A327" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B327" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C327" s="11" t="n">
+        <v>7045.92</v>
+      </c>
+      <c r="D327" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E327" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" customHeight="1" ht="15" spans="1:1">
+      <c r="A328" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="329" customHeight="1" ht="15" spans="1:10">
+      <c r="A329" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B329" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D329" s="6" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E329" s="7" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F329" s="7" t="n">
+        <v>14091.84</v>
+      </c>
+      <c r="G329" s="8">
         <v>46164</v>
       </c>
-      <c r="H254" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I254" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J254" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="255" customHeight="1" ht="15" spans="1:5">
-      <c r="A255" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B255" s="10" t="s">
+      <c r="H329" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I329" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J329" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="330" customHeight="1" ht="15" spans="1:5">
+      <c r="A330" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B330" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C255" s="11" t="n">
-        <v>25920</v>
-      </c>
-      <c r="D255" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E255" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" customHeight="1" ht="15" spans="1:1">
-      <c r="A256" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="257" customHeight="1" ht="15" spans="1:10">
-      <c r="A257" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B257" s="5" t="s">
+      <c r="C330" s="11" t="n">
+        <v>14091.84</v>
+      </c>
+      <c r="D330" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E330" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" customHeight="1" ht="15" spans="1:1">
+      <c r="A331" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="332" customHeight="1" ht="15" spans="1:10">
+      <c r="A332" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B332" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C332" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D332" s="6" t="n">
+        <v>520</v>
+      </c>
+      <c r="E332" s="7" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="F332" s="7" t="n">
+        <v>7519.2</v>
+      </c>
+      <c r="G332" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H332" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I332" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J332" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="333" customHeight="1" ht="15" spans="1:5">
+      <c r="A333" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B333" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C333" s="11" t="n">
+        <v>7519.2</v>
+      </c>
+      <c r="D333" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E333" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" customHeight="1" ht="15" spans="1:1">
+      <c r="A334" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="335" customHeight="1" ht="15" spans="1:10">
+      <c r="A335" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B335" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C335" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D335" s="6" t="n">
+        <v>648</v>
+      </c>
+      <c r="E335" s="7" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="F335" s="7" t="n">
+        <v>4847.04</v>
+      </c>
+      <c r="G335" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H335" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I335" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J335" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="336" customHeight="1" ht="15" spans="1:5">
+      <c r="A336" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B336" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C336" s="11" t="n">
+        <v>4847.04</v>
+      </c>
+      <c r="D336" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E336" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" customHeight="1" ht="15" spans="1:1">
+      <c r="A337" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C257" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D257" s="6" t="n">
+    </row>
+    <row r="338" customHeight="1" ht="15" spans="1:10">
+      <c r="A338" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B338" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C338" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D338" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E338" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F338" s="7" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G338" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H338" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I338" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J338" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="339" customHeight="1" ht="15" spans="1:5">
+      <c r="A339" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B339" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C339" s="11" t="n">
+        <v>10500</v>
+      </c>
+      <c r="D339" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E339" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A340" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" customHeight="1" ht="15" spans="1:12">
+      <c r="A341" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C341" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E341" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F341" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G341" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H341" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I341" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J341" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K341" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L341" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="342" customHeight="1" ht="15" spans="1:1">
+      <c r="A342" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="343" customHeight="1" ht="15" spans="1:10">
+      <c r="A343" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C343" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D343" s="6" t="n">
         <v>1512</v>
       </c>
-      <c r="E257" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="F257" s="7" t="n">
-        <v>19656</v>
-      </c>
-      <c r="G257" s="8">
+      <c r="E343" s="7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F343" s="7" t="n">
+        <v>10281.6</v>
+      </c>
+      <c r="G343" s="8">
         <v>46164</v>
       </c>
-      <c r="H257" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I257" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J257" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="258" customHeight="1" ht="15" spans="1:5">
-      <c r="A258" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B258" s="10" t="s">
+      <c r="H343" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I343" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="344" customHeight="1" ht="15" spans="1:10">
+      <c r="A344" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C344" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D344" s="6" t="n">
+        <v>1512</v>
+      </c>
+      <c r="E344" s="7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F344" s="7" t="n">
+        <v>10281.6</v>
+      </c>
+      <c r="G344" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H344" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I344" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J344" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="345" customHeight="1" ht="15" spans="1:5">
+      <c r="A345" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B345" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C258" s="11" t="n">
-        <v>19656</v>
-      </c>
-      <c r="D258" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E258" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A259" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260" customHeight="1" ht="15" spans="1:12">
-      <c r="A260" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D260" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E260" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F260" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G260" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H260" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I260" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J260" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K260" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L260" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="261" customHeight="1" ht="15" spans="1:1">
-      <c r="A261" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="262" customHeight="1" ht="15" spans="1:10">
-      <c r="A262" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B262" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C262" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D262" s="6" t="n">
-        <v>8028</v>
-      </c>
-      <c r="E262" s="7" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="F262" s="7" t="n">
-        <v>96255.72</v>
-      </c>
-      <c r="G262" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H262" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I262" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J262" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="263" customHeight="1" ht="15" spans="1:5">
-      <c r="A263" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B263" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C263" s="11" t="n">
-        <v>96255.72</v>
-      </c>
-      <c r="D263" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E263" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" customHeight="1" ht="15" spans="1:1">
-      <c r="A264" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="265" customHeight="1" ht="15" spans="1:10">
-      <c r="A265" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B265" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C265" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D265" s="6" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E265" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="F265" s="7" t="n">
-        <v>312000</v>
-      </c>
-      <c r="G265" s="8">
-        <v>46100</v>
-      </c>
-      <c r="H265" s="6" t="n">
-        <v>18900</v>
-      </c>
-      <c r="I265" s="9" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="J265" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="266" customHeight="1" ht="15" spans="1:5">
-      <c r="A266" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B266" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C266" s="11" t="n">
-        <v>312000</v>
-      </c>
-      <c r="D266" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E266" s="12" t="n">
-        <v>18900</v>
-      </c>
-    </row>
-    <row r="267" customHeight="1" ht="15" spans="1:1">
-      <c r="A267" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="268" customHeight="1" ht="15" spans="1:10">
-      <c r="A268" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B268" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C268" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D268" s="6" t="n">
-        <v>540</v>
-      </c>
-      <c r="E268" s="7" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="F268" s="7" t="n">
-        <v>8278.2</v>
-      </c>
-      <c r="G268" s="8">
-        <v>46168</v>
-      </c>
-      <c r="H268" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I268" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J268" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="269" customHeight="1" ht="15" spans="1:5">
-      <c r="A269" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B269" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C269" s="11" t="n">
-        <v>8278.2</v>
-      </c>
-      <c r="D269" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E269" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" customHeight="1" ht="15" spans="1:1">
-      <c r="A270" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="271" customHeight="1" ht="15" spans="1:10">
-      <c r="A271" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B271" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C271" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D271" s="6" t="n">
-        <v>210</v>
-      </c>
-      <c r="E271" s="7" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="F271" s="7" t="n">
-        <v>4174.8</v>
-      </c>
-      <c r="G271" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H271" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I271" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J271" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="272" customHeight="1" ht="15" spans="1:5">
-      <c r="A272" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B272" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C272" s="11" t="n">
-        <v>4174.8</v>
-      </c>
-      <c r="D272" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E272" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A273" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274" customHeight="1" ht="15" spans="1:12">
-      <c r="A274" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D274" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E274" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F274" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G274" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H274" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I274" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J274" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K274" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L274" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="275" customHeight="1" ht="15" spans="1:1">
-      <c r="A275" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="276" customHeight="1" ht="15" spans="1:10">
-      <c r="A276" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B276" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C276" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D276" s="6" t="n">
-        <v>320</v>
-      </c>
-      <c r="E276" s="7" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="F276" s="7" t="n">
-        <v>5040</v>
-      </c>
-      <c r="G276" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H276" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I276" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J276" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="277" customHeight="1" ht="15" spans="1:5">
-      <c r="A277" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B277" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C277" s="11" t="n">
-        <v>5040</v>
-      </c>
-      <c r="D277" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E277" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278" customHeight="1" ht="15" spans="1:1">
-      <c r="A278" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="279" customHeight="1" ht="15" spans="1:10">
-      <c r="A279" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B279" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C279" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D279" s="6" t="n">
-        <v>2016</v>
-      </c>
-      <c r="E279" s="7" t="n">
-        <v>16.58</v>
-      </c>
-      <c r="F279" s="7" t="n">
-        <v>33425.28</v>
-      </c>
-      <c r="G279" s="8">
-        <v>46162</v>
-      </c>
-      <c r="H279" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I279" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J279" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="280" customHeight="1" ht="15" spans="1:5">
-      <c r="A280" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B280" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C280" s="11" t="n">
-        <v>33425.28</v>
-      </c>
-      <c r="D280" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E280" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281" customHeight="1" ht="15" spans="1:1">
-      <c r="A281" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="282" customHeight="1" ht="15" spans="1:10">
-      <c r="A282" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B282" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C282" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D282" s="6" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E282" s="7" t="n">
-        <v>9.8</v>
-      </c>
-      <c r="F282" s="7" t="n">
-        <v>9996</v>
-      </c>
-      <c r="G282" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H282" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I282" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J282" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="283" customHeight="1" ht="15" spans="1:10">
-      <c r="A283" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B283" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C283" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D283" s="6" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E283" s="7" t="n">
-        <v>9.8</v>
-      </c>
-      <c r="F283" s="7" t="n">
-        <v>9996</v>
-      </c>
-      <c r="G283" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H283" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I283" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J283" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="284" customHeight="1" ht="15" spans="1:5">
-      <c r="A284" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B284" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C284" s="11" t="n">
-        <v>19992</v>
-      </c>
-      <c r="D284" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E284" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A285" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286" customHeight="1" ht="15" spans="1:12">
-      <c r="A286" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D286" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E286" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F286" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G286" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H286" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I286" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J286" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K286" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L286" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="287" customHeight="1" ht="15" spans="1:1">
-      <c r="A287" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="288" customHeight="1" ht="15" spans="1:10">
-      <c r="A288" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B288" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C288" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D288" s="6" t="n">
-        <v>4032</v>
-      </c>
-      <c r="E288" s="7" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F288" s="7" t="n">
-        <v>28183.68</v>
-      </c>
-      <c r="G288" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H288" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I288" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J288" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="289" customHeight="1" ht="15" spans="1:5">
-      <c r="A289" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B289" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C289" s="11" t="n">
-        <v>28183.68</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E289" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290" customHeight="1" ht="15" spans="1:1">
-      <c r="A290" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="291" customHeight="1" ht="15" spans="1:10">
-      <c r="A291" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B291" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C291" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D291" s="6" t="n">
-        <v>320</v>
-      </c>
-      <c r="E291" s="7" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="F291" s="7" t="n">
-        <v>5360</v>
-      </c>
-      <c r="G291" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H291" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I291" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J291" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="292" customHeight="1" ht="15" spans="1:5">
-      <c r="A292" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B292" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C292" s="11" t="n">
-        <v>5360</v>
-      </c>
-      <c r="D292" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E292" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" customHeight="1" ht="15" spans="1:1">
-      <c r="A293" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="294" customHeight="1" ht="15" spans="1:10">
-      <c r="A294" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B294" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C294" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D294" s="6" t="n">
-        <v>512</v>
-      </c>
-      <c r="E294" s="7" t="n">
-        <v>17.88</v>
-      </c>
-      <c r="F294" s="7" t="n">
-        <v>9154.56</v>
-      </c>
-      <c r="G294" s="8">
-        <v>46169</v>
-      </c>
-      <c r="H294" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I294" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J294" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="295" customHeight="1" ht="15" spans="1:5">
-      <c r="A295" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B295" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C295" s="11" t="n">
-        <v>9154.56</v>
-      </c>
-      <c r="D295" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E295" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296" customHeight="1" ht="15" spans="1:1">
-      <c r="A296" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="297" customHeight="1" ht="15" spans="1:10">
-      <c r="A297" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B297" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C297" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D297" s="6" t="n">
-        <v>714</v>
-      </c>
-      <c r="E297" s="7" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="F297" s="7" t="n">
-        <v>16921.8</v>
-      </c>
-      <c r="G297" s="8">
-        <v>46169</v>
-      </c>
-      <c r="H297" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I297" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J297" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="298" customHeight="1" ht="15" spans="1:5">
-      <c r="A298" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B298" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C298" s="11" t="n">
-        <v>16921.8</v>
-      </c>
-      <c r="D298" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E298" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A299" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" customHeight="1" ht="15" spans="1:12">
-      <c r="A300" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D300" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E300" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F300" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G300" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H300" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I300" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J300" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K300" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L300" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="301" customHeight="1" ht="15" spans="1:1">
-      <c r="A301" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="302" customHeight="1" ht="15" spans="1:10">
-      <c r="A302" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B302" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C302" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D302" s="6" t="n">
-        <v>1008</v>
-      </c>
-      <c r="E302" s="7" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F302" s="7" t="n">
-        <v>7045.92</v>
-      </c>
-      <c r="G302" s="8">
-        <v>46169</v>
-      </c>
-      <c r="H302" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I302" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J302" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="303" customHeight="1" ht="15" spans="1:5">
-      <c r="A303" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B303" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C303" s="11" t="n">
-        <v>7045.92</v>
-      </c>
-      <c r="D303" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E303" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304" customHeight="1" ht="15" spans="1:1">
-      <c r="A304" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="305" customHeight="1" ht="15" spans="1:10">
-      <c r="A305" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B305" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C305" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D305" s="6" t="n">
-        <v>2016</v>
-      </c>
-      <c r="E305" s="7" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F305" s="7" t="n">
-        <v>14091.84</v>
-      </c>
-      <c r="G305" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H305" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I305" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J305" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="306" customHeight="1" ht="15" spans="1:5">
-      <c r="A306" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B306" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C306" s="11" t="n">
-        <v>14091.84</v>
-      </c>
-      <c r="D306" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E306" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307" customHeight="1" ht="15" spans="1:1">
-      <c r="A307" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="308" customHeight="1" ht="15" spans="1:10">
-      <c r="A308" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B308" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C308" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D308" s="6" t="n">
-        <v>520</v>
-      </c>
-      <c r="E308" s="7" t="n">
-        <v>14.46</v>
-      </c>
-      <c r="F308" s="7" t="n">
-        <v>7519.2</v>
-      </c>
-      <c r="G308" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H308" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I308" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J308" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="309" customHeight="1" ht="15" spans="1:5">
-      <c r="A309" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B309" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C309" s="11" t="n">
-        <v>7519.2</v>
-      </c>
-      <c r="D309" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E309" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" customHeight="1" ht="15" spans="1:1">
-      <c r="A310" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="311" customHeight="1" ht="15" spans="1:10">
-      <c r="A311" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B311" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C311" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D311" s="6" t="n">
-        <v>648</v>
-      </c>
-      <c r="E311" s="7" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="F311" s="7" t="n">
-        <v>4847.04</v>
-      </c>
-      <c r="G311" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H311" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I311" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J311" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="312" customHeight="1" ht="15" spans="1:5">
-      <c r="A312" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B312" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C312" s="11" t="n">
-        <v>4847.04</v>
-      </c>
-      <c r="D312" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E312" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313" customHeight="1" ht="15" spans="1:1">
-      <c r="A313" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="314" customHeight="1" ht="15" spans="1:10">
-      <c r="A314" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B314" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C314" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D314" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E314" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="F314" s="7" t="n">
-        <v>10500</v>
-      </c>
-      <c r="G314" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H314" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I314" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J314" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="315" customHeight="1" ht="15" spans="1:5">
-      <c r="A315" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B315" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C315" s="11" t="n">
-        <v>10500</v>
-      </c>
-      <c r="D315" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E315" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A316" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317" customHeight="1" ht="15" spans="1:12">
-      <c r="A317" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C317" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D317" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E317" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F317" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G317" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H317" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I317" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J317" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K317" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L317" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="318" customHeight="1" ht="15" spans="1:1">
-      <c r="A318" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="319" customHeight="1" ht="15" spans="1:10">
-      <c r="A319" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B319" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C319" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D319" s="6" t="n">
-        <v>1512</v>
-      </c>
-      <c r="E319" s="7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F319" s="7" t="n">
-        <v>10281.6</v>
-      </c>
-      <c r="G319" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H319" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I319" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J319" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="320" customHeight="1" ht="15" spans="1:10">
-      <c r="A320" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B320" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C320" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D320" s="6" t="n">
-        <v>1512</v>
-      </c>
-      <c r="E320" s="7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F320" s="7" t="n">
-        <v>10281.6</v>
-      </c>
-      <c r="G320" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H320" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I320" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J320" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="321" customHeight="1" ht="15" spans="1:5">
-      <c r="A321" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B321" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C321" s="11" t="n">
+      <c r="C345" s="11" t="n">
         <v>20563.2</v>
       </c>
-      <c r="D321" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E321" s="12" t="n">
+      <c r="D345" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E345" s="12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,9 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="180">
-  <si>
-    <t>MATRIZ CNPJ: 40.357.820/0001-50 R Y DOIS - 58082-025 ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="182">
+  <si>
+    <t>MATRIZ CNPJ: 40.357.820/0001-50R Y DOIS - 58082-025
+ ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
   </si>
   <si>
     <t>Subgrupo:</t>
@@ -407,6 +408,12 @@
   </si>
   <si>
     <t>836</t>
+  </si>
+  <si>
+    <t>EMBRAESTER</t>
+  </si>
+  <si>
+    <t>893</t>
   </si>
   <si>
     <t>895</t>
@@ -709,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L345"/>
+  <dimension ref="A1:L350"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
   <cols>
     <col customWidth="1" width="89.23828125" min="1" max="1"/>
@@ -5973,7 +5980,7 @@
     </row>
     <row r="222" customHeight="1" ht="15" spans="1:1">
       <c r="A222" s="2" t="s">
-        <v>34</v>
+        <v>132</v>
       </c>
     </row>
     <row r="223" customHeight="1" ht="15" spans="1:10">
@@ -5981,19 +5988,19 @@
         <v>14</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C223" s="5" t="s">
         <v>129</v>
       </c>
       <c r="D223" s="6" t="n">
-        <v>2004</v>
+        <v>24</v>
       </c>
       <c r="E223" s="7" t="n">
-        <v>46.5</v>
+        <v>49.5</v>
       </c>
       <c r="F223" s="7" t="n">
-        <v>93186</v>
+        <v>1188</v>
       </c>
       <c r="G223" s="8">
         <v>46164</v>
@@ -6005,7 +6012,7 @@
         <v>0</v>
       </c>
       <c r="J223" s="6" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="224" customHeight="1" ht="15" spans="1:5">
@@ -6016,7 +6023,7 @@
         <v>27</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>93186</v>
+        <v>1188</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>26</v>
@@ -6027,7 +6034,7 @@
     </row>
     <row r="225" customHeight="1" ht="15" spans="1:1">
       <c r="A225" s="2" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
     </row>
     <row r="226" customHeight="1" ht="15" spans="1:10">
@@ -6041,25 +6048,25 @@
         <v>129</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>1500</v>
+        <v>2004</v>
       </c>
       <c r="E226" s="7" t="n">
-        <v>21.84</v>
+        <v>46.5</v>
       </c>
       <c r="F226" s="7" t="n">
-        <v>32760</v>
+        <v>93186</v>
       </c>
       <c r="G226" s="8">
-        <v>46127</v>
+        <v>46164</v>
       </c>
       <c r="H226" s="6" t="n">
-        <v>768</v>
+        <v>0</v>
       </c>
       <c r="I226" s="9" t="n">
-        <v>51.2</v>
+        <v>0</v>
       </c>
       <c r="J226" s="6" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
     </row>
     <row r="227" customHeight="1" ht="15" spans="1:5">
@@ -6070,13 +6077,13 @@
         <v>27</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>32760</v>
+        <v>93186</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E227" s="12" t="n">
-        <v>768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228" customHeight="1" ht="77.35" spans="1:1">
@@ -6089,7 +6096,7 @@
         <v>1</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>3</v>
@@ -6124,7 +6131,7 @@
     </row>
     <row r="230" customHeight="1" ht="15" spans="1:1">
       <c r="A230" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="231" customHeight="1" ht="15" spans="1:10">
@@ -6135,25 +6142,25 @@
         <v>136</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>11000</v>
+        <v>1500</v>
       </c>
       <c r="E231" s="7" t="n">
-        <v>0.4</v>
+        <v>21.84</v>
       </c>
       <c r="F231" s="7" t="n">
-        <v>4400</v>
+        <v>32760</v>
       </c>
       <c r="G231" s="8">
-        <v>46156</v>
+        <v>46127</v>
       </c>
       <c r="H231" s="6" t="n">
-        <v>0</v>
+        <v>768</v>
       </c>
       <c r="I231" s="9" t="n">
-        <v>0</v>
+        <v>51.2</v>
       </c>
       <c r="J231" s="6" t="s">
         <v>85</v>
@@ -6167,223 +6174,223 @@
         <v>27</v>
       </c>
       <c r="C232" s="11" t="n">
+        <v>32760</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E232" s="12" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A233" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" ht="15" spans="1:12">
+      <c r="A234" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H234" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I234" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J234" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K234" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L234" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" ht="15" spans="1:1">
+      <c r="A235" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="236" customHeight="1" ht="15" spans="1:10">
+      <c r="A236" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D236" s="6" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E236" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F236" s="7" t="n">
         <v>4400</v>
       </c>
-      <c r="D232" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E232" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" customHeight="1" ht="15" spans="1:1">
-      <c r="A233" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="234" customHeight="1" ht="15" spans="1:10">
-      <c r="A234" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B234" s="5" t="s">
+      <c r="G236" s="8">
+        <v>46156</v>
+      </c>
+      <c r="H236" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I236" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="237" customHeight="1" ht="15" spans="1:5">
+      <c r="A237" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B237" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C237" s="11" t="n">
+        <v>4400</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E237" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" customHeight="1" ht="15" spans="1:1">
+      <c r="A238" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="239" customHeight="1" ht="15" spans="1:10">
+      <c r="A239" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C239" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C234" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D234" s="6" t="n">
+      <c r="D239" s="6" t="n">
         <v>13000</v>
       </c>
-      <c r="E234" s="7" t="n">
+      <c r="E239" s="7" t="n">
         <v>0.42</v>
       </c>
-      <c r="F234" s="7" t="n">
+      <c r="F239" s="7" t="n">
         <v>5460</v>
       </c>
-      <c r="G234" s="8">
+      <c r="G239" s="8">
         <v>46168</v>
       </c>
-      <c r="H234" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I234" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J234" s="6" t="s">
+      <c r="H239" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I239" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="235" customHeight="1" ht="15" spans="1:5">
-      <c r="A235" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B235" s="10" t="s">
+    <row r="240" customHeight="1" ht="15" spans="1:5">
+      <c r="A240" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B240" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C235" s="11" t="n">
+      <c r="C240" s="11" t="n">
         <v>5460</v>
       </c>
-      <c r="D235" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E235" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" customHeight="1" ht="15" spans="1:1">
-      <c r="A236" s="2" t="s">
+      <c r="D240" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E240" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" customHeight="1" ht="15" spans="1:1">
+      <c r="A241" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="237" customHeight="1" ht="15" spans="1:10">
-      <c r="A237" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B237" s="5" t="s">
+    <row r="242" customHeight="1" ht="15" spans="1:10">
+      <c r="A242" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B242" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C237" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D237" s="6" t="n">
+      <c r="C242" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D242" s="6" t="n">
         <v>6000</v>
       </c>
-      <c r="E237" s="7" t="n">
+      <c r="E242" s="7" t="n">
         <v>0.44</v>
       </c>
-      <c r="F237" s="7" t="n">
+      <c r="F242" s="7" t="n">
         <v>2640</v>
       </c>
-      <c r="G237" s="8">
+      <c r="G242" s="8">
         <v>46164</v>
       </c>
-      <c r="H237" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I237" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J237" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="238" customHeight="1" ht="15" spans="1:5">
-      <c r="A238" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B238" s="10" t="s">
+      <c r="H242" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I242" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="243" customHeight="1" ht="15" spans="1:5">
+      <c r="A243" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B243" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C238" s="11" t="n">
+      <c r="C243" s="11" t="n">
         <v>2640</v>
       </c>
-      <c r="D238" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E238" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" customHeight="1" ht="15" spans="1:1">
-      <c r="A239" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="240" customHeight="1" ht="15" spans="1:10">
-      <c r="A240" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B240" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C240" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D240" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E240" s="7" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="F240" s="7" t="n">
-        <v>7900</v>
-      </c>
-      <c r="G240" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H240" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I240" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J240" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="241" customHeight="1" ht="15" spans="1:5">
-      <c r="A241" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B241" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C241" s="11" t="n">
-        <v>7900</v>
-      </c>
-      <c r="D241" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E241" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A242" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" customHeight="1" ht="15" spans="1:12">
-      <c r="A243" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D243" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E243" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F243" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G243" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H243" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I243" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J243" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K243" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L243" s="3" t="s">
-        <v>12</v>
+      <c r="D243" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E243" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="244" customHeight="1" ht="15" spans="1:1">
       <c r="A244" s="2" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
     </row>
     <row r="245" customHeight="1" ht="15" spans="1:10">
@@ -6391,22 +6398,22 @@
         <v>14</v>
       </c>
       <c r="B245" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C245" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C245" s="5" t="s">
-        <v>141</v>
-      </c>
       <c r="D245" s="6" t="n">
-        <v>21000</v>
+        <v>20000</v>
       </c>
       <c r="E245" s="7" t="n">
-        <v>0.44</v>
+        <v>0.395</v>
       </c>
       <c r="F245" s="7" t="n">
-        <v>9240</v>
+        <v>7900</v>
       </c>
       <c r="G245" s="8">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="H245" s="6" t="n">
         <v>0</v>
@@ -6415,7 +6422,7 @@
         <v>0</v>
       </c>
       <c r="J245" s="6" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="246" customHeight="1" ht="15" spans="1:5">
@@ -6426,255 +6433,255 @@
         <v>27</v>
       </c>
       <c r="C246" s="11" t="n">
+        <v>7900</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E246" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A247" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" customHeight="1" ht="15" spans="1:12">
+      <c r="A248" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H248" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I248" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J248" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K248" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L248" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="249" customHeight="1" ht="15" spans="1:1">
+      <c r="A249" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="250" customHeight="1" ht="15" spans="1:10">
+      <c r="A250" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D250" s="6" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E250" s="7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F250" s="7" t="n">
         <v>9240</v>
       </c>
-      <c r="D246" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E246" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247" customHeight="1" ht="15" spans="1:1">
-      <c r="A247" s="2" t="s">
+      <c r="G250" s="8">
+        <v>46168</v>
+      </c>
+      <c r="H250" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I250" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="251" customHeight="1" ht="15" spans="1:5">
+      <c r="A251" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B251" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C251" s="11" t="n">
+        <v>9240</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E251" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" customHeight="1" ht="15" spans="1:1">
+      <c r="A252" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="248" customHeight="1" ht="15" spans="1:10">
-      <c r="A248" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B248" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C248" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D248" s="6" t="n">
+    <row r="253" customHeight="1" ht="15" spans="1:10">
+      <c r="A253" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D253" s="6" t="n">
         <v>205000</v>
       </c>
-      <c r="E248" s="7" t="n">
+      <c r="E253" s="7" t="n">
         <v>0.38</v>
       </c>
-      <c r="F248" s="7" t="n">
+      <c r="F253" s="7" t="n">
         <v>77900</v>
       </c>
-      <c r="G248" s="8">
+      <c r="G253" s="8">
         <v>46168</v>
       </c>
-      <c r="H248" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I248" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J248" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="249" customHeight="1" ht="15" spans="1:10">
-      <c r="A249" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B249" s="5" t="s">
+      <c r="H253" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I253" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="254" customHeight="1" ht="15" spans="1:10">
+      <c r="A254" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C254" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C249" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D249" s="6" t="n">
+      <c r="D254" s="6" t="n">
         <v>205000</v>
       </c>
-      <c r="E249" s="7" t="n">
+      <c r="E254" s="7" t="n">
         <v>0.39</v>
       </c>
-      <c r="F249" s="7" t="n">
+      <c r="F254" s="7" t="n">
         <v>79950</v>
       </c>
-      <c r="G249" s="8">
+      <c r="G254" s="8">
         <v>46168</v>
       </c>
-      <c r="H249" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I249" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J249" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="250" customHeight="1" ht="15" spans="1:5">
-      <c r="A250" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B250" s="10" t="s">
+      <c r="H254" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I254" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="255" customHeight="1" ht="15" spans="1:5">
+      <c r="A255" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B255" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C250" s="11" t="n">
+      <c r="C255" s="11" t="n">
         <v>157850</v>
       </c>
-      <c r="D250" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E250" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" customHeight="1" ht="15" spans="1:1">
-      <c r="A251" s="2" t="s">
+      <c r="D255" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E255" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" customHeight="1" ht="15" spans="1:1">
+      <c r="A256" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="252" customHeight="1" ht="15" spans="1:10">
-      <c r="A252" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B252" s="5" t="s">
+    <row r="257" customHeight="1" ht="15" spans="1:10">
+      <c r="A257" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B257" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C252" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D252" s="6" t="n">
+      <c r="C257" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D257" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="E252" s="7" t="n">
+      <c r="E257" s="7" t="n">
         <v>0.415</v>
       </c>
-      <c r="F252" s="7" t="n">
+      <c r="F257" s="7" t="n">
         <v>12450</v>
       </c>
-      <c r="G252" s="8">
+      <c r="G257" s="8">
         <v>46169</v>
       </c>
-      <c r="H252" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I252" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J252" s="6" t="s">
+      <c r="H257" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I257" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" s="6" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="253" customHeight="1" ht="15" spans="1:5">
-      <c r="A253" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B253" s="10" t="s">
+    <row r="258" customHeight="1" ht="15" spans="1:5">
+      <c r="A258" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B258" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C253" s="11" t="n">
+      <c r="C258" s="11" t="n">
         <v>12450</v>
       </c>
-      <c r="D253" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E253" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" customHeight="1" ht="15" spans="1:1">
-      <c r="A254" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="255" customHeight="1" ht="15" spans="1:10">
-      <c r="A255" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B255" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C255" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D255" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E255" s="7" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="F255" s="7" t="n">
-        <v>21600</v>
-      </c>
-      <c r="G255" s="8">
-        <v>46168</v>
-      </c>
-      <c r="H255" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I255" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J255" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="256" customHeight="1" ht="15" spans="1:5">
-      <c r="A256" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B256" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C256" s="11" t="n">
-        <v>21600</v>
-      </c>
-      <c r="D256" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E256" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A257" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" customHeight="1" ht="15" spans="1:12">
-      <c r="A258" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G258" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H258" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I258" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J258" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K258" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L258" s="3" t="s">
-        <v>12</v>
+      <c r="D258" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E258" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="259" customHeight="1" ht="15" spans="1:1">
       <c r="A259" s="2" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="260" customHeight="1" ht="15" spans="1:10">
@@ -6682,22 +6689,22 @@
         <v>14</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D260" s="6" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="E260" s="7" t="n">
-        <v>0.415</v>
+        <v>0.216</v>
       </c>
       <c r="F260" s="7" t="n">
-        <v>20750</v>
+        <v>21600</v>
       </c>
       <c r="G260" s="8">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="H260" s="6" t="n">
         <v>0</v>
@@ -6717,201 +6724,201 @@
         <v>27</v>
       </c>
       <c r="C261" s="11" t="n">
+        <v>21600</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E261" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A262" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" customHeight="1" ht="15" spans="1:12">
+      <c r="A263" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G263" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H263" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I263" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J263" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K263" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L263" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="264" customHeight="1" ht="15" spans="1:1">
+      <c r="A264" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="265" customHeight="1" ht="15" spans="1:10">
+      <c r="A265" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D265" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E265" s="7" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F265" s="7" t="n">
         <v>20750</v>
       </c>
-      <c r="D261" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E261" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" customHeight="1" ht="15" spans="1:1">
-      <c r="A262" s="2" t="s">
+      <c r="G265" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H265" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="266" customHeight="1" ht="15" spans="1:5">
+      <c r="A266" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B266" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C266" s="11" t="n">
+        <v>20750</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E266" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" customHeight="1" ht="15" spans="1:1">
+      <c r="A267" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="263" customHeight="1" ht="15" spans="1:10">
-      <c r="A263" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B263" s="5" t="s">
+    <row r="268" customHeight="1" ht="15" spans="1:10">
+      <c r="A268" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B268" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C263" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D263" s="6" t="n">
+      <c r="C268" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D268" s="6" t="n">
         <v>12000</v>
       </c>
-      <c r="E263" s="7" t="n">
+      <c r="E268" s="7" t="n">
         <v>0.49</v>
       </c>
-      <c r="F263" s="7" t="n">
+      <c r="F268" s="7" t="n">
         <v>5880</v>
       </c>
-      <c r="G263" s="8">
+      <c r="G268" s="8">
         <v>46170</v>
       </c>
-      <c r="H263" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I263" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J263" s="6" t="s">
+      <c r="H268" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="264" customHeight="1" ht="15" spans="1:5">
-      <c r="A264" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B264" s="10" t="s">
+    <row r="269" customHeight="1" ht="15" spans="1:5">
+      <c r="A269" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B269" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C264" s="11" t="n">
+      <c r="C269" s="11" t="n">
         <v>5880</v>
       </c>
-      <c r="D264" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E264" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265" customHeight="1" ht="15" spans="1:1">
-      <c r="A265" s="2" t="s">
+      <c r="D269" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E269" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" customHeight="1" ht="15" spans="1:1">
+      <c r="A270" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="266" customHeight="1" ht="15" spans="1:10">
-      <c r="A266" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B266" s="5" t="s">
+    <row r="271" customHeight="1" ht="15" spans="1:10">
+      <c r="A271" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B271" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C266" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D266" s="6" t="n">
+      <c r="C271" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D271" s="6" t="n">
         <v>14000</v>
       </c>
-      <c r="E266" s="7" t="n">
+      <c r="E271" s="7" t="n">
         <v>0.49</v>
       </c>
-      <c r="F266" s="7" t="n">
+      <c r="F271" s="7" t="n">
         <v>6860</v>
       </c>
-      <c r="G266" s="8">
+      <c r="G271" s="8">
         <v>46168</v>
       </c>
-      <c r="H266" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I266" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J266" s="6" t="s">
+      <c r="H271" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I271" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" s="6" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="267" customHeight="1" ht="15" spans="1:10">
-      <c r="A267" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B267" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C267" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D267" s="6" t="n">
-        <v>16000</v>
-      </c>
-      <c r="E267" s="7" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F267" s="7" t="n">
-        <v>7040</v>
-      </c>
-      <c r="G267" s="8">
-        <v>46168</v>
-      </c>
-      <c r="H267" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I267" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J267" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="268" customHeight="1" ht="15" spans="1:5">
-      <c r="A268" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B268" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C268" s="11" t="n">
-        <v>13900</v>
-      </c>
-      <c r="D268" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E268" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A269" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" customHeight="1" ht="15" spans="1:12">
-      <c r="A270" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D270" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E270" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F270" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G270" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H270" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I270" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J270" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K270" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L270" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="271" customHeight="1" ht="15" spans="1:1">
-      <c r="A271" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="272" customHeight="1" ht="15" spans="1:10">
@@ -6919,22 +6926,22 @@
         <v>14</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D272" s="6" t="n">
-        <v>432</v>
+        <v>16000</v>
       </c>
       <c r="E272" s="7" t="n">
-        <v>15.44</v>
+        <v>0.44</v>
       </c>
       <c r="F272" s="7" t="n">
-        <v>6670.08</v>
+        <v>7040</v>
       </c>
       <c r="G272" s="8">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="H272" s="6" t="n">
         <v>0</v>
@@ -6943,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="J272" s="6" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
     </row>
     <row r="273" customHeight="1" ht="15" spans="1:5">
@@ -6954,223 +6961,223 @@
         <v>27</v>
       </c>
       <c r="C273" s="11" t="n">
+        <v>13900</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E273" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A274" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" customHeight="1" ht="15" spans="1:12">
+      <c r="A275" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H275" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I275" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J275" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K275" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L275" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="276" customHeight="1" ht="15" spans="1:1">
+      <c r="A276" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="277" customHeight="1" ht="15" spans="1:10">
+      <c r="A277" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D277" s="6" t="n">
+        <v>432</v>
+      </c>
+      <c r="E277" s="7" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="F277" s="7" t="n">
         <v>6670.08</v>
       </c>
-      <c r="D273" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E273" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274" customHeight="1" ht="15" spans="1:1">
-      <c r="A274" s="2" t="s">
+      <c r="G277" s="8">
+        <v>46170</v>
+      </c>
+      <c r="H277" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I277" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J277" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="278" customHeight="1" ht="15" spans="1:5">
+      <c r="A278" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B278" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C278" s="11" t="n">
+        <v>6670.08</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E278" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" customHeight="1" ht="15" spans="1:1">
+      <c r="A279" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="275" customHeight="1" ht="15" spans="1:10">
-      <c r="A275" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B275" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C275" s="5" t="s">
+    <row r="280" customHeight="1" ht="15" spans="1:10">
+      <c r="A280" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C280" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D280" s="6" t="n">
+        <v>1512</v>
+      </c>
+      <c r="E280" s="7" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F280" s="7" t="n">
+        <v>19202.4</v>
+      </c>
+      <c r="G280" s="8">
+        <v>46169</v>
+      </c>
+      <c r="H280" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="281" customHeight="1" ht="15" spans="1:5">
+      <c r="A281" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B281" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C281" s="11" t="n">
+        <v>19202.4</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E281" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" customHeight="1" ht="15" spans="1:1">
+      <c r="A282" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="283" customHeight="1" ht="15" spans="1:10">
+      <c r="A283" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C283" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D275" s="6" t="n">
-        <v>1512</v>
-      </c>
-      <c r="E275" s="7" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="F275" s="7" t="n">
-        <v>19202.4</v>
-      </c>
-      <c r="G275" s="8">
-        <v>46169</v>
-      </c>
-      <c r="H275" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I275" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J275" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="276" customHeight="1" ht="15" spans="1:5">
-      <c r="A276" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B276" s="10" t="s">
+      <c r="D283" s="6" t="n">
+        <v>2160</v>
+      </c>
+      <c r="E283" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F283" s="7" t="n">
+        <v>25920</v>
+      </c>
+      <c r="G283" s="8">
+        <v>46164</v>
+      </c>
+      <c r="H283" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I283" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="284" customHeight="1" ht="15" spans="1:5">
+      <c r="A284" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B284" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C276" s="11" t="n">
-        <v>19202.4</v>
-      </c>
-      <c r="D276" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E276" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277" customHeight="1" ht="15" spans="1:1">
-      <c r="A277" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="278" customHeight="1" ht="15" spans="1:10">
-      <c r="A278" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B278" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C278" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D278" s="6" t="n">
-        <v>2160</v>
-      </c>
-      <c r="E278" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="F278" s="7" t="n">
+      <c r="C284" s="11" t="n">
         <v>25920</v>
       </c>
-      <c r="G278" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H278" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I278" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J278" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="279" customHeight="1" ht="15" spans="1:5">
-      <c r="A279" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B279" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C279" s="11" t="n">
-        <v>25920</v>
-      </c>
-      <c r="D279" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E279" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280" customHeight="1" ht="15" spans="1:1">
-      <c r="A280" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="281" customHeight="1" ht="15" spans="1:10">
-      <c r="A281" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B281" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C281" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D281" s="6" t="n">
-        <v>1512</v>
-      </c>
-      <c r="E281" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="F281" s="7" t="n">
-        <v>19656</v>
-      </c>
-      <c r="G281" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H281" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I281" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J281" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="282" customHeight="1" ht="15" spans="1:5">
-      <c r="A282" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B282" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C282" s="11" t="n">
-        <v>19656</v>
-      </c>
-      <c r="D282" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E282" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A283" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284" customHeight="1" ht="15" spans="1:12">
-      <c r="A284" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E284" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F284" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G284" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H284" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I284" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J284" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K284" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L284" s="3" t="s">
-        <v>12</v>
+      <c r="D284" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E284" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="285" customHeight="1" ht="15" spans="1:1">
       <c r="A285" s="2" t="s">
-        <v>154</v>
+        <v>102</v>
       </c>
     </row>
     <row r="286" customHeight="1" ht="15" spans="1:10">
@@ -7178,22 +7185,22 @@
         <v>14</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D286" s="6" t="n">
-        <v>8028</v>
+        <v>1512</v>
       </c>
       <c r="E286" s="7" t="n">
-        <v>11.99</v>
+        <v>13</v>
       </c>
       <c r="F286" s="7" t="n">
-        <v>96255.72</v>
+        <v>19656</v>
       </c>
       <c r="G286" s="8">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="H286" s="6" t="n">
         <v>0</v>
@@ -7213,223 +7220,223 @@
         <v>27</v>
       </c>
       <c r="C287" s="11" t="n">
+        <v>19656</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E287" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A288" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" customHeight="1" ht="15" spans="1:12">
+      <c r="A289" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E289" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F289" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G289" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H289" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I289" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J289" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K289" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L289" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="290" customHeight="1" ht="15" spans="1:1">
+      <c r="A290" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="291" customHeight="1" ht="15" spans="1:10">
+      <c r="A291" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D291" s="6" t="n">
+        <v>8028</v>
+      </c>
+      <c r="E291" s="7" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="F291" s="7" t="n">
         <v>96255.72</v>
       </c>
-      <c r="D287" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E287" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288" customHeight="1" ht="15" spans="1:1">
-      <c r="A288" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="289" customHeight="1" ht="15" spans="1:10">
-      <c r="A289" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B289" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C289" s="5" t="s">
+      <c r="G291" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H291" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I291" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="292" customHeight="1" ht="15" spans="1:5">
+      <c r="A292" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B292" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C292" s="11" t="n">
+        <v>96255.72</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E292" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" customHeight="1" ht="15" spans="1:1">
+      <c r="A293" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D289" s="6" t="n">
+    </row>
+    <row r="294" customHeight="1" ht="15" spans="1:10">
+      <c r="A294" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D294" s="6" t="n">
         <v>24000</v>
       </c>
-      <c r="E289" s="7" t="n">
+      <c r="E294" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="F289" s="7" t="n">
+      <c r="F294" s="7" t="n">
         <v>312000</v>
       </c>
-      <c r="G289" s="8">
+      <c r="G294" s="8">
         <v>46100</v>
       </c>
-      <c r="H289" s="6" t="n">
+      <c r="H294" s="6" t="n">
         <v>18900</v>
       </c>
-      <c r="I289" s="9" t="n">
+      <c r="I294" s="9" t="n">
         <v>78.75</v>
       </c>
-      <c r="J289" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="290" customHeight="1" ht="15" spans="1:5">
-      <c r="A290" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B290" s="10" t="s">
+      <c r="J294" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="295" customHeight="1" ht="15" spans="1:5">
+      <c r="A295" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B295" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C290" s="11" t="n">
+      <c r="C295" s="11" t="n">
         <v>312000</v>
       </c>
-      <c r="D290" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E290" s="12" t="n">
+      <c r="D295" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E295" s="12" t="n">
         <v>18900</v>
       </c>
     </row>
-    <row r="291" customHeight="1" ht="15" spans="1:1">
-      <c r="A291" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="292" customHeight="1" ht="15" spans="1:10">
-      <c r="A292" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B292" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C292" s="5" t="s">
+    <row r="296" customHeight="1" ht="15" spans="1:1">
+      <c r="A296" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D292" s="6" t="n">
+    </row>
+    <row r="297" customHeight="1" ht="15" spans="1:10">
+      <c r="A297" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D297" s="6" t="n">
         <v>540</v>
       </c>
-      <c r="E292" s="7" t="n">
+      <c r="E297" s="7" t="n">
         <v>15.33</v>
       </c>
-      <c r="F292" s="7" t="n">
+      <c r="F297" s="7" t="n">
         <v>8278.2</v>
       </c>
-      <c r="G292" s="8">
+      <c r="G297" s="8">
         <v>46168</v>
       </c>
-      <c r="H292" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I292" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J292" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="293" customHeight="1" ht="15" spans="1:5">
-      <c r="A293" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B293" s="10" t="s">
+      <c r="H297" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I297" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="298" customHeight="1" ht="15" spans="1:5">
+      <c r="A298" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B298" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C293" s="11" t="n">
+      <c r="C298" s="11" t="n">
         <v>8278.2</v>
       </c>
-      <c r="D293" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E293" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" customHeight="1" ht="15" spans="1:1">
-      <c r="A294" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="295" customHeight="1" ht="15" spans="1:10">
-      <c r="A295" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B295" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C295" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D295" s="6" t="n">
-        <v>210</v>
-      </c>
-      <c r="E295" s="7" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="F295" s="7" t="n">
-        <v>4174.8</v>
-      </c>
-      <c r="G295" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H295" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I295" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J295" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="296" customHeight="1" ht="15" spans="1:5">
-      <c r="A296" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B296" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C296" s="11" t="n">
-        <v>4174.8</v>
-      </c>
-      <c r="D296" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E296" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A297" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" customHeight="1" ht="15" spans="1:12">
-      <c r="A298" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C298" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D298" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E298" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F298" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G298" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H298" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I298" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J298" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K298" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L298" s="3" t="s">
-        <v>12</v>
+      <c r="D298" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E298" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="299" customHeight="1" ht="15" spans="1:1">
       <c r="A299" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="300" customHeight="1" ht="15" spans="1:10">
@@ -7437,19 +7444,19 @@
         <v>14</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="C300" s="5" t="s">
         <v>164</v>
       </c>
       <c r="D300" s="6" t="n">
-        <v>320</v>
+        <v>210</v>
       </c>
       <c r="E300" s="7" t="n">
-        <v>15.75</v>
+        <v>19.88</v>
       </c>
       <c r="F300" s="7" t="n">
-        <v>5040</v>
+        <v>4174.8</v>
       </c>
       <c r="G300" s="8">
         <v>46167</v>
@@ -7461,7 +7468,7 @@
         <v>0</v>
       </c>
       <c r="J300" s="6" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="301" customHeight="1" ht="15" spans="1:5">
@@ -7472,201 +7479,201 @@
         <v>27</v>
       </c>
       <c r="C301" s="11" t="n">
+        <v>4174.8</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E301" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A302" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" customHeight="1" ht="15" spans="1:12">
+      <c r="A303" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G303" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H303" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I303" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J303" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K303" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L303" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="304" customHeight="1" ht="15" spans="1:1">
+      <c r="A304" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="305" customHeight="1" ht="15" spans="1:10">
+      <c r="A305" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C305" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D305" s="6" t="n">
+        <v>320</v>
+      </c>
+      <c r="E305" s="7" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="F305" s="7" t="n">
         <v>5040</v>
       </c>
-      <c r="D301" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E301" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" customHeight="1" ht="15" spans="1:1">
-      <c r="A302" s="2" t="s">
+      <c r="G305" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H305" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="306" customHeight="1" ht="15" spans="1:5">
+      <c r="A306" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B306" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C306" s="11" t="n">
+        <v>5040</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E306" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" customHeight="1" ht="15" spans="1:1">
+      <c r="A307" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="303" customHeight="1" ht="15" spans="1:10">
-      <c r="A303" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B303" s="5" t="s">
+    <row r="308" customHeight="1" ht="15" spans="1:10">
+      <c r="A308" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B308" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C303" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D303" s="6" t="n">
+      <c r="C308" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D308" s="6" t="n">
         <v>2016</v>
       </c>
-      <c r="E303" s="7" t="n">
+      <c r="E308" s="7" t="n">
         <v>16.58</v>
       </c>
-      <c r="F303" s="7" t="n">
+      <c r="F308" s="7" t="n">
         <v>33425.28</v>
       </c>
-      <c r="G303" s="8">
+      <c r="G308" s="8">
         <v>46162</v>
       </c>
-      <c r="H303" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I303" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J303" s="6" t="s">
+      <c r="H308" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="304" customHeight="1" ht="15" spans="1:5">
-      <c r="A304" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B304" s="10" t="s">
+    <row r="309" customHeight="1" ht="15" spans="1:5">
+      <c r="A309" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B309" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C304" s="11" t="n">
+      <c r="C309" s="11" t="n">
         <v>33425.28</v>
       </c>
-      <c r="D304" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E304" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305" customHeight="1" ht="15" spans="1:1">
-      <c r="A305" s="2" t="s">
+      <c r="D309" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E309" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" customHeight="1" ht="15" spans="1:1">
+      <c r="A310" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="306" customHeight="1" ht="15" spans="1:10">
-      <c r="A306" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B306" s="5" t="s">
+    <row r="311" customHeight="1" ht="15" spans="1:10">
+      <c r="A311" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B311" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C306" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D306" s="6" t="n">
+      <c r="C311" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D311" s="6" t="n">
         <v>1020</v>
       </c>
-      <c r="E306" s="7" t="n">
+      <c r="E311" s="7" t="n">
         <v>9.8</v>
       </c>
-      <c r="F306" s="7" t="n">
+      <c r="F311" s="7" t="n">
         <v>9996</v>
       </c>
-      <c r="G306" s="8">
+      <c r="G311" s="8">
         <v>46164</v>
       </c>
-      <c r="H306" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I306" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J306" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="307" customHeight="1" ht="15" spans="1:10">
-      <c r="A307" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B307" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C307" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D307" s="6" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E307" s="7" t="n">
-        <v>9.8</v>
-      </c>
-      <c r="F307" s="7" t="n">
-        <v>9996</v>
-      </c>
-      <c r="G307" s="8">
-        <v>46164</v>
-      </c>
-      <c r="H307" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I307" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J307" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="308" customHeight="1" ht="15" spans="1:5">
-      <c r="A308" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B308" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C308" s="11" t="n">
-        <v>19992</v>
-      </c>
-      <c r="D308" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E308" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A309" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" customHeight="1" ht="15" spans="1:12">
-      <c r="A310" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C310" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D310" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E310" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F310" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G310" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H310" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I310" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J310" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K310" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L310" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="311" customHeight="1" ht="15" spans="1:1">
-      <c r="A311" s="2" t="s">
-        <v>154</v>
+      <c r="H311" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I311" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="312" customHeight="1" ht="15" spans="1:10">
@@ -7674,22 +7681,22 @@
         <v>14</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="C312" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D312" s="6" t="n">
-        <v>4032</v>
+        <v>1020</v>
       </c>
       <c r="E312" s="7" t="n">
-        <v>6.99</v>
+        <v>9.8</v>
       </c>
       <c r="F312" s="7" t="n">
-        <v>28183.68</v>
+        <v>9996</v>
       </c>
       <c r="G312" s="8">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="H312" s="6" t="n">
         <v>0</v>
@@ -7709,223 +7716,223 @@
         <v>27</v>
       </c>
       <c r="C313" s="11" t="n">
+        <v>19992</v>
+      </c>
+      <c r="D313" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E313" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A314" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" customHeight="1" ht="15" spans="1:12">
+      <c r="A315" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E315" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F315" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G315" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H315" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I315" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J315" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K315" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L315" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="316" customHeight="1" ht="15" spans="1:1">
+      <c r="A316" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="317" customHeight="1" ht="15" spans="1:10">
+      <c r="A317" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D317" s="6" t="n">
+        <v>4032</v>
+      </c>
+      <c r="E317" s="7" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F317" s="7" t="n">
         <v>28183.68</v>
       </c>
-      <c r="D313" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E313" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314" customHeight="1" ht="15" spans="1:1">
-      <c r="A314" s="2" t="s">
+      <c r="G317" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H317" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I317" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="318" customHeight="1" ht="15" spans="1:5">
+      <c r="A318" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B318" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C318" s="11" t="n">
+        <v>28183.68</v>
+      </c>
+      <c r="D318" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E318" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" customHeight="1" ht="15" spans="1:1">
+      <c r="A319" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="315" customHeight="1" ht="15" spans="1:10">
-      <c r="A315" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B315" s="5" t="s">
+    <row r="320" customHeight="1" ht="15" spans="1:10">
+      <c r="A320" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B320" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C315" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D315" s="6" t="n">
+      <c r="C320" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D320" s="6" t="n">
         <v>320</v>
       </c>
-      <c r="E315" s="7" t="n">
+      <c r="E320" s="7" t="n">
         <v>16.75</v>
       </c>
-      <c r="F315" s="7" t="n">
+      <c r="F320" s="7" t="n">
         <v>5360</v>
       </c>
-      <c r="G315" s="8">
+      <c r="G320" s="8">
         <v>46167</v>
       </c>
-      <c r="H315" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I315" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J315" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="316" customHeight="1" ht="15" spans="1:5">
-      <c r="A316" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B316" s="10" t="s">
+      <c r="H320" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I320" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="321" customHeight="1" ht="15" spans="1:5">
+      <c r="A321" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B321" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C316" s="11" t="n">
+      <c r="C321" s="11" t="n">
         <v>5360</v>
       </c>
-      <c r="D316" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E316" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317" customHeight="1" ht="15" spans="1:1">
-      <c r="A317" s="2" t="s">
+      <c r="D321" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E321" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" customHeight="1" ht="15" spans="1:1">
+      <c r="A322" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="318" customHeight="1" ht="15" spans="1:10">
-      <c r="A318" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B318" s="5" t="s">
+    <row r="323" customHeight="1" ht="15" spans="1:10">
+      <c r="A323" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B323" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C318" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D318" s="6" t="n">
+      <c r="C323" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D323" s="6" t="n">
         <v>512</v>
       </c>
-      <c r="E318" s="7" t="n">
+      <c r="E323" s="7" t="n">
         <v>17.88</v>
       </c>
-      <c r="F318" s="7" t="n">
+      <c r="F323" s="7" t="n">
         <v>9154.56</v>
       </c>
-      <c r="G318" s="8">
+      <c r="G323" s="8">
         <v>46169</v>
       </c>
-      <c r="H318" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I318" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J318" s="6" t="s">
+      <c r="H323" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I323" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J323" s="6" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="319" customHeight="1" ht="15" spans="1:5">
-      <c r="A319" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B319" s="10" t="s">
+    <row r="324" customHeight="1" ht="15" spans="1:5">
+      <c r="A324" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B324" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C319" s="11" t="n">
+      <c r="C324" s="11" t="n">
         <v>9154.56</v>
       </c>
-      <c r="D319" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E319" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320" customHeight="1" ht="15" spans="1:1">
-      <c r="A320" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="321" customHeight="1" ht="15" spans="1:10">
-      <c r="A321" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B321" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C321" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D321" s="6" t="n">
-        <v>714</v>
-      </c>
-      <c r="E321" s="7" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="F321" s="7" t="n">
-        <v>16921.8</v>
-      </c>
-      <c r="G321" s="8">
-        <v>46169</v>
-      </c>
-      <c r="H321" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I321" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J321" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="322" customHeight="1" ht="15" spans="1:5">
-      <c r="A322" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B322" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C322" s="11" t="n">
-        <v>16921.8</v>
-      </c>
-      <c r="D322" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E322" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A323" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324" customHeight="1" ht="15" spans="1:12">
-      <c r="A324" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B324" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C324" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D324" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E324" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F324" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G324" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H324" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I324" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J324" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K324" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L324" s="3" t="s">
-        <v>12</v>
+      <c r="D324" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E324" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="325" customHeight="1" ht="15" spans="1:1">
       <c r="A325" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="326" customHeight="1" ht="15" spans="1:10">
@@ -7933,19 +7940,19 @@
         <v>14</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D326" s="6" t="n">
-        <v>1008</v>
+        <v>714</v>
       </c>
       <c r="E326" s="7" t="n">
-        <v>6.99</v>
+        <v>23.7</v>
       </c>
       <c r="F326" s="7" t="n">
-        <v>7045.92</v>
+        <v>16921.8</v>
       </c>
       <c r="G326" s="8">
         <v>46169</v>
@@ -7957,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="J326" s="6" t="s">
-        <v>92</v>
+        <v>174</v>
       </c>
     </row>
     <row r="327" customHeight="1" ht="15" spans="1:5">
@@ -7968,277 +7975,277 @@
         <v>27</v>
       </c>
       <c r="C327" s="11" t="n">
+        <v>16921.8</v>
+      </c>
+      <c r="D327" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E327" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A328" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" customHeight="1" ht="15" spans="1:12">
+      <c r="A329" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E329" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F329" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G329" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H329" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I329" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J329" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K329" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L329" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="330" customHeight="1" ht="15" spans="1:1">
+      <c r="A330" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="331" customHeight="1" ht="15" spans="1:10">
+      <c r="A331" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B331" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C331" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D331" s="6" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E331" s="7" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F331" s="7" t="n">
         <v>7045.92</v>
       </c>
-      <c r="D327" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E327" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" customHeight="1" ht="15" spans="1:1">
-      <c r="A328" s="2" t="s">
+      <c r="G331" s="8">
+        <v>46169</v>
+      </c>
+      <c r="H331" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I331" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J331" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="332" customHeight="1" ht="15" spans="1:5">
+      <c r="A332" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B332" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C332" s="11" t="n">
+        <v>7045.92</v>
+      </c>
+      <c r="D332" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E332" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" customHeight="1" ht="15" spans="1:1">
+      <c r="A333" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="329" customHeight="1" ht="15" spans="1:10">
-      <c r="A329" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B329" s="5" t="s">
+    <row r="334" customHeight="1" ht="15" spans="1:10">
+      <c r="A334" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B334" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C329" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D329" s="6" t="n">
+      <c r="C334" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D334" s="6" t="n">
         <v>2016</v>
       </c>
-      <c r="E329" s="7" t="n">
+      <c r="E334" s="7" t="n">
         <v>6.99</v>
       </c>
-      <c r="F329" s="7" t="n">
+      <c r="F334" s="7" t="n">
         <v>14091.84</v>
       </c>
-      <c r="G329" s="8">
+      <c r="G334" s="8">
         <v>46164</v>
       </c>
-      <c r="H329" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I329" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J329" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="330" customHeight="1" ht="15" spans="1:5">
-      <c r="A330" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B330" s="10" t="s">
+      <c r="H334" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I334" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J334" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="335" customHeight="1" ht="15" spans="1:5">
+      <c r="A335" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B335" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C330" s="11" t="n">
+      <c r="C335" s="11" t="n">
         <v>14091.84</v>
       </c>
-      <c r="D330" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E330" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" customHeight="1" ht="15" spans="1:1">
-      <c r="A331" s="2" t="s">
+      <c r="D335" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E335" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" customHeight="1" ht="15" spans="1:1">
+      <c r="A336" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="332" customHeight="1" ht="15" spans="1:10">
-      <c r="A332" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B332" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C332" s="5" t="s">
+    <row r="337" customHeight="1" ht="15" spans="1:10">
+      <c r="A337" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B337" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C337" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D337" s="6" t="n">
+        <v>520</v>
+      </c>
+      <c r="E337" s="7" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="F337" s="7" t="n">
+        <v>7519.2</v>
+      </c>
+      <c r="G337" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H337" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I337" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J337" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="338" customHeight="1" ht="15" spans="1:5">
+      <c r="A338" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B338" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C338" s="11" t="n">
+        <v>7519.2</v>
+      </c>
+      <c r="D338" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E338" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" customHeight="1" ht="15" spans="1:1">
+      <c r="A339" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="340" customHeight="1" ht="15" spans="1:10">
+      <c r="A340" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C340" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D332" s="6" t="n">
-        <v>520</v>
-      </c>
-      <c r="E332" s="7" t="n">
-        <v>14.46</v>
-      </c>
-      <c r="F332" s="7" t="n">
-        <v>7519.2</v>
-      </c>
-      <c r="G332" s="8">
+      <c r="D340" s="6" t="n">
+        <v>648</v>
+      </c>
+      <c r="E340" s="7" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="F340" s="7" t="n">
+        <v>4847.04</v>
+      </c>
+      <c r="G340" s="8">
         <v>46167</v>
       </c>
-      <c r="H332" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I332" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J332" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="333" customHeight="1" ht="15" spans="1:5">
-      <c r="A333" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B333" s="10" t="s">
+      <c r="H340" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I340" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J340" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="341" customHeight="1" ht="15" spans="1:5">
+      <c r="A341" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B341" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C333" s="11" t="n">
-        <v>7519.2</v>
-      </c>
-      <c r="D333" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E333" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334" customHeight="1" ht="15" spans="1:1">
-      <c r="A334" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="335" customHeight="1" ht="15" spans="1:10">
-      <c r="A335" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B335" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C335" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D335" s="6" t="n">
-        <v>648</v>
-      </c>
-      <c r="E335" s="7" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="F335" s="7" t="n">
+      <c r="C341" s="11" t="n">
         <v>4847.04</v>
       </c>
-      <c r="G335" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H335" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I335" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J335" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="336" customHeight="1" ht="15" spans="1:5">
-      <c r="A336" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B336" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C336" s="11" t="n">
-        <v>4847.04</v>
-      </c>
-      <c r="D336" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E336" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" customHeight="1" ht="15" spans="1:1">
-      <c r="A337" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="338" customHeight="1" ht="15" spans="1:10">
-      <c r="A338" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B338" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C338" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D338" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E338" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="F338" s="7" t="n">
-        <v>10500</v>
-      </c>
-      <c r="G338" s="8">
-        <v>46167</v>
-      </c>
-      <c r="H338" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I338" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J338" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="339" customHeight="1" ht="15" spans="1:5">
-      <c r="A339" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B339" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C339" s="11" t="n">
-        <v>10500</v>
-      </c>
-      <c r="D339" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E339" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="340" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A340" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341" customHeight="1" ht="15" spans="1:12">
-      <c r="A341" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B341" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C341" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D341" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E341" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F341" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G341" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H341" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I341" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J341" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K341" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L341" s="3" t="s">
-        <v>12</v>
+      <c r="D341" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E341" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="342" customHeight="1" ht="15" spans="1:1">
       <c r="A342" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="343" customHeight="1" ht="15" spans="1:10">
@@ -8246,79 +8253,176 @@
         <v>14</v>
       </c>
       <c r="B343" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C343" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D343" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E343" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F343" s="7" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G343" s="8">
+        <v>46167</v>
+      </c>
+      <c r="H343" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I343" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="344" customHeight="1" ht="15" spans="1:5">
+      <c r="A344" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B344" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C344" s="11" t="n">
+        <v>10500</v>
+      </c>
+      <c r="D344" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E344" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A345" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" customHeight="1" ht="15" spans="1:12">
+      <c r="A346" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E346" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F346" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G346" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H346" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I346" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J346" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K346" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L346" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="347" customHeight="1" ht="15" spans="1:1">
+      <c r="A347" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="348" customHeight="1" ht="15" spans="1:10">
+      <c r="A348" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B348" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C343" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D343" s="6" t="n">
+      <c r="C348" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D348" s="6" t="n">
         <v>1512</v>
       </c>
-      <c r="E343" s="7" t="n">
+      <c r="E348" s="7" t="n">
         <v>6.8</v>
       </c>
-      <c r="F343" s="7" t="n">
+      <c r="F348" s="7" t="n">
         <v>10281.6</v>
       </c>
-      <c r="G343" s="8">
+      <c r="G348" s="8">
         <v>46164</v>
       </c>
-      <c r="H343" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I343" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J343" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="344" customHeight="1" ht="15" spans="1:10">
-      <c r="A344" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B344" s="5" t="s">
+      <c r="H348" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I348" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J348" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="349" customHeight="1" ht="15" spans="1:10">
+      <c r="A349" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B349" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C344" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D344" s="6" t="n">
+      <c r="C349" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D349" s="6" t="n">
         <v>1512</v>
       </c>
-      <c r="E344" s="7" t="n">
+      <c r="E349" s="7" t="n">
         <v>6.8</v>
       </c>
-      <c r="F344" s="7" t="n">
+      <c r="F349" s="7" t="n">
         <v>10281.6</v>
       </c>
-      <c r="G344" s="8">
+      <c r="G349" s="8">
         <v>46164</v>
       </c>
-      <c r="H344" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I344" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J344" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="345" customHeight="1" ht="15" spans="1:5">
-      <c r="A345" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B345" s="10" t="s">
+      <c r="H349" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I349" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="350" customHeight="1" ht="15" spans="1:5">
+      <c r="A350" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B350" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C345" s="11" t="n">
+      <c r="C350" s="11" t="n">
         <v>20563.2</v>
       </c>
-      <c r="D345" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E345" s="12" t="n">
+      <c r="D350" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E350" s="12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="185">
   <si>
     <t>MATRIZ CNPJ: 40.357.820/0001-50R Y DOIS - 58082-025
  ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t>877</t>
+  </si>
+  <si>
+    <t>419 - ATADURA DE CREPE 13 FIOS 15 X 1,20   PCT 12  HOSPITALAR C Observação: Faturar em 30/06</t>
+  </si>
+  <si>
+    <t>423 - ATADURA DE CREPE 13 FIOS 20 X 1,20   PCT 12  HOSPITALAR C Observação: Faturar 30/06</t>
   </si>
   <si>
     <t>ATADURAS INDIVIDUAIS (FARMA)</t>
@@ -2131,7 +2137,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" customHeight="1" ht="19.65" spans="1:10">
+    <row r="61" customHeight="1" ht="27.95" spans="1:10">
       <c r="A61" s="5" t="s">
         <v>14</v>
       </c>
@@ -2139,7 +2145,7 @@
         <v>51</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="D61" s="8" t="n">
         <v>840</v>
@@ -2163,7 +2169,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" customHeight="1" ht="19.9" spans="1:10">
+    <row r="62" customHeight="1" ht="28.05" spans="1:10">
       <c r="A62" s="5" t="s">
         <v>14</v>
       </c>
@@ -2171,7 +2177,7 @@
         <v>51</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D62" s="8" t="n">
         <v>832</v>
@@ -2222,7 +2228,7 @@
         <v>1</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>3</v>
@@ -2257,7 +2263,7 @@
     </row>
     <row r="66" customHeight="1" ht="15" spans="1:1">
       <c r="A66" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" customHeight="1" ht="20.4" spans="1:10">
@@ -2265,10 +2271,10 @@
         <v>14</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D67" s="8" t="n">
         <v>500</v>
@@ -2297,10 +2303,10 @@
         <v>14</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D68" s="8" t="n">
         <v>1080</v>
@@ -2329,10 +2335,10 @@
         <v>14</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D69" s="8" t="n">
         <v>2025</v>
@@ -2361,10 +2367,10 @@
         <v>14</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D70" s="8" t="n">
         <v>2040</v>
@@ -2407,7 +2413,7 @@
     </row>
     <row r="72" customHeight="1" ht="15" spans="1:1">
       <c r="A72" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73" customHeight="1" ht="19.3" spans="1:10">
@@ -2415,10 +2421,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D73" s="8" t="n">
         <v>1012</v>
@@ -2447,10 +2453,10 @@
         <v>14</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D74" s="8" t="n">
         <v>920</v>
@@ -2479,10 +2485,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D75" s="8" t="n">
         <v>1500</v>
@@ -2525,7 +2531,7 @@
     </row>
     <row r="77" customHeight="1" ht="15" spans="1:1">
       <c r="A77" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" customHeight="1" ht="19.3" spans="1:10">
@@ -2533,10 +2539,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D78" s="8" t="n">
         <v>1100</v>
@@ -2565,10 +2571,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D79" s="8" t="n">
         <v>1080</v>
@@ -2619,7 +2625,7 @@
         <v>1</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>3</v>
@@ -2654,7 +2660,7 @@
     </row>
     <row r="83" customHeight="1" ht="15" spans="1:1">
       <c r="A83" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="84" customHeight="1" ht="20.4" spans="1:10">
@@ -2662,10 +2668,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D84" s="8" t="n">
         <v>300</v>
@@ -2686,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="85" customHeight="1" ht="19.4" spans="1:10">
@@ -2694,10 +2700,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D85" s="8" t="n">
         <v>450</v>
@@ -2718,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="86" customHeight="1" ht="18.35" spans="1:10">
@@ -2726,10 +2732,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D86" s="8" t="n">
         <v>60</v>
@@ -2750,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="J86" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="87" customHeight="1" ht="15" spans="1:5">
@@ -2772,7 +2778,7 @@
     </row>
     <row r="88" customHeight="1" ht="15" spans="1:1">
       <c r="A88" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89" customHeight="1" ht="18.6" spans="1:10">
@@ -2780,10 +2786,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D89" s="8" t="n">
         <v>240</v>
@@ -2826,7 +2832,7 @@
     </row>
     <row r="91" customHeight="1" ht="15" spans="1:1">
       <c r="A91" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92" customHeight="1" ht="27.95" spans="1:10">
@@ -2834,10 +2840,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D92" s="8" t="n">
         <v>21700</v>
@@ -2866,10 +2872,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D93" s="8" t="n">
         <v>1300</v>
@@ -2898,10 +2904,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D94" s="8" t="n">
         <v>1050</v>
@@ -2930,10 +2936,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D95" s="8" t="n">
         <v>1020</v>
@@ -2984,7 +2990,7 @@
         <v>1</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>3</v>
@@ -3019,7 +3025,7 @@
     </row>
     <row r="99" customHeight="1" ht="15" spans="1:1">
       <c r="A99" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" customHeight="1" ht="20.4" spans="1:10">
@@ -3027,10 +3033,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D100" s="8" t="n">
         <v>110</v>
@@ -3051,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="101" customHeight="1" ht="19.4" spans="1:10">
@@ -3059,10 +3065,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D101" s="8" t="n">
         <v>100</v>
@@ -3083,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102" customHeight="1" ht="18.35" spans="1:10">
@@ -3091,10 +3097,10 @@
         <v>14</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D102" s="8" t="n">
         <v>110</v>
@@ -3115,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="103" customHeight="1" ht="20.4" spans="1:10">
@@ -3123,10 +3129,10 @@
         <v>14</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D103" s="8" t="n">
         <v>90</v>
@@ -3147,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="104" customHeight="1" ht="19.15" spans="1:10">
@@ -3155,10 +3161,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D104" s="8" t="n">
         <v>90</v>
@@ -3179,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="J104" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="105" customHeight="1" ht="20.75" spans="1:10">
@@ -3187,10 +3193,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D105" s="8" t="n">
         <v>75</v>
@@ -3211,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="106" customHeight="1" ht="19.4" spans="1:10">
@@ -3219,10 +3225,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D106" s="8" t="n">
         <v>60</v>
@@ -3243,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="J106" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="107" customHeight="1" ht="15" spans="1:5">
@@ -3265,7 +3271,7 @@
     </row>
     <row r="108" customHeight="1" ht="15" spans="1:1">
       <c r="A108" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="109" customHeight="1" ht="19.9" spans="1:10">
@@ -3273,10 +3279,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D109" s="8" t="n">
         <v>400</v>
@@ -3297,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="110" customHeight="1" ht="20.95" spans="1:10">
@@ -3305,10 +3311,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D110" s="8" t="n">
         <v>270</v>
@@ -3329,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="111" customHeight="1" ht="18.6" spans="1:10">
@@ -3337,10 +3343,10 @@
         <v>14</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D111" s="8" t="n">
         <v>375</v>
@@ -3361,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="112" customHeight="1" ht="18.8" spans="1:10">
@@ -3369,10 +3375,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D112" s="8" t="n">
         <v>240</v>
@@ -3393,7 +3399,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="113" customHeight="1" ht="20.25" spans="1:10">
@@ -3401,10 +3407,10 @@
         <v>14</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D113" s="8" t="n">
         <v>200</v>
@@ -3425,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="114" customHeight="1" ht="15" spans="1:5">
@@ -3455,7 +3461,7 @@
         <v>1</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>3</v>
@@ -3490,7 +3496,7 @@
     </row>
     <row r="117" customHeight="1" ht="15" spans="1:1">
       <c r="A117" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="118" customHeight="1" ht="20.4" spans="1:10">
@@ -3498,10 +3504,10 @@
         <v>14</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D118" s="8" t="n">
         <v>110</v>
@@ -3522,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="119" customHeight="1" ht="19.4" spans="1:10">
@@ -3530,10 +3536,10 @@
         <v>14</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D119" s="8" t="n">
         <v>300</v>
@@ -3554,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="120" customHeight="1" ht="18.35" spans="1:10">
@@ -3562,10 +3568,10 @@
         <v>14</v>
       </c>
       <c r="B120" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C120" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>84</v>
       </c>
       <c r="D120" s="8" t="n">
         <v>200</v>
@@ -3586,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="J120" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="121" customHeight="1" ht="15" spans="1:5">
@@ -3608,7 +3614,7 @@
     </row>
     <row r="122" customHeight="1" ht="15" spans="1:1">
       <c r="A122" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="123" customHeight="1" ht="18.6" spans="1:10">
@@ -3616,10 +3622,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D123" s="8" t="n">
         <v>300</v>
@@ -3648,10 +3654,10 @@
         <v>14</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D124" s="8" t="n">
         <v>360</v>
@@ -3680,10 +3686,10 @@
         <v>14</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D125" s="8" t="n">
         <v>75</v>
@@ -3726,7 +3732,7 @@
     </row>
     <row r="127" customHeight="1" ht="15" spans="1:1">
       <c r="A127" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="128" customHeight="1" ht="19.9" spans="1:10">
@@ -3734,10 +3740,10 @@
         <v>14</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D128" s="8" t="n">
         <v>100</v>
@@ -3766,10 +3772,10 @@
         <v>14</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D129" s="8" t="n">
         <v>360</v>
@@ -3798,10 +3804,10 @@
         <v>14</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D130" s="8" t="n">
         <v>750</v>
@@ -3830,10 +3836,10 @@
         <v>14</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D131" s="8" t="n">
         <v>360</v>
@@ -3884,7 +3890,7 @@
         <v>1</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>3</v>
@@ -3919,7 +3925,7 @@
     </row>
     <row r="135" customHeight="1" ht="15" spans="1:1">
       <c r="A135" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="136" customHeight="1" ht="20.4" spans="1:10">
@@ -3927,10 +3933,10 @@
         <v>14</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D136" s="8" t="n">
         <v>550</v>
@@ -3959,10 +3965,10 @@
         <v>14</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D137" s="8" t="n">
         <v>560</v>
@@ -3991,10 +3997,10 @@
         <v>14</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D138" s="8" t="n">
         <v>250</v>
@@ -4023,10 +4029,10 @@
         <v>14</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D139" s="8" t="n">
         <v>550</v>
@@ -4055,10 +4061,10 @@
         <v>14</v>
       </c>
       <c r="B140" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C140" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>95</v>
       </c>
       <c r="D140" s="8" t="n">
         <v>560</v>
@@ -4087,10 +4093,10 @@
         <v>14</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D141" s="8" t="n">
         <v>250</v>
@@ -4133,7 +4139,7 @@
     </row>
     <row r="143" customHeight="1" ht="15" spans="1:1">
       <c r="A143" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="144" customHeight="1" ht="21.8" spans="1:10">
@@ -4141,10 +4147,10 @@
         <v>14</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D144" s="8" t="n">
         <v>2070</v>
@@ -4165,7 +4171,7 @@
         <v>0</v>
       </c>
       <c r="J144" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="145" customHeight="1" ht="19.8" spans="1:10">
@@ -4173,10 +4179,10 @@
         <v>14</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D145" s="8" t="n">
         <v>2030</v>
@@ -4197,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="J145" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="146" customHeight="1" ht="15" spans="1:5">
@@ -4227,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>3</v>
@@ -4262,7 +4268,7 @@
     </row>
     <row r="149" customHeight="1" ht="15" spans="1:1">
       <c r="A149" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="150" customHeight="1" ht="20.4" spans="1:10">
@@ -4270,10 +4276,10 @@
         <v>14</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D150" s="8" t="n">
         <v>600</v>
@@ -4294,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="J150" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="151" customHeight="1" ht="19.4" spans="1:10">
@@ -4302,10 +4308,10 @@
         <v>14</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D151" s="8" t="n">
         <v>525</v>
@@ -4326,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="J151" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="152" customHeight="1" ht="18.35" spans="1:10">
@@ -4334,10 +4340,10 @@
         <v>14</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D152" s="8" t="n">
         <v>600</v>
@@ -4358,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="J152" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="153" customHeight="1" ht="15" spans="1:5">
@@ -4388,7 +4394,7 @@
         <v>1</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>3</v>
@@ -4423,7 +4429,7 @@
     </row>
     <row r="156" customHeight="1" ht="15" spans="1:1">
       <c r="A156" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="157" customHeight="1" ht="20.4" spans="1:10">
@@ -4431,10 +4437,10 @@
         <v>14</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D157" s="8" t="n">
         <v>200100</v>
@@ -4455,7 +4461,7 @@
         <v>30.43</v>
       </c>
       <c r="J157" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="158" customHeight="1" ht="15" spans="1:5">
@@ -4477,7 +4483,7 @@
     </row>
     <row r="159" customHeight="1" ht="15" spans="1:1">
       <c r="A159" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="160" customHeight="1" ht="18.35" spans="1:10">
@@ -4485,10 +4491,10 @@
         <v>14</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D160" s="8" t="n">
         <v>50100</v>
@@ -4503,10 +4509,10 @@
         <v>46156</v>
       </c>
       <c r="H160" s="8" t="n">
-        <v>13350</v>
+        <v>17100</v>
       </c>
       <c r="I160" s="11" t="n">
-        <v>26.65</v>
+        <v>34.13</v>
       </c>
       <c r="J160" s="8" t="s">
         <v>23</v>
@@ -4517,10 +4523,10 @@
         <v>14</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D161" s="8" t="n">
         <v>50100</v>
@@ -4549,10 +4555,10 @@
         <v>14</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D162" s="8" t="n">
         <v>20100</v>
@@ -4590,12 +4596,12 @@
         <v>19</v>
       </c>
       <c r="E163" s="14" t="n">
-        <v>13350</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="164" customHeight="1" ht="15" spans="1:1">
       <c r="A164" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="165" customHeight="1" ht="18.7" spans="1:10">
@@ -4603,10 +4609,10 @@
         <v>14</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D165" s="8" t="n">
         <v>50100</v>
@@ -4627,7 +4633,7 @@
         <v>44.91</v>
       </c>
       <c r="J165" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="166" customHeight="1" ht="15" spans="1:5">
@@ -4649,7 +4655,7 @@
     </row>
     <row r="167" customHeight="1" ht="15" spans="1:1">
       <c r="A167" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="168" customHeight="1" ht="28.9" spans="1:10">
@@ -4657,10 +4663,10 @@
         <v>14</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D168" s="8" t="n">
         <v>10000</v>
@@ -4681,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="J168" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="169" customHeight="1" ht="15" spans="1:5">
@@ -4711,7 +4717,7 @@
         <v>1</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>3</v>
@@ -4757,7 +4763,7 @@
         <v>26</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D173" s="8" t="n">
         <v>3408</v>
@@ -4800,7 +4806,7 @@
     </row>
     <row r="175" customHeight="1" ht="15" spans="1:1">
       <c r="A175" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="176" customHeight="1" ht="18.35" spans="1:10">
@@ -4808,10 +4814,10 @@
         <v>14</v>
       </c>
       <c r="B176" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C176" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="C176" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="D176" s="8" t="n">
         <v>3000</v>
@@ -4832,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="J176" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="177" customHeight="1" ht="15" spans="1:5">
@@ -4854,7 +4860,7 @@
     </row>
     <row r="178" customHeight="1" ht="15" spans="1:1">
       <c r="A178" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="179" customHeight="1" ht="18.8" spans="1:10">
@@ -4862,10 +4868,10 @@
         <v>14</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D179" s="8" t="n">
         <v>300</v>
@@ -4886,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="J179" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="180" customHeight="1" ht="15" spans="1:5">
@@ -4916,10 +4922,10 @@
         <v>14</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D182" s="8" t="n">
         <v>2004</v>
@@ -4970,7 +4976,7 @@
         <v>1</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>3</v>
@@ -5005,7 +5011,7 @@
     </row>
     <row r="186" customHeight="1" ht="15" spans="1:1">
       <c r="A186" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="187" customHeight="1" ht="20.4" spans="1:10">
@@ -5013,10 +5019,10 @@
         <v>14</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D187" s="8" t="n">
         <v>100000</v>
@@ -5037,7 +5043,7 @@
         <v>0</v>
       </c>
       <c r="J187" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="188" customHeight="1" ht="15" spans="1:5">
@@ -5059,7 +5065,7 @@
     </row>
     <row r="189" customHeight="1" ht="15" spans="1:1">
       <c r="A189" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="190" customHeight="1" ht="15" spans="1:10">
@@ -5067,10 +5073,10 @@
         <v>14</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D190" s="8" t="n">
         <v>20000</v>
@@ -5091,7 +5097,7 @@
         <v>0</v>
       </c>
       <c r="J190" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="191" customHeight="1" ht="15" spans="1:5">
@@ -5113,7 +5119,7 @@
     </row>
     <row r="192" customHeight="1" ht="15" spans="1:1">
       <c r="A192" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="193" customHeight="1" ht="15" spans="1:10">
@@ -5121,10 +5127,10 @@
         <v>14</v>
       </c>
       <c r="B193" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C193" s="7" t="s">
         <v>131</v>
-      </c>
-      <c r="C193" s="7" t="s">
-        <v>129</v>
       </c>
       <c r="D193" s="8" t="n">
         <v>13000</v>
@@ -5145,7 +5151,7 @@
         <v>0</v>
       </c>
       <c r="J193" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="194" customHeight="1" ht="15" spans="1:5">
@@ -5167,7 +5173,7 @@
     </row>
     <row r="195" customHeight="1" ht="15" spans="1:1">
       <c r="A195" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="196" customHeight="1" ht="15" spans="1:10">
@@ -5175,10 +5181,10 @@
         <v>14</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D196" s="8" t="n">
         <v>60000</v>
@@ -5229,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>3</v>
@@ -5264,7 +5270,7 @@
     </row>
     <row r="200" customHeight="1" ht="15" spans="1:1">
       <c r="A200" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="201" customHeight="1" ht="15" spans="1:10">
@@ -5272,10 +5278,10 @@
         <v>14</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D201" s="8" t="n">
         <v>6000</v>
@@ -5318,7 +5324,7 @@
     </row>
     <row r="203" customHeight="1" ht="15" spans="1:1">
       <c r="A203" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="204" customHeight="1" ht="15" spans="1:10">
@@ -5326,10 +5332,10 @@
         <v>14</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D204" s="8" t="n">
         <v>30000</v>
@@ -5380,7 +5386,7 @@
         <v>1</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>3</v>
@@ -5415,7 +5421,7 @@
     </row>
     <row r="208" customHeight="1" ht="15" spans="1:1">
       <c r="A208" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="209" customHeight="1" ht="15" spans="1:10">
@@ -5423,10 +5429,10 @@
         <v>14</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D209" s="8" t="n">
         <v>21000</v>
@@ -5447,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="J209" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="210" customHeight="1" ht="15" spans="1:5">
@@ -5469,7 +5475,7 @@
     </row>
     <row r="211" customHeight="1" ht="15" spans="1:1">
       <c r="A211" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="212" customHeight="1" ht="15" spans="1:10">
@@ -5477,10 +5483,10 @@
         <v>14</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D212" s="8" t="n">
         <v>205000</v>
@@ -5509,10 +5515,10 @@
         <v>14</v>
       </c>
       <c r="B213" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C213" s="7" t="s">
         <v>141</v>
-      </c>
-      <c r="C213" s="7" t="s">
-        <v>139</v>
       </c>
       <c r="D213" s="8" t="n">
         <v>205000</v>
@@ -5555,7 +5561,7 @@
     </row>
     <row r="215" customHeight="1" ht="15" spans="1:1">
       <c r="A215" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="216" customHeight="1" ht="15" spans="1:10">
@@ -5563,10 +5569,10 @@
         <v>14</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C216" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D216" s="8" t="n">
         <v>30000</v>
@@ -5587,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="J216" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="217" customHeight="1" ht="15" spans="1:5">
@@ -5609,7 +5615,7 @@
     </row>
     <row r="218" customHeight="1" ht="15" spans="1:1">
       <c r="A218" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="219" customHeight="1" ht="15" spans="1:10">
@@ -5617,10 +5623,10 @@
         <v>14</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D219" s="8" t="n">
         <v>6000</v>
@@ -5671,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>3</v>
@@ -5706,7 +5712,7 @@
     </row>
     <row r="223" customHeight="1" ht="15" spans="1:1">
       <c r="A223" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="224" customHeight="1" ht="15" spans="1:10">
@@ -5714,10 +5720,10 @@
         <v>14</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C224" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D224" s="8" t="n">
         <v>12000</v>
@@ -5738,7 +5744,7 @@
         <v>0</v>
       </c>
       <c r="J224" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="225" customHeight="1" ht="15" spans="1:5">
@@ -5760,7 +5766,7 @@
     </row>
     <row r="226" customHeight="1" ht="15" spans="1:1">
       <c r="A226" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="227" customHeight="1" ht="18.8" spans="1:10">
@@ -5768,10 +5774,10 @@
         <v>14</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D227" s="8" t="n">
         <v>14000</v>
@@ -5792,7 +5798,7 @@
         <v>0</v>
       </c>
       <c r="J227" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="228" customHeight="1" ht="15" spans="1:5">
@@ -5814,7 +5820,7 @@
     </row>
     <row r="229" customHeight="1" ht="15" spans="1:1">
       <c r="A229" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="230" customHeight="1" ht="15" spans="1:10">
@@ -5822,10 +5828,10 @@
         <v>14</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C230" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D230" s="8" t="n">
         <v>50000</v>
@@ -5846,7 +5852,7 @@
         <v>0</v>
       </c>
       <c r="J230" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="231" customHeight="1" ht="15" spans="1:5">
@@ -5868,7 +5874,7 @@
     </row>
     <row r="232" customHeight="1" ht="15" spans="1:1">
       <c r="A232" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="233" customHeight="1" ht="15" spans="1:10">
@@ -5876,10 +5882,10 @@
         <v>14</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D233" s="8" t="n">
         <v>100000</v>
@@ -5900,7 +5906,7 @@
         <v>0</v>
       </c>
       <c r="J233" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="234" customHeight="1" ht="15" spans="1:10">
@@ -5908,10 +5914,10 @@
         <v>14</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D234" s="8" t="n">
         <v>1000</v>
@@ -5932,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="J234" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="235" customHeight="1" ht="15" spans="1:5">
@@ -5962,7 +5968,7 @@
         <v>1</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>3</v>
@@ -5997,7 +6003,7 @@
     </row>
     <row r="238" customHeight="1" ht="15" spans="1:1">
       <c r="A238" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="239" customHeight="1" ht="15" spans="1:10">
@@ -6005,10 +6011,10 @@
         <v>14</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D239" s="8" t="n">
         <v>8028</v>
@@ -6051,7 +6057,7 @@
     </row>
     <row r="241" customHeight="1" ht="15" spans="1:1">
       <c r="A241" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="242" customHeight="1" ht="15" spans="1:10">
@@ -6059,10 +6065,10 @@
         <v>14</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C242" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D242" s="8" t="n">
         <v>24000</v>
@@ -6113,7 +6119,7 @@
         <v>1</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>3</v>
@@ -6159,7 +6165,7 @@
         <v>48</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D247" s="8" t="n">
         <v>2016</v>
@@ -6202,7 +6208,7 @@
     </row>
     <row r="249" customHeight="1" ht="15" spans="1:1">
       <c r="A249" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="250" customHeight="1" ht="15" spans="1:10">
@@ -6210,10 +6216,10 @@
         <v>14</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D250" s="8" t="n">
         <v>1020</v>
@@ -6264,7 +6270,7 @@
         <v>1</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>3</v>
@@ -6299,7 +6305,7 @@
     </row>
     <row r="254" customHeight="1" ht="15" spans="1:1">
       <c r="A254" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="255" customHeight="1" ht="15" spans="1:10">
@@ -6307,10 +6313,10 @@
         <v>14</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C255" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D255" s="8" t="n">
         <v>4032</v>
@@ -6353,7 +6359,7 @@
     </row>
     <row r="257" customHeight="1" ht="15" spans="1:1">
       <c r="A257" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="258" customHeight="1" ht="18.8" spans="1:10">
@@ -6361,10 +6367,10 @@
         <v>14</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D258" s="8" t="n">
         <v>320</v>
@@ -6407,7 +6413,7 @@
     </row>
     <row r="260" customHeight="1" ht="15" spans="1:1">
       <c r="A260" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="261" customHeight="1" ht="19.55" spans="1:10">
@@ -6415,10 +6421,10 @@
         <v>14</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D261" s="8" t="n">
         <v>512</v>
@@ -6439,7 +6445,7 @@
         <v>0</v>
       </c>
       <c r="J261" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="262" customHeight="1" ht="21.45" spans="1:10">
@@ -6447,10 +6453,10 @@
         <v>14</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C262" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D262" s="8" t="n">
         <v>1216</v>
@@ -6471,7 +6477,7 @@
         <v>0</v>
       </c>
       <c r="J262" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="263" customHeight="1" ht="15" spans="1:5">
@@ -6493,7 +6499,7 @@
     </row>
     <row r="264" customHeight="1" ht="15" spans="1:1">
       <c r="A264" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="265" customHeight="1" ht="20.25" spans="1:10">
@@ -6501,10 +6507,10 @@
         <v>14</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D265" s="8" t="n">
         <v>720</v>
@@ -6525,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="J265" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="266" customHeight="1" ht="15" spans="1:5">
@@ -6555,7 +6561,7 @@
         <v>1</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>3</v>
@@ -6590,7 +6596,7 @@
     </row>
     <row r="269" customHeight="1" ht="15" spans="1:1">
       <c r="A269" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="270" customHeight="1" ht="15" spans="1:10">
@@ -6598,10 +6604,10 @@
         <v>14</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D270" s="8" t="n">
         <v>72</v>
@@ -6622,7 +6628,7 @@
         <v>0</v>
       </c>
       <c r="J270" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="271" customHeight="1" ht="15" spans="1:10">
@@ -6630,10 +6636,10 @@
         <v>14</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D271" s="8" t="n">
         <v>50</v>
@@ -6654,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="J271" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="272" customHeight="1" ht="15" spans="1:10">
@@ -6662,10 +6668,10 @@
         <v>14</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D272" s="8" t="n">
         <v>1008</v>
@@ -6686,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="J272" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="273" customHeight="1" ht="15" spans="1:10">
@@ -6694,10 +6700,10 @@
         <v>14</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D273" s="8" t="n">
         <v>32</v>
@@ -6718,7 +6724,7 @@
         <v>0</v>
       </c>
       <c r="J273" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="274" customHeight="1" ht="15" spans="1:5">
@@ -6740,7 +6746,7 @@
     </row>
     <row r="275" customHeight="1" ht="15" spans="1:1">
       <c r="A275" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="276" customHeight="1" ht="15" spans="1:10">
@@ -6748,10 +6754,10 @@
         <v>14</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D276" s="8" t="n">
         <v>2640</v>
@@ -6772,7 +6778,7 @@
         <v>0</v>
       </c>
       <c r="J276" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="277" customHeight="1" ht="15" spans="1:10">
@@ -6780,10 +6786,10 @@
         <v>14</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D277" s="8" t="n">
         <v>300</v>
@@ -6804,7 +6810,7 @@
         <v>0</v>
       </c>
       <c r="J277" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="278" customHeight="1" ht="15" spans="1:5">
@@ -6834,7 +6840,7 @@
         <v>1</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>3</v>
@@ -6869,7 +6875,7 @@
     </row>
     <row r="281" customHeight="1" ht="15" spans="1:1">
       <c r="A281" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="282" customHeight="1" ht="15" spans="1:10">
@@ -6877,10 +6883,10 @@
         <v>14</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D282" s="8" t="n">
         <v>1008</v>
@@ -6901,7 +6907,7 @@
         <v>0</v>
       </c>
       <c r="J282" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="283" customHeight="1" ht="15" spans="1:5">
@@ -6934,7 +6940,7 @@
         <v>46</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D285" s="8" t="n">
         <v>2016</v>
@@ -6977,7 +6983,7 @@
     </row>
     <row r="287" customHeight="1" ht="15" spans="1:1">
       <c r="A287" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="288" customHeight="1" ht="15" spans="1:10">
@@ -6985,10 +6991,10 @@
         <v>14</v>
       </c>
       <c r="B288" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C288" s="7" t="s">
         <v>179</v>
-      </c>
-      <c r="C288" s="7" t="s">
-        <v>177</v>
       </c>
       <c r="D288" s="8" t="n">
         <v>648</v>
@@ -7031,7 +7037,7 @@
     </row>
     <row r="290" customHeight="1" ht="15" spans="1:1">
       <c r="A290" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="291" customHeight="1" ht="15" spans="1:10">
@@ -7039,10 +7045,10 @@
         <v>14</v>
       </c>
       <c r="B291" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C291" s="7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D291" s="8" t="n">
         <v>1500</v>
@@ -7093,7 +7099,7 @@
         <v>1</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>3</v>
@@ -7128,7 +7134,7 @@
     </row>
     <row r="295" customHeight="1" ht="15" spans="1:1">
       <c r="A295" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="296" customHeight="1" ht="15" spans="1:10">
@@ -7136,10 +7142,10 @@
         <v>14</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C296" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D296" s="8" t="n">
         <v>1512</v>
@@ -7168,10 +7174,10 @@
         <v>14</v>
       </c>
       <c r="B297" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C297" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D297" s="8" t="n">
         <v>1512</v>
@@ -7214,7 +7220,7 @@
     </row>
     <row r="299" customHeight="1" ht="15" spans="1:1">
       <c r="A299" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="300" customHeight="1" ht="15" spans="1:10">
@@ -7222,10 +7228,10 @@
         <v>14</v>
       </c>
       <c r="B300" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C300" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D300" s="8" t="n">
         <v>1512</v>
@@ -7246,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="J300" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="301" customHeight="1" ht="15" spans="1:5">

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="231">
   <si>
     <t>MATRIZ CNPJ: 40.357.820/0001-50R Y DOIS - 58082-025
  ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
@@ -305,15 +305,6 @@
     <t>949</t>
   </si>
   <si>
-    <t>MAPEMI - BRASIL DISTRIBUICAO E LOGISTICA FARMACEUTICA</t>
-  </si>
-  <si>
-    <t>775</t>
-  </si>
-  <si>
-    <t>LEANDRA LUIZA SILVA</t>
-  </si>
-  <si>
     <t>PHARMACEUTICA DISTRIBUIDORA</t>
   </si>
   <si>
@@ -469,7 +460,7 @@
     <t>972</t>
   </si>
   <si>
-    <t>1586 - CAMPO OPERATORIO NAO ESTERIL  45X50 - PCT 50 Observação: FATURAR IMEDIATO</t>
+    <t>1586 - CAMPO OPERATORIO NAO ESTERIL  45X50 - PCT 50Observação: FATURAR IMEDIATO</t>
   </si>
   <si>
     <t>1797 - CAMPO OPERATORIO NAO ESTERIL  45X50 S/ RX - PCT 50 UND Observação: FATURAR IMEDIATO</t>
@@ -478,7 +469,7 @@
     <t>973</t>
   </si>
   <si>
-    <t>1586 - CAMPO OPERATORIO NAO ESTERIL  45X50 - PCT 50Observação: FATURAR PEDIDO DIA 16/07/2026</t>
+    <t>1586 - CAMPO OPERATORIO NAO ESTERIL  45X50 - PCT 50 Observação: FATURAR PEDIDO DIA 16/07/2026</t>
   </si>
   <si>
     <t>1797 - CAMPO OPERATORIO NAO ESTERIL  45X50 S/ RX - PCT 50 UND Observação: FATURAR PEDIDO DIA 16/07/2026</t>
@@ -517,6 +508,12 @@
     <t xml:space="preserve">02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND </t>
   </si>
   <si>
+    <t>981</t>
+  </si>
+  <si>
+    <t>02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND  Observação: CLIENTE VEM RETIRAR</t>
+  </si>
+  <si>
     <t>DIFARMA FARMACEUTICA</t>
   </si>
   <si>
@@ -535,6 +532,18 @@
     <t>939</t>
   </si>
   <si>
+    <t>DROGUISTA CEARENSE</t>
+  </si>
+  <si>
+    <t>982</t>
+  </si>
+  <si>
+    <t>MED &amp; FARMA DISTRIBUIDORA DE MEDICAMENTOS E PRODUTOS</t>
+  </si>
+  <si>
+    <t>983</t>
+  </si>
+  <si>
     <t>MULTIMAIS ATACADO LTDA</t>
   </si>
   <si>
@@ -562,12 +571,6 @@
     <t xml:space="preserve">1643 - GAZE ESTÉRIL 13FIOS - PCT 10 UND </t>
   </si>
   <si>
-    <t>HOSPMED</t>
-  </si>
-  <si>
-    <t>929</t>
-  </si>
-  <si>
     <t>MERCANTE HOSPITALAR</t>
   </si>
   <si>
@@ -604,7 +607,7 @@
     <t>967</t>
   </si>
   <si>
-    <t>03 - GAZE ESTÉRIL 13FIOS - PCT 10 UND  Observação: BONIFICAÇÃO FATURAR JUNTO COM O PEDIDO DO CONTRATO 967</t>
+    <t>03 - GAZE ESTÉRIL 13FIOS - PCT 10 UND  Observação: BONIFICAÇÃO FATURAR JUNTOCOM O PEDIDO DO CONTRATO 967</t>
   </si>
   <si>
     <t>VAL MED PRODUTOS E EQUIP. MED. HOSPITALAR LTDA</t>
@@ -868,7 +871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L405"/>
+  <dimension ref="A1:L398"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
   <cols>
     <col customWidth="1" width="89.23828125" min="1" max="1"/>
@@ -3978,19 +3981,19 @@
         <v>98</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="D135" s="8" t="n">
-        <v>400</v>
+        <v>110</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>2396</v>
+        <v>768.9</v>
       </c>
       <c r="G135" s="10">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="H135" s="8" t="n">
         <v>0</v>
@@ -3999,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="8" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="136" customHeight="1" ht="19.4" spans="1:10">
@@ -4010,19 +4013,19 @@
         <v>98</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D136" s="8" t="n">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="E136" s="9" t="n">
-        <v>7.55</v>
+        <v>10.92</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>2038.5</v>
+        <v>3276</v>
       </c>
       <c r="G136" s="10">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="H136" s="8" t="n">
         <v>0</v>
@@ -4031,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="8" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="137" customHeight="1" ht="18.35" spans="1:10">
@@ -4042,19 +4045,19 @@
         <v>98</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D137" s="8" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>8.84</v>
+        <v>15.62</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>3315</v>
+        <v>3124</v>
       </c>
       <c r="G137" s="10">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="H137" s="8" t="n">
         <v>0</v>
@@ -4063,96 +4066,96 @@
         <v>0</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="138" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A138" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D138" s="8" t="n">
-        <v>240</v>
-      </c>
-      <c r="E138" s="9" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="F138" s="9" t="n">
-        <v>2750.4</v>
-      </c>
-      <c r="G138" s="10">
-        <v>46134</v>
-      </c>
-      <c r="H138" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="139" customHeight="1" ht="19.15" spans="1:10">
-      <c r="A139" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B139" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C139" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D139" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="E139" s="9" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="F139" s="9" t="n">
-        <v>3282</v>
-      </c>
-      <c r="G139" s="10">
-        <v>46134</v>
-      </c>
-      <c r="H139" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="140" customHeight="1" ht="15" spans="1:5">
-      <c r="A140" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B140" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" ht="15" spans="1:5">
+      <c r="A138" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B138" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C140" s="13" t="n">
-        <v>13781.9</v>
-      </c>
-      <c r="D140" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E140" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" customHeight="1" ht="15" spans="1:1">
-      <c r="A141" s="2" t="s">
+      <c r="C138" s="13" t="n">
+        <v>7168.9</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E138" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" ht="15" spans="1:1">
+      <c r="A139" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="142" customHeight="1" ht="19.9" spans="1:10">
+    <row r="140" customHeight="1" ht="18.6" spans="1:10">
+      <c r="A140" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="E140" s="9" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="F140" s="9" t="n">
+        <v>1923</v>
+      </c>
+      <c r="G140" s="10">
+        <v>46168</v>
+      </c>
+      <c r="H140" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" ht="19.4" spans="1:10">
+      <c r="A141" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D141" s="8" t="n">
+        <v>360</v>
+      </c>
+      <c r="E141" s="9" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="F141" s="9" t="n">
+        <v>2851.2</v>
+      </c>
+      <c r="G141" s="10">
+        <v>46168</v>
+      </c>
+      <c r="H141" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" ht="20" spans="1:10">
       <c r="A142" s="5" t="s">
         <v>14</v>
       </c>
@@ -4160,298 +4163,298 @@
         <v>101</v>
       </c>
       <c r="C142" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D142" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E142" s="9" t="n">
+        <v>9.37</v>
+      </c>
+      <c r="F142" s="9" t="n">
+        <v>702.75</v>
+      </c>
+      <c r="G142" s="10">
+        <v>46168</v>
+      </c>
+      <c r="H142" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" ht="15" spans="1:5">
+      <c r="A143" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B143" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C143" s="13" t="n">
+        <v>5476.95</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E143" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" ht="15" spans="1:1">
+      <c r="A144" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D142" s="8" t="n">
-        <v>110</v>
-      </c>
-      <c r="E142" s="9" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F142" s="9" t="n">
-        <v>768.9</v>
-      </c>
-      <c r="G142" s="10">
-        <v>46141</v>
-      </c>
-      <c r="H142" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="143" customHeight="1" ht="18.35" spans="1:10">
-      <c r="A143" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C143" s="7" t="s">
+    </row>
+    <row r="145" customHeight="1" ht="19.9" spans="1:10">
+      <c r="A145" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E145" s="9" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="F145" s="9" t="n">
+        <v>641</v>
+      </c>
+      <c r="G145" s="10">
+        <v>46113</v>
+      </c>
+      <c r="H145" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" ht="19.3" spans="1:10">
+      <c r="A146" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D146" s="8" t="n">
+        <v>360</v>
+      </c>
+      <c r="E146" s="9" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="F146" s="9" t="n">
+        <v>2851.2</v>
+      </c>
+      <c r="G146" s="10">
+        <v>46113</v>
+      </c>
+      <c r="H146" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A147" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D147" s="8" t="n">
+        <v>750</v>
+      </c>
+      <c r="E147" s="9" t="n">
+        <v>9.37</v>
+      </c>
+      <c r="F147" s="9" t="n">
+        <v>7027.5</v>
+      </c>
+      <c r="G147" s="10">
+        <v>46113</v>
+      </c>
+      <c r="H147" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A148" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C148" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D143" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="E143" s="9" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="F143" s="9" t="n">
-        <v>3276</v>
-      </c>
-      <c r="G143" s="10">
-        <v>46141</v>
-      </c>
-      <c r="H143" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="144" customHeight="1" ht="20.15" spans="1:10">
-      <c r="A144" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B144" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C144" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D144" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="E144" s="9" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="F144" s="9" t="n">
-        <v>3124</v>
-      </c>
-      <c r="G144" s="10">
-        <v>46141</v>
-      </c>
-      <c r="H144" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="145" customHeight="1" ht="15" spans="1:5">
-      <c r="A145" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B145" s="12" t="s">
+      <c r="D148" s="8" t="n">
+        <v>360</v>
+      </c>
+      <c r="E148" s="9" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="F148" s="9" t="n">
+        <v>4330.8</v>
+      </c>
+      <c r="G148" s="10">
+        <v>46113</v>
+      </c>
+      <c r="H148" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" ht="15" spans="1:5">
+      <c r="A149" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B149" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C145" s="13" t="n">
-        <v>7168.9</v>
-      </c>
-      <c r="D145" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E145" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A146" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" customHeight="1" ht="15" spans="1:12">
-      <c r="A147" s="2" t="s">
+      <c r="C149" s="13" t="n">
+        <v>14850.5</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E149" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A150" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" ht="15" spans="1:12">
+      <c r="A151" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B151" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C151" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D147" s="2" t="s">
+      <c r="D151" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E147" s="4" t="s">
+      <c r="E151" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F147" s="4" t="s">
+      <c r="F151" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G147" s="4" t="s">
+      <c r="G151" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H147" s="4" t="s">
+      <c r="H151" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I147" s="4" t="s">
+      <c r="I151" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J147" s="4" t="s">
+      <c r="J151" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K147" s="2" t="s">
+      <c r="K151" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L147" s="4" t="s">
+      <c r="L151" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="148" customHeight="1" ht="15" spans="1:1">
-      <c r="A148" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="149" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A149" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B149" s="6" t="s">
+    <row r="152" customHeight="1" ht="15" spans="1:1">
+      <c r="A152" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C149" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D149" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="E149" s="9" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="F149" s="9" t="n">
-        <v>1923</v>
-      </c>
-      <c r="G149" s="10">
-        <v>46168</v>
-      </c>
-      <c r="H149" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I149" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" s="8" t="s">
+    </row>
+    <row r="153" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A153" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D153" s="8" t="n">
+        <v>550</v>
+      </c>
+      <c r="E153" s="9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F153" s="9" t="n">
+        <v>2860</v>
+      </c>
+      <c r="G153" s="10">
+        <v>46164</v>
+      </c>
+      <c r="H153" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="150" customHeight="1" ht="19.4" spans="1:10">
-      <c r="A150" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C150" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D150" s="8" t="n">
-        <v>360</v>
-      </c>
-      <c r="E150" s="9" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="F150" s="9" t="n">
-        <v>2851.2</v>
-      </c>
-      <c r="G150" s="10">
-        <v>46168</v>
-      </c>
-      <c r="H150" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I150" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="151" customHeight="1" ht="18.35" spans="1:10">
-      <c r="A151" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B151" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C151" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D151" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="E151" s="9" t="n">
-        <v>9.37</v>
-      </c>
-      <c r="F151" s="9" t="n">
-        <v>702.75</v>
-      </c>
-      <c r="G151" s="10">
-        <v>46168</v>
-      </c>
-      <c r="H151" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I151" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="152" customHeight="1" ht="15" spans="1:5">
-      <c r="A152" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B152" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C152" s="13" t="n">
-        <v>5476.95</v>
-      </c>
-      <c r="D152" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E152" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" customHeight="1" ht="15" spans="1:1">
-      <c r="A153" s="2" t="s">
+    <row r="154" customHeight="1" ht="19.4" spans="1:10">
+      <c r="A154" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B154" s="6" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="154" customHeight="1" ht="18.6" spans="1:10">
-      <c r="A154" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>106</v>
-      </c>
       <c r="C154" s="7" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="D154" s="8" t="n">
-        <v>100</v>
+        <v>560</v>
       </c>
       <c r="E154" s="9" t="n">
-        <v>6.41</v>
+        <v>7.5</v>
       </c>
       <c r="F154" s="9" t="n">
-        <v>641</v>
+        <v>4200</v>
       </c>
       <c r="G154" s="10">
-        <v>46113</v>
+        <v>46164</v>
       </c>
       <c r="H154" s="8" t="n">
         <v>0</v>
@@ -4463,27 +4466,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="155" customHeight="1" ht="19.4" spans="1:10">
+    <row r="155" customHeight="1" ht="18.35" spans="1:10">
       <c r="A155" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B155" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C155" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C155" s="7" t="s">
-        <v>69</v>
-      </c>
       <c r="D155" s="8" t="n">
-        <v>360</v>
+        <v>550</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>7.92</v>
+        <v>5.2</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>2851.2</v>
+        <v>2860</v>
       </c>
       <c r="G155" s="10">
-        <v>46113</v>
+        <v>46164</v>
       </c>
       <c r="H155" s="8" t="n">
         <v>0</v>
@@ -4495,27 +4498,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="156" customHeight="1" ht="20" spans="1:10">
+    <row r="156" customHeight="1" ht="20.4" spans="1:10">
       <c r="A156" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="D156" s="8" t="n">
-        <v>750</v>
+        <v>560</v>
       </c>
       <c r="E156" s="9" t="n">
-        <v>9.37</v>
+        <v>7.5</v>
       </c>
       <c r="F156" s="9" t="n">
-        <v>7027.5</v>
+        <v>4200</v>
       </c>
       <c r="G156" s="10">
-        <v>46113</v>
+        <v>46164</v>
       </c>
       <c r="H156" s="8" t="n">
         <v>0</v>
@@ -4527,27 +4530,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="157" customHeight="1" ht="18.45" spans="1:10">
+    <row r="157" customHeight="1" ht="19.15" spans="1:10">
       <c r="A157" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="D157" s="8" t="n">
-        <v>360</v>
+        <v>250</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>12.03</v>
+        <v>12.1</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>4330.8</v>
+        <v>3025</v>
       </c>
       <c r="G157" s="10">
-        <v>46113</v>
+        <v>46164</v>
       </c>
       <c r="H157" s="8" t="n">
         <v>0</v>
@@ -4567,7 +4570,7 @@
         <v>20</v>
       </c>
       <c r="C158" s="13" t="n">
-        <v>14850.5</v>
+        <v>17145</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>19</v>
@@ -4576,1252 +4579,1231 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A159" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" customHeight="1" ht="15" spans="1:12">
-      <c r="A160" s="2" t="s">
+    <row r="159" customHeight="1" ht="15" spans="1:1">
+      <c r="A159" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" ht="19.9" spans="1:10">
+      <c r="A160" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D160" s="8" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E160" s="9" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="F160" s="9" t="n">
+        <v>7507.5</v>
+      </c>
+      <c r="G160" s="10">
+        <v>46175</v>
+      </c>
+      <c r="H160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" ht="15" spans="1:5">
+      <c r="A161" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B161" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C161" s="13" t="n">
+        <v>7507.5</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E161" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A162" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" ht="15" spans="1:12">
+      <c r="A163" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B163" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="C163" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D160" s="2" t="s">
+      <c r="D163" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E160" s="4" t="s">
+      <c r="E163" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F160" s="4" t="s">
+      <c r="F163" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G160" s="4" t="s">
+      <c r="G163" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H160" s="4" t="s">
+      <c r="H163" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I160" s="4" t="s">
+      <c r="I163" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J160" s="4" t="s">
+      <c r="J163" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K160" s="2" t="s">
+      <c r="K163" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L160" s="4" t="s">
+      <c r="L163" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="161" customHeight="1" ht="15" spans="1:1">
-      <c r="A161" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="162" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A162" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B162" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C162" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D162" s="8" t="n">
-        <v>550</v>
-      </c>
-      <c r="E162" s="9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F162" s="9" t="n">
-        <v>2860</v>
-      </c>
-      <c r="G162" s="10">
+    <row r="164" customHeight="1" ht="15" spans="1:1">
+      <c r="A164" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" ht="47.15" spans="1:10">
+      <c r="A165" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D165" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="E165" s="9" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="F165" s="9" t="n">
+        <v>3228</v>
+      </c>
+      <c r="G165" s="10">
+        <v>46168</v>
+      </c>
+      <c r="H165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" ht="47.85" spans="1:10">
+      <c r="A166" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D166" s="8" t="n">
+        <v>525</v>
+      </c>
+      <c r="E166" s="9" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="F166" s="9" t="n">
+        <v>4168.5</v>
+      </c>
+      <c r="G166" s="10">
+        <v>46168</v>
+      </c>
+      <c r="H166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" ht="47" spans="1:10">
+      <c r="A167" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D167" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="E167" s="9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F167" s="9" t="n">
+        <v>6180</v>
+      </c>
+      <c r="G167" s="10">
+        <v>46168</v>
+      </c>
+      <c r="H167" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="168" customHeight="1" ht="15" spans="1:5">
+      <c r="A168" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B168" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C168" s="13" t="n">
+        <v>13576.5</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E168" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A169" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" ht="15" spans="1:12">
+      <c r="A170" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E170" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G170" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H170" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I170" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J170" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K170" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L170" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="171" customHeight="1" ht="15" spans="1:1">
+      <c r="A171" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" ht="30.35" spans="1:10">
+      <c r="A172" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D172" s="8" t="n">
+        <v>660</v>
+      </c>
+      <c r="E172" s="9" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="F172" s="9" t="n">
+        <v>2996.4</v>
+      </c>
+      <c r="G172" s="10">
+        <v>46188</v>
+      </c>
+      <c r="H172" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" ht="28.15" spans="1:10">
+      <c r="A173" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D173" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="E173" s="9" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="F173" s="9" t="n">
+        <v>1848</v>
+      </c>
+      <c r="G173" s="10">
+        <v>46188</v>
+      </c>
+      <c r="H173" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" ht="29.15" spans="1:10">
+      <c r="A174" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D174" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E174" s="9" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="F174" s="9" t="n">
+        <v>698.4</v>
+      </c>
+      <c r="G174" s="10">
+        <v>46188</v>
+      </c>
+      <c r="H174" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" ht="29.4" spans="1:10">
+      <c r="A175" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D175" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="E175" s="9" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="F175" s="9" t="n">
+        <v>1363.5</v>
+      </c>
+      <c r="G175" s="10">
+        <v>46188</v>
+      </c>
+      <c r="H175" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" ht="29.15" spans="1:10">
+      <c r="A176" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D176" s="8" t="n">
+        <v>280</v>
+      </c>
+      <c r="E176" s="9" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="F176" s="9" t="n">
+        <v>2324</v>
+      </c>
+      <c r="G176" s="10">
+        <v>46188</v>
+      </c>
+      <c r="H176" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177" customHeight="1" ht="28.55" spans="1:10">
+      <c r="A177" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D177" s="8" t="n">
+        <v>240</v>
+      </c>
+      <c r="E177" s="9" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="F177" s="9" t="n">
+        <v>2829.6</v>
+      </c>
+      <c r="G177" s="10">
+        <v>46188</v>
+      </c>
+      <c r="H177" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178" customHeight="1" ht="15" spans="1:5">
+      <c r="A178" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B178" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C178" s="13" t="n">
+        <v>12059.9</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E178" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A179" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" ht="15" spans="1:12">
+      <c r="A180" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E180" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G180" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H180" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I180" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J180" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K180" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L180" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" ht="15" spans="1:1">
+      <c r="A181" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" ht="47.15" spans="1:10">
+      <c r="A182" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D182" s="8" t="n">
+        <v>200100</v>
+      </c>
+      <c r="E182" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F182" s="9" t="n">
+        <v>820410</v>
+      </c>
+      <c r="G182" s="10">
+        <v>46119</v>
+      </c>
+      <c r="H182" s="8" t="n">
+        <v>75900</v>
+      </c>
+      <c r="I182" s="11" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="J182" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" ht="15" spans="1:5">
+      <c r="A183" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C183" s="13" t="n">
+        <v>820410</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E183" s="14" t="n">
+        <v>75900</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" ht="15" spans="1:1">
+      <c r="A184" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" ht="19.4" spans="1:10">
+      <c r="A185" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D185" s="8" t="n">
+        <v>50100</v>
+      </c>
+      <c r="E185" s="9" t="n">
+        <v>4.517</v>
+      </c>
+      <c r="F185" s="9" t="n">
+        <v>226301.7</v>
+      </c>
+      <c r="G185" s="10">
+        <v>46156</v>
+      </c>
+      <c r="H185" s="8" t="n">
+        <v>17100</v>
+      </c>
+      <c r="I185" s="11" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="J185" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" ht="20.25" spans="1:10">
+      <c r="A186" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D186" s="8" t="n">
+        <v>50100</v>
+      </c>
+      <c r="E186" s="9" t="n">
+        <v>4.517</v>
+      </c>
+      <c r="F186" s="9" t="n">
+        <v>226301.7</v>
+      </c>
+      <c r="G186" s="10">
+        <v>46163</v>
+      </c>
+      <c r="H186" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A187" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D187" s="8" t="n">
+        <v>20100</v>
+      </c>
+      <c r="E187" s="9" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="F187" s="9" t="n">
+        <v>90852</v>
+      </c>
+      <c r="G187" s="10">
+        <v>46167</v>
+      </c>
+      <c r="H187" s="8" t="n">
+        <v>6750</v>
+      </c>
+      <c r="I187" s="11" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="J187" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" ht="15" spans="1:5">
+      <c r="A188" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B188" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C188" s="13" t="n">
+        <v>543455.4</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E188" s="14" t="n">
+        <v>23850</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" ht="15" spans="1:1">
+      <c r="A189" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" ht="18.7" spans="1:10">
+      <c r="A190" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D190" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E190" s="9" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="F190" s="9" t="n">
+        <v>7935</v>
+      </c>
+      <c r="G190" s="10">
+        <v>46188</v>
+      </c>
+      <c r="H190" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" ht="15" spans="1:5">
+      <c r="A191" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C191" s="13" t="n">
+        <v>7935</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E191" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A192" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" ht="15" spans="1:12">
+      <c r="A193" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E193" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G193" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H193" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I193" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J193" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K193" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L193" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="194" customHeight="1" ht="15" spans="1:1">
+      <c r="A194" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="195" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A195" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D195" s="8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E195" s="9" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="F195" s="9" t="n">
+        <v>44550</v>
+      </c>
+      <c r="G195" s="10">
+        <v>46190</v>
+      </c>
+      <c r="H195" s="8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I195" s="11" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="J195" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="196" customHeight="1" ht="15" spans="1:5">
+      <c r="A196" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B196" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C196" s="13" t="n">
+        <v>44550</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E196" s="14" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="197" customHeight="1" ht="15" spans="1:1">
+      <c r="A197" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="198" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A198" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D198" s="8" t="n">
+        <v>50100</v>
+      </c>
+      <c r="E198" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F198" s="9" t="n">
+        <v>220440</v>
+      </c>
+      <c r="G198" s="10">
         <v>46164</v>
       </c>
-      <c r="H162" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" s="8" t="s">
+      <c r="H198" s="8" t="n">
+        <v>28650</v>
+      </c>
+      <c r="I198" s="11" t="n">
+        <v>57.19</v>
+      </c>
+      <c r="J198" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="199" customHeight="1" ht="15" spans="1:5">
+      <c r="A199" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B199" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C199" s="13" t="n">
+        <v>220440</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E199" s="14" t="n">
+        <v>28650</v>
+      </c>
+    </row>
+    <row r="200" customHeight="1" ht="15" spans="1:1">
+      <c r="A200" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" ht="29.95" spans="1:10">
+      <c r="A201" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D201" s="8" t="n">
+        <v>10200</v>
+      </c>
+      <c r="E201" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F201" s="9" t="n">
+        <v>25500</v>
+      </c>
+      <c r="G201" s="10">
+        <v>46176</v>
+      </c>
+      <c r="H201" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" ht="15" spans="1:5">
+      <c r="A202" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B202" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C202" s="13" t="n">
+        <v>25500</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E202" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A203" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" ht="15" spans="1:12">
+      <c r="A204" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E204" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G204" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H204" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I204" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J204" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K204" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L204" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" ht="15" spans="1:1">
+      <c r="A205" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A206" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D206" s="8" t="n">
+        <v>3408</v>
+      </c>
+      <c r="E206" s="9" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="F206" s="9" t="n">
+        <v>153019.2</v>
+      </c>
+      <c r="G206" s="10">
+        <v>46162</v>
+      </c>
+      <c r="H206" s="8" t="n">
+        <v>1104</v>
+      </c>
+      <c r="I206" s="11" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="J206" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="163" customHeight="1" ht="19.4" spans="1:10">
-      <c r="A163" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B163" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C163" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D163" s="8" t="n">
-        <v>560</v>
-      </c>
-      <c r="E163" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F163" s="9" t="n">
-        <v>4200</v>
-      </c>
-      <c r="G163" s="10">
-        <v>46164</v>
-      </c>
-      <c r="H163" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J163" s="8" t="s">
+    <row r="207" customHeight="1" ht="15" spans="1:5">
+      <c r="A207" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B207" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C207" s="13" t="n">
+        <v>153019.2</v>
+      </c>
+      <c r="D207" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E207" s="14" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" ht="15" spans="1:1">
+      <c r="A208" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A209" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C209" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D209" s="8" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E209" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="F209" s="9" t="n">
+        <v>44352</v>
+      </c>
+      <c r="G209" s="10">
+        <v>46188</v>
+      </c>
+      <c r="H209" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" ht="15" spans="1:5">
+      <c r="A210" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B210" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C210" s="13" t="n">
+        <v>44352</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E210" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" customHeight="1" ht="15" spans="1:1">
+      <c r="A211" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="212" customHeight="1" ht="29.95" spans="1:10">
+      <c r="A212" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C212" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D212" s="8" t="n">
+        <v>252</v>
+      </c>
+      <c r="E212" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="F212" s="9" t="n">
+        <v>10836</v>
+      </c>
+      <c r="G212" s="10">
+        <v>46189</v>
+      </c>
+      <c r="H212" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="164" customHeight="1" ht="18.35" spans="1:10">
-      <c r="A164" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B164" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C164" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D164" s="8" t="n">
-        <v>550</v>
-      </c>
-      <c r="E164" s="9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F164" s="9" t="n">
-        <v>2860</v>
-      </c>
-      <c r="G164" s="10">
-        <v>46164</v>
-      </c>
-      <c r="H164" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I164" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J164" s="8" t="s">
+    <row r="213" customHeight="1" ht="29.25" spans="1:10">
+      <c r="A213" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C213" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D213" s="8" t="n">
+        <v>504</v>
+      </c>
+      <c r="E213" s="9" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F213" s="9" t="n">
+        <v>20412</v>
+      </c>
+      <c r="G213" s="10">
+        <v>46189</v>
+      </c>
+      <c r="H213" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="165" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A165" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B165" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C165" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D165" s="8" t="n">
-        <v>560</v>
-      </c>
-      <c r="E165" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F165" s="9" t="n">
-        <v>4200</v>
-      </c>
-      <c r="G165" s="10">
-        <v>46164</v>
-      </c>
-      <c r="H165" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I165" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J165" s="8" t="s">
+    <row r="214" customHeight="1" ht="27.8" spans="1:10">
+      <c r="A214" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C214" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D214" s="8" t="n">
+        <v>252</v>
+      </c>
+      <c r="E214" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="F214" s="9" t="n">
+        <v>10836</v>
+      </c>
+      <c r="G214" s="10">
+        <v>46189</v>
+      </c>
+      <c r="H214" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="166" customHeight="1" ht="19.15" spans="1:10">
-      <c r="A166" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B166" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C166" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D166" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E166" s="9" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F166" s="9" t="n">
-        <v>3025</v>
-      </c>
-      <c r="G166" s="10">
-        <v>46164</v>
-      </c>
-      <c r="H166" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I166" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="167" customHeight="1" ht="15" spans="1:5">
-      <c r="A167" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B167" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C167" s="13" t="n">
-        <v>17145</v>
-      </c>
-      <c r="D167" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E167" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" customHeight="1" ht="15" spans="1:1">
-      <c r="A168" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="169" customHeight="1" ht="19.9" spans="1:10">
-      <c r="A169" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B169" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C169" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D169" s="8" t="n">
-        <v>1050</v>
-      </c>
-      <c r="E169" s="9" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="F169" s="9" t="n">
-        <v>7507.5</v>
-      </c>
-      <c r="G169" s="10">
-        <v>46175</v>
-      </c>
-      <c r="H169" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I169" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J169" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="170" customHeight="1" ht="15" spans="1:5">
-      <c r="A170" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B170" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C170" s="13" t="n">
-        <v>7507.5</v>
-      </c>
-      <c r="D170" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E170" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A171" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" customHeight="1" ht="15" spans="1:12">
-      <c r="A172" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E172" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F172" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G172" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H172" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I172" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J172" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K172" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L172" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="173" customHeight="1" ht="15" spans="1:1">
-      <c r="A173" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="174" customHeight="1" ht="47.15" spans="1:10">
-      <c r="A174" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B174" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C174" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D174" s="8" t="n">
-        <v>600</v>
-      </c>
-      <c r="E174" s="9" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="F174" s="9" t="n">
-        <v>3228</v>
-      </c>
-      <c r="G174" s="10">
-        <v>46168</v>
-      </c>
-      <c r="H174" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I174" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J174" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="175" customHeight="1" ht="47.85" spans="1:10">
-      <c r="A175" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B175" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C175" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D175" s="8" t="n">
-        <v>525</v>
-      </c>
-      <c r="E175" s="9" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="F175" s="9" t="n">
-        <v>4168.5</v>
-      </c>
-      <c r="G175" s="10">
-        <v>46168</v>
-      </c>
-      <c r="H175" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I175" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J175" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="176" customHeight="1" ht="47" spans="1:10">
-      <c r="A176" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B176" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C176" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D176" s="8" t="n">
-        <v>600</v>
-      </c>
-      <c r="E176" s="9" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="F176" s="9" t="n">
-        <v>6180</v>
-      </c>
-      <c r="G176" s="10">
-        <v>46168</v>
-      </c>
-      <c r="H176" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I176" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J176" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="177" customHeight="1" ht="15" spans="1:5">
-      <c r="A177" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B177" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C177" s="13" t="n">
-        <v>13576.5</v>
-      </c>
-      <c r="D177" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E177" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A178" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" customHeight="1" ht="15" spans="1:12">
-      <c r="A179" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E179" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F179" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G179" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H179" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I179" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J179" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K179" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L179" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="180" customHeight="1" ht="15" spans="1:1">
-      <c r="A180" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="181" customHeight="1" ht="30.35" spans="1:10">
-      <c r="A181" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C181" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D181" s="8" t="n">
-        <v>660</v>
-      </c>
-      <c r="E181" s="9" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="F181" s="9" t="n">
-        <v>2996.4</v>
-      </c>
-      <c r="G181" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H181" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I181" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J181" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="182" customHeight="1" ht="28.15" spans="1:10">
-      <c r="A182" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B182" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C182" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D182" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="E182" s="9" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="F182" s="9" t="n">
-        <v>1848</v>
-      </c>
-      <c r="G182" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H182" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I182" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J182" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="183" customHeight="1" ht="29.15" spans="1:10">
-      <c r="A183" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B183" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C183" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="D183" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="E183" s="9" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="F183" s="9" t="n">
-        <v>698.4</v>
-      </c>
-      <c r="G183" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H183" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I183" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J183" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="184" customHeight="1" ht="29.4" spans="1:10">
-      <c r="A184" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B184" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C184" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="D184" s="8" t="n">
+    <row r="215" customHeight="1" ht="28.05" spans="1:10">
+      <c r="A215" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B215" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E184" s="9" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="F184" s="9" t="n">
-        <v>1363.5</v>
-      </c>
-      <c r="G184" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H184" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I184" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J184" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="185" customHeight="1" ht="29.15" spans="1:10">
-      <c r="A185" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B185" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C185" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D185" s="8" t="n">
-        <v>280</v>
-      </c>
-      <c r="E185" s="9" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="F185" s="9" t="n">
-        <v>2324</v>
-      </c>
-      <c r="G185" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H185" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I185" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J185" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="186" customHeight="1" ht="28.55" spans="1:10">
-      <c r="A186" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B186" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C186" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D186" s="8" t="n">
-        <v>240</v>
-      </c>
-      <c r="E186" s="9" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="F186" s="9" t="n">
-        <v>2829.6</v>
-      </c>
-      <c r="G186" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H186" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I186" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J186" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="187" customHeight="1" ht="15" spans="1:5">
-      <c r="A187" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B187" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C187" s="13" t="n">
-        <v>12059.9</v>
-      </c>
-      <c r="D187" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E187" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A188" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" customHeight="1" ht="15" spans="1:12">
-      <c r="A189" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E189" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F189" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G189" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H189" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I189" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J189" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K189" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L189" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="190" customHeight="1" ht="15" spans="1:1">
-      <c r="A190" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="191" customHeight="1" ht="47.15" spans="1:10">
-      <c r="A191" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B191" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C191" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D191" s="8" t="n">
-        <v>200100</v>
-      </c>
-      <c r="E191" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F191" s="9" t="n">
-        <v>820410</v>
-      </c>
-      <c r="G191" s="10">
-        <v>46119</v>
-      </c>
-      <c r="H191" s="8" t="n">
-        <v>75900</v>
-      </c>
-      <c r="I191" s="11" t="n">
-        <v>37.93</v>
-      </c>
-      <c r="J191" s="8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="192" customHeight="1" ht="15" spans="1:5">
-      <c r="A192" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B192" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C192" s="13" t="n">
-        <v>820410</v>
-      </c>
-      <c r="D192" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E192" s="14" t="n">
-        <v>75900</v>
-      </c>
-    </row>
-    <row r="193" customHeight="1" ht="15" spans="1:1">
-      <c r="A193" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="194" customHeight="1" ht="19.4" spans="1:10">
-      <c r="A194" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B194" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C194" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D194" s="8" t="n">
-        <v>50100</v>
-      </c>
-      <c r="E194" s="9" t="n">
-        <v>4.517</v>
-      </c>
-      <c r="F194" s="9" t="n">
-        <v>226301.7</v>
-      </c>
-      <c r="G194" s="10">
-        <v>46156</v>
-      </c>
-      <c r="H194" s="8" t="n">
-        <v>17100</v>
-      </c>
-      <c r="I194" s="11" t="n">
-        <v>34.13</v>
-      </c>
-      <c r="J194" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="195" customHeight="1" ht="20.25" spans="1:10">
-      <c r="A195" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B195" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C195" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D195" s="8" t="n">
-        <v>50100</v>
-      </c>
-      <c r="E195" s="9" t="n">
-        <v>4.517</v>
-      </c>
-      <c r="F195" s="9" t="n">
-        <v>226301.7</v>
-      </c>
-      <c r="G195" s="10">
-        <v>46163</v>
-      </c>
-      <c r="H195" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I195" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J195" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="196" customHeight="1" ht="18.8" spans="1:10">
-      <c r="A196" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B196" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C196" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D196" s="8" t="n">
-        <v>20100</v>
-      </c>
-      <c r="E196" s="9" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="F196" s="9" t="n">
-        <v>90852</v>
-      </c>
-      <c r="G196" s="10">
-        <v>46167</v>
-      </c>
-      <c r="H196" s="8" t="n">
-        <v>6750</v>
-      </c>
-      <c r="I196" s="11" t="n">
-        <v>33.58</v>
-      </c>
-      <c r="J196" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="197" customHeight="1" ht="15" spans="1:5">
-      <c r="A197" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B197" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C197" s="13" t="n">
-        <v>543455.4</v>
-      </c>
-      <c r="D197" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E197" s="14" t="n">
-        <v>23850</v>
-      </c>
-    </row>
-    <row r="198" customHeight="1" ht="15" spans="1:1">
-      <c r="A198" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="199" customHeight="1" ht="18.7" spans="1:10">
-      <c r="A199" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B199" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C199" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D199" s="8" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E199" s="9" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="F199" s="9" t="n">
-        <v>7935</v>
-      </c>
-      <c r="G199" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H199" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I199" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J199" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="200" customHeight="1" ht="15" spans="1:5">
-      <c r="A200" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B200" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C200" s="13" t="n">
-        <v>7935</v>
-      </c>
-      <c r="D200" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E200" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A201" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" customHeight="1" ht="15" spans="1:12">
-      <c r="A202" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E202" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F202" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G202" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H202" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I202" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J202" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K202" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L202" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="203" customHeight="1" ht="15" spans="1:1">
-      <c r="A203" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="204" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A204" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B204" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C204" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D204" s="8" t="n">
-        <v>9000</v>
-      </c>
-      <c r="E204" s="9" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="F204" s="9" t="n">
-        <v>44550</v>
-      </c>
-      <c r="G204" s="10">
-        <v>46190</v>
-      </c>
-      <c r="H204" s="8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I204" s="11" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J204" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="205" customHeight="1" ht="15" spans="1:5">
-      <c r="A205" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B205" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C205" s="13" t="n">
-        <v>44550</v>
-      </c>
-      <c r="D205" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E205" s="14" t="n">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="206" customHeight="1" ht="15" spans="1:1">
-      <c r="A206" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="207" customHeight="1" ht="18.35" spans="1:10">
-      <c r="A207" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B207" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C207" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D207" s="8" t="n">
-        <v>50100</v>
-      </c>
-      <c r="E207" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F207" s="9" t="n">
-        <v>220440</v>
-      </c>
-      <c r="G207" s="10">
-        <v>46164</v>
-      </c>
-      <c r="H207" s="8" t="n">
-        <v>28650</v>
-      </c>
-      <c r="I207" s="11" t="n">
-        <v>57.19</v>
-      </c>
-      <c r="J207" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="208" customHeight="1" ht="15" spans="1:5">
-      <c r="A208" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B208" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C208" s="13" t="n">
-        <v>220440</v>
-      </c>
-      <c r="D208" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E208" s="14" t="n">
-        <v>28650</v>
-      </c>
-    </row>
-    <row r="209" customHeight="1" ht="15" spans="1:1">
-      <c r="A209" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="210" customHeight="1" ht="29.95" spans="1:10">
-      <c r="A210" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B210" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C210" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D210" s="8" t="n">
-        <v>10200</v>
-      </c>
-      <c r="E210" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F210" s="9" t="n">
-        <v>25500</v>
-      </c>
-      <c r="G210" s="10">
-        <v>46176</v>
-      </c>
-      <c r="H210" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I210" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J210" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="211" customHeight="1" ht="15" spans="1:5">
-      <c r="A211" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B211" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C211" s="13" t="n">
-        <v>25500</v>
-      </c>
-      <c r="D211" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E211" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A212" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" customHeight="1" ht="15" spans="1:12">
-      <c r="A213" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B213" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E213" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F213" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G213" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H213" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I213" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J213" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K213" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L213" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="214" customHeight="1" ht="15" spans="1:1">
-      <c r="A214" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="215" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A215" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B215" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="C215" s="7" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D215" s="8" t="n">
-        <v>3408</v>
+        <v>504</v>
       </c>
       <c r="E215" s="9" t="n">
-        <v>44.9</v>
+        <v>40.5</v>
       </c>
       <c r="F215" s="9" t="n">
-        <v>153019.2</v>
+        <v>20412</v>
       </c>
       <c r="G215" s="10">
-        <v>46162</v>
+        <v>46189</v>
       </c>
       <c r="H215" s="8" t="n">
-        <v>1104</v>
+        <v>0</v>
       </c>
       <c r="I215" s="11" t="n">
-        <v>32.39</v>
+        <v>0</v>
       </c>
       <c r="J215" s="8" t="s">
         <v>23</v>
@@ -5835,192 +5817,192 @@
         <v>20</v>
       </c>
       <c r="C216" s="13" t="n">
-        <v>153019.2</v>
+        <v>62496</v>
       </c>
       <c r="D216" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E216" s="14" t="n">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="217" customHeight="1" ht="15" spans="1:1">
-      <c r="A217" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="218" customHeight="1" ht="18.35" spans="1:10">
-      <c r="A218" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B218" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C218" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D218" s="8" t="n">
-        <v>1008</v>
-      </c>
-      <c r="E218" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A217" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" ht="15" spans="1:12">
+      <c r="A218" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E218" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G218" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H218" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I218" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J218" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K218" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L218" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" ht="15" spans="1:1">
+      <c r="A219" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A220" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C220" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D220" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="E220" s="9" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F220" s="9" t="n">
+        <v>5700</v>
+      </c>
+      <c r="G220" s="10">
+        <v>46188</v>
+      </c>
+      <c r="H220" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" ht="15" spans="1:5">
+      <c r="A221" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B221" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C221" s="13" t="n">
+        <v>5700</v>
+      </c>
+      <c r="D221" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E221" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" customHeight="1" ht="15" spans="1:1">
+      <c r="A222" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A223" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D223" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E223" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="F218" s="9" t="n">
-        <v>44352</v>
-      </c>
-      <c r="G218" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H218" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I218" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J218" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="219" customHeight="1" ht="15" spans="1:5">
-      <c r="A219" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B219" s="12" t="s">
+      <c r="F223" s="9" t="n">
+        <v>52800</v>
+      </c>
+      <c r="G223" s="10">
+        <v>46190</v>
+      </c>
+      <c r="H223" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="224" customHeight="1" ht="15" spans="1:5">
+      <c r="A224" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B224" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C219" s="13" t="n">
-        <v>44352</v>
-      </c>
-      <c r="D219" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E219" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" customHeight="1" ht="15" spans="1:1">
-      <c r="A220" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="221" customHeight="1" ht="18.8" spans="1:10">
-      <c r="A221" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B221" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C221" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D221" s="8" t="n">
-        <v>204</v>
-      </c>
-      <c r="E221" s="9" t="n">
-        <v>48.01</v>
-      </c>
-      <c r="F221" s="9" t="n">
-        <v>9794.04</v>
-      </c>
-      <c r="G221" s="10">
-        <v>46190</v>
-      </c>
-      <c r="H221" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I221" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J221" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="222" customHeight="1" ht="15" spans="1:5">
-      <c r="A222" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B222" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C222" s="13" t="n">
-        <v>9794.04</v>
-      </c>
-      <c r="D222" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E222" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A223" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" customHeight="1" ht="15" spans="1:12">
-      <c r="A224" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E224" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F224" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G224" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H224" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I224" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J224" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K224" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L224" s="4" t="s">
-        <v>12</v>
+      <c r="C224" s="13" t="n">
+        <v>52800</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E224" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="225" customHeight="1" ht="15" spans="1:1">
       <c r="A225" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="226" customHeight="1" ht="30.35" spans="1:10">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="226" customHeight="1" ht="18.8" spans="1:10">
       <c r="A226" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C226" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D226" s="8" t="n">
-        <v>252</v>
+        <v>1500</v>
       </c>
       <c r="E226" s="9" t="n">
         <v>43</v>
       </c>
       <c r="F226" s="9" t="n">
-        <v>10836</v>
+        <v>64500</v>
       </c>
       <c r="G226" s="10">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H226" s="8" t="n">
         <v>0</v>
@@ -6029,94 +6011,52 @@
         <v>0</v>
       </c>
       <c r="J226" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="227" customHeight="1" ht="28.15" spans="1:10">
-      <c r="A227" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B227" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C227" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D227" s="8" t="n">
-        <v>504</v>
-      </c>
-      <c r="E227" s="9" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="F227" s="9" t="n">
-        <v>20412</v>
-      </c>
-      <c r="G227" s="10">
-        <v>46189</v>
-      </c>
-      <c r="H227" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I227" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J227" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="228" customHeight="1" ht="29.15" spans="1:10">
-      <c r="A228" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B228" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C228" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D228" s="8" t="n">
-        <v>252</v>
-      </c>
-      <c r="E228" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="F228" s="9" t="n">
-        <v>10836</v>
-      </c>
-      <c r="G228" s="10">
-        <v>46189</v>
-      </c>
-      <c r="H228" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I228" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J228" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="229" customHeight="1" ht="29.4" spans="1:10">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="227" customHeight="1" ht="15" spans="1:5">
+      <c r="A227" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B227" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C227" s="13" t="n">
+        <v>64500</v>
+      </c>
+      <c r="D227" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E227" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" customHeight="1" ht="15" spans="1:1">
+      <c r="A228" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" ht="20.15" spans="1:10">
       <c r="A229" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="D229" s="8" t="n">
-        <v>504</v>
+        <v>288</v>
       </c>
       <c r="E229" s="9" t="n">
-        <v>40.5</v>
+        <v>46</v>
       </c>
       <c r="F229" s="9" t="n">
-        <v>20412</v>
+        <v>13248</v>
       </c>
       <c r="G229" s="10">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="H229" s="8" t="n">
         <v>0</v>
@@ -6125,7 +6065,7 @@
         <v>0</v>
       </c>
       <c r="J229" s="8" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
     </row>
     <row r="230" customHeight="1" ht="15" spans="1:5">
@@ -6136,7 +6076,7 @@
         <v>20</v>
       </c>
       <c r="C230" s="13" t="n">
-        <v>62496</v>
+        <v>13248</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>19</v>
@@ -6145,224 +6085,224 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" customHeight="1" ht="15" spans="1:1">
-      <c r="A231" s="2" t="s">
+    <row r="231" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A231" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" ht="15" spans="1:12">
+      <c r="A232" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E232" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G232" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H232" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I232" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J232" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K232" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L232" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" ht="15" spans="1:1">
+      <c r="A233" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" ht="15" spans="1:10">
+      <c r="A234" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C234" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D234" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E234" s="9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F234" s="9" t="n">
+        <v>1560</v>
+      </c>
+      <c r="G234" s="10">
+        <v>46190</v>
+      </c>
+      <c r="H234" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I234" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" ht="15" spans="1:5">
+      <c r="A235" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B235" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C235" s="13" t="n">
+        <v>1560</v>
+      </c>
+      <c r="D235" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E235" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" customHeight="1" ht="15" spans="1:1">
+      <c r="A236" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="237" customHeight="1" ht="15" spans="1:10">
+      <c r="A237" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C237" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D237" s="8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E237" s="9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F237" s="9" t="n">
+        <v>5760</v>
+      </c>
+      <c r="G237" s="10">
+        <v>46191</v>
+      </c>
+      <c r="H237" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I237" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="238" customHeight="1" ht="15" spans="1:5">
+      <c r="A238" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B238" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C238" s="13" t="n">
+        <v>5760</v>
+      </c>
+      <c r="D238" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E238" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" customHeight="1" ht="15" spans="1:1">
+      <c r="A239" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="232" customHeight="1" ht="18.45" spans="1:10">
-      <c r="A232" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B232" s="6" t="s">
+    <row r="240" customHeight="1" ht="15" spans="1:10">
+      <c r="A240" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B240" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C232" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D232" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="E232" s="9" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="F232" s="9" t="n">
-        <v>5700</v>
-      </c>
-      <c r="G232" s="10">
+      <c r="C240" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D240" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E240" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F240" s="9" t="n">
+        <v>840</v>
+      </c>
+      <c r="G240" s="10">
         <v>46185</v>
       </c>
-      <c r="H232" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I232" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J232" s="8" t="s">
+      <c r="H240" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I240" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="233" customHeight="1" ht="20.25" spans="1:10">
-      <c r="A233" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B233" s="6" t="s">
+    <row r="241" customHeight="1" ht="15" spans="1:10">
+      <c r="A241" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B241" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C233" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D233" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="E233" s="9" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="F233" s="9" t="n">
-        <v>5700</v>
-      </c>
-      <c r="G233" s="10">
+      <c r="C241" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D241" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E241" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F241" s="9" t="n">
+        <v>840</v>
+      </c>
+      <c r="G241" s="10">
         <v>46188</v>
       </c>
-      <c r="H233" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I233" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J233" s="8" t="s">
+      <c r="H241" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" s="8" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="234" customHeight="1" ht="15" spans="1:5">
-      <c r="A234" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B234" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C234" s="13" t="n">
-        <v>11400</v>
-      </c>
-      <c r="D234" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E234" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" customHeight="1" ht="15" spans="1:1">
-      <c r="A235" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="236" customHeight="1" ht="18.6" spans="1:10">
-      <c r="A236" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B236" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C236" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D236" s="8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E236" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="F236" s="9" t="n">
-        <v>52800</v>
-      </c>
-      <c r="G236" s="10">
-        <v>46190</v>
-      </c>
-      <c r="H236" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I236" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J236" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="237" customHeight="1" ht="15" spans="1:5">
-      <c r="A237" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B237" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C237" s="13" t="n">
-        <v>52800</v>
-      </c>
-      <c r="D237" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E237" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A238" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" customHeight="1" ht="15" spans="1:12">
-      <c r="A239" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B239" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D239" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E239" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F239" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G239" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H239" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I239" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J239" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K239" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L239" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="240" customHeight="1" ht="15" spans="1:1">
-      <c r="A240" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="241" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A241" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B241" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C241" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D241" s="8" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E241" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="F241" s="9" t="n">
-        <v>64500</v>
-      </c>
-      <c r="G241" s="10">
-        <v>46190</v>
-      </c>
-      <c r="H241" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I241" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J241" s="8" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="242" customHeight="1" ht="15" spans="1:5">
@@ -6373,7 +6313,7 @@
         <v>20</v>
       </c>
       <c r="C242" s="13" t="n">
-        <v>64500</v>
+        <v>1680</v>
       </c>
       <c r="D242" s="4" t="s">
         <v>19</v>
@@ -6382,129 +6322,129 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" customHeight="1" ht="15" spans="1:1">
-      <c r="A243" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="244" customHeight="1" ht="18.35" spans="1:10">
-      <c r="A244" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B244" s="6" t="s">
+    <row r="243" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A243" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" customHeight="1" ht="15" spans="1:12">
+      <c r="A244" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B244" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C244" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D244" s="8" t="n">
-        <v>288</v>
-      </c>
-      <c r="E244" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="F244" s="9" t="n">
-        <v>13248</v>
-      </c>
-      <c r="G244" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H244" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I244" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J244" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="245" customHeight="1" ht="15" spans="1:5">
-      <c r="A245" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B245" s="12" t="s">
+      <c r="C244" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E244" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F244" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G244" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H244" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I244" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J244" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K244" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L244" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="245" customHeight="1" ht="15" spans="1:1">
+      <c r="A245" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="246" customHeight="1" ht="15" spans="1:10">
+      <c r="A246" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C246" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D246" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E246" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F246" s="9" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G246" s="10">
+        <v>46184</v>
+      </c>
+      <c r="H246" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I246" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="247" customHeight="1" ht="15" spans="1:5">
+      <c r="A247" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B247" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C245" s="13" t="n">
-        <v>13248</v>
-      </c>
-      <c r="D245" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E245" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A246" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247" customHeight="1" ht="15" spans="1:12">
-      <c r="A247" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B247" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D247" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E247" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F247" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G247" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H247" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I247" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J247" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K247" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L247" s="4" t="s">
-        <v>12</v>
+      <c r="C247" s="13" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D247" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E247" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="248" customHeight="1" ht="15" spans="1:1">
       <c r="A248" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="249" customHeight="1" ht="15" spans="1:10">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="249" customHeight="1" ht="18.8" spans="1:10">
       <c r="A249" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>37</v>
+        <v>164</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D249" s="8" t="n">
-        <v>4000</v>
+        <v>25000</v>
       </c>
       <c r="E249" s="9" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="F249" s="9" t="n">
-        <v>1560</v>
+        <v>10750</v>
       </c>
       <c r="G249" s="10">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="H249" s="8" t="n">
         <v>0</v>
@@ -6513,7 +6453,7 @@
         <v>0</v>
       </c>
       <c r="J249" s="8" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="250" customHeight="1" ht="15" spans="1:5">
@@ -6524,7 +6464,7 @@
         <v>20</v>
       </c>
       <c r="C250" s="13" t="n">
-        <v>1560</v>
+        <v>10750</v>
       </c>
       <c r="D250" s="4" t="s">
         <v>19</v>
@@ -6535,7 +6475,7 @@
     </row>
     <row r="251" customHeight="1" ht="15" spans="1:1">
       <c r="A251" s="2" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
     </row>
     <row r="252" customHeight="1" ht="15" spans="1:10">
@@ -6543,22 +6483,22 @@
         <v>14</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="C252" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D252" s="8" t="n">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="E252" s="9" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="F252" s="9" t="n">
-        <v>5760</v>
+        <v>8200</v>
       </c>
       <c r="G252" s="10">
-        <v>46191</v>
+        <v>46169</v>
       </c>
       <c r="H252" s="8" t="n">
         <v>0</v>
@@ -6567,7 +6507,7 @@
         <v>0</v>
       </c>
       <c r="J252" s="8" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="253" customHeight="1" ht="15" spans="1:5">
@@ -6578,7 +6518,7 @@
         <v>20</v>
       </c>
       <c r="C253" s="13" t="n">
-        <v>5760</v>
+        <v>8200</v>
       </c>
       <c r="D253" s="4" t="s">
         <v>19</v>
@@ -6589,7 +6529,7 @@
     </row>
     <row r="254" customHeight="1" ht="15" spans="1:1">
       <c r="A254" s="2" t="s">
-        <v>88</v>
+        <v>168</v>
       </c>
     </row>
     <row r="255" customHeight="1" ht="15" spans="1:10">
@@ -6597,236 +6537,236 @@
         <v>14</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="C255" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D255" s="8" t="n">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="E255" s="9" t="n">
         <v>0.42</v>
       </c>
       <c r="F255" s="9" t="n">
-        <v>840</v>
+        <v>5460</v>
       </c>
       <c r="G255" s="10">
+        <v>46168</v>
+      </c>
+      <c r="H255" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I255" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="256" customHeight="1" ht="15" spans="1:5">
+      <c r="A256" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B256" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C256" s="13" t="n">
+        <v>5460</v>
+      </c>
+      <c r="D256" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E256" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A257" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" customHeight="1" ht="15" spans="1:12">
+      <c r="A258" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E258" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F258" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G258" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H258" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I258" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J258" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K258" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L258" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="259" customHeight="1" ht="15" spans="1:1">
+      <c r="A259" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="260" customHeight="1" ht="15" spans="1:10">
+      <c r="A260" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C260" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D260" s="8" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E260" s="9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F260" s="9" t="n">
+        <v>23400</v>
+      </c>
+      <c r="G260" s="10">
+        <v>46170</v>
+      </c>
+      <c r="H260" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I260" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="261" customHeight="1" ht="15" spans="1:5">
+      <c r="A261" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B261" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C261" s="13" t="n">
+        <v>23400</v>
+      </c>
+      <c r="D261" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E261" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" customHeight="1" ht="15" spans="1:1">
+      <c r="A262" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="263" customHeight="1" ht="15" spans="1:10">
+      <c r="A263" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C263" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D263" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E263" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F263" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G263" s="10">
+        <v>46191</v>
+      </c>
+      <c r="H263" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="264" customHeight="1" ht="15" spans="1:5">
+      <c r="A264" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B264" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C264" s="13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D264" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E264" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" customHeight="1" ht="15" spans="1:1">
+      <c r="A265" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="266" customHeight="1" ht="15" spans="1:10">
+      <c r="A266" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C266" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D266" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E266" s="9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F266" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G266" s="10">
         <v>46185</v>
       </c>
-      <c r="H255" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I255" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J255" s="8" t="s">
+      <c r="H266" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" s="8" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="256" customHeight="1" ht="15" spans="1:10">
-      <c r="A256" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B256" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C256" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D256" s="8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E256" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F256" s="9" t="n">
-        <v>840</v>
-      </c>
-      <c r="G256" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H256" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I256" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J256" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="257" customHeight="1" ht="15" spans="1:5">
-      <c r="A257" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B257" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C257" s="13" t="n">
-        <v>1680</v>
-      </c>
-      <c r="D257" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E257" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A258" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" customHeight="1" ht="15" spans="1:12">
-      <c r="A259" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B259" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D259" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E259" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F259" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G259" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H259" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I259" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J259" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K259" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L259" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="260" customHeight="1" ht="15" spans="1:1">
-      <c r="A260" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="261" customHeight="1" ht="15" spans="1:10">
-      <c r="A261" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B261" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C261" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D261" s="8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E261" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F261" s="9" t="n">
-        <v>4200</v>
-      </c>
-      <c r="G261" s="10">
-        <v>46184</v>
-      </c>
-      <c r="H261" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I261" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J261" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="262" customHeight="1" ht="15" spans="1:5">
-      <c r="A262" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B262" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C262" s="13" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D262" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E262" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" customHeight="1" ht="15" spans="1:1">
-      <c r="A263" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="264" customHeight="1" ht="15" spans="1:10">
-      <c r="A264" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B264" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C264" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D264" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E264" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="F264" s="9" t="n">
-        <v>8200</v>
-      </c>
-      <c r="G264" s="10">
-        <v>46169</v>
-      </c>
-      <c r="H264" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I264" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J264" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="265" customHeight="1" ht="15" spans="1:5">
-      <c r="A265" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B265" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C265" s="13" t="n">
-        <v>8200</v>
-      </c>
-      <c r="D265" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E265" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" customHeight="1" ht="15" spans="1:1">
-      <c r="A266" s="2" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="267" customHeight="1" ht="15" spans="1:10">
@@ -6834,22 +6774,22 @@
         <v>14</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>170</v>
+        <v>94</v>
       </c>
       <c r="C267" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D267" s="8" t="n">
-        <v>13000</v>
+        <v>5000</v>
       </c>
       <c r="E267" s="9" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="F267" s="9" t="n">
-        <v>5460</v>
+        <v>2200</v>
       </c>
       <c r="G267" s="10">
-        <v>46168</v>
+        <v>46188</v>
       </c>
       <c r="H267" s="8" t="n">
         <v>0</v>
@@ -6858,7 +6798,7 @@
         <v>0</v>
       </c>
       <c r="J267" s="8" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
     </row>
     <row r="268" customHeight="1" ht="15" spans="1:5">
@@ -6869,7 +6809,7 @@
         <v>20</v>
       </c>
       <c r="C268" s="13" t="n">
-        <v>5460</v>
+        <v>4400</v>
       </c>
       <c r="D268" s="4" t="s">
         <v>19</v>
@@ -6880,7 +6820,7 @@
     </row>
     <row r="269" customHeight="1" ht="15" spans="1:1">
       <c r="A269" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="270" customHeight="1" ht="15" spans="1:10">
@@ -6888,22 +6828,22 @@
         <v>14</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D270" s="8" t="n">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="E270" s="9" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="F270" s="9" t="n">
-        <v>23400</v>
+        <v>19000</v>
       </c>
       <c r="G270" s="10">
-        <v>46170</v>
+        <v>46191</v>
       </c>
       <c r="H270" s="8" t="n">
         <v>0</v>
@@ -6923,7 +6863,7 @@
         <v>20</v>
       </c>
       <c r="C271" s="13" t="n">
-        <v>23400</v>
+        <v>19000</v>
       </c>
       <c r="D271" s="4" t="s">
         <v>19</v>
@@ -6942,7 +6882,7 @@
         <v>1</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>3</v>
@@ -6977,7 +6917,7 @@
     </row>
     <row r="274" customHeight="1" ht="15" spans="1:1">
       <c r="A274" s="2" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
     </row>
     <row r="275" customHeight="1" ht="15" spans="1:10">
@@ -6985,290 +6925,290 @@
         <v>14</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D275" s="8" t="n">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="E275" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F275" s="9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G275" s="10">
+        <v>46202</v>
+      </c>
+      <c r="H275" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="276" customHeight="1" ht="15" spans="1:5">
+      <c r="A276" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B276" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C276" s="13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D276" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E276" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" customHeight="1" ht="15" spans="1:1">
+      <c r="A277" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="278" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A278" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C278" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D278" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E278" s="9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F278" s="9" t="n">
+        <v>9200</v>
+      </c>
+      <c r="G278" s="10">
+        <v>46188</v>
+      </c>
+      <c r="H278" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="279" customHeight="1" ht="15" spans="1:5">
+      <c r="A279" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B279" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C279" s="13" t="n">
+        <v>9200</v>
+      </c>
+      <c r="D279" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E279" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A280" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" customHeight="1" ht="15" spans="1:12">
+      <c r="A281" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E281" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F281" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G281" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H281" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I281" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J281" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K281" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L281" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="282" customHeight="1" ht="15" spans="1:1">
+      <c r="A282" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="283" customHeight="1" ht="15" spans="1:10">
+      <c r="A283" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C283" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D283" s="8" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E283" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F283" s="9" t="n">
+        <v>7560</v>
+      </c>
+      <c r="G283" s="10">
+        <v>46188</v>
+      </c>
+      <c r="H283" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I283" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="284" customHeight="1" ht="15" spans="1:5">
+      <c r="A284" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B284" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C284" s="13" t="n">
+        <v>7560</v>
+      </c>
+      <c r="D284" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E284" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" customHeight="1" ht="15" spans="1:1">
+      <c r="A285" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="286" customHeight="1" ht="15" spans="1:10">
+      <c r="A286" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C286" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D286" s="8" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E286" s="9" t="n">
         <v>0.44</v>
       </c>
-      <c r="F275" s="9" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G275" s="10">
-        <v>46185</v>
-      </c>
-      <c r="H275" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I275" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J275" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="276" customHeight="1" ht="15" spans="1:10">
-      <c r="A276" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B276" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C276" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D276" s="8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E276" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F276" s="9" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G276" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H276" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I276" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J276" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="277" customHeight="1" ht="15" spans="1:5">
-      <c r="A277" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B277" s="12" t="s">
+      <c r="F286" s="9" t="n">
+        <v>9240</v>
+      </c>
+      <c r="G286" s="10">
+        <v>46168</v>
+      </c>
+      <c r="H286" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I286" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="287" customHeight="1" ht="15" spans="1:5">
+      <c r="A287" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B287" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C277" s="13" t="n">
-        <v>4400</v>
-      </c>
-      <c r="D277" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E277" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278" customHeight="1" ht="15" spans="1:1">
-      <c r="A278" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="279" customHeight="1" ht="15" spans="1:10">
-      <c r="A279" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B279" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C279" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D279" s="8" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E279" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F279" s="9" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G279" s="10">
-        <v>46202</v>
-      </c>
-      <c r="H279" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I279" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J279" s="8" t="s">
+      <c r="C287" s="13" t="n">
+        <v>9240</v>
+      </c>
+      <c r="D287" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E287" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" customHeight="1" ht="15" spans="1:1">
+      <c r="A288" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="289" customHeight="1" ht="28.05" spans="1:10">
+      <c r="A289" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C289" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D289" s="8" t="n">
+        <v>205000</v>
+      </c>
+      <c r="E289" s="9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F289" s="9" t="n">
+        <v>77900</v>
+      </c>
+      <c r="G289" s="10">
+        <v>46168</v>
+      </c>
+      <c r="H289" s="8" t="n">
+        <v>80000</v>
+      </c>
+      <c r="I289" s="11" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="J289" s="8" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="280" customHeight="1" ht="15" spans="1:5">
-      <c r="A280" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B280" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C280" s="13" t="n">
-        <v>12000</v>
-      </c>
-      <c r="D280" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E280" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281" customHeight="1" ht="15" spans="1:1">
-      <c r="A281" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="282" customHeight="1" ht="19.15" spans="1:10">
-      <c r="A282" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B282" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C282" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D282" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E282" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="F282" s="9" t="n">
-        <v>9200</v>
-      </c>
-      <c r="G282" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H282" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I282" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J282" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="283" customHeight="1" ht="15" spans="1:5">
-      <c r="A283" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B283" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C283" s="13" t="n">
-        <v>9200</v>
-      </c>
-      <c r="D283" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E283" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A284" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" customHeight="1" ht="15" spans="1:12">
-      <c r="A285" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B285" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E285" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F285" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G285" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H285" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I285" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J285" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K285" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L285" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="286" customHeight="1" ht="15" spans="1:1">
-      <c r="A286" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="287" customHeight="1" ht="15" spans="1:10">
-      <c r="A287" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B287" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C287" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D287" s="8" t="n">
-        <v>18000</v>
-      </c>
-      <c r="E287" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F287" s="9" t="n">
-        <v>7560</v>
-      </c>
-      <c r="G287" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H287" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I287" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J287" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="288" customHeight="1" ht="15" spans="1:5">
-      <c r="A288" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B288" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C288" s="13" t="n">
-        <v>7560</v>
-      </c>
-      <c r="D288" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E288" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289" customHeight="1" ht="15" spans="1:1">
-      <c r="A289" s="2" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="290" customHeight="1" ht="15" spans="1:10">
@@ -7276,19 +7216,19 @@
         <v>14</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="C290" s="7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D290" s="8" t="n">
-        <v>21000</v>
+        <v>205000</v>
       </c>
       <c r="E290" s="9" t="n">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="F290" s="9" t="n">
-        <v>9240</v>
+        <v>79950</v>
       </c>
       <c r="G290" s="10">
         <v>46168</v>
@@ -7300,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="J290" s="8" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
     </row>
     <row r="291" customHeight="1" ht="15" spans="1:5">
@@ -7311,201 +7251,201 @@
         <v>20</v>
       </c>
       <c r="C291" s="13" t="n">
-        <v>9240</v>
+        <v>157850</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E291" s="14" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="292" customHeight="1" ht="15" spans="1:1">
       <c r="A292" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="293" customHeight="1" ht="28.05" spans="1:10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="293" customHeight="1" ht="15" spans="1:10">
       <c r="A293" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>178</v>
+        <v>83</v>
       </c>
       <c r="C293" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D293" s="8" t="n">
-        <v>205000</v>
+        <v>12000</v>
       </c>
       <c r="E293" s="9" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="F293" s="9" t="n">
-        <v>77900</v>
+        <v>5040</v>
       </c>
       <c r="G293" s="10">
-        <v>46168</v>
+        <v>46184</v>
       </c>
       <c r="H293" s="8" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="I293" s="11" t="n">
-        <v>39.02</v>
+        <v>0</v>
       </c>
       <c r="J293" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="294" customHeight="1" ht="15" spans="1:10">
-      <c r="A294" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B294" s="6" t="s">
+    <row r="294" customHeight="1" ht="15" spans="1:5">
+      <c r="A294" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B294" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C294" s="13" t="n">
+        <v>5040</v>
+      </c>
+      <c r="D294" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E294" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A295" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" customHeight="1" ht="15" spans="1:12">
+      <c r="A296" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E296" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F296" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G296" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H296" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I296" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J296" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K296" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L296" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="297" customHeight="1" ht="15" spans="1:1">
+      <c r="A297" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="298" customHeight="1" ht="15" spans="1:10">
+      <c r="A298" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C298" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C294" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D294" s="8" t="n">
-        <v>205000</v>
-      </c>
-      <c r="E294" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="F294" s="9" t="n">
-        <v>79950</v>
-      </c>
-      <c r="G294" s="10">
-        <v>46168</v>
-      </c>
-      <c r="H294" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I294" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J294" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="295" customHeight="1" ht="15" spans="1:5">
-      <c r="A295" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B295" s="12" t="s">
+      <c r="D298" s="8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E298" s="9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F298" s="9" t="n">
+        <v>6360</v>
+      </c>
+      <c r="G298" s="10">
+        <v>46191</v>
+      </c>
+      <c r="H298" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I298" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="299" customHeight="1" ht="15" spans="1:10">
+      <c r="A299" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C299" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D299" s="8" t="n">
+        <v>5400</v>
+      </c>
+      <c r="E299" s="9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F299" s="9" t="n">
+        <v>4428</v>
+      </c>
+      <c r="G299" s="10">
+        <v>46191</v>
+      </c>
+      <c r="H299" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I299" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="300" customHeight="1" ht="15" spans="1:5">
+      <c r="A300" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B300" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C295" s="13" t="n">
-        <v>157850</v>
-      </c>
-      <c r="D295" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E295" s="14" t="n">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="296" customHeight="1" ht="15" spans="1:1">
-      <c r="A296" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="297" customHeight="1" ht="15" spans="1:10">
-      <c r="A297" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B297" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C297" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D297" s="8" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E297" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F297" s="9" t="n">
-        <v>5040</v>
-      </c>
-      <c r="G297" s="10">
-        <v>46184</v>
-      </c>
-      <c r="H297" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I297" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J297" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="298" customHeight="1" ht="15" spans="1:5">
-      <c r="A298" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B298" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C298" s="13" t="n">
-        <v>5040</v>
-      </c>
-      <c r="D298" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E298" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A299" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" customHeight="1" ht="15" spans="1:12">
-      <c r="A300" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B300" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D300" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E300" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F300" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G300" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H300" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I300" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J300" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K300" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L300" s="4" t="s">
-        <v>12</v>
+      <c r="C300" s="13" t="n">
+        <v>10788</v>
+      </c>
+      <c r="D300" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E300" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="301" customHeight="1" ht="15" spans="1:1">
       <c r="A301" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
     </row>
     <row r="302" customHeight="1" ht="15" spans="1:10">
@@ -7513,22 +7453,22 @@
         <v>14</v>
       </c>
       <c r="B302" s="6" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="C302" s="7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D302" s="8" t="n">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="E302" s="9" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="F302" s="9" t="n">
-        <v>6360</v>
+        <v>8400</v>
       </c>
       <c r="G302" s="10">
-        <v>46191</v>
+        <v>46188</v>
       </c>
       <c r="H302" s="8" t="n">
         <v>0</v>
@@ -7537,61 +7477,61 @@
         <v>0</v>
       </c>
       <c r="J302" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="303" customHeight="1" ht="15" spans="1:10">
-      <c r="A303" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B303" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C303" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D303" s="8" t="n">
-        <v>5400</v>
-      </c>
-      <c r="E303" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="F303" s="9" t="n">
-        <v>4428</v>
-      </c>
-      <c r="G303" s="10">
-        <v>46191</v>
-      </c>
-      <c r="H303" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I303" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J303" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="304" customHeight="1" ht="15" spans="1:5">
-      <c r="A304" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B304" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="303" customHeight="1" ht="15" spans="1:5">
+      <c r="A303" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B303" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C304" s="13" t="n">
-        <v>10788</v>
-      </c>
-      <c r="D304" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E304" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305" customHeight="1" ht="15" spans="1:1">
-      <c r="A305" s="2" t="s">
-        <v>182</v>
+      <c r="C303" s="13" t="n">
+        <v>8400</v>
+      </c>
+      <c r="D303" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E303" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" customHeight="1" ht="15" spans="1:1">
+      <c r="A304" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="305" customHeight="1" ht="15" spans="1:10">
+      <c r="A305" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C305" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D305" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E305" s="9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F305" s="9" t="n">
+        <v>4600</v>
+      </c>
+      <c r="G305" s="10">
+        <v>46185</v>
+      </c>
+      <c r="H305" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="306" customHeight="1" ht="15" spans="1:10">
@@ -7599,22 +7539,22 @@
         <v>14</v>
       </c>
       <c r="B306" s="6" t="s">
-        <v>183</v>
+        <v>94</v>
       </c>
       <c r="C306" s="7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D306" s="8" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="E306" s="9" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="F306" s="9" t="n">
-        <v>5880</v>
+        <v>4600</v>
       </c>
       <c r="G306" s="10">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="H306" s="8" t="n">
         <v>0</v>
@@ -7623,7 +7563,7 @@
         <v>0</v>
       </c>
       <c r="J306" s="8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="307" customHeight="1" ht="15" spans="1:5">
@@ -7634,7 +7574,7 @@
         <v>20</v>
       </c>
       <c r="C307" s="13" t="n">
-        <v>5880</v>
+        <v>9200</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>19</v>
@@ -7645,7 +7585,7 @@
     </row>
     <row r="308" customHeight="1" ht="15" spans="1:1">
       <c r="A308" s="2" t="s">
-        <v>44</v>
+        <v>185</v>
       </c>
     </row>
     <row r="309" customHeight="1" ht="15" spans="1:10">
@@ -7653,22 +7593,22 @@
         <v>14</v>
       </c>
       <c r="B309" s="6" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="C309" s="7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D309" s="8" t="n">
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="E309" s="9" t="n">
-        <v>0.42</v>
+        <v>0.416</v>
       </c>
       <c r="F309" s="9" t="n">
-        <v>8400</v>
+        <v>41600</v>
       </c>
       <c r="G309" s="10">
-        <v>46188</v>
+        <v>46183</v>
       </c>
       <c r="H309" s="8" t="n">
         <v>0</v>
@@ -7677,7 +7617,7 @@
         <v>0</v>
       </c>
       <c r="J309" s="8" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
     </row>
     <row r="310" customHeight="1" ht="15" spans="1:5">
@@ -7688,7 +7628,7 @@
         <v>20</v>
       </c>
       <c r="C310" s="13" t="n">
-        <v>8400</v>
+        <v>41600</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>19</v>
@@ -7697,420 +7637,420 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" customHeight="1" ht="15" spans="1:1">
-      <c r="A311" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="312" customHeight="1" ht="15" spans="1:10">
-      <c r="A312" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B312" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C312" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D312" s="8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E312" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="F312" s="9" t="n">
-        <v>4600</v>
-      </c>
-      <c r="G312" s="10">
-        <v>46185</v>
-      </c>
-      <c r="H312" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I312" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J312" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="313" customHeight="1" ht="15" spans="1:10">
-      <c r="A313" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B313" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C313" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D313" s="8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E313" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="F313" s="9" t="n">
-        <v>4600</v>
-      </c>
-      <c r="G313" s="10">
+    <row r="311" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A311" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" customHeight="1" ht="15" spans="1:12">
+      <c r="A312" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B312" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E312" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G312" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H312" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I312" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J312" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K312" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L312" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="313" customHeight="1" ht="15" spans="1:1">
+      <c r="A313" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="314" customHeight="1" ht="15" spans="1:10">
+      <c r="A314" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C314" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D314" s="8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E314" s="9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F314" s="9" t="n">
+        <v>13200</v>
+      </c>
+      <c r="G314" s="10">
+        <v>46184</v>
+      </c>
+      <c r="H314" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I314" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J314" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="315" customHeight="1" ht="15" spans="1:5">
+      <c r="A315" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B315" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C315" s="13" t="n">
+        <v>13200</v>
+      </c>
+      <c r="D315" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E315" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" customHeight="1" ht="15" spans="1:1">
+      <c r="A316" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="317" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A317" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C317" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D317" s="8" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E317" s="9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F317" s="9" t="n">
+        <v>6860</v>
+      </c>
+      <c r="G317" s="10">
+        <v>46168</v>
+      </c>
+      <c r="H317" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I317" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="318" customHeight="1" ht="15" spans="1:5">
+      <c r="A318" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B318" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C318" s="13" t="n">
+        <v>6860</v>
+      </c>
+      <c r="D318" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E318" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" customHeight="1" ht="15" spans="1:1">
+      <c r="A319" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="320" customHeight="1" ht="15" spans="1:10">
+      <c r="A320" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C320" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D320" s="8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E320" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F320" s="9" t="n">
+        <v>5040</v>
+      </c>
+      <c r="G320" s="10">
+        <v>46190</v>
+      </c>
+      <c r="H320" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I320" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="321" customHeight="1" ht="15" spans="1:5">
+      <c r="A321" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B321" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C321" s="13" t="n">
+        <v>5040</v>
+      </c>
+      <c r="D321" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E321" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" customHeight="1" ht="15" spans="1:1">
+      <c r="A322" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="323" customHeight="1" ht="15" spans="1:10">
+      <c r="A323" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B323" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C323" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D323" s="8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E323" s="9" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F323" s="9" t="n">
+        <v>20750</v>
+      </c>
+      <c r="G323" s="10">
+        <v>46189</v>
+      </c>
+      <c r="H323" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I323" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J323" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="324" customHeight="1" ht="15" spans="1:5">
+      <c r="A324" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B324" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C324" s="13" t="n">
+        <v>20750</v>
+      </c>
+      <c r="D324" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E324" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A325" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" customHeight="1" ht="15" spans="1:12">
+      <c r="A326" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B326" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C326" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E326" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F326" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G326" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H326" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I326" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J326" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K326" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L326" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="327" customHeight="1" ht="15" spans="1:1">
+      <c r="A327" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="328" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A328" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B328" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C328" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D328" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E328" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F328" s="9" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G328" s="10">
+        <v>46175</v>
+      </c>
+      <c r="H328" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I328" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J328" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="329" customHeight="1" ht="15" spans="1:5">
+      <c r="A329" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B329" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C329" s="13" t="n">
+        <v>10500</v>
+      </c>
+      <c r="D329" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E329" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" customHeight="1" ht="15" spans="1:1">
+      <c r="A330" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="331" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A331" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B331" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C331" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D331" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E331" s="9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F331" s="9" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G331" s="10">
         <v>46188</v>
       </c>
-      <c r="H313" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I313" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J313" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="314" customHeight="1" ht="15" spans="1:5">
-      <c r="A314" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B314" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C314" s="13" t="n">
-        <v>9200</v>
-      </c>
-      <c r="D314" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E314" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A315" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316" customHeight="1" ht="15" spans="1:12">
-      <c r="A316" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B316" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C316" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D316" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E316" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F316" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G316" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H316" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I316" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J316" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K316" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L316" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="317" customHeight="1" ht="15" spans="1:1">
-      <c r="A317" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="318" customHeight="1" ht="15" spans="1:10">
-      <c r="A318" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B318" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C318" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D318" s="8" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E318" s="9" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="F318" s="9" t="n">
-        <v>41600</v>
-      </c>
-      <c r="G318" s="10">
-        <v>46183</v>
-      </c>
-      <c r="H318" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I318" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J318" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="319" customHeight="1" ht="15" spans="1:5">
-      <c r="A319" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B319" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C319" s="13" t="n">
-        <v>41600</v>
-      </c>
-      <c r="D319" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E319" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320" customHeight="1" ht="15" spans="1:1">
-      <c r="A320" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="321" customHeight="1" ht="15" spans="1:10">
-      <c r="A321" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B321" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C321" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D321" s="8" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E321" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F321" s="9" t="n">
-        <v>13200</v>
-      </c>
-      <c r="G321" s="10">
-        <v>46184</v>
-      </c>
-      <c r="H321" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I321" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J321" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="322" customHeight="1" ht="15" spans="1:5">
-      <c r="A322" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B322" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C322" s="13" t="n">
-        <v>13200</v>
-      </c>
-      <c r="D322" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E322" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323" customHeight="1" ht="15" spans="1:1">
-      <c r="A323" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="324" customHeight="1" ht="20.15" spans="1:10">
-      <c r="A324" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B324" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C324" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D324" s="8" t="n">
-        <v>14000</v>
-      </c>
-      <c r="E324" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="F324" s="9" t="n">
-        <v>6860</v>
-      </c>
-      <c r="G324" s="10">
-        <v>46168</v>
-      </c>
-      <c r="H324" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I324" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J324" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="325" customHeight="1" ht="15" spans="1:5">
-      <c r="A325" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B325" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C325" s="13" t="n">
-        <v>6860</v>
-      </c>
-      <c r="D325" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E325" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" customHeight="1" ht="15" spans="1:1">
-      <c r="A326" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="327" customHeight="1" ht="15" spans="1:10">
-      <c r="A327" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B327" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C327" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D327" s="8" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E327" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F327" s="9" t="n">
-        <v>5040</v>
-      </c>
-      <c r="G327" s="10">
-        <v>46190</v>
-      </c>
-      <c r="H327" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I327" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J327" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="328" customHeight="1" ht="15" spans="1:5">
-      <c r="A328" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B328" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C328" s="13" t="n">
-        <v>5040</v>
-      </c>
-      <c r="D328" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E328" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A329" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330" customHeight="1" ht="15" spans="1:12">
-      <c r="A330" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B330" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C330" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D330" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E330" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F330" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G330" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H330" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I330" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J330" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K330" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L330" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="331" customHeight="1" ht="15" spans="1:1">
-      <c r="A331" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="332" customHeight="1" ht="15" spans="1:10">
+      <c r="H331" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I331" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J331" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="332" customHeight="1" ht="36.95" spans="1:10">
       <c r="A332" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C332" s="7" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="D332" s="8" t="n">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="E332" s="9" t="n">
-        <v>0.415</v>
+        <v>0.48</v>
       </c>
       <c r="F332" s="9" t="n">
-        <v>20750</v>
+        <v>1440</v>
       </c>
       <c r="G332" s="10">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="H332" s="8" t="n">
         <v>0</v>
@@ -8119,7 +8059,7 @@
         <v>0</v>
       </c>
       <c r="J332" s="8" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
     </row>
     <row r="333" customHeight="1" ht="15" spans="1:5">
@@ -8130,7 +8070,7 @@
         <v>20</v>
       </c>
       <c r="C333" s="13" t="n">
-        <v>20750</v>
+        <v>11040</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>19</v>
@@ -8141,30 +8081,30 @@
     </row>
     <row r="334" customHeight="1" ht="15" spans="1:1">
       <c r="A334" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="335" customHeight="1" ht="18.8" spans="1:10">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="335" customHeight="1" ht="15" spans="1:10">
       <c r="A335" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="C335" s="7" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D335" s="8" t="n">
-        <v>25000</v>
+        <v>100000</v>
       </c>
       <c r="E335" s="9" t="n">
-        <v>0.42</v>
+        <v>0.416</v>
       </c>
       <c r="F335" s="9" t="n">
-        <v>10500</v>
+        <v>41600</v>
       </c>
       <c r="G335" s="10">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="H335" s="8" t="n">
         <v>0</v>
@@ -8173,467 +8113,467 @@
         <v>0</v>
       </c>
       <c r="J335" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="336" customHeight="1" ht="15" spans="1:5">
-      <c r="A336" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B336" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="336" customHeight="1" ht="15" spans="1:10">
+      <c r="A336" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B336" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C336" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D336" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E336" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F336" s="9" t="n">
+        <v>600</v>
+      </c>
+      <c r="G336" s="10">
+        <v>46176</v>
+      </c>
+      <c r="H336" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I336" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J336" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="337" customHeight="1" ht="15" spans="1:5">
+      <c r="A337" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B337" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C336" s="13" t="n">
-        <v>10500</v>
-      </c>
-      <c r="D336" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E336" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" customHeight="1" ht="15" spans="1:1">
-      <c r="A337" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="338" customHeight="1" ht="19.55" spans="1:10">
-      <c r="A338" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B338" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C338" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D338" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E338" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="F338" s="9" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G338" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H338" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I338" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J338" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="339" customHeight="1" ht="38.95" spans="1:10">
-      <c r="A339" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B339" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C339" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D339" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E339" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="F339" s="9" t="n">
-        <v>1440</v>
-      </c>
-      <c r="G339" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H339" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I339" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J339" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="340" customHeight="1" ht="15" spans="1:5">
-      <c r="A340" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B340" s="12" t="s">
+      <c r="C337" s="13" t="n">
+        <v>42200</v>
+      </c>
+      <c r="D337" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E337" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A338" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" customHeight="1" ht="15" spans="1:12">
+      <c r="A339" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B339" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C339" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E339" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F339" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G339" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H339" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I339" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J339" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K339" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L339" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="340" customHeight="1" ht="15" spans="1:1">
+      <c r="A340" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="341" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A341" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B341" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C341" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D341" s="8" t="n">
+        <v>1530</v>
+      </c>
+      <c r="E341" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F341" s="9" t="n">
+        <v>19890</v>
+      </c>
+      <c r="G341" s="10">
+        <v>46189</v>
+      </c>
+      <c r="H341" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I341" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="342" customHeight="1" ht="15" spans="1:5">
+      <c r="A342" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B342" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C340" s="13" t="n">
-        <v>11040</v>
-      </c>
-      <c r="D340" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E340" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341" customHeight="1" ht="15" spans="1:1">
-      <c r="A341" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="342" customHeight="1" ht="15" spans="1:10">
-      <c r="A342" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B342" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="C342" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D342" s="8" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E342" s="9" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="F342" s="9" t="n">
-        <v>41600</v>
-      </c>
-      <c r="G342" s="10">
-        <v>46176</v>
-      </c>
-      <c r="H342" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I342" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J342" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="343" customHeight="1" ht="15" spans="1:10">
-      <c r="A343" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B343" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="C343" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D343" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E343" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F343" s="9" t="n">
-        <v>600</v>
-      </c>
-      <c r="G343" s="10">
-        <v>46176</v>
-      </c>
-      <c r="H343" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I343" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J343" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="344" customHeight="1" ht="15" spans="1:5">
-      <c r="A344" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B344" s="12" t="s">
+      <c r="C342" s="13" t="n">
+        <v>19890</v>
+      </c>
+      <c r="D342" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E342" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A343" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" customHeight="1" ht="15" spans="1:12">
+      <c r="A344" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B344" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E344" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F344" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G344" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H344" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I344" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J344" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K344" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L344" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="345" customHeight="1" ht="15" spans="1:1">
+      <c r="A345" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="346" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A346" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B346" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C346" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D346" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E346" s="9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F346" s="9" t="n">
+        <v>26250</v>
+      </c>
+      <c r="G346" s="10">
+        <v>46189</v>
+      </c>
+      <c r="H346" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I346" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J346" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="347" customHeight="1" ht="15" spans="1:5">
+      <c r="A347" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B347" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C344" s="13" t="n">
-        <v>42200</v>
-      </c>
-      <c r="D344" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E344" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A345" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" customHeight="1" ht="15" spans="1:12">
-      <c r="A346" s="2" t="s">
+      <c r="C347" s="13" t="n">
+        <v>26250</v>
+      </c>
+      <c r="D347" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E347" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A348" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" customHeight="1" ht="15" spans="1:12">
+      <c r="A349" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B346" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C346" s="2" t="s">
+      <c r="B349" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C349" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D346" s="2" t="s">
+      <c r="D349" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E346" s="4" t="s">
+      <c r="E349" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F346" s="4" t="s">
+      <c r="F349" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G346" s="4" t="s">
+      <c r="G349" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H346" s="4" t="s">
+      <c r="H349" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I346" s="4" t="s">
+      <c r="I349" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J346" s="4" t="s">
+      <c r="J349" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K346" s="2" t="s">
+      <c r="K349" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L346" s="4" t="s">
+      <c r="L349" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="347" customHeight="1" ht="15" spans="1:1">
-      <c r="A347" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="348" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A348" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B348" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C348" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D348" s="8" t="n">
-        <v>1530</v>
-      </c>
-      <c r="E348" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="F348" s="9" t="n">
-        <v>19890</v>
-      </c>
-      <c r="G348" s="10">
+    <row r="350" customHeight="1" ht="15" spans="1:1">
+      <c r="A350" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="351" customHeight="1" ht="15" spans="1:10">
+      <c r="A351" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B351" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C351" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="D351" s="8" t="n">
+        <v>8028</v>
+      </c>
+      <c r="E351" s="9" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="F351" s="9" t="n">
+        <v>96255.72</v>
+      </c>
+      <c r="G351" s="10">
+        <v>46167</v>
+      </c>
+      <c r="H351" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I351" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J351" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="352" customHeight="1" ht="15" spans="1:5">
+      <c r="A352" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B352" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C352" s="13" t="n">
+        <v>96255.72</v>
+      </c>
+      <c r="D352" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E352" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" customHeight="1" ht="15" spans="1:1">
+      <c r="A353" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="354" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A354" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B354" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C354" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D354" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E354" s="9" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F354" s="9" t="n">
+        <v>34350</v>
+      </c>
+      <c r="G354" s="10">
         <v>46189</v>
       </c>
-      <c r="H348" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I348" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J348" s="8" t="s">
+      <c r="H354" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I354" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J354" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="349" customHeight="1" ht="15" spans="1:5">
-      <c r="A349" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B349" s="12" t="s">
+    <row r="355" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A355" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B355" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C355" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D355" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E355" s="9" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F355" s="9" t="n">
+        <v>34350</v>
+      </c>
+      <c r="G355" s="10">
+        <v>46189</v>
+      </c>
+      <c r="H355" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I355" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J355" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="356" customHeight="1" ht="15" spans="1:5">
+      <c r="A356" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B356" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C349" s="13" t="n">
-        <v>19890</v>
-      </c>
-      <c r="D349" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E349" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A350" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351" customHeight="1" ht="15" spans="1:12">
-      <c r="A351" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B351" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C351" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D351" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E351" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F351" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G351" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H351" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I351" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J351" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K351" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L351" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="352" customHeight="1" ht="15" spans="1:1">
-      <c r="A352" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="353" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A353" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B353" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C353" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D353" s="8" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E353" s="9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F353" s="9" t="n">
-        <v>26250</v>
-      </c>
-      <c r="G353" s="10">
-        <v>46189</v>
-      </c>
-      <c r="H353" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I353" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J353" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="354" customHeight="1" ht="15" spans="1:5">
-      <c r="A354" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B354" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C354" s="13" t="n">
-        <v>26250</v>
-      </c>
-      <c r="D354" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E354" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A355" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" customHeight="1" ht="15" spans="1:12">
-      <c r="A356" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B356" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C356" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D356" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E356" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F356" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G356" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H356" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I356" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J356" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K356" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L356" s="4" t="s">
-        <v>12</v>
+      <c r="C356" s="13" t="n">
+        <v>68700</v>
+      </c>
+      <c r="D356" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E356" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="357" customHeight="1" ht="15" spans="1:1">
       <c r="A357" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="358" customHeight="1" ht="15" spans="1:10">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="358" customHeight="1" ht="38.85" spans="1:10">
       <c r="A358" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C358" s="7" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D358" s="8" t="n">
-        <v>8028</v>
+        <v>24000</v>
       </c>
       <c r="E358" s="9" t="n">
-        <v>11.99</v>
+        <v>13</v>
       </c>
       <c r="F358" s="9" t="n">
-        <v>96255.72</v>
+        <v>312000</v>
       </c>
       <c r="G358" s="10">
-        <v>46167</v>
+        <v>46100</v>
       </c>
       <c r="H358" s="8" t="n">
-        <v>0</v>
+        <v>18900</v>
       </c>
       <c r="I358" s="11" t="n">
-        <v>0</v>
+        <v>78.75</v>
       </c>
       <c r="J358" s="8" t="s">
         <v>23</v>
@@ -8647,731 +8587,731 @@
         <v>20</v>
       </c>
       <c r="C359" s="13" t="n">
-        <v>96255.72</v>
+        <v>312000</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E359" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360" customHeight="1" ht="15" spans="1:1">
-      <c r="A360" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="361" customHeight="1" ht="18.8" spans="1:10">
-      <c r="A361" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B361" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C361" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D361" s="8" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E361" s="9" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="F361" s="9" t="n">
-        <v>34350</v>
-      </c>
-      <c r="G361" s="10">
-        <v>46189</v>
-      </c>
-      <c r="H361" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I361" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J361" s="8" t="s">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="360" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A360" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" customHeight="1" ht="15" spans="1:12">
+      <c r="A361" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B361" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E361" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F361" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G361" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H361" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I361" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J361" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K361" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L361" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="362" customHeight="1" ht="15" spans="1:1">
+      <c r="A362" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="363" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A363" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B363" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C363" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="D363" s="8" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E363" s="9" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="F363" s="9" t="n">
+        <v>33823.2</v>
+      </c>
+      <c r="G363" s="10">
+        <v>46162</v>
+      </c>
+      <c r="H363" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I363" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J363" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="364" customHeight="1" ht="15" spans="1:5">
+      <c r="A364" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B364" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C364" s="13" t="n">
+        <v>33823.2</v>
+      </c>
+      <c r="D364" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E364" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" customHeight="1" ht="15" spans="1:1">
+      <c r="A365" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="366" customHeight="1" ht="15" spans="1:10">
+      <c r="A366" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B366" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C366" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D366" s="8" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E366" s="9" t="n">
+        <v>9.8</v>
+      </c>
+      <c r="F366" s="9" t="n">
+        <v>9996</v>
+      </c>
+      <c r="G366" s="10">
+        <v>46164</v>
+      </c>
+      <c r="H366" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I366" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J366" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="362" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A362" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B362" s="6" t="s">
+    <row r="367" customHeight="1" ht="15" spans="1:5">
+      <c r="A367" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B367" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C367" s="13" t="n">
+        <v>9996</v>
+      </c>
+      <c r="D367" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E367" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A368" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" customHeight="1" ht="15" spans="1:12">
+      <c r="A369" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B369" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E369" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F369" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G369" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H369" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I369" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J369" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K369" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L369" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="370" customHeight="1" ht="15" spans="1:1">
+      <c r="A370" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="371" customHeight="1" ht="15" spans="1:10">
+      <c r="A371" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B371" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C371" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D371" s="8" t="n">
+        <v>4032</v>
+      </c>
+      <c r="E371" s="9" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F371" s="9" t="n">
+        <v>28183.68</v>
+      </c>
+      <c r="G371" s="10">
+        <v>46167</v>
+      </c>
+      <c r="H371" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I371" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J371" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="372" customHeight="1" ht="15" spans="1:5">
+      <c r="A372" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B372" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C372" s="13" t="n">
+        <v>28183.68</v>
+      </c>
+      <c r="D372" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E372" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" customHeight="1" ht="15" spans="1:1">
+      <c r="A373" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="374" customHeight="1" ht="15" spans="1:10">
+      <c r="A374" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B374" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C374" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D374" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E374" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F374" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G374" s="10">
+        <v>46191</v>
+      </c>
+      <c r="H374" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I374" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J374" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="375" customHeight="1" ht="15" spans="1:5">
+      <c r="A375" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B375" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C375" s="13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D375" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E375" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" customHeight="1" ht="15" spans="1:1">
+      <c r="A376" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="377" customHeight="1" ht="20.15" spans="1:10">
+      <c r="A377" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B377" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C377" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D377" s="8" t="n">
+        <v>320</v>
+      </c>
+      <c r="E377" s="9" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="F377" s="9" t="n">
+        <v>5360</v>
+      </c>
+      <c r="G377" s="10">
+        <v>46167</v>
+      </c>
+      <c r="H377" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I377" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J377" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="378" customHeight="1" ht="15" spans="1:5">
+      <c r="A378" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B378" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C378" s="13" t="n">
+        <v>5360</v>
+      </c>
+      <c r="D378" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E378" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" customHeight="1" ht="15" spans="1:1">
+      <c r="A379" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C362" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="D362" s="8" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E362" s="9" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="F362" s="9" t="n">
-        <v>34350</v>
-      </c>
-      <c r="G362" s="10">
-        <v>46189</v>
-      </c>
-      <c r="H362" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I362" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J362" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="363" customHeight="1" ht="15" spans="1:5">
-      <c r="A363" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B363" s="12" t="s">
+    </row>
+    <row r="380" customHeight="1" ht="19.9" spans="1:10">
+      <c r="A380" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B380" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C380" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D380" s="8" t="n">
+        <v>720</v>
+      </c>
+      <c r="E380" s="9" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="F380" s="9" t="n">
+        <v>17064</v>
+      </c>
+      <c r="G380" s="10">
+        <v>46169</v>
+      </c>
+      <c r="H380" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I380" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J380" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="381" customHeight="1" ht="15" spans="1:5">
+      <c r="A381" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B381" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C363" s="13" t="n">
-        <v>68700</v>
-      </c>
-      <c r="D363" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E363" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364" customHeight="1" ht="15" spans="1:1">
-      <c r="A364" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="365" customHeight="1" ht="38.85" spans="1:10">
-      <c r="A365" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B365" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C365" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="D365" s="8" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E365" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="F365" s="9" t="n">
-        <v>312000</v>
-      </c>
-      <c r="G365" s="10">
-        <v>46100</v>
-      </c>
-      <c r="H365" s="8" t="n">
-        <v>18900</v>
-      </c>
-      <c r="I365" s="11" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="J365" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="366" customHeight="1" ht="15" spans="1:5">
-      <c r="A366" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B366" s="12" t="s">
+      <c r="C381" s="13" t="n">
+        <v>17064</v>
+      </c>
+      <c r="D381" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E381" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A382" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" customHeight="1" ht="15" spans="1:12">
+      <c r="A383" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B383" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C383" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D383" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E383" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F383" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G383" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H383" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I383" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J383" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K383" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L383" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="384" customHeight="1" ht="15" spans="1:1">
+      <c r="A384" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="385" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A385" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B385" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C385" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D385" s="8" t="n">
+        <v>1320</v>
+      </c>
+      <c r="E385" s="9" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="F385" s="9" t="n">
+        <v>11682</v>
+      </c>
+      <c r="G385" s="10">
+        <v>46175</v>
+      </c>
+      <c r="H385" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I385" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J385" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="386" customHeight="1" ht="15" spans="1:5">
+      <c r="A386" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B386" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C366" s="13" t="n">
-        <v>312000</v>
-      </c>
-      <c r="D366" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E366" s="14" t="n">
-        <v>18900</v>
-      </c>
-    </row>
-    <row r="367" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A367" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" customHeight="1" ht="15" spans="1:12">
-      <c r="A368" s="2" t="s">
+      <c r="C386" s="13" t="n">
+        <v>11682</v>
+      </c>
+      <c r="D386" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E386" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A387" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" customHeight="1" ht="15" spans="1:12">
+      <c r="A388" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B368" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C368" s="2" t="s">
+      <c r="B388" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C388" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D368" s="2" t="s">
+      <c r="D388" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E368" s="4" t="s">
+      <c r="E388" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F368" s="4" t="s">
+      <c r="F388" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G368" s="4" t="s">
+      <c r="G388" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H368" s="4" t="s">
+      <c r="H388" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I368" s="4" t="s">
+      <c r="I388" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J368" s="4" t="s">
+      <c r="J388" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K368" s="2" t="s">
+      <c r="K388" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L368" s="4" t="s">
+      <c r="L388" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="369" customHeight="1" ht="15" spans="1:1">
-      <c r="A369" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="370" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A370" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B370" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C370" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="D370" s="8" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E370" s="9" t="n">
-        <v>16.58</v>
-      </c>
-      <c r="F370" s="9" t="n">
-        <v>33823.2</v>
-      </c>
-      <c r="G370" s="10">
-        <v>46162</v>
-      </c>
-      <c r="H370" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I370" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J370" s="8" t="s">
+    <row r="389" customHeight="1" ht="15" spans="1:1">
+      <c r="A389" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="390" customHeight="1" ht="15" spans="1:10">
+      <c r="A390" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B390" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C390" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D390" s="8" t="n">
+        <v>2160</v>
+      </c>
+      <c r="E390" s="9" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F390" s="9" t="n">
+        <v>15098.4</v>
+      </c>
+      <c r="G390" s="10">
+        <v>46190</v>
+      </c>
+      <c r="H390" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I390" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J390" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="371" customHeight="1" ht="15" spans="1:5">
-      <c r="A371" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B371" s="12" t="s">
+    <row r="391" customHeight="1" ht="15" spans="1:5">
+      <c r="A391" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B391" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C371" s="13" t="n">
-        <v>33823.2</v>
-      </c>
-      <c r="D371" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E371" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="372" customHeight="1" ht="15" spans="1:1">
-      <c r="A372" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="373" customHeight="1" ht="15" spans="1:10">
-      <c r="A373" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B373" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C373" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="D373" s="8" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E373" s="9" t="n">
-        <v>9.8</v>
-      </c>
-      <c r="F373" s="9" t="n">
-        <v>9996</v>
-      </c>
-      <c r="G373" s="10">
-        <v>46164</v>
-      </c>
-      <c r="H373" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I373" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J373" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="374" customHeight="1" ht="15" spans="1:5">
-      <c r="A374" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B374" s="12" t="s">
+      <c r="C391" s="13" t="n">
+        <v>15098.4</v>
+      </c>
+      <c r="D391" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E391" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" customHeight="1" ht="15" spans="1:1">
+      <c r="A392" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="393" customHeight="1" ht="15" spans="1:10">
+      <c r="A393" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B393" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C393" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D393" s="8" t="n">
+        <v>10008</v>
+      </c>
+      <c r="E393" s="9" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="F393" s="9" t="n">
+        <v>59947.92</v>
+      </c>
+      <c r="G393" s="10">
+        <v>46181</v>
+      </c>
+      <c r="H393" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I393" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J393" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="394" customHeight="1" ht="28.55" spans="1:10">
+      <c r="A394" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B394" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C394" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D394" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="E394" s="9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F394" s="9" t="n">
+        <v>8640</v>
+      </c>
+      <c r="G394" s="10">
+        <v>46181</v>
+      </c>
+      <c r="H394" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I394" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J394" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="395" customHeight="1" ht="15" spans="1:5">
+      <c r="A395" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B395" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C374" s="13" t="n">
-        <v>9996</v>
-      </c>
-      <c r="D374" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E374" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A375" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376" customHeight="1" ht="15" spans="1:12">
-      <c r="A376" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B376" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C376" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D376" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E376" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F376" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G376" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H376" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I376" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J376" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K376" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L376" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="377" customHeight="1" ht="15" spans="1:1">
-      <c r="A377" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="378" customHeight="1" ht="15" spans="1:10">
-      <c r="A378" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B378" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C378" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="D378" s="8" t="n">
-        <v>4032</v>
-      </c>
-      <c r="E378" s="9" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F378" s="9" t="n">
-        <v>28183.68</v>
-      </c>
-      <c r="G378" s="10">
-        <v>46167</v>
-      </c>
-      <c r="H378" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I378" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J378" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="379" customHeight="1" ht="15" spans="1:5">
-      <c r="A379" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B379" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C379" s="13" t="n">
-        <v>28183.68</v>
-      </c>
-      <c r="D379" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E379" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" customHeight="1" ht="15" spans="1:1">
-      <c r="A380" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="381" customHeight="1" ht="15" spans="1:10">
-      <c r="A381" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B381" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C381" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="D381" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E381" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F381" s="9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G381" s="10">
-        <v>46191</v>
-      </c>
-      <c r="H381" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I381" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J381" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="382" customHeight="1" ht="15" spans="1:5">
-      <c r="A382" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B382" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C382" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D382" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E382" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" customHeight="1" ht="15" spans="1:1">
-      <c r="A383" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="384" customHeight="1" ht="20.15" spans="1:10">
-      <c r="A384" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B384" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C384" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D384" s="8" t="n">
-        <v>320</v>
-      </c>
-      <c r="E384" s="9" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="F384" s="9" t="n">
-        <v>5360</v>
-      </c>
-      <c r="G384" s="10">
-        <v>46167</v>
-      </c>
-      <c r="H384" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I384" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J384" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="385" customHeight="1" ht="15" spans="1:5">
-      <c r="A385" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B385" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C385" s="13" t="n">
-        <v>5360</v>
-      </c>
-      <c r="D385" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E385" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="386" customHeight="1" ht="15" spans="1:1">
-      <c r="A386" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="387" customHeight="1" ht="19.9" spans="1:10">
-      <c r="A387" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B387" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C387" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="D387" s="8" t="n">
-        <v>720</v>
-      </c>
-      <c r="E387" s="9" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="F387" s="9" t="n">
-        <v>17064</v>
-      </c>
-      <c r="G387" s="10">
-        <v>46169</v>
-      </c>
-      <c r="H387" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I387" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J387" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="388" customHeight="1" ht="15" spans="1:5">
-      <c r="A388" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B388" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C388" s="13" t="n">
-        <v>17064</v>
-      </c>
-      <c r="D388" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E388" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="389" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A389" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="390" customHeight="1" ht="15" spans="1:12">
-      <c r="A390" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B390" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C390" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D390" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E390" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F390" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G390" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H390" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I390" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J390" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K390" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L390" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="391" customHeight="1" ht="15" spans="1:1">
-      <c r="A391" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="392" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A392" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B392" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C392" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="D392" s="8" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E392" s="9" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="F392" s="9" t="n">
-        <v>11682</v>
-      </c>
-      <c r="G392" s="10">
-        <v>46175</v>
-      </c>
-      <c r="H392" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I392" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J392" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="393" customHeight="1" ht="15" spans="1:5">
-      <c r="A393" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B393" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C393" s="13" t="n">
-        <v>11682</v>
-      </c>
-      <c r="D393" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E393" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="394" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A394" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="395" customHeight="1" ht="15" spans="1:12">
-      <c r="A395" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B395" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C395" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D395" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E395" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F395" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G395" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H395" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I395" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J395" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K395" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L395" s="4" t="s">
-        <v>12</v>
+      <c r="C395" s="13" t="n">
+        <v>68587.92</v>
+      </c>
+      <c r="D395" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E395" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="396" customHeight="1" ht="15" spans="1:1">
       <c r="A396" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="397" customHeight="1" ht="15" spans="1:10">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="397" customHeight="1" ht="21.2" spans="1:10">
       <c r="A397" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B397" s="6" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="C397" s="7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D397" s="8" t="n">
-        <v>2160</v>
+        <v>792</v>
       </c>
       <c r="E397" s="9" t="n">
         <v>6.99</v>
       </c>
       <c r="F397" s="9" t="n">
-        <v>15098.4</v>
+        <v>5536.08</v>
       </c>
       <c r="G397" s="10">
-        <v>46190</v>
+        <v>46175</v>
       </c>
       <c r="H397" s="8" t="n">
         <v>0</v>
@@ -9380,7 +9320,7 @@
         <v>0</v>
       </c>
       <c r="J397" s="8" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="398" customHeight="1" ht="15" spans="1:5">
@@ -9391,152 +9331,12 @@
         <v>20</v>
       </c>
       <c r="C398" s="13" t="n">
-        <v>15098.4</v>
+        <v>5536.08</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E398" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="399" customHeight="1" ht="15" spans="1:1">
-      <c r="A399" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="400" customHeight="1" ht="15" spans="1:10">
-      <c r="A400" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B400" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="C400" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="D400" s="8" t="n">
-        <v>10008</v>
-      </c>
-      <c r="E400" s="9" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="F400" s="9" t="n">
-        <v>59947.92</v>
-      </c>
-      <c r="G400" s="10">
-        <v>46181</v>
-      </c>
-      <c r="H400" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I400" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J400" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="401" customHeight="1" ht="28.55" spans="1:10">
-      <c r="A401" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B401" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="C401" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="D401" s="8" t="n">
-        <v>600</v>
-      </c>
-      <c r="E401" s="9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F401" s="9" t="n">
-        <v>8640</v>
-      </c>
-      <c r="G401" s="10">
-        <v>46181</v>
-      </c>
-      <c r="H401" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I401" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J401" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="402" customHeight="1" ht="15" spans="1:5">
-      <c r="A402" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B402" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C402" s="13" t="n">
-        <v>68587.92</v>
-      </c>
-      <c r="D402" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E402" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="403" customHeight="1" ht="15" spans="1:1">
-      <c r="A403" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="404" customHeight="1" ht="21.2" spans="1:10">
-      <c r="A404" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B404" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C404" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D404" s="8" t="n">
-        <v>792</v>
-      </c>
-      <c r="E404" s="9" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F404" s="9" t="n">
-        <v>5536.08</v>
-      </c>
-      <c r="G404" s="10">
-        <v>46175</v>
-      </c>
-      <c r="H404" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I404" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J404" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="405" customHeight="1" ht="15" spans="1:5">
-      <c r="A405" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B405" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C405" s="13" t="n">
-        <v>5536.08</v>
-      </c>
-      <c r="D405" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E405" s="14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="221">
   <si>
     <t>MATRIZ CNPJ: 40.357.820/0001-50R Y DOIS - 58082-025
  ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
@@ -578,12 +578,6 @@
     <t xml:space="preserve">84 - GAZE  CIRCULAR NAO ESTERIL 09 FIOS </t>
   </si>
   <si>
-    <t>FARMAGUEDES COMERCIO DE PROD FARMAC. MED E HOSP LTDA</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
     <t>88 - GAZE CIRCULAR NAO ESTERIL 09 FIOS H Observação: FATURAR PEDIDO DIA 16/07/2026</t>
   </si>
   <si>
@@ -647,7 +641,7 @@
     <t>978</t>
   </si>
   <si>
-    <t xml:space="preserve">325 - GAZE NAO ESTÉRIL 13 FIOS </t>
+    <t>325 - GAZE NAO ESTÉRIL 13 FIOS  Observação: IMPORTATE TER NO PACOTE 140  gr. PREÇO PROPORCIONAL CONFORME ULTIMO  PREÇO.</t>
   </si>
   <si>
     <t xml:space="preserve">326 - GAZE NAO ESTÉRIL 13 FIOS </t>
@@ -846,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L449"/>
+  <dimension ref="A1:L444"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
   <cols>
     <col customWidth="1" width="89.23828125" min="1" max="1"/>
@@ -7007,10 +7001,10 @@
         <v>1008</v>
       </c>
       <c r="E261" s="9" t="n">
-        <v>75.26</v>
+        <v>42</v>
       </c>
       <c r="F261" s="9" t="n">
-        <v>75862.08</v>
+        <v>42336</v>
       </c>
       <c r="G261" s="10">
         <v>46199</v>
@@ -7033,7 +7027,7 @@
         <v>20</v>
       </c>
       <c r="C262" s="13" t="n">
-        <v>75862.08</v>
+        <v>42336</v>
       </c>
       <c r="D262" s="4" t="s">
         <v>19</v>
@@ -8418,10 +8412,10 @@
         <v>46198</v>
       </c>
       <c r="H335" s="8" t="n">
-        <v>41400</v>
+        <v>32400</v>
       </c>
       <c r="I335" s="11" t="n">
-        <v>82.8</v>
+        <v>64.8</v>
       </c>
       <c r="J335" s="8" t="s">
         <v>100</v>
@@ -8441,7 +8435,7 @@
         <v>19</v>
       </c>
       <c r="E336" s="14" t="n">
-        <v>41400</v>
+        <v>32400</v>
       </c>
     </row>
     <row r="337" customHeight="1" ht="15" spans="1:1">
@@ -8856,30 +8850,30 @@
     </row>
     <row r="359" customHeight="1" ht="15" spans="1:1">
       <c r="A359" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="360" customHeight="1" ht="18.45" spans="1:10">
+      <c r="A360" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B360" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C360" s="7" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="360" customHeight="1" ht="15" spans="1:10">
-      <c r="A360" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B360" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C360" s="7" t="s">
-        <v>186</v>
-      </c>
       <c r="D360" s="8" t="n">
-        <v>1512</v>
+        <v>1530</v>
       </c>
       <c r="E360" s="9" t="n">
-        <v>11.99</v>
+        <v>13</v>
       </c>
       <c r="F360" s="9" t="n">
-        <v>18128.88</v>
+        <v>19890</v>
       </c>
       <c r="G360" s="10">
-        <v>46202.697662037</v>
+        <v>46189</v>
       </c>
       <c r="H360" s="8" t="n">
         <v>0</v>
@@ -8899,7 +8893,7 @@
         <v>20</v>
       </c>
       <c r="C361" s="13" t="n">
-        <v>18128.88</v>
+        <v>19890</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>19</v>
@@ -8918,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>3</v>
@@ -8967,13 +8961,13 @@
         <v>190</v>
       </c>
       <c r="D365" s="8" t="n">
-        <v>1530</v>
+        <v>1500</v>
       </c>
       <c r="E365" s="9" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="F365" s="9" t="n">
-        <v>19890</v>
+        <v>26250</v>
       </c>
       <c r="G365" s="10">
         <v>46189</v>
@@ -8996,7 +8990,7 @@
         <v>20</v>
       </c>
       <c r="C366" s="13" t="n">
-        <v>19890</v>
+        <v>26250</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>19</v>
@@ -9005,106 +8999,106 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A367" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" customHeight="1" ht="15" spans="1:12">
-      <c r="A368" s="2" t="s">
+    <row r="367" customHeight="1" ht="15" spans="1:1">
+      <c r="A367" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="368" customHeight="1" ht="15" spans="1:10">
+      <c r="A368" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B368" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C368" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D368" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="E368" s="9" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="F368" s="9" t="n">
+        <v>2194.8</v>
+      </c>
+      <c r="G368" s="10">
+        <v>46196.6411111111</v>
+      </c>
+      <c r="H368" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I368" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J368" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="369" customHeight="1" ht="15" spans="1:5">
+      <c r="A369" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B369" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C369" s="13" t="n">
+        <v>2194.8</v>
+      </c>
+      <c r="D369" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E369" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A370" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" customHeight="1" ht="15" spans="1:12">
+      <c r="A371" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B368" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C368" s="2" t="s">
+      <c r="B371" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C371" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D368" s="2" t="s">
+      <c r="D371" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E368" s="4" t="s">
+      <c r="E371" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F368" s="4" t="s">
+      <c r="F371" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G368" s="4" t="s">
+      <c r="G371" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H368" s="4" t="s">
+      <c r="H371" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I368" s="4" t="s">
+      <c r="I371" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J368" s="4" t="s">
+      <c r="J371" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K368" s="2" t="s">
+      <c r="K371" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L368" s="4" t="s">
+      <c r="L371" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="369" customHeight="1" ht="15" spans="1:1">
-      <c r="A369" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="370" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A370" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B370" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C370" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D370" s="8" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E370" s="9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F370" s="9" t="n">
-        <v>26250</v>
-      </c>
-      <c r="G370" s="10">
-        <v>46189</v>
-      </c>
-      <c r="H370" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I370" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J370" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="371" customHeight="1" ht="15" spans="1:5">
-      <c r="A371" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B371" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C371" s="13" t="n">
-        <v>26250</v>
-      </c>
-      <c r="D371" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E371" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="372" customHeight="1" ht="15" spans="1:1">
       <c r="A372" s="2" t="s">
-        <v>103</v>
+        <v>193</v>
       </c>
     </row>
     <row r="373" customHeight="1" ht="15" spans="1:10">
@@ -9112,22 +9106,22 @@
         <v>14</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="C373" s="7" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D373" s="8" t="n">
-        <v>120</v>
+        <v>8028</v>
       </c>
       <c r="E373" s="9" t="n">
-        <v>18.29</v>
+        <v>11.99</v>
       </c>
       <c r="F373" s="9" t="n">
-        <v>2194.8</v>
+        <v>96255.72</v>
       </c>
       <c r="G373" s="10">
-        <v>46196.6411111111</v>
+        <v>46167</v>
       </c>
       <c r="H373" s="8" t="n">
         <v>0</v>
@@ -9136,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="J373" s="8" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
     </row>
     <row r="374" customHeight="1" ht="15" spans="1:5">
@@ -9147,7 +9141,7 @@
         <v>20</v>
       </c>
       <c r="C374" s="13" t="n">
-        <v>2194.8</v>
+        <v>96255.72</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>19</v>
@@ -9156,246 +9150,246 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A375" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376" customHeight="1" ht="15" spans="1:12">
-      <c r="A376" s="2" t="s">
+    <row r="375" customHeight="1" ht="15" spans="1:1">
+      <c r="A375" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="376" customHeight="1" ht="15" spans="1:10">
+      <c r="A376" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B376" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C376" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D376" s="8" t="n">
+        <v>720</v>
+      </c>
+      <c r="E376" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F376" s="9" t="n">
+        <v>10800</v>
+      </c>
+      <c r="G376" s="10">
+        <v>46203</v>
+      </c>
+      <c r="H376" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I376" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J376" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="377" customHeight="1" ht="15" spans="1:5">
+      <c r="A377" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B377" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C377" s="13" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D377" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E377" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" customHeight="1" ht="15" spans="1:1">
+      <c r="A378" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="379" customHeight="1" ht="20.15" spans="1:10">
+      <c r="A379" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B379" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C379" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D379" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E379" s="9" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F379" s="9" t="n">
+        <v>34350</v>
+      </c>
+      <c r="G379" s="10">
+        <v>46189</v>
+      </c>
+      <c r="H379" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I379" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J379" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="380" customHeight="1" ht="15" spans="1:5">
+      <c r="A380" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B380" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C380" s="13" t="n">
+        <v>34350</v>
+      </c>
+      <c r="D380" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E380" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" customHeight="1" ht="15" spans="1:1">
+      <c r="A381" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="382" customHeight="1" ht="37.05" spans="1:10">
+      <c r="A382" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B382" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="C382" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D382" s="8" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E382" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F382" s="9" t="n">
+        <v>312000</v>
+      </c>
+      <c r="G382" s="10">
+        <v>46100</v>
+      </c>
+      <c r="H382" s="8" t="n">
+        <v>18900</v>
+      </c>
+      <c r="I382" s="11" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="J382" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="383" customHeight="1" ht="15" spans="1:5">
+      <c r="A383" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B383" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C383" s="13" t="n">
+        <v>312000</v>
+      </c>
+      <c r="D383" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E383" s="14" t="n">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="384" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A384" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" customHeight="1" ht="15" spans="1:12">
+      <c r="A385" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B376" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C376" s="2" t="s">
+      <c r="B385" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C385" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D376" s="2" t="s">
+      <c r="D385" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E376" s="4" t="s">
+      <c r="E385" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F376" s="4" t="s">
+      <c r="F385" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G376" s="4" t="s">
+      <c r="G385" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H376" s="4" t="s">
+      <c r="H385" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I376" s="4" t="s">
+      <c r="I385" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J376" s="4" t="s">
+      <c r="J385" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K376" s="2" t="s">
+      <c r="K385" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L376" s="4" t="s">
+      <c r="L385" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="377" customHeight="1" ht="15" spans="1:1">
-      <c r="A377" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="378" customHeight="1" ht="15" spans="1:10">
-      <c r="A378" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B378" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C378" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D378" s="8" t="n">
-        <v>8028</v>
-      </c>
-      <c r="E378" s="9" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="F378" s="9" t="n">
-        <v>96255.72</v>
-      </c>
-      <c r="G378" s="10">
-        <v>46167</v>
-      </c>
-      <c r="H378" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I378" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J378" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="379" customHeight="1" ht="15" spans="1:5">
-      <c r="A379" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B379" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C379" s="13" t="n">
-        <v>96255.72</v>
-      </c>
-      <c r="D379" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E379" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" customHeight="1" ht="15" spans="1:1">
-      <c r="A380" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="381" customHeight="1" ht="15" spans="1:10">
-      <c r="A381" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B381" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C381" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D381" s="8" t="n">
-        <v>720</v>
-      </c>
-      <c r="E381" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="F381" s="9" t="n">
-        <v>10800</v>
-      </c>
-      <c r="G381" s="10">
-        <v>46203</v>
-      </c>
-      <c r="H381" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I381" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J381" s="8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="382" customHeight="1" ht="15" spans="1:5">
-      <c r="A382" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B382" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C382" s="13" t="n">
-        <v>10800</v>
-      </c>
-      <c r="D382" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E382" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" customHeight="1" ht="15" spans="1:1">
-      <c r="A383" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="384" customHeight="1" ht="20.15" spans="1:10">
-      <c r="A384" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B384" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C384" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D384" s="8" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E384" s="9" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="F384" s="9" t="n">
-        <v>34350</v>
-      </c>
-      <c r="G384" s="10">
-        <v>46189</v>
-      </c>
-      <c r="H384" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I384" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J384" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="385" customHeight="1" ht="15" spans="1:5">
-      <c r="A385" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B385" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C385" s="13" t="n">
-        <v>34350</v>
-      </c>
-      <c r="D385" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E385" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="386" customHeight="1" ht="15" spans="1:1">
       <c r="A386" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="387" customHeight="1" ht="37.05" spans="1:10">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="387" customHeight="1" ht="15" spans="1:10">
       <c r="A387" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B387" s="6" t="s">
-        <v>202</v>
+        <v>115</v>
       </c>
       <c r="C387" s="7" t="s">
         <v>203</v>
       </c>
       <c r="D387" s="8" t="n">
-        <v>24000</v>
+        <v>240</v>
       </c>
       <c r="E387" s="9" t="n">
-        <v>13</v>
+        <v>9.74</v>
       </c>
       <c r="F387" s="9" t="n">
-        <v>312000</v>
+        <v>2337.6</v>
       </c>
       <c r="G387" s="10">
-        <v>46100</v>
+        <v>46197</v>
       </c>
       <c r="H387" s="8" t="n">
-        <v>18900</v>
+        <v>0</v>
       </c>
       <c r="I387" s="11" t="n">
-        <v>78.75</v>
+        <v>0</v>
       </c>
       <c r="J387" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="388" customHeight="1" ht="15" spans="1:5">
@@ -9406,192 +9400,192 @@
         <v>20</v>
       </c>
       <c r="C388" s="13" t="n">
-        <v>312000</v>
+        <v>2337.6</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E388" s="14" t="n">
-        <v>18900</v>
-      </c>
-    </row>
-    <row r="389" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A389" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="390" customHeight="1" ht="15" spans="1:12">
-      <c r="A390" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" customHeight="1" ht="15" spans="1:1">
+      <c r="A389" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="390" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A390" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B390" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C390" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D390" s="8" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E390" s="9" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="F390" s="9" t="n">
+        <v>33823.2</v>
+      </c>
+      <c r="G390" s="10">
+        <v>46162</v>
+      </c>
+      <c r="H390" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I390" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J390" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="391" customHeight="1" ht="15" spans="1:5">
+      <c r="A391" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B391" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C391" s="13" t="n">
+        <v>33823.2</v>
+      </c>
+      <c r="D391" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E391" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" customHeight="1" ht="15" spans="1:1">
+      <c r="A392" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="393" customHeight="1" ht="19.55" spans="1:10">
+      <c r="A393" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B393" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C393" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D393" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="E393" s="9" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="F393" s="9" t="n">
+        <v>1989.6</v>
+      </c>
+      <c r="G393" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H393" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I393" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J393" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="394" customHeight="1" ht="15" spans="1:5">
+      <c r="A394" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B394" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C394" s="13" t="n">
+        <v>1989.6</v>
+      </c>
+      <c r="D394" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E394" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A395" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" customHeight="1" ht="15" spans="1:12">
+      <c r="A396" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B390" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C390" s="2" t="s">
+      <c r="B396" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C396" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D390" s="2" t="s">
+      <c r="D396" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E390" s="4" t="s">
+      <c r="E396" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F390" s="4" t="s">
+      <c r="F396" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G390" s="4" t="s">
+      <c r="G396" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H390" s="4" t="s">
+      <c r="H396" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I390" s="4" t="s">
+      <c r="I396" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J390" s="4" t="s">
+      <c r="J396" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K390" s="2" t="s">
+      <c r="K396" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L390" s="4" t="s">
+      <c r="L396" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="391" customHeight="1" ht="15" spans="1:1">
-      <c r="A391" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="392" customHeight="1" ht="15" spans="1:10">
-      <c r="A392" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B392" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C392" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="D392" s="8" t="n">
-        <v>240</v>
-      </c>
-      <c r="E392" s="9" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="F392" s="9" t="n">
-        <v>2337.6</v>
-      </c>
-      <c r="G392" s="10">
-        <v>46197</v>
-      </c>
-      <c r="H392" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I392" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J392" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="393" customHeight="1" ht="15" spans="1:5">
-      <c r="A393" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B393" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C393" s="13" t="n">
-        <v>2337.6</v>
-      </c>
-      <c r="D393" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E393" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="394" customHeight="1" ht="15" spans="1:1">
-      <c r="A394" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="395" customHeight="1" ht="18.8" spans="1:10">
-      <c r="A395" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B395" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C395" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D395" s="8" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E395" s="9" t="n">
-        <v>16.58</v>
-      </c>
-      <c r="F395" s="9" t="n">
-        <v>33823.2</v>
-      </c>
-      <c r="G395" s="10">
-        <v>46162</v>
-      </c>
-      <c r="H395" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I395" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J395" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="396" customHeight="1" ht="15" spans="1:5">
-      <c r="A396" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B396" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C396" s="13" t="n">
-        <v>33823.2</v>
-      </c>
-      <c r="D396" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E396" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="397" customHeight="1" ht="15" spans="1:1">
       <c r="A397" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="398" customHeight="1" ht="19.55" spans="1:10">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="398" customHeight="1" ht="15" spans="1:10">
       <c r="A398" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B398" s="6" t="s">
-        <v>131</v>
+        <v>194</v>
       </c>
       <c r="C398" s="7" t="s">
         <v>206</v>
       </c>
       <c r="D398" s="8" t="n">
-        <v>120</v>
+        <v>4032</v>
       </c>
       <c r="E398" s="9" t="n">
-        <v>16.58</v>
+        <v>6.99</v>
       </c>
       <c r="F398" s="9" t="n">
-        <v>1989.6</v>
+        <v>28183.68</v>
       </c>
       <c r="G398" s="10">
-        <v>46198</v>
+        <v>46167</v>
       </c>
       <c r="H398" s="8" t="n">
         <v>0</v>
@@ -9600,7 +9594,7 @@
         <v>0</v>
       </c>
       <c r="J398" s="8" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
     </row>
     <row r="399" customHeight="1" ht="15" spans="1:5">
@@ -9611,7 +9605,7 @@
         <v>20</v>
       </c>
       <c r="C399" s="13" t="n">
-        <v>1989.6</v>
+        <v>28183.68</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>19</v>
@@ -9620,237 +9614,237 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A400" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="401" customHeight="1" ht="15" spans="1:12">
-      <c r="A401" s="2" t="s">
+    <row r="400" customHeight="1" ht="15" spans="1:1">
+      <c r="A400" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="401" customHeight="1" ht="45.6" spans="1:10">
+      <c r="A401" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B401" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C401" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D401" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E401" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F401" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G401" s="10">
+        <v>46191</v>
+      </c>
+      <c r="H401" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I401" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J401" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="402" customHeight="1" ht="15" spans="1:5">
+      <c r="A402" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B402" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C402" s="13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D402" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E402" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" customHeight="1" ht="15" spans="1:1">
+      <c r="A403" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="404" customHeight="1" ht="15" spans="1:10">
+      <c r="A404" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B404" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C404" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D404" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="E404" s="9" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="F404" s="9" t="n">
+        <v>7110</v>
+      </c>
+      <c r="G404" s="10">
+        <v>46197</v>
+      </c>
+      <c r="H404" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I404" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J404" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="405" customHeight="1" ht="15" spans="1:5">
+      <c r="A405" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B405" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C405" s="13" t="n">
+        <v>7110</v>
+      </c>
+      <c r="D405" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E405" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" customHeight="1" ht="15" spans="1:1">
+      <c r="A406" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="407" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A407" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B407" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C407" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D407" s="8" t="n">
+        <v>720</v>
+      </c>
+      <c r="E407" s="9" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="F407" s="9" t="n">
+        <v>17064</v>
+      </c>
+      <c r="G407" s="10">
+        <v>46169</v>
+      </c>
+      <c r="H407" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I407" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J407" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="408" customHeight="1" ht="15" spans="1:5">
+      <c r="A408" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B408" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C408" s="13" t="n">
+        <v>17064</v>
+      </c>
+      <c r="D408" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E408" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A409" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" customHeight="1" ht="15" spans="1:12">
+      <c r="A410" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B401" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C401" s="2" t="s">
+      <c r="B410" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C410" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D401" s="2" t="s">
+      <c r="D410" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E401" s="4" t="s">
+      <c r="E410" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F401" s="4" t="s">
+      <c r="F410" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G401" s="4" t="s">
+      <c r="G410" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H401" s="4" t="s">
+      <c r="H410" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I401" s="4" t="s">
+      <c r="I410" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J401" s="4" t="s">
+      <c r="J410" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K401" s="2" t="s">
+      <c r="K410" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L401" s="4" t="s">
+      <c r="L410" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="402" customHeight="1" ht="15" spans="1:1">
-      <c r="A402" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="403" customHeight="1" ht="15" spans="1:10">
-      <c r="A403" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B403" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C403" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="D403" s="8" t="n">
-        <v>4032</v>
-      </c>
-      <c r="E403" s="9" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F403" s="9" t="n">
-        <v>28183.68</v>
-      </c>
-      <c r="G403" s="10">
-        <v>46167</v>
-      </c>
-      <c r="H403" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I403" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J403" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="404" customHeight="1" ht="15" spans="1:5">
-      <c r="A404" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B404" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C404" s="13" t="n">
-        <v>28183.68</v>
-      </c>
-      <c r="D404" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E404" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405" customHeight="1" ht="15" spans="1:1">
-      <c r="A405" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="406" customHeight="1" ht="15" spans="1:10">
-      <c r="A406" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B406" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C406" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="D406" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E406" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F406" s="9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G406" s="10">
-        <v>46191</v>
-      </c>
-      <c r="H406" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I406" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J406" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="407" customHeight="1" ht="15" spans="1:5">
-      <c r="A407" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B407" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C407" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D407" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E407" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="408" customHeight="1" ht="15" spans="1:1">
-      <c r="A408" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="409" customHeight="1" ht="15" spans="1:10">
-      <c r="A409" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B409" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C409" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="D409" s="8" t="n">
-        <v>600</v>
-      </c>
-      <c r="E409" s="9" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="F409" s="9" t="n">
-        <v>7110</v>
-      </c>
-      <c r="G409" s="10">
-        <v>46197</v>
-      </c>
-      <c r="H409" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I409" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J409" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="410" customHeight="1" ht="15" spans="1:5">
-      <c r="A410" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B410" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C410" s="13" t="n">
-        <v>7110</v>
-      </c>
-      <c r="D410" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E410" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="411" customHeight="1" ht="15" spans="1:1">
       <c r="A411" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="412" customHeight="1" ht="18.45" spans="1:10">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="412" customHeight="1" ht="20.4" spans="1:10">
       <c r="A412" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B412" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C412" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C412" s="7" t="s">
-        <v>214</v>
-      </c>
       <c r="D412" s="8" t="n">
-        <v>720</v>
+        <v>96</v>
       </c>
       <c r="E412" s="9" t="n">
-        <v>23.7</v>
+        <v>19.22</v>
       </c>
       <c r="F412" s="9" t="n">
-        <v>17064</v>
+        <v>1845.12</v>
       </c>
       <c r="G412" s="10">
-        <v>46169</v>
+        <v>46198</v>
       </c>
       <c r="H412" s="8" t="n">
         <v>0</v>
@@ -9859,7 +9853,7 @@
         <v>0</v>
       </c>
       <c r="J412" s="8" t="s">
-        <v>162</v>
+        <v>75</v>
       </c>
     </row>
     <row r="413" customHeight="1" ht="15" spans="1:5">
@@ -9870,7 +9864,7 @@
         <v>20</v>
       </c>
       <c r="C413" s="13" t="n">
-        <v>17064</v>
+        <v>1845.12</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>19</v>
@@ -9889,7 +9883,7 @@
         <v>1</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>3</v>
@@ -9924,27 +9918,27 @@
     </row>
     <row r="416" customHeight="1" ht="15" spans="1:1">
       <c r="A416" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="417" customHeight="1" ht="20.4" spans="1:10">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="417" customHeight="1" ht="15" spans="1:10">
       <c r="A417" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B417" s="6" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="C417" s="7" t="s">
         <v>215</v>
       </c>
       <c r="D417" s="8" t="n">
-        <v>96</v>
+        <v>2016</v>
       </c>
       <c r="E417" s="9" t="n">
-        <v>19.22</v>
+        <v>6.99</v>
       </c>
       <c r="F417" s="9" t="n">
-        <v>1845.12</v>
+        <v>14091.84</v>
       </c>
       <c r="G417" s="10">
         <v>46198</v>
@@ -9956,7 +9950,7 @@
         <v>0</v>
       </c>
       <c r="J417" s="8" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
     </row>
     <row r="418" customHeight="1" ht="15" spans="1:5">
@@ -9967,7 +9961,7 @@
         <v>20</v>
       </c>
       <c r="C418" s="13" t="n">
-        <v>1845.12</v>
+        <v>14091.84</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>19</v>
@@ -9976,237 +9970,237 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A419" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="420" customHeight="1" ht="15" spans="1:12">
-      <c r="A420" s="2" t="s">
+    <row r="419" customHeight="1" ht="15" spans="1:1">
+      <c r="A419" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="420" customHeight="1" ht="15" spans="1:10">
+      <c r="A420" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B420" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C420" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D420" s="8" t="n">
+        <v>648</v>
+      </c>
+      <c r="E420" s="9" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F420" s="9" t="n">
+        <v>4529.52</v>
+      </c>
+      <c r="G420" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H420" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I420" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J420" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="421" customHeight="1" ht="15" spans="1:5">
+      <c r="A421" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B421" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C421" s="13" t="n">
+        <v>4529.52</v>
+      </c>
+      <c r="D421" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E421" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" customHeight="1" ht="15" spans="1:1">
+      <c r="A422" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="423" customHeight="1" ht="15" spans="1:10">
+      <c r="A423" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B423" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C423" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D423" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E423" s="9" t="n">
+        <v>4.893</v>
+      </c>
+      <c r="F423" s="9" t="n">
+        <v>5871.6</v>
+      </c>
+      <c r="G423" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H423" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I423" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J423" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="424" customHeight="1" ht="15" spans="1:5">
+      <c r="A424" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B424" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C424" s="13" t="n">
+        <v>5871.6</v>
+      </c>
+      <c r="D424" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E424" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" customHeight="1" ht="15" spans="1:1">
+      <c r="A425" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="426" customHeight="1" ht="36.6" spans="1:10">
+      <c r="A426" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B426" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C426" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D426" s="8" t="n">
+        <v>10008</v>
+      </c>
+      <c r="E426" s="9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F426" s="9" t="n">
+        <v>66052.8</v>
+      </c>
+      <c r="G426" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H426" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I426" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J426" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="427" customHeight="1" ht="15" spans="1:5">
+      <c r="A427" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B427" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C427" s="13" t="n">
+        <v>66052.8</v>
+      </c>
+      <c r="D427" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E427" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A428" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" customHeight="1" ht="15" spans="1:12">
+      <c r="A429" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B420" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C420" s="2" t="s">
+      <c r="B429" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C429" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D420" s="2" t="s">
+      <c r="D429" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E420" s="4" t="s">
+      <c r="E429" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F420" s="4" t="s">
+      <c r="F429" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G420" s="4" t="s">
+      <c r="G429" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H420" s="4" t="s">
+      <c r="H429" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I420" s="4" t="s">
+      <c r="I429" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J420" s="4" t="s">
+      <c r="J429" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K420" s="2" t="s">
+      <c r="K429" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L420" s="4" t="s">
+      <c r="L429" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="421" customHeight="1" ht="15" spans="1:1">
-      <c r="A421" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="422" customHeight="1" ht="15" spans="1:10">
-      <c r="A422" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B422" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C422" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D422" s="8" t="n">
-        <v>2016</v>
-      </c>
-      <c r="E422" s="9" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F422" s="9" t="n">
-        <v>14091.84</v>
-      </c>
-      <c r="G422" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H422" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I422" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J422" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="423" customHeight="1" ht="15" spans="1:5">
-      <c r="A423" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B423" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C423" s="13" t="n">
-        <v>14091.84</v>
-      </c>
-      <c r="D423" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E423" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="424" customHeight="1" ht="15" spans="1:1">
-      <c r="A424" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="425" customHeight="1" ht="15" spans="1:10">
-      <c r="A425" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B425" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C425" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D425" s="8" t="n">
-        <v>648</v>
-      </c>
-      <c r="E425" s="9" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F425" s="9" t="n">
-        <v>4529.52</v>
-      </c>
-      <c r="G425" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H425" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I425" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J425" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="426" customHeight="1" ht="15" spans="1:5">
-      <c r="A426" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B426" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C426" s="13" t="n">
-        <v>4529.52</v>
-      </c>
-      <c r="D426" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E426" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="427" customHeight="1" ht="15" spans="1:1">
-      <c r="A427" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="428" customHeight="1" ht="15" spans="1:10">
-      <c r="A428" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B428" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C428" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D428" s="8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E428" s="9" t="n">
-        <v>4.893</v>
-      </c>
-      <c r="F428" s="9" t="n">
-        <v>5871.6</v>
-      </c>
-      <c r="G428" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H428" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I428" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J428" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="429" customHeight="1" ht="15" spans="1:5">
-      <c r="A429" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B429" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C429" s="13" t="n">
-        <v>5871.6</v>
-      </c>
-      <c r="D429" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E429" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="430" customHeight="1" ht="15" spans="1:1">
       <c r="A430" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="431" customHeight="1" ht="36.6" spans="1:10">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="431" customHeight="1" ht="15" spans="1:10">
       <c r="A431" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B431" s="6" t="s">
-        <v>218</v>
+        <v>115</v>
       </c>
       <c r="C431" s="7" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D431" s="8" t="n">
-        <v>10008</v>
+        <v>1584</v>
       </c>
       <c r="E431" s="9" t="n">
-        <v>6.6</v>
+        <v>6.99</v>
       </c>
       <c r="F431" s="9" t="n">
-        <v>66052.8</v>
+        <v>11072.16</v>
       </c>
       <c r="G431" s="10">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="H431" s="8" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="J431" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="432" customHeight="1" ht="15" spans="1:5">
@@ -10226,7 +10220,7 @@
         <v>20</v>
       </c>
       <c r="C432" s="13" t="n">
-        <v>66052.8</v>
+        <v>11072.16</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>19</v>
@@ -10235,316 +10229,219 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A433" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="434" customHeight="1" ht="15" spans="1:12">
-      <c r="A434" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B434" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C434" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D434" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E434" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F434" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G434" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H434" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I434" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J434" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K434" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L434" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="435" customHeight="1" ht="15" spans="1:1">
-      <c r="A435" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="436" customHeight="1" ht="15" spans="1:10">
-      <c r="A436" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B436" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C436" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D436" s="8" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E436" s="9" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F436" s="9" t="n">
-        <v>11072.16</v>
-      </c>
-      <c r="G436" s="10">
-        <v>46197</v>
-      </c>
-      <c r="H436" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I436" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J436" s="8" t="s">
+    <row r="433" customHeight="1" ht="15" spans="1:1">
+      <c r="A433" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="434" customHeight="1" ht="15" spans="1:10">
+      <c r="A434" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B434" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C434" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D434" s="8" t="n">
+        <v>10008</v>
+      </c>
+      <c r="E434" s="9" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="F434" s="9" t="n">
+        <v>59947.92</v>
+      </c>
+      <c r="G434" s="10">
+        <v>46181</v>
+      </c>
+      <c r="H434" s="8" t="n">
+        <v>2808</v>
+      </c>
+      <c r="I434" s="11" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="J434" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="435" customHeight="1" ht="15" spans="1:5">
+      <c r="A435" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B435" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C435" s="13" t="n">
+        <v>59947.92</v>
+      </c>
+      <c r="D435" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E435" s="14" t="n">
+        <v>2808</v>
+      </c>
+    </row>
+    <row r="436" customHeight="1" ht="15" spans="1:1">
+      <c r="A436" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="437" customHeight="1" ht="15" spans="1:10">
+      <c r="A437" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B437" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C437" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D437" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="E437" s="9" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="F437" s="9" t="n">
+        <v>4599</v>
+      </c>
+      <c r="G437" s="10">
+        <v>46199</v>
+      </c>
+      <c r="H437" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I437" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J437" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="438" customHeight="1" ht="15" spans="1:5">
+      <c r="A438" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B438" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C438" s="13" t="n">
+        <v>4599</v>
+      </c>
+      <c r="D438" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E438" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" customHeight="1" ht="15" spans="1:1">
+      <c r="A439" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="440" customHeight="1" ht="15" spans="1:10">
+      <c r="A440" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B440" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C440" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D440" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E440" s="9" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="F440" s="9" t="n">
+        <v>1156.8</v>
+      </c>
+      <c r="G440" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H440" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I440" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J440" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="441" customHeight="1" ht="15" spans="1:5">
+      <c r="A441" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B441" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C441" s="13" t="n">
+        <v>1156.8</v>
+      </c>
+      <c r="D441" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E441" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" customHeight="1" ht="15" spans="1:1">
+      <c r="A442" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="443" customHeight="1" ht="15" spans="1:10">
+      <c r="A443" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B443" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C443" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D443" s="8" t="n">
+        <v>1512</v>
+      </c>
+      <c r="E443" s="9" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="F443" s="9" t="n">
+        <v>10251.36</v>
+      </c>
+      <c r="G443" s="10">
+        <v>46195</v>
+      </c>
+      <c r="H443" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I443" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J443" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="437" customHeight="1" ht="15" spans="1:5">
-      <c r="A437" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B437" s="12" t="s">
+    <row r="444" customHeight="1" ht="15" spans="1:5">
+      <c r="A444" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B444" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C437" s="13" t="n">
-        <v>11072.16</v>
-      </c>
-      <c r="D437" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E437" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="438" customHeight="1" ht="15" spans="1:1">
-      <c r="A438" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="439" customHeight="1" ht="15" spans="1:10">
-      <c r="A439" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B439" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C439" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D439" s="8" t="n">
-        <v>10008</v>
-      </c>
-      <c r="E439" s="9" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="F439" s="9" t="n">
-        <v>59947.92</v>
-      </c>
-      <c r="G439" s="10">
-        <v>46181</v>
-      </c>
-      <c r="H439" s="8" t="n">
-        <v>2808</v>
-      </c>
-      <c r="I439" s="11" t="n">
-        <v>28.06</v>
-      </c>
-      <c r="J439" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="440" customHeight="1" ht="15" spans="1:5">
-      <c r="A440" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B440" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C440" s="13" t="n">
-        <v>59947.92</v>
-      </c>
-      <c r="D440" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E440" s="14" t="n">
-        <v>2808</v>
-      </c>
-    </row>
-    <row r="441" customHeight="1" ht="15" spans="1:1">
-      <c r="A441" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="442" customHeight="1" ht="15" spans="1:10">
-      <c r="A442" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B442" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C442" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="D442" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="E442" s="9" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="F442" s="9" t="n">
-        <v>4599</v>
-      </c>
-      <c r="G442" s="10">
-        <v>46199</v>
-      </c>
-      <c r="H442" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I442" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J442" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="443" customHeight="1" ht="15" spans="1:5">
-      <c r="A443" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B443" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C443" s="13" t="n">
-        <v>4599</v>
-      </c>
-      <c r="D443" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E443" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="444" customHeight="1" ht="15" spans="1:1">
-      <c r="A444" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="445" customHeight="1" ht="15" spans="1:10">
-      <c r="A445" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B445" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C445" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="D445" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="E445" s="9" t="n">
-        <v>14.46</v>
-      </c>
-      <c r="F445" s="9" t="n">
-        <v>1156.8</v>
-      </c>
-      <c r="G445" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H445" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I445" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J445" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="446" customHeight="1" ht="15" spans="1:5">
-      <c r="A446" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B446" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C446" s="13" t="n">
-        <v>1156.8</v>
-      </c>
-      <c r="D446" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E446" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="447" customHeight="1" ht="15" spans="1:1">
-      <c r="A447" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="448" customHeight="1" ht="15" spans="1:10">
-      <c r="A448" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B448" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C448" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D448" s="8" t="n">
-        <v>1512</v>
-      </c>
-      <c r="E448" s="9" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="F448" s="9" t="n">
+      <c r="C444" s="13" t="n">
         <v>10251.36</v>
       </c>
-      <c r="G448" s="10">
-        <v>46195</v>
-      </c>
-      <c r="H448" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I448" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J448" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="449" customHeight="1" ht="15" spans="1:5">
-      <c r="A449" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B449" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C449" s="13" t="n">
-        <v>10251.36</v>
-      </c>
-      <c r="D449" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E449" s="14" t="n">
+      <c r="D444" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E444" s="14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="226">
   <si>
     <t>MATRIZ CNPJ: 40.357.820/0001-50R Y DOIS - 58082-025
  ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
@@ -347,9 +347,6 @@
     <t>JOSEMAR - BA</t>
   </si>
   <si>
-    <t>965</t>
-  </si>
-  <si>
     <t>K C L COSTA COMERCIO ATAC. DE MAT. HOSP. LTDA</t>
   </si>
   <si>
@@ -440,21 +437,31 @@
     <t>CAMPO - 25 X 28 C/05</t>
   </si>
   <si>
+    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>1023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1588 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND </t>
+  </si>
+  <si>
+    <t>DANILO - AL/SE/BA</t>
+  </si>
+  <si>
     <t>DBV COMERCIO IMPORTACAO E EXPORTACAO DO BRASIL LTDA</t>
   </si>
   <si>
     <t>704</t>
   </si>
   <si>
-    <t>2073 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND Observação: CONFORME ACORDADO ENTREGA DE 70.000 POR MÊS. 20/04 - 20/05 - 20/06</t>
+    <t>2073 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UNDObservação: CONFORME ACORDADO
+ ENTREGA DE 70.000 POR MÊS. 20/04 - 20/05 - 20/06</t>
   </si>
   <si>
     <t>ELIENE RESENDE - RJ</t>
   </si>
   <si>
-    <t xml:space="preserve">1588 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND </t>
-  </si>
-  <si>
     <t>884</t>
   </si>
   <si>
@@ -476,10 +483,8 @@
     <t>945</t>
   </si>
   <si>
-    <t>1588 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND  Observação:  ***MEIA NOTA (34 VOLUMES)***</t>
-  </si>
-  <si>
-    <t>DANILO - AL/SE/BA</t>
+    <t>1588 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND Observação: 
+ ***MEIA NOTA (34 VOLUMES)***</t>
   </si>
   <si>
     <t>CAMPO - 45 X 50</t>
@@ -509,157 +514,160 @@
     <t>974</t>
   </si>
   <si>
+    <t>RICCO FARMA DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>991</t>
+  </si>
+  <si>
+    <t>155 - CAMPO OPERATORIO NAO ESTERIL 45X50  - PCT 50 UND</t>
+  </si>
+  <si>
+    <t>ESTERIL - 09 FIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 - GAZE ESTÉRIL 09 FIOS - PCT 10 UND </t>
+  </si>
+  <si>
+    <t>ESTERIL - 11 FIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND </t>
+  </si>
+  <si>
+    <t>DROGUISTA CEARENSE</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND  Observação: 35/42/56</t>
+  </si>
+  <si>
+    <t>ESTERIL - 13 FIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1643 - GAZE ESTÉRIL 13FIOS - PCT 10 UND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">03 - GAZE ESTÉRIL 13FIOS - PCT 10 UND </t>
+  </si>
+  <si>
+    <t>909</t>
+  </si>
+  <si>
+    <t>910</t>
+  </si>
+  <si>
+    <t>1014</t>
+  </si>
+  <si>
+    <t>MEDLIFE PRODUTOS MEDICO-HOSPITALARES</t>
+  </si>
+  <si>
+    <t>1024</t>
+  </si>
+  <si>
+    <t>730 - GAZE ESTÉRIL 13FIOS - MEDLIFE - PCT 10  UND</t>
+  </si>
+  <si>
+    <t>03 - GAZE ESTÉRIL 13FIOS - PCT 10 UND  Observação:  ***PREVISÃO: 09/07 ou 10/07***</t>
+  </si>
+  <si>
+    <t>MERCANTE HOSPITALAR</t>
+  </si>
+  <si>
+    <t>954</t>
+  </si>
+  <si>
+    <t>GAZE EM ROLO - 09 FIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85 - GAZE CIRCULAR NAO ESTERIL 09 FIOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">84 - GAZE  CIRCULAR NAO ESTERIL 09 FIOS </t>
+  </si>
+  <si>
+    <t>88 - GAZE CIRCULAR NAO ESTERIL 09 FIOS H Observação: FATURAR PEDIDO DIA 16/07/2026</t>
+  </si>
+  <si>
+    <t>GAZE EM ROLO - 11 FIOS</t>
+  </si>
+  <si>
+    <t>290 - CIRCULAR NAO ESTERIL 11 FIOS  Observação: FATURAR PEDIDO DIA 16/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263 - GAZE CIRCULAR NAO ESTERIL 11 FIOS </t>
+  </si>
+  <si>
+    <t>GAZE EM ROLO - 13 FIOS</t>
+  </si>
+  <si>
+    <t>CACTOS DISTRIB. DE MEDIC. E MATERIAIS</t>
+  </si>
+  <si>
+    <t>900</t>
+  </si>
+  <si>
+    <t>359 - GAZE CIRCULAR NAO ESTERIL 13 FIOS</t>
+  </si>
+  <si>
+    <t>GM FARMA COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>299 - GAZE CIRCULAR NAO ESTERIL 13 FIOS CA Observação: FATURAR PEDIDO DIA 16/07/2026</t>
+  </si>
+  <si>
+    <t>NACIONAL COMERCIO E REPRESENTACAO</t>
+  </si>
+  <si>
+    <t>644</t>
+  </si>
+  <si>
+    <t>277 - GAZE CIRCULAR NAO ESTERIL 13 FIOS EA Observação: PEDIDO PARA ENTREGAR EM  ORGÃO PÚBLICO QUANDO FATURAR ENVIAR NF-E PARA CLIENTE</t>
+  </si>
+  <si>
+    <t>PCT NÃO EST. - 11 FIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">310 - GAZE NAO ESTÉRIL 11 FIOS </t>
+  </si>
+  <si>
+    <t>339 - GAZE NAO ESTÉRIL 11 FIOS BA - PCT 500  UND</t>
+  </si>
+  <si>
+    <t>PCT NÃO EST. - 13 FIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">321 - GAZE NAO ESTÉRIL 13 FIOS </t>
+  </si>
+  <si>
+    <t>CRM COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>978</t>
+  </si>
+  <si>
+    <t>325 - GAZE NAO ESTÉRIL 13 FIOS  Observação: IMPORTATE TER NO PACOTE 140  gr. PREÇO PROPORCIONAL CONFORME ULTIMO  PREÇO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326 - GAZE NAO ESTÉRIL 13 FIOS </t>
+  </si>
+  <si>
     <t>REALMED HOSPITALAR</t>
   </si>
   <si>
-    <t>979</t>
+    <t>908</t>
+  </si>
+  <si>
+    <t>2063 - GAZE NAO ESTÉRIL 13 FIOS - PCT 500  UND</t>
   </si>
   <si>
     <t>EDSON POLONIATO - GO</t>
-  </si>
-  <si>
-    <t>RICCO FARMA DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>991</t>
-  </si>
-  <si>
-    <t>155 - CAMPO OPERATORIO NAO ESTERIL 45X50  - PCT 50 UND</t>
-  </si>
-  <si>
-    <t>ESTERIL - 09 FIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01 - GAZE ESTÉRIL 09 FIOS - PCT 10 UND </t>
-  </si>
-  <si>
-    <t>ESTERIL - 11 FIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND </t>
-  </si>
-  <si>
-    <t>DROGUISTA CEARENSE</t>
-  </si>
-  <si>
-    <t>1009</t>
-  </si>
-  <si>
-    <t>02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND  Observação: 35/42/56</t>
-  </si>
-  <si>
-    <t>ESTERIL - 13 FIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03 - GAZE ESTÉRIL 13FIOS - PCT 10 UND </t>
-  </si>
-  <si>
-    <t>909</t>
-  </si>
-  <si>
-    <t>910</t>
-  </si>
-  <si>
-    <t>1014</t>
-  </si>
-  <si>
-    <t>MERCANTE HOSPITALAR</t>
-  </si>
-  <si>
-    <t>954</t>
-  </si>
-  <si>
-    <t>GAZE EM ROLO - 09 FIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85 - GAZE CIRCULAR NAO ESTERIL 09 FIOS </t>
-  </si>
-  <si>
-    <t>ATACAMED COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>1015</t>
-  </si>
-  <si>
-    <t>85 - GAZE CIRCULAR NAO ESTERIL 09 FIOS  Observação:  ****CLIENTE VEM RETIRAR****</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84 - GAZE  CIRCULAR NAO ESTERIL 09 FIOS </t>
-  </si>
-  <si>
-    <t>88 - GAZE CIRCULAR NAO ESTERIL 09 FIOS H Observação: FATURAR PEDIDO DIA 16/07/2026</t>
-  </si>
-  <si>
-    <t>GAZE EM ROLO - 11 FIOS</t>
-  </si>
-  <si>
-    <t>290 - CIRCULAR NAO ESTERIL 11 FIOS  Observação: FATURAR PEDIDO DIA 16/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263 - GAZE CIRCULAR NAO ESTERIL 11 FIOS </t>
-  </si>
-  <si>
-    <t>GAZE EM ROLO - 13 FIOS</t>
-  </si>
-  <si>
-    <t>CACTOS DISTRIB. DE MEDIC. E MATERIAIS</t>
-  </si>
-  <si>
-    <t>900</t>
-  </si>
-  <si>
-    <t>359 - GAZE CIRCULAR NAO ESTERIL 13 FIOS</t>
-  </si>
-  <si>
-    <t>GM FARMA COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>1013</t>
-  </si>
-  <si>
-    <t>299 - GAZE CIRCULAR NAO ESTERIL 13 FIOS CA Observação: FATURAR PEDIDO DIA 16/07/2026</t>
-  </si>
-  <si>
-    <t>NACIONAL COMERCIO E REPRESENTACAO</t>
-  </si>
-  <si>
-    <t>644</t>
-  </si>
-  <si>
-    <t>277 - GAZE CIRCULAR NAO ESTERIL 13 FIOS EA Observação: PEDIDO PARA ENTREGAR EM  ORGÃO PÚBLICO QUANDO FATURAR ENVIAR NF-E PARA CLIENTE</t>
-  </si>
-  <si>
-    <t>PCT NÃO EST. - 11 FIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">310 - GAZE NAO ESTÉRIL 11 FIOS </t>
-  </si>
-  <si>
-    <t>339 - GAZE NAO ESTÉRIL 11 FIOS BA - PCT 500  UND</t>
-  </si>
-  <si>
-    <t>PCT NÃO EST. - 13 FIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">321 - GAZE NAO ESTÉRIL 13 FIOS </t>
-  </si>
-  <si>
-    <t>CRM COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>978</t>
-  </si>
-  <si>
-    <t>325 - GAZE NAO ESTÉRIL 13 FIOS  Observação: IMPORTATE TER NO PACOTE 140  gr. PREÇO PROPORCIONAL CONFORME ULTIMO  PREÇO.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">326 - GAZE NAO ESTÉRIL 13 FIOS </t>
-  </si>
-  <si>
-    <t>908</t>
-  </si>
-  <si>
-    <t>2063 - GAZE NAO ESTÉRIL 13 FIOS - PCT 500  UND</t>
   </si>
   <si>
     <t>349 - GAZE NAO ESTÉRIL 13 FIOS  - PCT 500  UND</t>
@@ -849,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L453"/>
+  <dimension ref="A1:L445"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
   <cols>
     <col customWidth="1" width="89.23828125" min="1" max="1"/>
@@ -5171,303 +5179,303 @@
         <v>110</v>
       </c>
     </row>
-    <row r="181" customHeight="1" ht="18.8" spans="1:10">
-      <c r="A181" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B181" s="6" t="s">
+    <row r="181" customHeight="1" ht="15" spans="1:5">
+      <c r="A181" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B181" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C181" s="13" t="n">
+        <v>8992</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E181" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A182" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" ht="15" spans="1:12">
+      <c r="A183" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I183" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J183" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K183" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L183" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" ht="15" spans="1:1">
+      <c r="A184" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C181" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D181" s="8" t="n">
-        <v>330</v>
-      </c>
-      <c r="E181" s="9" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="F181" s="9" t="n">
-        <v>1372.8</v>
-      </c>
-      <c r="G181" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H181" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I181" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J181" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="182" customHeight="1" ht="18.95" spans="1:10">
-      <c r="A182" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B182" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C182" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D182" s="8" t="n">
-        <v>540</v>
-      </c>
-      <c r="E182" s="9" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="F182" s="9" t="n">
-        <v>3180.6</v>
-      </c>
-      <c r="G182" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H182" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I182" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J182" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="183" customHeight="1" ht="20.5" spans="1:10">
-      <c r="A183" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B183" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C183" s="7" t="s">
+    </row>
+    <row r="185" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A185" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C185" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D183" s="8" t="n">
+      <c r="D185" s="8" t="n">
         <v>225</v>
       </c>
-      <c r="E183" s="9" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="F183" s="9" t="n">
-        <v>1872</v>
-      </c>
-      <c r="G183" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H183" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I183" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J183" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="184" customHeight="1" ht="20.6" spans="1:10">
-      <c r="A184" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B184" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C184" s="7" t="s">
+      <c r="E185" s="9" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="F185" s="9" t="n">
+        <v>1930.5</v>
+      </c>
+      <c r="G185" s="10">
+        <v>46182</v>
+      </c>
+      <c r="H185" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" ht="19.4" spans="1:10">
+      <c r="A186" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C186" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D184" s="8" t="n">
-        <v>140</v>
-      </c>
-      <c r="E184" s="9" t="n">
-        <v>7.59</v>
-      </c>
-      <c r="F184" s="9" t="n">
-        <v>1062.6</v>
-      </c>
-      <c r="G184" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H184" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I184" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J184" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="185" customHeight="1" ht="15" spans="1:5">
-      <c r="A185" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B185" s="12" t="s">
+      <c r="D186" s="8" t="n">
+        <v>210</v>
+      </c>
+      <c r="E186" s="9" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="F186" s="9" t="n">
+        <v>1644.3</v>
+      </c>
+      <c r="G186" s="10">
+        <v>46182</v>
+      </c>
+      <c r="H186" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" ht="15" spans="1:5">
+      <c r="A187" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B187" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C185" s="13" t="n">
-        <v>16480</v>
-      </c>
-      <c r="D185" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E185" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A186" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" customHeight="1" ht="15" spans="1:12">
-      <c r="A187" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E187" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F187" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G187" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H187" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I187" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J187" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K187" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L187" s="4" t="s">
-        <v>12</v>
+      <c r="C187" s="13" t="n">
+        <v>3574.8</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E187" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="188" customHeight="1" ht="15" spans="1:1">
       <c r="A188" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="189" customHeight="1" ht="20.4" spans="1:10">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" ht="19.8" spans="1:10">
       <c r="A189" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C189" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D189" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="E189" s="9" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="F189" s="9" t="n">
+        <v>2464</v>
+      </c>
+      <c r="G189" s="10">
+        <v>46199.4372916667</v>
+      </c>
+      <c r="H189" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" ht="18.45" spans="1:10">
+      <c r="A190" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D190" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="E190" s="9" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="F190" s="9" t="n">
+        <v>6984</v>
+      </c>
+      <c r="G190" s="10">
+        <v>46199.4372916667</v>
+      </c>
+      <c r="H190" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" ht="19.3" spans="1:10">
+      <c r="A191" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C191" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D189" s="8" t="n">
-        <v>225</v>
-      </c>
-      <c r="E189" s="9" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="F189" s="9" t="n">
-        <v>1930.5</v>
-      </c>
-      <c r="G189" s="10">
-        <v>46182</v>
-      </c>
-      <c r="H189" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I189" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J189" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="190" customHeight="1" ht="19.4" spans="1:10">
-      <c r="A190" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B190" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C190" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D190" s="8" t="n">
+      <c r="D191" s="8" t="n">
+        <v>750</v>
+      </c>
+      <c r="E191" s="9" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="F191" s="9" t="n">
+        <v>6817.5</v>
+      </c>
+      <c r="G191" s="10">
+        <v>46199.4372916667</v>
+      </c>
+      <c r="H191" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="192" customHeight="1" ht="19.9" spans="1:10">
+      <c r="A192" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D192" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="E192" s="9" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="F192" s="9" t="n">
+        <v>3537</v>
+      </c>
+      <c r="G192" s="10">
+        <v>46199.4372916667</v>
+      </c>
+      <c r="H192" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A193" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D193" s="8" t="n">
         <v>210</v>
       </c>
-      <c r="E190" s="9" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="F190" s="9" t="n">
-        <v>1644.3</v>
-      </c>
-      <c r="G190" s="10">
-        <v>46182</v>
-      </c>
-      <c r="H190" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I190" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J190" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="191" customHeight="1" ht="15" spans="1:5">
-      <c r="A191" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B191" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C191" s="13" t="n">
-        <v>3574.8</v>
-      </c>
-      <c r="D191" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E191" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" customHeight="1" ht="15" spans="1:1">
-      <c r="A192" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="193" customHeight="1" ht="19.8" spans="1:10">
-      <c r="A193" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B193" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C193" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D193" s="8" t="n">
-        <v>400</v>
-      </c>
       <c r="E193" s="9" t="n">
-        <v>6.16</v>
+        <v>5.68</v>
       </c>
       <c r="F193" s="9" t="n">
-        <v>2464</v>
+        <v>1192.8</v>
       </c>
       <c r="G193" s="10">
         <v>46199.4372916667</v>
@@ -5482,325 +5490,283 @@
         <v>23</v>
       </c>
     </row>
-    <row r="194" customHeight="1" ht="18.45" spans="1:10">
-      <c r="A194" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B194" s="6" t="s">
+    <row r="194" customHeight="1" ht="15" spans="1:5">
+      <c r="A194" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B194" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C194" s="13" t="n">
+        <v>20995.3</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E194" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A195" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" customHeight="1" ht="15" spans="1:12">
+      <c r="A196" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E196" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G196" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H196" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J196" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K196" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L196" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197" customHeight="1" ht="15" spans="1:1">
+      <c r="A197" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C194" s="7" t="s">
+    </row>
+    <row r="198" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A198" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D198" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E198" s="9" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="F198" s="9" t="n">
+        <v>1162</v>
+      </c>
+      <c r="G198" s="10">
+        <v>46197</v>
+      </c>
+      <c r="H198" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199" customHeight="1" ht="19.4" spans="1:10">
+      <c r="A199" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C199" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D194" s="8" t="n">
+      <c r="D199" s="8" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E199" s="9" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="F199" s="9" t="n">
+        <v>7905.6</v>
+      </c>
+      <c r="G199" s="10">
+        <v>46197</v>
+      </c>
+      <c r="H199" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="200" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A200" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D200" s="8" t="n">
         <v>900</v>
       </c>
-      <c r="E194" s="9" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="F194" s="9" t="n">
-        <v>6984</v>
-      </c>
-      <c r="G194" s="10">
-        <v>46199.4372916667</v>
-      </c>
-      <c r="H194" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I194" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J194" s="8" t="s">
+      <c r="E200" s="9" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="F200" s="9" t="n">
+        <v>7722</v>
+      </c>
+      <c r="G200" s="10">
+        <v>46197</v>
+      </c>
+      <c r="H200" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A201" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D201" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="E201" s="9" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="F201" s="9" t="n">
+        <v>10008</v>
+      </c>
+      <c r="G201" s="10">
+        <v>46197</v>
+      </c>
+      <c r="H201" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" ht="15" spans="1:5">
+      <c r="A202" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B202" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C202" s="13" t="n">
+        <v>26797.6</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E202" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" ht="15" spans="1:1">
+      <c r="A203" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" ht="19.3" spans="1:10">
+      <c r="A204" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D204" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E204" s="9" t="n">
+        <v>5.8322</v>
+      </c>
+      <c r="F204" s="9" t="n">
+        <v>583.22</v>
+      </c>
+      <c r="G204" s="10">
+        <v>46199</v>
+      </c>
+      <c r="H204" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="195" customHeight="1" ht="19.3" spans="1:10">
-      <c r="A195" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B195" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C195" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D195" s="8" t="n">
-        <v>750</v>
-      </c>
-      <c r="E195" s="9" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="F195" s="9" t="n">
-        <v>6817.5</v>
-      </c>
-      <c r="G195" s="10">
-        <v>46199.4372916667</v>
-      </c>
-      <c r="H195" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I195" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J195" s="8" t="s">
+    <row r="205" customHeight="1" ht="19.9" spans="1:10">
+      <c r="A205" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D205" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E205" s="9" t="n">
+        <v>7.3875</v>
+      </c>
+      <c r="F205" s="9" t="n">
+        <v>664.875</v>
+      </c>
+      <c r="G205" s="10">
+        <v>46199</v>
+      </c>
+      <c r="H205" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" s="8" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="196" customHeight="1" ht="19.9" spans="1:10">
-      <c r="A196" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B196" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C196" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D196" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="E196" s="9" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="F196" s="9" t="n">
-        <v>3537</v>
-      </c>
-      <c r="G196" s="10">
-        <v>46199.4372916667</v>
-      </c>
-      <c r="H196" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I196" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J196" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="197" customHeight="1" ht="18.35" spans="1:10">
-      <c r="A197" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B197" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C197" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D197" s="8" t="n">
-        <v>210</v>
-      </c>
-      <c r="E197" s="9" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="F197" s="9" t="n">
-        <v>1192.8</v>
-      </c>
-      <c r="G197" s="10">
-        <v>46199.4372916667</v>
-      </c>
-      <c r="H197" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I197" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J197" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="198" customHeight="1" ht="15" spans="1:5">
-      <c r="A198" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B198" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C198" s="13" t="n">
-        <v>20995.3</v>
-      </c>
-      <c r="D198" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E198" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A199" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" customHeight="1" ht="15" spans="1:12">
-      <c r="A200" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B200" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E200" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F200" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G200" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H200" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I200" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J200" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K200" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L200" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="201" customHeight="1" ht="15" spans="1:1">
-      <c r="A201" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="202" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A202" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B202" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C202" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D202" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="E202" s="9" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="F202" s="9" t="n">
-        <v>1162</v>
-      </c>
-      <c r="G202" s="10">
-        <v>46197</v>
-      </c>
-      <c r="H202" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I202" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J202" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="203" customHeight="1" ht="19.4" spans="1:10">
-      <c r="A203" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B203" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C203" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D203" s="8" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E203" s="9" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="F203" s="9" t="n">
-        <v>7905.6</v>
-      </c>
-      <c r="G203" s="10">
-        <v>46197</v>
-      </c>
-      <c r="H203" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I203" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J203" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="204" customHeight="1" ht="18.35" spans="1:10">
-      <c r="A204" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B204" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C204" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D204" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="E204" s="9" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="F204" s="9" t="n">
-        <v>7722</v>
-      </c>
-      <c r="G204" s="10">
-        <v>46197</v>
-      </c>
-      <c r="H204" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I204" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J204" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="205" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A205" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B205" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C205" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D205" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="E205" s="9" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="F205" s="9" t="n">
-        <v>10008</v>
-      </c>
-      <c r="G205" s="10">
-        <v>46197</v>
-      </c>
-      <c r="H205" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I205" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J205" s="8" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="206" customHeight="1" ht="15" spans="1:5">
@@ -5811,7 +5777,7 @@
         <v>20</v>
       </c>
       <c r="C206" s="13" t="n">
-        <v>26797.6</v>
+        <v>1248.095</v>
       </c>
       <c r="D206" s="4" t="s">
         <v>19</v>
@@ -5822,30 +5788,30 @@
     </row>
     <row r="207" customHeight="1" ht="15" spans="1:1">
       <c r="A207" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="208" customHeight="1" ht="19.3" spans="1:10">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" ht="19.65" spans="1:10">
       <c r="A208" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="D208" s="8" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="E208" s="9" t="n">
-        <v>5.8322</v>
+        <v>10.4081</v>
       </c>
       <c r="F208" s="9" t="n">
-        <v>583.22</v>
+        <v>1457.134</v>
       </c>
       <c r="G208" s="10">
-        <v>46199</v>
+        <v>46203.4999189815</v>
       </c>
       <c r="H208" s="8" t="n">
         <v>0</v>
@@ -5857,27 +5823,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="209" customHeight="1" ht="19.9" spans="1:10">
+    <row r="209" customHeight="1" ht="19.15" spans="1:10">
       <c r="A209" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="D209" s="8" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E209" s="9" t="n">
-        <v>7.3875</v>
+        <v>13.3569</v>
       </c>
       <c r="F209" s="9" t="n">
-        <v>664.875</v>
+        <v>801.414</v>
       </c>
       <c r="G209" s="10">
-        <v>46199</v>
+        <v>46203.4999189815</v>
       </c>
       <c r="H209" s="8" t="n">
         <v>0</v>
@@ -5897,7 +5863,7 @@
         <v>20</v>
       </c>
       <c r="C210" s="13" t="n">
-        <v>1248.095</v>
+        <v>2258.548</v>
       </c>
       <c r="D210" s="4" t="s">
         <v>19</v>
@@ -5906,225 +5872,225 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" customHeight="1" ht="15" spans="1:1">
-      <c r="A211" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="212" customHeight="1" ht="19.65" spans="1:10">
-      <c r="A212" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B212" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C212" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D212" s="8" t="n">
-        <v>140</v>
-      </c>
-      <c r="E212" s="9" t="n">
-        <v>10.4081</v>
-      </c>
-      <c r="F212" s="9" t="n">
-        <v>1457.134</v>
-      </c>
-      <c r="G212" s="10">
-        <v>46203.4999189815</v>
-      </c>
-      <c r="H212" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I212" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J212" s="8" t="s">
+    <row r="211" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A211" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" customHeight="1" ht="15" spans="1:12">
+      <c r="A212" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E212" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G212" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H212" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I212" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J212" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K212" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L212" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="213" customHeight="1" ht="15" spans="1:1">
+      <c r="A213" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="214" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A214" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C214" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D214" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E214" s="9" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="F214" s="9" t="n">
+        <v>641</v>
+      </c>
+      <c r="G214" s="10">
+        <v>46113</v>
+      </c>
+      <c r="H214" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="213" customHeight="1" ht="19.15" spans="1:10">
-      <c r="A213" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B213" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C213" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D213" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="E213" s="9" t="n">
-        <v>13.3569</v>
-      </c>
-      <c r="F213" s="9" t="n">
-        <v>801.414</v>
-      </c>
-      <c r="G213" s="10">
-        <v>46203.4999189815</v>
-      </c>
-      <c r="H213" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I213" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J213" s="8" t="s">
+    <row r="215" customHeight="1" ht="19.4" spans="1:10">
+      <c r="A215" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C215" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D215" s="8" t="n">
+        <v>360</v>
+      </c>
+      <c r="E215" s="9" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="F215" s="9" t="n">
+        <v>2851.2</v>
+      </c>
+      <c r="G215" s="10">
+        <v>46113</v>
+      </c>
+      <c r="H215" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="214" customHeight="1" ht="15" spans="1:5">
-      <c r="A214" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B214" s="12" t="s">
+    <row r="216" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A216" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C216" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D216" s="8" t="n">
+        <v>750</v>
+      </c>
+      <c r="E216" s="9" t="n">
+        <v>9.37</v>
+      </c>
+      <c r="F216" s="9" t="n">
+        <v>7027.5</v>
+      </c>
+      <c r="G216" s="10">
+        <v>46113</v>
+      </c>
+      <c r="H216" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A217" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C217" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D217" s="8" t="n">
+        <v>360</v>
+      </c>
+      <c r="E217" s="9" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="F217" s="9" t="n">
+        <v>4330.8</v>
+      </c>
+      <c r="G217" s="10">
+        <v>46113</v>
+      </c>
+      <c r="H217" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" ht="15" spans="1:5">
+      <c r="A218" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B218" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C214" s="13" t="n">
-        <v>2258.548</v>
-      </c>
-      <c r="D214" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E214" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A215" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" customHeight="1" ht="15" spans="1:12">
-      <c r="A216" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B216" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E216" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F216" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G216" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H216" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I216" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J216" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K216" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L216" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="217" customHeight="1" ht="15" spans="1:1">
-      <c r="A217" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="218" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A218" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B218" s="6" t="s">
+      <c r="C218" s="13" t="n">
+        <v>14850.5</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E218" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" ht="15" spans="1:1">
+      <c r="A219" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C218" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D218" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="E218" s="9" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="F218" s="9" t="n">
-        <v>641</v>
-      </c>
-      <c r="G218" s="10">
-        <v>46113</v>
-      </c>
-      <c r="H218" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I218" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J218" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="219" customHeight="1" ht="19.4" spans="1:10">
-      <c r="A219" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B219" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C219" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D219" s="8" t="n">
-        <v>360</v>
-      </c>
-      <c r="E219" s="9" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="F219" s="9" t="n">
-        <v>2851.2</v>
-      </c>
-      <c r="G219" s="10">
-        <v>46113</v>
-      </c>
-      <c r="H219" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I219" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J219" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="220" customHeight="1" ht="18.35" spans="1:10">
+    </row>
+    <row r="220" customHeight="1" ht="19.3" spans="1:10">
       <c r="A220" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="D220" s="8" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
       <c r="E220" s="9" t="n">
-        <v>9.37</v>
+        <v>5.2</v>
       </c>
       <c r="F220" s="9" t="n">
-        <v>7027.5</v>
+        <v>2860</v>
       </c>
       <c r="G220" s="10">
-        <v>46113</v>
+        <v>46164</v>
       </c>
       <c r="H220" s="8" t="n">
         <v>0</v>
@@ -6136,27 +6102,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="221" customHeight="1" ht="20.4" spans="1:10">
+    <row r="221" customHeight="1" ht="19.9" spans="1:10">
       <c r="A221" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="D221" s="8" t="n">
-        <v>360</v>
+        <v>560</v>
       </c>
       <c r="E221" s="9" t="n">
-        <v>12.03</v>
+        <v>7.5</v>
       </c>
       <c r="F221" s="9" t="n">
-        <v>4330.8</v>
+        <v>4200</v>
       </c>
       <c r="G221" s="10">
-        <v>46113</v>
+        <v>46164</v>
       </c>
       <c r="H221" s="8" t="n">
         <v>0</v>
@@ -6168,46 +6134,88 @@
         <v>23</v>
       </c>
     </row>
-    <row r="222" customHeight="1" ht="15" spans="1:5">
-      <c r="A222" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B222" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C222" s="13" t="n">
-        <v>14850.5</v>
-      </c>
-      <c r="D222" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E222" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" customHeight="1" ht="15" spans="1:1">
-      <c r="A223" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="224" customHeight="1" ht="19.3" spans="1:10">
+    <row r="222" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A222" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D222" s="8" t="n">
+        <v>550</v>
+      </c>
+      <c r="E222" s="9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F222" s="9" t="n">
+        <v>2860</v>
+      </c>
+      <c r="G222" s="10">
+        <v>46164</v>
+      </c>
+      <c r="H222" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" ht="20.15" spans="1:10">
+      <c r="A223" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D223" s="8" t="n">
+        <v>560</v>
+      </c>
+      <c r="E223" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F223" s="9" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G223" s="10">
+        <v>46164</v>
+      </c>
+      <c r="H223" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="224" customHeight="1" ht="21.1" spans="1:10">
       <c r="A224" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C224" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D224" s="8" t="n">
-        <v>550</v>
+        <v>250</v>
       </c>
       <c r="E224" s="9" t="n">
-        <v>5.2</v>
+        <v>12.1</v>
       </c>
       <c r="F224" s="9" t="n">
-        <v>2860</v>
+        <v>3025</v>
       </c>
       <c r="G224" s="10">
         <v>46164</v>
@@ -6222,91 +6230,49 @@
         <v>23</v>
       </c>
     </row>
-    <row r="225" customHeight="1" ht="19.9" spans="1:10">
-      <c r="A225" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B225" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C225" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D225" s="8" t="n">
-        <v>560</v>
-      </c>
-      <c r="E225" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F225" s="9" t="n">
-        <v>4200</v>
-      </c>
-      <c r="G225" s="10">
-        <v>46164</v>
-      </c>
-      <c r="H225" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I225" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J225" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="226" customHeight="1" ht="18.35" spans="1:10">
-      <c r="A226" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B226" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C226" s="7" t="s">
+    <row r="225" customHeight="1" ht="15" spans="1:5">
+      <c r="A225" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B225" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C225" s="13" t="n">
+        <v>17145</v>
+      </c>
+      <c r="D225" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E225" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" customHeight="1" ht="15" spans="1:1">
+      <c r="A226" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="227" customHeight="1" ht="20.6" spans="1:10">
+      <c r="A227" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C227" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D226" s="8" t="n">
-        <v>550</v>
-      </c>
-      <c r="E226" s="9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F226" s="9" t="n">
-        <v>2860</v>
-      </c>
-      <c r="G226" s="10">
-        <v>46164</v>
-      </c>
-      <c r="H226" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I226" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J226" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="227" customHeight="1" ht="20.15" spans="1:10">
-      <c r="A227" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B227" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C227" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="D227" s="8" t="n">
-        <v>560</v>
+        <v>1050</v>
       </c>
       <c r="E227" s="9" t="n">
-        <v>7.5</v>
+        <v>7.15</v>
       </c>
       <c r="F227" s="9" t="n">
-        <v>4200</v>
+        <v>7507.5</v>
       </c>
       <c r="G227" s="10">
-        <v>46164</v>
+        <v>46175</v>
       </c>
       <c r="H227" s="8" t="n">
         <v>0</v>
@@ -6315,181 +6281,223 @@
         <v>0</v>
       </c>
       <c r="J227" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="228" customHeight="1" ht="21.1" spans="1:10">
-      <c r="A228" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B228" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C228" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D228" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E228" s="9" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F228" s="9" t="n">
-        <v>3025</v>
-      </c>
-      <c r="G228" s="10">
-        <v>46164</v>
-      </c>
-      <c r="H228" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I228" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J228" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="229" customHeight="1" ht="15" spans="1:5">
-      <c r="A229" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B229" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="228" customHeight="1" ht="15" spans="1:5">
+      <c r="A228" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B228" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C229" s="13" t="n">
-        <v>17145</v>
-      </c>
-      <c r="D229" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E229" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" customHeight="1" ht="15" spans="1:1">
+      <c r="C228" s="13" t="n">
+        <v>7507.5</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E228" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A229" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" customHeight="1" ht="15" spans="1:12">
       <c r="A230" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="231" customHeight="1" ht="20.6" spans="1:10">
-      <c r="A231" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B231" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E230" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F230" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G230" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H230" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I230" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J230" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K230" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L230" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="231" customHeight="1" ht="15" spans="1:1">
+      <c r="A231" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C231" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D231" s="8" t="n">
-        <v>1050</v>
-      </c>
-      <c r="E231" s="9" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="F231" s="9" t="n">
-        <v>7507.5</v>
-      </c>
-      <c r="G231" s="10">
-        <v>46175</v>
-      </c>
-      <c r="H231" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I231" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J231" s="8" t="s">
+    </row>
+    <row r="232" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A232" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C232" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D232" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="E232" s="9" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="F232" s="9" t="n">
+        <v>3766</v>
+      </c>
+      <c r="G232" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H232" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I232" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" s="8" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="232" customHeight="1" ht="15" spans="1:5">
-      <c r="A232" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B232" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C232" s="13" t="n">
-        <v>7507.5</v>
-      </c>
-      <c r="D232" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E232" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A233" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" customHeight="1" ht="15" spans="1:12">
-      <c r="A234" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B234" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D234" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E234" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F234" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G234" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H234" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I234" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J234" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K234" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L234" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="235" customHeight="1" ht="15" spans="1:1">
-      <c r="A235" s="2" t="s">
+    <row r="233" customHeight="1" ht="19.4" spans="1:10">
+      <c r="A233" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B233" s="6" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="236" customHeight="1" ht="20.4" spans="1:10">
+      <c r="C233" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D233" s="8" t="n">
+        <v>180</v>
+      </c>
+      <c r="E233" s="9" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="F233" s="9" t="n">
+        <v>1220.4</v>
+      </c>
+      <c r="G233" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H233" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A234" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C234" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D234" s="8" t="n">
+        <v>525</v>
+      </c>
+      <c r="E234" s="9" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="F234" s="9" t="n">
+        <v>4168.5</v>
+      </c>
+      <c r="G234" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H234" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I234" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A235" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C235" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D235" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="E235" s="9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F235" s="9" t="n">
+        <v>3090</v>
+      </c>
+      <c r="G235" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H235" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I235" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="236" customHeight="1" ht="46.3" spans="1:10">
       <c r="A236" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="D236" s="8" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E236" s="9" t="n">
         <v>5.38</v>
       </c>
       <c r="F236" s="9" t="n">
-        <v>3766</v>
+        <v>3228</v>
       </c>
       <c r="G236" s="10">
-        <v>46198</v>
+        <v>46168</v>
       </c>
       <c r="H236" s="8" t="n">
         <v>0</v>
@@ -6501,27 +6509,27 @@
         <v>80</v>
       </c>
     </row>
-    <row r="237" customHeight="1" ht="19.4" spans="1:10">
+    <row r="237" customHeight="1" ht="47.15" spans="1:10">
       <c r="A237" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D237" s="8" t="n">
-        <v>180</v>
+        <v>525</v>
       </c>
       <c r="E237" s="9" t="n">
-        <v>6.78</v>
+        <v>7.94</v>
       </c>
       <c r="F237" s="9" t="n">
-        <v>1220.4</v>
+        <v>4168.5</v>
       </c>
       <c r="G237" s="10">
-        <v>46198</v>
+        <v>46168</v>
       </c>
       <c r="H237" s="8" t="n">
         <v>0</v>
@@ -6533,27 +6541,27 @@
         <v>80</v>
       </c>
     </row>
-    <row r="238" customHeight="1" ht="18.35" spans="1:10">
+    <row r="238" customHeight="1" ht="47.5" spans="1:10">
       <c r="A238" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C238" s="7" t="s">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="D238" s="8" t="n">
-        <v>525</v>
+        <v>600</v>
       </c>
       <c r="E238" s="9" t="n">
-        <v>7.94</v>
+        <v>10.3</v>
       </c>
       <c r="F238" s="9" t="n">
-        <v>4168.5</v>
+        <v>6180</v>
       </c>
       <c r="G238" s="10">
-        <v>46198</v>
+        <v>46168</v>
       </c>
       <c r="H238" s="8" t="n">
         <v>0</v>
@@ -6565,262 +6573,220 @@
         <v>80</v>
       </c>
     </row>
-    <row r="239" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A239" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B239" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C239" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D239" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="E239" s="9" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="F239" s="9" t="n">
-        <v>3090</v>
-      </c>
-      <c r="G239" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H239" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I239" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J239" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="240" customHeight="1" ht="46.3" spans="1:10">
-      <c r="A240" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B240" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C240" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D240" s="8" t="n">
-        <v>600</v>
-      </c>
-      <c r="E240" s="9" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="F240" s="9" t="n">
-        <v>3228</v>
-      </c>
-      <c r="G240" s="10">
-        <v>46168</v>
-      </c>
-      <c r="H240" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I240" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J240" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="241" customHeight="1" ht="47.15" spans="1:10">
-      <c r="A241" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B241" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C241" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D241" s="8" t="n">
-        <v>525</v>
-      </c>
-      <c r="E241" s="9" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="F241" s="9" t="n">
-        <v>4168.5</v>
-      </c>
-      <c r="G241" s="10">
-        <v>46168</v>
-      </c>
-      <c r="H241" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I241" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J241" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="242" customHeight="1" ht="47.5" spans="1:10">
-      <c r="A242" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B242" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C242" s="7" t="s">
+    <row r="239" customHeight="1" ht="15" spans="1:5">
+      <c r="A239" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B239" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C239" s="13" t="n">
+        <v>25821.4</v>
+      </c>
+      <c r="D239" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E239" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A240" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" customHeight="1" ht="15" spans="1:12">
+      <c r="A241" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B241" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D242" s="8" t="n">
-        <v>600</v>
-      </c>
-      <c r="E242" s="9" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="F242" s="9" t="n">
-        <v>6180</v>
-      </c>
-      <c r="G242" s="10">
-        <v>46168</v>
-      </c>
-      <c r="H242" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I242" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J242" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="243" customHeight="1" ht="15" spans="1:5">
-      <c r="A243" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B243" s="12" t="s">
+      <c r="C241" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E241" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G241" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H241" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I241" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J241" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K241" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L241" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="242" customHeight="1" ht="15" spans="1:1">
+      <c r="A242" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="243" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A243" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C243" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D243" s="8" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E243" s="9" t="n">
+        <v>4.9902</v>
+      </c>
+      <c r="F243" s="9" t="n">
+        <v>10479.42</v>
+      </c>
+      <c r="G243" s="10">
+        <v>46205.6880208333</v>
+      </c>
+      <c r="H243" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="244" customHeight="1" ht="15" spans="1:5">
+      <c r="A244" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B244" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C243" s="13" t="n">
-        <v>25821.4</v>
-      </c>
-      <c r="D243" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E243" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A244" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" customHeight="1" ht="15" spans="1:12">
+      <c r="C244" s="13" t="n">
+        <v>10479.42</v>
+      </c>
+      <c r="D244" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E244" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" customHeight="1" ht="15" spans="1:1">
       <c r="A245" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B245" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D245" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E245" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F245" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G245" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H245" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I245" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J245" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K245" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L245" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="246" customHeight="1" ht="15" spans="1:1">
-      <c r="A246" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="247" customHeight="1" ht="47.15" spans="1:10">
-      <c r="A247" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B247" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="246" customHeight="1" ht="46.9" spans="1:10">
+      <c r="A246" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C246" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D246" s="8" t="n">
+        <v>200100</v>
+      </c>
+      <c r="E246" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F246" s="9" t="n">
+        <v>820410</v>
+      </c>
+      <c r="G246" s="10">
+        <v>46119</v>
+      </c>
+      <c r="H246" s="8" t="n">
+        <v>86400</v>
+      </c>
+      <c r="I246" s="11" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="J246" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="247" customHeight="1" ht="15" spans="1:5">
+      <c r="A247" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B247" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C247" s="13" t="n">
+        <v>820410</v>
+      </c>
+      <c r="D247" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E247" s="14" t="n">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="248" customHeight="1" ht="15" spans="1:1">
+      <c r="A248" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="249" customHeight="1" ht="19.8" spans="1:10">
+      <c r="A249" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C249" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C247" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D247" s="8" t="n">
-        <v>200100</v>
-      </c>
-      <c r="E247" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F247" s="9" t="n">
-        <v>820410</v>
-      </c>
-      <c r="G247" s="10">
-        <v>46119</v>
-      </c>
-      <c r="H247" s="8" t="n">
-        <v>86400</v>
-      </c>
-      <c r="I247" s="11" t="n">
-        <v>43.18</v>
-      </c>
-      <c r="J247" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="248" customHeight="1" ht="15" spans="1:5">
-      <c r="A248" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B248" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C248" s="13" t="n">
-        <v>820410</v>
-      </c>
-      <c r="D248" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E248" s="14" t="n">
-        <v>86400</v>
-      </c>
-    </row>
-    <row r="249" customHeight="1" ht="15" spans="1:1">
-      <c r="A249" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="250" customHeight="1" ht="19.4" spans="1:10">
+      <c r="D249" s="8" t="n">
+        <v>50100</v>
+      </c>
+      <c r="E249" s="9" t="n">
+        <v>4.517</v>
+      </c>
+      <c r="F249" s="9" t="n">
+        <v>226301.7</v>
+      </c>
+      <c r="G249" s="10">
+        <v>46156</v>
+      </c>
+      <c r="H249" s="8" t="n">
+        <v>17100</v>
+      </c>
+      <c r="I249" s="11" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="J249" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="250" customHeight="1" ht="20.75" spans="1:10">
       <c r="A250" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D250" s="8" t="n">
         <v>50100</v>
@@ -6832,575 +6798,575 @@
         <v>226301.7</v>
       </c>
       <c r="G250" s="10">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="H250" s="8" t="n">
-        <v>17100</v>
+        <v>15000</v>
       </c>
       <c r="I250" s="11" t="n">
-        <v>34.13</v>
+        <v>29.94</v>
       </c>
       <c r="J250" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="251" customHeight="1" ht="20.25" spans="1:10">
+    <row r="251" customHeight="1" ht="18.45" spans="1:10">
       <c r="A251" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="C251" s="7" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D251" s="8" t="n">
-        <v>50100</v>
+        <v>20100</v>
       </c>
       <c r="E251" s="9" t="n">
-        <v>4.517</v>
+        <v>4.45</v>
       </c>
       <c r="F251" s="9" t="n">
-        <v>226301.7</v>
+        <v>89445</v>
       </c>
       <c r="G251" s="10">
-        <v>46163</v>
+        <v>46167</v>
       </c>
       <c r="H251" s="8" t="n">
-        <v>15000</v>
+        <v>6750</v>
       </c>
       <c r="I251" s="11" t="n">
-        <v>29.94</v>
+        <v>33.58</v>
       </c>
       <c r="J251" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="252" customHeight="1" ht="18.8" spans="1:10">
-      <c r="A252" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B252" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C252" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D252" s="8" t="n">
-        <v>20100</v>
-      </c>
-      <c r="E252" s="9" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="F252" s="9" t="n">
-        <v>89445</v>
-      </c>
-      <c r="G252" s="10">
-        <v>46167</v>
-      </c>
-      <c r="H252" s="8" t="n">
-        <v>6750</v>
-      </c>
-      <c r="I252" s="11" t="n">
-        <v>33.58</v>
-      </c>
-      <c r="J252" s="8" t="s">
+    <row r="252" customHeight="1" ht="15" spans="1:5">
+      <c r="A252" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B252" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C252" s="13" t="n">
+        <v>542048.4</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E252" s="14" t="n">
+        <v>38850</v>
+      </c>
+    </row>
+    <row r="253" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A253" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" customHeight="1" ht="15" spans="1:12">
+      <c r="A254" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E254" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F254" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G254" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H254" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I254" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J254" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K254" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L254" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="255" customHeight="1" ht="15" spans="1:1">
+      <c r="A255" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="256" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A256" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C256" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D256" s="8" t="n">
+        <v>4050</v>
+      </c>
+      <c r="E256" s="9" t="n">
+        <v>5.1798</v>
+      </c>
+      <c r="F256" s="9" t="n">
+        <v>20978.19</v>
+      </c>
+      <c r="G256" s="10">
+        <v>46204.4622685185</v>
+      </c>
+      <c r="H256" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I256" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="257" customHeight="1" ht="15" spans="1:5">
+      <c r="A257" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B257" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C257" s="13" t="n">
+        <v>20978.19</v>
+      </c>
+      <c r="D257" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E257" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" customHeight="1" ht="15" spans="1:1">
+      <c r="A258" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="259" customHeight="1" ht="36.45" spans="1:10">
+      <c r="A259" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C259" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D259" s="8" t="n">
+        <v>10200</v>
+      </c>
+      <c r="E259" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F259" s="9" t="n">
+        <v>25500</v>
+      </c>
+      <c r="G259" s="10">
+        <v>46176</v>
+      </c>
+      <c r="H259" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I259" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="260" customHeight="1" ht="15" spans="1:5">
+      <c r="A260" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B260" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C260" s="13" t="n">
+        <v>25500</v>
+      </c>
+      <c r="D260" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E260" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A261" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" customHeight="1" ht="15" spans="1:12">
+      <c r="A262" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E262" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F262" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G262" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H262" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I262" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J262" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K262" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L262" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="263" customHeight="1" ht="15" spans="1:1">
+      <c r="A263" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="264" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A264" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B264" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C264" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D264" s="8" t="n">
+        <v>3408</v>
+      </c>
+      <c r="E264" s="9" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="F264" s="9" t="n">
+        <v>153019.2</v>
+      </c>
+      <c r="G264" s="10">
+        <v>46162</v>
+      </c>
+      <c r="H264" s="8" t="n">
+        <v>1104</v>
+      </c>
+      <c r="I264" s="11" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="J264" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="253" customHeight="1" ht="15" spans="1:5">
-      <c r="A253" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B253" s="12" t="s">
+    <row r="265" customHeight="1" ht="15" spans="1:5">
+      <c r="A265" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B265" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C253" s="13" t="n">
-        <v>542048.4</v>
-      </c>
-      <c r="D253" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E253" s="14" t="n">
-        <v>38850</v>
-      </c>
-    </row>
-    <row r="254" customHeight="1" ht="15" spans="1:1">
-      <c r="A254" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="255" customHeight="1" ht="18.7" spans="1:10">
-      <c r="A255" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B255" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C255" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D255" s="8" t="n">
-        <v>4050</v>
-      </c>
-      <c r="E255" s="9" t="n">
-        <v>5.1798</v>
-      </c>
-      <c r="F255" s="9" t="n">
-        <v>20978.19</v>
-      </c>
-      <c r="G255" s="10">
-        <v>46204.4622685185</v>
-      </c>
-      <c r="H255" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I255" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J255" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="256" customHeight="1" ht="15" spans="1:5">
-      <c r="A256" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B256" s="12" t="s">
+      <c r="C265" s="13" t="n">
+        <v>153019.2</v>
+      </c>
+      <c r="D265" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E265" s="14" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="266" customHeight="1" ht="15" spans="1:1">
+      <c r="A266" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="267" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A267" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B267" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C267" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D267" s="8" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E267" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="F267" s="9" t="n">
+        <v>44352</v>
+      </c>
+      <c r="G267" s="10">
+        <v>46188</v>
+      </c>
+      <c r="H267" s="8" t="n">
+        <v>360</v>
+      </c>
+      <c r="I267" s="11" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="J267" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="268" customHeight="1" ht="15" spans="1:5">
+      <c r="A268" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B268" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C256" s="13" t="n">
-        <v>20978.19</v>
-      </c>
-      <c r="D256" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E256" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A257" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" customHeight="1" ht="15" spans="1:12">
-      <c r="A258" s="2" t="s">
+      <c r="C268" s="13" t="n">
+        <v>44352</v>
+      </c>
+      <c r="D268" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E268" s="14" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="269" customHeight="1" ht="15" spans="1:1">
+      <c r="A269" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="270" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A270" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C270" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D270" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="E270" s="9" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F270" s="9" t="n">
+        <v>28500</v>
+      </c>
+      <c r="G270" s="10">
+        <v>46195</v>
+      </c>
+      <c r="H270" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I270" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="271" customHeight="1" ht="15" spans="1:5">
+      <c r="A271" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B271" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C271" s="13" t="n">
+        <v>28500</v>
+      </c>
+      <c r="D271" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E271" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" customHeight="1" ht="15" spans="1:1">
+      <c r="A272" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="273" customHeight="1" ht="20.15" spans="1:10">
+      <c r="A273" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C273" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D273" s="8" t="n">
+        <v>804</v>
+      </c>
+      <c r="E273" s="9" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="F273" s="9" t="n">
+        <v>27858.6</v>
+      </c>
+      <c r="G273" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H273" s="8" t="n">
+        <v>192</v>
+      </c>
+      <c r="I273" s="11" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="J273" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="274" customHeight="1" ht="15" spans="1:5">
+      <c r="A274" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B274" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C274" s="13" t="n">
+        <v>27858.6</v>
+      </c>
+      <c r="D274" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E274" s="14" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="275" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A275" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" customHeight="1" ht="15" spans="1:12">
+      <c r="A276" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B258" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C258" s="2" t="s">
+      <c r="B276" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C276" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D258" s="2" t="s">
+      <c r="D276" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E258" s="4" t="s">
+      <c r="E276" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F258" s="4" t="s">
+      <c r="F276" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G258" s="4" t="s">
+      <c r="G276" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H258" s="4" t="s">
+      <c r="H276" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I258" s="4" t="s">
+      <c r="I276" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J258" s="4" t="s">
+      <c r="J276" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K258" s="2" t="s">
+      <c r="K276" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L258" s="4" t="s">
+      <c r="L276" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="259" customHeight="1" ht="15" spans="1:1">
-      <c r="A259" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="260" customHeight="1" ht="37.05" spans="1:10">
-      <c r="A260" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B260" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C260" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D260" s="8" t="n">
-        <v>10200</v>
-      </c>
-      <c r="E260" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F260" s="9" t="n">
-        <v>25500</v>
-      </c>
-      <c r="G260" s="10">
-        <v>46176</v>
-      </c>
-      <c r="H260" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I260" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J260" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="261" customHeight="1" ht="15" spans="1:5">
-      <c r="A261" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B261" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C261" s="13" t="n">
-        <v>25500</v>
-      </c>
-      <c r="D261" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E261" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A262" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" customHeight="1" ht="15" spans="1:12">
-      <c r="A263" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B263" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C263" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D263" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E263" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F263" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G263" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H263" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I263" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J263" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K263" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L263" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="264" customHeight="1" ht="15" spans="1:1">
-      <c r="A264" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="265" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A265" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B265" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C265" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D265" s="8" t="n">
-        <v>3408</v>
-      </c>
-      <c r="E265" s="9" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="F265" s="9" t="n">
-        <v>153019.2</v>
-      </c>
-      <c r="G265" s="10">
-        <v>46162</v>
-      </c>
-      <c r="H265" s="8" t="n">
-        <v>1104</v>
-      </c>
-      <c r="I265" s="11" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="J265" s="8" t="s">
+    <row r="277" customHeight="1" ht="15" spans="1:1">
+      <c r="A277" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="278" customHeight="1" ht="30.35" spans="1:10">
+      <c r="A278" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C278" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D278" s="8" t="n">
+        <v>252</v>
+      </c>
+      <c r="E278" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="F278" s="9" t="n">
+        <v>10836</v>
+      </c>
+      <c r="G278" s="10">
+        <v>46189</v>
+      </c>
+      <c r="H278" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="266" customHeight="1" ht="15" spans="1:5">
-      <c r="A266" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B266" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C266" s="13" t="n">
-        <v>153019.2</v>
-      </c>
-      <c r="D266" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E266" s="14" t="n">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="267" customHeight="1" ht="15" spans="1:1">
-      <c r="A267" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="268" customHeight="1" ht="18.35" spans="1:10">
-      <c r="A268" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B268" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C268" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D268" s="8" t="n">
-        <v>1008</v>
-      </c>
-      <c r="E268" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="F268" s="9" t="n">
-        <v>44352</v>
-      </c>
-      <c r="G268" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H268" s="8" t="n">
-        <v>360</v>
-      </c>
-      <c r="I268" s="11" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="J268" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="269" customHeight="1" ht="15" spans="1:5">
-      <c r="A269" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B269" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C269" s="13" t="n">
-        <v>44352</v>
-      </c>
-      <c r="D269" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E269" s="14" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="270" customHeight="1" ht="15" spans="1:1">
-      <c r="A270" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="271" customHeight="1" ht="18.8" spans="1:10">
-      <c r="A271" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B271" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C271" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D271" s="8" t="n">
-        <v>600</v>
-      </c>
-      <c r="E271" s="9" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="F271" s="9" t="n">
-        <v>28500</v>
-      </c>
-      <c r="G271" s="10">
-        <v>46195</v>
-      </c>
-      <c r="H271" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I271" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J271" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="272" customHeight="1" ht="15" spans="1:5">
-      <c r="A272" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B272" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C272" s="13" t="n">
-        <v>28500</v>
-      </c>
-      <c r="D272" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E272" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273" customHeight="1" ht="15" spans="1:1">
-      <c r="A273" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="274" customHeight="1" ht="20.15" spans="1:10">
-      <c r="A274" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B274" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C274" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D274" s="8" t="n">
-        <v>804</v>
-      </c>
-      <c r="E274" s="9" t="n">
-        <v>34.65</v>
-      </c>
-      <c r="F274" s="9" t="n">
-        <v>27858.6</v>
-      </c>
-      <c r="G274" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H274" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I274" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J274" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="275" customHeight="1" ht="15" spans="1:5">
-      <c r="A275" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B275" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C275" s="13" t="n">
-        <v>27858.6</v>
-      </c>
-      <c r="D275" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E275" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A276" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277" customHeight="1" ht="15" spans="1:12">
-      <c r="A277" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B277" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E277" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F277" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G277" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H277" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I277" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J277" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K277" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L277" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="278" customHeight="1" ht="15" spans="1:1">
-      <c r="A278" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="279" customHeight="1" ht="30.35" spans="1:10">
+    <row r="279" customHeight="1" ht="28.15" spans="1:10">
       <c r="A279" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D279" s="8" t="n">
-        <v>252</v>
+        <v>504</v>
       </c>
       <c r="E279" s="9" t="n">
-        <v>43</v>
+        <v>40.5</v>
       </c>
       <c r="F279" s="9" t="n">
-        <v>10836</v>
+        <v>20412</v>
       </c>
       <c r="G279" s="10">
         <v>46189</v>
@@ -7415,975 +7381,975 @@
         <v>23</v>
       </c>
     </row>
-    <row r="280" customHeight="1" ht="28.15" spans="1:10">
-      <c r="A280" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B280" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C280" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D280" s="8" t="n">
-        <v>504</v>
-      </c>
-      <c r="E280" s="9" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="F280" s="9" t="n">
-        <v>20412</v>
-      </c>
-      <c r="G280" s="10">
-        <v>46189</v>
-      </c>
-      <c r="H280" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I280" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J280" s="8" t="s">
+    <row r="280" customHeight="1" ht="15" spans="1:5">
+      <c r="A280" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B280" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C280" s="13" t="n">
+        <v>31248</v>
+      </c>
+      <c r="D280" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E280" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" customHeight="1" ht="15" spans="1:1">
+      <c r="A281" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="282" customHeight="1" ht="18.6" spans="1:10">
+      <c r="A282" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C282" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D282" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E282" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="F282" s="9" t="n">
+        <v>52800</v>
+      </c>
+      <c r="G282" s="10">
+        <v>46190</v>
+      </c>
+      <c r="H282" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="I282" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="J282" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="283" customHeight="1" ht="15" spans="1:5">
+      <c r="A283" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B283" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C283" s="13" t="n">
+        <v>52800</v>
+      </c>
+      <c r="D283" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E283" s="14" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="284" customHeight="1" ht="15" spans="1:1">
+      <c r="A284" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="285" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A285" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C285" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D285" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E285" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F285" s="9" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G285" s="10">
+        <v>46196</v>
+      </c>
+      <c r="H285" s="8" t="n">
+        <v>384</v>
+      </c>
+      <c r="I285" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="J285" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="286" customHeight="1" ht="15" spans="1:5">
+      <c r="A286" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B286" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C286" s="13" t="n">
+        <v>57600</v>
+      </c>
+      <c r="D286" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E286" s="14" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="287" customHeight="1" ht="15" spans="1:1">
+      <c r="A287" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="288" customHeight="1" ht="19.55" spans="1:10">
+      <c r="A288" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C288" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D288" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="E288" s="9" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F288" s="9" t="n">
+        <v>2376</v>
+      </c>
+      <c r="G288" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H288" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I288" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="289" customHeight="1" ht="15" spans="1:5">
+      <c r="A289" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B289" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C289" s="13" t="n">
+        <v>2376</v>
+      </c>
+      <c r="D289" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E289" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A290" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" customHeight="1" ht="15" spans="1:12">
+      <c r="A291" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E291" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F291" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G291" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H291" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I291" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J291" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K291" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L291" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="292" customHeight="1" ht="15" spans="1:1">
+      <c r="A292" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="293" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A293" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C293" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D293" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="E293" s="9" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="F293" s="9" t="n">
+        <v>14760</v>
+      </c>
+      <c r="G293" s="10">
+        <v>46203</v>
+      </c>
+      <c r="H293" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I293" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J293" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="294" customHeight="1" ht="15" spans="1:5">
+      <c r="A294" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B294" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C294" s="13" t="n">
+        <v>14760</v>
+      </c>
+      <c r="D294" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E294" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A295" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" customHeight="1" ht="15" spans="1:12">
+      <c r="A296" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E296" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F296" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G296" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H296" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I296" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J296" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K296" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L296" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="297" customHeight="1" ht="15" spans="1:1">
+      <c r="A297" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="298" customHeight="1" ht="15" spans="1:10">
+      <c r="A298" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C298" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D298" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E298" s="9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F298" s="9" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G298" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H298" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I298" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="299" customHeight="1" ht="15" spans="1:5">
+      <c r="A299" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B299" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C299" s="13" t="n">
+        <v>3600</v>
+      </c>
+      <c r="D299" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E299" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" customHeight="1" ht="15" spans="1:1">
+      <c r="A300" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="301" customHeight="1" ht="15" spans="1:10">
+      <c r="A301" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C301" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D301" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E301" s="9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F301" s="9" t="n">
+        <v>1560</v>
+      </c>
+      <c r="G301" s="10">
+        <v>46195</v>
+      </c>
+      <c r="H301" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I301" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J301" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="302" customHeight="1" ht="15" spans="1:5">
+      <c r="A302" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B302" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C302" s="13" t="n">
+        <v>1560</v>
+      </c>
+      <c r="D302" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E302" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A303" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" customHeight="1" ht="15" spans="1:12">
+      <c r="A304" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B304" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E304" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F304" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G304" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H304" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I304" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J304" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K304" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L304" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="305" customHeight="1" ht="15" spans="1:1">
+      <c r="A305" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="306" customHeight="1" ht="15" spans="1:10">
+      <c r="A306" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C306" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D306" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E306" s="9" t="n">
+        <v>0.4171</v>
+      </c>
+      <c r="F306" s="9" t="n">
+        <v>8342</v>
+      </c>
+      <c r="G306" s="10">
+        <v>46203.3600231481</v>
+      </c>
+      <c r="H306" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I306" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="307" customHeight="1" ht="15" spans="1:5">
+      <c r="A307" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B307" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C307" s="13" t="n">
+        <v>8342</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E307" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" customHeight="1" ht="15" spans="1:1">
+      <c r="A308" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="309" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A309" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C309" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D309" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E309" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F309" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G309" s="10">
+        <v>46203.3507407407</v>
+      </c>
+      <c r="H309" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="310" customHeight="1" ht="15" spans="1:5">
+      <c r="A310" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B310" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C310" s="13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E310" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" customHeight="1" ht="15" spans="1:1">
+      <c r="A311" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="312" customHeight="1" ht="15" spans="1:10">
+      <c r="A312" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C312" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D312" s="8" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E312" s="9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F312" s="9" t="n">
+        <v>23400</v>
+      </c>
+      <c r="G312" s="10">
+        <v>46199.4372916667</v>
+      </c>
+      <c r="H312" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I312" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J312" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="281" customHeight="1" ht="15" spans="1:5">
-      <c r="A281" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B281" s="12" t="s">
+    <row r="313" customHeight="1" ht="15" spans="1:5">
+      <c r="A313" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B313" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C281" s="13" t="n">
-        <v>31248</v>
-      </c>
-      <c r="D281" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E281" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282" customHeight="1" ht="15" spans="1:1">
-      <c r="A282" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="283" customHeight="1" ht="18.6" spans="1:10">
-      <c r="A283" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B283" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C283" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D283" s="8" t="n">
+      <c r="C313" s="13" t="n">
+        <v>23400</v>
+      </c>
+      <c r="D313" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E313" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" customHeight="1" ht="15" spans="1:1">
+      <c r="A314" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="315" customHeight="1" ht="15" spans="1:10">
+      <c r="A315" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B315" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="E283" s="9" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="F283" s="9" t="n">
-        <v>5700</v>
-      </c>
-      <c r="G283" s="10">
-        <v>46188</v>
-      </c>
-      <c r="H283" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I283" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J283" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="284" customHeight="1" ht="15" spans="1:5">
-      <c r="A284" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B284" s="12" t="s">
+      <c r="C315" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D315" s="8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E315" s="9" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="F315" s="9" t="n">
+        <v>17848</v>
+      </c>
+      <c r="G315" s="10">
+        <v>46203.4999189815</v>
+      </c>
+      <c r="H315" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I315" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="316" customHeight="1" ht="15" spans="1:5">
+      <c r="A316" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B316" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C284" s="13" t="n">
-        <v>5700</v>
-      </c>
-      <c r="D284" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E284" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" customHeight="1" ht="15" spans="1:1">
-      <c r="A285" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="286" customHeight="1" ht="18.8" spans="1:10">
-      <c r="A286" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B286" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C286" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D286" s="8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E286" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="F286" s="9" t="n">
-        <v>52800</v>
-      </c>
-      <c r="G286" s="10">
-        <v>46190</v>
-      </c>
-      <c r="H286" s="8" t="n">
-        <v>600</v>
-      </c>
-      <c r="I286" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="J286" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="287" customHeight="1" ht="15" spans="1:5">
-      <c r="A287" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B287" s="12" t="s">
+      <c r="C316" s="13" t="n">
+        <v>17848</v>
+      </c>
+      <c r="D316" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E316" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A317" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" customHeight="1" ht="15" spans="1:12">
+      <c r="A318" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E318" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G318" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H318" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I318" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J318" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K318" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L318" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="319" customHeight="1" ht="15" spans="1:1">
+      <c r="A319" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="320" customHeight="1" ht="15" spans="1:10">
+      <c r="A320" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C320" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D320" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E320" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F320" s="9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G320" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H320" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I320" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="321" customHeight="1" ht="15" spans="1:5">
+      <c r="A321" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B321" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C287" s="13" t="n">
-        <v>52800</v>
-      </c>
-      <c r="D287" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E287" s="14" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="288" customHeight="1" ht="15" spans="1:1">
-      <c r="A288" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="289" customHeight="1" ht="19.55" spans="1:10">
-      <c r="A289" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B289" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C289" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D289" s="8" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E289" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="F289" s="9" t="n">
-        <v>64500</v>
-      </c>
-      <c r="G289" s="10">
-        <v>46190</v>
-      </c>
-      <c r="H289" s="8" t="n">
-        <v>600</v>
-      </c>
-      <c r="I289" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="J289" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="290" customHeight="1" ht="15" spans="1:5">
-      <c r="A290" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B290" s="12" t="s">
+      <c r="C321" s="13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D321" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E321" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A322" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" customHeight="1" ht="15" spans="1:12">
+      <c r="A323" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B323" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E323" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F323" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G323" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H323" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I323" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J323" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K323" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L323" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="324" customHeight="1" ht="15" spans="1:1">
+      <c r="A324" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="325" customHeight="1" ht="15" spans="1:10">
+      <c r="A325" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B325" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C325" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D325" s="8" t="n">
+        <v>12600</v>
+      </c>
+      <c r="E325" s="9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F325" s="9" t="n">
+        <v>8316</v>
+      </c>
+      <c r="G325" s="10">
+        <v>46205.6880208333</v>
+      </c>
+      <c r="H325" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I325" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J325" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="326" customHeight="1" ht="15" spans="1:5">
+      <c r="A326" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B326" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C290" s="13" t="n">
-        <v>64500</v>
-      </c>
-      <c r="D290" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E290" s="14" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="291" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A291" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292" customHeight="1" ht="15" spans="1:12">
-      <c r="A292" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B292" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D292" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E292" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F292" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G292" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H292" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I292" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J292" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K292" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L292" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="293" customHeight="1" ht="15" spans="1:1">
-      <c r="A293" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="294" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A294" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B294" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C294" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D294" s="8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E294" s="9" t="n">
-        <v>48</v>
-      </c>
-      <c r="F294" s="9" t="n">
-        <v>57600</v>
-      </c>
-      <c r="G294" s="10">
-        <v>46196</v>
-      </c>
-      <c r="H294" s="8" t="n">
-        <v>384</v>
-      </c>
-      <c r="I294" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="J294" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="295" customHeight="1" ht="15" spans="1:5">
-      <c r="A295" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B295" s="12" t="s">
+      <c r="C326" s="13" t="n">
+        <v>8316</v>
+      </c>
+      <c r="D326" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E326" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" customHeight="1" ht="15" spans="1:1">
+      <c r="A327" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="328" customHeight="1" ht="15" spans="1:10">
+      <c r="A328" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B328" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C328" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D328" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E328" s="9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F328" s="9" t="n">
+        <v>4300</v>
+      </c>
+      <c r="G328" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H328" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I328" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J328" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="329" customHeight="1" ht="15" spans="1:5">
+      <c r="A329" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B329" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C295" s="13" t="n">
-        <v>57600</v>
-      </c>
-      <c r="D295" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E295" s="14" t="n">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="296" customHeight="1" ht="15" spans="1:1">
-      <c r="A296" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="297" customHeight="1" ht="18.35" spans="1:10">
-      <c r="A297" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B297" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C297" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D297" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="E297" s="9" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="F297" s="9" t="n">
-        <v>2376</v>
-      </c>
-      <c r="G297" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H297" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I297" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J297" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="298" customHeight="1" ht="15" spans="1:5">
-      <c r="A298" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B298" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C298" s="13" t="n">
-        <v>2376</v>
-      </c>
-      <c r="D298" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E298" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299" customHeight="1" ht="15" spans="1:1">
-      <c r="A299" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="300" customHeight="1" ht="18.8" spans="1:10">
-      <c r="A300" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B300" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C300" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D300" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="E300" s="9" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="F300" s="9" t="n">
-        <v>14760</v>
-      </c>
-      <c r="G300" s="10">
-        <v>46203</v>
-      </c>
-      <c r="H300" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I300" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J300" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="301" customHeight="1" ht="15" spans="1:5">
-      <c r="A301" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B301" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C301" s="13" t="n">
-        <v>14760</v>
-      </c>
-      <c r="D301" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E301" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A302" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303" customHeight="1" ht="15" spans="1:12">
-      <c r="A303" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B303" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C303" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D303" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E303" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F303" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G303" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H303" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I303" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J303" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K303" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L303" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="304" customHeight="1" ht="15" spans="1:1">
-      <c r="A304" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="305" customHeight="1" ht="15" spans="1:10">
-      <c r="A305" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B305" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C305" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D305" s="8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E305" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="F305" s="9" t="n">
-        <v>3600</v>
-      </c>
-      <c r="G305" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H305" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I305" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J305" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="306" customHeight="1" ht="15" spans="1:5">
-      <c r="A306" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B306" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C306" s="13" t="n">
-        <v>3600</v>
-      </c>
-      <c r="D306" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E306" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307" customHeight="1" ht="15" spans="1:1">
-      <c r="A307" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="308" customHeight="1" ht="15" spans="1:10">
-      <c r="A308" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B308" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C308" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D308" s="8" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E308" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="F308" s="9" t="n">
-        <v>1560</v>
-      </c>
-      <c r="G308" s="10">
-        <v>46195</v>
-      </c>
-      <c r="H308" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I308" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J308" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="309" customHeight="1" ht="15" spans="1:5">
-      <c r="A309" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B309" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C309" s="13" t="n">
-        <v>1560</v>
-      </c>
-      <c r="D309" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E309" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A310" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" customHeight="1" ht="15" spans="1:12">
-      <c r="A311" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B311" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C311" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D311" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E311" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F311" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G311" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H311" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I311" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J311" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K311" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L311" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="312" customHeight="1" ht="15" spans="1:1">
-      <c r="A312" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="313" customHeight="1" ht="15" spans="1:10">
-      <c r="A313" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B313" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C313" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D313" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E313" s="9" t="n">
-        <v>0.4171</v>
-      </c>
-      <c r="F313" s="9" t="n">
-        <v>8342</v>
-      </c>
-      <c r="G313" s="10">
-        <v>46203.3600231481</v>
-      </c>
-      <c r="H313" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I313" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J313" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="314" customHeight="1" ht="15" spans="1:5">
-      <c r="A314" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B314" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C314" s="13" t="n">
-        <v>8342</v>
-      </c>
-      <c r="D314" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E314" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315" customHeight="1" ht="15" spans="1:1">
-      <c r="A315" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="316" customHeight="1" ht="18.8" spans="1:10">
-      <c r="A316" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B316" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="C316" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D316" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E316" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F316" s="9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G316" s="10">
-        <v>46203.3507407407</v>
-      </c>
-      <c r="H316" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I316" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J316" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="317" customHeight="1" ht="15" spans="1:5">
-      <c r="A317" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B317" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C317" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D317" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E317" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" customHeight="1" ht="15" spans="1:1">
-      <c r="A318" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="319" customHeight="1" ht="15" spans="1:10">
-      <c r="A319" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B319" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C319" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D319" s="8" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E319" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="F319" s="9" t="n">
-        <v>23400</v>
-      </c>
-      <c r="G319" s="10">
-        <v>46199.4372916667</v>
-      </c>
-      <c r="H319" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I319" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J319" s="8" t="s">
+      <c r="C329" s="13" t="n">
+        <v>4300</v>
+      </c>
+      <c r="D329" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E329" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" customHeight="1" ht="15" spans="1:1">
+      <c r="A330" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="331" customHeight="1" ht="15" spans="1:10">
+      <c r="A331" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B331" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C331" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D331" s="8" t="n">
+        <v>205000</v>
+      </c>
+      <c r="E331" s="9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F331" s="9" t="n">
+        <v>77900</v>
+      </c>
+      <c r="G331" s="10">
+        <v>46168</v>
+      </c>
+      <c r="H331" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="I331" s="11" t="n">
+        <v>78.05</v>
+      </c>
+      <c r="J331" s="8" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="320" customHeight="1" ht="15" spans="1:5">
-      <c r="A320" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B320" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C320" s="13" t="n">
-        <v>23400</v>
-      </c>
-      <c r="D320" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E320" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321" customHeight="1" ht="15" spans="1:1">
-      <c r="A321" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="322" customHeight="1" ht="15" spans="1:10">
-      <c r="A322" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B322" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C322" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D322" s="8" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E322" s="9" t="n">
-        <v>0.4462</v>
-      </c>
-      <c r="F322" s="9" t="n">
-        <v>17848</v>
-      </c>
-      <c r="G322" s="10">
-        <v>46203.4999189815</v>
-      </c>
-      <c r="H322" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I322" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J322" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="323" customHeight="1" ht="15" spans="1:5">
-      <c r="A323" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B323" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C323" s="13" t="n">
-        <v>17848</v>
-      </c>
-      <c r="D323" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E323" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A324" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" customHeight="1" ht="15" spans="1:12">
-      <c r="A325" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B325" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C325" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D325" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E325" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F325" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G325" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H325" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I325" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J325" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K325" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L325" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="326" customHeight="1" ht="15" spans="1:1">
-      <c r="A326" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="327" customHeight="1" ht="15" spans="1:10">
-      <c r="A327" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B327" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C327" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D327" s="8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E327" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F327" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G327" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H327" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I327" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J327" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="328" customHeight="1" ht="15" spans="1:5">
-      <c r="A328" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B328" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C328" s="13" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D328" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E328" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A329" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330" customHeight="1" ht="15" spans="1:12">
-      <c r="A330" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B330" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C330" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D330" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E330" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F330" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G330" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H330" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I330" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J330" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K330" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L330" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="331" customHeight="1" ht="15" spans="1:1">
-      <c r="A331" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="332" customHeight="1" ht="15" spans="1:10">
@@ -8391,22 +8357,22 @@
         <v>14</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="C332" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D332" s="8" t="n">
-        <v>10000</v>
+        <v>205000</v>
       </c>
       <c r="E332" s="9" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="F332" s="9" t="n">
-        <v>4300</v>
+        <v>79950</v>
       </c>
       <c r="G332" s="10">
-        <v>46198</v>
+        <v>46168</v>
       </c>
       <c r="H332" s="8" t="n">
         <v>0</v>
@@ -8415,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="J332" s="8" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
     </row>
     <row r="333" customHeight="1" ht="15" spans="1:5">
@@ -8426,18 +8392,18 @@
         <v>20</v>
       </c>
       <c r="C333" s="13" t="n">
-        <v>4300</v>
+        <v>157850</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E333" s="14" t="n">
-        <v>0</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="334" customHeight="1" ht="15" spans="1:1">
       <c r="A334" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="335" customHeight="1" ht="15" spans="1:10">
@@ -8445,236 +8411,236 @@
         <v>14</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>180</v>
+        <v>101</v>
       </c>
       <c r="C335" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D335" s="8" t="n">
-        <v>205000</v>
+        <v>50000</v>
       </c>
       <c r="E335" s="9" t="n">
-        <v>0.38</v>
+        <v>0.315</v>
       </c>
       <c r="F335" s="9" t="n">
-        <v>77900</v>
+        <v>15750</v>
       </c>
       <c r="G335" s="10">
-        <v>46168</v>
+        <v>46198</v>
       </c>
       <c r="H335" s="8" t="n">
-        <v>160000</v>
+        <v>32400</v>
       </c>
       <c r="I335" s="11" t="n">
-        <v>78.05</v>
+        <v>64.8</v>
       </c>
       <c r="J335" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="336" customHeight="1" ht="15" spans="1:10">
-      <c r="A336" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B336" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="336" customHeight="1" ht="15" spans="1:5">
+      <c r="A336" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B336" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C336" s="13" t="n">
+        <v>15750</v>
+      </c>
+      <c r="D336" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E336" s="14" t="n">
+        <v>32400</v>
+      </c>
+    </row>
+    <row r="337" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A337" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" customHeight="1" ht="15" spans="1:12">
+      <c r="A338" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B338" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C338" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E338" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F338" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G338" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H338" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I338" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J338" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K338" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L338" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="339" customHeight="1" ht="15" spans="1:1">
+      <c r="A339" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="340" customHeight="1" ht="15" spans="1:10">
+      <c r="A340" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B340" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="C336" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D336" s="8" t="n">
-        <v>205000</v>
-      </c>
-      <c r="E336" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="F336" s="9" t="n">
-        <v>79950</v>
-      </c>
-      <c r="G336" s="10">
-        <v>46168</v>
-      </c>
-      <c r="H336" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I336" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J336" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="337" customHeight="1" ht="15" spans="1:5">
-      <c r="A337" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B337" s="12" t="s">
+      <c r="C340" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D340" s="8" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E340" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F340" s="9" t="n">
+        <v>63000</v>
+      </c>
+      <c r="G340" s="10">
+        <v>46199</v>
+      </c>
+      <c r="H340" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I340" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J340" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="341" customHeight="1" ht="15" spans="1:5">
+      <c r="A341" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B341" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C337" s="13" t="n">
-        <v>157850</v>
-      </c>
-      <c r="D337" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E337" s="14" t="n">
-        <v>160000</v>
-      </c>
-    </row>
-    <row r="338" customHeight="1" ht="15" spans="1:1">
-      <c r="A338" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="339" customHeight="1" ht="15" spans="1:10">
-      <c r="A339" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B339" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C339" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D339" s="8" t="n">
+      <c r="C341" s="13" t="n">
+        <v>63000</v>
+      </c>
+      <c r="D341" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E341" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" customHeight="1" ht="15" spans="1:1">
+      <c r="A342" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="343" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A343" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B343" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C343" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D343" s="8" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E343" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F343" s="9" t="n">
+        <v>42000</v>
+      </c>
+      <c r="G343" s="10">
+        <v>46205.6764351852</v>
+      </c>
+      <c r="H343" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I343" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="344" customHeight="1" ht="27.95" spans="1:10">
+      <c r="A344" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B344" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C344" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D344" s="8" t="n">
         <v>50000</v>
       </c>
-      <c r="E339" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="F339" s="9" t="n">
-        <v>15750</v>
-      </c>
-      <c r="G339" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H339" s="8" t="n">
-        <v>32400</v>
-      </c>
-      <c r="I339" s="11" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="J339" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="340" customHeight="1" ht="15" spans="1:5">
-      <c r="A340" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B340" s="12" t="s">
+      <c r="E344" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F344" s="9" t="n">
+        <v>21000</v>
+      </c>
+      <c r="G344" s="10">
+        <v>46205.6764351852</v>
+      </c>
+      <c r="H344" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I344" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J344" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="345" customHeight="1" ht="15" spans="1:5">
+      <c r="A345" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B345" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C340" s="13" t="n">
-        <v>15750</v>
-      </c>
-      <c r="D340" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E340" s="14" t="n">
-        <v>32400</v>
-      </c>
-    </row>
-    <row r="341" customHeight="1" ht="15" spans="1:1">
-      <c r="A341" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="342" customHeight="1" ht="15" spans="1:10">
-      <c r="A342" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B342" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C342" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D342" s="8" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E342" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F342" s="9" t="n">
+      <c r="C345" s="13" t="n">
         <v>63000</v>
       </c>
-      <c r="G342" s="10">
-        <v>46199</v>
-      </c>
-      <c r="H342" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I342" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J342" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="343" customHeight="1" ht="15" spans="1:5">
-      <c r="A343" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B343" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C343" s="13" t="n">
-        <v>63000</v>
-      </c>
-      <c r="D343" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E343" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A344" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345" customHeight="1" ht="15" spans="1:12">
-      <c r="A345" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B345" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C345" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D345" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E345" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F345" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G345" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H345" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I345" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J345" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K345" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L345" s="4" t="s">
-        <v>12</v>
+      <c r="D345" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E345" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="346" customHeight="1" ht="15" spans="1:1">
       <c r="A346" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="347" customHeight="1" ht="15" spans="1:10">
@@ -8682,10 +8648,10 @@
         <v>14</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C347" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D347" s="8" t="n">
         <v>100000</v>
@@ -8706,7 +8672,7 @@
         <v>50</v>
       </c>
       <c r="J347" s="8" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
     </row>
     <row r="348" customHeight="1" ht="15" spans="1:5">
@@ -8728,7 +8694,7 @@
     </row>
     <row r="349" customHeight="1" ht="15" spans="1:1">
       <c r="A349" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="350" customHeight="1" ht="15" spans="1:10">
@@ -8736,10 +8702,10 @@
         <v>14</v>
       </c>
       <c r="B350" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C350" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D350" s="8" t="n">
         <v>20000</v>
@@ -8790,7 +8756,7 @@
         <v>1</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>3</v>
@@ -8825,7 +8791,7 @@
     </row>
     <row r="354" customHeight="1" ht="15" spans="1:1">
       <c r="A354" s="2" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="355" customHeight="1" ht="15" spans="1:10">
@@ -8833,19 +8799,19 @@
         <v>14</v>
       </c>
       <c r="B355" s="6" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="C355" s="7" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D355" s="8" t="n">
-        <v>3024</v>
+        <v>216</v>
       </c>
       <c r="E355" s="9" t="n">
-        <v>12.3</v>
+        <v>15.98</v>
       </c>
       <c r="F355" s="9" t="n">
-        <v>37195.2</v>
+        <v>3451.68</v>
       </c>
       <c r="G355" s="10">
         <v>46198</v>
@@ -8857,7 +8823,7 @@
         <v>0</v>
       </c>
       <c r="J355" s="8" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
     </row>
     <row r="356" customHeight="1" ht="15" spans="1:5">
@@ -8868,7 +8834,7 @@
         <v>20</v>
       </c>
       <c r="C356" s="13" t="n">
-        <v>37195.2</v>
+        <v>3451.68</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>19</v>
@@ -8879,30 +8845,30 @@
     </row>
     <row r="357" customHeight="1" ht="15" spans="1:1">
       <c r="A357" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="358" customHeight="1" ht="29.5" spans="1:10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="358" customHeight="1" ht="15" spans="1:10">
       <c r="A358" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>188</v>
+        <v>101</v>
       </c>
       <c r="C358" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D358" s="8" t="n">
-        <v>540</v>
+        <v>1200</v>
       </c>
       <c r="E358" s="9" t="n">
-        <v>15.3</v>
+        <v>10.29</v>
       </c>
       <c r="F358" s="9" t="n">
-        <v>8262</v>
+        <v>12348</v>
       </c>
       <c r="G358" s="10">
-        <v>46203</v>
+        <v>46198</v>
       </c>
       <c r="H358" s="8" t="n">
         <v>0</v>
@@ -8911,7 +8877,7 @@
         <v>0</v>
       </c>
       <c r="J358" s="8" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
     </row>
     <row r="359" customHeight="1" ht="15" spans="1:5">
@@ -8922,7 +8888,7 @@
         <v>20</v>
       </c>
       <c r="C359" s="13" t="n">
-        <v>8262</v>
+        <v>12348</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>19</v>
@@ -8933,30 +8899,30 @@
     </row>
     <row r="360" customHeight="1" ht="15" spans="1:1">
       <c r="A360" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="361" customHeight="1" ht="15" spans="1:10">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="361" customHeight="1" ht="20.15" spans="1:10">
       <c r="A361" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B361" s="6" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="C361" s="7" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D361" s="8" t="n">
-        <v>216</v>
+        <v>1530</v>
       </c>
       <c r="E361" s="9" t="n">
-        <v>15.98</v>
+        <v>13</v>
       </c>
       <c r="F361" s="9" t="n">
-        <v>3451.68</v>
+        <v>19890</v>
       </c>
       <c r="G361" s="10">
-        <v>46198</v>
+        <v>46189</v>
       </c>
       <c r="H361" s="8" t="n">
         <v>0</v>
@@ -8965,7 +8931,7 @@
         <v>0</v>
       </c>
       <c r="J361" s="8" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
     </row>
     <row r="362" customHeight="1" ht="15" spans="1:5">
@@ -8976,7 +8942,7 @@
         <v>20</v>
       </c>
       <c r="C362" s="13" t="n">
-        <v>3451.68</v>
+        <v>19890</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>19</v>
@@ -8985,129 +8951,129 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" customHeight="1" ht="15" spans="1:1">
-      <c r="A363" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="364" customHeight="1" ht="15" spans="1:10">
-      <c r="A364" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B364" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C364" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D364" s="8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E364" s="9" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="F364" s="9" t="n">
-        <v>12348</v>
-      </c>
-      <c r="G364" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H364" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I364" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J364" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="365" customHeight="1" ht="15" spans="1:5">
-      <c r="A365" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B365" s="12" t="s">
+    <row r="363" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A363" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" customHeight="1" ht="15" spans="1:12">
+      <c r="A364" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B364" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D364" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E364" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F364" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G364" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H364" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I364" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J364" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K364" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L364" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="365" customHeight="1" ht="15" spans="1:1">
+      <c r="A365" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="366" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A366" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B366" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C366" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D366" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E366" s="9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F366" s="9" t="n">
+        <v>26250</v>
+      </c>
+      <c r="G366" s="10">
+        <v>46189</v>
+      </c>
+      <c r="H366" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I366" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J366" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="367" customHeight="1" ht="15" spans="1:5">
+      <c r="A367" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B367" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C365" s="13" t="n">
-        <v>12348</v>
-      </c>
-      <c r="D365" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E365" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="366" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A366" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" customHeight="1" ht="15" spans="1:12">
-      <c r="A367" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B367" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C367" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D367" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E367" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F367" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G367" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H367" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I367" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J367" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K367" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L367" s="4" t="s">
-        <v>12</v>
+      <c r="C367" s="13" t="n">
+        <v>26250</v>
+      </c>
+      <c r="D367" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E367" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="368" customHeight="1" ht="15" spans="1:1">
       <c r="A368" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="369" customHeight="1" ht="20.4" spans="1:10">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="369" customHeight="1" ht="15" spans="1:10">
       <c r="A369" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B369" s="6" t="s">
-        <v>160</v>
+        <v>106</v>
       </c>
       <c r="C369" s="7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D369" s="8" t="n">
-        <v>1530</v>
+        <v>120</v>
       </c>
       <c r="E369" s="9" t="n">
-        <v>13</v>
+        <v>18.29</v>
       </c>
       <c r="F369" s="9" t="n">
-        <v>19890</v>
+        <v>2194.8</v>
       </c>
       <c r="G369" s="10">
-        <v>46189</v>
+        <v>46196.6411111111</v>
       </c>
       <c r="H369" s="8" t="n">
         <v>0</v>
@@ -9116,7 +9082,7 @@
         <v>0</v>
       </c>
       <c r="J369" s="8" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
     </row>
     <row r="370" customHeight="1" ht="15" spans="1:5">
@@ -9127,7 +9093,7 @@
         <v>20</v>
       </c>
       <c r="C370" s="13" t="n">
-        <v>19890</v>
+        <v>2194.8</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>19</v>
@@ -9146,7 +9112,7 @@
         <v>1</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>3</v>
@@ -9181,30 +9147,30 @@
     </row>
     <row r="373" customHeight="1" ht="15" spans="1:1">
       <c r="A373" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="374" customHeight="1" ht="20.4" spans="1:10">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="374" customHeight="1" ht="15" spans="1:10">
       <c r="A374" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B374" s="6" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="C374" s="7" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D374" s="8" t="n">
-        <v>1500</v>
+        <v>8028</v>
       </c>
       <c r="E374" s="9" t="n">
-        <v>17.5</v>
+        <v>11.99</v>
       </c>
       <c r="F374" s="9" t="n">
-        <v>26250</v>
+        <v>96255.72</v>
       </c>
       <c r="G374" s="10">
-        <v>46189</v>
+        <v>46167</v>
       </c>
       <c r="H374" s="8" t="n">
         <v>0</v>
@@ -9224,7 +9190,7 @@
         <v>20</v>
       </c>
       <c r="C375" s="13" t="n">
-        <v>26250</v>
+        <v>96255.72</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>19</v>
@@ -9235,7 +9201,7 @@
     </row>
     <row r="376" customHeight="1" ht="15" spans="1:1">
       <c r="A376" s="2" t="s">
-        <v>105</v>
+        <v>199</v>
       </c>
     </row>
     <row r="377" customHeight="1" ht="15" spans="1:10">
@@ -9243,22 +9209,22 @@
         <v>14</v>
       </c>
       <c r="B377" s="6" t="s">
-        <v>106</v>
+        <v>200</v>
       </c>
       <c r="C377" s="7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D377" s="8" t="n">
-        <v>120</v>
+        <v>720</v>
       </c>
       <c r="E377" s="9" t="n">
-        <v>18.29</v>
+        <v>15</v>
       </c>
       <c r="F377" s="9" t="n">
-        <v>2194.8</v>
+        <v>10800</v>
       </c>
       <c r="G377" s="10">
-        <v>46196.6411111111</v>
+        <v>46203</v>
       </c>
       <c r="H377" s="8" t="n">
         <v>0</v>
@@ -9267,7 +9233,7 @@
         <v>0</v>
       </c>
       <c r="J377" s="8" t="s">
-        <v>80</v>
+        <v>144</v>
       </c>
     </row>
     <row r="378" customHeight="1" ht="15" spans="1:5">
@@ -9278,7 +9244,7 @@
         <v>20</v>
       </c>
       <c r="C378" s="13" t="n">
-        <v>2194.8</v>
+        <v>10800</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>19</v>
@@ -9287,183 +9253,183 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A379" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" customHeight="1" ht="15" spans="1:12">
-      <c r="A380" s="2" t="s">
+    <row r="379" customHeight="1" ht="15" spans="1:1">
+      <c r="A379" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="380" customHeight="1" ht="20.15" spans="1:10">
+      <c r="A380" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B380" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C380" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D380" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E380" s="9" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F380" s="9" t="n">
+        <v>34350</v>
+      </c>
+      <c r="G380" s="10">
+        <v>46189</v>
+      </c>
+      <c r="H380" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I380" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J380" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="381" customHeight="1" ht="15" spans="1:5">
+      <c r="A381" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B381" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C381" s="13" t="n">
+        <v>34350</v>
+      </c>
+      <c r="D381" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E381" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" customHeight="1" ht="15" spans="1:1">
+      <c r="A382" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="383" customHeight="1" ht="37.05" spans="1:10">
+      <c r="A383" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B383" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C383" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D383" s="8" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E383" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F383" s="9" t="n">
+        <v>312000</v>
+      </c>
+      <c r="G383" s="10">
+        <v>46100</v>
+      </c>
+      <c r="H383" s="8" t="n">
+        <v>18900</v>
+      </c>
+      <c r="I383" s="11" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="J383" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="384" customHeight="1" ht="15" spans="1:5">
+      <c r="A384" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B384" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C384" s="13" t="n">
+        <v>312000</v>
+      </c>
+      <c r="D384" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E384" s="14" t="n">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="385" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A385" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" customHeight="1" ht="15" spans="1:12">
+      <c r="A386" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B380" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C380" s="2" t="s">
+      <c r="B386" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C386" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D380" s="2" t="s">
+      <c r="D386" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E380" s="4" t="s">
+      <c r="E386" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F380" s="4" t="s">
+      <c r="F386" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G380" s="4" t="s">
+      <c r="G386" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H380" s="4" t="s">
+      <c r="H386" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I380" s="4" t="s">
+      <c r="I386" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J380" s="4" t="s">
+      <c r="J386" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K380" s="2" t="s">
+      <c r="K386" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L380" s="4" t="s">
+      <c r="L386" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="381" customHeight="1" ht="15" spans="1:1">
-      <c r="A381" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="382" customHeight="1" ht="15" spans="1:10">
-      <c r="A382" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B382" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C382" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="D382" s="8" t="n">
-        <v>8028</v>
-      </c>
-      <c r="E382" s="9" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="F382" s="9" t="n">
-        <v>96255.72</v>
-      </c>
-      <c r="G382" s="10">
-        <v>46167</v>
-      </c>
-      <c r="H382" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I382" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J382" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="383" customHeight="1" ht="15" spans="1:5">
-      <c r="A383" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B383" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C383" s="13" t="n">
-        <v>96255.72</v>
-      </c>
-      <c r="D383" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E383" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384" customHeight="1" ht="15" spans="1:1">
-      <c r="A384" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="385" customHeight="1" ht="15" spans="1:10">
-      <c r="A385" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B385" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C385" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="D385" s="8" t="n">
-        <v>720</v>
-      </c>
-      <c r="E385" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="F385" s="9" t="n">
-        <v>10800</v>
-      </c>
-      <c r="G385" s="10">
-        <v>46203</v>
-      </c>
-      <c r="H385" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I385" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J385" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="386" customHeight="1" ht="15" spans="1:5">
-      <c r="A386" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B386" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C386" s="13" t="n">
-        <v>10800</v>
-      </c>
-      <c r="D386" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E386" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="387" customHeight="1" ht="15" spans="1:1">
       <c r="A387" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="388" customHeight="1" ht="20.15" spans="1:10">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="388" customHeight="1" ht="15" spans="1:10">
       <c r="A388" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B388" s="6" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C388" s="7" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D388" s="8" t="n">
-        <v>1500</v>
+        <v>240</v>
       </c>
       <c r="E388" s="9" t="n">
-        <v>22.9</v>
+        <v>9.74</v>
       </c>
       <c r="F388" s="9" t="n">
-        <v>34350</v>
+        <v>2337.6</v>
       </c>
       <c r="G388" s="10">
-        <v>46189</v>
+        <v>46197</v>
       </c>
       <c r="H388" s="8" t="n">
         <v>0</v>
@@ -9472,7 +9438,7 @@
         <v>0</v>
       </c>
       <c r="J388" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="389" customHeight="1" ht="15" spans="1:5">
@@ -9483,7 +9449,7 @@
         <v>20</v>
       </c>
       <c r="C389" s="13" t="n">
-        <v>34350</v>
+        <v>2337.6</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>19</v>
@@ -9494,39 +9460,39 @@
     </row>
     <row r="390" customHeight="1" ht="15" spans="1:1">
       <c r="A390" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="391" customHeight="1" ht="37.05" spans="1:10">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="391" customHeight="1" ht="18.8" spans="1:10">
       <c r="A391" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B391" s="6" t="s">
-        <v>203</v>
+        <v>55</v>
       </c>
       <c r="C391" s="7" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D391" s="8" t="n">
-        <v>24000</v>
+        <v>2040</v>
       </c>
       <c r="E391" s="9" t="n">
-        <v>13</v>
+        <v>16.58</v>
       </c>
       <c r="F391" s="9" t="n">
-        <v>312000</v>
+        <v>33823.2</v>
       </c>
       <c r="G391" s="10">
-        <v>46100</v>
+        <v>46162</v>
       </c>
       <c r="H391" s="8" t="n">
-        <v>18900</v>
+        <v>0</v>
       </c>
       <c r="I391" s="11" t="n">
-        <v>78.75</v>
+        <v>0</v>
       </c>
       <c r="J391" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="392" customHeight="1" ht="15" spans="1:5">
@@ -9537,138 +9503,138 @@
         <v>20</v>
       </c>
       <c r="C392" s="13" t="n">
-        <v>312000</v>
+        <v>33823.2</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E392" s="14" t="n">
-        <v>18900</v>
-      </c>
-    </row>
-    <row r="393" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A393" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="394" customHeight="1" ht="15" spans="1:12">
-      <c r="A394" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" customHeight="1" ht="15" spans="1:1">
+      <c r="A393" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="394" customHeight="1" ht="19.55" spans="1:10">
+      <c r="A394" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B394" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C394" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="D394" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="E394" s="9" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="F394" s="9" t="n">
+        <v>1989.6</v>
+      </c>
+      <c r="G394" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H394" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I394" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J394" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="395" customHeight="1" ht="15" spans="1:5">
+      <c r="A395" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B395" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C395" s="13" t="n">
+        <v>1989.6</v>
+      </c>
+      <c r="D395" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E395" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A396" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" customHeight="1" ht="15" spans="1:12">
+      <c r="A397" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B394" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C394" s="2" t="s">
+      <c r="B397" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C397" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D394" s="2" t="s">
+      <c r="D397" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E394" s="4" t="s">
+      <c r="E397" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F394" s="4" t="s">
+      <c r="F397" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G394" s="4" t="s">
+      <c r="G397" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H394" s="4" t="s">
+      <c r="H397" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I394" s="4" t="s">
+      <c r="I397" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J394" s="4" t="s">
+      <c r="J397" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K394" s="2" t="s">
+      <c r="K397" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L394" s="4" t="s">
+      <c r="L397" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="395" customHeight="1" ht="15" spans="1:1">
-      <c r="A395" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="396" customHeight="1" ht="15" spans="1:10">
-      <c r="A396" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B396" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C396" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D396" s="8" t="n">
-        <v>240</v>
-      </c>
-      <c r="E396" s="9" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="F396" s="9" t="n">
-        <v>2337.6</v>
-      </c>
-      <c r="G396" s="10">
-        <v>46197</v>
-      </c>
-      <c r="H396" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I396" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J396" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="397" customHeight="1" ht="15" spans="1:5">
-      <c r="A397" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B397" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C397" s="13" t="n">
-        <v>2337.6</v>
-      </c>
-      <c r="D397" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E397" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="398" customHeight="1" ht="15" spans="1:1">
       <c r="A398" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="399" customHeight="1" ht="18.8" spans="1:10">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="399" customHeight="1" ht="15" spans="1:10">
       <c r="A399" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B399" s="6" t="s">
-        <v>55</v>
+        <v>197</v>
       </c>
       <c r="C399" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D399" s="8" t="n">
-        <v>2040</v>
+        <v>4032</v>
       </c>
       <c r="E399" s="9" t="n">
-        <v>16.58</v>
+        <v>6.99</v>
       </c>
       <c r="F399" s="9" t="n">
-        <v>33823.2</v>
+        <v>28183.68</v>
       </c>
       <c r="G399" s="10">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="H399" s="8" t="n">
         <v>0</v>
@@ -9677,7 +9643,7 @@
         <v>0</v>
       </c>
       <c r="J399" s="8" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="400" customHeight="1" ht="15" spans="1:5">
@@ -9688,7 +9654,7 @@
         <v>20</v>
       </c>
       <c r="C400" s="13" t="n">
-        <v>33823.2</v>
+        <v>28183.68</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>19</v>
@@ -9699,30 +9665,30 @@
     </row>
     <row r="401" customHeight="1" ht="15" spans="1:1">
       <c r="A401" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="402" customHeight="1" ht="19.55" spans="1:10">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="402" customHeight="1" ht="45.6" spans="1:10">
       <c r="A402" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B402" s="6" t="s">
-        <v>135</v>
+        <v>211</v>
       </c>
       <c r="C402" s="7" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D402" s="8" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="E402" s="9" t="n">
-        <v>16.58</v>
+        <v>8</v>
       </c>
       <c r="F402" s="9" t="n">
-        <v>1989.6</v>
+        <v>8000</v>
       </c>
       <c r="G402" s="10">
-        <v>46198</v>
+        <v>46191</v>
       </c>
       <c r="H402" s="8" t="n">
         <v>0</v>
@@ -9731,7 +9697,7 @@
         <v>0</v>
       </c>
       <c r="J402" s="8" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
     </row>
     <row r="403" customHeight="1" ht="15" spans="1:5">
@@ -9742,7 +9708,7 @@
         <v>20</v>
       </c>
       <c r="C403" s="13" t="n">
-        <v>1989.6</v>
+        <v>8000</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>19</v>
@@ -9751,183 +9717,183 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A404" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405" customHeight="1" ht="15" spans="1:12">
-      <c r="A405" s="2" t="s">
+    <row r="404" customHeight="1" ht="15" spans="1:1">
+      <c r="A404" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="405" customHeight="1" ht="15" spans="1:10">
+      <c r="A405" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B405" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C405" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D405" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="E405" s="9" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="F405" s="9" t="n">
+        <v>7110</v>
+      </c>
+      <c r="G405" s="10">
+        <v>46197</v>
+      </c>
+      <c r="H405" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I405" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J405" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="406" customHeight="1" ht="15" spans="1:5">
+      <c r="A406" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B406" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C406" s="13" t="n">
+        <v>7110</v>
+      </c>
+      <c r="D406" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E406" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" customHeight="1" ht="15" spans="1:1">
+      <c r="A407" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="408" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A408" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B408" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C408" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D408" s="8" t="n">
+        <v>720</v>
+      </c>
+      <c r="E408" s="9" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="F408" s="9" t="n">
+        <v>17064</v>
+      </c>
+      <c r="G408" s="10">
+        <v>46169</v>
+      </c>
+      <c r="H408" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I408" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J408" s="8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="409" customHeight="1" ht="15" spans="1:5">
+      <c r="A409" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B409" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C409" s="13" t="n">
+        <v>17064</v>
+      </c>
+      <c r="D409" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E409" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A410" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" customHeight="1" ht="15" spans="1:12">
+      <c r="A411" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B405" s="3" t="s">
+      <c r="B411" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C405" s="2" t="s">
+      <c r="C411" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D405" s="2" t="s">
+      <c r="D411" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E405" s="4" t="s">
+      <c r="E411" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F405" s="4" t="s">
+      <c r="F411" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G405" s="4" t="s">
+      <c r="G411" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H405" s="4" t="s">
+      <c r="H411" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I405" s="4" t="s">
+      <c r="I411" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J405" s="4" t="s">
+      <c r="J411" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K405" s="2" t="s">
+      <c r="K411" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L405" s="4" t="s">
+      <c r="L411" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="406" customHeight="1" ht="15" spans="1:1">
-      <c r="A406" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="407" customHeight="1" ht="15" spans="1:10">
-      <c r="A407" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B407" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C407" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="D407" s="8" t="n">
-        <v>4032</v>
-      </c>
-      <c r="E407" s="9" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F407" s="9" t="n">
-        <v>28183.68</v>
-      </c>
-      <c r="G407" s="10">
-        <v>46167</v>
-      </c>
-      <c r="H407" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I407" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J407" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="408" customHeight="1" ht="15" spans="1:5">
-      <c r="A408" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B408" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C408" s="13" t="n">
-        <v>28183.68</v>
-      </c>
-      <c r="D408" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E408" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="409" customHeight="1" ht="15" spans="1:1">
-      <c r="A409" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="410" customHeight="1" ht="45.6" spans="1:10">
-      <c r="A410" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B410" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="C410" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="D410" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E410" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F410" s="9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G410" s="10">
-        <v>46191</v>
-      </c>
-      <c r="H410" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I410" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J410" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="411" customHeight="1" ht="15" spans="1:5">
-      <c r="A411" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B411" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C411" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D411" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E411" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="412" customHeight="1" ht="15" spans="1:1">
       <c r="A412" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="413" customHeight="1" ht="15" spans="1:10">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="413" customHeight="1" ht="20.4" spans="1:10">
       <c r="A413" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B413" s="6" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C413" s="7" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D413" s="8" t="n">
-        <v>600</v>
+        <v>96</v>
       </c>
       <c r="E413" s="9" t="n">
-        <v>11.85</v>
+        <v>19.22</v>
       </c>
       <c r="F413" s="9" t="n">
-        <v>7110</v>
+        <v>1845.12</v>
       </c>
       <c r="G413" s="10">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="H413" s="8" t="n">
         <v>0</v>
@@ -9936,7 +9902,7 @@
         <v>0</v>
       </c>
       <c r="J413" s="8" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
     </row>
     <row r="414" customHeight="1" ht="15" spans="1:5">
@@ -9947,7 +9913,7 @@
         <v>20</v>
       </c>
       <c r="C414" s="13" t="n">
-        <v>7110</v>
+        <v>1845.12</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>19</v>
@@ -9956,126 +9922,126 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" customHeight="1" ht="15" spans="1:1">
-      <c r="A415" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="416" customHeight="1" ht="18.8" spans="1:10">
-      <c r="A416" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B416" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="C416" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="D416" s="8" t="n">
-        <v>720</v>
-      </c>
-      <c r="E416" s="9" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="F416" s="9" t="n">
-        <v>17064</v>
-      </c>
-      <c r="G416" s="10">
-        <v>46169</v>
-      </c>
-      <c r="H416" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I416" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J416" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="417" customHeight="1" ht="15" spans="1:5">
-      <c r="A417" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B417" s="12" t="s">
+    <row r="415" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A415" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" customHeight="1" ht="15" spans="1:12">
+      <c r="A416" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B416" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C416" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D416" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E416" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F416" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G416" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H416" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I416" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J416" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K416" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L416" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="417" customHeight="1" ht="15" spans="1:1">
+      <c r="A417" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="418" customHeight="1" ht="15" spans="1:10">
+      <c r="A418" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B418" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C418" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D418" s="8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E418" s="9" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F418" s="9" t="n">
+        <v>14091.84</v>
+      </c>
+      <c r="G418" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H418" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I418" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J418" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="419" customHeight="1" ht="15" spans="1:5">
+      <c r="A419" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B419" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C417" s="13" t="n">
-        <v>17064</v>
-      </c>
-      <c r="D417" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E417" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="418" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A418" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="419" customHeight="1" ht="15" spans="1:12">
-      <c r="A419" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B419" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C419" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D419" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E419" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F419" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G419" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H419" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I419" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J419" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K419" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L419" s="4" t="s">
-        <v>12</v>
+      <c r="C419" s="13" t="n">
+        <v>14091.84</v>
+      </c>
+      <c r="D419" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E419" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="420" customHeight="1" ht="15" spans="1:1">
       <c r="A420" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="421" customHeight="1" ht="20.4" spans="1:10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="421" customHeight="1" ht="15" spans="1:10">
       <c r="A421" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B421" s="6" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="C421" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D421" s="8" t="n">
-        <v>96</v>
+        <v>648</v>
       </c>
       <c r="E421" s="9" t="n">
-        <v>19.22</v>
+        <v>6.99</v>
       </c>
       <c r="F421" s="9" t="n">
-        <v>1845.12</v>
+        <v>4529.52</v>
       </c>
       <c r="G421" s="10">
         <v>46198</v>
@@ -10098,7 +10064,7 @@
         <v>20</v>
       </c>
       <c r="C422" s="13" t="n">
-        <v>1845.12</v>
+        <v>4529.52</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>19</v>
@@ -10107,160 +10073,160 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A423" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="424" customHeight="1" ht="15" spans="1:12">
-      <c r="A424" s="2" t="s">
+    <row r="423" customHeight="1" ht="15" spans="1:1">
+      <c r="A423" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="424" customHeight="1" ht="15" spans="1:10">
+      <c r="A424" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B424" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C424" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D424" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E424" s="9" t="n">
+        <v>4.893</v>
+      </c>
+      <c r="F424" s="9" t="n">
+        <v>5871.6</v>
+      </c>
+      <c r="G424" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H424" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I424" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J424" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="425" customHeight="1" ht="15" spans="1:5">
+      <c r="A425" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B425" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C425" s="13" t="n">
+        <v>5871.6</v>
+      </c>
+      <c r="D425" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E425" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" customHeight="1" ht="15" spans="1:1">
+      <c r="A426" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="427" customHeight="1" ht="36.6" spans="1:10">
+      <c r="A427" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B427" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C427" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D427" s="8" t="n">
+        <v>10008</v>
+      </c>
+      <c r="E427" s="9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F427" s="9" t="n">
+        <v>66052.8</v>
+      </c>
+      <c r="G427" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H427" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I427" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J427" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="428" customHeight="1" ht="15" spans="1:5">
+      <c r="A428" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B428" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C428" s="13" t="n">
+        <v>66052.8</v>
+      </c>
+      <c r="D428" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E428" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A429" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" customHeight="1" ht="15" spans="1:12">
+      <c r="A430" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B424" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C424" s="2" t="s">
+      <c r="B430" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C430" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D424" s="2" t="s">
+      <c r="D430" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E424" s="4" t="s">
+      <c r="E430" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F424" s="4" t="s">
+      <c r="F430" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G424" s="4" t="s">
+      <c r="G430" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H424" s="4" t="s">
+      <c r="H430" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I424" s="4" t="s">
+      <c r="I430" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J424" s="4" t="s">
+      <c r="J430" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K424" s="2" t="s">
+      <c r="K430" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L424" s="4" t="s">
+      <c r="L430" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="425" customHeight="1" ht="15" spans="1:1">
-      <c r="A425" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="426" customHeight="1" ht="15" spans="1:10">
-      <c r="A426" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B426" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C426" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D426" s="8" t="n">
-        <v>2016</v>
-      </c>
-      <c r="E426" s="9" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F426" s="9" t="n">
-        <v>14091.84</v>
-      </c>
-      <c r="G426" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H426" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I426" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J426" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="427" customHeight="1" ht="15" spans="1:5">
-      <c r="A427" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B427" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C427" s="13" t="n">
-        <v>14091.84</v>
-      </c>
-      <c r="D427" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E427" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="428" customHeight="1" ht="15" spans="1:1">
-      <c r="A428" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="429" customHeight="1" ht="15" spans="1:10">
-      <c r="A429" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B429" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C429" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D429" s="8" t="n">
-        <v>648</v>
-      </c>
-      <c r="E429" s="9" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F429" s="9" t="n">
-        <v>4529.52</v>
-      </c>
-      <c r="G429" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H429" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I429" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J429" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="430" customHeight="1" ht="15" spans="1:5">
-      <c r="A430" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B430" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C430" s="13" t="n">
-        <v>4529.52</v>
-      </c>
-      <c r="D430" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E430" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="431" customHeight="1" ht="15" spans="1:1">
       <c r="A431" s="2" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="432" customHeight="1" ht="15" spans="1:10">
@@ -10268,22 +10234,22 @@
         <v>14</v>
       </c>
       <c r="B432" s="6" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C432" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D432" s="8" t="n">
-        <v>1200</v>
+        <v>1584</v>
       </c>
       <c r="E432" s="9" t="n">
-        <v>4.893</v>
+        <v>6.99</v>
       </c>
       <c r="F432" s="9" t="n">
-        <v>5871.6</v>
+        <v>11072.16</v>
       </c>
       <c r="G432" s="10">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="H432" s="8" t="n">
         <v>0</v>
@@ -10292,7 +10258,7 @@
         <v>0</v>
       </c>
       <c r="J432" s="8" t="s">
-        <v>102</v>
+        <v>17</v>
       </c>
     </row>
     <row r="433" customHeight="1" ht="15" spans="1:5">
@@ -10303,7 +10269,7 @@
         <v>20</v>
       </c>
       <c r="C433" s="13" t="n">
-        <v>5871.6</v>
+        <v>11072.16</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>19</v>
@@ -10314,15 +10280,15 @@
     </row>
     <row r="434" customHeight="1" ht="15" spans="1:1">
       <c r="A434" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="435" customHeight="1" ht="36.6" spans="1:10">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="435" customHeight="1" ht="15" spans="1:10">
       <c r="A435" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B435" s="6" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C435" s="7" t="s">
         <v>220</v>
@@ -10331,22 +10297,22 @@
         <v>10008</v>
       </c>
       <c r="E435" s="9" t="n">
-        <v>6.6</v>
+        <v>5.99</v>
       </c>
       <c r="F435" s="9" t="n">
-        <v>66052.8</v>
+        <v>59947.92</v>
       </c>
       <c r="G435" s="10">
-        <v>46198</v>
+        <v>46181</v>
       </c>
       <c r="H435" s="8" t="n">
-        <v>0</v>
+        <v>2808</v>
       </c>
       <c r="I435" s="11" t="n">
-        <v>0</v>
+        <v>28.06</v>
       </c>
       <c r="J435" s="8" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
     </row>
     <row r="436" customHeight="1" ht="15" spans="1:5">
@@ -10357,325 +10323,174 @@
         <v>20</v>
       </c>
       <c r="C436" s="13" t="n">
-        <v>66052.8</v>
+        <v>59947.92</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E436" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="437" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A437" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="438" customHeight="1" ht="15" spans="1:12">
-      <c r="A438" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B438" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C438" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D438" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E438" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F438" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G438" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H438" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I438" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J438" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K438" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L438" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="439" customHeight="1" ht="15" spans="1:1">
-      <c r="A439" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="440" customHeight="1" ht="15" spans="1:10">
-      <c r="A440" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B440" s="6" t="s">
+        <v>2808</v>
+      </c>
+    </row>
+    <row r="437" customHeight="1" ht="15" spans="1:1">
+      <c r="A437" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C440" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D440" s="8" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E440" s="9" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F440" s="9" t="n">
-        <v>11072.16</v>
-      </c>
-      <c r="G440" s="10">
-        <v>46197</v>
-      </c>
-      <c r="H440" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I440" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J440" s="8" t="s">
+    </row>
+    <row r="438" customHeight="1" ht="15" spans="1:10">
+      <c r="A438" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B438" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C438" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D438" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="E438" s="9" t="n">
+        <v>14.8992</v>
+      </c>
+      <c r="F438" s="9" t="n">
+        <v>4469.76</v>
+      </c>
+      <c r="G438" s="10">
+        <v>46199</v>
+      </c>
+      <c r="H438" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I438" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J438" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="439" customHeight="1" ht="15" spans="1:5">
+      <c r="A439" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B439" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C439" s="13" t="n">
+        <v>4469.76</v>
+      </c>
+      <c r="D439" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E439" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" customHeight="1" ht="15" spans="1:1">
+      <c r="A440" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="441" customHeight="1" ht="15" spans="1:10">
+      <c r="A441" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B441" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C441" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D441" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E441" s="9" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="F441" s="9" t="n">
+        <v>1156.8</v>
+      </c>
+      <c r="G441" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H441" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I441" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J441" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="442" customHeight="1" ht="15" spans="1:5">
+      <c r="A442" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B442" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C442" s="13" t="n">
+        <v>1156.8</v>
+      </c>
+      <c r="D442" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E442" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" customHeight="1" ht="15" spans="1:1">
+      <c r="A443" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="444" customHeight="1" ht="15" spans="1:10">
+      <c r="A444" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B444" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C444" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D444" s="8" t="n">
+        <v>1512</v>
+      </c>
+      <c r="E444" s="9" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="F444" s="9" t="n">
+        <v>10251.36</v>
+      </c>
+      <c r="G444" s="10">
+        <v>46195</v>
+      </c>
+      <c r="H444" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I444" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J444" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="441" customHeight="1" ht="15" spans="1:5">
-      <c r="A441" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B441" s="12" t="s">
+    <row r="445" customHeight="1" ht="15" spans="1:5">
+      <c r="A445" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B445" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C441" s="13" t="n">
-        <v>11072.16</v>
-      </c>
-      <c r="D441" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E441" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="442" customHeight="1" ht="15" spans="1:1">
-      <c r="A442" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="443" customHeight="1" ht="15" spans="1:10">
-      <c r="A443" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B443" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C443" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D443" s="8" t="n">
-        <v>10008</v>
-      </c>
-      <c r="E443" s="9" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="F443" s="9" t="n">
-        <v>59947.92</v>
-      </c>
-      <c r="G443" s="10">
-        <v>46181</v>
-      </c>
-      <c r="H443" s="8" t="n">
-        <v>2808</v>
-      </c>
-      <c r="I443" s="11" t="n">
-        <v>28.06</v>
-      </c>
-      <c r="J443" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="444" customHeight="1" ht="15" spans="1:5">
-      <c r="A444" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B444" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C444" s="13" t="n">
-        <v>59947.92</v>
-      </c>
-      <c r="D444" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E444" s="14" t="n">
-        <v>2808</v>
-      </c>
-    </row>
-    <row r="445" customHeight="1" ht="15" spans="1:1">
-      <c r="A445" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="446" customHeight="1" ht="15" spans="1:10">
-      <c r="A446" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B446" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C446" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="D446" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="E446" s="9" t="n">
-        <v>14.8992</v>
-      </c>
-      <c r="F446" s="9" t="n">
-        <v>4469.76</v>
-      </c>
-      <c r="G446" s="10">
-        <v>46199</v>
-      </c>
-      <c r="H446" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I446" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J446" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="447" customHeight="1" ht="15" spans="1:5">
-      <c r="A447" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B447" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C447" s="13" t="n">
-        <v>4469.76</v>
-      </c>
-      <c r="D447" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E447" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="448" customHeight="1" ht="15" spans="1:1">
-      <c r="A448" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="449" customHeight="1" ht="15" spans="1:10">
-      <c r="A449" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B449" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C449" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="D449" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="E449" s="9" t="n">
-        <v>14.46</v>
-      </c>
-      <c r="F449" s="9" t="n">
-        <v>1156.8</v>
-      </c>
-      <c r="G449" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H449" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I449" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J449" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="450" customHeight="1" ht="15" spans="1:5">
-      <c r="A450" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B450" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C450" s="13" t="n">
-        <v>1156.8</v>
-      </c>
-      <c r="D450" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E450" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="451" customHeight="1" ht="15" spans="1:1">
-      <c r="A451" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="452" customHeight="1" ht="15" spans="1:10">
-      <c r="A452" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B452" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C452" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D452" s="8" t="n">
-        <v>1512</v>
-      </c>
-      <c r="E452" s="9" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="F452" s="9" t="n">
+      <c r="C445" s="13" t="n">
         <v>10251.36</v>
       </c>
-      <c r="G452" s="10">
-        <v>46195</v>
-      </c>
-      <c r="H452" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I452" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J452" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="453" customHeight="1" ht="15" spans="1:5">
-      <c r="A453" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B453" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C453" s="13" t="n">
-        <v>10251.36</v>
-      </c>
-      <c r="D453" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E453" s="14" t="n">
+      <c r="D445" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E445" s="14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="206">
   <si>
     <t>MATRIZ CNPJ: 40.357.820/0001-50R Y DOIS - 58082-025
  ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
@@ -218,13 +218,13 @@
     <t>1037</t>
   </si>
   <si>
-    <t>1661 - ATADURA DE CREPE 13 FIOS 10 X 1,80   PCT 12</t>
-  </si>
-  <si>
-    <t>1662 - ATADURA DE CREPE 13 FIOS 12 X 1,80   PCT 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1663 - ATADURA DE CREPE13 FIOS 15 X 1,80   PCT 12 </t>
+    <t>1661 - ATADURA DE CREPE 13 FIOS 10 X 1,80   PCT 12 Observação: 4%</t>
+  </si>
+  <si>
+    <t>1662 - ATADURA DE CREPE 13 FIOS 12 X 1,80   PCT 12 Observação: 4%</t>
+  </si>
+  <si>
+    <t>1663 - ATADURA DE CREPE13 FIOS 15 X 1,80   PCT 12 Observação: 4%</t>
   </si>
   <si>
     <t>DROGAFONTE</t>
@@ -370,6 +370,15 @@
  PEDIDO PARA ABATER NO CREDITO DA  DEVOLUÇÃO</t>
   </si>
   <si>
+    <t>CAMPO - 25 X 28 C/02</t>
+  </si>
+  <si>
+    <t>1041</t>
+  </si>
+  <si>
+    <t>1587 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 2 UND  Observação: 2%</t>
+  </si>
+  <si>
     <t>CAMPO - 25 X 28 C/05</t>
   </si>
   <si>
@@ -389,6 +398,9 @@
     <t>ELIENE RESENDE - RJ</t>
   </si>
   <si>
+    <t>1588 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND  Observação: 3%</t>
+  </si>
+  <si>
     <t>884</t>
   </si>
   <si>
@@ -401,12 +413,22 @@
     <t>945</t>
   </si>
   <si>
-    <t>1588 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND  Observação:  ***MEIA NOTA (34 VOLUMES)***</t>
+    <t>1588 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND Observação: 
+ ***MEIA NOTA (34 VOLUMES)***</t>
   </si>
   <si>
     <t>DANILO - AL/SE/BA</t>
   </si>
   <si>
+    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>1045</t>
+  </si>
+  <si>
+    <t>1588 - CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND  Observação: 4%</t>
+  </si>
+  <si>
     <t>CAMPO - 45 X 50</t>
   </si>
   <si>
@@ -416,6 +438,15 @@
     <t>1797 - CAMPO OPERATORIO NAO ESTERIL  45X50 S/ RX - PCT 50 UND</t>
   </si>
   <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>155 - CAMPO OPERATORIO NAO ESTERIL 45X50  - PCT 50 UND</t>
+  </si>
+  <si>
+    <t>155 - CAMPO OPERATORIO NAO ESTERIL 45X50  - PCT 50 UNDObservação: 2%</t>
+  </si>
+  <si>
     <t>1586 - CAMPO OPERATORIO NAO ESTERIL  45X50 - PCT 50 Observação: 3%</t>
   </si>
   <si>
@@ -443,28 +474,76 @@
     <t>01 - GAZE ESTÉRIL 09 FIOS - PCT 10 UND  Observação: 1% ************* CLIENTE VEM RETIRAR</t>
   </si>
   <si>
+    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS</t>
+  </si>
+  <si>
+    <t>1038</t>
+  </si>
+  <si>
+    <t>01 - GAZE ESTÉRIL 09 FIOS - PCT 10 UND  Observação: 2%</t>
+  </si>
+  <si>
+    <t>1039</t>
+  </si>
+  <si>
     <t>ESTERIL - 11 FIOS</t>
   </si>
   <si>
     <t xml:space="preserve">02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND </t>
   </si>
   <si>
+    <t>1047</t>
+  </si>
+  <si>
+    <t>02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND  Observação: 1% ****CLIENTE VEM RETIRAR*****</t>
+  </si>
+  <si>
+    <t>DROGUISTA CEARENSE</t>
+  </si>
+  <si>
+    <t>1043</t>
+  </si>
+  <si>
+    <t>02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND  Observação: 2% - 37/44/58</t>
+  </si>
+  <si>
+    <t>02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND  Observação: 2%</t>
+  </si>
+  <si>
     <t>ESTERIL - 13 FIOS</t>
   </si>
   <si>
     <t xml:space="preserve">03 - GAZE ESTÉRIL 13FIOS - PCT 10 UND </t>
   </si>
   <si>
-    <t xml:space="preserve">154 - GAZE ESTERIL 13 FIOS PCT 10 UND </t>
+    <t>154 - GAZE ESTERIL 13 FIOS PCT 10 UND  Observação: 3%</t>
   </si>
   <si>
     <t>03 - GAZE ESTÉRIL 13FIOS - PCT 10 UND  Observação: 3%</t>
   </si>
   <si>
+    <t>03 - GAZE ESTÉRIL 13FIOS - PCT 10 UND  Observação: 2,5% - 37/44/58</t>
+  </si>
+  <si>
+    <t>NOVAMED</t>
+  </si>
+  <si>
+    <t>1046</t>
+  </si>
+  <si>
+    <t>03 - GAZE ESTÉRIL 13FIOS - PCT 10 UND  Observação: 2%</t>
+  </si>
+  <si>
+    <t>GAZE EM ROLO - 09 FIOS</t>
+  </si>
+  <si>
+    <t>85 - GAZE CIRCULAR NAO ESTERIL 09 FIOS  Observação: 2%</t>
+  </si>
+  <si>
     <t>GAZE EM ROLO - 11 FIOS</t>
   </si>
   <si>
-    <t>2162 - GAZE CIRCULAR NAO ESTERIL 11 FIOS  Observação: 2%</t>
+    <t>266 - GAZE CIRCULAR NAO ESTERIL 11 FIOS  Observação: 2%</t>
   </si>
   <si>
     <t xml:space="preserve">263 - GAZE CIRCULAR NAO ESTERIL 11 FIOS </t>
@@ -482,7 +561,7 @@
     <t>359 - GAZE CIRCULAR NAO ESTERIL 13 FIOS</t>
   </si>
   <si>
-    <t xml:space="preserve">1962 - GAZE CIRCULAR NAO ESTERIL 13 FIOS </t>
+    <t>1962 - GAZE CIRCULAR NAO ESTERIL 13 FIOS  Observação: 3%</t>
   </si>
   <si>
     <t>NACIONAL COMERCIO E REPRESENTACAO</t>
@@ -491,7 +570,17 @@
     <t>644</t>
   </si>
   <si>
-    <t>277 - GAZE CIRCULAR NAO ESTERIL 13 FIOS EA Observação: PEDIDO PARA ENTREGAR EM  ORGÃO PÚBLICOQUANDO FATURAR ENVIAR NF-E PARA CLIENTE</t>
+    <t>277 - GAZE CIRCULAR NAO ESTERIL 13 FIOS EA Observação: PEDIDO PARA ENTREGAR EM ORGÃO PÚBLICO
+ QUANDO FATURAR ENVIAR NF-E PARA CLIENTE</t>
+  </si>
+  <si>
+    <t>PARNAMED</t>
+  </si>
+  <si>
+    <t>1042</t>
+  </si>
+  <si>
+    <t>279 - GAZE CIRCULAR NAO ESTERIL 13 FIOS GA Observação: 2%</t>
   </si>
   <si>
     <t>PCT NÃO EST. - 11 FIOS</t>
@@ -510,6 +599,9 @@
   </si>
   <si>
     <t xml:space="preserve">321 - GAZE NAO ESTÉRIL 13 FIOS </t>
+  </si>
+  <si>
+    <t>349 - GAZE NAO ESTÉRIL 13 FIOS  - PCT 500  UND Observação: 3%</t>
   </si>
   <si>
     <t>PCT NÃO EST. - 9 FIOS</t>
@@ -532,6 +624,18 @@
   <si>
     <t>08 - GAZE NAO ESTÉRIL 09 FIOS  Observação: FATURAMENTO ACORDADO PARA 30/06 COM FIUZA
  CLIENTE VEM COLETAR.</t>
+  </si>
+  <si>
+    <t>NATAL CLEAN</t>
+  </si>
+  <si>
+    <t>1040</t>
+  </si>
+  <si>
+    <t>08 - GAZE NAO ESTÉRIL 09 FIOS  Observação: 2,5%</t>
+  </si>
+  <si>
+    <t>51 - GAZE NAO ESTÉRIL 09 FIOS - PCT 500 UND Observação: 4%</t>
   </si>
 </sst>
 </file>
@@ -696,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L319"/>
+  <dimension ref="A1:L383"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
   <cols>
     <col customWidth="1" width="89.23828125" min="1" max="1"/>
@@ -2434,7 +2538,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="74" customHeight="1" ht="20.4" spans="1:10">
+    <row r="74" customHeight="1" ht="30.35" spans="1:10">
       <c r="A74" s="5" t="s">
         <v>14</v>
       </c>
@@ -2445,13 +2549,13 @@
         <v>68</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="E74" s="9" t="n">
         <v>7.48</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>2468.4</v>
+        <v>2692.8</v>
       </c>
       <c r="G74" s="10">
         <v>46212</v>
@@ -2466,7 +2570,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" customHeight="1" ht="19.4" spans="1:10">
+    <row r="75" customHeight="1" ht="28.15" spans="1:10">
       <c r="A75" s="5" t="s">
         <v>14</v>
       </c>
@@ -2477,13 +2581,13 @@
         <v>69</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="E75" s="9" t="n">
         <v>9.24</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>2772</v>
+        <v>2956.8</v>
       </c>
       <c r="G75" s="10">
         <v>46212</v>
@@ -2498,7 +2602,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="76" customHeight="1" ht="18.35" spans="1:10">
+    <row r="76" customHeight="1" ht="29.15" spans="1:10">
       <c r="A76" s="5" t="s">
         <v>14</v>
       </c>
@@ -2509,13 +2613,13 @@
         <v>70</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E76" s="9" t="n">
         <v>10.93</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>2951.1</v>
+        <v>3060.4</v>
       </c>
       <c r="G76" s="10">
         <v>46212</v>
@@ -2538,7 +2642,7 @@
         <v>20</v>
       </c>
       <c r="C77" s="13" t="n">
-        <v>8191.5</v>
+        <v>8710</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>19</v>
@@ -2552,7 +2656,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="79" customHeight="1" ht="27.7" spans="1:10">
+    <row r="79" customHeight="1" ht="29" spans="1:10">
       <c r="A79" s="5" t="s">
         <v>14</v>
       </c>
@@ -2575,16 +2679,16 @@
         <v>46156</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="I79" s="11" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="80" customHeight="1" ht="18.8" spans="1:10">
+    <row r="80" customHeight="1" ht="18.45" spans="1:10">
       <c r="A80" s="5" t="s">
         <v>14</v>
       </c>
@@ -2592,182 +2696,182 @@
         <v>74</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>1050</v>
+        <v>1020</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>6.84</v>
+        <v>8.28</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>7182</v>
+        <v>8445.6</v>
       </c>
       <c r="G80" s="10">
         <v>46167</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>525</v>
+        <v>420</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>50</v>
+        <v>41.18</v>
       </c>
       <c r="J80" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="81" customHeight="1" ht="19.3" spans="1:10">
-      <c r="A81" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D81" s="8" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E81" s="9" t="n">
-        <v>8.28</v>
-      </c>
-      <c r="F81" s="9" t="n">
-        <v>8445.6</v>
-      </c>
-      <c r="G81" s="10">
-        <v>46167</v>
-      </c>
-      <c r="H81" s="8" t="n">
-        <v>420</v>
-      </c>
-      <c r="I81" s="11" t="n">
-        <v>41.18</v>
-      </c>
-      <c r="J81" s="8" t="s">
+    <row r="81" customHeight="1" ht="15" spans="1:5">
+      <c r="A81" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81" s="13" t="n">
+        <v>103231.2</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81" s="14" t="n">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" ht="15" spans="1:1">
+      <c r="A82" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" ht="19.8" spans="1:10">
+      <c r="A83" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D83" s="8" t="n">
+        <v>630</v>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="F83" s="9" t="n">
+        <v>3830.4</v>
+      </c>
+      <c r="G83" s="10">
+        <v>46184</v>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="82" customHeight="1" ht="15" spans="1:5">
-      <c r="A82" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B82" s="12" t="s">
+    <row r="84" customHeight="1" ht="15" spans="1:5">
+      <c r="A84" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B84" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C82" s="13" t="n">
-        <v>110413.2</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E82" s="14" t="n">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" ht="15" spans="1:1">
-      <c r="A83" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="84" customHeight="1" ht="18.95" spans="1:10">
-      <c r="A84" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D84" s="8" t="n">
-        <v>630</v>
-      </c>
-      <c r="E84" s="9" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="F84" s="9" t="n">
+      <c r="C84" s="13" t="n">
         <v>3830.4</v>
       </c>
-      <c r="G84" s="10">
-        <v>46184</v>
-      </c>
-      <c r="H84" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" ht="15" spans="1:5">
-      <c r="A85" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B85" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C85" s="13" t="n">
-        <v>3830.4</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E85" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A86" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" ht="15" spans="1:12">
+      <c r="D84" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E84" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A85" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" ht="15" spans="1:12">
+      <c r="A86" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I86" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" ht="15" spans="1:1">
       <c r="A87" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C87" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A88" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D88" s="8" t="n">
+        <v>660</v>
+      </c>
+      <c r="E88" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D87" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I87" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J87" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K87" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L87" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="88" customHeight="1" ht="15" spans="1:1">
-      <c r="A88" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" ht="20.4" spans="1:10">
+      <c r="F88" s="9" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G88" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" ht="19.4" spans="1:10">
       <c r="A89" s="5" t="s">
         <v>14</v>
       </c>
@@ -2775,16 +2879,16 @@
         <v>78</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>660</v>
+        <v>400</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>3</v>
+        <v>4.067</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>1980</v>
+        <v>1626.8</v>
       </c>
       <c r="G89" s="10">
         <v>46198</v>
@@ -2799,7 +2903,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="90" customHeight="1" ht="19.4" spans="1:10">
+    <row r="90" customHeight="1" ht="18.35" spans="1:10">
       <c r="A90" s="5" t="s">
         <v>14</v>
       </c>
@@ -2807,16 +2911,16 @@
         <v>78</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>4.067</v>
+        <v>3.71</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>1626.8</v>
+        <v>1224.3</v>
       </c>
       <c r="G90" s="10">
         <v>46198</v>
@@ -2831,7 +2935,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="91" customHeight="1" ht="18.35" spans="1:10">
+    <row r="91" customHeight="1" ht="20.4" spans="1:10">
       <c r="A91" s="5" t="s">
         <v>14</v>
       </c>
@@ -2839,16 +2943,16 @@
         <v>78</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>3.71</v>
+        <v>5.124</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1224.3</v>
+        <v>1383.48</v>
       </c>
       <c r="G91" s="10">
         <v>46198</v>
@@ -2863,7 +2967,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="92" customHeight="1" ht="20.4" spans="1:10">
+    <row r="92" customHeight="1" ht="19.15" spans="1:10">
       <c r="A92" s="5" t="s">
         <v>14</v>
       </c>
@@ -2871,16 +2975,16 @@
         <v>78</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>270</v>
+        <v>450</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>5.124</v>
+        <v>4.25</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>1383.48</v>
+        <v>1912.5</v>
       </c>
       <c r="G92" s="10">
         <v>46198</v>
@@ -2895,7 +2999,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="93" customHeight="1" ht="19.15" spans="1:10">
+    <row r="93" customHeight="1" ht="20.75" spans="1:10">
       <c r="A93" s="5" t="s">
         <v>14</v>
       </c>
@@ -2903,16 +3007,16 @@
         <v>78</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>4.25</v>
+        <v>6.006</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>1912.5</v>
+        <v>5405.4</v>
       </c>
       <c r="G93" s="10">
         <v>46198</v>
@@ -2927,7 +3031,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="94" customHeight="1" ht="20.75" spans="1:10">
+    <row r="94" customHeight="1" ht="19.4" spans="1:10">
       <c r="A94" s="5" t="s">
         <v>14</v>
       </c>
@@ -2935,16 +3039,16 @@
         <v>78</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>900</v>
+        <v>490</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>6.006</v>
+        <v>5.48</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>5405.4</v>
+        <v>2685.2</v>
       </c>
       <c r="G94" s="10">
         <v>46198</v>
@@ -2959,7 +3063,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="95" customHeight="1" ht="19.4" spans="1:10">
+    <row r="95" customHeight="1" ht="20.25" spans="1:10">
       <c r="A95" s="5" t="s">
         <v>14</v>
       </c>
@@ -2967,16 +3071,16 @@
         <v>78</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D95" s="8" t="n">
-        <v>490</v>
+        <v>420</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>5.48</v>
+        <v>7.78</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>2685.2</v>
+        <v>3267.6</v>
       </c>
       <c r="G95" s="10">
         <v>46198</v>
@@ -2991,7 +3095,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="96" customHeight="1" ht="20.25" spans="1:10">
+    <row r="96" customHeight="1" ht="18.8" spans="1:10">
       <c r="A96" s="5" t="s">
         <v>14</v>
       </c>
@@ -2999,16 +3103,16 @@
         <v>78</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>420</v>
+        <v>100</v>
       </c>
       <c r="E96" s="9" t="n">
-        <v>7.78</v>
+        <v>8.12</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>3267.6</v>
+        <v>812</v>
       </c>
       <c r="G96" s="10">
         <v>46198</v>
@@ -3023,7 +3127,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="97" customHeight="1" ht="18.8" spans="1:10">
+    <row r="97" customHeight="1" ht="19.4" spans="1:10">
       <c r="A97" s="5" t="s">
         <v>14</v>
       </c>
@@ -3031,16 +3135,16 @@
         <v>78</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D97" s="8" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>8.12</v>
+        <v>11.144</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>812</v>
+        <v>2228.8</v>
       </c>
       <c r="G97" s="10">
         <v>46198</v>
@@ -3055,61 +3159,61 @@
         <v>79</v>
       </c>
     </row>
-    <row r="98" customHeight="1" ht="19.4" spans="1:10">
-      <c r="A98" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D98" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="E98" s="9" t="n">
-        <v>11.144</v>
-      </c>
-      <c r="F98" s="9" t="n">
-        <v>2228.8</v>
-      </c>
-      <c r="G98" s="10">
+    <row r="98" customHeight="1" ht="15" spans="1:5">
+      <c r="A98" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C98" s="13" t="n">
+        <v>22526.08</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" ht="15" spans="1:1">
+      <c r="A99" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" ht="18.95" spans="1:10">
+      <c r="A100" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D100" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="E100" s="9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F100" s="9" t="n">
+        <v>1560</v>
+      </c>
+      <c r="G100" s="10">
         <v>46198</v>
       </c>
-      <c r="H98" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="99" customHeight="1" ht="15" spans="1:5">
-      <c r="A99" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B99" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C99" s="13" t="n">
-        <v>22526.08</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E99" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" ht="15" spans="1:1">
-      <c r="A100" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" ht="18.95" spans="1:10">
+      <c r="H100" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" ht="20.4" spans="1:10">
       <c r="A101" s="5" t="s">
         <v>14</v>
       </c>
@@ -3117,16 +3221,16 @@
         <v>82</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D101" s="8" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5.2</v>
+        <v>6.78</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>1560</v>
+        <v>1830.6</v>
       </c>
       <c r="G101" s="10">
         <v>46198</v>
@@ -3141,7 +3245,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="102" customHeight="1" ht="20.4" spans="1:10">
+    <row r="102" customHeight="1" ht="20.5" spans="1:10">
       <c r="A102" s="5" t="s">
         <v>14</v>
       </c>
@@ -3149,16 +3253,16 @@
         <v>82</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D102" s="8" t="n">
-        <v>270</v>
+        <v>75</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>6.78</v>
+        <v>7.94</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>1830.6</v>
+        <v>595.5</v>
       </c>
       <c r="G102" s="10">
         <v>46198</v>
@@ -3173,7 +3277,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="103" customHeight="1" ht="20.5" spans="1:10">
+    <row r="103" customHeight="1" ht="19.3" spans="1:10">
       <c r="A103" s="5" t="s">
         <v>14</v>
       </c>
@@ -3181,16 +3285,16 @@
         <v>82</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D103" s="8" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>7.94</v>
+        <v>10.3</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>595.5</v>
+        <v>618</v>
       </c>
       <c r="G103" s="10">
         <v>46198</v>
@@ -3205,104 +3309,104 @@
         <v>23</v>
       </c>
     </row>
-    <row r="104" customHeight="1" ht="19.3" spans="1:10">
-      <c r="A104" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D104" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="E104" s="9" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="F104" s="9" t="n">
-        <v>618</v>
-      </c>
-      <c r="G104" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H104" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="105" customHeight="1" ht="15" spans="1:5">
-      <c r="A105" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B105" s="12" t="s">
+    <row r="104" customHeight="1" ht="15" spans="1:5">
+      <c r="A104" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B104" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C105" s="13" t="n">
+      <c r="C104" s="13" t="n">
         <v>4604.1</v>
       </c>
-      <c r="D105" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E105" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A106" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" customHeight="1" ht="15" spans="1:12">
+      <c r="D104" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A105" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" ht="15" spans="1:12">
+      <c r="A106" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L106" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" ht="15" spans="1:1">
       <c r="A107" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G107" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I107" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J107" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K107" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L107" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="108" customHeight="1" ht="15" spans="1:1">
-      <c r="A108" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="109" customHeight="1" ht="30.35" spans="1:10">
+    <row r="108" customHeight="1" ht="30.35" spans="1:10">
+      <c r="A108" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D108" s="8" t="n">
+        <v>330</v>
+      </c>
+      <c r="E108" s="9" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="F108" s="9" t="n">
+        <v>1527.9</v>
+      </c>
+      <c r="G108" s="10">
+        <v>46209</v>
+      </c>
+      <c r="H108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" ht="28.15" spans="1:10">
       <c r="A109" s="5" t="s">
         <v>14</v>
       </c>
@@ -3310,16 +3414,16 @@
         <v>84</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D109" s="8" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>4.63</v>
+        <v>6.28</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1527.9</v>
+        <v>1884</v>
       </c>
       <c r="G109" s="10">
         <v>46209</v>
@@ -3334,7 +3438,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="110" customHeight="1" ht="28.15" spans="1:10">
+    <row r="110" customHeight="1" ht="29.15" spans="1:10">
       <c r="A110" s="5" t="s">
         <v>14</v>
       </c>
@@ -3342,16 +3446,16 @@
         <v>84</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D110" s="8" t="n">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>6.28</v>
+        <v>5.73</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>1884</v>
+        <v>1890.9</v>
       </c>
       <c r="G110" s="10">
         <v>46209</v>
@@ -3366,7 +3470,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="111" customHeight="1" ht="29.15" spans="1:10">
+    <row r="111" customHeight="1" ht="29.4" spans="1:10">
       <c r="A111" s="5" t="s">
         <v>14</v>
       </c>
@@ -3374,16 +3478,16 @@
         <v>84</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D111" s="8" t="n">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>5.73</v>
+        <v>7.91</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>1890.9</v>
+        <v>2135.7</v>
       </c>
       <c r="G111" s="10">
         <v>46209</v>
@@ -3398,61 +3502,61 @@
         <v>49</v>
       </c>
     </row>
-    <row r="112" customHeight="1" ht="29.4" spans="1:10">
-      <c r="A112" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D112" s="8" t="n">
-        <v>270</v>
-      </c>
-      <c r="E112" s="9" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="F112" s="9" t="n">
-        <v>2135.7</v>
-      </c>
-      <c r="G112" s="10">
-        <v>46209</v>
-      </c>
-      <c r="H112" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="113" customHeight="1" ht="15" spans="1:5">
-      <c r="A113" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B113" s="12" t="s">
+    <row r="112" customHeight="1" ht="15" spans="1:5">
+      <c r="A112" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B112" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C113" s="13" t="n">
+      <c r="C112" s="13" t="n">
         <v>7438.5</v>
       </c>
-      <c r="D113" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E113" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" customHeight="1" ht="15" spans="1:1">
-      <c r="A114" s="2" t="s">
+      <c r="D112" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" ht="15" spans="1:1">
+      <c r="A113" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="115" customHeight="1" ht="18.45" spans="1:10">
+    <row r="114" customHeight="1" ht="18.45" spans="1:10">
+      <c r="A114" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D114" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>1128</v>
+      </c>
+      <c r="G114" s="10">
+        <v>46196.6411111111</v>
+      </c>
+      <c r="H114" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" ht="20.25" spans="1:10">
       <c r="A115" s="5" t="s">
         <v>14</v>
       </c>
@@ -3460,16 +3564,16 @@
         <v>90</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D115" s="8" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>5.64</v>
+        <v>7.1</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>1128</v>
+        <v>639</v>
       </c>
       <c r="G115" s="10">
         <v>46196.6411111111</v>
@@ -3484,7 +3588,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="116" customHeight="1" ht="20.25" spans="1:10">
+    <row r="116" customHeight="1" ht="18.35" spans="1:10">
       <c r="A116" s="5" t="s">
         <v>14</v>
       </c>
@@ -3492,16 +3596,16 @@
         <v>90</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>7.1</v>
+        <v>8.32</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>639</v>
+        <v>2496</v>
       </c>
       <c r="G116" s="10">
         <v>46196.6411111111</v>
@@ -3516,7 +3620,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="117" customHeight="1" ht="18.35" spans="1:10">
+    <row r="117" customHeight="1" ht="19.3" spans="1:10">
       <c r="A117" s="5" t="s">
         <v>14</v>
       </c>
@@ -3524,16 +3628,16 @@
         <v>90</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D117" s="8" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>8.32</v>
+        <v>10.79</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>2496</v>
+        <v>1294.8</v>
       </c>
       <c r="G117" s="10">
         <v>46196.6411111111</v>
@@ -3548,7 +3652,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="118" customHeight="1" ht="19.3" spans="1:10">
+    <row r="118" customHeight="1" ht="19.55" spans="1:10">
       <c r="A118" s="5" t="s">
         <v>14</v>
       </c>
@@ -3556,16 +3660,16 @@
         <v>90</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="D118" s="8" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>10.79</v>
+        <v>5.2</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>1294.8</v>
+        <v>546</v>
       </c>
       <c r="G118" s="10">
         <v>46196.6411111111</v>
@@ -3580,104 +3684,104 @@
         <v>58</v>
       </c>
     </row>
-    <row r="119" customHeight="1" ht="19.55" spans="1:10">
-      <c r="A119" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D119" s="8" t="n">
-        <v>105</v>
-      </c>
-      <c r="E119" s="9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F119" s="9" t="n">
-        <v>546</v>
-      </c>
-      <c r="G119" s="10">
-        <v>46196.6411111111</v>
-      </c>
-      <c r="H119" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="120" customHeight="1" ht="15" spans="1:5">
-      <c r="A120" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B120" s="12" t="s">
+    <row r="119" customHeight="1" ht="15" spans="1:5">
+      <c r="A119" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B119" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C120" s="13" t="n">
+      <c r="C119" s="13" t="n">
         <v>6103.8</v>
       </c>
-      <c r="D120" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E120" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A121" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" customHeight="1" ht="15" spans="1:12">
+      <c r="D119" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E119" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A120" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" ht="15" spans="1:12">
+      <c r="A121" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J121" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L121" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" ht="15" spans="1:1">
       <c r="A122" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E122" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H122" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I122" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J122" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K122" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L122" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="123" customHeight="1" ht="15" spans="1:1">
-      <c r="A123" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="124" customHeight="1" ht="20.4" spans="1:10">
+    <row r="123" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A123" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D123" s="8" t="n">
+        <v>1210</v>
+      </c>
+      <c r="E123" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F123" s="9" t="n">
+        <v>4356</v>
+      </c>
+      <c r="G123" s="10">
+        <v>46185</v>
+      </c>
+      <c r="H123" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" ht="19.4" spans="1:10">
       <c r="A124" s="5" t="s">
         <v>14</v>
       </c>
@@ -3685,16 +3789,16 @@
         <v>93</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D124" s="8" t="n">
-        <v>1210</v>
+        <v>225</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>3.6</v>
+        <v>7.88</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>4356</v>
+        <v>1773</v>
       </c>
       <c r="G124" s="10">
         <v>46185</v>
@@ -3709,7 +3813,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="125" customHeight="1" ht="19.4" spans="1:10">
+    <row r="125" customHeight="1" ht="18.35" spans="1:10">
       <c r="A125" s="5" t="s">
         <v>14</v>
       </c>
@@ -3717,16 +3821,16 @@
         <v>93</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D125" s="8" t="n">
-        <v>225</v>
+        <v>350</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>7.88</v>
+        <v>6.58</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1773</v>
+        <v>2303</v>
       </c>
       <c r="G125" s="10">
         <v>46185</v>
@@ -3741,7 +3845,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="126" customHeight="1" ht="18.35" spans="1:10">
+    <row r="126" customHeight="1" ht="20.4" spans="1:10">
       <c r="A126" s="5" t="s">
         <v>14</v>
       </c>
@@ -3749,16 +3853,16 @@
         <v>93</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D126" s="8" t="n">
-        <v>350</v>
+        <v>40</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>6.58</v>
+        <v>14</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>2303</v>
+        <v>560</v>
       </c>
       <c r="G126" s="10">
         <v>46185</v>
@@ -3773,61 +3877,61 @@
         <v>94</v>
       </c>
     </row>
-    <row r="127" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A127" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D127" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="E127" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="F127" s="9" t="n">
-        <v>560</v>
-      </c>
-      <c r="G127" s="10">
-        <v>46185</v>
-      </c>
-      <c r="H127" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="128" customHeight="1" ht="15" spans="1:5">
-      <c r="A128" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B128" s="12" t="s">
+    <row r="127" customHeight="1" ht="15" spans="1:5">
+      <c r="A127" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B127" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C128" s="13" t="n">
+      <c r="C127" s="13" t="n">
         <v>8992</v>
       </c>
-      <c r="D128" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E128" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" customHeight="1" ht="15" spans="1:1">
-      <c r="A129" s="2" t="s">
+      <c r="D127" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" ht="15" spans="1:1">
+      <c r="A128" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="130" customHeight="1" ht="19.3" spans="1:10">
+    <row r="129" customHeight="1" ht="19.3" spans="1:10">
+      <c r="A129" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D129" s="8" t="n">
+        <v>225</v>
+      </c>
+      <c r="E129" s="9" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="F129" s="9" t="n">
+        <v>1930.5</v>
+      </c>
+      <c r="G129" s="10">
+        <v>46182</v>
+      </c>
+      <c r="H129" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" ht="19.9" spans="1:10">
       <c r="A130" s="5" t="s">
         <v>14</v>
       </c>
@@ -3835,16 +3939,16 @@
         <v>96</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D130" s="8" t="n">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>8.58</v>
+        <v>7.83</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>1930.5</v>
+        <v>1644.3</v>
       </c>
       <c r="G130" s="10">
         <v>46182</v>
@@ -3859,104 +3963,104 @@
         <v>36</v>
       </c>
     </row>
-    <row r="131" customHeight="1" ht="19.9" spans="1:10">
-      <c r="A131" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D131" s="8" t="n">
-        <v>210</v>
-      </c>
-      <c r="E131" s="9" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="F131" s="9" t="n">
-        <v>1644.3</v>
-      </c>
-      <c r="G131" s="10">
-        <v>46182</v>
-      </c>
-      <c r="H131" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="132" customHeight="1" ht="15" spans="1:5">
-      <c r="A132" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B132" s="12" t="s">
+    <row r="131" customHeight="1" ht="15" spans="1:5">
+      <c r="A131" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B131" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C132" s="13" t="n">
+      <c r="C131" s="13" t="n">
         <v>3574.8</v>
       </c>
-      <c r="D132" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E132" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A133" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" customHeight="1" ht="15" spans="1:12">
+      <c r="D131" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A132" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" ht="15" spans="1:12">
+      <c r="A133" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H133" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I133" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J133" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L133" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" ht="15" spans="1:1">
       <c r="A134" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G134" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H134" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I134" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J134" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K134" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L134" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="135" customHeight="1" ht="15" spans="1:1">
-      <c r="A135" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="136" customHeight="1" ht="20.4" spans="1:10">
+    <row r="135" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A135" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D135" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="E135" s="9" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="F135" s="9" t="n">
+        <v>2464</v>
+      </c>
+      <c r="G135" s="10">
+        <v>46199.4372916667</v>
+      </c>
+      <c r="H135" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" ht="19.4" spans="1:10">
       <c r="A136" s="5" t="s">
         <v>14</v>
       </c>
@@ -3964,16 +4068,16 @@
         <v>98</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D136" s="8" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="E136" s="9" t="n">
-        <v>6.16</v>
+        <v>7.76</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>2464</v>
+        <v>6984</v>
       </c>
       <c r="G136" s="10">
         <v>46199.4372916667</v>
@@ -3988,7 +4092,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="137" customHeight="1" ht="19.4" spans="1:10">
+    <row r="137" customHeight="1" ht="18.35" spans="1:10">
       <c r="A137" s="5" t="s">
         <v>14</v>
       </c>
@@ -3996,16 +4100,16 @@
         <v>98</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D137" s="8" t="n">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>7.76</v>
+        <v>9.09</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>6984</v>
+        <v>6817.5</v>
       </c>
       <c r="G137" s="10">
         <v>46199.4372916667</v>
@@ -4020,7 +4124,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="138" customHeight="1" ht="18.35" spans="1:10">
+    <row r="138" customHeight="1" ht="20.4" spans="1:10">
       <c r="A138" s="5" t="s">
         <v>14</v>
       </c>
@@ -4028,16 +4132,16 @@
         <v>98</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D138" s="8" t="n">
-        <v>750</v>
+        <v>300</v>
       </c>
       <c r="E138" s="9" t="n">
-        <v>9.09</v>
+        <v>11.79</v>
       </c>
       <c r="F138" s="9" t="n">
-        <v>6817.5</v>
+        <v>3537</v>
       </c>
       <c r="G138" s="10">
         <v>46199.4372916667</v>
@@ -4052,7 +4156,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" customHeight="1" ht="20.4" spans="1:10">
+    <row r="139" customHeight="1" ht="19.15" spans="1:10">
       <c r="A139" s="5" t="s">
         <v>14</v>
       </c>
@@ -4060,16 +4164,16 @@
         <v>98</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="D139" s="8" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>11.79</v>
+        <v>5.68</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>3537</v>
+        <v>1192.8</v>
       </c>
       <c r="G139" s="10">
         <v>46199.4372916667</v>
@@ -4084,61 +4188,61 @@
         <v>23</v>
       </c>
     </row>
-    <row r="140" customHeight="1" ht="19.15" spans="1:10">
-      <c r="A140" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D140" s="8" t="n">
-        <v>210</v>
-      </c>
-      <c r="E140" s="9" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="F140" s="9" t="n">
-        <v>1192.8</v>
-      </c>
-      <c r="G140" s="10">
-        <v>46199.4372916667</v>
-      </c>
-      <c r="H140" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="141" customHeight="1" ht="15" spans="1:5">
-      <c r="A141" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B141" s="12" t="s">
+    <row r="140" customHeight="1" ht="15" spans="1:5">
+      <c r="A140" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B140" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C141" s="13" t="n">
+      <c r="C140" s="13" t="n">
         <v>20995.3</v>
       </c>
-      <c r="D141" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E141" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" customHeight="1" ht="15" spans="1:1">
-      <c r="A142" s="2" t="s">
+      <c r="D140" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E140" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" ht="15" spans="1:1">
+      <c r="A141" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="143" customHeight="1" ht="19.9" spans="1:10">
+    <row r="142" customHeight="1" ht="19.9" spans="1:10">
+      <c r="A142" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D142" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E142" s="9" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="F142" s="9" t="n">
+        <v>1162</v>
+      </c>
+      <c r="G142" s="10">
+        <v>46197</v>
+      </c>
+      <c r="H142" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" ht="18.35" spans="1:10">
       <c r="A143" s="5" t="s">
         <v>14</v>
       </c>
@@ -4146,16 +4250,16 @@
         <v>100</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D143" s="8" t="n">
-        <v>200</v>
+        <v>1080</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>5.81</v>
+        <v>7.32</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>1162</v>
+        <v>7905.6</v>
       </c>
       <c r="G143" s="10">
         <v>46197</v>
@@ -4170,7 +4274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" customHeight="1" ht="18.35" spans="1:10">
+    <row r="144" customHeight="1" ht="20.15" spans="1:10">
       <c r="A144" s="5" t="s">
         <v>14</v>
       </c>
@@ -4178,16 +4282,16 @@
         <v>100</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D144" s="8" t="n">
-        <v>1080</v>
+        <v>900</v>
       </c>
       <c r="E144" s="9" t="n">
-        <v>7.32</v>
+        <v>8.58</v>
       </c>
       <c r="F144" s="9" t="n">
-        <v>7905.6</v>
+        <v>7722</v>
       </c>
       <c r="G144" s="10">
         <v>46197</v>
@@ -4202,7 +4306,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" customHeight="1" ht="20.15" spans="1:10">
+    <row r="145" customHeight="1" ht="21.1" spans="1:10">
       <c r="A145" s="5" t="s">
         <v>14</v>
       </c>
@@ -4210,16 +4314,16 @@
         <v>100</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D145" s="8" t="n">
         <v>900</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>8.58</v>
+        <v>11.12</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>7722</v>
+        <v>10008</v>
       </c>
       <c r="G145" s="10">
         <v>46197</v>
@@ -4234,104 +4338,104 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" customHeight="1" ht="21.1" spans="1:10">
-      <c r="A146" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B146" s="6" t="s">
+    <row r="146" customHeight="1" ht="15" spans="1:5">
+      <c r="A146" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C146" s="13" t="n">
+        <v>26797.6</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E146" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A147" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" ht="15" spans="1:12">
+      <c r="A148" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G148" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H148" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I148" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J148" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K148" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L148" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" ht="15" spans="1:1">
+      <c r="A149" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A150" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D150" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="C146" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D146" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="E146" s="9" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="F146" s="9" t="n">
-        <v>10008</v>
-      </c>
-      <c r="G146" s="10">
-        <v>46197</v>
-      </c>
-      <c r="H146" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="147" customHeight="1" ht="15" spans="1:5">
-      <c r="A147" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B147" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C147" s="13" t="n">
-        <v>26797.6</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E147" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A148" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" customHeight="1" ht="15" spans="1:12">
-      <c r="A149" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E149" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F149" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G149" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H149" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I149" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J149" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K149" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L149" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="150" customHeight="1" ht="15" spans="1:1">
-      <c r="A150" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="151" customHeight="1" ht="20.4" spans="1:10">
+      <c r="E150" s="9" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="F150" s="9" t="n">
+        <v>641</v>
+      </c>
+      <c r="G150" s="10">
+        <v>46113</v>
+      </c>
+      <c r="H150" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" ht="19.4" spans="1:10">
       <c r="A151" s="5" t="s">
         <v>14</v>
       </c>
@@ -4339,16 +4443,16 @@
         <v>102</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D151" s="8" t="n">
-        <v>100</v>
+        <v>360</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>6.41</v>
+        <v>7.92</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>641</v>
+        <v>2851.2</v>
       </c>
       <c r="G151" s="10">
         <v>46113</v>
@@ -4363,7 +4467,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="152" customHeight="1" ht="19.4" spans="1:10">
+    <row r="152" customHeight="1" ht="18.35" spans="1:10">
       <c r="A152" s="5" t="s">
         <v>14</v>
       </c>
@@ -4371,16 +4475,16 @@
         <v>102</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D152" s="8" t="n">
-        <v>360</v>
+        <v>750</v>
       </c>
       <c r="E152" s="9" t="n">
-        <v>7.92</v>
+        <v>9.37</v>
       </c>
       <c r="F152" s="9" t="n">
-        <v>2851.2</v>
+        <v>7027.5</v>
       </c>
       <c r="G152" s="10">
         <v>46113</v>
@@ -4395,7 +4499,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="153" customHeight="1" ht="18.35" spans="1:10">
+    <row r="153" customHeight="1" ht="20.4" spans="1:10">
       <c r="A153" s="5" t="s">
         <v>14</v>
       </c>
@@ -4403,16 +4507,16 @@
         <v>102</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D153" s="8" t="n">
-        <v>750</v>
+        <v>360</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>9.37</v>
+        <v>12.03</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>7027.5</v>
+        <v>4330.8</v>
       </c>
       <c r="G153" s="10">
         <v>46113</v>
@@ -4427,61 +4531,61 @@
         <v>23</v>
       </c>
     </row>
-    <row r="154" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A154" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C154" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D154" s="8" t="n">
-        <v>360</v>
-      </c>
-      <c r="E154" s="9" t="n">
-        <v>12.03</v>
-      </c>
-      <c r="F154" s="9" t="n">
-        <v>4330.8</v>
-      </c>
-      <c r="G154" s="10">
-        <v>46113</v>
-      </c>
-      <c r="H154" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I154" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J154" s="8" t="s">
+    <row r="154" customHeight="1" ht="15" spans="1:5">
+      <c r="A154" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B154" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C154" s="13" t="n">
+        <v>14850.5</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E154" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" ht="15" spans="1:1">
+      <c r="A155" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" ht="19.3" spans="1:10">
+      <c r="A156" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D156" s="8" t="n">
+        <v>550</v>
+      </c>
+      <c r="E156" s="9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F156" s="9" t="n">
+        <v>2860</v>
+      </c>
+      <c r="G156" s="10">
+        <v>46164</v>
+      </c>
+      <c r="H156" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="155" customHeight="1" ht="15" spans="1:5">
-      <c r="A155" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B155" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C155" s="13" t="n">
-        <v>14850.5</v>
-      </c>
-      <c r="D155" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E155" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" customHeight="1" ht="15" spans="1:1">
-      <c r="A156" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="157" customHeight="1" ht="19.3" spans="1:10">
+    <row r="157" customHeight="1" ht="19.9" spans="1:10">
       <c r="A157" s="5" t="s">
         <v>14</v>
       </c>
@@ -4489,16 +4593,16 @@
         <v>104</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D157" s="8" t="n">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>2860</v>
+        <v>4200</v>
       </c>
       <c r="G157" s="10">
         <v>46164</v>
@@ -4513,24 +4617,24 @@
         <v>23</v>
       </c>
     </row>
-    <row r="158" customHeight="1" ht="19.9" spans="1:10">
+    <row r="158" customHeight="1" ht="18.35" spans="1:10">
       <c r="A158" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D158" s="8" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="E158" s="9" t="n">
-        <v>7.5</v>
+        <v>5.2</v>
       </c>
       <c r="F158" s="9" t="n">
-        <v>4200</v>
+        <v>2860</v>
       </c>
       <c r="G158" s="10">
         <v>46164</v>
@@ -4545,7 +4649,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="159" customHeight="1" ht="18.35" spans="1:10">
+    <row r="159" customHeight="1" ht="20.15" spans="1:10">
       <c r="A159" s="5" t="s">
         <v>14</v>
       </c>
@@ -4553,16 +4657,16 @@
         <v>107</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D159" s="8" t="n">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>2860</v>
+        <v>4200</v>
       </c>
       <c r="G159" s="10">
         <v>46164</v>
@@ -4577,7 +4681,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="160" customHeight="1" ht="20.15" spans="1:10">
+    <row r="160" customHeight="1" ht="21.1" spans="1:10">
       <c r="A160" s="5" t="s">
         <v>14</v>
       </c>
@@ -4585,16 +4689,16 @@
         <v>107</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D160" s="8" t="n">
-        <v>560</v>
+        <v>250</v>
       </c>
       <c r="E160" s="9" t="n">
-        <v>7.5</v>
+        <v>12.1</v>
       </c>
       <c r="F160" s="9" t="n">
-        <v>4200</v>
+        <v>3025</v>
       </c>
       <c r="G160" s="10">
         <v>46164</v>
@@ -4609,104 +4713,104 @@
         <v>23</v>
       </c>
     </row>
-    <row r="161" customHeight="1" ht="21.1" spans="1:10">
-      <c r="A161" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B161" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C161" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D161" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E161" s="9" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F161" s="9" t="n">
-        <v>3025</v>
-      </c>
-      <c r="G161" s="10">
-        <v>46164</v>
-      </c>
-      <c r="H161" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J161" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="162" customHeight="1" ht="15" spans="1:5">
-      <c r="A162" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B162" s="12" t="s">
+    <row r="161" customHeight="1" ht="15" spans="1:5">
+      <c r="A161" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B161" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C162" s="13" t="n">
+      <c r="C161" s="13" t="n">
         <v>17145</v>
       </c>
-      <c r="D162" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E162" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A163" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" customHeight="1" ht="15" spans="1:12">
+      <c r="D161" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E161" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A162" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" ht="15" spans="1:12">
+      <c r="A163" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H163" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I163" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J163" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K163" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L163" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" ht="15" spans="1:1">
       <c r="A164" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E164" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F164" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G164" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H164" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I164" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J164" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K164" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L164" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="165" customHeight="1" ht="15" spans="1:1">
-      <c r="A165" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="166" customHeight="1" ht="30.35" spans="1:10">
+    <row r="165" customHeight="1" ht="30.35" spans="1:10">
+      <c r="A165" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D165" s="8" t="n">
+        <v>330</v>
+      </c>
+      <c r="E165" s="9" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="F165" s="9" t="n">
+        <v>1527.9</v>
+      </c>
+      <c r="G165" s="10">
+        <v>46209</v>
+      </c>
+      <c r="H165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" ht="28.15" spans="1:10">
       <c r="A166" s="5" t="s">
         <v>14</v>
       </c>
@@ -4714,16 +4818,16 @@
         <v>110</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D166" s="8" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="E166" s="9" t="n">
-        <v>4.63</v>
+        <v>6.28</v>
       </c>
       <c r="F166" s="9" t="n">
-        <v>1527.9</v>
+        <v>1884</v>
       </c>
       <c r="G166" s="10">
         <v>46209</v>
@@ -4738,7 +4842,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="167" customHeight="1" ht="28.15" spans="1:10">
+    <row r="167" customHeight="1" ht="29.15" spans="1:10">
       <c r="A167" s="5" t="s">
         <v>14</v>
       </c>
@@ -4746,16 +4850,16 @@
         <v>110</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D167" s="8" t="n">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="E167" s="9" t="n">
-        <v>6.28</v>
+        <v>5.73</v>
       </c>
       <c r="F167" s="9" t="n">
-        <v>1884</v>
+        <v>1890.9</v>
       </c>
       <c r="G167" s="10">
         <v>46209</v>
@@ -4770,7 +4874,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="168" customHeight="1" ht="29.15" spans="1:10">
+    <row r="168" customHeight="1" ht="29.4" spans="1:10">
       <c r="A168" s="5" t="s">
         <v>14</v>
       </c>
@@ -4778,16 +4882,16 @@
         <v>110</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D168" s="8" t="n">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="E168" s="9" t="n">
-        <v>5.73</v>
+        <v>7.91</v>
       </c>
       <c r="F168" s="9" t="n">
-        <v>1890.9</v>
+        <v>2135.7</v>
       </c>
       <c r="G168" s="10">
         <v>46209</v>
@@ -4802,158 +4906,158 @@
         <v>49</v>
       </c>
     </row>
-    <row r="169" customHeight="1" ht="29.4" spans="1:10">
-      <c r="A169" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B169" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C169" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D169" s="8" t="n">
-        <v>270</v>
-      </c>
-      <c r="E169" s="9" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="F169" s="9" t="n">
-        <v>2135.7</v>
-      </c>
-      <c r="G169" s="10">
-        <v>46209</v>
-      </c>
-      <c r="H169" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I169" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J169" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="170" customHeight="1" ht="15" spans="1:5">
-      <c r="A170" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B170" s="12" t="s">
+    <row r="169" customHeight="1" ht="15" spans="1:5">
+      <c r="A169" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B169" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C170" s="13" t="n">
+      <c r="C169" s="13" t="n">
         <v>7438.5</v>
       </c>
-      <c r="D170" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E170" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" customHeight="1" ht="15" spans="1:1">
-      <c r="A171" s="2" t="s">
+      <c r="D169" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E169" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" ht="15" spans="1:1">
+      <c r="A170" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="172" customHeight="1" ht="18.45" spans="1:10">
-      <c r="A172" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B172" s="6" t="s">
+    <row r="171" customHeight="1" ht="18.45" spans="1:10">
+      <c r="A171" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B171" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C172" s="7" t="s">
+      <c r="C171" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D172" s="8" t="n">
+      <c r="D171" s="8" t="n">
         <v>1050</v>
       </c>
-      <c r="E172" s="9" t="n">
+      <c r="E171" s="9" t="n">
         <v>7.15</v>
       </c>
-      <c r="F172" s="9" t="n">
+      <c r="F171" s="9" t="n">
         <v>7507.5</v>
       </c>
-      <c r="G172" s="10">
+      <c r="G171" s="10">
         <v>46175</v>
       </c>
-      <c r="H172" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I172" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J172" s="8" t="s">
+      <c r="H171" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="173" customHeight="1" ht="15" spans="1:5">
-      <c r="A173" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B173" s="12" t="s">
+    <row r="172" customHeight="1" ht="15" spans="1:5">
+      <c r="A172" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B172" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C173" s="13" t="n">
+      <c r="C172" s="13" t="n">
         <v>7507.5</v>
       </c>
-      <c r="D173" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E173" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A174" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" customHeight="1" ht="15" spans="1:12">
+      <c r="D172" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E172" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A173" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" ht="15" spans="1:12">
+      <c r="A174" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E174" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G174" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H174" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I174" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J174" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L174" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" ht="15" spans="1:1">
       <c r="A175" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E175" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F175" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G175" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H175" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I175" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J175" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K175" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L175" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="176" customHeight="1" ht="15" spans="1:1">
-      <c r="A176" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="177" customHeight="1" ht="47.15" spans="1:10">
+    <row r="176" customHeight="1" ht="47.15" spans="1:10">
+      <c r="A176" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D176" s="8" t="n">
+        <v>616</v>
+      </c>
+      <c r="E176" s="9" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="F176" s="9" t="n">
+        <v>3314.08</v>
+      </c>
+      <c r="G176" s="10">
+        <v>46168</v>
+      </c>
+      <c r="H176" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="177" customHeight="1" ht="47.85" spans="1:10">
       <c r="A177" s="5" t="s">
         <v>14</v>
       </c>
@@ -4961,16 +5065,16 @@
         <v>114</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D177" s="8" t="n">
-        <v>616</v>
+        <v>540</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>5.38</v>
+        <v>7.94</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3314.08</v>
+        <v>4287.6</v>
       </c>
       <c r="G177" s="10">
         <v>46168</v>
@@ -4985,7 +5089,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="178" customHeight="1" ht="47.85" spans="1:10">
+    <row r="178" customHeight="1" ht="47" spans="1:10">
       <c r="A178" s="5" t="s">
         <v>14</v>
       </c>
@@ -4993,16 +5097,16 @@
         <v>114</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D178" s="8" t="n">
-        <v>540</v>
+        <v>616</v>
       </c>
       <c r="E178" s="9" t="n">
-        <v>7.94</v>
+        <v>10.3</v>
       </c>
       <c r="F178" s="9" t="n">
-        <v>4287.6</v>
+        <v>6344.8</v>
       </c>
       <c r="G178" s="10">
         <v>46168</v>
@@ -5017,327 +5121,306 @@
         <v>58</v>
       </c>
     </row>
-    <row r="179" customHeight="1" ht="47" spans="1:10">
-      <c r="A179" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B179" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C179" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D179" s="8" t="n">
-        <v>616</v>
-      </c>
-      <c r="E179" s="9" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="F179" s="9" t="n">
-        <v>6344.8</v>
-      </c>
-      <c r="G179" s="10">
-        <v>46168</v>
-      </c>
-      <c r="H179" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I179" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J179" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="180" customHeight="1" ht="15" spans="1:5">
-      <c r="A180" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B180" s="12" t="s">
+    <row r="179" customHeight="1" ht="15" spans="1:5">
+      <c r="A179" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B179" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C180" s="13" t="n">
+      <c r="C179" s="13" t="n">
         <v>13946.48</v>
       </c>
-      <c r="D180" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E180" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A181" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" customHeight="1" ht="15" spans="1:12">
+      <c r="D179" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E179" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A180" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" ht="15" spans="1:12">
+      <c r="A181" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E181" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G181" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H181" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I181" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J181" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K181" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L181" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" ht="15" spans="1:1">
       <c r="A182" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" ht="30.35" spans="1:10">
+      <c r="A183" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C183" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D183" s="8" t="n">
+        <v>5100</v>
+      </c>
+      <c r="E183" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F183" s="9" t="n">
+        <v>12750</v>
+      </c>
+      <c r="G183" s="10">
+        <v>46216.3893171296</v>
+      </c>
+      <c r="H183" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" ht="15" spans="1:5">
+      <c r="A184" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B184" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C184" s="13" t="n">
+        <v>12750</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E184" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A185" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" ht="15" spans="1:12">
+      <c r="A186" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B182" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C182" s="2" t="s">
+      <c r="B186" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C186" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D182" s="2" t="s">
+      <c r="D186" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E182" s="4" t="s">
+      <c r="E186" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F182" s="4" t="s">
+      <c r="F186" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G182" s="4" t="s">
+      <c r="G186" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H182" s="4" t="s">
+      <c r="H186" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I182" s="4" t="s">
+      <c r="I186" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J182" s="4" t="s">
+      <c r="J186" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K182" s="2" t="s">
+      <c r="K186" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L182" s="4" t="s">
+      <c r="L186" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="183" customHeight="1" ht="15" spans="1:1">
-      <c r="A183" s="2" t="s">
+    <row r="187" customHeight="1" ht="15" spans="1:1">
+      <c r="A187" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="184" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A184" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B184" s="6" t="s">
+    <row r="188" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A188" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B188" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C184" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D184" s="8" t="n">
+      <c r="C188" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D188" s="8" t="n">
         <v>2100</v>
       </c>
-      <c r="E184" s="9" t="n">
+      <c r="E188" s="9" t="n">
         <v>5.76</v>
       </c>
-      <c r="F184" s="9" t="n">
+      <c r="F188" s="9" t="n">
         <v>12096</v>
       </c>
-      <c r="G184" s="10">
+      <c r="G188" s="10">
         <v>46209</v>
       </c>
-      <c r="H184" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I184" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J184" s="8" t="s">
+      <c r="H188" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="185" customHeight="1" ht="15" spans="1:5">
-      <c r="A185" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B185" s="12" t="s">
+    <row r="189" customHeight="1" ht="15" spans="1:5">
+      <c r="A189" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B189" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C185" s="13" t="n">
+      <c r="C189" s="13" t="n">
         <v>12096</v>
       </c>
-      <c r="D185" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E185" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" customHeight="1" ht="15" spans="1:1">
-      <c r="A186" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="187" customHeight="1" ht="46.9" spans="1:10">
-      <c r="A187" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B187" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C187" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D187" s="8" t="n">
+      <c r="D189" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E189" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" ht="15" spans="1:1">
+      <c r="A190" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" ht="46.9" spans="1:10">
+      <c r="A191" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D191" s="8" t="n">
         <v>200100</v>
       </c>
-      <c r="E187" s="9" t="n">
+      <c r="E191" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="F187" s="9" t="n">
+      <c r="F191" s="9" t="n">
         <v>820410</v>
       </c>
-      <c r="G187" s="10">
+      <c r="G191" s="10">
         <v>46119</v>
       </c>
-      <c r="H187" s="8" t="n">
-        <v>86400</v>
-      </c>
-      <c r="I187" s="11" t="n">
-        <v>43.18</v>
-      </c>
-      <c r="J187" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="188" customHeight="1" ht="15" spans="1:5">
-      <c r="A188" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B188" s="12" t="s">
+      <c r="H191" s="8" t="n">
+        <v>101400</v>
+      </c>
+      <c r="I191" s="11" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="J191" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="192" customHeight="1" ht="15" spans="1:5">
+      <c r="A192" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B192" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C188" s="13" t="n">
+      <c r="C192" s="13" t="n">
         <v>820410</v>
       </c>
-      <c r="D188" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E188" s="14" t="n">
-        <v>86400</v>
-      </c>
-    </row>
-    <row r="189" customHeight="1" ht="15" spans="1:1">
-      <c r="A189" s="2" t="s">
+      <c r="D192" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E192" s="14" t="n">
+        <v>101400</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" ht="15" spans="1:1">
+      <c r="A193" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="190" customHeight="1" ht="19.8" spans="1:10">
-      <c r="A190" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B190" s="6" t="s">
+    <row r="194" customHeight="1" ht="29.6" spans="1:10">
+      <c r="A194" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B194" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C190" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D190" s="8" t="n">
+      <c r="C194" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D194" s="8" t="n">
         <v>2100</v>
       </c>
-      <c r="E190" s="9" t="n">
+      <c r="E194" s="9" t="n">
         <v>5.76</v>
       </c>
-      <c r="F190" s="9" t="n">
+      <c r="F194" s="9" t="n">
         <v>12096</v>
       </c>
-      <c r="G190" s="10">
+      <c r="G194" s="10">
         <v>46212</v>
       </c>
-      <c r="H190" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I190" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J190" s="8" t="s">
+      <c r="H194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" s="8" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="191" customHeight="1" ht="15" spans="1:5">
-      <c r="A191" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B191" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C191" s="13" t="n">
-        <v>12096</v>
-      </c>
-      <c r="D191" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E191" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" customHeight="1" ht="15" spans="1:1">
-      <c r="A192" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="193" customHeight="1" ht="21.35" spans="1:10">
-      <c r="A193" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B193" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C193" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D193" s="8" t="n">
-        <v>50100</v>
-      </c>
-      <c r="E193" s="9" t="n">
-        <v>4.517</v>
-      </c>
-      <c r="F193" s="9" t="n">
-        <v>226301.7</v>
-      </c>
-      <c r="G193" s="10">
-        <v>46156</v>
-      </c>
-      <c r="H193" s="8" t="n">
-        <v>18750</v>
-      </c>
-      <c r="I193" s="11" t="n">
-        <v>37.43</v>
-      </c>
-      <c r="J193" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="194" customHeight="1" ht="20" spans="1:10">
-      <c r="A194" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B194" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C194" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="D194" s="8" t="n">
-        <v>50100</v>
-      </c>
-      <c r="E194" s="9" t="n">
-        <v>4.517</v>
-      </c>
-      <c r="F194" s="9" t="n">
-        <v>226301.7</v>
-      </c>
-      <c r="G194" s="10">
-        <v>46163</v>
-      </c>
-      <c r="H194" s="8" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I194" s="11" t="n">
-        <v>29.94</v>
-      </c>
-      <c r="J194" s="8" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="195" customHeight="1" ht="15" spans="1:5">
@@ -5348,13 +5431,13 @@
         <v>20</v>
       </c>
       <c r="C195" s="13" t="n">
-        <v>452603.4</v>
+        <v>12096</v>
       </c>
       <c r="D195" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E195" s="14" t="n">
-        <v>33750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" customHeight="1" ht="77.35" spans="1:1">
@@ -5367,7 +5450,7 @@
         <v>1</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>3</v>
@@ -5402,386 +5485,407 @@
     </row>
     <row r="198" customHeight="1" ht="15" spans="1:1">
       <c r="A198" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="199" customHeight="1" ht="37.05" spans="1:10">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="199" customHeight="1" ht="20.4" spans="1:10">
       <c r="A199" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="C199" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D199" s="8" t="n">
+        <v>50100</v>
+      </c>
+      <c r="E199" s="9" t="n">
+        <v>4.517</v>
+      </c>
+      <c r="F199" s="9" t="n">
+        <v>226301.7</v>
+      </c>
+      <c r="G199" s="10">
+        <v>46156</v>
+      </c>
+      <c r="H199" s="8" t="n">
+        <v>18750</v>
+      </c>
+      <c r="I199" s="11" t="n">
+        <v>37.43</v>
+      </c>
+      <c r="J199" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="200" customHeight="1" ht="19.4" spans="1:10">
+      <c r="A200" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B200" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D199" s="8" t="n">
+      <c r="C200" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D200" s="8" t="n">
+        <v>50100</v>
+      </c>
+      <c r="E200" s="9" t="n">
+        <v>4.517</v>
+      </c>
+      <c r="F200" s="9" t="n">
+        <v>226301.7</v>
+      </c>
+      <c r="G200" s="10">
+        <v>46163</v>
+      </c>
+      <c r="H200" s="8" t="n">
+        <v>22200</v>
+      </c>
+      <c r="I200" s="11" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="J200" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" ht="15" spans="1:5">
+      <c r="A201" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B201" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C201" s="13" t="n">
+        <v>452603.4</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E201" s="14" t="n">
+        <v>40950</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" ht="15" spans="1:1">
+      <c r="A202" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" ht="36.7" spans="1:10">
+      <c r="A203" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D203" s="8" t="n">
         <v>10200</v>
       </c>
-      <c r="E199" s="9" t="n">
+      <c r="E203" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F199" s="9" t="n">
+      <c r="F203" s="9" t="n">
         <v>25500</v>
       </c>
-      <c r="G199" s="10">
+      <c r="G203" s="10">
         <v>46176</v>
       </c>
-      <c r="H199" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I199" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J199" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="200" customHeight="1" ht="15" spans="1:5">
-      <c r="A200" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B200" s="12" t="s">
+      <c r="H203" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I203" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" ht="15" spans="1:5">
+      <c r="A204" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B204" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C200" s="13" t="n">
+      <c r="C204" s="13" t="n">
         <v>25500</v>
       </c>
-      <c r="D200" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E200" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A201" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" customHeight="1" ht="15" spans="1:12">
-      <c r="A202" s="2" t="s">
+      <c r="D204" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E204" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" ht="15" spans="1:1">
+      <c r="A205" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" ht="28.05" spans="1:10">
+      <c r="A206" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D206" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="E206" s="9" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="F206" s="9" t="n">
+        <v>849</v>
+      </c>
+      <c r="G206" s="10">
+        <v>46216.7521180556</v>
+      </c>
+      <c r="H206" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I206" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" ht="15" spans="1:5">
+      <c r="A207" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B207" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C207" s="13" t="n">
+        <v>849</v>
+      </c>
+      <c r="D207" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E207" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A208" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" ht="15" spans="1:12">
+      <c r="A209" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B202" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C202" s="2" t="s">
+      <c r="B209" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C209" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D202" s="2" t="s">
+      <c r="D209" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E202" s="4" t="s">
+      <c r="E209" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F202" s="4" t="s">
+      <c r="F209" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G202" s="4" t="s">
+      <c r="G209" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H202" s="4" t="s">
+      <c r="H209" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I202" s="4" t="s">
+      <c r="I209" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J202" s="4" t="s">
+      <c r="J209" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K202" s="2" t="s">
+      <c r="K209" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L202" s="4" t="s">
+      <c r="L209" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="203" customHeight="1" ht="15" spans="1:1">
-      <c r="A203" s="2" t="s">
+    <row r="210" customHeight="1" ht="15" spans="1:1">
+      <c r="A210" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="204" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A204" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B204" s="6" t="s">
+    <row r="211" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A211" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B211" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C204" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D204" s="8" t="n">
+      <c r="C211" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D211" s="8" t="n">
         <v>3408</v>
       </c>
-      <c r="E204" s="9" t="n">
+      <c r="E211" s="9" t="n">
         <v>44.9</v>
       </c>
-      <c r="F204" s="9" t="n">
+      <c r="F211" s="9" t="n">
         <v>153019.2</v>
       </c>
-      <c r="G204" s="10">
+      <c r="G211" s="10">
         <v>46162</v>
       </c>
-      <c r="H204" s="8" t="n">
+      <c r="H211" s="8" t="n">
         <v>1104</v>
       </c>
-      <c r="I204" s="11" t="n">
+      <c r="I211" s="11" t="n">
         <v>32.39</v>
       </c>
-      <c r="J204" s="8" t="s">
+      <c r="J211" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="205" customHeight="1" ht="15" spans="1:5">
-      <c r="A205" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B205" s="12" t="s">
+    <row r="212" customHeight="1" ht="15" spans="1:5">
+      <c r="A212" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B212" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C205" s="13" t="n">
+      <c r="C212" s="13" t="n">
         <v>153019.2</v>
       </c>
-      <c r="D205" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E205" s="14" t="n">
+      <c r="D212" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E212" s="14" t="n">
         <v>1104</v>
       </c>
     </row>
-    <row r="206" customHeight="1" ht="15" spans="1:1">
-      <c r="A206" s="2" t="s">
+    <row r="213" customHeight="1" ht="15" spans="1:1">
+      <c r="A213" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="207" customHeight="1" ht="18.35" spans="1:10">
-      <c r="A207" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B207" s="6" t="s">
+    <row r="214" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A214" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B214" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C207" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D207" s="8" t="n">
+      <c r="C214" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D214" s="8" t="n">
         <v>1008</v>
       </c>
-      <c r="E207" s="9" t="n">
+      <c r="E214" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="F207" s="9" t="n">
+      <c r="F214" s="9" t="n">
         <v>44352</v>
       </c>
-      <c r="G207" s="10">
+      <c r="G214" s="10">
         <v>46188</v>
       </c>
-      <c r="H207" s="8" t="n">
+      <c r="H214" s="8" t="n">
         <v>360</v>
       </c>
-      <c r="I207" s="11" t="n">
+      <c r="I214" s="11" t="n">
         <v>35.71</v>
       </c>
-      <c r="J207" s="8" t="s">
+      <c r="J214" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="208" customHeight="1" ht="15" spans="1:5">
-      <c r="A208" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B208" s="12" t="s">
+    <row r="215" customHeight="1" ht="15" spans="1:5">
+      <c r="A215" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B215" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C208" s="13" t="n">
+      <c r="C215" s="13" t="n">
         <v>44352</v>
       </c>
-      <c r="D208" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E208" s="14" t="n">
+      <c r="D215" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E215" s="14" t="n">
         <v>360</v>
       </c>
     </row>
-    <row r="209" customHeight="1" ht="15" spans="1:1">
-      <c r="A209" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="210" customHeight="1" ht="18.8" spans="1:10">
-      <c r="A210" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B210" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C210" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D210" s="8" t="n">
-        <v>804</v>
-      </c>
-      <c r="E210" s="9" t="n">
-        <v>34.65</v>
-      </c>
-      <c r="F210" s="9" t="n">
-        <v>27858.6</v>
-      </c>
-      <c r="G210" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H210" s="8" t="n">
-        <v>600</v>
-      </c>
-      <c r="I210" s="11" t="n">
-        <v>74.63</v>
-      </c>
-      <c r="J210" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="211" customHeight="1" ht="15" spans="1:5">
-      <c r="A211" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B211" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C211" s="13" t="n">
-        <v>27858.6</v>
-      </c>
-      <c r="D211" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E211" s="14" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="212" customHeight="1" ht="15" spans="1:1">
-      <c r="A212" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="213" customHeight="1" ht="29" spans="1:10">
-      <c r="A213" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B213" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C213" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D213" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="E213" s="9" t="n">
-        <v>53.46</v>
-      </c>
-      <c r="F213" s="9" t="n">
-        <v>1283.04</v>
-      </c>
-      <c r="G213" s="10">
-        <v>46209</v>
-      </c>
-      <c r="H213" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I213" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J213" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="214" customHeight="1" ht="15" spans="1:5">
-      <c r="A214" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B214" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C214" s="13" t="n">
-        <v>1283.04</v>
-      </c>
-      <c r="D214" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E214" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A215" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" customHeight="1" ht="15" spans="1:12">
+    <row r="216" customHeight="1" ht="15" spans="1:1">
       <c r="A216" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B216" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E216" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F216" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G216" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H216" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I216" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J216" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K216" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L216" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="217" customHeight="1" ht="15" spans="1:1">
-      <c r="A217" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="218" customHeight="1" ht="30.35" spans="1:10">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A217" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C217" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D217" s="8" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E217" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="F217" s="9" t="n">
+        <v>42336</v>
+      </c>
+      <c r="G217" s="10">
+        <v>46199</v>
+      </c>
+      <c r="H217" s="8" t="n">
+        <v>960</v>
+      </c>
+      <c r="I217" s="11" t="n">
+        <v>95.24</v>
+      </c>
+      <c r="J217" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" ht="27.45" spans="1:10">
       <c r="A218" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C218" s="7" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D218" s="8" t="n">
-        <v>504</v>
+        <v>1608</v>
       </c>
       <c r="E218" s="9" t="n">
-        <v>40.5</v>
+        <v>42</v>
       </c>
       <c r="F218" s="9" t="n">
-        <v>20412</v>
+        <v>67536</v>
       </c>
       <c r="G218" s="10">
-        <v>46189</v>
+        <v>46216.3893171296</v>
       </c>
       <c r="H218" s="8" t="n">
         <v>0</v>
@@ -5801,50 +5905,50 @@
         <v>20</v>
       </c>
       <c r="C219" s="13" t="n">
-        <v>20412</v>
+        <v>109872</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E219" s="14" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
     </row>
     <row r="220" customHeight="1" ht="15" spans="1:1">
       <c r="A220" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="221" customHeight="1" ht="20.4" spans="1:10">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" ht="21.6" spans="1:10">
       <c r="A221" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D221" s="8" t="n">
-        <v>408</v>
+        <v>804</v>
       </c>
       <c r="E221" s="9" t="n">
-        <v>44.498</v>
+        <v>34.65</v>
       </c>
       <c r="F221" s="9" t="n">
-        <v>18155.184</v>
+        <v>27858.6</v>
       </c>
       <c r="G221" s="10">
-        <v>46210.3934606481</v>
+        <v>46198</v>
       </c>
       <c r="H221" s="8" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I221" s="11" t="n">
-        <v>0</v>
+        <v>74.63</v>
       </c>
       <c r="J221" s="8" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
     </row>
     <row r="222" customHeight="1" ht="15" spans="1:5">
@@ -5855,138 +5959,138 @@
         <v>20</v>
       </c>
       <c r="C222" s="13" t="n">
-        <v>18155.184</v>
+        <v>27858.6</v>
       </c>
       <c r="D222" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E222" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" customHeight="1" ht="15" spans="1:1">
-      <c r="A223" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="224" customHeight="1" ht="28.4" spans="1:10">
-      <c r="A224" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B224" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C224" s="7" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A223" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" customHeight="1" ht="15" spans="1:12">
+      <c r="A224" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B224" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D224" s="8" t="n">
+      <c r="C224" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E224" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F224" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G224" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H224" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I224" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J224" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K224" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L224" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="225" customHeight="1" ht="15" spans="1:1">
+      <c r="A225" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="226" customHeight="1" ht="30.35" spans="1:10">
+      <c r="A226" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C226" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D226" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="E224" s="9" t="n">
+      <c r="E226" s="9" t="n">
         <v>53.46</v>
       </c>
-      <c r="F224" s="9" t="n">
+      <c r="F226" s="9" t="n">
         <v>1283.04</v>
       </c>
-      <c r="G224" s="10">
+      <c r="G226" s="10">
         <v>46209</v>
       </c>
-      <c r="H224" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I224" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J224" s="8" t="s">
+      <c r="H226" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I226" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="225" customHeight="1" ht="15" spans="1:5">
-      <c r="A225" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B225" s="12" t="s">
+    <row r="227" customHeight="1" ht="15" spans="1:5">
+      <c r="A227" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B227" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C225" s="13" t="n">
+      <c r="C227" s="13" t="n">
         <v>1283.04</v>
       </c>
-      <c r="D225" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E225" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A226" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" customHeight="1" ht="15" spans="1:12">
-      <c r="A227" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E227" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F227" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G227" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H227" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I227" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J227" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K227" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L227" s="4" t="s">
-        <v>12</v>
+      <c r="D227" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E227" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="228" customHeight="1" ht="15" spans="1:1">
       <c r="A228" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="229" customHeight="1" ht="37.05" spans="1:10">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" ht="27.95" spans="1:10">
       <c r="A229" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D229" s="8" t="n">
-        <v>10000</v>
+        <v>504</v>
       </c>
       <c r="E229" s="9" t="n">
-        <v>0.41</v>
+        <v>40.5</v>
       </c>
       <c r="F229" s="9" t="n">
-        <v>4100</v>
+        <v>20412</v>
       </c>
       <c r="G229" s="10">
-        <v>46212</v>
+        <v>46189</v>
       </c>
       <c r="H229" s="8" t="n">
         <v>0</v>
@@ -5995,7 +6099,7 @@
         <v>0</v>
       </c>
       <c r="J229" s="8" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="230" customHeight="1" ht="15" spans="1:5">
@@ -6006,7 +6110,7 @@
         <v>20</v>
       </c>
       <c r="C230" s="13" t="n">
-        <v>4100</v>
+        <v>20412</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>19</v>
@@ -6015,183 +6119,183 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A231" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" customHeight="1" ht="15" spans="1:12">
-      <c r="A232" s="2" t="s">
+    <row r="231" customHeight="1" ht="15" spans="1:1">
+      <c r="A231" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" ht="20.6" spans="1:10">
+      <c r="A232" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C232" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D232" s="8" t="n">
+        <v>408</v>
+      </c>
+      <c r="E232" s="9" t="n">
+        <v>44.498</v>
+      </c>
+      <c r="F232" s="9" t="n">
+        <v>18155.184</v>
+      </c>
+      <c r="G232" s="10">
+        <v>46210.3934606481</v>
+      </c>
+      <c r="H232" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I232" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" ht="15" spans="1:5">
+      <c r="A233" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B233" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C233" s="13" t="n">
+        <v>18155.184</v>
+      </c>
+      <c r="D233" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E233" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" ht="15" spans="1:1">
+      <c r="A234" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" ht="30.45" spans="1:10">
+      <c r="A235" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C235" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D235" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E235" s="9" t="n">
+        <v>53.46</v>
+      </c>
+      <c r="F235" s="9" t="n">
+        <v>1283.04</v>
+      </c>
+      <c r="G235" s="10">
+        <v>46209</v>
+      </c>
+      <c r="H235" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I235" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="236" customHeight="1" ht="15" spans="1:5">
+      <c r="A236" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B236" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C236" s="13" t="n">
+        <v>1283.04</v>
+      </c>
+      <c r="D236" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E236" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A237" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" customHeight="1" ht="15" spans="1:12">
+      <c r="A238" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B232" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C232" s="2" t="s">
+      <c r="B238" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C238" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D232" s="2" t="s">
+      <c r="D238" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E232" s="4" t="s">
+      <c r="E238" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F232" s="4" t="s">
+      <c r="F238" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G232" s="4" t="s">
+      <c r="G238" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H232" s="4" t="s">
+      <c r="H238" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I232" s="4" t="s">
+      <c r="I238" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J232" s="4" t="s">
+      <c r="J238" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K232" s="2" t="s">
+      <c r="K238" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L232" s="4" t="s">
+      <c r="L238" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="233" customHeight="1" ht="15" spans="1:1">
-      <c r="A233" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="234" customHeight="1" ht="15" spans="1:10">
-      <c r="A234" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B234" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C234" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="D234" s="8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E234" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="F234" s="9" t="n">
-        <v>4700</v>
-      </c>
-      <c r="G234" s="10">
-        <v>46209</v>
-      </c>
-      <c r="H234" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I234" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J234" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="235" customHeight="1" ht="15" spans="1:5">
-      <c r="A235" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B235" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C235" s="13" t="n">
-        <v>4700</v>
-      </c>
-      <c r="D235" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E235" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" customHeight="1" ht="15" spans="1:1">
-      <c r="A236" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="237" customHeight="1" ht="15" spans="1:10">
-      <c r="A237" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B237" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C237" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="D237" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E237" s="9" t="n">
-        <v>0.4171</v>
-      </c>
-      <c r="F237" s="9" t="n">
-        <v>8342</v>
-      </c>
-      <c r="G237" s="10">
-        <v>46203.3600231481</v>
-      </c>
-      <c r="H237" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I237" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J237" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="238" customHeight="1" ht="15" spans="1:5">
-      <c r="A238" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B238" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C238" s="13" t="n">
-        <v>8342</v>
-      </c>
-      <c r="D238" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E238" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="239" customHeight="1" ht="15" spans="1:1">
       <c r="A239" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="240" customHeight="1" ht="15" spans="1:10">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="240" customHeight="1" ht="37.05" spans="1:10">
       <c r="A240" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D240" s="8" t="n">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="E240" s="9" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="F240" s="9" t="n">
-        <v>23400</v>
+        <v>4100</v>
       </c>
       <c r="G240" s="10">
-        <v>46199.4372916667</v>
+        <v>46212</v>
       </c>
       <c r="H240" s="8" t="n">
         <v>0</v>
@@ -6200,7 +6304,7 @@
         <v>0</v>
       </c>
       <c r="J240" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="241" customHeight="1" ht="15" spans="1:5">
@@ -6211,7 +6315,7 @@
         <v>20</v>
       </c>
       <c r="C241" s="13" t="n">
-        <v>23400</v>
+        <v>4100</v>
       </c>
       <c r="D241" s="4" t="s">
         <v>19</v>
@@ -6220,366 +6324,345 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A242" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" customHeight="1" ht="15" spans="1:12">
-      <c r="A243" s="2" t="s">
+    <row r="242" customHeight="1" ht="15" spans="1:1">
+      <c r="A242" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="243" customHeight="1" ht="20" spans="1:10">
+      <c r="A243" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C243" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D243" s="8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E243" s="9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F243" s="9" t="n">
+        <v>19500</v>
+      </c>
+      <c r="G243" s="10">
+        <v>46212.6098726852</v>
+      </c>
+      <c r="H243" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="244" customHeight="1" ht="15" spans="1:5">
+      <c r="A244" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B244" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C244" s="13" t="n">
+        <v>19500</v>
+      </c>
+      <c r="D244" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E244" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" customHeight="1" ht="15" spans="1:1">
+      <c r="A245" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="246" customHeight="1" ht="20.85" spans="1:10">
+      <c r="A246" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C246" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D246" s="8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E246" s="9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F246" s="9" t="n">
+        <v>19500</v>
+      </c>
+      <c r="G246" s="10">
+        <v>46212.6038541667</v>
+      </c>
+      <c r="H246" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I246" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="247" customHeight="1" ht="15" spans="1:5">
+      <c r="A247" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B247" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C247" s="13" t="n">
+        <v>19500</v>
+      </c>
+      <c r="D247" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E247" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A248" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" customHeight="1" ht="15" spans="1:12">
+      <c r="A249" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B243" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C243" s="2" t="s">
+      <c r="B249" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C249" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D243" s="2" t="s">
+      <c r="D249" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E243" s="4" t="s">
+      <c r="E249" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F243" s="4" t="s">
+      <c r="F249" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G243" s="4" t="s">
+      <c r="G249" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H243" s="4" t="s">
+      <c r="H249" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I243" s="4" t="s">
+      <c r="I249" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J243" s="4" t="s">
+      <c r="J249" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K243" s="2" t="s">
+      <c r="K249" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L243" s="4" t="s">
+      <c r="L249" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="244" customHeight="1" ht="15" spans="1:1">
-      <c r="A244" s="2" t="s">
+    <row r="250" customHeight="1" ht="15" spans="1:1">
+      <c r="A250" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="245" customHeight="1" ht="15" spans="1:10">
-      <c r="A245" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B245" s="6" t="s">
+    <row r="251" customHeight="1" ht="15" spans="1:10">
+      <c r="A251" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B251" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C245" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D245" s="8" t="n">
+      <c r="C251" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D251" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E251" s="9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F251" s="9" t="n">
+        <v>4700</v>
+      </c>
+      <c r="G251" s="10">
+        <v>46209</v>
+      </c>
+      <c r="H251" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I251" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="252" customHeight="1" ht="15" spans="1:5">
+      <c r="A252" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B252" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C252" s="13" t="n">
+        <v>4700</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E252" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" customHeight="1" ht="15" spans="1:1">
+      <c r="A253" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="254" customHeight="1" ht="29.5" spans="1:10">
+      <c r="A254" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C254" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D254" s="8" t="n">
         <v>30000</v>
       </c>
-      <c r="E245" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="F245" s="9" t="n">
-        <v>14700</v>
-      </c>
-      <c r="G245" s="10">
-        <v>46209</v>
-      </c>
-      <c r="H245" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I245" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J245" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="246" customHeight="1" ht="15" spans="1:5">
-      <c r="A246" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B246" s="12" t="s">
+      <c r="E254" s="9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F254" s="9" t="n">
+        <v>12900</v>
+      </c>
+      <c r="G254" s="10">
+        <v>46217</v>
+      </c>
+      <c r="H254" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I254" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="255" customHeight="1" ht="15" spans="1:5">
+      <c r="A255" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B255" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C246" s="13" t="n">
-        <v>14700</v>
-      </c>
-      <c r="D246" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E246" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247" customHeight="1" ht="15" spans="1:1">
-      <c r="A247" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="248" customHeight="1" ht="15" spans="1:10">
-      <c r="A248" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B248" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C248" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D248" s="8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E248" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="F248" s="9" t="n">
-        <v>2850</v>
-      </c>
-      <c r="G248" s="10">
-        <v>46212</v>
-      </c>
-      <c r="H248" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I248" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J248" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="249" customHeight="1" ht="15" spans="1:10">
-      <c r="A249" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B249" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C249" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D249" s="8" t="n">
+      <c r="C255" s="13" t="n">
+        <v>12900</v>
+      </c>
+      <c r="D255" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E255" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" customHeight="1" ht="15" spans="1:1">
+      <c r="A256" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="257" customHeight="1" ht="15" spans="1:10">
+      <c r="A257" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C257" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D257" s="8" t="n">
         <v>20000</v>
       </c>
-      <c r="E249" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="F249" s="9" t="n">
-        <v>9800</v>
-      </c>
-      <c r="G249" s="10">
-        <v>46212</v>
-      </c>
-      <c r="H249" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I249" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J249" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="250" customHeight="1" ht="15" spans="1:5">
-      <c r="A250" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B250" s="12" t="s">
+      <c r="E257" s="9" t="n">
+        <v>0.4171</v>
+      </c>
+      <c r="F257" s="9" t="n">
+        <v>8342</v>
+      </c>
+      <c r="G257" s="10">
+        <v>46203.3600231481</v>
+      </c>
+      <c r="H257" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I257" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="258" customHeight="1" ht="15" spans="1:5">
+      <c r="A258" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B258" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C250" s="13" t="n">
-        <v>12650</v>
-      </c>
-      <c r="D250" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E250" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" customHeight="1" ht="15" spans="1:1">
-      <c r="A251" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="252" customHeight="1" ht="15" spans="1:10">
-      <c r="A252" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B252" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C252" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D252" s="8" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E252" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="F252" s="9" t="n">
-        <v>15750</v>
-      </c>
-      <c r="G252" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H252" s="8" t="n">
-        <v>32400</v>
-      </c>
-      <c r="I252" s="11" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="J252" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="253" customHeight="1" ht="15" spans="1:5">
-      <c r="A253" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B253" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C253" s="13" t="n">
-        <v>15750</v>
-      </c>
-      <c r="D253" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E253" s="14" t="n">
-        <v>32400</v>
-      </c>
-    </row>
-    <row r="254" customHeight="1" ht="15" spans="1:1">
-      <c r="A254" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="255" customHeight="1" ht="19.65" spans="1:10">
-      <c r="A255" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B255" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C255" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D255" s="8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E255" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="F255" s="9" t="n">
-        <v>2450</v>
-      </c>
-      <c r="G255" s="10">
-        <v>46209</v>
-      </c>
-      <c r="H255" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I255" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J255" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="256" customHeight="1" ht="15" spans="1:5">
-      <c r="A256" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B256" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C256" s="13" t="n">
-        <v>2450</v>
-      </c>
-      <c r="D256" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E256" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A257" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" customHeight="1" ht="15" spans="1:12">
-      <c r="A258" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B258" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E258" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F258" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G258" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H258" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I258" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J258" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K258" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L258" s="4" t="s">
-        <v>12</v>
+      <c r="C258" s="13" t="n">
+        <v>8342</v>
+      </c>
+      <c r="D258" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E258" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="259" customHeight="1" ht="15" spans="1:1">
       <c r="A259" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="260" customHeight="1" ht="20.4" spans="1:10">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="260" customHeight="1" ht="18.8" spans="1:10">
       <c r="A260" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="D260" s="8" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="E260" s="9" t="n">
-        <v>0.49</v>
+        <v>0.38</v>
       </c>
       <c r="F260" s="9" t="n">
-        <v>2450</v>
+        <v>7600</v>
       </c>
       <c r="G260" s="10">
-        <v>46209</v>
+        <v>46216.3151041667</v>
       </c>
       <c r="H260" s="8" t="n">
         <v>0</v>
@@ -6588,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="J260" s="8" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="261" customHeight="1" ht="15" spans="1:5">
@@ -6599,7 +6682,7 @@
         <v>20</v>
       </c>
       <c r="C261" s="13" t="n">
-        <v>2450</v>
+        <v>7600</v>
       </c>
       <c r="D261" s="4" t="s">
         <v>19</v>
@@ -6618,7 +6701,7 @@
         <v>1</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>3</v>
@@ -6653,30 +6736,30 @@
     </row>
     <row r="264" customHeight="1" ht="15" spans="1:1">
       <c r="A264" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="265" customHeight="1" ht="20.4" spans="1:10">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="265" customHeight="1" ht="15" spans="1:10">
       <c r="A265" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D265" s="8" t="n">
-        <v>20</v>
+        <v>60000</v>
       </c>
       <c r="E265" s="9" t="n">
-        <v>17.91</v>
+        <v>0.39</v>
       </c>
       <c r="F265" s="9" t="n">
-        <v>358.2</v>
+        <v>23400</v>
       </c>
       <c r="G265" s="10">
-        <v>46209</v>
+        <v>46199.4372916667</v>
       </c>
       <c r="H265" s="8" t="n">
         <v>0</v>
@@ -6685,7 +6768,7 @@
         <v>0</v>
       </c>
       <c r="J265" s="8" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="266" customHeight="1" ht="15" spans="1:5">
@@ -6696,7 +6779,7 @@
         <v>20</v>
       </c>
       <c r="C266" s="13" t="n">
-        <v>358.2</v>
+        <v>23400</v>
       </c>
       <c r="D266" s="4" t="s">
         <v>19</v>
@@ -6707,30 +6790,30 @@
     </row>
     <row r="267" customHeight="1" ht="15" spans="1:1">
       <c r="A267" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="268" customHeight="1" ht="15" spans="1:10">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="268" customHeight="1" ht="18.8" spans="1:10">
       <c r="A268" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>90</v>
+        <v>153</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="D268" s="8" t="n">
-        <v>120</v>
+        <v>40000</v>
       </c>
       <c r="E268" s="9" t="n">
-        <v>18.29</v>
+        <v>0.4</v>
       </c>
       <c r="F268" s="9" t="n">
-        <v>2194.8</v>
+        <v>16000</v>
       </c>
       <c r="G268" s="10">
-        <v>46196.6411111111</v>
+        <v>46212.6098726852</v>
       </c>
       <c r="H268" s="8" t="n">
         <v>0</v>
@@ -6739,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="J268" s="8" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
     </row>
     <row r="269" customHeight="1" ht="15" spans="1:5">
@@ -6750,7 +6833,7 @@
         <v>20</v>
       </c>
       <c r="C269" s="13" t="n">
-        <v>2194.8</v>
+        <v>16000</v>
       </c>
       <c r="D269" s="4" t="s">
         <v>19</v>
@@ -6761,30 +6844,30 @@
     </row>
     <row r="270" customHeight="1" ht="15" spans="1:1">
       <c r="A270" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="271" customHeight="1" ht="19.3" spans="1:10">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="271" customHeight="1" ht="19.55" spans="1:10">
       <c r="A271" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="D271" s="8" t="n">
-        <v>20</v>
+        <v>80000</v>
       </c>
       <c r="E271" s="9" t="n">
-        <v>17.91</v>
+        <v>0.4</v>
       </c>
       <c r="F271" s="9" t="n">
-        <v>358.2</v>
+        <v>32000</v>
       </c>
       <c r="G271" s="10">
-        <v>46209</v>
+        <v>46212.6038541667</v>
       </c>
       <c r="H271" s="8" t="n">
         <v>0</v>
@@ -6793,7 +6876,7 @@
         <v>0</v>
       </c>
       <c r="J271" s="8" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="272" customHeight="1" ht="15" spans="1:5">
@@ -6804,7 +6887,7 @@
         <v>20</v>
       </c>
       <c r="C272" s="13" t="n">
-        <v>358.2</v>
+        <v>32000</v>
       </c>
       <c r="D272" s="4" t="s">
         <v>19</v>
@@ -6823,7 +6906,7 @@
         <v>1</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>3</v>
@@ -6858,7 +6941,7 @@
     </row>
     <row r="275" customHeight="1" ht="15" spans="1:1">
       <c r="A275" s="2" t="s">
-        <v>152</v>
+        <v>47</v>
       </c>
     </row>
     <row r="276" customHeight="1" ht="15" spans="1:10">
@@ -6866,22 +6949,22 @@
         <v>14</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>153</v>
+        <v>48</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="D276" s="8" t="n">
-        <v>8028</v>
+        <v>30000</v>
       </c>
       <c r="E276" s="9" t="n">
-        <v>11.99</v>
+        <v>0.49</v>
       </c>
       <c r="F276" s="9" t="n">
-        <v>96255.72</v>
+        <v>14700</v>
       </c>
       <c r="G276" s="10">
-        <v>46167</v>
+        <v>46209</v>
       </c>
       <c r="H276" s="8" t="n">
         <v>0</v>
@@ -6890,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="J276" s="8" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="277" customHeight="1" ht="15" spans="1:5">
@@ -6901,7 +6984,7 @@
         <v>20</v>
       </c>
       <c r="C277" s="13" t="n">
-        <v>96255.72</v>
+        <v>14700</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>19</v>
@@ -6915,7 +6998,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="279" customHeight="1" ht="15" spans="1:10">
+    <row r="279" customHeight="1" ht="18.8" spans="1:10">
       <c r="A279" s="5" t="s">
         <v>14</v>
       </c>
@@ -6923,16 +7006,16 @@
         <v>67</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D279" s="8" t="n">
-        <v>90</v>
+        <v>5000</v>
       </c>
       <c r="E279" s="9" t="n">
-        <v>116.04</v>
+        <v>0.57</v>
       </c>
       <c r="F279" s="9" t="n">
-        <v>10443.6</v>
+        <v>2850</v>
       </c>
       <c r="G279" s="10">
         <v>46212</v>
@@ -6947,727 +7030,748 @@
         <v>49</v>
       </c>
     </row>
-    <row r="280" customHeight="1" ht="15" spans="1:5">
-      <c r="A280" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B280" s="12" t="s">
+    <row r="280" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A280" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C280" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D280" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E280" s="9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F280" s="9" t="n">
+        <v>9800</v>
+      </c>
+      <c r="G280" s="10">
+        <v>46212</v>
+      </c>
+      <c r="H280" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="281" customHeight="1" ht="15" spans="1:5">
+      <c r="A281" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B281" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C280" s="13" t="n">
-        <v>10443.6</v>
-      </c>
-      <c r="D280" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E280" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281" customHeight="1" ht="15" spans="1:1">
-      <c r="A281" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="282" customHeight="1" ht="39.95" spans="1:10">
-      <c r="A282" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B282" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C282" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D282" s="8" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E282" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="F282" s="9" t="n">
-        <v>312000</v>
-      </c>
-      <c r="G282" s="10">
-        <v>46100</v>
-      </c>
-      <c r="H282" s="8" t="n">
-        <v>18900</v>
-      </c>
-      <c r="I282" s="11" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="J282" s="8" t="s">
+      <c r="C281" s="13" t="n">
+        <v>12650</v>
+      </c>
+      <c r="D281" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E281" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" customHeight="1" ht="15" spans="1:1">
+      <c r="A282" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="283" customHeight="1" ht="21.35" spans="1:10">
+      <c r="A283" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C283" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D283" s="8" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E283" s="9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F283" s="9" t="n">
+        <v>9680</v>
+      </c>
+      <c r="G283" s="10">
+        <v>46216.3151041667</v>
+      </c>
+      <c r="H283" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I283" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="284" customHeight="1" ht="15" spans="1:5">
+      <c r="A284" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B284" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C284" s="13" t="n">
+        <v>9680</v>
+      </c>
+      <c r="D284" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E284" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" customHeight="1" ht="15" spans="1:1">
+      <c r="A285" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="286" customHeight="1" ht="15" spans="1:10">
+      <c r="A286" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C286" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D286" s="8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E286" s="9" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="F286" s="9" t="n">
+        <v>15750</v>
+      </c>
+      <c r="G286" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H286" s="8" t="n">
+        <v>32400</v>
+      </c>
+      <c r="I286" s="11" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="J286" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="287" customHeight="1" ht="15" spans="1:5">
+      <c r="A287" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B287" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C287" s="13" t="n">
+        <v>15750</v>
+      </c>
+      <c r="D287" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E287" s="14" t="n">
+        <v>32400</v>
+      </c>
+    </row>
+    <row r="288" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A288" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" customHeight="1" ht="15" spans="1:12">
+      <c r="A289" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B289" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E289" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F289" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G289" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H289" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I289" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J289" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K289" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L289" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="290" customHeight="1" ht="15" spans="1:1">
+      <c r="A290" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="291" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A291" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C291" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D291" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E291" s="9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F291" s="9" t="n">
+        <v>2450</v>
+      </c>
+      <c r="G291" s="10">
+        <v>46209</v>
+      </c>
+      <c r="H291" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I291" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="292" customHeight="1" ht="15" spans="1:5">
+      <c r="A292" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B292" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C292" s="13" t="n">
+        <v>2450</v>
+      </c>
+      <c r="D292" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E292" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" customHeight="1" ht="15" spans="1:1">
+      <c r="A293" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="294" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A294" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C294" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D294" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E294" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F294" s="9" t="n">
+        <v>8400</v>
+      </c>
+      <c r="G294" s="10">
+        <v>46216.7721759259</v>
+      </c>
+      <c r="H294" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I294" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="295" customHeight="1" ht="15" spans="1:5">
+      <c r="A295" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B295" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C295" s="13" t="n">
+        <v>8400</v>
+      </c>
+      <c r="D295" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E295" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" customHeight="1" ht="15" spans="1:1">
+      <c r="A296" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="297" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A297" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C297" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D297" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E297" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F297" s="9" t="n">
+        <v>8400</v>
+      </c>
+      <c r="G297" s="10">
+        <v>46212.6098726852</v>
+      </c>
+      <c r="H297" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I297" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="283" customHeight="1" ht="15" spans="1:5">
-      <c r="A283" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B283" s="12" t="s">
+    <row r="298" customHeight="1" ht="15" spans="1:5">
+      <c r="A298" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B298" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C283" s="13" t="n">
-        <v>312000</v>
-      </c>
-      <c r="D283" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E283" s="14" t="n">
-        <v>18900</v>
-      </c>
-    </row>
-    <row r="284" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A284" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" customHeight="1" ht="15" spans="1:12">
-      <c r="A285" s="2" t="s">
+      <c r="C298" s="13" t="n">
+        <v>8400</v>
+      </c>
+      <c r="D298" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E298" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" customHeight="1" ht="15" spans="1:1">
+      <c r="A299" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="300" customHeight="1" ht="20.15" spans="1:10">
+      <c r="A300" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C300" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D300" s="8" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E300" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F300" s="9" t="n">
+        <v>33600</v>
+      </c>
+      <c r="G300" s="10">
+        <v>46212.6038541667</v>
+      </c>
+      <c r="H300" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I300" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="301" customHeight="1" ht="15" spans="1:5">
+      <c r="A301" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B301" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C301" s="13" t="n">
+        <v>33600</v>
+      </c>
+      <c r="D301" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E301" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A302" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" customHeight="1" ht="15" spans="1:12">
+      <c r="A303" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B285" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C285" s="2" t="s">
+      <c r="B303" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C303" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D285" s="2" t="s">
+      <c r="D303" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E285" s="4" t="s">
+      <c r="E303" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F285" s="4" t="s">
+      <c r="F303" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G285" s="4" t="s">
+      <c r="G303" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H285" s="4" t="s">
+      <c r="H303" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I285" s="4" t="s">
+      <c r="I303" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J285" s="4" t="s">
+      <c r="J303" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K285" s="2" t="s">
+      <c r="K303" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L285" s="4" t="s">
+      <c r="L303" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="286" customHeight="1" ht="15" spans="1:1">
-      <c r="A286" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="287" customHeight="1" ht="30.35" spans="1:10">
-      <c r="A287" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B287" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C287" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D287" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="E287" s="9" t="n">
-        <v>17.91</v>
-      </c>
-      <c r="F287" s="9" t="n">
-        <v>716.4</v>
-      </c>
-      <c r="G287" s="10">
+    <row r="304" customHeight="1" ht="15" spans="1:1">
+      <c r="A304" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="305" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A305" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C305" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D305" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E305" s="9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F305" s="9" t="n">
+        <v>2450</v>
+      </c>
+      <c r="G305" s="10">
         <v>46209</v>
       </c>
-      <c r="H287" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I287" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J287" s="8" t="s">
+      <c r="H305" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="288" customHeight="1" ht="15" spans="1:5">
-      <c r="A288" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B288" s="12" t="s">
+    <row r="306" customHeight="1" ht="15" spans="1:5">
+      <c r="A306" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B306" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C288" s="13" t="n">
-        <v>716.4</v>
-      </c>
-      <c r="D288" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E288" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289" customHeight="1" ht="15" spans="1:1">
-      <c r="A289" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="290" customHeight="1" ht="15" spans="1:10">
-      <c r="A290" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B290" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C290" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D290" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E290" s="9" t="n">
-        <v>7.3303</v>
-      </c>
-      <c r="F290" s="9" t="n">
-        <v>21990.9</v>
-      </c>
-      <c r="G290" s="10">
-        <v>46210.3934606481</v>
-      </c>
-      <c r="H290" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I290" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J290" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="291" customHeight="1" ht="15" spans="1:5">
-      <c r="A291" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B291" s="12" t="s">
+      <c r="C306" s="13" t="n">
+        <v>2450</v>
+      </c>
+      <c r="D306" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E306" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" customHeight="1" ht="15" spans="1:1">
+      <c r="A307" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="308" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A308" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C308" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D308" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E308" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F308" s="9" t="n">
+        <v>900</v>
+      </c>
+      <c r="G308" s="10">
+        <v>46216.7521180556</v>
+      </c>
+      <c r="H308" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="309" customHeight="1" ht="15" spans="1:5">
+      <c r="A309" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B309" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C291" s="13" t="n">
-        <v>21990.9</v>
-      </c>
-      <c r="D291" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E291" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292" customHeight="1" ht="15" spans="1:1">
-      <c r="A292" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="293" customHeight="1" ht="29.6" spans="1:10">
-      <c r="A293" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B293" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C293" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D293" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="E293" s="9" t="n">
-        <v>17.91</v>
-      </c>
-      <c r="F293" s="9" t="n">
-        <v>716.4</v>
-      </c>
-      <c r="G293" s="10">
-        <v>46209</v>
-      </c>
-      <c r="H293" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I293" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J293" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="294" customHeight="1" ht="15" spans="1:5">
-      <c r="A294" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B294" s="12" t="s">
+      <c r="C309" s="13" t="n">
+        <v>900</v>
+      </c>
+      <c r="D309" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E309" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A310" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" customHeight="1" ht="15" spans="1:12">
+      <c r="A311" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C311" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E311" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G311" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H311" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I311" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J311" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K311" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L311" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="312" customHeight="1" ht="15" spans="1:1">
+      <c r="A312" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="313" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A313" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C313" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D313" s="8" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E313" s="9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F313" s="9" t="n">
+        <v>13003.2</v>
+      </c>
+      <c r="G313" s="10">
+        <v>46216.3893171296</v>
+      </c>
+      <c r="H313" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I313" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J313" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="314" customHeight="1" ht="15" spans="1:5">
+      <c r="A314" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B314" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C294" s="13" t="n">
-        <v>716.4</v>
-      </c>
-      <c r="D294" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E294" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A295" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296" customHeight="1" ht="15" spans="1:12">
-      <c r="A296" s="2" t="s">
+      <c r="C314" s="13" t="n">
+        <v>13003.2</v>
+      </c>
+      <c r="D314" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E314" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A315" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" customHeight="1" ht="15" spans="1:12">
+      <c r="A316" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B296" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C296" s="2" t="s">
+      <c r="B316" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C316" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D296" s="2" t="s">
+      <c r="D316" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E296" s="4" t="s">
+      <c r="E316" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F296" s="4" t="s">
+      <c r="F316" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G296" s="4" t="s">
+      <c r="G316" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H296" s="4" t="s">
+      <c r="H316" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I296" s="4" t="s">
+      <c r="I316" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J296" s="4" t="s">
+      <c r="J316" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K296" s="2" t="s">
+      <c r="K316" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L296" s="4" t="s">
+      <c r="L316" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="297" customHeight="1" ht="15" spans="1:1">
-      <c r="A297" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="298" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A298" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B298" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C298" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D298" s="8" t="n">
-        <v>640</v>
-      </c>
-      <c r="E298" s="9" t="n">
-        <v>20.76</v>
-      </c>
-      <c r="F298" s="9" t="n">
-        <v>13286.4</v>
-      </c>
-      <c r="G298" s="10">
-        <v>46209</v>
-      </c>
-      <c r="H298" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I298" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J298" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="299" customHeight="1" ht="15" spans="1:5">
-      <c r="A299" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B299" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C299" s="13" t="n">
-        <v>13286.4</v>
-      </c>
-      <c r="D299" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E299" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" customHeight="1" ht="15" spans="1:1">
-      <c r="A300" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="301" customHeight="1" ht="15" spans="1:10">
-      <c r="A301" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B301" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C301" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D301" s="8" t="n">
-        <v>4032</v>
-      </c>
-      <c r="E301" s="9" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F301" s="9" t="n">
-        <v>28183.68</v>
-      </c>
-      <c r="G301" s="10">
-        <v>46167</v>
-      </c>
-      <c r="H301" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I301" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J301" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="302" customHeight="1" ht="15" spans="1:5">
-      <c r="A302" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B302" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C302" s="13" t="n">
-        <v>28183.68</v>
-      </c>
-      <c r="D302" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E302" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303" customHeight="1" ht="15" spans="1:1">
-      <c r="A303" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="304" customHeight="1" ht="19.3" spans="1:10">
-      <c r="A304" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B304" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C304" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D304" s="8" t="n">
-        <v>128</v>
-      </c>
-      <c r="E304" s="9" t="n">
-        <v>20.76</v>
-      </c>
-      <c r="F304" s="9" t="n">
-        <v>2657.28</v>
-      </c>
-      <c r="G304" s="10">
-        <v>46212</v>
-      </c>
-      <c r="H304" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I304" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J304" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="305" customHeight="1" ht="15" spans="1:5">
-      <c r="A305" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B305" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C305" s="13" t="n">
-        <v>2657.28</v>
-      </c>
-      <c r="D305" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E305" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A306" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307" customHeight="1" ht="15" spans="1:12">
-      <c r="A307" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B307" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C307" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D307" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E307" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F307" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G307" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H307" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I307" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J307" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K307" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L307" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="308" customHeight="1" ht="15" spans="1:1">
-      <c r="A308" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="309" customHeight="1" ht="15" spans="1:10">
-      <c r="A309" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B309" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C309" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D309" s="8" t="n">
-        <v>2016</v>
-      </c>
-      <c r="E309" s="9" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F309" s="9" t="n">
-        <v>14091.84</v>
-      </c>
-      <c r="G309" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H309" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I309" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J309" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="310" customHeight="1" ht="15" spans="1:5">
-      <c r="A310" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B310" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C310" s="13" t="n">
-        <v>14091.84</v>
-      </c>
-      <c r="D310" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E310" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" customHeight="1" ht="15" spans="1:1">
-      <c r="A311" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="312" customHeight="1" ht="15" spans="1:10">
-      <c r="A312" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B312" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C312" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D312" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E312" s="9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F312" s="9" t="n">
-        <v>28800</v>
-      </c>
-      <c r="G312" s="10">
-        <v>46210</v>
-      </c>
-      <c r="H312" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I312" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J312" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="313" customHeight="1" ht="15" spans="1:5">
-      <c r="A313" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B313" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C313" s="13" t="n">
-        <v>28800</v>
-      </c>
-      <c r="D313" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E313" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314" customHeight="1" ht="15" spans="1:1">
-      <c r="A314" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="315" customHeight="1" ht="15" spans="1:10">
-      <c r="A315" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B315" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C315" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D315" s="8" t="n">
-        <v>1224</v>
-      </c>
-      <c r="E315" s="9" t="n">
-        <v>4.893</v>
-      </c>
-      <c r="F315" s="9" t="n">
-        <v>5989.032</v>
-      </c>
-      <c r="G315" s="10">
-        <v>46198</v>
-      </c>
-      <c r="H315" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I315" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J315" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="316" customHeight="1" ht="15" spans="1:5">
-      <c r="A316" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B316" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C316" s="13" t="n">
-        <v>5989.032</v>
-      </c>
-      <c r="D316" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E316" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="317" customHeight="1" ht="15" spans="1:1">
       <c r="A317" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="318" customHeight="1" ht="36.6" spans="1:10">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="318" customHeight="1" ht="20.4" spans="1:10">
       <c r="A318" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B318" s="6" t="s">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="C318" s="7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D318" s="8" t="n">
-        <v>10008</v>
+        <v>20</v>
       </c>
       <c r="E318" s="9" t="n">
-        <v>6.6</v>
+        <v>17.91</v>
       </c>
       <c r="F318" s="9" t="n">
-        <v>66052.8</v>
+        <v>358.2</v>
       </c>
       <c r="G318" s="10">
-        <v>46198</v>
+        <v>46209</v>
       </c>
       <c r="H318" s="8" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="I318" s="11" t="n">
-        <v>30.22</v>
+        <v>0</v>
       </c>
       <c r="J318" s="8" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="319" customHeight="1" ht="15" spans="1:5">
@@ -7678,13 +7782,1200 @@
         <v>20</v>
       </c>
       <c r="C319" s="13" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="D319" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E319" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" customHeight="1" ht="15" spans="1:1">
+      <c r="A320" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="321" customHeight="1" ht="15" spans="1:10">
+      <c r="A321" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C321" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D321" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="E321" s="9" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="F321" s="9" t="n">
+        <v>2194.8</v>
+      </c>
+      <c r="G321" s="10">
+        <v>46196.6411111111</v>
+      </c>
+      <c r="H321" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I321" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="322" customHeight="1" ht="15" spans="1:5">
+      <c r="A322" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B322" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C322" s="13" t="n">
+        <v>2194.8</v>
+      </c>
+      <c r="D322" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E322" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" customHeight="1" ht="15" spans="1:1">
+      <c r="A323" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="324" customHeight="1" ht="19.3" spans="1:10">
+      <c r="A324" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B324" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C324" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D324" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E324" s="9" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="F324" s="9" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="G324" s="10">
+        <v>46209</v>
+      </c>
+      <c r="H324" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I324" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J324" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="325" customHeight="1" ht="15" spans="1:5">
+      <c r="A325" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B325" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C325" s="13" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="D325" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E325" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A326" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" customHeight="1" ht="15" spans="1:12">
+      <c r="A327" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B327" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E327" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F327" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G327" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H327" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I327" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J327" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K327" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L327" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="328" customHeight="1" ht="15" spans="1:1">
+      <c r="A328" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="329" customHeight="1" ht="15" spans="1:10">
+      <c r="A329" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B329" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C329" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D329" s="8" t="n">
+        <v>8028</v>
+      </c>
+      <c r="E329" s="9" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="F329" s="9" t="n">
+        <v>96255.72</v>
+      </c>
+      <c r="G329" s="10">
+        <v>46167</v>
+      </c>
+      <c r="H329" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I329" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J329" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="330" customHeight="1" ht="15" spans="1:5">
+      <c r="A330" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B330" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C330" s="13" t="n">
+        <v>96255.72</v>
+      </c>
+      <c r="D330" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E330" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" customHeight="1" ht="15" spans="1:1">
+      <c r="A331" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="332" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A332" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B332" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C332" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D332" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E332" s="9" t="n">
+        <v>116.04</v>
+      </c>
+      <c r="F332" s="9" t="n">
+        <v>10443.6</v>
+      </c>
+      <c r="G332" s="10">
+        <v>46212</v>
+      </c>
+      <c r="H332" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I332" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J332" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="333" customHeight="1" ht="15" spans="1:5">
+      <c r="A333" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B333" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C333" s="13" t="n">
+        <v>10443.6</v>
+      </c>
+      <c r="D333" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E333" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" customHeight="1" ht="15" spans="1:1">
+      <c r="A334" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="335" customHeight="1" ht="38.75" spans="1:10">
+      <c r="A335" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B335" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C335" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D335" s="8" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E335" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F335" s="9" t="n">
+        <v>312000</v>
+      </c>
+      <c r="G335" s="10">
+        <v>46100</v>
+      </c>
+      <c r="H335" s="8" t="n">
+        <v>18900</v>
+      </c>
+      <c r="I335" s="11" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="J335" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="336" customHeight="1" ht="15" spans="1:5">
+      <c r="A336" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B336" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C336" s="13" t="n">
+        <v>312000</v>
+      </c>
+      <c r="D336" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E336" s="14" t="n">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="337" customHeight="1" ht="15" spans="1:1">
+      <c r="A337" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="338" customHeight="1" ht="18.7" spans="1:10">
+      <c r="A338" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B338" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C338" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D338" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="E338" s="9" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="F338" s="9" t="n">
+        <v>9198</v>
+      </c>
+      <c r="G338" s="10">
+        <v>46213.4944444444</v>
+      </c>
+      <c r="H338" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I338" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J338" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="339" customHeight="1" ht="15" spans="1:5">
+      <c r="A339" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B339" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C339" s="13" t="n">
+        <v>9198</v>
+      </c>
+      <c r="D339" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E339" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A340" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" customHeight="1" ht="15" spans="1:12">
+      <c r="A341" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B341" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C341" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E341" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F341" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G341" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H341" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I341" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J341" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K341" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L341" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="342" customHeight="1" ht="15" spans="1:1">
+      <c r="A342" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="343" customHeight="1" ht="30.35" spans="1:10">
+      <c r="A343" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B343" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C343" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D343" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E343" s="9" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="F343" s="9" t="n">
+        <v>716.4</v>
+      </c>
+      <c r="G343" s="10">
+        <v>46209</v>
+      </c>
+      <c r="H343" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I343" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="344" customHeight="1" ht="15" spans="1:5">
+      <c r="A344" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B344" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C344" s="13" t="n">
+        <v>716.4</v>
+      </c>
+      <c r="D344" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E344" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" customHeight="1" ht="15" spans="1:1">
+      <c r="A345" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="346" customHeight="1" ht="15" spans="1:10">
+      <c r="A346" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B346" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C346" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D346" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E346" s="9" t="n">
+        <v>7.3303</v>
+      </c>
+      <c r="F346" s="9" t="n">
+        <v>21990.9</v>
+      </c>
+      <c r="G346" s="10">
+        <v>46210.3934606481</v>
+      </c>
+      <c r="H346" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I346" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J346" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="347" customHeight="1" ht="15" spans="1:5">
+      <c r="A347" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B347" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C347" s="13" t="n">
+        <v>21990.9</v>
+      </c>
+      <c r="D347" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E347" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" customHeight="1" ht="15" spans="1:1">
+      <c r="A348" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="349" customHeight="1" ht="29.6" spans="1:10">
+      <c r="A349" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B349" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C349" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D349" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E349" s="9" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="F349" s="9" t="n">
+        <v>716.4</v>
+      </c>
+      <c r="G349" s="10">
+        <v>46209</v>
+      </c>
+      <c r="H349" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I349" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="350" customHeight="1" ht="15" spans="1:5">
+      <c r="A350" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B350" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C350" s="13" t="n">
+        <v>716.4</v>
+      </c>
+      <c r="D350" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E350" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A351" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" customHeight="1" ht="15" spans="1:12">
+      <c r="A352" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B352" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E352" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F352" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G352" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H352" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I352" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J352" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K352" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L352" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="353" customHeight="1" ht="15" spans="1:1">
+      <c r="A353" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="354" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A354" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B354" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C354" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D354" s="8" t="n">
+        <v>640</v>
+      </c>
+      <c r="E354" s="9" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="F354" s="9" t="n">
+        <v>13286.4</v>
+      </c>
+      <c r="G354" s="10">
+        <v>46209</v>
+      </c>
+      <c r="H354" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I354" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J354" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="355" customHeight="1" ht="15" spans="1:5">
+      <c r="A355" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B355" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C355" s="13" t="n">
+        <v>13286.4</v>
+      </c>
+      <c r="D355" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E355" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" customHeight="1" ht="15" spans="1:1">
+      <c r="A356" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="357" customHeight="1" ht="15" spans="1:10">
+      <c r="A357" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B357" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C357" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D357" s="8" t="n">
+        <v>4032</v>
+      </c>
+      <c r="E357" s="9" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F357" s="9" t="n">
+        <v>28183.68</v>
+      </c>
+      <c r="G357" s="10">
+        <v>46167</v>
+      </c>
+      <c r="H357" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I357" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J357" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="358" customHeight="1" ht="15" spans="1:5">
+      <c r="A358" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B358" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C358" s="13" t="n">
+        <v>28183.68</v>
+      </c>
+      <c r="D358" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E358" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" customHeight="1" ht="15" spans="1:1">
+      <c r="A359" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="360" customHeight="1" ht="30.8" spans="1:10">
+      <c r="A360" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B360" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C360" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D360" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="E360" s="9" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="F360" s="9" t="n">
+        <v>2657.28</v>
+      </c>
+      <c r="G360" s="10">
+        <v>46212</v>
+      </c>
+      <c r="H360" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I360" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J360" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="361" customHeight="1" ht="15" spans="1:5">
+      <c r="A361" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B361" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C361" s="13" t="n">
+        <v>2657.28</v>
+      </c>
+      <c r="D361" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E361" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A362" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" customHeight="1" ht="15" spans="1:12">
+      <c r="A363" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B363" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E363" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F363" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G363" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H363" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I363" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J363" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K363" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L363" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="364" customHeight="1" ht="15" spans="1:1">
+      <c r="A364" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="365" customHeight="1" ht="15" spans="1:10">
+      <c r="A365" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B365" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C365" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D365" s="8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E365" s="9" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F365" s="9" t="n">
+        <v>14091.84</v>
+      </c>
+      <c r="G365" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H365" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I365" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J365" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="366" customHeight="1" ht="15" spans="1:5">
+      <c r="A366" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B366" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C366" s="13" t="n">
+        <v>14091.84</v>
+      </c>
+      <c r="D366" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E366" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" customHeight="1" ht="15" spans="1:1">
+      <c r="A367" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="368" customHeight="1" ht="15" spans="1:10">
+      <c r="A368" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B368" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C368" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D368" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E368" s="9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F368" s="9" t="n">
+        <v>28800</v>
+      </c>
+      <c r="G368" s="10">
+        <v>46210</v>
+      </c>
+      <c r="H368" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I368" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J368" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="369" customHeight="1" ht="15" spans="1:5">
+      <c r="A369" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B369" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C369" s="13" t="n">
+        <v>28800</v>
+      </c>
+      <c r="D369" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E369" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" customHeight="1" ht="15" spans="1:1">
+      <c r="A370" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="371" customHeight="1" ht="15" spans="1:10">
+      <c r="A371" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B371" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C371" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D371" s="8" t="n">
+        <v>1224</v>
+      </c>
+      <c r="E371" s="9" t="n">
+        <v>4.893</v>
+      </c>
+      <c r="F371" s="9" t="n">
+        <v>5989.032</v>
+      </c>
+      <c r="G371" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H371" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I371" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J371" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="372" customHeight="1" ht="15" spans="1:5">
+      <c r="A372" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B372" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C372" s="13" t="n">
+        <v>5989.032</v>
+      </c>
+      <c r="D372" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E372" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" customHeight="1" ht="15" spans="1:1">
+      <c r="A373" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="374" customHeight="1" ht="36.6" spans="1:10">
+      <c r="A374" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B374" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="C374" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D374" s="8" t="n">
+        <v>10008</v>
+      </c>
+      <c r="E374" s="9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F374" s="9" t="n">
         <v>66052.8</v>
       </c>
-      <c r="D319" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E319" s="14" t="n">
+      <c r="G374" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H374" s="8" t="n">
         <v>3024</v>
+      </c>
+      <c r="I374" s="11" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="J374" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="375" customHeight="1" ht="15" spans="1:5">
+      <c r="A375" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B375" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C375" s="13" t="n">
+        <v>66052.8</v>
+      </c>
+      <c r="D375" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E375" s="14" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="376" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A376" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" customHeight="1" ht="15" spans="1:12">
+      <c r="A377" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B377" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D377" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E377" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F377" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G377" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H377" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I377" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J377" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K377" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L377" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="378" customHeight="1" ht="15" spans="1:1">
+      <c r="A378" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="379" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A379" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B379" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C379" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D379" s="8" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E379" s="9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F379" s="9" t="n">
+        <v>6854.4</v>
+      </c>
+      <c r="G379" s="10">
+        <v>46212.7064583333</v>
+      </c>
+      <c r="H379" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I379" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J379" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="380" customHeight="1" ht="15" spans="1:5">
+      <c r="A380" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B380" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C380" s="13" t="n">
+        <v>6854.4</v>
+      </c>
+      <c r="D380" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E380" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" customHeight="1" ht="15" spans="1:1">
+      <c r="A381" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="382" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A382" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B382" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C382" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D382" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E382" s="9" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="F382" s="9" t="n">
+        <v>613.2</v>
+      </c>
+      <c r="G382" s="10">
+        <v>46216.7521180556</v>
+      </c>
+      <c r="H382" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I382" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J382" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="383" customHeight="1" ht="15" spans="1:5">
+      <c r="A383" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B383" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C383" s="13" t="n">
+        <v>613.2</v>
+      </c>
+      <c r="D383" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E383" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="210">
   <si>
     <t>MATRIZ CNPJ: 40.357.820/0001-50R Y DOIS - 58082-025
  ACOMPANHAMENTO DE CONTRATOS PENDENTES</t>
@@ -507,6 +507,12 @@
     <t>02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND  Observação: 2% - 37/44/58</t>
   </si>
   <si>
+    <t>ENDOMED COMERCIO E REPRES DE MEDIC LTDA</t>
+  </si>
+  <si>
+    <t>1048</t>
+  </si>
+  <si>
     <t>02 - GAZE ESTÉRIL 11FIOS - PCT 10 UND  Observação: 2%</t>
   </si>
   <si>
@@ -532,6 +538,12 @@
   </si>
   <si>
     <t>03 - GAZE ESTÉRIL 13FIOS - PCT 10 UND  Observação: 2%</t>
+  </si>
+  <si>
+    <t>SABRINA MARTHA RAMALHO MENDES COM. DE ART. MED. LTDA</t>
+  </si>
+  <si>
+    <t>1049</t>
   </si>
   <si>
     <t>GAZE EM ROLO - 09 FIOS</t>
@@ -800,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L383"/>
+  <dimension ref="A1:L389"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
   <cols>
     <col customWidth="1" width="89.23828125" min="1" max="1"/>
@@ -6736,7 +6748,7 @@
     </row>
     <row r="264" customHeight="1" ht="15" spans="1:1">
       <c r="A264" s="2" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
     </row>
     <row r="265" customHeight="1" ht="15" spans="1:10">
@@ -6744,22 +6756,22 @@
         <v>14</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="C265" s="7" t="s">
         <v>157</v>
       </c>
       <c r="D265" s="8" t="n">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="E265" s="9" t="n">
         <v>0.39</v>
       </c>
       <c r="F265" s="9" t="n">
-        <v>23400</v>
+        <v>3900</v>
       </c>
       <c r="G265" s="10">
-        <v>46199.4372916667</v>
+        <v>46217.4264583333</v>
       </c>
       <c r="H265" s="8" t="n">
         <v>0</v>
@@ -6779,7 +6791,7 @@
         <v>20</v>
       </c>
       <c r="C266" s="13" t="n">
-        <v>23400</v>
+        <v>3900</v>
       </c>
       <c r="D266" s="4" t="s">
         <v>19</v>
@@ -6790,30 +6802,30 @@
     </row>
     <row r="267" customHeight="1" ht="15" spans="1:1">
       <c r="A267" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="268" customHeight="1" ht="18.8" spans="1:10">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="268" customHeight="1" ht="15" spans="1:10">
       <c r="A268" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D268" s="8" t="n">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="E268" s="9" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F268" s="9" t="n">
-        <v>16000</v>
+        <v>23400</v>
       </c>
       <c r="G268" s="10">
-        <v>46212.6098726852</v>
+        <v>46199.4372916667</v>
       </c>
       <c r="H268" s="8" t="n">
         <v>0</v>
@@ -6833,7 +6845,7 @@
         <v>20</v>
       </c>
       <c r="C269" s="13" t="n">
-        <v>16000</v>
+        <v>23400</v>
       </c>
       <c r="D269" s="4" t="s">
         <v>19</v>
@@ -6844,30 +6856,30 @@
     </row>
     <row r="270" customHeight="1" ht="15" spans="1:1">
       <c r="A270" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="271" customHeight="1" ht="19.55" spans="1:10">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="271" customHeight="1" ht="20.15" spans="1:10">
       <c r="A271" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D271" s="8" t="n">
-        <v>80000</v>
+        <v>40000</v>
       </c>
       <c r="E271" s="9" t="n">
         <v>0.4</v>
       </c>
       <c r="F271" s="9" t="n">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="G271" s="10">
-        <v>46212.6038541667</v>
+        <v>46212.6098726852</v>
       </c>
       <c r="H271" s="8" t="n">
         <v>0</v>
@@ -6887,138 +6899,138 @@
         <v>20</v>
       </c>
       <c r="C272" s="13" t="n">
+        <v>16000</v>
+      </c>
+      <c r="D272" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E272" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" customHeight="1" ht="15" spans="1:1">
+      <c r="A273" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="274" customHeight="1" ht="19.9" spans="1:10">
+      <c r="A274" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C274" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D274" s="8" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E274" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F274" s="9" t="n">
         <v>32000</v>
       </c>
-      <c r="D272" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E272" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A273" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274" customHeight="1" ht="15" spans="1:12">
-      <c r="A274" s="2" t="s">
+      <c r="G274" s="10">
+        <v>46212.6038541667</v>
+      </c>
+      <c r="H274" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I274" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="275" customHeight="1" ht="15" spans="1:5">
+      <c r="A275" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B275" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C275" s="13" t="n">
+        <v>32000</v>
+      </c>
+      <c r="D275" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E275" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A276" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" customHeight="1" ht="15" spans="1:12">
+      <c r="A277" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B274" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C274" s="2" t="s">
+      <c r="B277" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C277" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D274" s="2" t="s">
+      <c r="D277" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E274" s="4" t="s">
+      <c r="E277" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F274" s="4" t="s">
+      <c r="F277" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G274" s="4" t="s">
+      <c r="G277" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H274" s="4" t="s">
+      <c r="H277" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I274" s="4" t="s">
+      <c r="I277" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J274" s="4" t="s">
+      <c r="J277" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K274" s="2" t="s">
+      <c r="K277" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L274" s="4" t="s">
+      <c r="L277" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="275" customHeight="1" ht="15" spans="1:1">
-      <c r="A275" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="276" customHeight="1" ht="15" spans="1:10">
-      <c r="A276" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B276" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C276" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="D276" s="8" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E276" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="F276" s="9" t="n">
-        <v>14700</v>
-      </c>
-      <c r="G276" s="10">
-        <v>46209</v>
-      </c>
-      <c r="H276" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I276" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J276" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="277" customHeight="1" ht="15" spans="1:5">
-      <c r="A277" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B277" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C277" s="13" t="n">
-        <v>14700</v>
-      </c>
-      <c r="D277" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E277" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="278" customHeight="1" ht="15" spans="1:1">
       <c r="A278" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="279" customHeight="1" ht="18.8" spans="1:10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="279" customHeight="1" ht="15" spans="1:10">
       <c r="A279" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D279" s="8" t="n">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="E279" s="9" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="F279" s="9" t="n">
-        <v>2850</v>
+        <v>14700</v>
       </c>
       <c r="G279" s="10">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="H279" s="8" t="n">
         <v>0</v>
@@ -7030,90 +7042,90 @@
         <v>49</v>
       </c>
     </row>
-    <row r="280" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A280" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B280" s="6" t="s">
+    <row r="280" customHeight="1" ht="15" spans="1:5">
+      <c r="A280" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B280" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C280" s="13" t="n">
+        <v>14700</v>
+      </c>
+      <c r="D280" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E280" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" customHeight="1" ht="15" spans="1:1">
+      <c r="A281" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="282" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A282" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B282" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C280" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D280" s="8" t="n">
+      <c r="C282" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D282" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E282" s="9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F282" s="9" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G282" s="10">
+        <v>46212</v>
+      </c>
+      <c r="H282" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I282" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J282" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="283" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A283" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C283" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D283" s="8" t="n">
         <v>20000</v>
       </c>
-      <c r="E280" s="9" t="n">
+      <c r="E283" s="9" t="n">
         <v>0.49</v>
       </c>
-      <c r="F280" s="9" t="n">
+      <c r="F283" s="9" t="n">
         <v>9800</v>
       </c>
-      <c r="G280" s="10">
+      <c r="G283" s="10">
         <v>46212</v>
       </c>
-      <c r="H280" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I280" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J280" s="8" t="s">
+      <c r="H283" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I283" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" s="8" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="281" customHeight="1" ht="15" spans="1:5">
-      <c r="A281" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B281" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C281" s="13" t="n">
-        <v>12650</v>
-      </c>
-      <c r="D281" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E281" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282" customHeight="1" ht="15" spans="1:1">
-      <c r="A282" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="283" customHeight="1" ht="21.35" spans="1:10">
-      <c r="A283" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B283" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C283" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D283" s="8" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E283" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F283" s="9" t="n">
-        <v>9680</v>
-      </c>
-      <c r="G283" s="10">
-        <v>46216.3151041667</v>
-      </c>
-      <c r="H283" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I283" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J283" s="8" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="284" customHeight="1" ht="15" spans="1:5">
@@ -7124,7 +7136,7 @@
         <v>20</v>
       </c>
       <c r="C284" s="13" t="n">
-        <v>9680</v>
+        <v>12650</v>
       </c>
       <c r="D284" s="4" t="s">
         <v>19</v>
@@ -7135,39 +7147,39 @@
     </row>
     <row r="285" customHeight="1" ht="15" spans="1:1">
       <c r="A285" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="286" customHeight="1" ht="15" spans="1:10">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="286" customHeight="1" ht="21.35" spans="1:10">
       <c r="A286" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="C286" s="7" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D286" s="8" t="n">
-        <v>50000</v>
+        <v>22000</v>
       </c>
       <c r="E286" s="9" t="n">
-        <v>0.315</v>
+        <v>0.44</v>
       </c>
       <c r="F286" s="9" t="n">
-        <v>15750</v>
+        <v>9680</v>
       </c>
       <c r="G286" s="10">
-        <v>46198</v>
+        <v>46216.3151041667</v>
       </c>
       <c r="H286" s="8" t="n">
-        <v>32400</v>
+        <v>0</v>
       </c>
       <c r="I286" s="11" t="n">
-        <v>64.8</v>
+        <v>0</v>
       </c>
       <c r="J286" s="8" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
     </row>
     <row r="287" customHeight="1" ht="15" spans="1:5">
@@ -7178,138 +7190,138 @@
         <v>20</v>
       </c>
       <c r="C287" s="13" t="n">
+        <v>9680</v>
+      </c>
+      <c r="D287" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E287" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" customHeight="1" ht="15" spans="1:1">
+      <c r="A288" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="289" customHeight="1" ht="15" spans="1:10">
+      <c r="A289" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C289" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D289" s="8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E289" s="9" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="F289" s="9" t="n">
         <v>15750</v>
       </c>
-      <c r="D287" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E287" s="14" t="n">
+      <c r="G289" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H289" s="8" t="n">
         <v>32400</v>
       </c>
-    </row>
-    <row r="288" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A288" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289" customHeight="1" ht="15" spans="1:12">
-      <c r="A289" s="2" t="s">
+      <c r="I289" s="11" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="J289" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="290" customHeight="1" ht="15" spans="1:5">
+      <c r="A290" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B290" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C290" s="13" t="n">
+        <v>15750</v>
+      </c>
+      <c r="D290" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E290" s="14" t="n">
+        <v>32400</v>
+      </c>
+    </row>
+    <row r="291" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A291" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" customHeight="1" ht="15" spans="1:12">
+      <c r="A292" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B289" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C289" s="2" t="s">
+      <c r="B292" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C292" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D289" s="2" t="s">
+      <c r="D292" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E289" s="4" t="s">
+      <c r="E292" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F289" s="4" t="s">
+      <c r="F292" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G289" s="4" t="s">
+      <c r="G292" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H289" s="4" t="s">
+      <c r="H292" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I289" s="4" t="s">
+      <c r="I292" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J289" s="4" t="s">
+      <c r="J292" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K289" s="2" t="s">
+      <c r="K292" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L289" s="4" t="s">
+      <c r="L292" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="290" customHeight="1" ht="15" spans="1:1">
-      <c r="A290" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="291" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A291" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B291" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C291" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D291" s="8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E291" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="F291" s="9" t="n">
-        <v>2450</v>
-      </c>
-      <c r="G291" s="10">
-        <v>46209</v>
-      </c>
-      <c r="H291" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I291" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J291" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="292" customHeight="1" ht="15" spans="1:5">
-      <c r="A292" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B292" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C292" s="13" t="n">
-        <v>2450</v>
-      </c>
-      <c r="D292" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E292" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="293" customHeight="1" ht="15" spans="1:1">
       <c r="A293" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="294" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A294" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C294" s="7" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="294" customHeight="1" ht="18.35" spans="1:10">
-      <c r="A294" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B294" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C294" s="7" t="s">
-        <v>171</v>
-      </c>
       <c r="D294" s="8" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="E294" s="9" t="n">
-        <v>0.42</v>
+        <v>0.49</v>
       </c>
       <c r="F294" s="9" t="n">
-        <v>8400</v>
+        <v>2450</v>
       </c>
       <c r="G294" s="10">
-        <v>46216.7721759259</v>
+        <v>46209</v>
       </c>
       <c r="H294" s="8" t="n">
         <v>0</v>
@@ -7318,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="J294" s="8" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
     </row>
     <row r="295" customHeight="1" ht="15" spans="1:5">
@@ -7329,7 +7341,7 @@
         <v>20</v>
       </c>
       <c r="C295" s="13" t="n">
-        <v>8400</v>
+        <v>2450</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>19</v>
@@ -7340,18 +7352,18 @@
     </row>
     <row r="296" customHeight="1" ht="15" spans="1:1">
       <c r="A296" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="297" customHeight="1" ht="18.8" spans="1:10">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="297" customHeight="1" ht="18.35" spans="1:10">
       <c r="A297" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B297" s="6" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="C297" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D297" s="8" t="n">
         <v>20000</v>
@@ -7363,7 +7375,7 @@
         <v>8400</v>
       </c>
       <c r="G297" s="10">
-        <v>46212.6098726852</v>
+        <v>46216.7721759259</v>
       </c>
       <c r="H297" s="8" t="n">
         <v>0</v>
@@ -7372,7 +7384,7 @@
         <v>0</v>
       </c>
       <c r="J297" s="8" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
     </row>
     <row r="298" customHeight="1" ht="15" spans="1:5">
@@ -7394,30 +7406,30 @@
     </row>
     <row r="299" customHeight="1" ht="15" spans="1:1">
       <c r="A299" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="300" customHeight="1" ht="20.15" spans="1:10">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="300" customHeight="1" ht="18.8" spans="1:10">
       <c r="A300" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B300" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C300" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D300" s="8" t="n">
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="E300" s="9" t="n">
         <v>0.42</v>
       </c>
       <c r="F300" s="9" t="n">
-        <v>33600</v>
+        <v>8400</v>
       </c>
       <c r="G300" s="10">
-        <v>46212.6038541667</v>
+        <v>46212.6098726852</v>
       </c>
       <c r="H300" s="8" t="n">
         <v>0</v>
@@ -7437,138 +7449,138 @@
         <v>20</v>
       </c>
       <c r="C301" s="13" t="n">
+        <v>8400</v>
+      </c>
+      <c r="D301" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E301" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" customHeight="1" ht="15" spans="1:1">
+      <c r="A302" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="303" customHeight="1" ht="20.15" spans="1:10">
+      <c r="A303" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C303" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D303" s="8" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E303" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F303" s="9" t="n">
         <v>33600</v>
       </c>
-      <c r="D301" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E301" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A302" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303" customHeight="1" ht="15" spans="1:12">
-      <c r="A303" s="2" t="s">
+      <c r="G303" s="10">
+        <v>46212.6038541667</v>
+      </c>
+      <c r="H303" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I303" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J303" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="304" customHeight="1" ht="15" spans="1:5">
+      <c r="A304" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B304" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C304" s="13" t="n">
+        <v>33600</v>
+      </c>
+      <c r="D304" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E304" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A305" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" customHeight="1" ht="15" spans="1:12">
+      <c r="A306" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B303" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C303" s="2" t="s">
+      <c r="B306" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C306" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D303" s="2" t="s">
+      <c r="D306" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E303" s="4" t="s">
+      <c r="E306" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F303" s="4" t="s">
+      <c r="F306" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G303" s="4" t="s">
+      <c r="G306" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H303" s="4" t="s">
+      <c r="H306" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I303" s="4" t="s">
+      <c r="I306" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J303" s="4" t="s">
+      <c r="J306" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K303" s="2" t="s">
+      <c r="K306" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L303" s="4" t="s">
+      <c r="L306" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="304" customHeight="1" ht="15" spans="1:1">
-      <c r="A304" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="305" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A305" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B305" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C305" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D305" s="8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E305" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="F305" s="9" t="n">
-        <v>2450</v>
-      </c>
-      <c r="G305" s="10">
-        <v>46209</v>
-      </c>
-      <c r="H305" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I305" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J305" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="306" customHeight="1" ht="15" spans="1:5">
-      <c r="A306" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B306" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C306" s="13" t="n">
-        <v>2450</v>
-      </c>
-      <c r="D306" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E306" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="307" customHeight="1" ht="15" spans="1:1">
       <c r="A307" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="308" customHeight="1" ht="18.35" spans="1:10">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="308" customHeight="1" ht="20.4" spans="1:10">
       <c r="A308" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B308" s="6" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="C308" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D308" s="8" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="E308" s="9" t="n">
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="F308" s="9" t="n">
-        <v>900</v>
+        <v>2450</v>
       </c>
       <c r="G308" s="10">
-        <v>46216.7521180556</v>
+        <v>46209</v>
       </c>
       <c r="H308" s="8" t="n">
         <v>0</v>
@@ -7577,7 +7589,7 @@
         <v>0</v>
       </c>
       <c r="J308" s="8" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="309" customHeight="1" ht="15" spans="1:5">
@@ -7588,277 +7600,277 @@
         <v>20</v>
       </c>
       <c r="C309" s="13" t="n">
+        <v>2450</v>
+      </c>
+      <c r="D309" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E309" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" customHeight="1" ht="15" spans="1:1">
+      <c r="A310" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="311" customHeight="1" ht="18.35" spans="1:10">
+      <c r="A311" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C311" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D311" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E311" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F311" s="9" t="n">
         <v>900</v>
       </c>
-      <c r="D309" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E309" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A310" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" customHeight="1" ht="15" spans="1:12">
-      <c r="A311" s="2" t="s">
+      <c r="G311" s="10">
+        <v>46216.7521180556</v>
+      </c>
+      <c r="H311" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I311" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="312" customHeight="1" ht="15" spans="1:5">
+      <c r="A312" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B312" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C312" s="13" t="n">
+        <v>900</v>
+      </c>
+      <c r="D312" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E312" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" customHeight="1" ht="15" spans="1:1">
+      <c r="A313" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="314" customHeight="1" ht="15" spans="1:10">
+      <c r="A314" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C314" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D314" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E314" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F314" s="9" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G314" s="10">
+        <v>46217</v>
+      </c>
+      <c r="H314" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I314" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J314" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="315" customHeight="1" ht="15" spans="1:5">
+      <c r="A315" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B315" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C315" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D315" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E315" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A316" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" customHeight="1" ht="15" spans="1:12">
+      <c r="A317" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B311" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C311" s="2" t="s">
+      <c r="B317" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C317" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D311" s="2" t="s">
+      <c r="D317" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E311" s="4" t="s">
+      <c r="E317" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F311" s="4" t="s">
+      <c r="F317" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G311" s="4" t="s">
+      <c r="G317" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H311" s="4" t="s">
+      <c r="H317" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I311" s="4" t="s">
+      <c r="I317" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J311" s="4" t="s">
+      <c r="J317" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K311" s="2" t="s">
+      <c r="K317" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L311" s="4" t="s">
+      <c r="L317" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="312" customHeight="1" ht="15" spans="1:1">
-      <c r="A312" s="2" t="s">
+    <row r="318" customHeight="1" ht="15" spans="1:1">
+      <c r="A318" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="313" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A313" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B313" s="6" t="s">
+    <row r="319" customHeight="1" ht="20.4" spans="1:10">
+      <c r="A319" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B319" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C313" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D313" s="8" t="n">
+      <c r="C319" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D319" s="8" t="n">
         <v>1008</v>
       </c>
-      <c r="E313" s="9" t="n">
+      <c r="E319" s="9" t="n">
         <v>12.9</v>
       </c>
-      <c r="F313" s="9" t="n">
+      <c r="F319" s="9" t="n">
         <v>13003.2</v>
       </c>
-      <c r="G313" s="10">
+      <c r="G319" s="10">
         <v>46216.3893171296</v>
       </c>
-      <c r="H313" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I313" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J313" s="8" t="s">
+      <c r="H319" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I319" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J319" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="314" customHeight="1" ht="15" spans="1:5">
-      <c r="A314" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B314" s="12" t="s">
+    <row r="320" customHeight="1" ht="15" spans="1:5">
+      <c r="A320" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B320" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C314" s="13" t="n">
+      <c r="C320" s="13" t="n">
         <v>13003.2</v>
       </c>
-      <c r="D314" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E314" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A315" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316" customHeight="1" ht="15" spans="1:12">
-      <c r="A316" s="2" t="s">
+      <c r="D320" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E320" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A321" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" customHeight="1" ht="15" spans="1:12">
+      <c r="A322" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B316" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C316" s="2" t="s">
+      <c r="B322" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C322" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D316" s="2" t="s">
+      <c r="D322" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E316" s="4" t="s">
+      <c r="E322" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F316" s="4" t="s">
+      <c r="F322" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G316" s="4" t="s">
+      <c r="G322" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H316" s="4" t="s">
+      <c r="H322" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I316" s="4" t="s">
+      <c r="I322" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J316" s="4" t="s">
+      <c r="J322" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K316" s="2" t="s">
+      <c r="K322" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L316" s="4" t="s">
+      <c r="L322" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="317" customHeight="1" ht="15" spans="1:1">
-      <c r="A317" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="318" customHeight="1" ht="20.4" spans="1:10">
-      <c r="A318" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B318" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C318" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D318" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="E318" s="9" t="n">
-        <v>17.91</v>
-      </c>
-      <c r="F318" s="9" t="n">
-        <v>358.2</v>
-      </c>
-      <c r="G318" s="10">
-        <v>46209</v>
-      </c>
-      <c r="H318" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I318" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J318" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="319" customHeight="1" ht="15" spans="1:5">
-      <c r="A319" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B319" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C319" s="13" t="n">
-        <v>358.2</v>
-      </c>
-      <c r="D319" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E319" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320" customHeight="1" ht="15" spans="1:1">
-      <c r="A320" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="321" customHeight="1" ht="15" spans="1:10">
-      <c r="A321" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B321" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C321" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D321" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="E321" s="9" t="n">
-        <v>18.29</v>
-      </c>
-      <c r="F321" s="9" t="n">
-        <v>2194.8</v>
-      </c>
-      <c r="G321" s="10">
-        <v>46196.6411111111</v>
-      </c>
-      <c r="H321" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I321" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J321" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="322" customHeight="1" ht="15" spans="1:5">
-      <c r="A322" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B322" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C322" s="13" t="n">
-        <v>2194.8</v>
-      </c>
-      <c r="D322" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E322" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="323" customHeight="1" ht="15" spans="1:1">
       <c r="A323" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="324" customHeight="1" ht="19.3" spans="1:10">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="324" customHeight="1" ht="20.4" spans="1:10">
       <c r="A324" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B324" s="6" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="C324" s="7" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D324" s="8" t="n">
         <v>20</v>
@@ -7899,155 +7911,155 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A326" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" customHeight="1" ht="15" spans="1:12">
-      <c r="A327" s="2" t="s">
+    <row r="326" customHeight="1" ht="15" spans="1:1">
+      <c r="A326" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="327" customHeight="1" ht="15" spans="1:10">
+      <c r="A327" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B327" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C327" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D327" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="E327" s="9" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="F327" s="9" t="n">
+        <v>2194.8</v>
+      </c>
+      <c r="G327" s="10">
+        <v>46196.6411111111</v>
+      </c>
+      <c r="H327" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I327" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J327" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="328" customHeight="1" ht="15" spans="1:5">
+      <c r="A328" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B328" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C328" s="13" t="n">
+        <v>2194.8</v>
+      </c>
+      <c r="D328" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E328" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" customHeight="1" ht="15" spans="1:1">
+      <c r="A329" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="330" customHeight="1" ht="19.3" spans="1:10">
+      <c r="A330" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B330" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C330" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D330" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E330" s="9" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="F330" s="9" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="G330" s="10">
+        <v>46209</v>
+      </c>
+      <c r="H330" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I330" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="331" customHeight="1" ht="15" spans="1:5">
+      <c r="A331" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B331" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C331" s="13" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="D331" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E331" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A332" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" customHeight="1" ht="15" spans="1:12">
+      <c r="A333" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B327" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C327" s="2" t="s">
+      <c r="B333" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C333" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D327" s="2" t="s">
+      <c r="D333" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E327" s="4" t="s">
+      <c r="E333" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F327" s="4" t="s">
+      <c r="F333" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G327" s="4" t="s">
+      <c r="G333" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H327" s="4" t="s">
+      <c r="H333" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I327" s="4" t="s">
+      <c r="I333" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J327" s="4" t="s">
+      <c r="J333" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K327" s="2" t="s">
+      <c r="K333" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L327" s="4" t="s">
+      <c r="L333" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="328" customHeight="1" ht="15" spans="1:1">
-      <c r="A328" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="329" customHeight="1" ht="15" spans="1:10">
-      <c r="A329" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B329" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="C329" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D329" s="8" t="n">
-        <v>8028</v>
-      </c>
-      <c r="E329" s="9" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="F329" s="9" t="n">
-        <v>96255.72</v>
-      </c>
-      <c r="G329" s="10">
-        <v>46167</v>
-      </c>
-      <c r="H329" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I329" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J329" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="330" customHeight="1" ht="15" spans="1:5">
-      <c r="A330" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B330" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C330" s="13" t="n">
-        <v>96255.72</v>
-      </c>
-      <c r="D330" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E330" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" customHeight="1" ht="15" spans="1:1">
-      <c r="A331" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="332" customHeight="1" ht="18.8" spans="1:10">
-      <c r="A332" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B332" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C332" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D332" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="E332" s="9" t="n">
-        <v>116.04</v>
-      </c>
-      <c r="F332" s="9" t="n">
-        <v>10443.6</v>
-      </c>
-      <c r="G332" s="10">
-        <v>46212</v>
-      </c>
-      <c r="H332" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I332" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J332" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="333" customHeight="1" ht="15" spans="1:5">
-      <c r="A333" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B333" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C333" s="13" t="n">
-        <v>10443.6</v>
-      </c>
-      <c r="D333" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E333" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="334" customHeight="1" ht="15" spans="1:1">
@@ -8055,7 +8067,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="335" customHeight="1" ht="38.75" spans="1:10">
+    <row r="335" customHeight="1" ht="15" spans="1:10">
       <c r="A335" s="5" t="s">
         <v>14</v>
       </c>
@@ -8066,22 +8078,22 @@
         <v>184</v>
       </c>
       <c r="D335" s="8" t="n">
-        <v>24000</v>
+        <v>8028</v>
       </c>
       <c r="E335" s="9" t="n">
-        <v>13</v>
+        <v>11.99</v>
       </c>
       <c r="F335" s="9" t="n">
-        <v>312000</v>
+        <v>96255.72</v>
       </c>
       <c r="G335" s="10">
-        <v>46100</v>
+        <v>46167</v>
       </c>
       <c r="H335" s="8" t="n">
-        <v>18900</v>
+        <v>0</v>
       </c>
       <c r="I335" s="11" t="n">
-        <v>78.75</v>
+        <v>0</v>
       </c>
       <c r="J335" s="8" t="s">
         <v>23</v>
@@ -8095,41 +8107,41 @@
         <v>20</v>
       </c>
       <c r="C336" s="13" t="n">
-        <v>312000</v>
+        <v>96255.72</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E336" s="14" t="n">
-        <v>18900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337" customHeight="1" ht="15" spans="1:1">
       <c r="A337" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="338" customHeight="1" ht="18.8" spans="1:10">
+      <c r="A338" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B338" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C338" s="7" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="338" customHeight="1" ht="18.7" spans="1:10">
-      <c r="A338" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B338" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C338" s="7" t="s">
-        <v>187</v>
-      </c>
       <c r="D338" s="8" t="n">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="E338" s="9" t="n">
-        <v>15.33</v>
+        <v>116.04</v>
       </c>
       <c r="F338" s="9" t="n">
-        <v>9198</v>
+        <v>10443.6</v>
       </c>
       <c r="G338" s="10">
-        <v>46213.4944444444</v>
+        <v>46212</v>
       </c>
       <c r="H338" s="8" t="n">
         <v>0</v>
@@ -8138,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="J338" s="8" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="339" customHeight="1" ht="15" spans="1:5">
@@ -8149,180 +8161,180 @@
         <v>20</v>
       </c>
       <c r="C339" s="13" t="n">
+        <v>10443.6</v>
+      </c>
+      <c r="D339" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E339" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" customHeight="1" ht="15" spans="1:1">
+      <c r="A340" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="341" customHeight="1" ht="38.75" spans="1:10">
+      <c r="A341" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B341" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C341" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D341" s="8" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E341" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F341" s="9" t="n">
+        <v>312000</v>
+      </c>
+      <c r="G341" s="10">
+        <v>46100</v>
+      </c>
+      <c r="H341" s="8" t="n">
+        <v>18900</v>
+      </c>
+      <c r="I341" s="11" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="J341" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="342" customHeight="1" ht="15" spans="1:5">
+      <c r="A342" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B342" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C342" s="13" t="n">
+        <v>312000</v>
+      </c>
+      <c r="D342" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E342" s="14" t="n">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="343" customHeight="1" ht="15" spans="1:1">
+      <c r="A343" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="344" customHeight="1" ht="18.7" spans="1:10">
+      <c r="A344" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B344" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C344" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D344" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="E344" s="9" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="F344" s="9" t="n">
         <v>9198</v>
       </c>
-      <c r="D339" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E339" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="340" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A340" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341" customHeight="1" ht="15" spans="1:12">
-      <c r="A341" s="2" t="s">
+      <c r="G344" s="10">
+        <v>46213.4944444444</v>
+      </c>
+      <c r="H344" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I344" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J344" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="345" customHeight="1" ht="15" spans="1:5">
+      <c r="A345" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B345" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C345" s="13" t="n">
+        <v>9198</v>
+      </c>
+      <c r="D345" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E345" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" customHeight="1" ht="77.35" spans="1:1">
+      <c r="A346" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" customHeight="1" ht="15" spans="1:12">
+      <c r="A347" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B341" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C341" s="2" t="s">
+      <c r="B347" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C347" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D341" s="2" t="s">
+      <c r="D347" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E341" s="4" t="s">
+      <c r="E347" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F341" s="4" t="s">
+      <c r="F347" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G341" s="4" t="s">
+      <c r="G347" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H341" s="4" t="s">
+      <c r="H347" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I341" s="4" t="s">
+      <c r="I347" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J341" s="4" t="s">
+      <c r="J347" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K341" s="2" t="s">
+      <c r="K347" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L341" s="4" t="s">
+      <c r="L347" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="342" customHeight="1" ht="15" spans="1:1">
-      <c r="A342" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="343" customHeight="1" ht="30.35" spans="1:10">
-      <c r="A343" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B343" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C343" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D343" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="E343" s="9" t="n">
-        <v>17.91</v>
-      </c>
-      <c r="F343" s="9" t="n">
-        <v>716.4</v>
-      </c>
-      <c r="G343" s="10">
-        <v>46209</v>
-      </c>
-      <c r="H343" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I343" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J343" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="344" customHeight="1" ht="15" spans="1:5">
-      <c r="A344" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B344" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C344" s="13" t="n">
-        <v>716.4</v>
-      </c>
-      <c r="D344" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E344" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345" customHeight="1" ht="15" spans="1:1">
-      <c r="A345" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="346" customHeight="1" ht="15" spans="1:10">
-      <c r="A346" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B346" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C346" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D346" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E346" s="9" t="n">
-        <v>7.3303</v>
-      </c>
-      <c r="F346" s="9" t="n">
-        <v>21990.9</v>
-      </c>
-      <c r="G346" s="10">
-        <v>46210.3934606481</v>
-      </c>
-      <c r="H346" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I346" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J346" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="347" customHeight="1" ht="15" spans="1:5">
-      <c r="A347" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B347" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C347" s="13" t="n">
-        <v>21990.9</v>
-      </c>
-      <c r="D347" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E347" s="14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="348" customHeight="1" ht="15" spans="1:1">
       <c r="A348" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="349" customHeight="1" ht="29.6" spans="1:10">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="349" customHeight="1" ht="30.35" spans="1:10">
       <c r="A349" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B349" s="6" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="C349" s="7" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D349" s="8" t="n">
         <v>40</v>
@@ -8363,183 +8375,183 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" customHeight="1" ht="77.35" spans="1:1">
-      <c r="A351" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352" customHeight="1" ht="15" spans="1:12">
-      <c r="A352" s="2" t="s">
+    <row r="351" customHeight="1" ht="15" spans="1:1">
+      <c r="A351" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="352" customHeight="1" ht="15" spans="1:10">
+      <c r="A352" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B352" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C352" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D352" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E352" s="9" t="n">
+        <v>7.3303</v>
+      </c>
+      <c r="F352" s="9" t="n">
+        <v>21990.9</v>
+      </c>
+      <c r="G352" s="10">
+        <v>46210.3934606481</v>
+      </c>
+      <c r="H352" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I352" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J352" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="353" customHeight="1" ht="15" spans="1:5">
+      <c r="A353" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B353" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C353" s="13" t="n">
+        <v>21990.9</v>
+      </c>
+      <c r="D353" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E353" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" customHeight="1" ht="15" spans="1:1">
+      <c r="A354" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="355" customHeight="1" ht="29.6" spans="1:10">
+      <c r="A355" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B355" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C355" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D355" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E355" s="9" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="F355" s="9" t="n">
+        <v>716.4</v>
+      </c>
+      <c r="G355" s="10">
+        <v>46209</v>
+      </c>
+      <c r="H355" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I355" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J355" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="356" customHeight="1" ht="15" spans="1:5">
+      <c r="A356" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B356" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C356" s="13" t="n">
+        <v>716.4</v>
+      </c>
+      <c r="D356" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E356" s="14" t="n">
+        <v>0</v>
+